--- a/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
+++ b/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
   <si>
     <t>SampleId</t>
   </si>
@@ -125,6 +125,15 @@
     <t>10f94b5e201f7be986454ceb7acc67c2</t>
   </si>
   <si>
+    <t>118021893d882d58d0031c52a6c1f5f5</t>
+  </si>
+  <si>
+    <t>3PT</t>
+  </si>
+  <si>
+    <t>Gray</t>
+  </si>
+  <si>
     <t>12a4de0ce45c9f08d5016c60fa4951aa</t>
   </si>
   <si>
@@ -152,15 +161,15 @@
     <t>1a3eb2f5a89a586bd848cae3565cee56</t>
   </si>
   <si>
-    <t>3PT</t>
-  </si>
-  <si>
     <t>1a4fa710efe5fc410beaedb13bf20e90</t>
   </si>
   <si>
     <t>1d65cdea633ddda5700f4b0348ade2ae</t>
   </si>
   <si>
+    <t>1f4b8f067d145565d8dfa7ed510c61be</t>
+  </si>
+  <si>
     <t>2156c1baa4c60ec37885fb9c845d6d07</t>
   </si>
   <si>
@@ -206,15 +215,15 @@
     <t>371684847a27dcde9af7569765d2e637</t>
   </si>
   <si>
+    <t>37da418868c24078248f53d1e6fdda8a</t>
+  </si>
+  <si>
     <t>38a05ab2fc788d45aaa7b53b09c9e5f9</t>
   </si>
   <si>
     <t>38cf319919d11ed79510034a9d16feb9</t>
   </si>
   <si>
-    <t>Gray</t>
-  </si>
-  <si>
     <t>39245fadc0ea2b60346d778f6081be8f</t>
   </si>
   <si>
@@ -284,9 +293,18 @@
     <t>581e1670e651ce62ec250cbc26f8c4ff</t>
   </si>
   <si>
+    <t>582094a80243cb924dbe526e4826bdca</t>
+  </si>
+  <si>
     <t>5848db1a4b0d5c8b6adc8bcbaaf943c0</t>
   </si>
   <si>
+    <t>5d1e09da3d396678ddbaf942afa46a35</t>
+  </si>
+  <si>
+    <t>Debugging</t>
+  </si>
+  <si>
     <t>5d2984f8b0ed67c2f8be021cb9339718</t>
   </si>
   <si>
@@ -308,6 +326,9 @@
     <t>6531181dcee4ebbaf7721b3c29c30c23</t>
   </si>
   <si>
+    <t>65ccdcfc0b9b14c0963b78b0641d3489</t>
+  </si>
+  <si>
     <t>672501fb25ef1fea56c352f1ede7945c</t>
   </si>
   <si>
@@ -380,6 +401,9 @@
     <t>885bc07fe6d505316d2c94dfcce058aa</t>
   </si>
   <si>
+    <t>88fc6837345eb4c3adf2e536120f47c9</t>
+  </si>
+  <si>
     <t>8aceb4cd728995daecc5c71b1397461b</t>
   </si>
   <si>
@@ -419,6 +443,9 @@
     <t>9b9c5e8d22f20ad9211d4a4de2104d34</t>
   </si>
   <si>
+    <t>9c61465dfb96892f79670ca75587dff7</t>
+  </si>
+  <si>
     <t>a3555d9588d44ba18a23a4cdf226e9a0</t>
   </si>
   <si>
@@ -446,6 +473,9 @@
     <t>babc7bc2bd8061ed88d7db1ddfeefcae</t>
   </si>
   <si>
+    <t>bae68a3b48fc27fa4709c58e5b681680</t>
+  </si>
+  <si>
     <t>bd913d121c812f22ab077a5252c19a88</t>
   </si>
   <si>
@@ -473,6 +503,9 @@
     <t>c9e0ca7cfd3257a9da6ab9f38d364ad4</t>
   </si>
   <si>
+    <t>ccd8195b4713fe3ae97eb579f397251e</t>
+  </si>
+  <si>
     <t>d05daff23820586a061dfd35505697cb</t>
   </si>
   <si>
@@ -482,6 +515,12 @@
     <t>d0e4a2dbf76e4bc632d85a7556d6df80</t>
   </si>
   <si>
+    <t>d439ecff83eab159061c8ee5e67269a1</t>
+  </si>
+  <si>
+    <t>d4d950756ef6ef62223c653fb985b0a7</t>
+  </si>
+  <si>
     <t>d4e07621062d9aba79dd62eee4167f07</t>
   </si>
   <si>
@@ -494,9 +533,15 @@
     <t>d81c23f65bde5549bbccd1fec0b531b5</t>
   </si>
   <si>
+    <t>d989df69cacd8f363958642d0774b56c</t>
+  </si>
+  <si>
     <t>d99722912178973c6bf755aff5deff26</t>
   </si>
   <si>
+    <t>dbc806190a8fc54f8bce0578dd24030b</t>
+  </si>
+  <si>
     <t>dbf62b9d0b0c3c05f3dce3a83e091945</t>
   </si>
   <si>
@@ -539,6 +584,9 @@
     <t>eb4cf3ff356f969d8223279d569e5c54</t>
   </si>
   <si>
+    <t>ee2cdfec9a1043b97573e075481e1f60</t>
+  </si>
+  <si>
     <t>ee309744100bdf9b07f7bf8fe2770b88</t>
   </si>
   <si>
@@ -564,6 +612,9 @@
   </si>
   <si>
     <t>faec9937fecd8466b7ac7ad83bd81b69</t>
+  </si>
+  <si>
+    <t>fd06cf7b15df3b08e2815a28c30fe7f4</t>
   </si>
   <si>
     <t>fd6b96d119097a07f75197e7a5e97a9f</t>
@@ -620,8 +671,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AicsGlobal_Classifications_TimeWindows" displayName="AicsGlobal_Classifications_TimeWindows" ref="A1:V156" headerRowCount="1">
-  <autoFilter ref="A1:V156"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AicsGlobal_Classifications_TimeWindows" displayName="AicsGlobal_Classifications_TimeWindows" ref="A1:V172" headerRowCount="1">
+  <autoFilter ref="A1:V172"/>
   <tableColumns count="22">
     <tableColumn id="1" name="SampleId"/>
     <tableColumn id="2" name="SIGDetection"/>
@@ -652,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:V156"/>
+  <dimension ref="A1:V172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.540952682495117" customWidth="1"/>
@@ -746,7 +797,7 @@
         <v>46204.34583333333</v>
       </c>
       <c r="F2" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>24</v>
@@ -814,7 +865,7 @@
         <v>46207.15827546296</v>
       </c>
       <c r="F3" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>24</v>
@@ -882,7 +933,7 @@
         <v>46200.30415509259</v>
       </c>
       <c r="F4" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>24</v>
@@ -950,7 +1001,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F5" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>30</v>
@@ -1018,7 +1069,7 @@
         <v>46198.75680555555</v>
       </c>
       <c r="F6" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>30</v>
@@ -1086,7 +1137,7 @@
         <v>46200.02773148148</v>
       </c>
       <c r="F7" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>24</v>
@@ -1098,7 +1149,7 @@
         <v>24</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K7" s="0" t="s">
         <v>25</v>
@@ -1118,8 +1169,8 @@
       <c r="P7" s="0">
         <v>0</v>
       </c>
-      <c r="Q7" s="0" t="s">
-        <v>25</v>
+      <c r="Q7" s="0">
+        <v>0</v>
       </c>
       <c r="R7" s="0" t="s">
         <v>25</v>
@@ -1154,7 +1205,7 @@
         <v>46200.57623842593</v>
       </c>
       <c r="F8" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>24</v>
@@ -1222,7 +1273,7 @@
         <v>46198.764027777775</v>
       </c>
       <c r="F9" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>30</v>
@@ -1290,7 +1341,7 @@
         <v>46198.18491898148</v>
       </c>
       <c r="F10" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>24</v>
@@ -1346,28 +1397,28 @@
         <v>37</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C11" s="0">
-        <v>2108</v>
+        <v>355</v>
       </c>
       <c r="D11" s="1">
-        <v>46200.779074074075</v>
+        <v>46203.81460648148</v>
       </c>
       <c r="E11" s="1">
-        <v>46201.33733796296</v>
+        <v>46203.81460648148</v>
       </c>
       <c r="F11" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>25</v>
@@ -1385,10 +1436,10 @@
         <v>25</v>
       </c>
       <c r="O11" s="0">
-        <v>1</v>
-      </c>
-      <c r="P11" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P11" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q11" s="0" t="s">
         <v>25</v>
@@ -1406,27 +1457,27 @@
         <v>25</v>
       </c>
       <c r="V11" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="0">
-        <v>2046</v>
+        <v>2108</v>
       </c>
       <c r="D12" s="1">
-        <v>46202.74914351852</v>
+        <v>46200.779074074075</v>
       </c>
       <c r="E12" s="1">
-        <v>46203.71907407408</v>
+        <v>46201.33733796296</v>
       </c>
       <c r="F12" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>24</v>
@@ -1453,10 +1504,10 @@
         <v>25</v>
       </c>
       <c r="O12" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="0" t="s">
         <v>25</v>
@@ -1479,34 +1530,34 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C13" s="0">
-        <v>0</v>
+        <v>2046</v>
       </c>
       <c r="D13" s="1">
-        <v>46195.59105324074</v>
+        <v>46202.74914351852</v>
       </c>
       <c r="E13" s="1">
-        <v>46195.59105324074</v>
+        <v>46203.71907407408</v>
       </c>
       <c r="F13" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K13" s="0" t="s">
         <v>25</v>
@@ -1521,13 +1572,13 @@
         <v>25</v>
       </c>
       <c r="O13" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="0">
         <v>0</v>
       </c>
-      <c r="Q13" s="0">
-        <v>1</v>
+      <c r="Q13" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R13" s="0" t="s">
         <v>25</v>
@@ -1542,39 +1593,39 @@
         <v>25</v>
       </c>
       <c r="V13" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C14" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>46200.10091435185</v>
+        <v>46195.59105324074</v>
       </c>
       <c r="E14" s="1">
-        <v>46201.06361111111</v>
+        <v>46195.59105324074</v>
       </c>
       <c r="F14" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K14" s="0" t="s">
         <v>25</v>
@@ -1589,13 +1640,13 @@
         <v>25</v>
       </c>
       <c r="O14" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="0">
+        <v>1</v>
       </c>
       <c r="R14" s="0" t="s">
         <v>25</v>
@@ -1610,36 +1661,36 @@
         <v>25</v>
       </c>
       <c r="V14" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C15" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D15" s="1">
-        <v>46197.83574074074</v>
+        <v>46200.10091435185</v>
       </c>
       <c r="E15" s="1">
-        <v>46197.83574074074</v>
+        <v>46201.06361111111</v>
       </c>
       <c r="F15" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>25</v>
@@ -1657,10 +1708,10 @@
         <v>25</v>
       </c>
       <c r="O15" s="0">
-        <v>1</v>
-      </c>
-      <c r="P15" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P15" s="0">
+        <v>1</v>
       </c>
       <c r="Q15" s="0" t="s">
         <v>25</v>
@@ -1678,27 +1729,27 @@
         <v>25</v>
       </c>
       <c r="V15" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C16" s="0">
-        <v>700160</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1">
-        <v>46198.5140625</v>
+        <v>46197.83574074074</v>
       </c>
       <c r="E16" s="1">
-        <v>46198.5140625</v>
+        <v>46197.83574074074</v>
       </c>
       <c r="F16" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>30</v>
@@ -1751,31 +1802,31 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C17" s="0">
-        <v>2108</v>
+        <v>700160</v>
       </c>
       <c r="D17" s="1">
-        <v>46200.81953703704</v>
+        <v>46198.5140625</v>
       </c>
       <c r="E17" s="1">
-        <v>46202.38591435185</v>
+        <v>46198.5140625</v>
       </c>
       <c r="F17" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>25</v>
@@ -1796,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="0" t="s">
         <v>25</v>
@@ -1814,36 +1865,36 @@
         <v>25</v>
       </c>
       <c r="V17" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C18" s="0">
-        <v>344</v>
+        <v>2108</v>
       </c>
       <c r="D18" s="1">
-        <v>46203.665925925925</v>
+        <v>46200.81953703704</v>
       </c>
       <c r="E18" s="1">
-        <v>46203.665925925925</v>
+        <v>46202.38591435185</v>
       </c>
       <c r="F18" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>25</v>
@@ -1863,8 +1914,8 @@
       <c r="O18" s="0">
         <v>1</v>
       </c>
-      <c r="P18" s="0" t="s">
-        <v>25</v>
+      <c r="P18" s="0">
+        <v>1</v>
       </c>
       <c r="Q18" s="0" t="s">
         <v>25</v>
@@ -1882,33 +1933,33 @@
         <v>25</v>
       </c>
       <c r="V18" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C19" s="0">
-        <v>13108</v>
+        <v>344</v>
       </c>
       <c r="D19" s="1">
-        <v>46204.75709490741</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="E19" s="1">
-        <v>46205.25707175926</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="F19" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I19" s="0" t="s">
         <v>25</v>
@@ -1950,27 +2001,27 @@
         <v>25</v>
       </c>
       <c r="V19" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C20" s="0">
-        <v>2025</v>
+        <v>13108</v>
       </c>
       <c r="D20" s="1">
-        <v>46202.91679398148</v>
+        <v>46204.75709490741</v>
       </c>
       <c r="E20" s="1">
-        <v>46204.23569444445</v>
+        <v>46205.25707175926</v>
       </c>
       <c r="F20" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G20" s="0" t="s">
         <v>24</v>
@@ -1997,7 +2048,7 @@
         <v>25</v>
       </c>
       <c r="O20" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="0">
         <v>0</v>
@@ -2023,31 +2074,31 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C21" s="0">
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="D21" s="1">
-        <v>46198.763715277775</v>
+        <v>46202.91679398148</v>
       </c>
       <c r="E21" s="1">
-        <v>46198.763715277775</v>
+        <v>46204.23569444445</v>
       </c>
       <c r="F21" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J21" s="0" t="s">
         <v>25</v>
@@ -2065,10 +2116,10 @@
         <v>25</v>
       </c>
       <c r="O21" s="0">
-        <v>1</v>
-      </c>
-      <c r="P21" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P21" s="0">
+        <v>0</v>
       </c>
       <c r="Q21" s="0" t="s">
         <v>25</v>
@@ -2086,33 +2137,33 @@
         <v>25</v>
       </c>
       <c r="V21" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="0">
-        <v>2108</v>
+        <v>2521</v>
       </c>
       <c r="D22" s="1">
-        <v>46205.502962962964</v>
+        <v>46203.711377314816</v>
       </c>
       <c r="E22" s="1">
-        <v>46205.502962962964</v>
+        <v>46206.293020833335</v>
       </c>
       <c r="F22" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I22" s="0" t="s">
         <v>25</v>
@@ -2133,7 +2184,7 @@
         <v>25</v>
       </c>
       <c r="O22" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="0" t="s">
         <v>25</v>
@@ -2154,12 +2205,12 @@
         <v>25</v>
       </c>
       <c r="V22" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>29</v>
@@ -2168,13 +2219,13 @@
         <v>0</v>
       </c>
       <c r="D23" s="1">
-        <v>46198.06826388889</v>
+        <v>46198.763715277775</v>
       </c>
       <c r="E23" s="1">
-        <v>46200.67046296296</v>
+        <v>46198.763715277775</v>
       </c>
       <c r="F23" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G23" s="0" t="s">
         <v>30</v>
@@ -2227,7 +2278,7 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>23</v>
@@ -2236,13 +2287,13 @@
         <v>2108</v>
       </c>
       <c r="D24" s="1">
-        <v>46199.574282407404</v>
+        <v>46205.502962962964</v>
       </c>
       <c r="E24" s="1">
-        <v>46199.574282407404</v>
+        <v>46205.502962962964</v>
       </c>
       <c r="F24" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>24</v>
@@ -2251,7 +2302,7 @@
         <v>24</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J24" s="0" t="s">
         <v>25</v>
@@ -2269,10 +2320,10 @@
         <v>25</v>
       </c>
       <c r="O24" s="0">
-        <v>1</v>
-      </c>
-      <c r="P24" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P24" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q24" s="0" t="s">
         <v>25</v>
@@ -2295,7 +2346,7 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>29</v>
@@ -2304,13 +2355,13 @@
         <v>0</v>
       </c>
       <c r="D25" s="1">
-        <v>46198.758518518516</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="E25" s="1">
-        <v>46198.758518518516</v>
+        <v>46200.67046296296</v>
       </c>
       <c r="F25" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G25" s="0" t="s">
         <v>30</v>
@@ -2319,7 +2370,7 @@
         <v>30</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>25</v>
@@ -2339,8 +2390,8 @@
       <c r="O25" s="0">
         <v>1</v>
       </c>
-      <c r="P25" s="0" t="s">
-        <v>25</v>
+      <c r="P25" s="0">
+        <v>0</v>
       </c>
       <c r="Q25" s="0" t="s">
         <v>25</v>
@@ -2363,22 +2414,22 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C26" s="0">
-        <v>13108</v>
+        <v>2108</v>
       </c>
       <c r="D26" s="1">
-        <v>46197.86509259259</v>
+        <v>46199.574282407404</v>
       </c>
       <c r="E26" s="1">
-        <v>46199.20893518518</v>
+        <v>46199.574282407404</v>
       </c>
       <c r="F26" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>24</v>
@@ -2431,7 +2482,7 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>29</v>
@@ -2440,13 +2491,13 @@
         <v>0</v>
       </c>
       <c r="D27" s="1">
-        <v>46198.76384259259</v>
+        <v>46198.758518518516</v>
       </c>
       <c r="E27" s="1">
-        <v>46198.76384259259</v>
+        <v>46198.758518518516</v>
       </c>
       <c r="F27" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G27" s="0" t="s">
         <v>30</v>
@@ -2499,22 +2550,22 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C28" s="0">
-        <v>2046</v>
+        <v>13108</v>
       </c>
       <c r="D28" s="1">
-        <v>46207.86888888889</v>
+        <v>46197.86509259259</v>
       </c>
       <c r="E28" s="1">
-        <v>46207.98546296296</v>
+        <v>46199.20893518518</v>
       </c>
       <c r="F28" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>24</v>
@@ -2523,10 +2574,10 @@
         <v>24</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K28" s="0" t="s">
         <v>25</v>
@@ -2541,13 +2592,13 @@
         <v>25</v>
       </c>
       <c r="O28" s="0">
-        <v>0</v>
-      </c>
-      <c r="P28" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q28" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P28" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="0">
+        <v>0</v>
       </c>
       <c r="R28" s="0" t="s">
         <v>25</v>
@@ -2567,7 +2618,7 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>29</v>
@@ -2576,13 +2627,13 @@
         <v>0</v>
       </c>
       <c r="D29" s="1">
-        <v>46198.758414351854</v>
+        <v>46198.76384259259</v>
       </c>
       <c r="E29" s="1">
-        <v>46198.758414351854</v>
+        <v>46198.76384259259</v>
       </c>
       <c r="F29" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>30</v>
@@ -2635,22 +2686,22 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C30" s="0">
-        <v>2123</v>
+        <v>2046</v>
       </c>
       <c r="D30" s="1">
-        <v>46194.2578587963</v>
+        <v>46207.86888888889</v>
       </c>
       <c r="E30" s="1">
-        <v>46194.2578587963</v>
+        <v>46207.98546296296</v>
       </c>
       <c r="F30" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>24</v>
@@ -2659,7 +2710,7 @@
         <v>24</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>25</v>
@@ -2679,8 +2730,8 @@
       <c r="O30" s="0">
         <v>1</v>
       </c>
-      <c r="P30" s="0">
-        <v>1</v>
+      <c r="P30" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q30" s="0" t="s">
         <v>25</v>
@@ -2703,7 +2754,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>29</v>
@@ -2712,13 +2763,13 @@
         <v>0</v>
       </c>
       <c r="D31" s="1">
-        <v>46197.83574074074</v>
+        <v>46198.758414351854</v>
       </c>
       <c r="E31" s="1">
-        <v>46197.83574074074</v>
+        <v>46198.758414351854</v>
       </c>
       <c r="F31" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>30</v>
@@ -2771,31 +2822,31 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C32" s="0">
-        <v>0</v>
+        <v>2123</v>
       </c>
       <c r="D32" s="1">
-        <v>46198.763449074075</v>
+        <v>46194.2578587963</v>
       </c>
       <c r="E32" s="1">
-        <v>46198.763449074075</v>
+        <v>46194.2578587963</v>
       </c>
       <c r="F32" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>25</v>
@@ -2815,8 +2866,8 @@
       <c r="O32" s="0">
         <v>1</v>
       </c>
-      <c r="P32" s="0" t="s">
-        <v>25</v>
+      <c r="P32" s="0">
+        <v>1</v>
       </c>
       <c r="Q32" s="0" t="s">
         <v>25</v>
@@ -2834,12 +2885,12 @@
         <v>25</v>
       </c>
       <c r="V32" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>29</v>
@@ -2848,13 +2899,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="1">
-        <v>46198.758125</v>
+        <v>46197.83574074074</v>
       </c>
       <c r="E33" s="1">
-        <v>46198.758125</v>
+        <v>46197.83574074074</v>
       </c>
       <c r="F33" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>30</v>
@@ -2863,7 +2914,7 @@
         <v>30</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>25</v>
@@ -2883,8 +2934,8 @@
       <c r="O33" s="0">
         <v>1</v>
       </c>
-      <c r="P33" s="0" t="s">
-        <v>25</v>
+      <c r="P33" s="0">
+        <v>0</v>
       </c>
       <c r="Q33" s="0" t="s">
         <v>25</v>
@@ -2907,31 +2958,31 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C34" s="0">
-        <v>2106</v>
+        <v>0</v>
       </c>
       <c r="D34" s="1">
-        <v>46201.54498842593</v>
+        <v>46198.763449074075</v>
       </c>
       <c r="E34" s="1">
-        <v>46201.54498842593</v>
+        <v>46198.763449074075</v>
       </c>
       <c r="F34" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>25</v>
@@ -2949,10 +3000,10 @@
         <v>25</v>
       </c>
       <c r="O34" s="0">
-        <v>0</v>
-      </c>
-      <c r="P34" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P34" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q34" s="0" t="s">
         <v>25</v>
@@ -2970,12 +3021,12 @@
         <v>25</v>
       </c>
       <c r="V34" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>29</v>
@@ -2984,13 +3035,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="1">
-        <v>46198.76478009259</v>
+        <v>46198.758125</v>
       </c>
       <c r="E35" s="1">
-        <v>46198.76478009259</v>
+        <v>46198.758125</v>
       </c>
       <c r="F35" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>30</v>
@@ -3043,22 +3094,22 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C36" s="0">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="D36" s="1">
-        <v>46203.412881944445</v>
+        <v>46201.54498842593</v>
       </c>
       <c r="E36" s="1">
-        <v>46204.83986111111</v>
+        <v>46201.54498842593</v>
       </c>
       <c r="F36" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>24</v>
@@ -3067,7 +3118,7 @@
         <v>24</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>25</v>
@@ -3087,8 +3138,8 @@
       <c r="O36" s="0">
         <v>0</v>
       </c>
-      <c r="P36" s="0" t="s">
-        <v>25</v>
+      <c r="P36" s="0">
+        <v>0</v>
       </c>
       <c r="Q36" s="0" t="s">
         <v>25</v>
@@ -3111,31 +3162,31 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C37" s="0">
-        <v>2106</v>
+        <v>0</v>
       </c>
       <c r="D37" s="1">
-        <v>46202.94956018519</v>
+        <v>46198.76478009259</v>
       </c>
       <c r="E37" s="1">
-        <v>46203.69975694444</v>
+        <v>46198.76478009259</v>
       </c>
       <c r="F37" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>25</v>
@@ -3155,8 +3206,8 @@
       <c r="O37" s="0">
         <v>1</v>
       </c>
-      <c r="P37" s="0">
-        <v>0</v>
+      <c r="P37" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q37" s="0" t="s">
         <v>25</v>
@@ -3174,7 +3225,7 @@
         <v>25</v>
       </c>
       <c r="V37" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
@@ -3185,16 +3236,16 @@
         <v>23</v>
       </c>
       <c r="C38" s="0">
-        <v>2114</v>
+        <v>2108</v>
       </c>
       <c r="D38" s="1">
-        <v>46206.98871527778</v>
+        <v>46204.26725694445</v>
       </c>
       <c r="E38" s="1">
-        <v>46208.10663194444</v>
+        <v>46205.76315972222</v>
       </c>
       <c r="F38" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>24</v>
@@ -3250,28 +3301,28 @@
         <v>68</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C39" s="0">
-        <v>337</v>
+        <v>2108</v>
       </c>
       <c r="D39" s="1">
-        <v>46200.844143518516</v>
+        <v>46203.412881944445</v>
       </c>
       <c r="E39" s="1">
-        <v>46200.854166666664</v>
+        <v>46204.83986111111</v>
       </c>
       <c r="F39" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J39" s="0" t="s">
         <v>25</v>
@@ -3289,10 +3340,10 @@
         <v>25</v>
       </c>
       <c r="O39" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="0" t="s">
         <v>25</v>
@@ -3310,7 +3361,7 @@
         <v>25</v>
       </c>
       <c r="V39" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
@@ -3318,28 +3369,28 @@
         <v>69</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C40" s="0">
-        <v>702049</v>
+        <v>2106</v>
       </c>
       <c r="D40" s="1">
-        <v>46204.145219907405</v>
+        <v>46202.94956018519</v>
       </c>
       <c r="E40" s="1">
-        <v>46204.145219907405</v>
+        <v>46203.69975694444</v>
       </c>
       <c r="F40" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J40" s="0" t="s">
         <v>25</v>
@@ -3357,10 +3408,10 @@
         <v>25</v>
       </c>
       <c r="O40" s="0">
-        <v>0</v>
-      </c>
-      <c r="P40" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P40" s="0">
+        <v>1</v>
       </c>
       <c r="Q40" s="0" t="s">
         <v>25</v>
@@ -3378,7 +3429,7 @@
         <v>25</v>
       </c>
       <c r="V40" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -3386,31 +3437,31 @@
         <v>70</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C41" s="0">
-        <v>262</v>
+        <v>2114</v>
       </c>
       <c r="D41" s="1">
-        <v>46191.31182870371</v>
+        <v>46206.98871527778</v>
       </c>
       <c r="E41" s="1">
-        <v>46191.31182870371</v>
+        <v>46208.10663194444</v>
       </c>
       <c r="F41" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K41" s="0" t="s">
         <v>25</v>
@@ -3425,13 +3476,13 @@
         <v>25</v>
       </c>
       <c r="O41" s="0">
-        <v>1</v>
-      </c>
-      <c r="P41" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P41" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q41" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R41" s="0" t="s">
         <v>25</v>
@@ -3446,7 +3497,7 @@
         <v>25</v>
       </c>
       <c r="V41" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
@@ -3454,31 +3505,31 @@
         <v>71</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C42" s="0">
-        <v>2108</v>
+        <v>337</v>
       </c>
       <c r="D42" s="1">
-        <v>46198.00052083333</v>
+        <v>46200.844143518516</v>
       </c>
       <c r="E42" s="1">
-        <v>46199.29518518518</v>
+        <v>46200.854166666664</v>
       </c>
       <c r="F42" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J42" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K42" s="0" t="s">
         <v>25</v>
@@ -3496,10 +3547,10 @@
         <v>1</v>
       </c>
       <c r="P42" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q42" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R42" s="0" t="s">
         <v>25</v>
@@ -3514,7 +3565,7 @@
         <v>25</v>
       </c>
       <c r="V42" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
@@ -3522,19 +3573,19 @@
         <v>72</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C43" s="0">
-        <v>0</v>
+        <v>702049</v>
       </c>
       <c r="D43" s="1">
-        <v>46198.758576388886</v>
+        <v>46204.145219907405</v>
       </c>
       <c r="E43" s="1">
-        <v>46198.758576388886</v>
+        <v>46204.145219907405</v>
       </c>
       <c r="F43" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>30</v>
@@ -3561,7 +3612,7 @@
         <v>25</v>
       </c>
       <c r="O43" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" s="0" t="s">
         <v>25</v>
@@ -3590,31 +3641,31 @@
         <v>73</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C44" s="0">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="D44" s="1">
-        <v>46192.00283564815</v>
+        <v>46191.31182870371</v>
       </c>
       <c r="E44" s="1">
-        <v>46196.6612962963</v>
+        <v>46191.31182870371</v>
       </c>
       <c r="F44" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K44" s="0" t="s">
         <v>25</v>
@@ -3635,7 +3686,7 @@
         <v>1</v>
       </c>
       <c r="Q44" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" s="0" t="s">
         <v>25</v>
@@ -3650,7 +3701,7 @@
         <v>25</v>
       </c>
       <c r="V44" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
@@ -3658,31 +3709,31 @@
         <v>74</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C45" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D45" s="1">
-        <v>46203.386967592596</v>
+        <v>46198.00052083333</v>
       </c>
       <c r="E45" s="1">
-        <v>46203.386967592596</v>
+        <v>46199.29518518518</v>
       </c>
       <c r="F45" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K45" s="0" t="s">
         <v>25</v>
@@ -3699,11 +3750,11 @@
       <c r="O45" s="0">
         <v>1</v>
       </c>
-      <c r="P45" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q45" s="0" t="s">
-        <v>25</v>
+      <c r="P45" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="0">
+        <v>0</v>
       </c>
       <c r="R45" s="0" t="s">
         <v>25</v>
@@ -3718,7 +3769,7 @@
         <v>25</v>
       </c>
       <c r="V45" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
@@ -3726,25 +3777,25 @@
         <v>75</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C46" s="0">
-        <v>2003</v>
+        <v>0</v>
       </c>
       <c r="D46" s="1">
-        <v>46203.73695601852</v>
+        <v>46198.758576388886</v>
       </c>
       <c r="E46" s="1">
-        <v>46203.73695601852</v>
+        <v>46198.758576388886</v>
       </c>
       <c r="F46" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I46" s="0" t="s">
         <v>25</v>
@@ -3765,7 +3816,7 @@
         <v>25</v>
       </c>
       <c r="O46" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" s="0" t="s">
         <v>25</v>
@@ -3786,7 +3837,7 @@
         <v>25</v>
       </c>
       <c r="V46" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47">
@@ -3794,31 +3845,31 @@
         <v>76</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C47" s="0">
-        <v>2114</v>
+        <v>305</v>
       </c>
       <c r="D47" s="1">
-        <v>46201.10230324074</v>
+        <v>46192.00283564815</v>
       </c>
       <c r="E47" s="1">
-        <v>46202.30238425926</v>
+        <v>46196.6612962963</v>
       </c>
       <c r="F47" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K47" s="0" t="s">
         <v>25</v>
@@ -3836,10 +3887,10 @@
         <v>1</v>
       </c>
       <c r="P47" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="Q47" s="0">
+        <v>1</v>
       </c>
       <c r="R47" s="0" t="s">
         <v>25</v>
@@ -3854,7 +3905,7 @@
         <v>25</v>
       </c>
       <c r="V47" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48">
@@ -3862,19 +3913,19 @@
         <v>77</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C48" s="0">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="D48" s="1">
-        <v>46198.007743055554</v>
+        <v>46203.386967592596</v>
       </c>
       <c r="E48" s="1">
-        <v>46198.007743055554</v>
+        <v>46203.386967592596</v>
       </c>
       <c r="F48" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>30</v>
@@ -3886,7 +3937,7 @@
         <v>30</v>
       </c>
       <c r="J48" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K48" s="0" t="s">
         <v>25</v>
@@ -3904,10 +3955,10 @@
         <v>1</v>
       </c>
       <c r="P48" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R48" s="0" t="s">
         <v>25</v>
@@ -3930,25 +3981,25 @@
         <v>78</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C49" s="0">
-        <v>0</v>
+        <v>2003</v>
       </c>
       <c r="D49" s="1">
-        <v>46204.82892361111</v>
+        <v>46203.73695601852</v>
       </c>
       <c r="E49" s="1">
-        <v>46204.82892361111</v>
+        <v>46203.73695601852</v>
       </c>
       <c r="F49" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I49" s="0" t="s">
         <v>25</v>
@@ -3969,7 +4020,7 @@
         <v>25</v>
       </c>
       <c r="O49" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" s="0" t="s">
         <v>25</v>
@@ -3990,7 +4041,7 @@
         <v>25</v>
       </c>
       <c r="V49" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50">
@@ -4001,16 +4052,16 @@
         <v>23</v>
       </c>
       <c r="C50" s="0">
-        <v>2108</v>
+        <v>2114</v>
       </c>
       <c r="D50" s="1">
-        <v>46202.13394675926</v>
+        <v>46201.10230324074</v>
       </c>
       <c r="E50" s="1">
-        <v>46206.49621527778</v>
+        <v>46202.30238425926</v>
       </c>
       <c r="F50" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>24</v>
@@ -4019,7 +4070,7 @@
         <v>24</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J50" s="0" t="s">
         <v>25</v>
@@ -4039,8 +4090,8 @@
       <c r="O50" s="0">
         <v>1</v>
       </c>
-      <c r="P50" s="0" t="s">
-        <v>25</v>
+      <c r="P50" s="0">
+        <v>0</v>
       </c>
       <c r="Q50" s="0" t="s">
         <v>25</v>
@@ -4066,19 +4117,19 @@
         <v>80</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C51" s="0">
         <v>262</v>
       </c>
       <c r="D51" s="1">
-        <v>46194.10880787037</v>
+        <v>46198.007743055554</v>
       </c>
       <c r="E51" s="1">
-        <v>46194.10880787037</v>
+        <v>46198.007743055554</v>
       </c>
       <c r="F51" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>30</v>
@@ -4134,25 +4185,25 @@
         <v>81</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C52" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D52" s="1">
-        <v>46202.674155092594</v>
+        <v>46204.82892361111</v>
       </c>
       <c r="E52" s="1">
-        <v>46202.80762731482</v>
+        <v>46204.82892361111</v>
       </c>
       <c r="F52" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I52" s="0" t="s">
         <v>25</v>
@@ -4194,7 +4245,7 @@
         <v>25</v>
       </c>
       <c r="V52" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
@@ -4205,16 +4256,16 @@
         <v>23</v>
       </c>
       <c r="C53" s="0">
-        <v>2025</v>
+        <v>2108</v>
       </c>
       <c r="D53" s="1">
-        <v>46196.60855324074</v>
+        <v>46202.13394675926</v>
       </c>
       <c r="E53" s="1">
-        <v>46198.053506944445</v>
+        <v>46206.49621527778</v>
       </c>
       <c r="F53" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>24</v>
@@ -4223,10 +4274,10 @@
         <v>24</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K53" s="0" t="s">
         <v>25</v>
@@ -4243,11 +4294,11 @@
       <c r="O53" s="0">
         <v>1</v>
       </c>
-      <c r="P53" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="0">
-        <v>1</v>
+      <c r="P53" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R53" s="0" t="s">
         <v>25</v>
@@ -4270,31 +4321,31 @@
         <v>83</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C54" s="0">
-        <v>2518</v>
+        <v>262</v>
       </c>
       <c r="D54" s="1">
-        <v>46205.84306712963</v>
+        <v>46194.10880787037</v>
       </c>
       <c r="E54" s="1">
-        <v>46208.01679398148</v>
+        <v>46194.10880787037</v>
       </c>
       <c r="F54" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J54" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K54" s="0" t="s">
         <v>25</v>
@@ -4311,11 +4362,11 @@
       <c r="O54" s="0">
         <v>1</v>
       </c>
-      <c r="P54" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q54" s="0" t="s">
-        <v>25</v>
+      <c r="P54" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="0">
+        <v>0</v>
       </c>
       <c r="R54" s="0" t="s">
         <v>25</v>
@@ -4330,7 +4381,7 @@
         <v>25</v>
       </c>
       <c r="V54" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
@@ -4338,28 +4389,28 @@
         <v>84</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C55" s="0">
-        <v>206</v>
+        <v>2108</v>
       </c>
       <c r="D55" s="1">
-        <v>46199.4216087963</v>
+        <v>46202.674155092594</v>
       </c>
       <c r="E55" s="1">
-        <v>46199.4216087963</v>
+        <v>46202.80762731482</v>
       </c>
       <c r="F55" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>25</v>
@@ -4380,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="P55" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="0" t="s">
         <v>25</v>
@@ -4398,7 +4449,7 @@
         <v>25</v>
       </c>
       <c r="V55" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56">
@@ -4406,31 +4457,31 @@
         <v>85</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C56" s="0">
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="D56" s="1">
-        <v>46203.398622685185</v>
+        <v>46196.60855324074</v>
       </c>
       <c r="E56" s="1">
-        <v>46203.398622685185</v>
+        <v>46198.053506944445</v>
       </c>
       <c r="F56" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J56" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K56" s="0" t="s">
         <v>25</v>
@@ -4447,11 +4498,11 @@
       <c r="O56" s="0">
         <v>1</v>
       </c>
-      <c r="P56" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q56" s="0" t="s">
-        <v>25</v>
+      <c r="P56" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="0">
+        <v>1</v>
       </c>
       <c r="R56" s="0" t="s">
         <v>25</v>
@@ -4466,7 +4517,7 @@
         <v>25</v>
       </c>
       <c r="V56" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -4474,25 +4525,25 @@
         <v>86</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C57" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D57" s="1">
-        <v>46204.071388888886</v>
+        <v>46205.84306712963</v>
       </c>
       <c r="E57" s="1">
-        <v>46204.071388888886</v>
+        <v>46208.01679398148</v>
       </c>
       <c r="F57" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I57" s="0" t="s">
         <v>25</v>
@@ -4534,7 +4585,7 @@
         <v>25</v>
       </c>
       <c r="V57" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
@@ -4542,28 +4593,28 @@
         <v>87</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C58" s="0">
-        <v>2108</v>
+        <v>206</v>
       </c>
       <c r="D58" s="1">
-        <v>46199.145104166666</v>
+        <v>46199.4216087963</v>
       </c>
       <c r="E58" s="1">
-        <v>46207.340208333335</v>
+        <v>46199.4216087963</v>
       </c>
       <c r="F58" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J58" s="0" t="s">
         <v>25</v>
@@ -4581,10 +4632,10 @@
         <v>25</v>
       </c>
       <c r="O58" s="0">
-        <v>0</v>
-      </c>
-      <c r="P58" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P58" s="0">
+        <v>1</v>
       </c>
       <c r="Q58" s="0" t="s">
         <v>25</v>
@@ -4602,7 +4653,7 @@
         <v>25</v>
       </c>
       <c r="V58" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
@@ -4610,25 +4661,25 @@
         <v>88</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C59" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D59" s="1">
-        <v>46203.22761574074</v>
+        <v>46203.398622685185</v>
       </c>
       <c r="E59" s="1">
-        <v>46203.22761574074</v>
+        <v>46203.398622685185</v>
       </c>
       <c r="F59" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I59" s="0" t="s">
         <v>25</v>
@@ -4649,7 +4700,7 @@
         <v>25</v>
       </c>
       <c r="O59" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" s="0" t="s">
         <v>25</v>
@@ -4670,7 +4721,7 @@
         <v>25</v>
       </c>
       <c r="V59" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60">
@@ -4678,25 +4729,25 @@
         <v>89</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C60" s="0">
-        <v>2003</v>
+        <v>0</v>
       </c>
       <c r="D60" s="1">
-        <v>46203.73695601852</v>
+        <v>46204.071388888886</v>
       </c>
       <c r="E60" s="1">
-        <v>46203.73695601852</v>
+        <v>46204.071388888886</v>
       </c>
       <c r="F60" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I60" s="0" t="s">
         <v>25</v>
@@ -4717,7 +4768,7 @@
         <v>25</v>
       </c>
       <c r="O60" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P60" s="0" t="s">
         <v>25</v>
@@ -4738,7 +4789,7 @@
         <v>25</v>
       </c>
       <c r="V60" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61">
@@ -4746,19 +4797,19 @@
         <v>90</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C61" s="0">
-        <v>13108</v>
+        <v>2108</v>
       </c>
       <c r="D61" s="1">
-        <v>46202.06835648148</v>
+        <v>46199.145104166666</v>
       </c>
       <c r="E61" s="1">
-        <v>46203.241944444446</v>
+        <v>46207.340208333335</v>
       </c>
       <c r="F61" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>24</v>
@@ -4767,7 +4818,7 @@
         <v>24</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J61" s="0" t="s">
         <v>25</v>
@@ -4785,10 +4836,10 @@
         <v>25</v>
       </c>
       <c r="O61" s="0">
-        <v>1</v>
-      </c>
-      <c r="P61" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P61" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q61" s="0" t="s">
         <v>25</v>
@@ -4814,19 +4865,19 @@
         <v>91</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C62" s="0">
-        <v>225</v>
+        <v>2108</v>
       </c>
       <c r="D62" s="1">
-        <v>46192.854166666664</v>
+        <v>46203.22761574074</v>
       </c>
       <c r="E62" s="1">
-        <v>46201.17297453704</v>
+        <v>46203.22761574074</v>
       </c>
       <c r="F62" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>24</v>
@@ -4835,7 +4886,7 @@
         <v>24</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J62" s="0" t="s">
         <v>25</v>
@@ -4853,10 +4904,10 @@
         <v>25</v>
       </c>
       <c r="O62" s="0">
-        <v>1</v>
-      </c>
-      <c r="P62" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P62" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q62" s="0" t="s">
         <v>25</v>
@@ -4885,28 +4936,28 @@
         <v>23</v>
       </c>
       <c r="C63" s="0">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="D63" s="1">
-        <v>46197.398356481484</v>
+        <v>46203.73695601852</v>
       </c>
       <c r="E63" s="1">
-        <v>46197.398356481484</v>
+        <v>46203.73695601852</v>
       </c>
       <c r="F63" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J63" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K63" s="0" t="s">
         <v>25</v>
@@ -4923,11 +4974,11 @@
       <c r="O63" s="0">
         <v>0</v>
       </c>
-      <c r="P63" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="0">
-        <v>0</v>
+      <c r="P63" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q63" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R63" s="0" t="s">
         <v>25</v>
@@ -4942,7 +4993,7 @@
         <v>25</v>
       </c>
       <c r="V63" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
@@ -4950,25 +5001,25 @@
         <v>93</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C64" s="0">
-        <v>0</v>
+        <v>2114</v>
       </c>
       <c r="D64" s="1">
-        <v>46198.06826388889</v>
+        <v>46208.60796296296</v>
       </c>
       <c r="E64" s="1">
-        <v>46198.06826388889</v>
+        <v>46209.27856481481</v>
       </c>
       <c r="F64" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I64" s="0" t="s">
         <v>25</v>
@@ -5010,7 +5061,7 @@
         <v>25</v>
       </c>
       <c r="V64" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
@@ -5018,28 +5069,28 @@
         <v>94</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C65" s="0">
-        <v>0</v>
+        <v>13108</v>
       </c>
       <c r="D65" s="1">
-        <v>46198.76695601852</v>
+        <v>46202.06835648148</v>
       </c>
       <c r="E65" s="1">
-        <v>46198.76695601852</v>
+        <v>46203.241944444446</v>
       </c>
       <c r="F65" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J65" s="0" t="s">
         <v>25</v>
@@ -5059,8 +5110,8 @@
       <c r="O65" s="0">
         <v>1</v>
       </c>
-      <c r="P65" s="0" t="s">
-        <v>25</v>
+      <c r="P65" s="0">
+        <v>0</v>
       </c>
       <c r="Q65" s="0" t="s">
         <v>25</v>
@@ -5078,7 +5129,7 @@
         <v>25</v>
       </c>
       <c r="V65" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
@@ -5086,25 +5137,25 @@
         <v>95</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="C66" s="0">
-        <v>0</v>
+        <v>1102304</v>
       </c>
       <c r="D66" s="1">
-        <v>46199.06940972222</v>
+        <v>46197.000439814816</v>
       </c>
       <c r="E66" s="1">
-        <v>46199.06940972222</v>
+        <v>46200.90429398148</v>
       </c>
       <c r="F66" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I66" s="0" t="s">
         <v>25</v>
@@ -5146,27 +5197,27 @@
         <v>25</v>
       </c>
       <c r="V66" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C67" s="0">
-        <v>2518</v>
+        <v>225</v>
       </c>
       <c r="D67" s="1">
-        <v>46205.52684027778</v>
+        <v>46192.854166666664</v>
       </c>
       <c r="E67" s="1">
-        <v>46207.38381944445</v>
+        <v>46201.17297453704</v>
       </c>
       <c r="F67" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>24</v>
@@ -5175,7 +5226,7 @@
         <v>24</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>25</v>
@@ -5193,10 +5244,10 @@
         <v>25</v>
       </c>
       <c r="O67" s="0">
-        <v>0</v>
-      </c>
-      <c r="P67" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P67" s="0">
+        <v>1</v>
       </c>
       <c r="Q67" s="0" t="s">
         <v>25</v>
@@ -5219,22 +5270,22 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C68" s="0">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="D68" s="1">
-        <v>46198.764710648145</v>
+        <v>46197.398356481484</v>
       </c>
       <c r="E68" s="1">
-        <v>46198.764710648145</v>
+        <v>46197.398356481484</v>
       </c>
       <c r="F68" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>30</v>
@@ -5243,10 +5294,10 @@
         <v>30</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J68" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K68" s="0" t="s">
         <v>25</v>
@@ -5261,13 +5312,13 @@
         <v>25</v>
       </c>
       <c r="O68" s="0">
-        <v>1</v>
-      </c>
-      <c r="P68" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q68" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P68" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="0">
+        <v>0</v>
       </c>
       <c r="R68" s="0" t="s">
         <v>25</v>
@@ -5287,7 +5338,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>29</v>
@@ -5302,13 +5353,13 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F69" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I69" s="0" t="s">
         <v>25</v>
@@ -5350,12 +5401,12 @@
         <v>25</v>
       </c>
       <c r="V69" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>29</v>
@@ -5364,13 +5415,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="1">
-        <v>46198.7566087963</v>
+        <v>46198.76695601852</v>
       </c>
       <c r="E70" s="1">
-        <v>46198.7566087963</v>
+        <v>46198.76695601852</v>
       </c>
       <c r="F70" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G70" s="0" t="s">
         <v>30</v>
@@ -5423,7 +5474,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>29</v>
@@ -5432,19 +5483,19 @@
         <v>0</v>
       </c>
       <c r="D71" s="1">
-        <v>46203.38690972222</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="E71" s="1">
-        <v>46203.38690972222</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="F71" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I71" s="0" t="s">
         <v>25</v>
@@ -5486,27 +5537,27 @@
         <v>25</v>
       </c>
       <c r="V71" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C72" s="0">
-        <v>2521</v>
+        <v>2518</v>
       </c>
       <c r="D72" s="1">
-        <v>46196.88789351852</v>
+        <v>46205.52684027778</v>
       </c>
       <c r="E72" s="1">
-        <v>46199.954201388886</v>
+        <v>46207.38381944445</v>
       </c>
       <c r="F72" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>24</v>
@@ -5559,7 +5610,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>29</v>
@@ -5568,19 +5619,19 @@
         <v>0</v>
       </c>
       <c r="D73" s="1">
-        <v>46199.06940972222</v>
+        <v>46198.764710648145</v>
       </c>
       <c r="E73" s="1">
-        <v>46199.06940972222</v>
+        <v>46198.764710648145</v>
       </c>
       <c r="F73" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I73" s="0" t="s">
         <v>25</v>
@@ -5622,36 +5673,36 @@
         <v>25</v>
       </c>
       <c r="V73" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C74" s="0">
-        <v>2115</v>
+        <v>2106</v>
       </c>
       <c r="D74" s="1">
-        <v>46193.45674768519</v>
+        <v>46208.60445601852</v>
       </c>
       <c r="E74" s="1">
-        <v>46193.45674768519</v>
+        <v>46208.60445601852</v>
       </c>
       <c r="F74" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>25</v>
@@ -5671,8 +5722,8 @@
       <c r="O74" s="0">
         <v>1</v>
       </c>
-      <c r="P74" s="0">
-        <v>1</v>
+      <c r="P74" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q74" s="0" t="s">
         <v>25</v>
@@ -5690,39 +5741,39 @@
         <v>25</v>
       </c>
       <c r="V74" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C75" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D75" s="1">
-        <v>46196.430972222224</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="E75" s="1">
-        <v>46196.43208333333</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="F75" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K75" s="0" t="s">
         <v>25</v>
@@ -5739,11 +5790,11 @@
       <c r="O75" s="0">
         <v>1</v>
       </c>
-      <c r="P75" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="0">
-        <v>0</v>
+      <c r="P75" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q75" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R75" s="0" t="s">
         <v>25</v>
@@ -5758,27 +5809,27 @@
         <v>25</v>
       </c>
       <c r="V75" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C76" s="0">
-        <v>2012</v>
+        <v>0</v>
       </c>
       <c r="D76" s="1">
-        <v>46205.85377314815</v>
+        <v>46198.7566087963</v>
       </c>
       <c r="E76" s="1">
-        <v>46205.85377314815</v>
+        <v>46198.7566087963</v>
       </c>
       <c r="F76" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>30</v>
@@ -5805,7 +5856,7 @@
         <v>25</v>
       </c>
       <c r="O76" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P76" s="0" t="s">
         <v>25</v>
@@ -5831,31 +5882,31 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C77" s="0">
-        <v>2106</v>
+        <v>0</v>
       </c>
       <c r="D77" s="1">
-        <v>46194.496782407405</v>
+        <v>46203.38690972222</v>
       </c>
       <c r="E77" s="1">
-        <v>46194.496782407405</v>
+        <v>46203.38690972222</v>
       </c>
       <c r="F77" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>25</v>
@@ -5876,7 +5927,7 @@
         <v>1</v>
       </c>
       <c r="P77" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="0" t="s">
         <v>25</v>
@@ -5894,27 +5945,27 @@
         <v>25</v>
       </c>
       <c r="V77" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C78" s="0">
-        <v>2108</v>
+        <v>2521</v>
       </c>
       <c r="D78" s="1">
-        <v>46206.041817129626</v>
+        <v>46196.88789351852</v>
       </c>
       <c r="E78" s="1">
-        <v>46206.041817129626</v>
+        <v>46199.954201388886</v>
       </c>
       <c r="F78" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>24</v>
@@ -5923,7 +5974,7 @@
         <v>24</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>25</v>
@@ -5941,10 +5992,10 @@
         <v>25</v>
       </c>
       <c r="O78" s="0">
-        <v>0</v>
-      </c>
-      <c r="P78" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P78" s="0">
+        <v>0</v>
       </c>
       <c r="Q78" s="0" t="s">
         <v>25</v>
@@ -5967,7 +6018,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>29</v>
@@ -5976,19 +6027,19 @@
         <v>0</v>
       </c>
       <c r="D79" s="1">
-        <v>46198.76357638889</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="E79" s="1">
-        <v>46198.76357638889</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="F79" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>25</v>
@@ -6030,36 +6081,36 @@
         <v>25</v>
       </c>
       <c r="V79" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C80" s="0">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="D80" s="1">
-        <v>46203.900046296294</v>
+        <v>46193.45674768519</v>
       </c>
       <c r="E80" s="1">
-        <v>46203.900046296294</v>
+        <v>46193.45674768519</v>
       </c>
       <c r="F80" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J80" s="0" t="s">
         <v>25</v>
@@ -6079,8 +6130,8 @@
       <c r="O80" s="0">
         <v>1</v>
       </c>
-      <c r="P80" s="0" t="s">
-        <v>25</v>
+      <c r="P80" s="0">
+        <v>1</v>
       </c>
       <c r="Q80" s="0" t="s">
         <v>25</v>
@@ -6098,39 +6149,39 @@
         <v>25</v>
       </c>
       <c r="V80" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C81" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D81" s="1">
-        <v>46198.75818287037</v>
+        <v>46196.430972222224</v>
       </c>
       <c r="E81" s="1">
-        <v>46198.75818287037</v>
+        <v>46196.43208333333</v>
       </c>
       <c r="F81" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J81" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K81" s="0" t="s">
         <v>25</v>
@@ -6147,11 +6198,11 @@
       <c r="O81" s="0">
         <v>1</v>
       </c>
-      <c r="P81" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q81" s="0" t="s">
-        <v>25</v>
+      <c r="P81" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="0">
+        <v>0</v>
       </c>
       <c r="R81" s="0" t="s">
         <v>25</v>
@@ -6166,39 +6217,39 @@
         <v>25</v>
       </c>
       <c r="V81" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C82" s="0">
-        <v>2108</v>
+        <v>2012</v>
       </c>
       <c r="D82" s="1">
-        <v>46198.57461805556</v>
+        <v>46205.85377314815</v>
       </c>
       <c r="E82" s="1">
-        <v>46199.24039351852</v>
+        <v>46205.85377314815</v>
       </c>
       <c r="F82" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J82" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K82" s="0" t="s">
         <v>25</v>
@@ -6213,13 +6264,13 @@
         <v>25</v>
       </c>
       <c r="O82" s="0">
-        <v>1</v>
-      </c>
-      <c r="P82" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q82" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P82" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q82" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R82" s="0" t="s">
         <v>25</v>
@@ -6234,36 +6285,36 @@
         <v>25</v>
       </c>
       <c r="V82" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B83" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C83" s="0">
-        <v>2025</v>
+        <v>2106</v>
       </c>
       <c r="D83" s="1">
-        <v>46206.35917824074</v>
+        <v>46194.496782407405</v>
       </c>
       <c r="E83" s="1">
-        <v>46207.7878125</v>
+        <v>46194.496782407405</v>
       </c>
       <c r="F83" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J83" s="0" t="s">
         <v>25</v>
@@ -6281,10 +6332,10 @@
         <v>25</v>
       </c>
       <c r="O83" s="0">
-        <v>0</v>
-      </c>
-      <c r="P83" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P83" s="0">
+        <v>1</v>
       </c>
       <c r="Q83" s="0" t="s">
         <v>25</v>
@@ -6302,12 +6353,12 @@
         <v>25</v>
       </c>
       <c r="V83" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>23</v>
@@ -6316,22 +6367,22 @@
         <v>2108</v>
       </c>
       <c r="D84" s="1">
-        <v>46199.62337962963</v>
+        <v>46206.041817129626</v>
       </c>
       <c r="E84" s="1">
-        <v>46200.88856481481</v>
+        <v>46206.041817129626</v>
       </c>
       <c r="F84" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="J84" s="0" t="s">
         <v>25</v>
@@ -6349,10 +6400,10 @@
         <v>25</v>
       </c>
       <c r="O84" s="0">
-        <v>1</v>
-      </c>
-      <c r="P84" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P84" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q84" s="0" t="s">
         <v>25</v>
@@ -6370,33 +6421,33 @@
         <v>25</v>
       </c>
       <c r="V84" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C85" s="0">
-        <v>2009</v>
+        <v>0</v>
       </c>
       <c r="D85" s="1">
-        <v>46207.091145833336</v>
+        <v>46198.76357638889</v>
       </c>
       <c r="E85" s="1">
-        <v>46207.091145833336</v>
+        <v>46198.76357638889</v>
       </c>
       <c r="F85" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I85" s="0" t="s">
         <v>25</v>
@@ -6438,36 +6489,36 @@
         <v>25</v>
       </c>
       <c r="V85" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C86" s="0">
-        <v>2012</v>
+        <v>0</v>
       </c>
       <c r="D86" s="1">
-        <v>46202.603946759256</v>
+        <v>46203.900046296294</v>
       </c>
       <c r="E86" s="1">
-        <v>46202.603946759256</v>
+        <v>46203.900046296294</v>
       </c>
       <c r="F86" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J86" s="0" t="s">
         <v>25</v>
@@ -6485,10 +6536,10 @@
         <v>25</v>
       </c>
       <c r="O86" s="0">
-        <v>0</v>
-      </c>
-      <c r="P86" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P86" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q86" s="0" t="s">
         <v>25</v>
@@ -6506,33 +6557,33 @@
         <v>25</v>
       </c>
       <c r="V86" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C87" s="0">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="D87" s="1">
-        <v>46200.47917824074</v>
+        <v>46198.75818287037</v>
       </c>
       <c r="E87" s="1">
-        <v>46208.28020833333</v>
+        <v>46198.75818287037</v>
       </c>
       <c r="F87" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I87" s="0" t="s">
         <v>25</v>
@@ -6553,7 +6604,7 @@
         <v>25</v>
       </c>
       <c r="O87" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" s="0" t="s">
         <v>25</v>
@@ -6574,39 +6625,39 @@
         <v>25</v>
       </c>
       <c r="V87" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C88" s="0">
-        <v>344</v>
+        <v>2108</v>
       </c>
       <c r="D88" s="1">
-        <v>46203.665925925925</v>
+        <v>46198.57461805556</v>
       </c>
       <c r="E88" s="1">
-        <v>46203.665925925925</v>
+        <v>46199.24039351852</v>
       </c>
       <c r="F88" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J88" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K88" s="0" t="s">
         <v>25</v>
@@ -6621,13 +6672,13 @@
         <v>25</v>
       </c>
       <c r="O88" s="0">
-        <v>0</v>
-      </c>
-      <c r="P88" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q88" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P88" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="0">
+        <v>0</v>
       </c>
       <c r="R88" s="0" t="s">
         <v>25</v>
@@ -6642,27 +6693,27 @@
         <v>25</v>
       </c>
       <c r="V88" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B89" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C89" s="0">
-        <v>2108</v>
+        <v>2025</v>
       </c>
       <c r="D89" s="1">
-        <v>46202.769537037035</v>
+        <v>46206.35917824074</v>
       </c>
       <c r="E89" s="1">
-        <v>46204.36974537037</v>
+        <v>46207.7878125</v>
       </c>
       <c r="F89" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>24</v>
@@ -6671,7 +6722,7 @@
         <v>24</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J89" s="0" t="s">
         <v>25</v>
@@ -6689,10 +6740,10 @@
         <v>25</v>
       </c>
       <c r="O89" s="0">
-        <v>1</v>
-      </c>
-      <c r="P89" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P89" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q89" s="0" t="s">
         <v>25</v>
@@ -6715,31 +6766,31 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B90" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C90" s="0">
-        <v>2099</v>
+        <v>2108</v>
       </c>
       <c r="D90" s="1">
-        <v>46200.000439814816</v>
+        <v>46199.62337962963</v>
       </c>
       <c r="E90" s="1">
-        <v>46201.332870370374</v>
+        <v>46200.88856481481</v>
       </c>
       <c r="F90" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J90" s="0" t="s">
         <v>25</v>
@@ -6778,39 +6829,39 @@
         <v>25</v>
       </c>
       <c r="V90" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C91" s="0">
-        <v>112304</v>
+        <v>2009</v>
       </c>
       <c r="D91" s="1">
-        <v>46197.03113425926</v>
+        <v>46207.091145833336</v>
       </c>
       <c r="E91" s="1">
-        <v>46197.03113425926</v>
+        <v>46207.091145833336</v>
       </c>
       <c r="F91" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J91" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K91" s="0" t="s">
         <v>25</v>
@@ -6825,13 +6876,13 @@
         <v>25</v>
       </c>
       <c r="O91" s="0">
-        <v>0</v>
-      </c>
-      <c r="P91" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q91" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P91" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q91" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R91" s="0" t="s">
         <v>25</v>
@@ -6846,36 +6897,36 @@
         <v>25</v>
       </c>
       <c r="V91" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B92" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C92" s="0">
-        <v>2108</v>
+        <v>2012</v>
       </c>
       <c r="D92" s="1">
-        <v>46200.04966435185</v>
+        <v>46202.603946759256</v>
       </c>
       <c r="E92" s="1">
-        <v>46200.98619212963</v>
+        <v>46202.603946759256</v>
       </c>
       <c r="F92" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J92" s="0" t="s">
         <v>25</v>
@@ -6893,10 +6944,10 @@
         <v>25</v>
       </c>
       <c r="O92" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P92" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" s="0" t="s">
         <v>25</v>
@@ -6914,33 +6965,33 @@
         <v>25</v>
       </c>
       <c r="V92" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C93" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D93" s="1">
-        <v>46198.763344907406</v>
+        <v>46200.47917824074</v>
       </c>
       <c r="E93" s="1">
-        <v>46198.763344907406</v>
+        <v>46208.28020833333</v>
       </c>
       <c r="F93" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I93" s="0" t="s">
         <v>25</v>
@@ -6982,36 +7033,36 @@
         <v>25</v>
       </c>
       <c r="V93" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C94" s="0">
-        <v>2120</v>
+        <v>344</v>
       </c>
       <c r="D94" s="1">
-        <v>46196.68797453704</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="E94" s="1">
-        <v>46198.86886574074</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="F94" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J94" s="0" t="s">
         <v>25</v>
@@ -7029,10 +7080,10 @@
         <v>25</v>
       </c>
       <c r="O94" s="0">
-        <v>1</v>
-      </c>
-      <c r="P94" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P94" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q94" s="0" t="s">
         <v>25</v>
@@ -7050,36 +7101,36 @@
         <v>25</v>
       </c>
       <c r="V94" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C95" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D95" s="1">
-        <v>46198.76422453704</v>
+        <v>46202.769537037035</v>
       </c>
       <c r="E95" s="1">
-        <v>46198.76422453704</v>
+        <v>46204.36974537037</v>
       </c>
       <c r="F95" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J95" s="0" t="s">
         <v>25</v>
@@ -7099,8 +7150,8 @@
       <c r="O95" s="0">
         <v>1</v>
       </c>
-      <c r="P95" s="0" t="s">
-        <v>25</v>
+      <c r="P95" s="0">
+        <v>0</v>
       </c>
       <c r="Q95" s="0" t="s">
         <v>25</v>
@@ -7118,36 +7169,36 @@
         <v>25</v>
       </c>
       <c r="V95" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C96" s="0">
-        <v>2123</v>
+        <v>2099</v>
       </c>
       <c r="D96" s="1">
-        <v>46206.39832175926</v>
+        <v>46200.000439814816</v>
       </c>
       <c r="E96" s="1">
-        <v>46206.39832175926</v>
+        <v>46201.332870370374</v>
       </c>
       <c r="F96" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J96" s="0" t="s">
         <v>25</v>
@@ -7165,10 +7216,10 @@
         <v>25</v>
       </c>
       <c r="O96" s="0">
-        <v>0</v>
-      </c>
-      <c r="P96" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P96" s="0">
+        <v>1</v>
       </c>
       <c r="Q96" s="0" t="s">
         <v>25</v>
@@ -7186,39 +7237,39 @@
         <v>25</v>
       </c>
       <c r="V96" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C97" s="0">
-        <v>2108</v>
+        <v>112304</v>
       </c>
       <c r="D97" s="1">
-        <v>46197.72638888889</v>
+        <v>46197.03113425926</v>
       </c>
       <c r="E97" s="1">
-        <v>46201.828206018516</v>
+        <v>46197.03113425926</v>
       </c>
       <c r="F97" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J97" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K97" s="0" t="s">
         <v>25</v>
@@ -7236,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="P97" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="Q97" s="0">
+        <v>0</v>
       </c>
       <c r="R97" s="0" t="s">
         <v>25</v>
@@ -7254,39 +7305,39 @@
         <v>25</v>
       </c>
       <c r="V97" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="C98" s="0">
-        <v>64</v>
+        <v>2108</v>
       </c>
       <c r="D98" s="1">
-        <v>46198.13282407408</v>
+        <v>46200.04966435185</v>
       </c>
       <c r="E98" s="1">
-        <v>46198.13486111111</v>
+        <v>46200.98619212963</v>
       </c>
       <c r="F98" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J98" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K98" s="0" t="s">
         <v>25</v>
@@ -7304,10 +7355,10 @@
         <v>1</v>
       </c>
       <c r="P98" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q98" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q98" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R98" s="0" t="s">
         <v>25</v>
@@ -7322,7 +7373,7 @@
         <v>25</v>
       </c>
       <c r="V98" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99">
@@ -7333,16 +7384,16 @@
         <v>23</v>
       </c>
       <c r="C99" s="0">
-        <v>2518</v>
+        <v>2108</v>
       </c>
       <c r="D99" s="1">
-        <v>46198.26168981481</v>
+        <v>46207.068391203706</v>
       </c>
       <c r="E99" s="1">
-        <v>46198.487546296295</v>
+        <v>46207.18613425926</v>
       </c>
       <c r="F99" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>24</v>
@@ -7351,10 +7402,10 @@
         <v>24</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J99" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K99" s="0" t="s">
         <v>25</v>
@@ -7371,11 +7422,11 @@
       <c r="O99" s="0">
         <v>1</v>
       </c>
-      <c r="P99" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="0">
-        <v>0</v>
+      <c r="P99" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q99" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R99" s="0" t="s">
         <v>25</v>
@@ -7398,31 +7449,31 @@
         <v>130</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C100" s="0">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="D100" s="1">
-        <v>46198.6140625</v>
+        <v>46198.763344907406</v>
       </c>
       <c r="E100" s="1">
-        <v>46199.37</v>
+        <v>46198.763344907406</v>
       </c>
       <c r="F100" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J100" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K100" s="0" t="s">
         <v>25</v>
@@ -7439,11 +7490,11 @@
       <c r="O100" s="0">
         <v>1</v>
       </c>
-      <c r="P100" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q100" s="0">
-        <v>0</v>
+      <c r="P100" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q100" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R100" s="0" t="s">
         <v>25</v>
@@ -7458,7 +7509,7 @@
         <v>25</v>
       </c>
       <c r="V100" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101">
@@ -7466,19 +7517,19 @@
         <v>131</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C101" s="0">
-        <v>13108</v>
+        <v>2120</v>
       </c>
       <c r="D101" s="1">
-        <v>46200.21556712963</v>
+        <v>46196.68797453704</v>
       </c>
       <c r="E101" s="1">
-        <v>46200.507418981484</v>
+        <v>46198.86886574074</v>
       </c>
       <c r="F101" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>24</v>
@@ -7490,7 +7541,7 @@
         <v>24</v>
       </c>
       <c r="J101" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K101" s="0" t="s">
         <v>25</v>
@@ -7510,8 +7561,8 @@
       <c r="P101" s="0">
         <v>1</v>
       </c>
-      <c r="Q101" s="0" t="s">
-        <v>25</v>
+      <c r="Q101" s="0">
+        <v>0</v>
       </c>
       <c r="R101" s="0" t="s">
         <v>25</v>
@@ -7534,25 +7585,25 @@
         <v>132</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C102" s="0">
-        <v>2126</v>
+        <v>0</v>
       </c>
       <c r="D102" s="1">
-        <v>46206.616875</v>
+        <v>46198.76422453704</v>
       </c>
       <c r="E102" s="1">
-        <v>46206.616875</v>
+        <v>46198.76422453704</v>
       </c>
       <c r="F102" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I102" s="0" t="s">
         <v>25</v>
@@ -7573,7 +7624,7 @@
         <v>25</v>
       </c>
       <c r="O102" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P102" s="0" t="s">
         <v>25</v>
@@ -7594,7 +7645,7 @@
         <v>25</v>
       </c>
       <c r="V102" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103">
@@ -7605,22 +7656,22 @@
         <v>23</v>
       </c>
       <c r="C103" s="0">
-        <v>2012</v>
+        <v>2123</v>
       </c>
       <c r="D103" s="1">
-        <v>46206.85376157407</v>
+        <v>46206.39832175926</v>
       </c>
       <c r="E103" s="1">
-        <v>46206.85376157407</v>
+        <v>46206.39832175926</v>
       </c>
       <c r="F103" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>25</v>
@@ -7662,7 +7713,7 @@
         <v>25</v>
       </c>
       <c r="V103" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104">
@@ -7673,25 +7724,25 @@
         <v>23</v>
       </c>
       <c r="C104" s="0">
-        <v>2518</v>
+        <v>2108</v>
       </c>
       <c r="D104" s="1">
-        <v>46208.34142361111</v>
+        <v>46197.72638888889</v>
       </c>
       <c r="E104" s="1">
-        <v>46208.34142361111</v>
+        <v>46201.828206018516</v>
       </c>
       <c r="F104" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J104" s="0" t="s">
         <v>25</v>
@@ -7709,10 +7760,10 @@
         <v>25</v>
       </c>
       <c r="O104" s="0">
-        <v>1</v>
-      </c>
-      <c r="P104" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P104" s="0">
+        <v>0</v>
       </c>
       <c r="Q104" s="0" t="s">
         <v>25</v>
@@ -7730,7 +7781,7 @@
         <v>25</v>
       </c>
       <c r="V104" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="105">
@@ -7738,31 +7789,31 @@
         <v>135</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="C105" s="0">
-        <v>318</v>
+        <v>64</v>
       </c>
       <c r="D105" s="1">
-        <v>46205.74003472222</v>
+        <v>46198.13282407408</v>
       </c>
       <c r="E105" s="1">
-        <v>46205.74003472222</v>
+        <v>46198.13486111111</v>
       </c>
       <c r="F105" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J105" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K105" s="0" t="s">
         <v>25</v>
@@ -7777,13 +7828,13 @@
         <v>25</v>
       </c>
       <c r="O105" s="0">
-        <v>0</v>
-      </c>
-      <c r="P105" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q105" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P105" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q105" s="0">
+        <v>1</v>
       </c>
       <c r="R105" s="0" t="s">
         <v>25</v>
@@ -7798,39 +7849,39 @@
         <v>25</v>
       </c>
       <c r="V105" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B106" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C106" s="0">
-        <v>2521</v>
+        <v>2518</v>
       </c>
       <c r="D106" s="1">
-        <v>46196.88789351852</v>
+        <v>46198.26168981481</v>
       </c>
       <c r="E106" s="1">
-        <v>46199.95371527778</v>
+        <v>46198.487546296295</v>
       </c>
       <c r="F106" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="J106" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K106" s="0" t="s">
         <v>25</v>
@@ -7848,10 +7899,10 @@
         <v>1</v>
       </c>
       <c r="P106" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q106" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="Q106" s="0">
+        <v>0</v>
       </c>
       <c r="R106" s="0" t="s">
         <v>25</v>
@@ -7866,39 +7917,39 @@
         <v>25</v>
       </c>
       <c r="V106" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C107" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D107" s="1">
-        <v>46203.39921296296</v>
+        <v>46198.6140625</v>
       </c>
       <c r="E107" s="1">
-        <v>46203.39921296296</v>
+        <v>46199.37</v>
       </c>
       <c r="F107" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J107" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K107" s="0" t="s">
         <v>25</v>
@@ -7915,11 +7966,11 @@
       <c r="O107" s="0">
         <v>1</v>
       </c>
-      <c r="P107" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q107" s="0" t="s">
-        <v>25</v>
+      <c r="P107" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q107" s="0">
+        <v>0</v>
       </c>
       <c r="R107" s="0" t="s">
         <v>25</v>
@@ -7934,36 +7985,36 @@
         <v>25</v>
       </c>
       <c r="V107" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C108" s="0">
-        <v>300144</v>
+        <v>13108</v>
       </c>
       <c r="D108" s="1">
-        <v>46206.91523148148</v>
+        <v>46200.21556712963</v>
       </c>
       <c r="E108" s="1">
-        <v>46206.91523148148</v>
+        <v>46200.507418981484</v>
       </c>
       <c r="F108" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J108" s="0" t="s">
         <v>25</v>
@@ -7981,10 +8032,10 @@
         <v>25</v>
       </c>
       <c r="O108" s="0">
-        <v>0</v>
-      </c>
-      <c r="P108" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P108" s="0">
+        <v>1</v>
       </c>
       <c r="Q108" s="0" t="s">
         <v>25</v>
@@ -8002,33 +8053,33 @@
         <v>25</v>
       </c>
       <c r="V108" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C109" s="0">
-        <v>0</v>
+        <v>2126</v>
       </c>
       <c r="D109" s="1">
-        <v>46199.06940972222</v>
+        <v>46206.616875</v>
       </c>
       <c r="E109" s="1">
-        <v>46199.06940972222</v>
+        <v>46206.616875</v>
       </c>
       <c r="F109" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I109" s="0" t="s">
         <v>25</v>
@@ -8049,7 +8100,7 @@
         <v>25</v>
       </c>
       <c r="O109" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P109" s="0" t="s">
         <v>25</v>
@@ -8070,36 +8121,36 @@
         <v>25</v>
       </c>
       <c r="V109" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B110" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C110" s="0">
-        <v>2092</v>
+        <v>2012</v>
       </c>
       <c r="D110" s="1">
-        <v>46198.29152777778</v>
+        <v>46206.85376157407</v>
       </c>
       <c r="E110" s="1">
-        <v>46199.395949074074</v>
+        <v>46206.85376157407</v>
       </c>
       <c r="F110" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J110" s="0" t="s">
         <v>25</v>
@@ -8117,10 +8168,10 @@
         <v>25</v>
       </c>
       <c r="O110" s="0">
-        <v>1</v>
-      </c>
-      <c r="P110" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P110" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q110" s="0" t="s">
         <v>25</v>
@@ -8138,33 +8189,33 @@
         <v>25</v>
       </c>
       <c r="V110" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C111" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D111" s="1">
-        <v>46198.756527777776</v>
+        <v>46208.34142361111</v>
       </c>
       <c r="E111" s="1">
-        <v>46198.756527777776</v>
+        <v>46208.34142361111</v>
       </c>
       <c r="F111" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I111" s="0" t="s">
         <v>25</v>
@@ -8206,33 +8257,33 @@
         <v>25</v>
       </c>
       <c r="V111" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C112" s="0">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="D112" s="1">
-        <v>46198.76427083334</v>
+        <v>46206.18699074074</v>
       </c>
       <c r="E112" s="1">
-        <v>46198.76427083334</v>
+        <v>46207.44116898148</v>
       </c>
       <c r="F112" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>25</v>
@@ -8253,7 +8304,7 @@
         <v>25</v>
       </c>
       <c r="O112" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P112" s="0" t="s">
         <v>25</v>
@@ -8274,39 +8325,39 @@
         <v>25</v>
       </c>
       <c r="V112" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C113" s="0">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="D113" s="1">
-        <v>46196.08101851852</v>
+        <v>46205.74003472222</v>
       </c>
       <c r="E113" s="1">
-        <v>46196.08101851852</v>
+        <v>46205.74003472222</v>
       </c>
       <c r="F113" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J113" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K113" s="0" t="s">
         <v>25</v>
@@ -8321,13 +8372,13 @@
         <v>25</v>
       </c>
       <c r="O113" s="0">
-        <v>1</v>
-      </c>
-      <c r="P113" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q113" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P113" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q113" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R113" s="0" t="s">
         <v>25</v>
@@ -8342,39 +8393,39 @@
         <v>25</v>
       </c>
       <c r="V113" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C114" s="0">
-        <v>262</v>
+        <v>2521</v>
       </c>
       <c r="D114" s="1">
-        <v>46196.788564814815</v>
+        <v>46196.88789351852</v>
       </c>
       <c r="E114" s="1">
-        <v>46196.788564814815</v>
+        <v>46199.95371527778</v>
       </c>
       <c r="F114" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J114" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K114" s="0" t="s">
         <v>25</v>
@@ -8391,11 +8442,11 @@
       <c r="O114" s="0">
         <v>1</v>
       </c>
-      <c r="P114" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q114" s="0" t="s">
-        <v>25</v>
+      <c r="P114" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q114" s="0">
+        <v>0</v>
       </c>
       <c r="R114" s="0" t="s">
         <v>25</v>
@@ -8410,36 +8461,36 @@
         <v>25</v>
       </c>
       <c r="V114" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C115" s="0">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="D115" s="1">
-        <v>46200.45096064815</v>
+        <v>46203.39921296296</v>
       </c>
       <c r="E115" s="1">
-        <v>46200.45096064815</v>
+        <v>46203.39921296296</v>
       </c>
       <c r="F115" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="J115" s="0" t="s">
         <v>25</v>
@@ -8457,10 +8508,10 @@
         <v>25</v>
       </c>
       <c r="O115" s="0">
-        <v>0</v>
-      </c>
-      <c r="P115" s="0">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="P115" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q115" s="0" t="s">
         <v>25</v>
@@ -8478,27 +8529,27 @@
         <v>25</v>
       </c>
       <c r="V115" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B116" s="0" t="s">
         <v>46</v>
       </c>
       <c r="C116" s="0">
-        <v>336</v>
+        <v>300144</v>
       </c>
       <c r="D116" s="1">
-        <v>46198.12163194444</v>
+        <v>46206.91523148148</v>
       </c>
       <c r="E116" s="1">
-        <v>46207.18237268519</v>
+        <v>46206.91523148148</v>
       </c>
       <c r="F116" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>30</v>
@@ -8525,7 +8576,7 @@
         <v>25</v>
       </c>
       <c r="O116" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P116" s="0" t="s">
         <v>25</v>
@@ -8551,34 +8602,34 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C117" s="0">
-        <v>13108</v>
+        <v>0</v>
       </c>
       <c r="D117" s="1">
-        <v>46197.70695601852</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="E117" s="1">
-        <v>46198.89733796296</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="F117" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J117" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K117" s="0" t="s">
         <v>25</v>
@@ -8593,13 +8644,13 @@
         <v>25</v>
       </c>
       <c r="O117" s="0">
-        <v>0</v>
-      </c>
-      <c r="P117" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q117" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P117" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q117" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R117" s="0" t="s">
         <v>25</v>
@@ -8614,27 +8665,27 @@
         <v>25</v>
       </c>
       <c r="V117" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C118" s="0">
-        <v>13108</v>
+        <v>2092</v>
       </c>
       <c r="D118" s="1">
-        <v>46201.693333333336</v>
+        <v>46198.29152777778</v>
       </c>
       <c r="E118" s="1">
-        <v>46205.19603009259</v>
+        <v>46199.395949074074</v>
       </c>
       <c r="F118" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>24</v>
@@ -8643,10 +8694,10 @@
         <v>24</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J118" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K118" s="0" t="s">
         <v>25</v>
@@ -8661,13 +8712,13 @@
         <v>25</v>
       </c>
       <c r="O118" s="0">
-        <v>0</v>
-      </c>
-      <c r="P118" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q118" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P118" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="0">
+        <v>0</v>
       </c>
       <c r="R118" s="0" t="s">
         <v>25</v>
@@ -8687,7 +8738,7 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B119" s="0" t="s">
         <v>29</v>
@@ -8696,13 +8747,13 @@
         <v>0</v>
       </c>
       <c r="D119" s="1">
-        <v>46196.08101851852</v>
+        <v>46198.756527777776</v>
       </c>
       <c r="E119" s="1">
-        <v>46196.08101851852</v>
+        <v>46198.756527777776</v>
       </c>
       <c r="F119" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>30</v>
@@ -8711,10 +8762,10 @@
         <v>30</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J119" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K119" s="0" t="s">
         <v>25</v>
@@ -8731,11 +8782,11 @@
       <c r="O119" s="0">
         <v>1</v>
       </c>
-      <c r="P119" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q119" s="0">
-        <v>0</v>
+      <c r="P119" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q119" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R119" s="0" t="s">
         <v>25</v>
@@ -8755,22 +8806,22 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C120" s="0">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="D120" s="1">
-        <v>46196.88885416667</v>
+        <v>46198.76427083334</v>
       </c>
       <c r="E120" s="1">
-        <v>46196.88885416667</v>
+        <v>46198.76427083334</v>
       </c>
       <c r="F120" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>30</v>
@@ -8779,7 +8830,7 @@
         <v>30</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J120" s="0" t="s">
         <v>25</v>
@@ -8799,8 +8850,8 @@
       <c r="O120" s="0">
         <v>1</v>
       </c>
-      <c r="P120" s="0">
-        <v>0</v>
+      <c r="P120" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q120" s="0" t="s">
         <v>25</v>
@@ -8823,34 +8874,34 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C121" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D121" s="1">
-        <v>46199.89765046296</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="E121" s="1">
-        <v>46199.89765046296</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="F121" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J121" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K121" s="0" t="s">
         <v>25</v>
@@ -8870,8 +8921,8 @@
       <c r="P121" s="0">
         <v>0</v>
       </c>
-      <c r="Q121" s="0" t="s">
-        <v>25</v>
+      <c r="Q121" s="0">
+        <v>1</v>
       </c>
       <c r="R121" s="0" t="s">
         <v>25</v>
@@ -8886,12 +8937,12 @@
         <v>25</v>
       </c>
       <c r="V121" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B122" s="0" t="s">
         <v>29</v>
@@ -8900,13 +8951,13 @@
         <v>0</v>
       </c>
       <c r="D122" s="1">
-        <v>46203.38673611111</v>
+        <v>46207.28523148148</v>
       </c>
       <c r="E122" s="1">
-        <v>46203.38673611111</v>
+        <v>46207.28523148148</v>
       </c>
       <c r="F122" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>30</v>
@@ -8959,28 +9010,28 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C123" s="0">
-        <v>2025</v>
+        <v>262</v>
       </c>
       <c r="D123" s="1">
-        <v>46202.83125</v>
+        <v>46196.788564814815</v>
       </c>
       <c r="E123" s="1">
-        <v>46205.35525462963</v>
+        <v>46196.788564814815</v>
       </c>
       <c r="F123" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I123" s="0" t="s">
         <v>25</v>
@@ -9001,7 +9052,7 @@
         <v>25</v>
       </c>
       <c r="O123" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P123" s="0" t="s">
         <v>25</v>
@@ -9022,36 +9073,36 @@
         <v>25</v>
       </c>
       <c r="V123" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C124" s="0">
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="D124" s="1">
-        <v>46199.259988425925</v>
+        <v>46200.45096064815</v>
       </c>
       <c r="E124" s="1">
-        <v>46200.595925925925</v>
+        <v>46200.45096064815</v>
       </c>
       <c r="F124" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J124" s="0" t="s">
         <v>25</v>
@@ -9069,7 +9120,7 @@
         <v>25</v>
       </c>
       <c r="O124" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P124" s="0">
         <v>1</v>
@@ -9090,39 +9141,39 @@
         <v>25</v>
       </c>
       <c r="V124" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C125" s="0">
-        <v>2108</v>
+        <v>336</v>
       </c>
       <c r="D125" s="1">
-        <v>46196.84064814815</v>
+        <v>46198.12163194444</v>
       </c>
       <c r="E125" s="1">
-        <v>46198.36408564815</v>
+        <v>46207.18237268519</v>
       </c>
       <c r="F125" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J125" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K125" s="0" t="s">
         <v>25</v>
@@ -9137,13 +9188,13 @@
         <v>25</v>
       </c>
       <c r="O125" s="0">
-        <v>0</v>
-      </c>
-      <c r="P125" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q125" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P125" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q125" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R125" s="0" t="s">
         <v>25</v>
@@ -9158,39 +9209,39 @@
         <v>25</v>
       </c>
       <c r="V125" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C126" s="0">
-        <v>344</v>
+        <v>13108</v>
       </c>
       <c r="D126" s="1">
-        <v>46203.6659375</v>
+        <v>46197.70695601852</v>
       </c>
       <c r="E126" s="1">
-        <v>46203.6659375</v>
+        <v>46198.89733796296</v>
       </c>
       <c r="F126" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J126" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K126" s="0" t="s">
         <v>25</v>
@@ -9207,11 +9258,11 @@
       <c r="O126" s="0">
         <v>0</v>
       </c>
-      <c r="P126" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q126" s="0" t="s">
-        <v>25</v>
+      <c r="P126" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="0">
+        <v>0</v>
       </c>
       <c r="R126" s="0" t="s">
         <v>25</v>
@@ -9226,27 +9277,27 @@
         <v>25</v>
       </c>
       <c r="V126" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C127" s="0">
-        <v>2518</v>
+        <v>13108</v>
       </c>
       <c r="D127" s="1">
-        <v>46200.18853009259</v>
+        <v>46201.693333333336</v>
       </c>
       <c r="E127" s="1">
-        <v>46200.84137731481</v>
+        <v>46205.19603009259</v>
       </c>
       <c r="F127" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>24</v>
@@ -9273,10 +9324,10 @@
         <v>25</v>
       </c>
       <c r="O127" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P127" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q127" s="0" t="s">
         <v>25</v>
@@ -9299,34 +9350,34 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C128" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D128" s="1">
-        <v>46205.6671412037</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="E128" s="1">
-        <v>46207.322233796294</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="F128" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J128" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K128" s="0" t="s">
         <v>25</v>
@@ -9343,11 +9394,11 @@
       <c r="O128" s="0">
         <v>1</v>
       </c>
-      <c r="P128" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q128" s="0" t="s">
-        <v>25</v>
+      <c r="P128" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q128" s="0">
+        <v>0</v>
       </c>
       <c r="R128" s="0" t="s">
         <v>25</v>
@@ -9362,27 +9413,27 @@
         <v>25</v>
       </c>
       <c r="V128" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C129" s="0">
-        <v>344</v>
+        <v>262</v>
       </c>
       <c r="D129" s="1">
-        <v>46203.665925925925</v>
+        <v>46196.88885416667</v>
       </c>
       <c r="E129" s="1">
-        <v>46203.665925925925</v>
+        <v>46196.88885416667</v>
       </c>
       <c r="F129" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>30</v>
@@ -9391,7 +9442,7 @@
         <v>30</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J129" s="0" t="s">
         <v>25</v>
@@ -9409,10 +9460,10 @@
         <v>25</v>
       </c>
       <c r="O129" s="0">
-        <v>0</v>
-      </c>
-      <c r="P129" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P129" s="0">
+        <v>1</v>
       </c>
       <c r="Q129" s="0" t="s">
         <v>25</v>
@@ -9435,31 +9486,31 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B130" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C130" s="0">
-        <v>2123</v>
+        <v>2108</v>
       </c>
       <c r="D130" s="1">
-        <v>46205.68171296296</v>
+        <v>46199.89765046296</v>
       </c>
       <c r="E130" s="1">
-        <v>46207.24060185185</v>
+        <v>46199.89765046296</v>
       </c>
       <c r="F130" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J130" s="0" t="s">
         <v>25</v>
@@ -9479,8 +9530,8 @@
       <c r="O130" s="0">
         <v>1</v>
       </c>
-      <c r="P130" s="0" t="s">
-        <v>25</v>
+      <c r="P130" s="0">
+        <v>0</v>
       </c>
       <c r="Q130" s="0" t="s">
         <v>25</v>
@@ -9498,12 +9549,12 @@
         <v>25</v>
       </c>
       <c r="V130" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B131" s="0" t="s">
         <v>29</v>
@@ -9512,25 +9563,25 @@
         <v>0</v>
       </c>
       <c r="D131" s="1">
-        <v>46196.08100694444</v>
+        <v>46203.38673611111</v>
       </c>
       <c r="E131" s="1">
-        <v>46196.08100694444</v>
+        <v>46203.38673611111</v>
       </c>
       <c r="F131" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="J131" s="0" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="K131" s="0" t="s">
         <v>25</v>
@@ -9550,8 +9601,8 @@
       <c r="P131" s="0">
         <v>0</v>
       </c>
-      <c r="Q131" s="0">
-        <v>1</v>
+      <c r="Q131" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R131" s="0" t="s">
         <v>25</v>
@@ -9566,12 +9617,12 @@
         <v>25</v>
       </c>
       <c r="V131" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B132" s="0" t="s">
         <v>23</v>
@@ -9580,22 +9631,22 @@
         <v>2518</v>
       </c>
       <c r="D132" s="1">
-        <v>46198.78761574074</v>
+        <v>46208.24219907408</v>
       </c>
       <c r="E132" s="1">
-        <v>46200.24690972222</v>
+        <v>46208.49730324074</v>
       </c>
       <c r="F132" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J132" s="0" t="s">
         <v>25</v>
@@ -9615,8 +9666,8 @@
       <c r="O132" s="0">
         <v>1</v>
       </c>
-      <c r="P132" s="0">
-        <v>1</v>
+      <c r="P132" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q132" s="0" t="s">
         <v>25</v>
@@ -9634,36 +9685,36 @@
         <v>25</v>
       </c>
       <c r="V132" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B133" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C133" s="0">
-        <v>2099</v>
+        <v>2025</v>
       </c>
       <c r="D133" s="1">
-        <v>46200.39493055556</v>
+        <v>46202.83125</v>
       </c>
       <c r="E133" s="1">
-        <v>46200.39493055556</v>
+        <v>46205.35525462963</v>
       </c>
       <c r="F133" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J133" s="0" t="s">
         <v>25</v>
@@ -9684,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="P133" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q133" s="0" t="s">
         <v>25</v>
@@ -9702,36 +9753,36 @@
         <v>25</v>
       </c>
       <c r="V133" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C134" s="0">
-        <v>2046</v>
+        <v>206</v>
       </c>
       <c r="D134" s="1">
-        <v>46200.55334490741</v>
+        <v>46199.259988425925</v>
       </c>
       <c r="E134" s="1">
-        <v>46201.81197916667</v>
+        <v>46200.595925925925</v>
       </c>
       <c r="F134" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J134" s="0" t="s">
         <v>25</v>
@@ -9749,10 +9800,10 @@
         <v>25</v>
       </c>
       <c r="O134" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P134" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q134" s="0" t="s">
         <v>25</v>
@@ -9770,12 +9821,12 @@
         <v>25</v>
       </c>
       <c r="V134" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B135" s="0" t="s">
         <v>23</v>
@@ -9784,13 +9835,13 @@
         <v>2108</v>
       </c>
       <c r="D135" s="1">
-        <v>46196.56989583333</v>
+        <v>46196.84064814815</v>
       </c>
       <c r="E135" s="1">
-        <v>46196.87100694444</v>
+        <v>46198.36408564815</v>
       </c>
       <c r="F135" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>24</v>
@@ -9820,7 +9871,7 @@
         <v>0</v>
       </c>
       <c r="P135" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q135" s="0">
         <v>0</v>
@@ -9843,28 +9894,28 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C136" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D136" s="1">
-        <v>46203.38674768519</v>
+        <v>46208.95462962963</v>
       </c>
       <c r="E136" s="1">
-        <v>46203.38674768519</v>
+        <v>46208.95462962963</v>
       </c>
       <c r="F136" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I136" s="0" t="s">
         <v>25</v>
@@ -9906,36 +9957,36 @@
         <v>25</v>
       </c>
       <c r="V136" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C137" s="0">
-        <v>0</v>
+        <v>13108</v>
       </c>
       <c r="D137" s="1">
-        <v>46199.38827546296</v>
+        <v>46205.32334490741</v>
       </c>
       <c r="E137" s="1">
-        <v>46199.38827546296</v>
+        <v>46209.34474537037</v>
       </c>
       <c r="F137" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J137" s="0" t="s">
         <v>25</v>
@@ -9953,10 +10004,10 @@
         <v>25</v>
       </c>
       <c r="O137" s="0">
-        <v>1</v>
-      </c>
-      <c r="P137" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P137" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q137" s="0" t="s">
         <v>25</v>
@@ -9974,27 +10025,27 @@
         <v>25</v>
       </c>
       <c r="V137" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C138" s="0">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="D138" s="1">
-        <v>46198.75832175926</v>
+        <v>46203.6659375</v>
       </c>
       <c r="E138" s="1">
-        <v>46198.75832175926</v>
+        <v>46203.6659375</v>
       </c>
       <c r="F138" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>30</v>
@@ -10021,7 +10072,7 @@
         <v>25</v>
       </c>
       <c r="O138" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P138" s="0" t="s">
         <v>25</v>
@@ -10047,22 +10098,22 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B139" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C139" s="0">
-        <v>2025</v>
+        <v>2518</v>
       </c>
       <c r="D139" s="1">
-        <v>46200.08666666667</v>
+        <v>46200.18853009259</v>
       </c>
       <c r="E139" s="1">
-        <v>46200.08666666667</v>
+        <v>46200.84137731481</v>
       </c>
       <c r="F139" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>24</v>
@@ -10092,7 +10143,7 @@
         <v>1</v>
       </c>
       <c r="P139" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q139" s="0" t="s">
         <v>25</v>
@@ -10115,34 +10166,34 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C140" s="0">
-        <v>336</v>
+        <v>2108</v>
       </c>
       <c r="D140" s="1">
-        <v>46191.19981481481</v>
+        <v>46205.6671412037</v>
       </c>
       <c r="E140" s="1">
-        <v>46191.20039351852</v>
+        <v>46207.322233796294</v>
       </c>
       <c r="F140" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J140" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K140" s="0" t="s">
         <v>25</v>
@@ -10157,13 +10208,13 @@
         <v>25</v>
       </c>
       <c r="O140" s="0">
-        <v>0</v>
-      </c>
-      <c r="P140" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q140" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P140" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q140" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R140" s="0" t="s">
         <v>25</v>
@@ -10178,27 +10229,27 @@
         <v>25</v>
       </c>
       <c r="V140" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C141" s="0">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="D141" s="1">
-        <v>46198.06826388889</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="E141" s="1">
-        <v>46198.06826388889</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="F141" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G141" s="0" t="s">
         <v>30</v>
@@ -10251,34 +10302,34 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C142" s="0">
-        <v>262</v>
+        <v>2108</v>
       </c>
       <c r="D142" s="1">
-        <v>46197.6375462963</v>
+        <v>46207.904699074075</v>
       </c>
       <c r="E142" s="1">
-        <v>46197.6375462963</v>
+        <v>46208.80619212963</v>
       </c>
       <c r="F142" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J142" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K142" s="0" t="s">
         <v>25</v>
@@ -10295,11 +10346,11 @@
       <c r="O142" s="0">
         <v>0</v>
       </c>
-      <c r="P142" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q142" s="0">
-        <v>0</v>
+      <c r="P142" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q142" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R142" s="0" t="s">
         <v>25</v>
@@ -10314,27 +10365,27 @@
         <v>25</v>
       </c>
       <c r="V142" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C143" s="0">
-        <v>304112</v>
+        <v>2123</v>
       </c>
       <c r="D143" s="1">
-        <v>46197.037523148145</v>
+        <v>46205.68171296296</v>
       </c>
       <c r="E143" s="1">
-        <v>46197.037523148145</v>
+        <v>46207.24060185185</v>
       </c>
       <c r="F143" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>30</v>
@@ -10343,10 +10394,10 @@
         <v>30</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J143" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K143" s="0" t="s">
         <v>25</v>
@@ -10363,11 +10414,11 @@
       <c r="O143" s="0">
         <v>1</v>
       </c>
-      <c r="P143" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q143" s="0">
-        <v>0</v>
+      <c r="P143" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q143" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R143" s="0" t="s">
         <v>25</v>
@@ -10387,22 +10438,22 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B144" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C144" s="0">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="D144" s="1">
-        <v>46197.12175925926</v>
+        <v>46199.41601851852</v>
       </c>
       <c r="E144" s="1">
-        <v>46198.31060185185</v>
+        <v>46202.50537037037</v>
       </c>
       <c r="F144" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>24</v>
@@ -10411,10 +10462,10 @@
         <v>24</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J144" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K144" s="0" t="s">
         <v>25</v>
@@ -10429,13 +10480,13 @@
         <v>25</v>
       </c>
       <c r="O144" s="0">
-        <v>1</v>
-      </c>
-      <c r="P144" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q144" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P144" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q144" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R144" s="0" t="s">
         <v>25</v>
@@ -10455,34 +10506,34 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C145" s="0">
-        <v>2009</v>
+        <v>0</v>
       </c>
       <c r="D145" s="1">
-        <v>46206.72038194445</v>
+        <v>46196.08100694444</v>
       </c>
       <c r="E145" s="1">
-        <v>46206.72038194445</v>
+        <v>46196.08100694444</v>
       </c>
       <c r="F145" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J145" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K145" s="0" t="s">
         <v>25</v>
@@ -10499,11 +10550,11 @@
       <c r="O145" s="0">
         <v>1</v>
       </c>
-      <c r="P145" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q145" s="0" t="s">
-        <v>25</v>
+      <c r="P145" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="0">
+        <v>1</v>
       </c>
       <c r="R145" s="0" t="s">
         <v>25</v>
@@ -10518,39 +10569,39 @@
         <v>25</v>
       </c>
       <c r="V145" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B146" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C146" s="0">
-        <v>2044</v>
+        <v>2518</v>
       </c>
       <c r="D146" s="1">
-        <v>46197.46810185185</v>
+        <v>46198.78761574074</v>
       </c>
       <c r="E146" s="1">
-        <v>46197.46810185185</v>
+        <v>46200.24690972222</v>
       </c>
       <c r="F146" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J146" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K146" s="0" t="s">
         <v>25</v>
@@ -10565,13 +10616,13 @@
         <v>25</v>
       </c>
       <c r="O146" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P146" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q146" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R146" s="0" t="s">
         <v>25</v>
@@ -10586,36 +10637,36 @@
         <v>25</v>
       </c>
       <c r="V146" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B147" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C147" s="0">
-        <v>2518</v>
+        <v>2099</v>
       </c>
       <c r="D147" s="1">
-        <v>46200.77527777778</v>
+        <v>46200.39493055556</v>
       </c>
       <c r="E147" s="1">
-        <v>46202.349328703705</v>
+        <v>46200.39493055556</v>
       </c>
       <c r="F147" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J147" s="0" t="s">
         <v>25</v>
@@ -10633,7 +10684,7 @@
         <v>25</v>
       </c>
       <c r="O147" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P147" s="0">
         <v>1</v>
@@ -10654,36 +10705,36 @@
         <v>25</v>
       </c>
       <c r="V147" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C148" s="0">
-        <v>0</v>
+        <v>2046</v>
       </c>
       <c r="D148" s="1">
-        <v>46198.75665509259</v>
+        <v>46200.55334490741</v>
       </c>
       <c r="E148" s="1">
-        <v>46198.75665509259</v>
+        <v>46201.81197916667</v>
       </c>
       <c r="F148" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J148" s="0" t="s">
         <v>25</v>
@@ -10701,10 +10752,10 @@
         <v>25</v>
       </c>
       <c r="O148" s="0">
-        <v>1</v>
-      </c>
-      <c r="P148" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P148" s="0">
+        <v>0</v>
       </c>
       <c r="Q148" s="0" t="s">
         <v>25</v>
@@ -10722,12 +10773,12 @@
         <v>25</v>
       </c>
       <c r="V148" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B149" s="0" t="s">
         <v>23</v>
@@ -10736,25 +10787,25 @@
         <v>2108</v>
       </c>
       <c r="D149" s="1">
-        <v>46205.784363425926</v>
+        <v>46196.56989583333</v>
       </c>
       <c r="E149" s="1">
-        <v>46205.784363425926</v>
+        <v>46196.87100694444</v>
       </c>
       <c r="F149" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J149" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K149" s="0" t="s">
         <v>25</v>
@@ -10769,13 +10820,13 @@
         <v>25</v>
       </c>
       <c r="O149" s="0">
-        <v>1</v>
-      </c>
-      <c r="P149" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q149" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P149" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="0">
+        <v>0</v>
       </c>
       <c r="R149" s="0" t="s">
         <v>25</v>
@@ -10790,12 +10841,12 @@
         <v>25</v>
       </c>
       <c r="V149" s="0" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B150" s="0" t="s">
         <v>29</v>
@@ -10804,13 +10855,13 @@
         <v>0</v>
       </c>
       <c r="D150" s="1">
-        <v>46198.75827546296</v>
+        <v>46203.38674768519</v>
       </c>
       <c r="E150" s="1">
-        <v>46198.75827546296</v>
+        <v>46203.38674768519</v>
       </c>
       <c r="F150" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>30</v>
@@ -10819,7 +10870,7 @@
         <v>30</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J150" s="0" t="s">
         <v>25</v>
@@ -10839,8 +10890,8 @@
       <c r="O150" s="0">
         <v>1</v>
       </c>
-      <c r="P150" s="0" t="s">
-        <v>25</v>
+      <c r="P150" s="0">
+        <v>0</v>
       </c>
       <c r="Q150" s="0" t="s">
         <v>25</v>
@@ -10863,31 +10914,31 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C151" s="0">
-        <v>2025</v>
+        <v>0</v>
       </c>
       <c r="D151" s="1">
-        <v>46203.80048611111</v>
+        <v>46199.38827546296</v>
       </c>
       <c r="E151" s="1">
-        <v>46203.80048611111</v>
+        <v>46199.38827546296</v>
       </c>
       <c r="F151" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J151" s="0" t="s">
         <v>25</v>
@@ -10907,8 +10958,8 @@
       <c r="O151" s="0">
         <v>1</v>
       </c>
-      <c r="P151" s="0" t="s">
-        <v>25</v>
+      <c r="P151" s="0">
+        <v>1</v>
       </c>
       <c r="Q151" s="0" t="s">
         <v>25</v>
@@ -10926,33 +10977,33 @@
         <v>25</v>
       </c>
       <c r="V151" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C152" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D152" s="1">
-        <v>46205.49758101852</v>
+        <v>46198.75832175926</v>
       </c>
       <c r="E152" s="1">
-        <v>46207.377118055556</v>
+        <v>46198.75832175926</v>
       </c>
       <c r="F152" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I152" s="0" t="s">
         <v>25</v>
@@ -10994,36 +11045,36 @@
         <v>25</v>
       </c>
       <c r="V152" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C153" s="0">
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="D153" s="1">
-        <v>46198.76320601852</v>
+        <v>46200.08666666667</v>
       </c>
       <c r="E153" s="1">
-        <v>46198.76320601852</v>
+        <v>46200.08666666667</v>
       </c>
       <c r="F153" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G153" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J153" s="0" t="s">
         <v>25</v>
@@ -11043,8 +11094,8 @@
       <c r="O153" s="0">
         <v>1</v>
       </c>
-      <c r="P153" s="0" t="s">
-        <v>25</v>
+      <c r="P153" s="0">
+        <v>0</v>
       </c>
       <c r="Q153" s="0" t="s">
         <v>25</v>
@@ -11062,27 +11113,27 @@
         <v>25</v>
       </c>
       <c r="V153" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C154" s="0">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="D154" s="1">
-        <v>46198.76327546296</v>
+        <v>46191.19981481481</v>
       </c>
       <c r="E154" s="1">
-        <v>46198.76327546296</v>
+        <v>46191.20039351852</v>
       </c>
       <c r="F154" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>30</v>
@@ -11091,10 +11142,10 @@
         <v>30</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J154" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K154" s="0" t="s">
         <v>25</v>
@@ -11109,13 +11160,13 @@
         <v>25</v>
       </c>
       <c r="O154" s="0">
-        <v>1</v>
-      </c>
-      <c r="P154" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q154" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P154" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q154" s="0">
+        <v>0</v>
       </c>
       <c r="R154" s="0" t="s">
         <v>25</v>
@@ -11135,22 +11186,22 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C155" s="0">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="D155" s="1">
-        <v>46197.041238425925</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="E155" s="1">
-        <v>46197.041238425925</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="F155" s="1">
-        <v>46209.0422787037</v>
+        <v>46210.042245717596</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>30</v>
@@ -11159,10 +11210,10 @@
         <v>30</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J155" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K155" s="0" t="s">
         <v>25</v>
@@ -11179,11 +11230,11 @@
       <c r="O155" s="0">
         <v>1</v>
       </c>
-      <c r="P155" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q155" s="0">
-        <v>0</v>
+      <c r="P155" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q155" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R155" s="0" t="s">
         <v>25</v>
@@ -11203,69 +11254,1157 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C156" s="0">
         <v>262</v>
       </c>
       <c r="D156" s="1">
+        <v>46197.6375462963</v>
+      </c>
+      <c r="E156" s="1">
+        <v>46197.6375462963</v>
+      </c>
+      <c r="F156" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G156" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H156" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I156" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J156" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K156" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L156" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M156" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N156" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O156" s="0">
+        <v>0</v>
+      </c>
+      <c r="P156" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q156" s="0">
+        <v>0</v>
+      </c>
+      <c r="R156" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S156" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T156" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U156" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V156" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B157" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C157" s="0">
+        <v>304112</v>
+      </c>
+      <c r="D157" s="1">
+        <v>46197.037523148145</v>
+      </c>
+      <c r="E157" s="1">
+        <v>46197.037523148145</v>
+      </c>
+      <c r="F157" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G157" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H157" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I157" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J157" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K157" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L157" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M157" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N157" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O157" s="0">
+        <v>1</v>
+      </c>
+      <c r="P157" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q157" s="0">
+        <v>0</v>
+      </c>
+      <c r="R157" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S157" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T157" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U157" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V157" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="B158" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C158" s="0">
+        <v>2106</v>
+      </c>
+      <c r="D158" s="1">
+        <v>46197.12175925926</v>
+      </c>
+      <c r="E158" s="1">
+        <v>46198.31060185185</v>
+      </c>
+      <c r="F158" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G158" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H158" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I158" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="J158" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="K158" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L158" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M158" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N158" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O158" s="0">
+        <v>1</v>
+      </c>
+      <c r="P158" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q158" s="0">
+        <v>0</v>
+      </c>
+      <c r="R158" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S158" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T158" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U158" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V158" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="B159" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C159" s="0">
+        <v>2108</v>
+      </c>
+      <c r="D159" s="1">
+        <v>46202.840995370374</v>
+      </c>
+      <c r="E159" s="1">
+        <v>46209.31466435185</v>
+      </c>
+      <c r="F159" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G159" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H159" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O159" s="0">
+        <v>0</v>
+      </c>
+      <c r="P159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U159" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V159" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B160" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C160" s="0">
+        <v>2009</v>
+      </c>
+      <c r="D160" s="1">
+        <v>46206.72038194445</v>
+      </c>
+      <c r="E160" s="1">
+        <v>46206.72038194445</v>
+      </c>
+      <c r="F160" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G160" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H160" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O160" s="0">
+        <v>1</v>
+      </c>
+      <c r="P160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U160" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V160" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B161" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C161" s="0">
+        <v>2044</v>
+      </c>
+      <c r="D161" s="1">
+        <v>46197.46810185185</v>
+      </c>
+      <c r="E161" s="1">
+        <v>46197.46810185185</v>
+      </c>
+      <c r="F161" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G161" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H161" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I161" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J161" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K161" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L161" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M161" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N161" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O161" s="0">
+        <v>0</v>
+      </c>
+      <c r="P161" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q161" s="0">
+        <v>1</v>
+      </c>
+      <c r="R161" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S161" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T161" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U161" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V161" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B162" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C162" s="0">
+        <v>2518</v>
+      </c>
+      <c r="D162" s="1">
+        <v>46200.77527777778</v>
+      </c>
+      <c r="E162" s="1">
+        <v>46202.349328703705</v>
+      </c>
+      <c r="F162" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G162" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H162" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I162" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="J162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O162" s="0">
+        <v>1</v>
+      </c>
+      <c r="P162" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V162" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B163" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C163" s="0">
+        <v>0</v>
+      </c>
+      <c r="D163" s="1">
+        <v>46198.75665509259</v>
+      </c>
+      <c r="E163" s="1">
+        <v>46198.75665509259</v>
+      </c>
+      <c r="F163" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G163" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H163" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O163" s="0">
+        <v>1</v>
+      </c>
+      <c r="P163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U163" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V163" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="B164" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C164" s="0">
+        <v>2108</v>
+      </c>
+      <c r="D164" s="1">
+        <v>46205.784363425926</v>
+      </c>
+      <c r="E164" s="1">
+        <v>46205.784363425926</v>
+      </c>
+      <c r="F164" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G164" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="H164" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O164" s="0">
+        <v>1</v>
+      </c>
+      <c r="P164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U164" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V164" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="B165" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C165" s="0">
+        <v>0</v>
+      </c>
+      <c r="D165" s="1">
+        <v>46198.75827546296</v>
+      </c>
+      <c r="E165" s="1">
+        <v>46198.75827546296</v>
+      </c>
+      <c r="F165" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G165" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H165" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O165" s="0">
+        <v>1</v>
+      </c>
+      <c r="P165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U165" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V165" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B166" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C166" s="0">
+        <v>2025</v>
+      </c>
+      <c r="D166" s="1">
+        <v>46203.80048611111</v>
+      </c>
+      <c r="E166" s="1">
+        <v>46203.80048611111</v>
+      </c>
+      <c r="F166" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G166" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="H166" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O166" s="0">
+        <v>1</v>
+      </c>
+      <c r="P166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U166" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V166" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="B167" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C167" s="0">
+        <v>2108</v>
+      </c>
+      <c r="D167" s="1">
+        <v>46205.49758101852</v>
+      </c>
+      <c r="E167" s="1">
+        <v>46207.377118055556</v>
+      </c>
+      <c r="F167" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G167" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H167" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O167" s="0">
+        <v>1</v>
+      </c>
+      <c r="P167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U167" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V167" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="B168" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C168" s="0">
+        <v>0</v>
+      </c>
+      <c r="D168" s="1">
+        <v>46198.76320601852</v>
+      </c>
+      <c r="E168" s="1">
+        <v>46198.76320601852</v>
+      </c>
+      <c r="F168" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G168" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H168" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O168" s="0">
+        <v>1</v>
+      </c>
+      <c r="P168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U168" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V168" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="B169" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C169" s="0">
+        <v>205</v>
+      </c>
+      <c r="D169" s="1">
+        <v>46207.94667824074</v>
+      </c>
+      <c r="E169" s="1">
+        <v>46209.364849537036</v>
+      </c>
+      <c r="F169" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G169" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="H169" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O169" s="0">
+        <v>1</v>
+      </c>
+      <c r="P169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U169" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V169" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="B170" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C170" s="0">
+        <v>0</v>
+      </c>
+      <c r="D170" s="1">
+        <v>46198.76327546296</v>
+      </c>
+      <c r="E170" s="1">
+        <v>46198.76327546296</v>
+      </c>
+      <c r="F170" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G170" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H170" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O170" s="0">
+        <v>1</v>
+      </c>
+      <c r="P170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U170" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V170" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="B171" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C171" s="0">
+        <v>312</v>
+      </c>
+      <c r="D171" s="1">
+        <v>46197.041238425925</v>
+      </c>
+      <c r="E171" s="1">
+        <v>46197.041238425925</v>
+      </c>
+      <c r="F171" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G171" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H171" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I171" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J171" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K171" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L171" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M171" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N171" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O171" s="0">
+        <v>1</v>
+      </c>
+      <c r="P171" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q171" s="0">
+        <v>0</v>
+      </c>
+      <c r="R171" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S171" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T171" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U171" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V171" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="B172" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C172" s="0">
+        <v>262</v>
+      </c>
+      <c r="D172" s="1">
         <v>46200.44310185185</v>
       </c>
-      <c r="E156" s="1">
+      <c r="E172" s="1">
         <v>46200.44310185185</v>
       </c>
-      <c r="F156" s="1">
-        <v>46209.0422787037</v>
-      </c>
-      <c r="G156" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="H156" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="I156" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="J156" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="K156" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="L156" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="M156" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="N156" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="O156" s="0">
-        <v>0</v>
-      </c>
-      <c r="P156" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q156" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="R156" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="S156" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="T156" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="U156" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="V156" s="0" t="s">
+      <c r="F172" s="1">
+        <v>46210.042245717596</v>
+      </c>
+      <c r="G172" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H172" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I172" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O172" s="0">
+        <v>0</v>
+      </c>
+      <c r="P172" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V172" s="0" t="s">
         <v>30</v>
       </c>
     </row>

--- a/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
+++ b/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
   <si>
     <t>SampleId</t>
   </si>
@@ -155,6 +155,9 @@
     <t>Zeroday</t>
   </si>
   <si>
+    <t>172b21604f73456bb7683f2d09c05b11</t>
+  </si>
+  <si>
     <t>1762f1e64b02fdd3fb1c4a6b5b467da8</t>
   </si>
   <si>
@@ -230,6 +233,9 @@
     <t>39405427788c2e852b92a99d4ef76181</t>
   </si>
   <si>
+    <t>3a5ec316e07a3d72055c719b420af810</t>
+  </si>
+  <si>
     <t>3ac8eda39e07f2cfe49d3fb4c61b26e6</t>
   </si>
   <si>
@@ -254,6 +260,9 @@
     <t>4035ac82d429ada4ad1e42ae2446c33a</t>
   </si>
   <si>
+    <t>446d01880200c96109ae6585367efdb6</t>
+  </si>
+  <si>
     <t>46e6ba41020b4d3b10e6494f571acf19</t>
   </si>
   <si>
@@ -380,6 +389,9 @@
     <t>79667d1731ee4f94ef0173328c623cbf</t>
   </si>
   <si>
+    <t>7a58f6a326b1b174097d45703a3a0dc7</t>
+  </si>
+  <si>
     <t>7a81a930e55f40fbfee093e2ce0fd878</t>
   </si>
   <si>
@@ -413,6 +425,9 @@
     <t>8bbd11bfa46879289844ded98b5c368f</t>
   </si>
   <si>
+    <t>8bc6d67b0f4291eb88fe876181a4fc4d</t>
+  </si>
+  <si>
     <t>8bfbe54fe78bc6a4c9b5e3dc23499b1e</t>
   </si>
   <si>
@@ -434,6 +449,9 @@
     <t>921835b9cd71bae983e0800e08d509b4</t>
   </si>
   <si>
+    <t>928d342defdb0ee8a82d30c20ab6d27f</t>
+  </si>
+  <si>
     <t>9564066d7cabda4c95ad12903c010cb9</t>
   </si>
   <si>
@@ -452,6 +470,9 @@
     <t>a9046fe09317aec821cc5cff20305c80</t>
   </si>
   <si>
+    <t>aa4fae1ba7d3627f356175068b213630</t>
+  </si>
+  <si>
     <t>ad2616c73daeab5a5792df3bc75540df</t>
   </si>
   <si>
@@ -465,6 +486,9 @@
   </si>
   <si>
     <t>b5f95c9417be43523a136c5701bb3917</t>
+  </si>
+  <si>
+    <t>b75ea0f64802a6465addc942868b2728</t>
   </si>
   <si>
     <t>b9c866b7b67700406dd9361529f6b01b</t>
@@ -671,8 +695,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AicsGlobal_Classifications_TimeWindows" displayName="AicsGlobal_Classifications_TimeWindows" ref="A1:V172" headerRowCount="1">
-  <autoFilter ref="A1:V172"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AicsGlobal_Classifications_TimeWindows" displayName="AicsGlobal_Classifications_TimeWindows" ref="A1:V180" headerRowCount="1">
+  <autoFilter ref="A1:V180"/>
   <tableColumns count="22">
     <tableColumn id="1" name="SampleId"/>
     <tableColumn id="2" name="SIGDetection"/>
@@ -703,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:V172"/>
+  <dimension ref="A1:V180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.540952682495117" customWidth="1"/>
@@ -797,7 +821,7 @@
         <v>46204.34583333333</v>
       </c>
       <c r="F2" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>24</v>
@@ -865,7 +889,7 @@
         <v>46207.15827546296</v>
       </c>
       <c r="F3" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>24</v>
@@ -933,7 +957,7 @@
         <v>46200.30415509259</v>
       </c>
       <c r="F4" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>24</v>
@@ -945,7 +969,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>25</v>
@@ -965,8 +989,8 @@
       <c r="P4" s="0">
         <v>0</v>
       </c>
-      <c r="Q4" s="0" t="s">
-        <v>25</v>
+      <c r="Q4" s="0">
+        <v>0</v>
       </c>
       <c r="R4" s="0" t="s">
         <v>25</v>
@@ -1001,7 +1025,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F5" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>30</v>
@@ -1069,7 +1093,7 @@
         <v>46198.75680555555</v>
       </c>
       <c r="F6" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>30</v>
@@ -1137,7 +1161,7 @@
         <v>46200.02773148148</v>
       </c>
       <c r="F7" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>24</v>
@@ -1205,7 +1229,7 @@
         <v>46200.57623842593</v>
       </c>
       <c r="F8" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>24</v>
@@ -1217,7 +1241,7 @@
         <v>24</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K8" s="0" t="s">
         <v>25</v>
@@ -1237,8 +1261,8 @@
       <c r="P8" s="0">
         <v>0</v>
       </c>
-      <c r="Q8" s="0" t="s">
-        <v>25</v>
+      <c r="Q8" s="0">
+        <v>0</v>
       </c>
       <c r="R8" s="0" t="s">
         <v>25</v>
@@ -1273,7 +1297,7 @@
         <v>46198.764027777775</v>
       </c>
       <c r="F9" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>30</v>
@@ -1341,7 +1365,7 @@
         <v>46198.18491898148</v>
       </c>
       <c r="F10" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>24</v>
@@ -1409,7 +1433,7 @@
         <v>46203.81460648148</v>
       </c>
       <c r="F11" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>39</v>
@@ -1477,7 +1501,7 @@
         <v>46201.33733796296</v>
       </c>
       <c r="F12" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>24</v>
@@ -1489,7 +1513,7 @@
         <v>24</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12" s="0" t="s">
         <v>25</v>
@@ -1509,8 +1533,8 @@
       <c r="P12" s="0">
         <v>1</v>
       </c>
-      <c r="Q12" s="0" t="s">
-        <v>25</v>
+      <c r="Q12" s="0">
+        <v>0</v>
       </c>
       <c r="R12" s="0" t="s">
         <v>25</v>
@@ -1545,7 +1569,7 @@
         <v>46203.71907407408</v>
       </c>
       <c r="F13" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>24</v>
@@ -1613,7 +1637,7 @@
         <v>46195.59105324074</v>
       </c>
       <c r="F14" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>30</v>
@@ -1681,7 +1705,7 @@
         <v>46201.06361111111</v>
       </c>
       <c r="F15" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>24</v>
@@ -1749,7 +1773,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F16" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>30</v>
@@ -1817,7 +1841,7 @@
         <v>46198.5140625</v>
       </c>
       <c r="F17" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G17" s="0" t="s">
         <v>30</v>
@@ -1847,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="0" t="s">
         <v>25</v>
@@ -1876,25 +1900,25 @@
         <v>23</v>
       </c>
       <c r="C18" s="0">
-        <v>2108</v>
+        <v>2518</v>
       </c>
       <c r="D18" s="1">
-        <v>46200.81953703704</v>
+        <v>46209.61792824074</v>
       </c>
       <c r="E18" s="1">
-        <v>46202.38591435185</v>
+        <v>46209.61792824074</v>
       </c>
       <c r="F18" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>25</v>
@@ -1914,8 +1938,8 @@
       <c r="O18" s="0">
         <v>1</v>
       </c>
-      <c r="P18" s="0">
-        <v>1</v>
+      <c r="P18" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q18" s="0" t="s">
         <v>25</v>
@@ -1933,7 +1957,7 @@
         <v>25</v>
       </c>
       <c r="V18" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1941,28 +1965,28 @@
         <v>48</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C19" s="0">
-        <v>344</v>
+        <v>2108</v>
       </c>
       <c r="D19" s="1">
-        <v>46203.665925925925</v>
+        <v>46200.81953703704</v>
       </c>
       <c r="E19" s="1">
-        <v>46203.665925925925</v>
+        <v>46202.38591435185</v>
       </c>
       <c r="F19" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J19" s="0" t="s">
         <v>25</v>
@@ -1982,8 +2006,8 @@
       <c r="O19" s="0">
         <v>1</v>
       </c>
-      <c r="P19" s="0" t="s">
-        <v>25</v>
+      <c r="P19" s="0">
+        <v>1</v>
       </c>
       <c r="Q19" s="0" t="s">
         <v>25</v>
@@ -2001,7 +2025,7 @@
         <v>25</v>
       </c>
       <c r="V19" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -2009,28 +2033,28 @@
         <v>49</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C20" s="0">
-        <v>13108</v>
+        <v>344</v>
       </c>
       <c r="D20" s="1">
-        <v>46204.75709490741</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="E20" s="1">
-        <v>46205.25707175926</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="F20" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>25</v>
@@ -2050,8 +2074,8 @@
       <c r="O20" s="0">
         <v>1</v>
       </c>
-      <c r="P20" s="0">
-        <v>0</v>
+      <c r="P20" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q20" s="0" t="s">
         <v>25</v>
@@ -2069,7 +2093,7 @@
         <v>25</v>
       </c>
       <c r="V20" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -2077,19 +2101,19 @@
         <v>50</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C21" s="0">
-        <v>2025</v>
+        <v>13108</v>
       </c>
       <c r="D21" s="1">
-        <v>46202.91679398148</v>
+        <v>46204.75709490741</v>
       </c>
       <c r="E21" s="1">
-        <v>46204.23569444445</v>
+        <v>46205.25707175926</v>
       </c>
       <c r="F21" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G21" s="0" t="s">
         <v>24</v>
@@ -2116,10 +2140,10 @@
         <v>25</v>
       </c>
       <c r="O21" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="0" t="s">
         <v>25</v>
@@ -2148,25 +2172,25 @@
         <v>23</v>
       </c>
       <c r="C22" s="0">
-        <v>2521</v>
+        <v>2025</v>
       </c>
       <c r="D22" s="1">
-        <v>46203.711377314816</v>
+        <v>46202.91679398148</v>
       </c>
       <c r="E22" s="1">
-        <v>46206.293020833335</v>
+        <v>46204.23569444445</v>
       </c>
       <c r="F22" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>25</v>
@@ -2184,10 +2208,10 @@
         <v>25</v>
       </c>
       <c r="O22" s="0">
-        <v>1</v>
-      </c>
-      <c r="P22" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P22" s="0">
+        <v>1</v>
       </c>
       <c r="Q22" s="0" t="s">
         <v>25</v>
@@ -2205,7 +2229,7 @@
         <v>25</v>
       </c>
       <c r="V22" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -2213,25 +2237,25 @@
         <v>52</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C23" s="0">
-        <v>0</v>
+        <v>2521</v>
       </c>
       <c r="D23" s="1">
-        <v>46198.763715277775</v>
+        <v>46203.711377314816</v>
       </c>
       <c r="E23" s="1">
-        <v>46198.763715277775</v>
+        <v>46206.293020833335</v>
       </c>
       <c r="F23" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>25</v>
@@ -2273,7 +2297,7 @@
         <v>25</v>
       </c>
       <c r="V23" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
@@ -2281,25 +2305,25 @@
         <v>53</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C24" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D24" s="1">
-        <v>46205.502962962964</v>
+        <v>46198.763715277775</v>
       </c>
       <c r="E24" s="1">
-        <v>46205.502962962964</v>
+        <v>46198.763715277775</v>
       </c>
       <c r="F24" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>25</v>
@@ -2320,7 +2344,7 @@
         <v>25</v>
       </c>
       <c r="O24" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="0" t="s">
         <v>25</v>
@@ -2341,7 +2365,7 @@
         <v>25</v>
       </c>
       <c r="V24" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -2349,28 +2373,28 @@
         <v>54</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C25" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D25" s="1">
-        <v>46198.06826388889</v>
+        <v>46205.502962962964</v>
       </c>
       <c r="E25" s="1">
-        <v>46200.67046296296</v>
+        <v>46205.502962962964</v>
       </c>
       <c r="F25" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>25</v>
@@ -2388,10 +2412,10 @@
         <v>25</v>
       </c>
       <c r="O25" s="0">
-        <v>1</v>
-      </c>
-      <c r="P25" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P25" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q25" s="0" t="s">
         <v>25</v>
@@ -2409,7 +2433,7 @@
         <v>25</v>
       </c>
       <c r="V25" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -2417,31 +2441,31 @@
         <v>55</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C26" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D26" s="1">
-        <v>46199.574282407404</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="E26" s="1">
-        <v>46199.574282407404</v>
+        <v>46200.67046296296</v>
       </c>
       <c r="F26" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K26" s="0" t="s">
         <v>25</v>
@@ -2461,8 +2485,8 @@
       <c r="P26" s="0">
         <v>0</v>
       </c>
-      <c r="Q26" s="0">
-        <v>0</v>
+      <c r="Q26" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R26" s="0" t="s">
         <v>25</v>
@@ -2477,7 +2501,7 @@
         <v>25</v>
       </c>
       <c r="V26" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -2485,31 +2509,31 @@
         <v>56</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C27" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D27" s="1">
-        <v>46198.758518518516</v>
+        <v>46199.574282407404</v>
       </c>
       <c r="E27" s="1">
-        <v>46198.758518518516</v>
+        <v>46199.574282407404</v>
       </c>
       <c r="F27" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K27" s="0" t="s">
         <v>25</v>
@@ -2526,11 +2550,11 @@
       <c r="O27" s="0">
         <v>1</v>
       </c>
-      <c r="P27" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q27" s="0" t="s">
-        <v>25</v>
+      <c r="P27" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="0">
+        <v>0</v>
       </c>
       <c r="R27" s="0" t="s">
         <v>25</v>
@@ -2545,7 +2569,7 @@
         <v>25</v>
       </c>
       <c r="V27" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -2553,31 +2577,31 @@
         <v>57</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C28" s="0">
-        <v>13108</v>
+        <v>0</v>
       </c>
       <c r="D28" s="1">
-        <v>46197.86509259259</v>
+        <v>46198.758518518516</v>
       </c>
       <c r="E28" s="1">
-        <v>46199.20893518518</v>
+        <v>46198.758518518516</v>
       </c>
       <c r="F28" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K28" s="0" t="s">
         <v>25</v>
@@ -2594,11 +2618,11 @@
       <c r="O28" s="0">
         <v>1</v>
       </c>
-      <c r="P28" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="0">
-        <v>0</v>
+      <c r="P28" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R28" s="0" t="s">
         <v>25</v>
@@ -2613,7 +2637,7 @@
         <v>25</v>
       </c>
       <c r="V28" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
@@ -2621,31 +2645,31 @@
         <v>58</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C29" s="0">
-        <v>0</v>
+        <v>13108</v>
       </c>
       <c r="D29" s="1">
-        <v>46198.76384259259</v>
+        <v>46197.86509259259</v>
       </c>
       <c r="E29" s="1">
-        <v>46198.76384259259</v>
+        <v>46199.20893518518</v>
       </c>
       <c r="F29" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K29" s="0" t="s">
         <v>25</v>
@@ -2662,11 +2686,11 @@
       <c r="O29" s="0">
         <v>1</v>
       </c>
-      <c r="P29" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q29" s="0" t="s">
-        <v>25</v>
+      <c r="P29" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="0">
+        <v>0</v>
       </c>
       <c r="R29" s="0" t="s">
         <v>25</v>
@@ -2681,7 +2705,7 @@
         <v>25</v>
       </c>
       <c r="V29" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -2689,25 +2713,25 @@
         <v>59</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C30" s="0">
-        <v>2046</v>
+        <v>0</v>
       </c>
       <c r="D30" s="1">
-        <v>46207.86888888889</v>
+        <v>46198.76384259259</v>
       </c>
       <c r="E30" s="1">
-        <v>46207.98546296296</v>
+        <v>46198.76384259259</v>
       </c>
       <c r="F30" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I30" s="0" t="s">
         <v>25</v>
@@ -2749,7 +2773,7 @@
         <v>25</v>
       </c>
       <c r="V30" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -2757,25 +2781,25 @@
         <v>60</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C31" s="0">
-        <v>0</v>
+        <v>2046</v>
       </c>
       <c r="D31" s="1">
-        <v>46198.758414351854</v>
+        <v>46207.86888888889</v>
       </c>
       <c r="E31" s="1">
-        <v>46198.758414351854</v>
+        <v>46207.98546296296</v>
       </c>
       <c r="F31" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I31" s="0" t="s">
         <v>25</v>
@@ -2817,7 +2841,7 @@
         <v>25</v>
       </c>
       <c r="V31" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -2825,28 +2849,28 @@
         <v>61</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C32" s="0">
-        <v>2123</v>
+        <v>0</v>
       </c>
       <c r="D32" s="1">
-        <v>46194.2578587963</v>
+        <v>46198.758414351854</v>
       </c>
       <c r="E32" s="1">
-        <v>46194.2578587963</v>
+        <v>46198.758414351854</v>
       </c>
       <c r="F32" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>25</v>
@@ -2866,8 +2890,8 @@
       <c r="O32" s="0">
         <v>1</v>
       </c>
-      <c r="P32" s="0">
-        <v>1</v>
+      <c r="P32" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q32" s="0" t="s">
         <v>25</v>
@@ -2885,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="V32" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -2893,31 +2917,31 @@
         <v>62</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C33" s="0">
-        <v>0</v>
+        <v>2123</v>
       </c>
       <c r="D33" s="1">
-        <v>46197.83574074074</v>
+        <v>46194.2578587963</v>
       </c>
       <c r="E33" s="1">
-        <v>46197.83574074074</v>
+        <v>46194.2578587963</v>
       </c>
       <c r="F33" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K33" s="0" t="s">
         <v>25</v>
@@ -2935,10 +2959,10 @@
         <v>1</v>
       </c>
       <c r="P33" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="Q33" s="0">
+        <v>0</v>
       </c>
       <c r="R33" s="0" t="s">
         <v>25</v>
@@ -2953,7 +2977,7 @@
         <v>25</v>
       </c>
       <c r="V33" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -2967,13 +2991,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="1">
-        <v>46198.763449074075</v>
+        <v>46197.83574074074</v>
       </c>
       <c r="E34" s="1">
-        <v>46198.763449074075</v>
+        <v>46197.83574074074</v>
       </c>
       <c r="F34" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>30</v>
@@ -2982,7 +3006,7 @@
         <v>30</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>25</v>
@@ -3002,8 +3026,8 @@
       <c r="O34" s="0">
         <v>1</v>
       </c>
-      <c r="P34" s="0" t="s">
-        <v>25</v>
+      <c r="P34" s="0">
+        <v>0</v>
       </c>
       <c r="Q34" s="0" t="s">
         <v>25</v>
@@ -3035,13 +3059,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="1">
-        <v>46198.758125</v>
+        <v>46198.763449074075</v>
       </c>
       <c r="E35" s="1">
-        <v>46198.758125</v>
+        <v>46198.763449074075</v>
       </c>
       <c r="F35" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>30</v>
@@ -3097,28 +3121,28 @@
         <v>65</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C36" s="0">
-        <v>2106</v>
+        <v>0</v>
       </c>
       <c r="D36" s="1">
-        <v>46201.54498842593</v>
+        <v>46198.758125</v>
       </c>
       <c r="E36" s="1">
-        <v>46201.54498842593</v>
+        <v>46198.758125</v>
       </c>
       <c r="F36" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>25</v>
@@ -3136,10 +3160,10 @@
         <v>25</v>
       </c>
       <c r="O36" s="0">
-        <v>0</v>
-      </c>
-      <c r="P36" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P36" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q36" s="0" t="s">
         <v>25</v>
@@ -3157,7 +3181,7 @@
         <v>25</v>
       </c>
       <c r="V36" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
@@ -3165,28 +3189,28 @@
         <v>66</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C37" s="0">
-        <v>0</v>
+        <v>2106</v>
       </c>
       <c r="D37" s="1">
-        <v>46198.76478009259</v>
+        <v>46201.54498842593</v>
       </c>
       <c r="E37" s="1">
-        <v>46198.76478009259</v>
+        <v>46201.54498842593</v>
       </c>
       <c r="F37" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>25</v>
@@ -3204,10 +3228,10 @@
         <v>25</v>
       </c>
       <c r="O37" s="0">
-        <v>1</v>
-      </c>
-      <c r="P37" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P37" s="0">
+        <v>0</v>
       </c>
       <c r="Q37" s="0" t="s">
         <v>25</v>
@@ -3225,7 +3249,7 @@
         <v>25</v>
       </c>
       <c r="V37" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -3233,25 +3257,25 @@
         <v>67</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C38" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D38" s="1">
-        <v>46204.26725694445</v>
+        <v>46198.76478009259</v>
       </c>
       <c r="E38" s="1">
-        <v>46205.76315972222</v>
+        <v>46198.76478009259</v>
       </c>
       <c r="F38" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I38" s="0" t="s">
         <v>25</v>
@@ -3272,7 +3296,7 @@
         <v>25</v>
       </c>
       <c r="O38" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" s="0" t="s">
         <v>25</v>
@@ -3293,7 +3317,7 @@
         <v>25</v>
       </c>
       <c r="V38" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -3307,13 +3331,13 @@
         <v>2108</v>
       </c>
       <c r="D39" s="1">
-        <v>46203.412881944445</v>
+        <v>46204.26725694445</v>
       </c>
       <c r="E39" s="1">
-        <v>46204.83986111111</v>
+        <v>46205.76315972222</v>
       </c>
       <c r="F39" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>24</v>
@@ -3322,7 +3346,7 @@
         <v>24</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J39" s="0" t="s">
         <v>25</v>
@@ -3342,8 +3366,8 @@
       <c r="O39" s="0">
         <v>0</v>
       </c>
-      <c r="P39" s="0">
-        <v>0</v>
+      <c r="P39" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q39" s="0" t="s">
         <v>25</v>
@@ -3372,25 +3396,25 @@
         <v>23</v>
       </c>
       <c r="C40" s="0">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="D40" s="1">
-        <v>46202.94956018519</v>
+        <v>46203.412881944445</v>
       </c>
       <c r="E40" s="1">
-        <v>46203.69975694444</v>
+        <v>46204.83986111111</v>
       </c>
       <c r="F40" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J40" s="0" t="s">
         <v>25</v>
@@ -3408,10 +3432,10 @@
         <v>25</v>
       </c>
       <c r="O40" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="0" t="s">
         <v>25</v>
@@ -3429,7 +3453,7 @@
         <v>25</v>
       </c>
       <c r="V40" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
@@ -3440,25 +3464,25 @@
         <v>23</v>
       </c>
       <c r="C41" s="0">
-        <v>2114</v>
+        <v>2106</v>
       </c>
       <c r="D41" s="1">
-        <v>46206.98871527778</v>
+        <v>46202.94956018519</v>
       </c>
       <c r="E41" s="1">
-        <v>46208.10663194444</v>
+        <v>46203.69975694444</v>
       </c>
       <c r="F41" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J41" s="0" t="s">
         <v>25</v>
@@ -3476,10 +3500,10 @@
         <v>25</v>
       </c>
       <c r="O41" s="0">
-        <v>0</v>
-      </c>
-      <c r="P41" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P41" s="0">
+        <v>1</v>
       </c>
       <c r="Q41" s="0" t="s">
         <v>25</v>
@@ -3497,7 +3521,7 @@
         <v>25</v>
       </c>
       <c r="V41" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
@@ -3505,28 +3529,28 @@
         <v>71</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C42" s="0">
-        <v>337</v>
+        <v>2114</v>
       </c>
       <c r="D42" s="1">
-        <v>46200.844143518516</v>
+        <v>46206.98871527778</v>
       </c>
       <c r="E42" s="1">
-        <v>46200.854166666664</v>
+        <v>46208.10663194444</v>
       </c>
       <c r="F42" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J42" s="0" t="s">
         <v>25</v>
@@ -3544,10 +3568,10 @@
         <v>25</v>
       </c>
       <c r="O42" s="0">
-        <v>1</v>
-      </c>
-      <c r="P42" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P42" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q42" s="0" t="s">
         <v>25</v>
@@ -3565,7 +3589,7 @@
         <v>25</v>
       </c>
       <c r="V42" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43">
@@ -3573,19 +3597,19 @@
         <v>72</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C43" s="0">
-        <v>702049</v>
+        <v>337</v>
       </c>
       <c r="D43" s="1">
-        <v>46204.145219907405</v>
+        <v>46200.844143518516</v>
       </c>
       <c r="E43" s="1">
-        <v>46204.145219907405</v>
+        <v>46200.854166666664</v>
       </c>
       <c r="F43" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>30</v>
@@ -3594,10 +3618,10 @@
         <v>30</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K43" s="0" t="s">
         <v>25</v>
@@ -3612,13 +3636,13 @@
         <v>25</v>
       </c>
       <c r="O43" s="0">
-        <v>0</v>
-      </c>
-      <c r="P43" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q43" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P43" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="0">
+        <v>0</v>
       </c>
       <c r="R43" s="0" t="s">
         <v>25</v>
@@ -3647,13 +3671,13 @@
         <v>262</v>
       </c>
       <c r="D44" s="1">
-        <v>46191.31182870371</v>
+        <v>46205.07099537037</v>
       </c>
       <c r="E44" s="1">
-        <v>46191.31182870371</v>
+        <v>46205.07099537037</v>
       </c>
       <c r="F44" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>30</v>
@@ -3662,10 +3686,10 @@
         <v>30</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K44" s="0" t="s">
         <v>25</v>
@@ -3680,13 +3704,13 @@
         <v>25</v>
       </c>
       <c r="O44" s="0">
-        <v>1</v>
-      </c>
-      <c r="P44" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q44" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P44" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q44" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R44" s="0" t="s">
         <v>25</v>
@@ -3709,31 +3733,31 @@
         <v>74</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C45" s="0">
-        <v>2108</v>
+        <v>702049</v>
       </c>
       <c r="D45" s="1">
-        <v>46198.00052083333</v>
+        <v>46204.145219907405</v>
       </c>
       <c r="E45" s="1">
-        <v>46199.29518518518</v>
+        <v>46204.145219907405</v>
       </c>
       <c r="F45" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K45" s="0" t="s">
         <v>25</v>
@@ -3750,11 +3774,11 @@
       <c r="O45" s="0">
         <v>1</v>
       </c>
-      <c r="P45" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="0">
-        <v>0</v>
+      <c r="P45" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q45" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R45" s="0" t="s">
         <v>25</v>
@@ -3769,7 +3793,7 @@
         <v>25</v>
       </c>
       <c r="V45" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
@@ -3777,19 +3801,19 @@
         <v>75</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C46" s="0">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="D46" s="1">
-        <v>46198.758576388886</v>
+        <v>46191.31182870371</v>
       </c>
       <c r="E46" s="1">
-        <v>46198.758576388886</v>
+        <v>46191.31182870371</v>
       </c>
       <c r="F46" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>30</v>
@@ -3798,10 +3822,10 @@
         <v>30</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J46" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K46" s="0" t="s">
         <v>25</v>
@@ -3818,11 +3842,11 @@
       <c r="O46" s="0">
         <v>1</v>
       </c>
-      <c r="P46" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q46" s="0" t="s">
-        <v>25</v>
+      <c r="P46" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="0">
+        <v>0</v>
       </c>
       <c r="R46" s="0" t="s">
         <v>25</v>
@@ -3845,31 +3869,31 @@
         <v>76</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C47" s="0">
-        <v>305</v>
+        <v>2108</v>
       </c>
       <c r="D47" s="1">
-        <v>46192.00283564815</v>
+        <v>46198.00052083333</v>
       </c>
       <c r="E47" s="1">
-        <v>46196.6612962963</v>
+        <v>46199.29518518518</v>
       </c>
       <c r="F47" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K47" s="0" t="s">
         <v>25</v>
@@ -3887,10 +3911,10 @@
         <v>1</v>
       </c>
       <c r="P47" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="0" t="s">
         <v>25</v>
@@ -3905,7 +3929,7 @@
         <v>25</v>
       </c>
       <c r="V47" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48">
@@ -3919,13 +3943,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="1">
-        <v>46203.386967592596</v>
+        <v>46198.758576388886</v>
       </c>
       <c r="E48" s="1">
-        <v>46203.386967592596</v>
+        <v>46198.758576388886</v>
       </c>
       <c r="F48" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>30</v>
@@ -3934,7 +3958,7 @@
         <v>30</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J48" s="0" t="s">
         <v>25</v>
@@ -3954,8 +3978,8 @@
       <c r="O48" s="0">
         <v>1</v>
       </c>
-      <c r="P48" s="0">
-        <v>0</v>
+      <c r="P48" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q48" s="0" t="s">
         <v>25</v>
@@ -3981,31 +4005,31 @@
         <v>78</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C49" s="0">
-        <v>2003</v>
+        <v>305</v>
       </c>
       <c r="D49" s="1">
-        <v>46203.73695601852</v>
+        <v>46192.00283564815</v>
       </c>
       <c r="E49" s="1">
-        <v>46203.73695601852</v>
+        <v>46196.6612962963</v>
       </c>
       <c r="F49" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J49" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K49" s="0" t="s">
         <v>25</v>
@@ -4020,13 +4044,13 @@
         <v>25</v>
       </c>
       <c r="O49" s="0">
-        <v>0</v>
-      </c>
-      <c r="P49" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q49" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P49" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="0">
+        <v>1</v>
       </c>
       <c r="R49" s="0" t="s">
         <v>25</v>
@@ -4041,7 +4065,7 @@
         <v>25</v>
       </c>
       <c r="V49" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
@@ -4049,28 +4073,28 @@
         <v>79</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C50" s="0">
-        <v>2114</v>
+        <v>0</v>
       </c>
       <c r="D50" s="1">
-        <v>46201.10230324074</v>
+        <v>46203.386967592596</v>
       </c>
       <c r="E50" s="1">
-        <v>46202.30238425926</v>
+        <v>46203.386967592596</v>
       </c>
       <c r="F50" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J50" s="0" t="s">
         <v>25</v>
@@ -4109,7 +4133,7 @@
         <v>25</v>
       </c>
       <c r="V50" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -4117,31 +4141,31 @@
         <v>80</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C51" s="0">
-        <v>262</v>
+        <v>2003</v>
       </c>
       <c r="D51" s="1">
-        <v>46198.007743055554</v>
+        <v>46203.73695601852</v>
       </c>
       <c r="E51" s="1">
-        <v>46198.007743055554</v>
+        <v>46203.73695601852</v>
       </c>
       <c r="F51" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J51" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K51" s="0" t="s">
         <v>25</v>
@@ -4156,13 +4180,13 @@
         <v>25</v>
       </c>
       <c r="O51" s="0">
-        <v>1</v>
-      </c>
-      <c r="P51" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q51" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P51" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q51" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R51" s="0" t="s">
         <v>25</v>
@@ -4177,7 +4201,7 @@
         <v>25</v>
       </c>
       <c r="V51" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
@@ -4185,28 +4209,28 @@
         <v>81</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C52" s="0">
-        <v>0</v>
+        <v>2114</v>
       </c>
       <c r="D52" s="1">
-        <v>46204.82892361111</v>
+        <v>46201.10230324074</v>
       </c>
       <c r="E52" s="1">
-        <v>46204.82892361111</v>
+        <v>46202.30238425926</v>
       </c>
       <c r="F52" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J52" s="0" t="s">
         <v>25</v>
@@ -4226,8 +4250,8 @@
       <c r="O52" s="0">
         <v>1</v>
       </c>
-      <c r="P52" s="0" t="s">
-        <v>25</v>
+      <c r="P52" s="0">
+        <v>0</v>
       </c>
       <c r="Q52" s="0" t="s">
         <v>25</v>
@@ -4245,7 +4269,7 @@
         <v>25</v>
       </c>
       <c r="V52" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
@@ -4253,25 +4277,25 @@
         <v>82</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C53" s="0">
-        <v>2108</v>
+        <v>344</v>
       </c>
       <c r="D53" s="1">
-        <v>46202.13394675926</v>
+        <v>46203.41339120371</v>
       </c>
       <c r="E53" s="1">
-        <v>46206.49621527778</v>
+        <v>46208.76116898148</v>
       </c>
       <c r="F53" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I53" s="0" t="s">
         <v>25</v>
@@ -4292,7 +4316,7 @@
         <v>25</v>
       </c>
       <c r="O53" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" s="0" t="s">
         <v>25</v>
@@ -4313,7 +4337,7 @@
         <v>25</v>
       </c>
       <c r="V53" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54">
@@ -4327,13 +4351,13 @@
         <v>262</v>
       </c>
       <c r="D54" s="1">
-        <v>46194.10880787037</v>
+        <v>46198.007743055554</v>
       </c>
       <c r="E54" s="1">
-        <v>46194.10880787037</v>
+        <v>46198.007743055554</v>
       </c>
       <c r="F54" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>30</v>
@@ -4389,28 +4413,28 @@
         <v>84</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C55" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D55" s="1">
-        <v>46202.674155092594</v>
+        <v>46204.82892361111</v>
       </c>
       <c r="E55" s="1">
-        <v>46202.80762731482</v>
+        <v>46204.82892361111</v>
       </c>
       <c r="F55" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>25</v>
@@ -4430,8 +4454,8 @@
       <c r="O55" s="0">
         <v>1</v>
       </c>
-      <c r="P55" s="0">
-        <v>0</v>
+      <c r="P55" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q55" s="0" t="s">
         <v>25</v>
@@ -4449,7 +4473,7 @@
         <v>25</v>
       </c>
       <c r="V55" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
@@ -4460,16 +4484,16 @@
         <v>23</v>
       </c>
       <c r="C56" s="0">
-        <v>2025</v>
+        <v>2108</v>
       </c>
       <c r="D56" s="1">
-        <v>46196.60855324074</v>
+        <v>46202.13394675926</v>
       </c>
       <c r="E56" s="1">
-        <v>46198.053506944445</v>
+        <v>46206.49621527778</v>
       </c>
       <c r="F56" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>24</v>
@@ -4478,10 +4502,10 @@
         <v>24</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J56" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K56" s="0" t="s">
         <v>25</v>
@@ -4498,11 +4522,11 @@
       <c r="O56" s="0">
         <v>1</v>
       </c>
-      <c r="P56" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="0">
-        <v>1</v>
+      <c r="P56" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R56" s="0" t="s">
         <v>25</v>
@@ -4525,31 +4549,31 @@
         <v>86</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C57" s="0">
-        <v>2518</v>
+        <v>262</v>
       </c>
       <c r="D57" s="1">
-        <v>46205.84306712963</v>
+        <v>46194.10880787037</v>
       </c>
       <c r="E57" s="1">
-        <v>46208.01679398148</v>
+        <v>46194.10880787037</v>
       </c>
       <c r="F57" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K57" s="0" t="s">
         <v>25</v>
@@ -4566,11 +4590,11 @@
       <c r="O57" s="0">
         <v>1</v>
       </c>
-      <c r="P57" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q57" s="0" t="s">
-        <v>25</v>
+      <c r="P57" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="0">
+        <v>0</v>
       </c>
       <c r="R57" s="0" t="s">
         <v>25</v>
@@ -4585,7 +4609,7 @@
         <v>25</v>
       </c>
       <c r="V57" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58">
@@ -4593,28 +4617,28 @@
         <v>87</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C58" s="0">
-        <v>206</v>
+        <v>2108</v>
       </c>
       <c r="D58" s="1">
-        <v>46199.4216087963</v>
+        <v>46202.674155092594</v>
       </c>
       <c r="E58" s="1">
-        <v>46199.4216087963</v>
+        <v>46202.80762731482</v>
       </c>
       <c r="F58" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J58" s="0" t="s">
         <v>25</v>
@@ -4635,7 +4659,7 @@
         <v>1</v>
       </c>
       <c r="P58" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="0" t="s">
         <v>25</v>
@@ -4653,7 +4677,7 @@
         <v>25</v>
       </c>
       <c r="V58" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
@@ -4661,31 +4685,31 @@
         <v>88</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C59" s="0">
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="D59" s="1">
-        <v>46203.398622685185</v>
+        <v>46196.60855324074</v>
       </c>
       <c r="E59" s="1">
-        <v>46203.398622685185</v>
+        <v>46198.053506944445</v>
       </c>
       <c r="F59" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K59" s="0" t="s">
         <v>25</v>
@@ -4702,11 +4726,11 @@
       <c r="O59" s="0">
         <v>1</v>
       </c>
-      <c r="P59" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q59" s="0" t="s">
-        <v>25</v>
+      <c r="P59" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="0">
+        <v>1</v>
       </c>
       <c r="R59" s="0" t="s">
         <v>25</v>
@@ -4721,7 +4745,7 @@
         <v>25</v>
       </c>
       <c r="V59" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
@@ -4729,25 +4753,25 @@
         <v>89</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C60" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D60" s="1">
-        <v>46204.071388888886</v>
+        <v>46205.84306712963</v>
       </c>
       <c r="E60" s="1">
-        <v>46204.071388888886</v>
+        <v>46208.01679398148</v>
       </c>
       <c r="F60" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I60" s="0" t="s">
         <v>25</v>
@@ -4789,7 +4813,7 @@
         <v>25</v>
       </c>
       <c r="V60" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
@@ -4797,31 +4821,31 @@
         <v>90</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C61" s="0">
-        <v>2108</v>
+        <v>206</v>
       </c>
       <c r="D61" s="1">
-        <v>46199.145104166666</v>
+        <v>46199.4216087963</v>
       </c>
       <c r="E61" s="1">
-        <v>46207.340208333335</v>
+        <v>46199.4216087963</v>
       </c>
       <c r="F61" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J61" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K61" s="0" t="s">
         <v>25</v>
@@ -4836,13 +4860,13 @@
         <v>25</v>
       </c>
       <c r="O61" s="0">
-        <v>0</v>
-      </c>
-      <c r="P61" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q61" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P61" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="0">
+        <v>0</v>
       </c>
       <c r="R61" s="0" t="s">
         <v>25</v>
@@ -4857,7 +4881,7 @@
         <v>25</v>
       </c>
       <c r="V61" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62">
@@ -4865,25 +4889,25 @@
         <v>91</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C62" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D62" s="1">
-        <v>46203.22761574074</v>
+        <v>46203.398622685185</v>
       </c>
       <c r="E62" s="1">
-        <v>46203.22761574074</v>
+        <v>46203.398622685185</v>
       </c>
       <c r="F62" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I62" s="0" t="s">
         <v>25</v>
@@ -4904,7 +4928,7 @@
         <v>25</v>
       </c>
       <c r="O62" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P62" s="0" t="s">
         <v>25</v>
@@ -4925,7 +4949,7 @@
         <v>25</v>
       </c>
       <c r="V62" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
@@ -4933,25 +4957,25 @@
         <v>92</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C63" s="0">
-        <v>2003</v>
+        <v>0</v>
       </c>
       <c r="D63" s="1">
-        <v>46203.73695601852</v>
+        <v>46204.071388888886</v>
       </c>
       <c r="E63" s="1">
-        <v>46203.73695601852</v>
+        <v>46204.071388888886</v>
       </c>
       <c r="F63" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I63" s="0" t="s">
         <v>25</v>
@@ -4972,7 +4996,7 @@
         <v>25</v>
       </c>
       <c r="O63" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P63" s="0" t="s">
         <v>25</v>
@@ -4993,7 +5017,7 @@
         <v>25</v>
       </c>
       <c r="V63" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -5004,16 +5028,16 @@
         <v>23</v>
       </c>
       <c r="C64" s="0">
-        <v>2114</v>
+        <v>2108</v>
       </c>
       <c r="D64" s="1">
-        <v>46208.60796296296</v>
+        <v>46199.145104166666</v>
       </c>
       <c r="E64" s="1">
-        <v>46209.27856481481</v>
+        <v>46207.340208333335</v>
       </c>
       <c r="F64" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>24</v>
@@ -5040,7 +5064,7 @@
         <v>25</v>
       </c>
       <c r="O64" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P64" s="0" t="s">
         <v>25</v>
@@ -5069,19 +5093,19 @@
         <v>94</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C65" s="0">
-        <v>13108</v>
+        <v>2108</v>
       </c>
       <c r="D65" s="1">
-        <v>46202.06835648148</v>
+        <v>46203.22761574074</v>
       </c>
       <c r="E65" s="1">
-        <v>46203.241944444446</v>
+        <v>46203.22761574074</v>
       </c>
       <c r="F65" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>24</v>
@@ -5090,7 +5114,7 @@
         <v>24</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J65" s="0" t="s">
         <v>25</v>
@@ -5108,10 +5132,10 @@
         <v>25</v>
       </c>
       <c r="O65" s="0">
-        <v>1</v>
-      </c>
-      <c r="P65" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P65" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q65" s="0" t="s">
         <v>25</v>
@@ -5137,25 +5161,25 @@
         <v>95</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="C66" s="0">
-        <v>1102304</v>
+        <v>2003</v>
       </c>
       <c r="D66" s="1">
-        <v>46197.000439814816</v>
+        <v>46203.73695601852</v>
       </c>
       <c r="E66" s="1">
-        <v>46200.90429398148</v>
+        <v>46203.73695601852</v>
       </c>
       <c r="F66" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I66" s="0" t="s">
         <v>25</v>
@@ -5176,7 +5200,7 @@
         <v>25</v>
       </c>
       <c r="O66" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" s="0" t="s">
         <v>25</v>
@@ -5197,27 +5221,27 @@
         <v>25</v>
       </c>
       <c r="V66" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C67" s="0">
-        <v>225</v>
+        <v>2114</v>
       </c>
       <c r="D67" s="1">
-        <v>46192.854166666664</v>
+        <v>46208.60796296296</v>
       </c>
       <c r="E67" s="1">
-        <v>46201.17297453704</v>
+        <v>46209.27856481481</v>
       </c>
       <c r="F67" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>24</v>
@@ -5226,7 +5250,7 @@
         <v>24</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>25</v>
@@ -5246,8 +5270,8 @@
       <c r="O67" s="0">
         <v>1</v>
       </c>
-      <c r="P67" s="0">
-        <v>1</v>
+      <c r="P67" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q67" s="0" t="s">
         <v>25</v>
@@ -5270,34 +5294,34 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C68" s="0">
-        <v>2012</v>
+        <v>13108</v>
       </c>
       <c r="D68" s="1">
-        <v>46197.398356481484</v>
+        <v>46202.06835648148</v>
       </c>
       <c r="E68" s="1">
-        <v>46197.398356481484</v>
+        <v>46203.241944444446</v>
       </c>
       <c r="F68" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J68" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K68" s="0" t="s">
         <v>25</v>
@@ -5312,13 +5336,13 @@
         <v>25</v>
       </c>
       <c r="O68" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P68" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q68" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R68" s="0" t="s">
         <v>25</v>
@@ -5333,27 +5357,27 @@
         <v>25</v>
       </c>
       <c r="V68" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B69" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="B69" s="0" t="s">
-        <v>29</v>
-      </c>
       <c r="C69" s="0">
-        <v>0</v>
+        <v>1102304</v>
       </c>
       <c r="D69" s="1">
-        <v>46198.06826388889</v>
+        <v>46197.000439814816</v>
       </c>
       <c r="E69" s="1">
-        <v>46198.06826388889</v>
+        <v>46200.90429398148</v>
       </c>
       <c r="F69" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>30</v>
@@ -5409,31 +5433,31 @@
         <v>100</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C70" s="0">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="D70" s="1">
-        <v>46198.76695601852</v>
+        <v>46192.854166666664</v>
       </c>
       <c r="E70" s="1">
-        <v>46198.76695601852</v>
+        <v>46201.17297453704</v>
       </c>
       <c r="F70" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J70" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K70" s="0" t="s">
         <v>25</v>
@@ -5450,11 +5474,11 @@
       <c r="O70" s="0">
         <v>1</v>
       </c>
-      <c r="P70" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q70" s="0" t="s">
-        <v>25</v>
+      <c r="P70" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="0">
+        <v>0</v>
       </c>
       <c r="R70" s="0" t="s">
         <v>25</v>
@@ -5469,7 +5493,7 @@
         <v>25</v>
       </c>
       <c r="V70" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71">
@@ -5477,31 +5501,31 @@
         <v>101</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C71" s="0">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="D71" s="1">
-        <v>46199.06940972222</v>
+        <v>46197.398356481484</v>
       </c>
       <c r="E71" s="1">
-        <v>46199.06940972222</v>
+        <v>46197.398356481484</v>
       </c>
       <c r="F71" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J71" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K71" s="0" t="s">
         <v>25</v>
@@ -5516,13 +5540,13 @@
         <v>25</v>
       </c>
       <c r="O71" s="0">
-        <v>1</v>
-      </c>
-      <c r="P71" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q71" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P71" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="0">
+        <v>0</v>
       </c>
       <c r="R71" s="0" t="s">
         <v>25</v>
@@ -5537,7 +5561,7 @@
         <v>25</v>
       </c>
       <c r="V71" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72">
@@ -5545,25 +5569,25 @@
         <v>102</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C72" s="0">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="D72" s="1">
-        <v>46205.52684027778</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="E72" s="1">
-        <v>46207.38381944445</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="F72" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I72" s="0" t="s">
         <v>25</v>
@@ -5605,7 +5629,7 @@
         <v>25</v>
       </c>
       <c r="V72" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73">
@@ -5619,13 +5643,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="1">
-        <v>46198.764710648145</v>
+        <v>46198.76695601852</v>
       </c>
       <c r="E73" s="1">
-        <v>46198.764710648145</v>
+        <v>46198.76695601852</v>
       </c>
       <c r="F73" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>30</v>
@@ -5681,25 +5705,25 @@
         <v>104</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C74" s="0">
-        <v>2106</v>
+        <v>0</v>
       </c>
       <c r="D74" s="1">
-        <v>46208.60445601852</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="E74" s="1">
-        <v>46208.60445601852</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="F74" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I74" s="0" t="s">
         <v>25</v>
@@ -5741,7 +5765,7 @@
         <v>25</v>
       </c>
       <c r="V74" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75">
@@ -5749,25 +5773,25 @@
         <v>105</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C75" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D75" s="1">
-        <v>46198.06826388889</v>
+        <v>46205.52684027778</v>
       </c>
       <c r="E75" s="1">
-        <v>46198.06826388889</v>
+        <v>46207.38381944445</v>
       </c>
       <c r="F75" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I75" s="0" t="s">
         <v>25</v>
@@ -5809,7 +5833,7 @@
         <v>25</v>
       </c>
       <c r="V75" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76">
@@ -5823,13 +5847,13 @@
         <v>0</v>
       </c>
       <c r="D76" s="1">
-        <v>46198.7566087963</v>
+        <v>46198.764710648145</v>
       </c>
       <c r="E76" s="1">
-        <v>46198.7566087963</v>
+        <v>46198.764710648145</v>
       </c>
       <c r="F76" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>30</v>
@@ -5885,28 +5909,28 @@
         <v>107</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C77" s="0">
-        <v>0</v>
+        <v>2106</v>
       </c>
       <c r="D77" s="1">
-        <v>46203.38690972222</v>
+        <v>46208.60445601852</v>
       </c>
       <c r="E77" s="1">
-        <v>46203.38690972222</v>
+        <v>46208.60445601852</v>
       </c>
       <c r="F77" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>25</v>
@@ -5926,8 +5950,8 @@
       <c r="O77" s="0">
         <v>1</v>
       </c>
-      <c r="P77" s="0">
-        <v>0</v>
+      <c r="P77" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q77" s="0" t="s">
         <v>25</v>
@@ -5945,7 +5969,7 @@
         <v>25</v>
       </c>
       <c r="V77" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -5953,28 +5977,28 @@
         <v>108</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C78" s="0">
-        <v>2521</v>
+        <v>0</v>
       </c>
       <c r="D78" s="1">
-        <v>46196.88789351852</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="E78" s="1">
-        <v>46199.954201388886</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="F78" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>25</v>
@@ -5994,8 +6018,8 @@
       <c r="O78" s="0">
         <v>1</v>
       </c>
-      <c r="P78" s="0">
-        <v>0</v>
+      <c r="P78" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q78" s="0" t="s">
         <v>25</v>
@@ -6013,7 +6037,7 @@
         <v>25</v>
       </c>
       <c r="V78" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="79">
@@ -6027,19 +6051,19 @@
         <v>0</v>
       </c>
       <c r="D79" s="1">
-        <v>46199.06940972222</v>
+        <v>46198.7566087963</v>
       </c>
       <c r="E79" s="1">
-        <v>46199.06940972222</v>
+        <v>46198.7566087963</v>
       </c>
       <c r="F79" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>25</v>
@@ -6081,7 +6105,7 @@
         <v>25</v>
       </c>
       <c r="V79" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80">
@@ -6089,19 +6113,19 @@
         <v>110</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C80" s="0">
-        <v>2115</v>
+        <v>0</v>
       </c>
       <c r="D80" s="1">
-        <v>46193.45674768519</v>
+        <v>46203.38690972222</v>
       </c>
       <c r="E80" s="1">
-        <v>46193.45674768519</v>
+        <v>46203.38690972222</v>
       </c>
       <c r="F80" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>30</v>
@@ -6131,7 +6155,7 @@
         <v>1</v>
       </c>
       <c r="P80" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="0" t="s">
         <v>25</v>
@@ -6160,16 +6184,16 @@
         <v>23</v>
       </c>
       <c r="C81" s="0">
-        <v>2108</v>
+        <v>2521</v>
       </c>
       <c r="D81" s="1">
-        <v>46196.430972222224</v>
+        <v>46196.88789351852</v>
       </c>
       <c r="E81" s="1">
-        <v>46196.43208333333</v>
+        <v>46199.954201388886</v>
       </c>
       <c r="F81" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>24</v>
@@ -6181,7 +6205,7 @@
         <v>24</v>
       </c>
       <c r="J81" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K81" s="0" t="s">
         <v>25</v>
@@ -6199,10 +6223,10 @@
         <v>1</v>
       </c>
       <c r="P81" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q81" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R81" s="0" t="s">
         <v>25</v>
@@ -6225,25 +6249,25 @@
         <v>112</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C82" s="0">
-        <v>2012</v>
+        <v>0</v>
       </c>
       <c r="D82" s="1">
-        <v>46205.85377314815</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="E82" s="1">
-        <v>46205.85377314815</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="F82" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I82" s="0" t="s">
         <v>25</v>
@@ -6264,7 +6288,7 @@
         <v>25</v>
       </c>
       <c r="O82" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P82" s="0" t="s">
         <v>25</v>
@@ -6285,7 +6309,7 @@
         <v>25</v>
       </c>
       <c r="V82" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83">
@@ -6296,25 +6320,25 @@
         <v>23</v>
       </c>
       <c r="C83" s="0">
-        <v>2106</v>
+        <v>2115</v>
       </c>
       <c r="D83" s="1">
-        <v>46194.496782407405</v>
+        <v>46193.45674768519</v>
       </c>
       <c r="E83" s="1">
-        <v>46194.496782407405</v>
+        <v>46193.45674768519</v>
       </c>
       <c r="F83" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J83" s="0" t="s">
         <v>25</v>
@@ -6353,7 +6377,7 @@
         <v>25</v>
       </c>
       <c r="V83" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84">
@@ -6367,13 +6391,13 @@
         <v>2108</v>
       </c>
       <c r="D84" s="1">
-        <v>46206.041817129626</v>
+        <v>46196.430972222224</v>
       </c>
       <c r="E84" s="1">
-        <v>46206.041817129626</v>
+        <v>46196.43208333333</v>
       </c>
       <c r="F84" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>24</v>
@@ -6382,10 +6406,10 @@
         <v>24</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J84" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K84" s="0" t="s">
         <v>25</v>
@@ -6400,13 +6424,13 @@
         <v>25</v>
       </c>
       <c r="O84" s="0">
-        <v>0</v>
-      </c>
-      <c r="P84" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q84" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P84" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="0">
+        <v>0</v>
       </c>
       <c r="R84" s="0" t="s">
         <v>25</v>
@@ -6429,19 +6453,19 @@
         <v>115</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C85" s="0">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="D85" s="1">
-        <v>46198.76357638889</v>
+        <v>46205.85377314815</v>
       </c>
       <c r="E85" s="1">
-        <v>46198.76357638889</v>
+        <v>46205.85377314815</v>
       </c>
       <c r="F85" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>30</v>
@@ -6468,7 +6492,7 @@
         <v>25</v>
       </c>
       <c r="O85" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" s="0" t="s">
         <v>25</v>
@@ -6497,19 +6521,19 @@
         <v>116</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C86" s="0">
-        <v>0</v>
+        <v>2106</v>
       </c>
       <c r="D86" s="1">
-        <v>46203.900046296294</v>
+        <v>46194.496782407405</v>
       </c>
       <c r="E86" s="1">
-        <v>46203.900046296294</v>
+        <v>46194.496782407405</v>
       </c>
       <c r="F86" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>39</v>
@@ -6518,10 +6542,10 @@
         <v>39</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J86" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K86" s="0" t="s">
         <v>25</v>
@@ -6538,11 +6562,11 @@
       <c r="O86" s="0">
         <v>1</v>
       </c>
-      <c r="P86" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q86" s="0" t="s">
-        <v>25</v>
+      <c r="P86" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q86" s="0">
+        <v>0</v>
       </c>
       <c r="R86" s="0" t="s">
         <v>25</v>
@@ -6565,25 +6589,25 @@
         <v>117</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C87" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D87" s="1">
-        <v>46198.75818287037</v>
+        <v>46206.041817129626</v>
       </c>
       <c r="E87" s="1">
-        <v>46198.75818287037</v>
+        <v>46206.041817129626</v>
       </c>
       <c r="F87" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I87" s="0" t="s">
         <v>25</v>
@@ -6604,7 +6628,7 @@
         <v>25</v>
       </c>
       <c r="O87" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87" s="0" t="s">
         <v>25</v>
@@ -6625,7 +6649,7 @@
         <v>25</v>
       </c>
       <c r="V87" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
@@ -6633,31 +6657,31 @@
         <v>118</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C88" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D88" s="1">
-        <v>46198.57461805556</v>
+        <v>46198.76357638889</v>
       </c>
       <c r="E88" s="1">
-        <v>46199.24039351852</v>
+        <v>46198.76357638889</v>
       </c>
       <c r="F88" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J88" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K88" s="0" t="s">
         <v>25</v>
@@ -6674,11 +6698,11 @@
       <c r="O88" s="0">
         <v>1</v>
       </c>
-      <c r="P88" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q88" s="0">
-        <v>0</v>
+      <c r="P88" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q88" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R88" s="0" t="s">
         <v>25</v>
@@ -6693,7 +6717,7 @@
         <v>25</v>
       </c>
       <c r="V88" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89">
@@ -6701,25 +6725,25 @@
         <v>119</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C89" s="0">
-        <v>2025</v>
+        <v>0</v>
       </c>
       <c r="D89" s="1">
-        <v>46206.35917824074</v>
+        <v>46203.900046296294</v>
       </c>
       <c r="E89" s="1">
-        <v>46207.7878125</v>
+        <v>46203.900046296294</v>
       </c>
       <c r="F89" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I89" s="0" t="s">
         <v>25</v>
@@ -6740,7 +6764,7 @@
         <v>25</v>
       </c>
       <c r="O89" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89" s="0" t="s">
         <v>25</v>
@@ -6761,7 +6785,7 @@
         <v>25</v>
       </c>
       <c r="V89" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90">
@@ -6769,28 +6793,28 @@
         <v>120</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C90" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D90" s="1">
-        <v>46199.62337962963</v>
+        <v>46198.75818287037</v>
       </c>
       <c r="E90" s="1">
-        <v>46200.88856481481</v>
+        <v>46198.75818287037</v>
       </c>
       <c r="F90" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J90" s="0" t="s">
         <v>25</v>
@@ -6810,8 +6834,8 @@
       <c r="O90" s="0">
         <v>1</v>
       </c>
-      <c r="P90" s="0">
-        <v>1</v>
+      <c r="P90" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q90" s="0" t="s">
         <v>25</v>
@@ -6829,7 +6853,7 @@
         <v>25</v>
       </c>
       <c r="V90" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91">
@@ -6840,16 +6864,16 @@
         <v>23</v>
       </c>
       <c r="C91" s="0">
-        <v>2009</v>
+        <v>2108</v>
       </c>
       <c r="D91" s="1">
-        <v>46207.091145833336</v>
+        <v>46198.57461805556</v>
       </c>
       <c r="E91" s="1">
-        <v>46207.091145833336</v>
+        <v>46199.24039351852</v>
       </c>
       <c r="F91" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>24</v>
@@ -6858,10 +6882,10 @@
         <v>24</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J91" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K91" s="0" t="s">
         <v>25</v>
@@ -6878,11 +6902,11 @@
       <c r="O91" s="0">
         <v>1</v>
       </c>
-      <c r="P91" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q91" s="0" t="s">
-        <v>25</v>
+      <c r="P91" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="0">
+        <v>0</v>
       </c>
       <c r="R91" s="0" t="s">
         <v>25</v>
@@ -6908,25 +6932,25 @@
         <v>23</v>
       </c>
       <c r="C92" s="0">
-        <v>2012</v>
+        <v>2025</v>
       </c>
       <c r="D92" s="1">
-        <v>46202.603946759256</v>
+        <v>46206.35917824074</v>
       </c>
       <c r="E92" s="1">
-        <v>46202.603946759256</v>
+        <v>46207.7878125</v>
       </c>
       <c r="F92" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J92" s="0" t="s">
         <v>25</v>
@@ -6946,8 +6970,8 @@
       <c r="O92" s="0">
         <v>0</v>
       </c>
-      <c r="P92" s="0">
-        <v>1</v>
+      <c r="P92" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q92" s="0" t="s">
         <v>25</v>
@@ -6965,7 +6989,7 @@
         <v>25</v>
       </c>
       <c r="V92" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93">
@@ -6976,16 +7000,16 @@
         <v>23</v>
       </c>
       <c r="C93" s="0">
-        <v>2518</v>
+        <v>2108</v>
       </c>
       <c r="D93" s="1">
-        <v>46200.47917824074</v>
+        <v>46199.62337962963</v>
       </c>
       <c r="E93" s="1">
-        <v>46208.28020833333</v>
+        <v>46200.88856481481</v>
       </c>
       <c r="F93" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>39</v>
@@ -6994,10 +7018,10 @@
         <v>39</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J93" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K93" s="0" t="s">
         <v>25</v>
@@ -7014,11 +7038,11 @@
       <c r="O93" s="0">
         <v>1</v>
       </c>
-      <c r="P93" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q93" s="0" t="s">
-        <v>25</v>
+      <c r="P93" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="0">
+        <v>0</v>
       </c>
       <c r="R93" s="0" t="s">
         <v>25</v>
@@ -7041,25 +7065,25 @@
         <v>124</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C94" s="0">
-        <v>344</v>
+        <v>2009</v>
       </c>
       <c r="D94" s="1">
-        <v>46203.665925925925</v>
+        <v>46207.091145833336</v>
       </c>
       <c r="E94" s="1">
-        <v>46203.665925925925</v>
+        <v>46207.091145833336</v>
       </c>
       <c r="F94" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I94" s="0" t="s">
         <v>25</v>
@@ -7080,7 +7104,7 @@
         <v>25</v>
       </c>
       <c r="O94" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94" s="0" t="s">
         <v>25</v>
@@ -7101,7 +7125,7 @@
         <v>25</v>
       </c>
       <c r="V94" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95">
@@ -7109,28 +7133,28 @@
         <v>125</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C95" s="0">
-        <v>2108</v>
+        <v>344</v>
       </c>
       <c r="D95" s="1">
-        <v>46202.769537037035</v>
+        <v>46203.41339120371</v>
       </c>
       <c r="E95" s="1">
-        <v>46204.36974537037</v>
+        <v>46208.76133101852</v>
       </c>
       <c r="F95" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J95" s="0" t="s">
         <v>25</v>
@@ -7148,10 +7172,10 @@
         <v>25</v>
       </c>
       <c r="O95" s="0">
-        <v>1</v>
-      </c>
-      <c r="P95" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P95" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q95" s="0" t="s">
         <v>25</v>
@@ -7169,7 +7193,7 @@
         <v>25</v>
       </c>
       <c r="V95" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96">
@@ -7180,16 +7204,16 @@
         <v>23</v>
       </c>
       <c r="C96" s="0">
-        <v>2099</v>
+        <v>2012</v>
       </c>
       <c r="D96" s="1">
-        <v>46200.000439814816</v>
+        <v>46202.603946759256</v>
       </c>
       <c r="E96" s="1">
-        <v>46201.332870370374</v>
+        <v>46202.603946759256</v>
       </c>
       <c r="F96" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>30</v>
@@ -7216,7 +7240,7 @@
         <v>25</v>
       </c>
       <c r="O96" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P96" s="0">
         <v>1</v>
@@ -7245,31 +7269,31 @@
         <v>127</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C97" s="0">
-        <v>112304</v>
+        <v>2518</v>
       </c>
       <c r="D97" s="1">
-        <v>46197.03113425926</v>
+        <v>46200.47917824074</v>
       </c>
       <c r="E97" s="1">
-        <v>46197.03113425926</v>
+        <v>46208.28020833333</v>
       </c>
       <c r="F97" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J97" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K97" s="0" t="s">
         <v>25</v>
@@ -7284,13 +7308,13 @@
         <v>25</v>
       </c>
       <c r="O97" s="0">
-        <v>0</v>
-      </c>
-      <c r="P97" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q97" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P97" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q97" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R97" s="0" t="s">
         <v>25</v>
@@ -7305,7 +7329,7 @@
         <v>25</v>
       </c>
       <c r="V97" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98">
@@ -7313,28 +7337,28 @@
         <v>128</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C98" s="0">
-        <v>2108</v>
+        <v>344</v>
       </c>
       <c r="D98" s="1">
-        <v>46200.04966435185</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="E98" s="1">
-        <v>46200.98619212963</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="F98" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J98" s="0" t="s">
         <v>25</v>
@@ -7352,10 +7376,10 @@
         <v>25</v>
       </c>
       <c r="O98" s="0">
-        <v>1</v>
-      </c>
-      <c r="P98" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P98" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q98" s="0" t="s">
         <v>25</v>
@@ -7373,7 +7397,7 @@
         <v>25</v>
       </c>
       <c r="V98" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99">
@@ -7387,13 +7411,13 @@
         <v>2108</v>
       </c>
       <c r="D99" s="1">
-        <v>46207.068391203706</v>
+        <v>46202.769537037035</v>
       </c>
       <c r="E99" s="1">
-        <v>46207.18613425926</v>
+        <v>46204.36974537037</v>
       </c>
       <c r="F99" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>24</v>
@@ -7402,7 +7426,7 @@
         <v>24</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J99" s="0" t="s">
         <v>25</v>
@@ -7422,8 +7446,8 @@
       <c r="O99" s="0">
         <v>1</v>
       </c>
-      <c r="P99" s="0" t="s">
-        <v>25</v>
+      <c r="P99" s="0">
+        <v>0</v>
       </c>
       <c r="Q99" s="0" t="s">
         <v>25</v>
@@ -7449,19 +7473,19 @@
         <v>130</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C100" s="0">
-        <v>0</v>
+        <v>2099</v>
       </c>
       <c r="D100" s="1">
-        <v>46198.763344907406</v>
+        <v>46200.000439814816</v>
       </c>
       <c r="E100" s="1">
-        <v>46198.763344907406</v>
+        <v>46201.332870370374</v>
       </c>
       <c r="F100" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>30</v>
@@ -7470,10 +7494,10 @@
         <v>30</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J100" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K100" s="0" t="s">
         <v>25</v>
@@ -7490,11 +7514,11 @@
       <c r="O100" s="0">
         <v>1</v>
       </c>
-      <c r="P100" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q100" s="0" t="s">
-        <v>25</v>
+      <c r="P100" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q100" s="0">
+        <v>0</v>
       </c>
       <c r="R100" s="0" t="s">
         <v>25</v>
@@ -7517,31 +7541,31 @@
         <v>131</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C101" s="0">
-        <v>2120</v>
+        <v>112304</v>
       </c>
       <c r="D101" s="1">
-        <v>46196.68797453704</v>
+        <v>46197.03113425926</v>
       </c>
       <c r="E101" s="1">
-        <v>46198.86886574074</v>
+        <v>46197.03113425926</v>
       </c>
       <c r="F101" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J101" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K101" s="0" t="s">
         <v>25</v>
@@ -7556,7 +7580,7 @@
         <v>25</v>
       </c>
       <c r="O101" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P101" s="0">
         <v>1</v>
@@ -7577,7 +7601,7 @@
         <v>25</v>
       </c>
       <c r="V101" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102">
@@ -7585,28 +7609,28 @@
         <v>132</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C102" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D102" s="1">
-        <v>46198.76422453704</v>
+        <v>46200.04966435185</v>
       </c>
       <c r="E102" s="1">
-        <v>46198.76422453704</v>
+        <v>46200.98619212963</v>
       </c>
       <c r="F102" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J102" s="0" t="s">
         <v>25</v>
@@ -7626,8 +7650,8 @@
       <c r="O102" s="0">
         <v>1</v>
       </c>
-      <c r="P102" s="0" t="s">
-        <v>25</v>
+      <c r="P102" s="0">
+        <v>0</v>
       </c>
       <c r="Q102" s="0" t="s">
         <v>25</v>
@@ -7645,7 +7669,7 @@
         <v>25</v>
       </c>
       <c r="V102" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103">
@@ -7656,16 +7680,16 @@
         <v>23</v>
       </c>
       <c r="C103" s="0">
-        <v>2123</v>
+        <v>2108</v>
       </c>
       <c r="D103" s="1">
-        <v>46206.39832175926</v>
+        <v>46207.068391203706</v>
       </c>
       <c r="E103" s="1">
-        <v>46206.39832175926</v>
+        <v>46207.18613425926</v>
       </c>
       <c r="F103" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>24</v>
@@ -7692,7 +7716,7 @@
         <v>25</v>
       </c>
       <c r="O103" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P103" s="0" t="s">
         <v>25</v>
@@ -7721,28 +7745,28 @@
         <v>134</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C104" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D104" s="1">
-        <v>46197.72638888889</v>
+        <v>46198.763344907406</v>
       </c>
       <c r="E104" s="1">
-        <v>46201.828206018516</v>
+        <v>46198.763344907406</v>
       </c>
       <c r="F104" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J104" s="0" t="s">
         <v>25</v>
@@ -7760,10 +7784,10 @@
         <v>25</v>
       </c>
       <c r="O104" s="0">
-        <v>0</v>
-      </c>
-      <c r="P104" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P104" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q104" s="0" t="s">
         <v>25</v>
@@ -7781,7 +7805,7 @@
         <v>25</v>
       </c>
       <c r="V104" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105">
@@ -7789,31 +7813,31 @@
         <v>135</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="C105" s="0">
-        <v>64</v>
+        <v>2120</v>
       </c>
       <c r="D105" s="1">
-        <v>46198.13282407408</v>
+        <v>46196.68797453704</v>
       </c>
       <c r="E105" s="1">
-        <v>46198.13486111111</v>
+        <v>46198.86886574074</v>
       </c>
       <c r="F105" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J105" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K105" s="0" t="s">
         <v>25</v>
@@ -7834,7 +7858,7 @@
         <v>1</v>
       </c>
       <c r="Q105" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" s="0" t="s">
         <v>25</v>
@@ -7849,39 +7873,39 @@
         <v>25</v>
       </c>
       <c r="V105" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C106" s="0">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="D106" s="1">
-        <v>46198.26168981481</v>
+        <v>46198.76422453704</v>
       </c>
       <c r="E106" s="1">
-        <v>46198.487546296295</v>
+        <v>46198.76422453704</v>
       </c>
       <c r="F106" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J106" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K106" s="0" t="s">
         <v>25</v>
@@ -7898,11 +7922,11 @@
       <c r="O106" s="0">
         <v>1</v>
       </c>
-      <c r="P106" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="0">
-        <v>0</v>
+      <c r="P106" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q106" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R106" s="0" t="s">
         <v>25</v>
@@ -7917,39 +7941,39 @@
         <v>25</v>
       </c>
       <c r="V106" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B107" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C107" s="0">
-        <v>2518</v>
+        <v>2521</v>
       </c>
       <c r="D107" s="1">
-        <v>46198.6140625</v>
+        <v>46203.63976851852</v>
       </c>
       <c r="E107" s="1">
-        <v>46199.37</v>
+        <v>46206.29314814815</v>
       </c>
       <c r="F107" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J107" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K107" s="0" t="s">
         <v>25</v>
@@ -7966,11 +7990,11 @@
       <c r="O107" s="0">
         <v>1</v>
       </c>
-      <c r="P107" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q107" s="0">
-        <v>0</v>
+      <c r="P107" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q107" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R107" s="0" t="s">
         <v>25</v>
@@ -7985,27 +8009,27 @@
         <v>25</v>
       </c>
       <c r="V107" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C108" s="0">
-        <v>13108</v>
+        <v>2123</v>
       </c>
       <c r="D108" s="1">
-        <v>46200.21556712963</v>
+        <v>46206.39832175926</v>
       </c>
       <c r="E108" s="1">
-        <v>46200.507418981484</v>
+        <v>46206.39832175926</v>
       </c>
       <c r="F108" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>24</v>
@@ -8014,7 +8038,7 @@
         <v>24</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J108" s="0" t="s">
         <v>25</v>
@@ -8032,10 +8056,10 @@
         <v>25</v>
       </c>
       <c r="O108" s="0">
-        <v>1</v>
-      </c>
-      <c r="P108" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P108" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q108" s="0" t="s">
         <v>25</v>
@@ -8058,22 +8082,22 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B109" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C109" s="0">
-        <v>2126</v>
+        <v>2108</v>
       </c>
       <c r="D109" s="1">
-        <v>46206.616875</v>
+        <v>46197.72638888889</v>
       </c>
       <c r="E109" s="1">
-        <v>46206.616875</v>
+        <v>46201.828206018516</v>
       </c>
       <c r="F109" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>24</v>
@@ -8082,7 +8106,7 @@
         <v>24</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J109" s="0" t="s">
         <v>25</v>
@@ -8102,8 +8126,8 @@
       <c r="O109" s="0">
         <v>0</v>
       </c>
-      <c r="P109" s="0" t="s">
-        <v>25</v>
+      <c r="P109" s="0">
+        <v>0</v>
       </c>
       <c r="Q109" s="0" t="s">
         <v>25</v>
@@ -8126,22 +8150,22 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B110" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="B110" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="C110" s="0">
-        <v>2012</v>
+        <v>64</v>
       </c>
       <c r="D110" s="1">
-        <v>46206.85376157407</v>
+        <v>46198.13282407408</v>
       </c>
       <c r="E110" s="1">
-        <v>46206.85376157407</v>
+        <v>46198.13486111111</v>
       </c>
       <c r="F110" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>30</v>
@@ -8150,10 +8174,10 @@
         <v>30</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J110" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K110" s="0" t="s">
         <v>25</v>
@@ -8168,13 +8192,13 @@
         <v>25</v>
       </c>
       <c r="O110" s="0">
-        <v>0</v>
-      </c>
-      <c r="P110" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q110" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P110" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q110" s="0">
+        <v>1</v>
       </c>
       <c r="R110" s="0" t="s">
         <v>25</v>
@@ -8203,25 +8227,25 @@
         <v>2518</v>
       </c>
       <c r="D111" s="1">
-        <v>46208.34142361111</v>
+        <v>46198.26168981481</v>
       </c>
       <c r="E111" s="1">
-        <v>46208.34142361111</v>
+        <v>46198.487546296295</v>
       </c>
       <c r="F111" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J111" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K111" s="0" t="s">
         <v>25</v>
@@ -8238,11 +8262,11 @@
       <c r="O111" s="0">
         <v>1</v>
       </c>
-      <c r="P111" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q111" s="0" t="s">
-        <v>25</v>
+      <c r="P111" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="0">
+        <v>0</v>
       </c>
       <c r="R111" s="0" t="s">
         <v>25</v>
@@ -8257,7 +8281,7 @@
         <v>25</v>
       </c>
       <c r="V111" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="112">
@@ -8265,31 +8289,31 @@
         <v>143</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C112" s="0">
-        <v>305</v>
+        <v>2518</v>
       </c>
       <c r="D112" s="1">
-        <v>46206.18699074074</v>
+        <v>46198.6140625</v>
       </c>
       <c r="E112" s="1">
-        <v>46207.44116898148</v>
+        <v>46199.37</v>
       </c>
       <c r="F112" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J112" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K112" s="0" t="s">
         <v>25</v>
@@ -8304,13 +8328,13 @@
         <v>25</v>
       </c>
       <c r="O112" s="0">
-        <v>0</v>
-      </c>
-      <c r="P112" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q112" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P112" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q112" s="0">
+        <v>0</v>
       </c>
       <c r="R112" s="0" t="s">
         <v>25</v>
@@ -8325,7 +8349,7 @@
         <v>25</v>
       </c>
       <c r="V112" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="113">
@@ -8333,31 +8357,31 @@
         <v>144</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C113" s="0">
-        <v>318</v>
+        <v>13108</v>
       </c>
       <c r="D113" s="1">
-        <v>46205.74003472222</v>
+        <v>46200.21556712963</v>
       </c>
       <c r="E113" s="1">
-        <v>46205.74003472222</v>
+        <v>46200.507418981484</v>
       </c>
       <c r="F113" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J113" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K113" s="0" t="s">
         <v>25</v>
@@ -8372,13 +8396,13 @@
         <v>25</v>
       </c>
       <c r="O113" s="0">
-        <v>0</v>
-      </c>
-      <c r="P113" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q113" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P113" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q113" s="0">
+        <v>0</v>
       </c>
       <c r="R113" s="0" t="s">
         <v>25</v>
@@ -8393,7 +8417,7 @@
         <v>25</v>
       </c>
       <c r="V113" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="114">
@@ -8401,19 +8425,19 @@
         <v>145</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C114" s="0">
-        <v>2521</v>
+        <v>344</v>
       </c>
       <c r="D114" s="1">
-        <v>46196.88789351852</v>
+        <v>46203.41339120371</v>
       </c>
       <c r="E114" s="1">
-        <v>46199.95371527778</v>
+        <v>46208.7612037037</v>
       </c>
       <c r="F114" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>39</v>
@@ -8422,10 +8446,10 @@
         <v>39</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J114" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K114" s="0" t="s">
         <v>25</v>
@@ -8440,13 +8464,13 @@
         <v>25</v>
       </c>
       <c r="O114" s="0">
-        <v>1</v>
-      </c>
-      <c r="P114" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q114" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P114" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q114" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R114" s="0" t="s">
         <v>25</v>
@@ -8469,25 +8493,25 @@
         <v>146</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C115" s="0">
-        <v>0</v>
+        <v>2126</v>
       </c>
       <c r="D115" s="1">
-        <v>46203.39921296296</v>
+        <v>46206.616875</v>
       </c>
       <c r="E115" s="1">
-        <v>46203.39921296296</v>
+        <v>46206.616875</v>
       </c>
       <c r="F115" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>25</v>
@@ -8529,7 +8553,7 @@
         <v>25</v>
       </c>
       <c r="V115" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="116">
@@ -8537,19 +8561,19 @@
         <v>147</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C116" s="0">
-        <v>300144</v>
+        <v>2012</v>
       </c>
       <c r="D116" s="1">
-        <v>46206.91523148148</v>
+        <v>46206.85376157407</v>
       </c>
       <c r="E116" s="1">
-        <v>46206.91523148148</v>
+        <v>46206.85376157407</v>
       </c>
       <c r="F116" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>30</v>
@@ -8605,25 +8629,25 @@
         <v>148</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C117" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D117" s="1">
-        <v>46199.06940972222</v>
+        <v>46208.34142361111</v>
       </c>
       <c r="E117" s="1">
-        <v>46199.06940972222</v>
+        <v>46208.34142361111</v>
       </c>
       <c r="F117" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I117" s="0" t="s">
         <v>25</v>
@@ -8665,7 +8689,7 @@
         <v>25</v>
       </c>
       <c r="V117" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="118">
@@ -8673,31 +8697,31 @@
         <v>149</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C118" s="0">
-        <v>2092</v>
+        <v>305</v>
       </c>
       <c r="D118" s="1">
-        <v>46198.29152777778</v>
+        <v>46206.18699074074</v>
       </c>
       <c r="E118" s="1">
-        <v>46199.395949074074</v>
+        <v>46207.44116898148</v>
       </c>
       <c r="F118" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J118" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K118" s="0" t="s">
         <v>25</v>
@@ -8712,13 +8736,13 @@
         <v>25</v>
       </c>
       <c r="O118" s="0">
-        <v>1</v>
-      </c>
-      <c r="P118" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P118" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q118" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R118" s="0" t="s">
         <v>25</v>
@@ -8733,7 +8757,7 @@
         <v>25</v>
       </c>
       <c r="V118" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="119">
@@ -8741,25 +8765,25 @@
         <v>150</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C119" s="0">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="D119" s="1">
-        <v>46198.756527777776</v>
+        <v>46205.74003472222</v>
       </c>
       <c r="E119" s="1">
-        <v>46198.756527777776</v>
+        <v>46205.74003472222</v>
       </c>
       <c r="F119" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>25</v>
@@ -8801,7 +8825,7 @@
         <v>25</v>
       </c>
       <c r="V119" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120">
@@ -8809,31 +8833,31 @@
         <v>151</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C120" s="0">
-        <v>0</v>
+        <v>2521</v>
       </c>
       <c r="D120" s="1">
-        <v>46198.76427083334</v>
+        <v>46196.88789351852</v>
       </c>
       <c r="E120" s="1">
-        <v>46198.76427083334</v>
+        <v>46199.95371527778</v>
       </c>
       <c r="F120" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J120" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K120" s="0" t="s">
         <v>25</v>
@@ -8850,11 +8874,11 @@
       <c r="O120" s="0">
         <v>1</v>
       </c>
-      <c r="P120" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q120" s="0" t="s">
-        <v>25</v>
+      <c r="P120" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q120" s="0">
+        <v>0</v>
       </c>
       <c r="R120" s="0" t="s">
         <v>25</v>
@@ -8869,7 +8893,7 @@
         <v>25</v>
       </c>
       <c r="V120" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121">
@@ -8877,19 +8901,19 @@
         <v>152</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C121" s="0">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="D121" s="1">
-        <v>46196.08101851852</v>
+        <v>46205.07099537037</v>
       </c>
       <c r="E121" s="1">
-        <v>46196.08101851852</v>
+        <v>46205.07099537037</v>
       </c>
       <c r="F121" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>30</v>
@@ -8898,10 +8922,10 @@
         <v>30</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J121" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K121" s="0" t="s">
         <v>25</v>
@@ -8916,13 +8940,13 @@
         <v>25</v>
       </c>
       <c r="O121" s="0">
-        <v>1</v>
-      </c>
-      <c r="P121" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q121" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P121" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q121" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R121" s="0" t="s">
         <v>25</v>
@@ -8951,13 +8975,13 @@
         <v>0</v>
       </c>
       <c r="D122" s="1">
-        <v>46207.28523148148</v>
+        <v>46203.39921296296</v>
       </c>
       <c r="E122" s="1">
-        <v>46207.28523148148</v>
+        <v>46203.39921296296</v>
       </c>
       <c r="F122" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>30</v>
@@ -9013,19 +9037,19 @@
         <v>154</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C123" s="0">
-        <v>262</v>
+        <v>300144</v>
       </c>
       <c r="D123" s="1">
-        <v>46196.788564814815</v>
+        <v>46206.91523148148</v>
       </c>
       <c r="E123" s="1">
-        <v>46196.788564814815</v>
+        <v>46206.91523148148</v>
       </c>
       <c r="F123" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>30</v>
@@ -9052,7 +9076,7 @@
         <v>25</v>
       </c>
       <c r="O123" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P123" s="0" t="s">
         <v>25</v>
@@ -9081,28 +9105,28 @@
         <v>155</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C124" s="0">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="D124" s="1">
-        <v>46200.45096064815</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="E124" s="1">
-        <v>46200.45096064815</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="F124" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J124" s="0" t="s">
         <v>25</v>
@@ -9120,10 +9144,10 @@
         <v>25</v>
       </c>
       <c r="O124" s="0">
-        <v>0</v>
-      </c>
-      <c r="P124" s="0">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="P124" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q124" s="0" t="s">
         <v>25</v>
@@ -9141,7 +9165,7 @@
         <v>25</v>
       </c>
       <c r="V124" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125">
@@ -9149,31 +9173,31 @@
         <v>156</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C125" s="0">
-        <v>336</v>
+        <v>2092</v>
       </c>
       <c r="D125" s="1">
-        <v>46198.12163194444</v>
+        <v>46198.29152777778</v>
       </c>
       <c r="E125" s="1">
-        <v>46207.18237268519</v>
+        <v>46199.395949074074</v>
       </c>
       <c r="F125" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J125" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K125" s="0" t="s">
         <v>25</v>
@@ -9190,11 +9214,11 @@
       <c r="O125" s="0">
         <v>1</v>
       </c>
-      <c r="P125" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q125" s="0" t="s">
-        <v>25</v>
+      <c r="P125" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="0">
+        <v>0</v>
       </c>
       <c r="R125" s="0" t="s">
         <v>25</v>
@@ -9209,7 +9233,7 @@
         <v>25</v>
       </c>
       <c r="V125" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="126">
@@ -9217,31 +9241,31 @@
         <v>157</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C126" s="0">
-        <v>13108</v>
+        <v>0</v>
       </c>
       <c r="D126" s="1">
-        <v>46197.70695601852</v>
+        <v>46198.756527777776</v>
       </c>
       <c r="E126" s="1">
-        <v>46198.89733796296</v>
+        <v>46198.756527777776</v>
       </c>
       <c r="F126" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J126" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K126" s="0" t="s">
         <v>25</v>
@@ -9256,13 +9280,13 @@
         <v>25</v>
       </c>
       <c r="O126" s="0">
-        <v>0</v>
-      </c>
-      <c r="P126" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q126" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P126" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q126" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R126" s="0" t="s">
         <v>25</v>
@@ -9277,7 +9301,7 @@
         <v>25</v>
       </c>
       <c r="V126" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127">
@@ -9285,28 +9309,28 @@
         <v>158</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C127" s="0">
-        <v>13108</v>
+        <v>344</v>
       </c>
       <c r="D127" s="1">
-        <v>46201.693333333336</v>
+        <v>46203.41339120371</v>
       </c>
       <c r="E127" s="1">
-        <v>46205.19603009259</v>
+        <v>46208.76128472222</v>
       </c>
       <c r="F127" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J127" s="0" t="s">
         <v>25</v>
@@ -9326,8 +9350,8 @@
       <c r="O127" s="0">
         <v>0</v>
       </c>
-      <c r="P127" s="0">
-        <v>0</v>
+      <c r="P127" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q127" s="0" t="s">
         <v>25</v>
@@ -9345,7 +9369,7 @@
         <v>25</v>
       </c>
       <c r="V127" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128">
@@ -9359,13 +9383,13 @@
         <v>0</v>
       </c>
       <c r="D128" s="1">
-        <v>46196.08101851852</v>
+        <v>46198.76427083334</v>
       </c>
       <c r="E128" s="1">
-        <v>46196.08101851852</v>
+        <v>46198.76427083334</v>
       </c>
       <c r="F128" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>30</v>
@@ -9374,10 +9398,10 @@
         <v>30</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J128" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K128" s="0" t="s">
         <v>25</v>
@@ -9394,11 +9418,11 @@
       <c r="O128" s="0">
         <v>1</v>
       </c>
-      <c r="P128" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q128" s="0">
-        <v>0</v>
+      <c r="P128" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q128" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R128" s="0" t="s">
         <v>25</v>
@@ -9421,19 +9445,19 @@
         <v>160</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C129" s="0">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="D129" s="1">
-        <v>46196.88885416667</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="E129" s="1">
-        <v>46196.88885416667</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="F129" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>30</v>
@@ -9445,7 +9469,7 @@
         <v>30</v>
       </c>
       <c r="J129" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K129" s="0" t="s">
         <v>25</v>
@@ -9463,10 +9487,10 @@
         <v>1</v>
       </c>
       <c r="P129" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q129" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="Q129" s="0">
+        <v>1</v>
       </c>
       <c r="R129" s="0" t="s">
         <v>25</v>
@@ -9489,28 +9513,28 @@
         <v>161</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C130" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D130" s="1">
-        <v>46199.89765046296</v>
+        <v>46207.28523148148</v>
       </c>
       <c r="E130" s="1">
-        <v>46199.89765046296</v>
+        <v>46207.28523148148</v>
       </c>
       <c r="F130" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G130" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H130" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J130" s="0" t="s">
         <v>25</v>
@@ -9530,8 +9554,8 @@
       <c r="O130" s="0">
         <v>1</v>
       </c>
-      <c r="P130" s="0">
-        <v>0</v>
+      <c r="P130" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q130" s="0" t="s">
         <v>25</v>
@@ -9549,7 +9573,7 @@
         <v>25</v>
       </c>
       <c r="V130" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131">
@@ -9557,19 +9581,19 @@
         <v>162</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C131" s="0">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="D131" s="1">
-        <v>46203.38673611111</v>
+        <v>46196.788564814815</v>
       </c>
       <c r="E131" s="1">
-        <v>46203.38673611111</v>
+        <v>46196.788564814815</v>
       </c>
       <c r="F131" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>30</v>
@@ -9578,7 +9602,7 @@
         <v>30</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J131" s="0" t="s">
         <v>25</v>
@@ -9598,8 +9622,8 @@
       <c r="O131" s="0">
         <v>1</v>
       </c>
-      <c r="P131" s="0">
-        <v>0</v>
+      <c r="P131" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q131" s="0" t="s">
         <v>25</v>
@@ -9625,19 +9649,19 @@
         <v>163</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C132" s="0">
-        <v>2518</v>
+        <v>262</v>
       </c>
       <c r="D132" s="1">
-        <v>46208.24219907408</v>
+        <v>46200.45096064815</v>
       </c>
       <c r="E132" s="1">
-        <v>46208.49730324074</v>
+        <v>46200.45096064815</v>
       </c>
       <c r="F132" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>39</v>
@@ -9646,10 +9670,10 @@
         <v>39</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J132" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K132" s="0" t="s">
         <v>25</v>
@@ -9664,13 +9688,13 @@
         <v>25</v>
       </c>
       <c r="O132" s="0">
-        <v>1</v>
-      </c>
-      <c r="P132" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q132" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P132" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q132" s="0">
+        <v>0</v>
       </c>
       <c r="R132" s="0" t="s">
         <v>25</v>
@@ -9693,28 +9717,28 @@
         <v>164</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C133" s="0">
-        <v>2025</v>
+        <v>336</v>
       </c>
       <c r="D133" s="1">
-        <v>46202.83125</v>
+        <v>46198.12163194444</v>
       </c>
       <c r="E133" s="1">
-        <v>46205.35525462963</v>
+        <v>46207.18237268519</v>
       </c>
       <c r="F133" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J133" s="0" t="s">
         <v>25</v>
@@ -9732,10 +9756,10 @@
         <v>25</v>
       </c>
       <c r="O133" s="0">
-        <v>0</v>
-      </c>
-      <c r="P133" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P133" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q133" s="0" t="s">
         <v>25</v>
@@ -9753,7 +9777,7 @@
         <v>25</v>
       </c>
       <c r="V133" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134">
@@ -9761,31 +9785,31 @@
         <v>165</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C134" s="0">
-        <v>206</v>
+        <v>13108</v>
       </c>
       <c r="D134" s="1">
-        <v>46199.259988425925</v>
+        <v>46197.70695601852</v>
       </c>
       <c r="E134" s="1">
-        <v>46200.595925925925</v>
+        <v>46198.89733796296</v>
       </c>
       <c r="F134" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J134" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K134" s="0" t="s">
         <v>25</v>
@@ -9800,13 +9824,13 @@
         <v>25</v>
       </c>
       <c r="O134" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P134" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q134" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="Q134" s="0">
+        <v>0</v>
       </c>
       <c r="R134" s="0" t="s">
         <v>25</v>
@@ -9821,7 +9845,7 @@
         <v>25</v>
       </c>
       <c r="V134" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="135">
@@ -9829,19 +9853,19 @@
         <v>166</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C135" s="0">
-        <v>2108</v>
+        <v>13108</v>
       </c>
       <c r="D135" s="1">
-        <v>46196.84064814815</v>
+        <v>46201.693333333336</v>
       </c>
       <c r="E135" s="1">
-        <v>46198.36408564815</v>
+        <v>46205.19603009259</v>
       </c>
       <c r="F135" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>24</v>
@@ -9853,7 +9877,7 @@
         <v>24</v>
       </c>
       <c r="J135" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K135" s="0" t="s">
         <v>25</v>
@@ -9871,10 +9895,10 @@
         <v>0</v>
       </c>
       <c r="P135" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q135" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q135" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R135" s="0" t="s">
         <v>25</v>
@@ -9897,31 +9921,31 @@
         <v>167</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C136" s="0">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="D136" s="1">
-        <v>46208.95462962963</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="E136" s="1">
-        <v>46208.95462962963</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="F136" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J136" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K136" s="0" t="s">
         <v>25</v>
@@ -9938,11 +9962,11 @@
       <c r="O136" s="0">
         <v>1</v>
       </c>
-      <c r="P136" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q136" s="0" t="s">
-        <v>25</v>
+      <c r="P136" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q136" s="0">
+        <v>0</v>
       </c>
       <c r="R136" s="0" t="s">
         <v>25</v>
@@ -9957,7 +9981,7 @@
         <v>25</v>
       </c>
       <c r="V136" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137">
@@ -9965,28 +9989,28 @@
         <v>168</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C137" s="0">
-        <v>13108</v>
+        <v>262</v>
       </c>
       <c r="D137" s="1">
-        <v>46205.32334490741</v>
+        <v>46196.88885416667</v>
       </c>
       <c r="E137" s="1">
-        <v>46209.34474537037</v>
+        <v>46196.88885416667</v>
       </c>
       <c r="F137" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G137" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H137" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J137" s="0" t="s">
         <v>25</v>
@@ -10004,10 +10028,10 @@
         <v>25</v>
       </c>
       <c r="O137" s="0">
-        <v>0</v>
-      </c>
-      <c r="P137" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P137" s="0">
+        <v>1</v>
       </c>
       <c r="Q137" s="0" t="s">
         <v>25</v>
@@ -10025,7 +10049,7 @@
         <v>25</v>
       </c>
       <c r="V137" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138">
@@ -10033,28 +10057,28 @@
         <v>169</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C138" s="0">
-        <v>344</v>
+        <v>2108</v>
       </c>
       <c r="D138" s="1">
-        <v>46203.6659375</v>
+        <v>46199.89765046296</v>
       </c>
       <c r="E138" s="1">
-        <v>46203.6659375</v>
+        <v>46199.89765046296</v>
       </c>
       <c r="F138" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H138" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J138" s="0" t="s">
         <v>25</v>
@@ -10072,10 +10096,10 @@
         <v>25</v>
       </c>
       <c r="O138" s="0">
-        <v>0</v>
-      </c>
-      <c r="P138" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P138" s="0">
+        <v>1</v>
       </c>
       <c r="Q138" s="0" t="s">
         <v>25</v>
@@ -10093,7 +10117,7 @@
         <v>25</v>
       </c>
       <c r="V138" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="139">
@@ -10101,28 +10125,28 @@
         <v>170</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C139" s="0">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="D139" s="1">
-        <v>46200.18853009259</v>
+        <v>46203.38673611111</v>
       </c>
       <c r="E139" s="1">
-        <v>46200.84137731481</v>
+        <v>46203.38673611111</v>
       </c>
       <c r="F139" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J139" s="0" t="s">
         <v>25</v>
@@ -10143,7 +10167,7 @@
         <v>1</v>
       </c>
       <c r="P139" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q139" s="0" t="s">
         <v>25</v>
@@ -10161,7 +10185,7 @@
         <v>25</v>
       </c>
       <c r="V139" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140">
@@ -10172,22 +10196,22 @@
         <v>23</v>
       </c>
       <c r="C140" s="0">
-        <v>2108</v>
+        <v>2518</v>
       </c>
       <c r="D140" s="1">
-        <v>46205.6671412037</v>
+        <v>46208.24219907408</v>
       </c>
       <c r="E140" s="1">
-        <v>46207.322233796294</v>
+        <v>46208.49730324074</v>
       </c>
       <c r="F140" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I140" s="0" t="s">
         <v>25</v>
@@ -10229,7 +10253,7 @@
         <v>25</v>
       </c>
       <c r="V140" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="141">
@@ -10237,28 +10261,28 @@
         <v>172</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C141" s="0">
-        <v>344</v>
+        <v>2025</v>
       </c>
       <c r="D141" s="1">
-        <v>46203.665925925925</v>
+        <v>46202.83125</v>
       </c>
       <c r="E141" s="1">
-        <v>46203.665925925925</v>
+        <v>46205.35525462963</v>
       </c>
       <c r="F141" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J141" s="0" t="s">
         <v>25</v>
@@ -10276,10 +10300,10 @@
         <v>25</v>
       </c>
       <c r="O141" s="0">
-        <v>1</v>
-      </c>
-      <c r="P141" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P141" s="0">
+        <v>0</v>
       </c>
       <c r="Q141" s="0" t="s">
         <v>25</v>
@@ -10297,7 +10321,7 @@
         <v>25</v>
       </c>
       <c r="V141" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142">
@@ -10305,31 +10329,31 @@
         <v>173</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C142" s="0">
-        <v>2108</v>
+        <v>206</v>
       </c>
       <c r="D142" s="1">
-        <v>46207.904699074075</v>
+        <v>46199.259988425925</v>
       </c>
       <c r="E142" s="1">
-        <v>46208.80619212963</v>
+        <v>46200.595925925925</v>
       </c>
       <c r="F142" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J142" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K142" s="0" t="s">
         <v>25</v>
@@ -10344,13 +10368,13 @@
         <v>25</v>
       </c>
       <c r="O142" s="0">
-        <v>0</v>
-      </c>
-      <c r="P142" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q142" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P142" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q142" s="0">
+        <v>0</v>
       </c>
       <c r="R142" s="0" t="s">
         <v>25</v>
@@ -10365,7 +10389,7 @@
         <v>25</v>
       </c>
       <c r="V142" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143">
@@ -10376,28 +10400,28 @@
         <v>23</v>
       </c>
       <c r="C143" s="0">
-        <v>2123</v>
+        <v>2108</v>
       </c>
       <c r="D143" s="1">
-        <v>46205.68171296296</v>
+        <v>46196.84064814815</v>
       </c>
       <c r="E143" s="1">
-        <v>46207.24060185185</v>
+        <v>46198.36408564815</v>
       </c>
       <c r="F143" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J143" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K143" s="0" t="s">
         <v>25</v>
@@ -10412,13 +10436,13 @@
         <v>25</v>
       </c>
       <c r="O143" s="0">
-        <v>1</v>
-      </c>
-      <c r="P143" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q143" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P143" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q143" s="0">
+        <v>0</v>
       </c>
       <c r="R143" s="0" t="s">
         <v>25</v>
@@ -10433,7 +10457,7 @@
         <v>25</v>
       </c>
       <c r="V143" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144">
@@ -10444,22 +10468,22 @@
         <v>23</v>
       </c>
       <c r="C144" s="0">
-        <v>2108</v>
+        <v>2518</v>
       </c>
       <c r="D144" s="1">
-        <v>46199.41601851852</v>
+        <v>46208.95462962963</v>
       </c>
       <c r="E144" s="1">
-        <v>46202.50537037037</v>
+        <v>46208.95462962963</v>
       </c>
       <c r="F144" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I144" s="0" t="s">
         <v>25</v>
@@ -10480,7 +10504,7 @@
         <v>25</v>
       </c>
       <c r="O144" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P144" s="0" t="s">
         <v>25</v>
@@ -10501,7 +10525,7 @@
         <v>25</v>
       </c>
       <c r="V144" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="145">
@@ -10509,31 +10533,31 @@
         <v>176</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C145" s="0">
-        <v>0</v>
+        <v>13108</v>
       </c>
       <c r="D145" s="1">
-        <v>46196.08100694444</v>
+        <v>46205.32334490741</v>
       </c>
       <c r="E145" s="1">
-        <v>46196.08100694444</v>
+        <v>46209.34474537037</v>
       </c>
       <c r="F145" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J145" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K145" s="0" t="s">
         <v>25</v>
@@ -10550,11 +10574,11 @@
       <c r="O145" s="0">
         <v>1</v>
       </c>
-      <c r="P145" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q145" s="0">
-        <v>1</v>
+      <c r="P145" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q145" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R145" s="0" t="s">
         <v>25</v>
@@ -10569,7 +10593,7 @@
         <v>25</v>
       </c>
       <c r="V145" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146">
@@ -10577,31 +10601,31 @@
         <v>177</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C146" s="0">
-        <v>2518</v>
+        <v>344</v>
       </c>
       <c r="D146" s="1">
-        <v>46198.78761574074</v>
+        <v>46203.6659375</v>
       </c>
       <c r="E146" s="1">
-        <v>46200.24690972222</v>
+        <v>46203.6659375</v>
       </c>
       <c r="F146" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J146" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K146" s="0" t="s">
         <v>25</v>
@@ -10616,13 +10640,13 @@
         <v>25</v>
       </c>
       <c r="O146" s="0">
-        <v>1</v>
-      </c>
-      <c r="P146" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q146" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P146" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q146" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R146" s="0" t="s">
         <v>25</v>
@@ -10637,7 +10661,7 @@
         <v>25</v>
       </c>
       <c r="V146" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147">
@@ -10648,28 +10672,28 @@
         <v>23</v>
       </c>
       <c r="C147" s="0">
-        <v>2099</v>
+        <v>2518</v>
       </c>
       <c r="D147" s="1">
-        <v>46200.39493055556</v>
+        <v>46200.18853009259</v>
       </c>
       <c r="E147" s="1">
-        <v>46200.39493055556</v>
+        <v>46200.84137731481</v>
       </c>
       <c r="F147" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J147" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K147" s="0" t="s">
         <v>25</v>
@@ -10684,13 +10708,13 @@
         <v>25</v>
       </c>
       <c r="O147" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P147" s="0">
         <v>1</v>
       </c>
-      <c r="Q147" s="0" t="s">
-        <v>25</v>
+      <c r="Q147" s="0">
+        <v>0</v>
       </c>
       <c r="R147" s="0" t="s">
         <v>25</v>
@@ -10705,7 +10729,7 @@
         <v>25</v>
       </c>
       <c r="V147" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="148">
@@ -10716,16 +10740,16 @@
         <v>23</v>
       </c>
       <c r="C148" s="0">
-        <v>2046</v>
+        <v>2108</v>
       </c>
       <c r="D148" s="1">
-        <v>46200.55334490741</v>
+        <v>46205.6671412037</v>
       </c>
       <c r="E148" s="1">
-        <v>46201.81197916667</v>
+        <v>46207.322233796294</v>
       </c>
       <c r="F148" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>24</v>
@@ -10734,7 +10758,7 @@
         <v>24</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J148" s="0" t="s">
         <v>25</v>
@@ -10752,10 +10776,10 @@
         <v>25</v>
       </c>
       <c r="O148" s="0">
-        <v>0</v>
-      </c>
-      <c r="P148" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P148" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q148" s="0" t="s">
         <v>25</v>
@@ -10781,31 +10805,31 @@
         <v>180</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C149" s="0">
-        <v>2108</v>
+        <v>344</v>
       </c>
       <c r="D149" s="1">
-        <v>46196.56989583333</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="E149" s="1">
-        <v>46196.87100694444</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="F149" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J149" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K149" s="0" t="s">
         <v>25</v>
@@ -10820,13 +10844,13 @@
         <v>25</v>
       </c>
       <c r="O149" s="0">
-        <v>0</v>
-      </c>
-      <c r="P149" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q149" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P149" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q149" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R149" s="0" t="s">
         <v>25</v>
@@ -10841,7 +10865,7 @@
         <v>25</v>
       </c>
       <c r="V149" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150">
@@ -10849,28 +10873,28 @@
         <v>181</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C150" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D150" s="1">
-        <v>46203.38674768519</v>
+        <v>46207.904699074075</v>
       </c>
       <c r="E150" s="1">
-        <v>46203.38674768519</v>
+        <v>46208.80619212963</v>
       </c>
       <c r="F150" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J150" s="0" t="s">
         <v>25</v>
@@ -10888,10 +10912,10 @@
         <v>25</v>
       </c>
       <c r="O150" s="0">
-        <v>1</v>
-      </c>
-      <c r="P150" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P150" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q150" s="0" t="s">
         <v>25</v>
@@ -10909,7 +10933,7 @@
         <v>25</v>
       </c>
       <c r="V150" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="151">
@@ -10917,19 +10941,19 @@
         <v>182</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C151" s="0">
-        <v>0</v>
+        <v>2123</v>
       </c>
       <c r="D151" s="1">
-        <v>46199.38827546296</v>
+        <v>46205.68171296296</v>
       </c>
       <c r="E151" s="1">
-        <v>46199.38827546296</v>
+        <v>46207.24060185185</v>
       </c>
       <c r="F151" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>30</v>
@@ -10938,7 +10962,7 @@
         <v>30</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J151" s="0" t="s">
         <v>25</v>
@@ -10958,8 +10982,8 @@
       <c r="O151" s="0">
         <v>1</v>
       </c>
-      <c r="P151" s="0">
-        <v>1</v>
+      <c r="P151" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q151" s="0" t="s">
         <v>25</v>
@@ -10985,25 +11009,25 @@
         <v>183</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C152" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D152" s="1">
-        <v>46198.75832175926</v>
+        <v>46199.41601851852</v>
       </c>
       <c r="E152" s="1">
-        <v>46198.75832175926</v>
+        <v>46202.50537037037</v>
       </c>
       <c r="F152" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I152" s="0" t="s">
         <v>25</v>
@@ -11024,7 +11048,7 @@
         <v>25</v>
       </c>
       <c r="O152" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P152" s="0" t="s">
         <v>25</v>
@@ -11045,7 +11069,7 @@
         <v>25</v>
       </c>
       <c r="V152" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="153">
@@ -11053,31 +11077,31 @@
         <v>184</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C153" s="0">
-        <v>2025</v>
+        <v>0</v>
       </c>
       <c r="D153" s="1">
-        <v>46200.08666666667</v>
+        <v>46196.08100694444</v>
       </c>
       <c r="E153" s="1">
-        <v>46200.08666666667</v>
+        <v>46196.08100694444</v>
       </c>
       <c r="F153" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G153" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J153" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K153" s="0" t="s">
         <v>25</v>
@@ -11097,8 +11121,8 @@
       <c r="P153" s="0">
         <v>0</v>
       </c>
-      <c r="Q153" s="0" t="s">
-        <v>25</v>
+      <c r="Q153" s="0">
+        <v>1</v>
       </c>
       <c r="R153" s="0" t="s">
         <v>25</v>
@@ -11113,7 +11137,7 @@
         <v>25</v>
       </c>
       <c r="V153" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="154">
@@ -11121,31 +11145,31 @@
         <v>185</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C154" s="0">
-        <v>336</v>
+        <v>2518</v>
       </c>
       <c r="D154" s="1">
-        <v>46191.19981481481</v>
+        <v>46198.78761574074</v>
       </c>
       <c r="E154" s="1">
-        <v>46191.20039351852</v>
+        <v>46200.24690972222</v>
       </c>
       <c r="F154" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J154" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K154" s="0" t="s">
         <v>25</v>
@@ -11160,13 +11184,13 @@
         <v>25</v>
       </c>
       <c r="O154" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P154" s="0">
         <v>1</v>
       </c>
       <c r="Q154" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R154" s="0" t="s">
         <v>25</v>
@@ -11181,7 +11205,7 @@
         <v>25</v>
       </c>
       <c r="V154" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="155">
@@ -11189,19 +11213,19 @@
         <v>186</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C155" s="0">
-        <v>0</v>
+        <v>2099</v>
       </c>
       <c r="D155" s="1">
-        <v>46198.06826388889</v>
+        <v>46200.39493055556</v>
       </c>
       <c r="E155" s="1">
-        <v>46198.06826388889</v>
+        <v>46200.39493055556</v>
       </c>
       <c r="F155" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>30</v>
@@ -11210,10 +11234,10 @@
         <v>30</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J155" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K155" s="0" t="s">
         <v>25</v>
@@ -11228,13 +11252,13 @@
         <v>25</v>
       </c>
       <c r="O155" s="0">
-        <v>1</v>
-      </c>
-      <c r="P155" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q155" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P155" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q155" s="0">
+        <v>0</v>
       </c>
       <c r="R155" s="0" t="s">
         <v>25</v>
@@ -11257,31 +11281,31 @@
         <v>187</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C156" s="0">
-        <v>262</v>
+        <v>2046</v>
       </c>
       <c r="D156" s="1">
-        <v>46197.6375462963</v>
+        <v>46200.55334490741</v>
       </c>
       <c r="E156" s="1">
-        <v>46197.6375462963</v>
+        <v>46201.81197916667</v>
       </c>
       <c r="F156" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G156" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J156" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K156" s="0" t="s">
         <v>25</v>
@@ -11299,10 +11323,10 @@
         <v>0</v>
       </c>
       <c r="P156" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q156" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q156" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R156" s="0" t="s">
         <v>25</v>
@@ -11317,7 +11341,7 @@
         <v>25</v>
       </c>
       <c r="V156" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="157">
@@ -11325,31 +11349,31 @@
         <v>188</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C157" s="0">
-        <v>304112</v>
+        <v>2108</v>
       </c>
       <c r="D157" s="1">
-        <v>46197.037523148145</v>
+        <v>46196.56989583333</v>
       </c>
       <c r="E157" s="1">
-        <v>46197.037523148145</v>
+        <v>46196.87100694444</v>
       </c>
       <c r="F157" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J157" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K157" s="0" t="s">
         <v>25</v>
@@ -11364,10 +11388,10 @@
         <v>25</v>
       </c>
       <c r="O157" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P157" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q157" s="0">
         <v>0</v>
@@ -11385,7 +11409,7 @@
         <v>25</v>
       </c>
       <c r="V157" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="158">
@@ -11393,31 +11417,31 @@
         <v>189</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C158" s="0">
-        <v>2106</v>
+        <v>0</v>
       </c>
       <c r="D158" s="1">
-        <v>46197.12175925926</v>
+        <v>46203.38674768519</v>
       </c>
       <c r="E158" s="1">
-        <v>46198.31060185185</v>
+        <v>46203.38674768519</v>
       </c>
       <c r="F158" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J158" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K158" s="0" t="s">
         <v>25</v>
@@ -11435,10 +11459,10 @@
         <v>1</v>
       </c>
       <c r="P158" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q158" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q158" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R158" s="0" t="s">
         <v>25</v>
@@ -11453,7 +11477,7 @@
         <v>25</v>
       </c>
       <c r="V158" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159">
@@ -11461,28 +11485,28 @@
         <v>190</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C159" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D159" s="1">
-        <v>46202.840995370374</v>
+        <v>46199.38827546296</v>
       </c>
       <c r="E159" s="1">
-        <v>46209.31466435185</v>
+        <v>46199.38827546296</v>
       </c>
       <c r="F159" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G159" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J159" s="0" t="s">
         <v>25</v>
@@ -11500,10 +11524,10 @@
         <v>25</v>
       </c>
       <c r="O159" s="0">
-        <v>0</v>
-      </c>
-      <c r="P159" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P159" s="0">
+        <v>1</v>
       </c>
       <c r="Q159" s="0" t="s">
         <v>25</v>
@@ -11521,7 +11545,7 @@
         <v>25</v>
       </c>
       <c r="V159" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160">
@@ -11529,25 +11553,25 @@
         <v>191</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C160" s="0">
-        <v>2009</v>
+        <v>0</v>
       </c>
       <c r="D160" s="1">
-        <v>46206.72038194445</v>
+        <v>46198.75832175926</v>
       </c>
       <c r="E160" s="1">
-        <v>46206.72038194445</v>
+        <v>46198.75832175926</v>
       </c>
       <c r="F160" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G160" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I160" s="0" t="s">
         <v>25</v>
@@ -11589,7 +11613,7 @@
         <v>25</v>
       </c>
       <c r="V160" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="161">
@@ -11600,28 +11624,28 @@
         <v>23</v>
       </c>
       <c r="C161" s="0">
-        <v>2044</v>
+        <v>2025</v>
       </c>
       <c r="D161" s="1">
-        <v>46197.46810185185</v>
+        <v>46200.08666666667</v>
       </c>
       <c r="E161" s="1">
-        <v>46197.46810185185</v>
+        <v>46200.08666666667</v>
       </c>
       <c r="F161" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J161" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K161" s="0" t="s">
         <v>25</v>
@@ -11636,13 +11660,13 @@
         <v>25</v>
       </c>
       <c r="O161" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P161" s="0">
         <v>0</v>
       </c>
-      <c r="Q161" s="0">
-        <v>1</v>
+      <c r="Q161" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R161" s="0" t="s">
         <v>25</v>
@@ -11657,7 +11681,7 @@
         <v>25</v>
       </c>
       <c r="V161" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="162">
@@ -11665,31 +11689,31 @@
         <v>193</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C162" s="0">
-        <v>2518</v>
+        <v>336</v>
       </c>
       <c r="D162" s="1">
-        <v>46200.77527777778</v>
+        <v>46191.19981481481</v>
       </c>
       <c r="E162" s="1">
-        <v>46202.349328703705</v>
+        <v>46191.20039351852</v>
       </c>
       <c r="F162" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J162" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K162" s="0" t="s">
         <v>25</v>
@@ -11704,13 +11728,13 @@
         <v>25</v>
       </c>
       <c r="O162" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P162" s="0">
         <v>1</v>
       </c>
-      <c r="Q162" s="0" t="s">
-        <v>25</v>
+      <c r="Q162" s="0">
+        <v>0</v>
       </c>
       <c r="R162" s="0" t="s">
         <v>25</v>
@@ -11725,7 +11749,7 @@
         <v>25</v>
       </c>
       <c r="V162" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="163">
@@ -11739,13 +11763,13 @@
         <v>0</v>
       </c>
       <c r="D163" s="1">
-        <v>46198.75665509259</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="E163" s="1">
-        <v>46198.75665509259</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="F163" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>30</v>
@@ -11801,31 +11825,31 @@
         <v>195</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C164" s="0">
-        <v>2108</v>
+        <v>262</v>
       </c>
       <c r="D164" s="1">
-        <v>46205.784363425926</v>
+        <v>46197.6375462963</v>
       </c>
       <c r="E164" s="1">
-        <v>46205.784363425926</v>
+        <v>46197.6375462963</v>
       </c>
       <c r="F164" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G164" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H164" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J164" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K164" s="0" t="s">
         <v>25</v>
@@ -11840,13 +11864,13 @@
         <v>25</v>
       </c>
       <c r="O164" s="0">
-        <v>1</v>
-      </c>
-      <c r="P164" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q164" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P164" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q164" s="0">
+        <v>0</v>
       </c>
       <c r="R164" s="0" t="s">
         <v>25</v>
@@ -11861,7 +11885,7 @@
         <v>25</v>
       </c>
       <c r="V164" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165">
@@ -11869,19 +11893,19 @@
         <v>196</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C165" s="0">
-        <v>0</v>
+        <v>304112</v>
       </c>
       <c r="D165" s="1">
-        <v>46198.75827546296</v>
+        <v>46197.037523148145</v>
       </c>
       <c r="E165" s="1">
-        <v>46198.75827546296</v>
+        <v>46197.037523148145</v>
       </c>
       <c r="F165" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>30</v>
@@ -11890,10 +11914,10 @@
         <v>30</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J165" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K165" s="0" t="s">
         <v>25</v>
@@ -11910,11 +11934,11 @@
       <c r="O165" s="0">
         <v>1</v>
       </c>
-      <c r="P165" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q165" s="0" t="s">
-        <v>25</v>
+      <c r="P165" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q165" s="0">
+        <v>0</v>
       </c>
       <c r="R165" s="0" t="s">
         <v>25</v>
@@ -11940,28 +11964,28 @@
         <v>23</v>
       </c>
       <c r="C166" s="0">
-        <v>2025</v>
+        <v>2106</v>
       </c>
       <c r="D166" s="1">
-        <v>46203.80048611111</v>
+        <v>46197.12175925926</v>
       </c>
       <c r="E166" s="1">
-        <v>46203.80048611111</v>
+        <v>46198.31060185185</v>
       </c>
       <c r="F166" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G166" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J166" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K166" s="0" t="s">
         <v>25</v>
@@ -11978,11 +12002,11 @@
       <c r="O166" s="0">
         <v>1</v>
       </c>
-      <c r="P166" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q166" s="0" t="s">
-        <v>25</v>
+      <c r="P166" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q166" s="0">
+        <v>0</v>
       </c>
       <c r="R166" s="0" t="s">
         <v>25</v>
@@ -11997,7 +12021,7 @@
         <v>25</v>
       </c>
       <c r="V166" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="167">
@@ -12011,13 +12035,13 @@
         <v>2108</v>
       </c>
       <c r="D167" s="1">
-        <v>46205.49758101852</v>
+        <v>46202.840995370374</v>
       </c>
       <c r="E167" s="1">
-        <v>46207.377118055556</v>
+        <v>46209.31466435185</v>
       </c>
       <c r="F167" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>24</v>
@@ -12044,7 +12068,7 @@
         <v>25</v>
       </c>
       <c r="O167" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P167" s="0" t="s">
         <v>25</v>
@@ -12073,25 +12097,25 @@
         <v>199</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C168" s="0">
-        <v>0</v>
+        <v>2009</v>
       </c>
       <c r="D168" s="1">
-        <v>46198.76320601852</v>
+        <v>46206.72038194445</v>
       </c>
       <c r="E168" s="1">
-        <v>46198.76320601852</v>
+        <v>46206.72038194445</v>
       </c>
       <c r="F168" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I168" s="0" t="s">
         <v>25</v>
@@ -12133,7 +12157,7 @@
         <v>25</v>
       </c>
       <c r="V168" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="169">
@@ -12141,31 +12165,31 @@
         <v>200</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C169" s="0">
-        <v>205</v>
+        <v>2044</v>
       </c>
       <c r="D169" s="1">
-        <v>46207.94667824074</v>
+        <v>46197.46810185185</v>
       </c>
       <c r="E169" s="1">
-        <v>46209.364849537036</v>
+        <v>46197.46810185185</v>
       </c>
       <c r="F169" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G169" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J169" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K169" s="0" t="s">
         <v>25</v>
@@ -12180,13 +12204,13 @@
         <v>25</v>
       </c>
       <c r="O169" s="0">
-        <v>1</v>
-      </c>
-      <c r="P169" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q169" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P169" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q169" s="0">
+        <v>1</v>
       </c>
       <c r="R169" s="0" t="s">
         <v>25</v>
@@ -12201,7 +12225,7 @@
         <v>25</v>
       </c>
       <c r="V169" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170">
@@ -12209,28 +12233,28 @@
         <v>201</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C170" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D170" s="1">
-        <v>46198.76327546296</v>
+        <v>46200.77527777778</v>
       </c>
       <c r="E170" s="1">
-        <v>46198.76327546296</v>
+        <v>46202.349328703705</v>
       </c>
       <c r="F170" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J170" s="0" t="s">
         <v>25</v>
@@ -12250,8 +12274,8 @@
       <c r="O170" s="0">
         <v>1</v>
       </c>
-      <c r="P170" s="0" t="s">
-        <v>25</v>
+      <c r="P170" s="0">
+        <v>1</v>
       </c>
       <c r="Q170" s="0" t="s">
         <v>25</v>
@@ -12269,7 +12293,7 @@
         <v>25</v>
       </c>
       <c r="V170" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="171">
@@ -12277,19 +12301,19 @@
         <v>202</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C171" s="0">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="D171" s="1">
-        <v>46197.041238425925</v>
+        <v>46198.75665509259</v>
       </c>
       <c r="E171" s="1">
-        <v>46197.041238425925</v>
+        <v>46198.75665509259</v>
       </c>
       <c r="F171" s="1">
-        <v>46210.042245717596</v>
+        <v>46211.04225972222</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>30</v>
@@ -12298,10 +12322,10 @@
         <v>30</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J171" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K171" s="0" t="s">
         <v>25</v>
@@ -12318,11 +12342,11 @@
       <c r="O171" s="0">
         <v>1</v>
       </c>
-      <c r="P171" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q171" s="0">
-        <v>0</v>
+      <c r="P171" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q171" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R171" s="0" t="s">
         <v>25</v>
@@ -12345,66 +12369,610 @@
         <v>203</v>
       </c>
       <c r="B172" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C172" s="0">
+        <v>2108</v>
+      </c>
+      <c r="D172" s="1">
+        <v>46205.784363425926</v>
+      </c>
+      <c r="E172" s="1">
+        <v>46205.784363425926</v>
+      </c>
+      <c r="F172" s="1">
+        <v>46211.04225972222</v>
+      </c>
+      <c r="G172" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="H172" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O172" s="0">
+        <v>1</v>
+      </c>
+      <c r="P172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U172" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V172" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="B173" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C173" s="0">
+        <v>0</v>
+      </c>
+      <c r="D173" s="1">
+        <v>46198.75827546296</v>
+      </c>
+      <c r="E173" s="1">
+        <v>46198.75827546296</v>
+      </c>
+      <c r="F173" s="1">
+        <v>46211.04225972222</v>
+      </c>
+      <c r="G173" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H173" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O173" s="0">
+        <v>1</v>
+      </c>
+      <c r="P173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U173" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V173" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="B174" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C174" s="0">
+        <v>2025</v>
+      </c>
+      <c r="D174" s="1">
+        <v>46203.80048611111</v>
+      </c>
+      <c r="E174" s="1">
+        <v>46203.80048611111</v>
+      </c>
+      <c r="F174" s="1">
+        <v>46211.04225972222</v>
+      </c>
+      <c r="G174" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="H174" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O174" s="0">
+        <v>1</v>
+      </c>
+      <c r="P174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U174" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V174" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="B175" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C175" s="0">
+        <v>2108</v>
+      </c>
+      <c r="D175" s="1">
+        <v>46205.49758101852</v>
+      </c>
+      <c r="E175" s="1">
+        <v>46207.377118055556</v>
+      </c>
+      <c r="F175" s="1">
+        <v>46211.04225972222</v>
+      </c>
+      <c r="G175" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H175" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O175" s="0">
+        <v>1</v>
+      </c>
+      <c r="P175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U175" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V175" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="B176" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C176" s="0">
+        <v>0</v>
+      </c>
+      <c r="D176" s="1">
+        <v>46198.76320601852</v>
+      </c>
+      <c r="E176" s="1">
+        <v>46198.76320601852</v>
+      </c>
+      <c r="F176" s="1">
+        <v>46211.04225972222</v>
+      </c>
+      <c r="G176" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H176" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O176" s="0">
+        <v>1</v>
+      </c>
+      <c r="P176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U176" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V176" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="B177" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C172" s="0">
+      <c r="C177" s="0">
+        <v>205</v>
+      </c>
+      <c r="D177" s="1">
+        <v>46207.94667824074</v>
+      </c>
+      <c r="E177" s="1">
+        <v>46209.364849537036</v>
+      </c>
+      <c r="F177" s="1">
+        <v>46211.04225972222</v>
+      </c>
+      <c r="G177" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="H177" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O177" s="0">
+        <v>1</v>
+      </c>
+      <c r="P177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U177" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V177" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="B178" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C178" s="0">
+        <v>0</v>
+      </c>
+      <c r="D178" s="1">
+        <v>46198.76327546296</v>
+      </c>
+      <c r="E178" s="1">
+        <v>46198.76327546296</v>
+      </c>
+      <c r="F178" s="1">
+        <v>46211.04225972222</v>
+      </c>
+      <c r="G178" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H178" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O178" s="0">
+        <v>1</v>
+      </c>
+      <c r="P178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U178" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V178" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="B179" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C179" s="0">
+        <v>312</v>
+      </c>
+      <c r="D179" s="1">
+        <v>46197.041238425925</v>
+      </c>
+      <c r="E179" s="1">
+        <v>46197.041238425925</v>
+      </c>
+      <c r="F179" s="1">
+        <v>46211.04225972222</v>
+      </c>
+      <c r="G179" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H179" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I179" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J179" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K179" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L179" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M179" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N179" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O179" s="0">
+        <v>1</v>
+      </c>
+      <c r="P179" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q179" s="0">
+        <v>0</v>
+      </c>
+      <c r="R179" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S179" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T179" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U179" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V179" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="B180" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C180" s="0">
         <v>262</v>
       </c>
-      <c r="D172" s="1">
+      <c r="D180" s="1">
         <v>46200.44310185185</v>
       </c>
-      <c r="E172" s="1">
+      <c r="E180" s="1">
         <v>46200.44310185185</v>
       </c>
-      <c r="F172" s="1">
-        <v>46210.042245717596</v>
-      </c>
-      <c r="G172" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="H172" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="I172" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="J172" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="K172" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="L172" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="M172" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="N172" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="O172" s="0">
-        <v>0</v>
-      </c>
-      <c r="P172" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q172" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="R172" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="S172" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="T172" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="U172" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="V172" s="0" t="s">
+      <c r="F180" s="1">
+        <v>46211.04225972222</v>
+      </c>
+      <c r="G180" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H180" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I180" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J180" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O180" s="0">
+        <v>0</v>
+      </c>
+      <c r="P180" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q180" s="0">
+        <v>0</v>
+      </c>
+      <c r="R180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V180" s="0" t="s">
         <v>30</v>
       </c>
     </row>

--- a/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
+++ b/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
   <si>
     <t>SampleId</t>
   </si>
@@ -269,6 +269,9 @@
     <t>48a9a7e9f58c72b49f61d9b8f2b62d41</t>
   </si>
   <si>
+    <t>49c97e13e5c56cfc8830373c5f470419</t>
+  </si>
+  <si>
     <t>4aa8d2b9e7148b55341bbef8eb3bf0d5</t>
   </si>
   <si>
@@ -356,6 +359,9 @@
     <t>6c9a265491b038b6bf432f12b6ead67e</t>
   </si>
   <si>
+    <t>6cdbec8d4bfa7aa48a6fb654632748dc</t>
+  </si>
+  <si>
     <t>70d6fde22cc3addc70766e5fd0aeff92</t>
   </si>
   <si>
@@ -389,6 +395,9 @@
     <t>79667d1731ee4f94ef0173328c623cbf</t>
   </si>
   <si>
+    <t>79bfb2684eb9e30e05136a24a0585d5c</t>
+  </si>
+  <si>
     <t>7a58f6a326b1b174097d45703a3a0dc7</t>
   </si>
   <si>
@@ -416,6 +425,9 @@
     <t>88fc6837345eb4c3adf2e536120f47c9</t>
   </si>
   <si>
+    <t>8915f5f76097f2facad7e7535a34899e</t>
+  </si>
+  <si>
     <t>8aceb4cd728995daecc5c71b1397461b</t>
   </si>
   <si>
@@ -579,6 +591,9 @@
   </si>
   <si>
     <t>e29d151df9172cccbbd4682b1e677776</t>
+  </si>
+  <si>
+    <t>e2dfaa6c86221b8e2bc1cf63ee61f0c2</t>
   </si>
   <si>
     <t>e45bcbaf6b3029d0106177307518596e</t>
@@ -695,8 +710,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AicsGlobal_Classifications_TimeWindows" displayName="AicsGlobal_Classifications_TimeWindows" ref="A1:V180" headerRowCount="1">
-  <autoFilter ref="A1:V180"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AicsGlobal_Classifications_TimeWindows" displayName="AicsGlobal_Classifications_TimeWindows" ref="A1:V185" headerRowCount="1">
+  <autoFilter ref="A1:V185"/>
   <tableColumns count="22">
     <tableColumn id="1" name="SampleId"/>
     <tableColumn id="2" name="SIGDetection"/>
@@ -727,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:V180"/>
+  <dimension ref="A1:V185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.540952682495117" customWidth="1"/>
@@ -821,7 +836,7 @@
         <v>46204.34583333333</v>
       </c>
       <c r="F2" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>24</v>
@@ -889,7 +904,7 @@
         <v>46207.15827546296</v>
       </c>
       <c r="F3" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>24</v>
@@ -898,7 +913,7 @@
         <v>24</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>25</v>
@@ -918,8 +933,8 @@
       <c r="O3" s="0">
         <v>1</v>
       </c>
-      <c r="P3" s="0" t="s">
-        <v>25</v>
+      <c r="P3" s="0">
+        <v>0</v>
       </c>
       <c r="Q3" s="0" t="s">
         <v>25</v>
@@ -957,7 +972,7 @@
         <v>46200.30415509259</v>
       </c>
       <c r="F4" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>24</v>
@@ -1025,7 +1040,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F5" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>30</v>
@@ -1093,7 +1108,7 @@
         <v>46198.75680555555</v>
       </c>
       <c r="F6" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>30</v>
@@ -1102,7 +1117,7 @@
         <v>30</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>25</v>
@@ -1122,8 +1137,8 @@
       <c r="O6" s="0">
         <v>1</v>
       </c>
-      <c r="P6" s="0" t="s">
-        <v>25</v>
+      <c r="P6" s="0">
+        <v>0</v>
       </c>
       <c r="Q6" s="0" t="s">
         <v>25</v>
@@ -1161,7 +1176,7 @@
         <v>46200.02773148148</v>
       </c>
       <c r="F7" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>24</v>
@@ -1229,7 +1244,7 @@
         <v>46200.57623842593</v>
       </c>
       <c r="F8" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>24</v>
@@ -1297,7 +1312,7 @@
         <v>46198.764027777775</v>
       </c>
       <c r="F9" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>30</v>
@@ -1306,7 +1321,7 @@
         <v>30</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>25</v>
@@ -1326,8 +1341,8 @@
       <c r="O9" s="0">
         <v>1</v>
       </c>
-      <c r="P9" s="0" t="s">
-        <v>25</v>
+      <c r="P9" s="0">
+        <v>0</v>
       </c>
       <c r="Q9" s="0" t="s">
         <v>25</v>
@@ -1365,7 +1380,7 @@
         <v>46198.18491898148</v>
       </c>
       <c r="F10" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>24</v>
@@ -1433,7 +1448,7 @@
         <v>46203.81460648148</v>
       </c>
       <c r="F11" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>39</v>
@@ -1501,7 +1516,7 @@
         <v>46201.33733796296</v>
       </c>
       <c r="F12" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>24</v>
@@ -1569,7 +1584,7 @@
         <v>46203.71907407408</v>
       </c>
       <c r="F13" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>24</v>
@@ -1637,7 +1652,7 @@
         <v>46195.59105324074</v>
       </c>
       <c r="F14" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>30</v>
@@ -1705,7 +1720,7 @@
         <v>46201.06361111111</v>
       </c>
       <c r="F15" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>24</v>
@@ -1717,7 +1732,7 @@
         <v>24</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K15" s="0" t="s">
         <v>25</v>
@@ -1737,8 +1752,8 @@
       <c r="P15" s="0">
         <v>1</v>
       </c>
-      <c r="Q15" s="0" t="s">
-        <v>25</v>
+      <c r="Q15" s="0">
+        <v>0</v>
       </c>
       <c r="R15" s="0" t="s">
         <v>25</v>
@@ -1773,7 +1788,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F16" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>30</v>
@@ -1803,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="0" t="s">
         <v>25</v>
@@ -1841,7 +1856,7 @@
         <v>46198.5140625</v>
       </c>
       <c r="F17" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G17" s="0" t="s">
         <v>30</v>
@@ -1909,7 +1924,7 @@
         <v>46209.61792824074</v>
       </c>
       <c r="F18" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>39</v>
@@ -1977,7 +1992,7 @@
         <v>46202.38591435185</v>
       </c>
       <c r="F19" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G19" s="0" t="s">
         <v>24</v>
@@ -1989,7 +2004,7 @@
         <v>24</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K19" s="0" t="s">
         <v>25</v>
@@ -2009,8 +2024,8 @@
       <c r="P19" s="0">
         <v>1</v>
       </c>
-      <c r="Q19" s="0" t="s">
-        <v>25</v>
+      <c r="Q19" s="0">
+        <v>0</v>
       </c>
       <c r="R19" s="0" t="s">
         <v>25</v>
@@ -2045,7 +2060,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F20" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G20" s="0" t="s">
         <v>30</v>
@@ -2054,7 +2069,7 @@
         <v>30</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>25</v>
@@ -2074,8 +2089,8 @@
       <c r="O20" s="0">
         <v>1</v>
       </c>
-      <c r="P20" s="0" t="s">
-        <v>25</v>
+      <c r="P20" s="0">
+        <v>0</v>
       </c>
       <c r="Q20" s="0" t="s">
         <v>25</v>
@@ -2113,7 +2128,7 @@
         <v>46205.25707175926</v>
       </c>
       <c r="F21" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G21" s="0" t="s">
         <v>24</v>
@@ -2181,7 +2196,7 @@
         <v>46204.23569444445</v>
       </c>
       <c r="F22" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>24</v>
@@ -2249,7 +2264,7 @@
         <v>46206.293020833335</v>
       </c>
       <c r="F23" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G23" s="0" t="s">
         <v>39</v>
@@ -2317,7 +2332,7 @@
         <v>46198.763715277775</v>
       </c>
       <c r="F24" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>30</v>
@@ -2326,7 +2341,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J24" s="0" t="s">
         <v>25</v>
@@ -2346,8 +2361,8 @@
       <c r="O24" s="0">
         <v>1</v>
       </c>
-      <c r="P24" s="0" t="s">
-        <v>25</v>
+      <c r="P24" s="0">
+        <v>0</v>
       </c>
       <c r="Q24" s="0" t="s">
         <v>25</v>
@@ -2385,7 +2400,7 @@
         <v>46205.502962962964</v>
       </c>
       <c r="F25" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G25" s="0" t="s">
         <v>24</v>
@@ -2394,7 +2409,7 @@
         <v>24</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>25</v>
@@ -2414,8 +2429,8 @@
       <c r="O25" s="0">
         <v>0</v>
       </c>
-      <c r="P25" s="0" t="s">
-        <v>25</v>
+      <c r="P25" s="0">
+        <v>0</v>
       </c>
       <c r="Q25" s="0" t="s">
         <v>25</v>
@@ -2453,7 +2468,7 @@
         <v>46200.67046296296</v>
       </c>
       <c r="F26" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>30</v>
@@ -2521,7 +2536,7 @@
         <v>46199.574282407404</v>
       </c>
       <c r="F27" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G27" s="0" t="s">
         <v>24</v>
@@ -2589,7 +2604,7 @@
         <v>46198.758518518516</v>
       </c>
       <c r="F28" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>30</v>
@@ -2598,7 +2613,7 @@
         <v>30</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>25</v>
@@ -2618,8 +2633,8 @@
       <c r="O28" s="0">
         <v>1</v>
       </c>
-      <c r="P28" s="0" t="s">
-        <v>25</v>
+      <c r="P28" s="0">
+        <v>0</v>
       </c>
       <c r="Q28" s="0" t="s">
         <v>25</v>
@@ -2657,7 +2672,7 @@
         <v>46199.20893518518</v>
       </c>
       <c r="F29" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>24</v>
@@ -2690,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="0" t="s">
         <v>25</v>
@@ -2725,7 +2740,7 @@
         <v>46198.76384259259</v>
       </c>
       <c r="F30" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>30</v>
@@ -2734,7 +2749,7 @@
         <v>30</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>25</v>
@@ -2754,8 +2769,8 @@
       <c r="O30" s="0">
         <v>1</v>
       </c>
-      <c r="P30" s="0" t="s">
-        <v>25</v>
+      <c r="P30" s="0">
+        <v>0</v>
       </c>
       <c r="Q30" s="0" t="s">
         <v>25</v>
@@ -2793,7 +2808,7 @@
         <v>46207.98546296296</v>
       </c>
       <c r="F31" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>24</v>
@@ -2861,7 +2876,7 @@
         <v>46198.758414351854</v>
       </c>
       <c r="F32" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>30</v>
@@ -2870,7 +2885,7 @@
         <v>30</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>25</v>
@@ -2890,8 +2905,8 @@
       <c r="O32" s="0">
         <v>1</v>
       </c>
-      <c r="P32" s="0" t="s">
-        <v>25</v>
+      <c r="P32" s="0">
+        <v>0</v>
       </c>
       <c r="Q32" s="0" t="s">
         <v>25</v>
@@ -2929,7 +2944,7 @@
         <v>46194.2578587963</v>
       </c>
       <c r="F33" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>24</v>
@@ -2962,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="Q33" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="0" t="s">
         <v>25</v>
@@ -2997,7 +3012,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F34" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>30</v>
@@ -3027,7 +3042,7 @@
         <v>1</v>
       </c>
       <c r="P34" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="0" t="s">
         <v>25</v>
@@ -3065,7 +3080,7 @@
         <v>46198.763449074075</v>
       </c>
       <c r="F35" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>30</v>
@@ -3074,7 +3089,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>25</v>
@@ -3094,8 +3109,8 @@
       <c r="O35" s="0">
         <v>1</v>
       </c>
-      <c r="P35" s="0" t="s">
-        <v>25</v>
+      <c r="P35" s="0">
+        <v>0</v>
       </c>
       <c r="Q35" s="0" t="s">
         <v>25</v>
@@ -3133,7 +3148,7 @@
         <v>46198.758125</v>
       </c>
       <c r="F36" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>30</v>
@@ -3142,7 +3157,7 @@
         <v>30</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>25</v>
@@ -3162,8 +3177,8 @@
       <c r="O36" s="0">
         <v>1</v>
       </c>
-      <c r="P36" s="0" t="s">
-        <v>25</v>
+      <c r="P36" s="0">
+        <v>0</v>
       </c>
       <c r="Q36" s="0" t="s">
         <v>25</v>
@@ -3201,7 +3216,7 @@
         <v>46201.54498842593</v>
       </c>
       <c r="F37" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>24</v>
@@ -3213,7 +3228,7 @@
         <v>24</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K37" s="0" t="s">
         <v>25</v>
@@ -3233,8 +3248,8 @@
       <c r="P37" s="0">
         <v>0</v>
       </c>
-      <c r="Q37" s="0" t="s">
-        <v>25</v>
+      <c r="Q37" s="0">
+        <v>0</v>
       </c>
       <c r="R37" s="0" t="s">
         <v>25</v>
@@ -3269,7 +3284,7 @@
         <v>46198.76478009259</v>
       </c>
       <c r="F38" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>30</v>
@@ -3278,7 +3293,7 @@
         <v>30</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J38" s="0" t="s">
         <v>25</v>
@@ -3298,8 +3313,8 @@
       <c r="O38" s="0">
         <v>1</v>
       </c>
-      <c r="P38" s="0" t="s">
-        <v>25</v>
+      <c r="P38" s="0">
+        <v>0</v>
       </c>
       <c r="Q38" s="0" t="s">
         <v>25</v>
@@ -3337,7 +3352,7 @@
         <v>46205.76315972222</v>
       </c>
       <c r="F39" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>24</v>
@@ -3405,7 +3420,7 @@
         <v>46204.83986111111</v>
       </c>
       <c r="F40" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>24</v>
@@ -3473,7 +3488,7 @@
         <v>46203.69975694444</v>
       </c>
       <c r="F41" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>39</v>
@@ -3541,7 +3556,7 @@
         <v>46208.10663194444</v>
       </c>
       <c r="F42" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>24</v>
@@ -3609,7 +3624,7 @@
         <v>46200.854166666664</v>
       </c>
       <c r="F43" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>30</v>
@@ -3677,7 +3692,7 @@
         <v>46205.07099537037</v>
       </c>
       <c r="F44" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>30</v>
@@ -3704,7 +3719,7 @@
         <v>25</v>
       </c>
       <c r="O44" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" s="0" t="s">
         <v>25</v>
@@ -3745,7 +3760,7 @@
         <v>46204.145219907405</v>
       </c>
       <c r="F45" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>30</v>
@@ -3754,7 +3769,7 @@
         <v>30</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J45" s="0" t="s">
         <v>25</v>
@@ -3774,8 +3789,8 @@
       <c r="O45" s="0">
         <v>1</v>
       </c>
-      <c r="P45" s="0" t="s">
-        <v>25</v>
+      <c r="P45" s="0">
+        <v>0</v>
       </c>
       <c r="Q45" s="0" t="s">
         <v>25</v>
@@ -3813,7 +3828,7 @@
         <v>46191.31182870371</v>
       </c>
       <c r="F46" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>30</v>
@@ -3846,7 +3861,7 @@
         <v>1</v>
       </c>
       <c r="Q46" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="0" t="s">
         <v>25</v>
@@ -3881,7 +3896,7 @@
         <v>46199.29518518518</v>
       </c>
       <c r="F47" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>24</v>
@@ -3949,7 +3964,7 @@
         <v>46198.758576388886</v>
       </c>
       <c r="F48" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>30</v>
@@ -3958,7 +3973,7 @@
         <v>30</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J48" s="0" t="s">
         <v>25</v>
@@ -3978,8 +3993,8 @@
       <c r="O48" s="0">
         <v>1</v>
       </c>
-      <c r="P48" s="0" t="s">
-        <v>25</v>
+      <c r="P48" s="0">
+        <v>0</v>
       </c>
       <c r="Q48" s="0" t="s">
         <v>25</v>
@@ -4017,7 +4032,7 @@
         <v>46196.6612962963</v>
       </c>
       <c r="F49" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G49" s="0" t="s">
         <v>39</v>
@@ -4085,7 +4100,7 @@
         <v>46203.386967592596</v>
       </c>
       <c r="F50" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>30</v>
@@ -4153,7 +4168,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F51" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>24</v>
@@ -4221,7 +4236,7 @@
         <v>46202.30238425926</v>
       </c>
       <c r="F52" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>24</v>
@@ -4233,7 +4248,7 @@
         <v>24</v>
       </c>
       <c r="J52" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K52" s="0" t="s">
         <v>25</v>
@@ -4253,8 +4268,8 @@
       <c r="P52" s="0">
         <v>0</v>
       </c>
-      <c r="Q52" s="0" t="s">
-        <v>25</v>
+      <c r="Q52" s="0">
+        <v>0</v>
       </c>
       <c r="R52" s="0" t="s">
         <v>25</v>
@@ -4289,7 +4304,7 @@
         <v>46208.76116898148</v>
       </c>
       <c r="F53" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>39</v>
@@ -4316,7 +4331,7 @@
         <v>25</v>
       </c>
       <c r="O53" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" s="0" t="s">
         <v>25</v>
@@ -4357,7 +4372,7 @@
         <v>46198.007743055554</v>
       </c>
       <c r="F54" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>30</v>
@@ -4390,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="Q54" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="0" t="s">
         <v>25</v>
@@ -4425,7 +4440,7 @@
         <v>46204.82892361111</v>
       </c>
       <c r="F55" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>30</v>
@@ -4434,7 +4449,7 @@
         <v>30</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>25</v>
@@ -4454,8 +4469,8 @@
       <c r="O55" s="0">
         <v>1</v>
       </c>
-      <c r="P55" s="0" t="s">
-        <v>25</v>
+      <c r="P55" s="0">
+        <v>0</v>
       </c>
       <c r="Q55" s="0" t="s">
         <v>25</v>
@@ -4484,22 +4499,22 @@
         <v>23</v>
       </c>
       <c r="C56" s="0">
-        <v>2108</v>
+        <v>2099</v>
       </c>
       <c r="D56" s="1">
-        <v>46202.13394675926</v>
+        <v>46211.026354166665</v>
       </c>
       <c r="E56" s="1">
-        <v>46206.49621527778</v>
+        <v>46211.026354166665</v>
       </c>
       <c r="F56" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I56" s="0" t="s">
         <v>25</v>
@@ -4541,7 +4556,7 @@
         <v>25</v>
       </c>
       <c r="V56" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57">
@@ -4549,31 +4564,31 @@
         <v>86</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C57" s="0">
-        <v>262</v>
+        <v>2108</v>
       </c>
       <c r="D57" s="1">
-        <v>46194.10880787037</v>
+        <v>46202.13394675926</v>
       </c>
       <c r="E57" s="1">
-        <v>46194.10880787037</v>
+        <v>46206.49621527778</v>
       </c>
       <c r="F57" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K57" s="0" t="s">
         <v>25</v>
@@ -4591,10 +4606,10 @@
         <v>1</v>
       </c>
       <c r="P57" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q57" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R57" s="0" t="s">
         <v>25</v>
@@ -4609,7 +4624,7 @@
         <v>25</v>
       </c>
       <c r="V57" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
@@ -4617,31 +4632,31 @@
         <v>87</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C58" s="0">
-        <v>2108</v>
+        <v>262</v>
       </c>
       <c r="D58" s="1">
-        <v>46202.674155092594</v>
+        <v>46194.10880787037</v>
       </c>
       <c r="E58" s="1">
-        <v>46202.80762731482</v>
+        <v>46194.10880787037</v>
       </c>
       <c r="F58" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K58" s="0" t="s">
         <v>25</v>
@@ -4659,10 +4674,10 @@
         <v>1</v>
       </c>
       <c r="P58" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="Q58" s="0">
+        <v>0</v>
       </c>
       <c r="R58" s="0" t="s">
         <v>25</v>
@@ -4677,7 +4692,7 @@
         <v>25</v>
       </c>
       <c r="V58" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59">
@@ -4688,16 +4703,16 @@
         <v>23</v>
       </c>
       <c r="C59" s="0">
-        <v>2025</v>
+        <v>2108</v>
       </c>
       <c r="D59" s="1">
-        <v>46196.60855324074</v>
+        <v>46202.674155092594</v>
       </c>
       <c r="E59" s="1">
-        <v>46198.053506944445</v>
+        <v>46202.80762731482</v>
       </c>
       <c r="F59" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>24</v>
@@ -4709,7 +4724,7 @@
         <v>24</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K59" s="0" t="s">
         <v>25</v>
@@ -4729,8 +4744,8 @@
       <c r="P59" s="0">
         <v>0</v>
       </c>
-      <c r="Q59" s="0">
-        <v>1</v>
+      <c r="Q59" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R59" s="0" t="s">
         <v>25</v>
@@ -4756,16 +4771,16 @@
         <v>23</v>
       </c>
       <c r="C60" s="0">
-        <v>2518</v>
+        <v>2025</v>
       </c>
       <c r="D60" s="1">
-        <v>46205.84306712963</v>
+        <v>46196.60855324074</v>
       </c>
       <c r="E60" s="1">
-        <v>46208.01679398148</v>
+        <v>46198.053506944445</v>
       </c>
       <c r="F60" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G60" s="0" t="s">
         <v>24</v>
@@ -4774,10 +4789,10 @@
         <v>24</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J60" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K60" s="0" t="s">
         <v>25</v>
@@ -4794,11 +4809,11 @@
       <c r="O60" s="0">
         <v>1</v>
       </c>
-      <c r="P60" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q60" s="0" t="s">
-        <v>25</v>
+      <c r="P60" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="0">
+        <v>1</v>
       </c>
       <c r="R60" s="0" t="s">
         <v>25</v>
@@ -4821,31 +4836,31 @@
         <v>90</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C61" s="0">
-        <v>206</v>
+        <v>2518</v>
       </c>
       <c r="D61" s="1">
-        <v>46199.4216087963</v>
+        <v>46205.84306712963</v>
       </c>
       <c r="E61" s="1">
-        <v>46199.4216087963</v>
+        <v>46208.01679398148</v>
       </c>
       <c r="F61" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J61" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K61" s="0" t="s">
         <v>25</v>
@@ -4862,11 +4877,11 @@
       <c r="O61" s="0">
         <v>1</v>
       </c>
-      <c r="P61" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="0">
-        <v>0</v>
+      <c r="P61" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q61" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R61" s="0" t="s">
         <v>25</v>
@@ -4881,7 +4896,7 @@
         <v>25</v>
       </c>
       <c r="V61" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62">
@@ -4889,31 +4904,31 @@
         <v>91</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C62" s="0">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="D62" s="1">
-        <v>46203.398622685185</v>
+        <v>46199.4216087963</v>
       </c>
       <c r="E62" s="1">
-        <v>46203.398622685185</v>
+        <v>46199.4216087963</v>
       </c>
       <c r="F62" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J62" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K62" s="0" t="s">
         <v>25</v>
@@ -4930,11 +4945,11 @@
       <c r="O62" s="0">
         <v>1</v>
       </c>
-      <c r="P62" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q62" s="0" t="s">
-        <v>25</v>
+      <c r="P62" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="0">
+        <v>0</v>
       </c>
       <c r="R62" s="0" t="s">
         <v>25</v>
@@ -4949,7 +4964,7 @@
         <v>25</v>
       </c>
       <c r="V62" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63">
@@ -4963,13 +4978,13 @@
         <v>0</v>
       </c>
       <c r="D63" s="1">
-        <v>46204.071388888886</v>
+        <v>46203.398622685185</v>
       </c>
       <c r="E63" s="1">
-        <v>46204.071388888886</v>
+        <v>46203.398622685185</v>
       </c>
       <c r="F63" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>30</v>
@@ -4978,7 +4993,7 @@
         <v>30</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J63" s="0" t="s">
         <v>25</v>
@@ -4998,8 +5013,8 @@
       <c r="O63" s="0">
         <v>1</v>
       </c>
-      <c r="P63" s="0" t="s">
-        <v>25</v>
+      <c r="P63" s="0">
+        <v>0</v>
       </c>
       <c r="Q63" s="0" t="s">
         <v>25</v>
@@ -5025,25 +5040,25 @@
         <v>93</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C64" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D64" s="1">
-        <v>46199.145104166666</v>
+        <v>46204.071388888886</v>
       </c>
       <c r="E64" s="1">
-        <v>46207.340208333335</v>
+        <v>46204.071388888886</v>
       </c>
       <c r="F64" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I64" s="0" t="s">
         <v>25</v>
@@ -5064,7 +5079,7 @@
         <v>25</v>
       </c>
       <c r="O64" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64" s="0" t="s">
         <v>25</v>
@@ -5085,7 +5100,7 @@
         <v>25</v>
       </c>
       <c r="V64" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
@@ -5099,13 +5114,13 @@
         <v>2108</v>
       </c>
       <c r="D65" s="1">
-        <v>46203.22761574074</v>
+        <v>46199.145104166666</v>
       </c>
       <c r="E65" s="1">
-        <v>46203.22761574074</v>
+        <v>46207.340208333335</v>
       </c>
       <c r="F65" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>24</v>
@@ -5114,7 +5129,7 @@
         <v>24</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J65" s="0" t="s">
         <v>25</v>
@@ -5134,8 +5149,8 @@
       <c r="O65" s="0">
         <v>0</v>
       </c>
-      <c r="P65" s="0" t="s">
-        <v>25</v>
+      <c r="P65" s="0">
+        <v>0</v>
       </c>
       <c r="Q65" s="0" t="s">
         <v>25</v>
@@ -5164,16 +5179,16 @@
         <v>23</v>
       </c>
       <c r="C66" s="0">
-        <v>2003</v>
+        <v>2108</v>
       </c>
       <c r="D66" s="1">
-        <v>46203.73695601852</v>
+        <v>46203.22761574074</v>
       </c>
       <c r="E66" s="1">
-        <v>46203.73695601852</v>
+        <v>46203.22761574074</v>
       </c>
       <c r="F66" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>24</v>
@@ -5182,7 +5197,7 @@
         <v>24</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J66" s="0" t="s">
         <v>25</v>
@@ -5202,8 +5217,8 @@
       <c r="O66" s="0">
         <v>0</v>
       </c>
-      <c r="P66" s="0" t="s">
-        <v>25</v>
+      <c r="P66" s="0">
+        <v>0</v>
       </c>
       <c r="Q66" s="0" t="s">
         <v>25</v>
@@ -5232,16 +5247,16 @@
         <v>23</v>
       </c>
       <c r="C67" s="0">
-        <v>2114</v>
+        <v>2003</v>
       </c>
       <c r="D67" s="1">
-        <v>46208.60796296296</v>
+        <v>46203.73695601852</v>
       </c>
       <c r="E67" s="1">
-        <v>46209.27856481481</v>
+        <v>46203.73695601852</v>
       </c>
       <c r="F67" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>24</v>
@@ -5268,7 +5283,7 @@
         <v>25</v>
       </c>
       <c r="O67" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67" s="0" t="s">
         <v>25</v>
@@ -5297,19 +5312,19 @@
         <v>97</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C68" s="0">
-        <v>13108</v>
+        <v>2114</v>
       </c>
       <c r="D68" s="1">
-        <v>46202.06835648148</v>
+        <v>46208.60796296296</v>
       </c>
       <c r="E68" s="1">
-        <v>46203.241944444446</v>
+        <v>46209.27856481481</v>
       </c>
       <c r="F68" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>24</v>
@@ -5318,7 +5333,7 @@
         <v>24</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J68" s="0" t="s">
         <v>25</v>
@@ -5338,8 +5353,8 @@
       <c r="O68" s="0">
         <v>1</v>
       </c>
-      <c r="P68" s="0">
-        <v>0</v>
+      <c r="P68" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q68" s="0" t="s">
         <v>25</v>
@@ -5365,28 +5380,28 @@
         <v>98</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="C69" s="0">
-        <v>1102304</v>
+        <v>13108</v>
       </c>
       <c r="D69" s="1">
-        <v>46197.000439814816</v>
+        <v>46202.06835648148</v>
       </c>
       <c r="E69" s="1">
-        <v>46200.90429398148</v>
+        <v>46203.241944444446</v>
       </c>
       <c r="F69" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J69" s="0" t="s">
         <v>25</v>
@@ -5406,8 +5421,8 @@
       <c r="O69" s="0">
         <v>1</v>
       </c>
-      <c r="P69" s="0" t="s">
-        <v>25</v>
+      <c r="P69" s="0">
+        <v>0</v>
       </c>
       <c r="Q69" s="0" t="s">
         <v>25</v>
@@ -5425,39 +5440,39 @@
         <v>25</v>
       </c>
       <c r="V69" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="B70" s="0" t="s">
-        <v>38</v>
-      </c>
       <c r="C70" s="0">
-        <v>225</v>
+        <v>1102304</v>
       </c>
       <c r="D70" s="1">
-        <v>46192.854166666664</v>
+        <v>46197.000439814816</v>
       </c>
       <c r="E70" s="1">
-        <v>46201.17297453704</v>
+        <v>46200.90429398148</v>
       </c>
       <c r="F70" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J70" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K70" s="0" t="s">
         <v>25</v>
@@ -5474,11 +5489,11 @@
       <c r="O70" s="0">
         <v>1</v>
       </c>
-      <c r="P70" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="0">
-        <v>0</v>
+      <c r="P70" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q70" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R70" s="0" t="s">
         <v>25</v>
@@ -5493,7 +5508,7 @@
         <v>25</v>
       </c>
       <c r="V70" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71">
@@ -5501,31 +5516,31 @@
         <v>101</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C71" s="0">
-        <v>2012</v>
+        <v>225</v>
       </c>
       <c r="D71" s="1">
-        <v>46197.398356481484</v>
+        <v>46192.854166666664</v>
       </c>
       <c r="E71" s="1">
-        <v>46197.398356481484</v>
+        <v>46201.17297453704</v>
       </c>
       <c r="F71" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J71" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K71" s="0" t="s">
         <v>25</v>
@@ -5540,7 +5555,7 @@
         <v>25</v>
       </c>
       <c r="O71" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P71" s="0">
         <v>1</v>
@@ -5561,7 +5576,7 @@
         <v>25</v>
       </c>
       <c r="V71" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
@@ -5569,19 +5584,19 @@
         <v>102</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C72" s="0">
-        <v>0</v>
+        <v>2012</v>
       </c>
       <c r="D72" s="1">
-        <v>46198.06826388889</v>
+        <v>46197.398356481484</v>
       </c>
       <c r="E72" s="1">
-        <v>46198.06826388889</v>
+        <v>46197.398356481484</v>
       </c>
       <c r="F72" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>30</v>
@@ -5590,10 +5605,10 @@
         <v>30</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J72" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K72" s="0" t="s">
         <v>25</v>
@@ -5608,13 +5623,13 @@
         <v>25</v>
       </c>
       <c r="O72" s="0">
-        <v>1</v>
-      </c>
-      <c r="P72" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q72" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P72" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="0">
+        <v>1</v>
       </c>
       <c r="R72" s="0" t="s">
         <v>25</v>
@@ -5643,13 +5658,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="1">
-        <v>46198.76695601852</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="E73" s="1">
-        <v>46198.76695601852</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="F73" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>30</v>
@@ -5658,7 +5673,7 @@
         <v>30</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J73" s="0" t="s">
         <v>25</v>
@@ -5678,8 +5693,8 @@
       <c r="O73" s="0">
         <v>1</v>
       </c>
-      <c r="P73" s="0" t="s">
-        <v>25</v>
+      <c r="P73" s="0">
+        <v>0</v>
       </c>
       <c r="Q73" s="0" t="s">
         <v>25</v>
@@ -5711,22 +5726,22 @@
         <v>0</v>
       </c>
       <c r="D74" s="1">
-        <v>46199.06940972222</v>
+        <v>46198.76695601852</v>
       </c>
       <c r="E74" s="1">
-        <v>46199.06940972222</v>
+        <v>46198.76695601852</v>
       </c>
       <c r="F74" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>25</v>
@@ -5746,8 +5761,8 @@
       <c r="O74" s="0">
         <v>1</v>
       </c>
-      <c r="P74" s="0" t="s">
-        <v>25</v>
+      <c r="P74" s="0">
+        <v>0</v>
       </c>
       <c r="Q74" s="0" t="s">
         <v>25</v>
@@ -5765,7 +5780,7 @@
         <v>25</v>
       </c>
       <c r="V74" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75">
@@ -5773,28 +5788,28 @@
         <v>105</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C75" s="0">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="D75" s="1">
-        <v>46205.52684027778</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="E75" s="1">
-        <v>46207.38381944445</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="F75" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J75" s="0" t="s">
         <v>25</v>
@@ -5814,8 +5829,8 @@
       <c r="O75" s="0">
         <v>1</v>
       </c>
-      <c r="P75" s="0" t="s">
-        <v>25</v>
+      <c r="P75" s="0">
+        <v>0</v>
       </c>
       <c r="Q75" s="0" t="s">
         <v>25</v>
@@ -5833,7 +5848,7 @@
         <v>25</v>
       </c>
       <c r="V75" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76">
@@ -5841,28 +5856,28 @@
         <v>106</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C76" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D76" s="1">
-        <v>46198.764710648145</v>
+        <v>46205.52684027778</v>
       </c>
       <c r="E76" s="1">
-        <v>46198.764710648145</v>
+        <v>46207.38381944445</v>
       </c>
       <c r="F76" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>25</v>
@@ -5882,8 +5897,8 @@
       <c r="O76" s="0">
         <v>1</v>
       </c>
-      <c r="P76" s="0" t="s">
-        <v>25</v>
+      <c r="P76" s="0">
+        <v>0</v>
       </c>
       <c r="Q76" s="0" t="s">
         <v>25</v>
@@ -5901,7 +5916,7 @@
         <v>25</v>
       </c>
       <c r="V76" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77">
@@ -5909,28 +5924,28 @@
         <v>107</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C77" s="0">
-        <v>2106</v>
+        <v>0</v>
       </c>
       <c r="D77" s="1">
-        <v>46208.60445601852</v>
+        <v>46198.764710648145</v>
       </c>
       <c r="E77" s="1">
-        <v>46208.60445601852</v>
+        <v>46198.764710648145</v>
       </c>
       <c r="F77" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>25</v>
@@ -5950,8 +5965,8 @@
       <c r="O77" s="0">
         <v>1</v>
       </c>
-      <c r="P77" s="0" t="s">
-        <v>25</v>
+      <c r="P77" s="0">
+        <v>0</v>
       </c>
       <c r="Q77" s="0" t="s">
         <v>25</v>
@@ -5969,7 +5984,7 @@
         <v>25</v>
       </c>
       <c r="V77" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78">
@@ -5977,25 +5992,25 @@
         <v>108</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C78" s="0">
-        <v>0</v>
+        <v>2106</v>
       </c>
       <c r="D78" s="1">
-        <v>46198.06826388889</v>
+        <v>46208.60445601852</v>
       </c>
       <c r="E78" s="1">
-        <v>46198.06826388889</v>
+        <v>46208.60445601852</v>
       </c>
       <c r="F78" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I78" s="0" t="s">
         <v>25</v>
@@ -6037,7 +6052,7 @@
         <v>25</v>
       </c>
       <c r="V78" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
@@ -6051,22 +6066,22 @@
         <v>0</v>
       </c>
       <c r="D79" s="1">
-        <v>46198.7566087963</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="E79" s="1">
-        <v>46198.7566087963</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="F79" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J79" s="0" t="s">
         <v>25</v>
@@ -6086,8 +6101,8 @@
       <c r="O79" s="0">
         <v>1</v>
       </c>
-      <c r="P79" s="0" t="s">
-        <v>25</v>
+      <c r="P79" s="0">
+        <v>0</v>
       </c>
       <c r="Q79" s="0" t="s">
         <v>25</v>
@@ -6105,7 +6120,7 @@
         <v>25</v>
       </c>
       <c r="V79" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80">
@@ -6119,13 +6134,13 @@
         <v>0</v>
       </c>
       <c r="D80" s="1">
-        <v>46203.38690972222</v>
+        <v>46198.7566087963</v>
       </c>
       <c r="E80" s="1">
-        <v>46203.38690972222</v>
+        <v>46198.7566087963</v>
       </c>
       <c r="F80" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>30</v>
@@ -6181,28 +6196,28 @@
         <v>111</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C81" s="0">
-        <v>2521</v>
+        <v>0</v>
       </c>
       <c r="D81" s="1">
-        <v>46196.88789351852</v>
+        <v>46203.38690972222</v>
       </c>
       <c r="E81" s="1">
-        <v>46199.954201388886</v>
+        <v>46203.38690972222</v>
       </c>
       <c r="F81" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J81" s="0" t="s">
         <v>25</v>
@@ -6223,7 +6238,7 @@
         <v>1</v>
       </c>
       <c r="P81" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="0" t="s">
         <v>25</v>
@@ -6241,7 +6256,7 @@
         <v>25</v>
       </c>
       <c r="V81" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82">
@@ -6249,28 +6264,28 @@
         <v>112</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C82" s="0">
-        <v>0</v>
+        <v>2521</v>
       </c>
       <c r="D82" s="1">
-        <v>46199.06940972222</v>
+        <v>46196.88789351852</v>
       </c>
       <c r="E82" s="1">
-        <v>46199.06940972222</v>
+        <v>46199.954201388886</v>
       </c>
       <c r="F82" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J82" s="0" t="s">
         <v>25</v>
@@ -6290,8 +6305,8 @@
       <c r="O82" s="0">
         <v>1</v>
       </c>
-      <c r="P82" s="0" t="s">
-        <v>25</v>
+      <c r="P82" s="0">
+        <v>1</v>
       </c>
       <c r="Q82" s="0" t="s">
         <v>25</v>
@@ -6309,7 +6324,7 @@
         <v>25</v>
       </c>
       <c r="V82" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83">
@@ -6317,28 +6332,28 @@
         <v>113</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C83" s="0">
-        <v>2115</v>
+        <v>0</v>
       </c>
       <c r="D83" s="1">
-        <v>46193.45674768519</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="E83" s="1">
-        <v>46193.45674768519</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="F83" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J83" s="0" t="s">
         <v>25</v>
@@ -6359,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="P83" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="0" t="s">
         <v>25</v>
@@ -6377,7 +6392,7 @@
         <v>25</v>
       </c>
       <c r="V83" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84">
@@ -6388,28 +6403,28 @@
         <v>23</v>
       </c>
       <c r="C84" s="0">
-        <v>2108</v>
+        <v>2115</v>
       </c>
       <c r="D84" s="1">
-        <v>46196.430972222224</v>
+        <v>46193.45674768519</v>
       </c>
       <c r="E84" s="1">
-        <v>46196.43208333333</v>
+        <v>46193.45674768519</v>
       </c>
       <c r="F84" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J84" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K84" s="0" t="s">
         <v>25</v>
@@ -6427,10 +6442,10 @@
         <v>1</v>
       </c>
       <c r="P84" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q84" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R84" s="0" t="s">
         <v>25</v>
@@ -6445,7 +6460,7 @@
         <v>25</v>
       </c>
       <c r="V84" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85">
@@ -6456,16 +6471,16 @@
         <v>23</v>
       </c>
       <c r="C85" s="0">
-        <v>2012</v>
+        <v>2099</v>
       </c>
       <c r="D85" s="1">
-        <v>46205.85377314815</v>
+        <v>46210.895787037036</v>
       </c>
       <c r="E85" s="1">
-        <v>46205.85377314815</v>
+        <v>46211.339479166665</v>
       </c>
       <c r="F85" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>30</v>
@@ -6492,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="O85" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" s="0" t="s">
         <v>25</v>
@@ -6524,28 +6539,28 @@
         <v>23</v>
       </c>
       <c r="C86" s="0">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="D86" s="1">
-        <v>46194.496782407405</v>
+        <v>46196.430972222224</v>
       </c>
       <c r="E86" s="1">
-        <v>46194.496782407405</v>
+        <v>46196.43208333333</v>
       </c>
       <c r="F86" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J86" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K86" s="0" t="s">
         <v>25</v>
@@ -6563,7 +6578,7 @@
         <v>1</v>
       </c>
       <c r="P86" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q86" s="0">
         <v>0</v>
@@ -6581,7 +6596,7 @@
         <v>25</v>
       </c>
       <c r="V86" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
@@ -6592,25 +6607,25 @@
         <v>23</v>
       </c>
       <c r="C87" s="0">
-        <v>2108</v>
+        <v>2012</v>
       </c>
       <c r="D87" s="1">
-        <v>46206.041817129626</v>
+        <v>46205.85377314815</v>
       </c>
       <c r="E87" s="1">
-        <v>46206.041817129626</v>
+        <v>46205.85377314815</v>
       </c>
       <c r="F87" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J87" s="0" t="s">
         <v>25</v>
@@ -6630,8 +6645,8 @@
       <c r="O87" s="0">
         <v>0</v>
       </c>
-      <c r="P87" s="0" t="s">
-        <v>25</v>
+      <c r="P87" s="0">
+        <v>1</v>
       </c>
       <c r="Q87" s="0" t="s">
         <v>25</v>
@@ -6649,7 +6664,7 @@
         <v>25</v>
       </c>
       <c r="V87" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88">
@@ -6657,31 +6672,31 @@
         <v>118</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C88" s="0">
-        <v>0</v>
+        <v>2106</v>
       </c>
       <c r="D88" s="1">
-        <v>46198.76357638889</v>
+        <v>46194.496782407405</v>
       </c>
       <c r="E88" s="1">
-        <v>46198.76357638889</v>
+        <v>46194.496782407405</v>
       </c>
       <c r="F88" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J88" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K88" s="0" t="s">
         <v>25</v>
@@ -6698,11 +6713,11 @@
       <c r="O88" s="0">
         <v>1</v>
       </c>
-      <c r="P88" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q88" s="0" t="s">
-        <v>25</v>
+      <c r="P88" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="0">
+        <v>0</v>
       </c>
       <c r="R88" s="0" t="s">
         <v>25</v>
@@ -6717,7 +6732,7 @@
         <v>25</v>
       </c>
       <c r="V88" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89">
@@ -6725,25 +6740,25 @@
         <v>119</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C89" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D89" s="1">
-        <v>46203.900046296294</v>
+        <v>46206.041817129626</v>
       </c>
       <c r="E89" s="1">
-        <v>46203.900046296294</v>
+        <v>46206.041817129626</v>
       </c>
       <c r="F89" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G89" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I89" s="0" t="s">
         <v>25</v>
@@ -6785,7 +6800,7 @@
         <v>25</v>
       </c>
       <c r="V89" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90">
@@ -6799,13 +6814,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="1">
-        <v>46198.75818287037</v>
+        <v>46198.76357638889</v>
       </c>
       <c r="E90" s="1">
-        <v>46198.75818287037</v>
+        <v>46198.76357638889</v>
       </c>
       <c r="F90" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>30</v>
@@ -6814,7 +6829,7 @@
         <v>30</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J90" s="0" t="s">
         <v>25</v>
@@ -6834,8 +6849,8 @@
       <c r="O90" s="0">
         <v>1</v>
       </c>
-      <c r="P90" s="0" t="s">
-        <v>25</v>
+      <c r="P90" s="0">
+        <v>0</v>
       </c>
       <c r="Q90" s="0" t="s">
         <v>25</v>
@@ -6861,31 +6876,31 @@
         <v>121</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C91" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D91" s="1">
-        <v>46198.57461805556</v>
+        <v>46203.900046296294</v>
       </c>
       <c r="E91" s="1">
-        <v>46199.24039351852</v>
+        <v>46203.900046296294</v>
       </c>
       <c r="F91" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J91" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K91" s="0" t="s">
         <v>25</v>
@@ -6903,10 +6918,10 @@
         <v>1</v>
       </c>
       <c r="P91" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q91" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q91" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R91" s="0" t="s">
         <v>25</v>
@@ -6921,7 +6936,7 @@
         <v>25</v>
       </c>
       <c r="V91" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92">
@@ -6929,28 +6944,28 @@
         <v>122</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C92" s="0">
-        <v>2025</v>
+        <v>0</v>
       </c>
       <c r="D92" s="1">
-        <v>46206.35917824074</v>
+        <v>46198.75818287037</v>
       </c>
       <c r="E92" s="1">
-        <v>46207.7878125</v>
+        <v>46198.75818287037</v>
       </c>
       <c r="F92" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J92" s="0" t="s">
         <v>25</v>
@@ -6968,10 +6983,10 @@
         <v>25</v>
       </c>
       <c r="O92" s="0">
-        <v>0</v>
-      </c>
-      <c r="P92" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P92" s="0">
+        <v>0</v>
       </c>
       <c r="Q92" s="0" t="s">
         <v>25</v>
@@ -6989,7 +7004,7 @@
         <v>25</v>
       </c>
       <c r="V92" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93">
@@ -7003,25 +7018,25 @@
         <v>2108</v>
       </c>
       <c r="D93" s="1">
-        <v>46199.62337962963</v>
+        <v>46198.57461805556</v>
       </c>
       <c r="E93" s="1">
-        <v>46200.88856481481</v>
+        <v>46199.24039351852</v>
       </c>
       <c r="F93" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J93" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K93" s="0" t="s">
         <v>25</v>
@@ -7057,7 +7072,7 @@
         <v>25</v>
       </c>
       <c r="V93" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94">
@@ -7068,16 +7083,16 @@
         <v>23</v>
       </c>
       <c r="C94" s="0">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="D94" s="1">
-        <v>46207.091145833336</v>
+        <v>46206.35917824074</v>
       </c>
       <c r="E94" s="1">
-        <v>46207.091145833336</v>
+        <v>46207.7878125</v>
       </c>
       <c r="F94" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>24</v>
@@ -7104,7 +7119,7 @@
         <v>25</v>
       </c>
       <c r="O94" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P94" s="0" t="s">
         <v>25</v>
@@ -7133,31 +7148,31 @@
         <v>125</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C95" s="0">
-        <v>344</v>
+        <v>2108</v>
       </c>
       <c r="D95" s="1">
-        <v>46203.41339120371</v>
+        <v>46199.62337962963</v>
       </c>
       <c r="E95" s="1">
-        <v>46208.76133101852</v>
+        <v>46200.88856481481</v>
       </c>
       <c r="F95" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J95" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K95" s="0" t="s">
         <v>25</v>
@@ -7172,13 +7187,13 @@
         <v>25</v>
       </c>
       <c r="O95" s="0">
-        <v>0</v>
-      </c>
-      <c r="P95" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q95" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P95" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="0">
+        <v>0</v>
       </c>
       <c r="R95" s="0" t="s">
         <v>25</v>
@@ -7193,7 +7208,7 @@
         <v>25</v>
       </c>
       <c r="V95" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96">
@@ -7204,25 +7219,25 @@
         <v>23</v>
       </c>
       <c r="C96" s="0">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="D96" s="1">
-        <v>46202.603946759256</v>
+        <v>46207.091145833336</v>
       </c>
       <c r="E96" s="1">
-        <v>46202.603946759256</v>
+        <v>46207.091145833336</v>
       </c>
       <c r="F96" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J96" s="0" t="s">
         <v>25</v>
@@ -7240,10 +7255,10 @@
         <v>25</v>
       </c>
       <c r="O96" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="0" t="s">
         <v>25</v>
@@ -7261,7 +7276,7 @@
         <v>25</v>
       </c>
       <c r="V96" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97">
@@ -7272,22 +7287,22 @@
         <v>23</v>
       </c>
       <c r="C97" s="0">
-        <v>2518</v>
+        <v>2012</v>
       </c>
       <c r="D97" s="1">
-        <v>46200.47917824074</v>
+        <v>46209.81253472222</v>
       </c>
       <c r="E97" s="1">
-        <v>46208.28020833333</v>
+        <v>46209.81253472222</v>
       </c>
       <c r="F97" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I97" s="0" t="s">
         <v>25</v>
@@ -7308,7 +7323,7 @@
         <v>25</v>
       </c>
       <c r="O97" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P97" s="0" t="s">
         <v>25</v>
@@ -7329,7 +7344,7 @@
         <v>25</v>
       </c>
       <c r="V97" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98">
@@ -7343,13 +7358,13 @@
         <v>344</v>
       </c>
       <c r="D98" s="1">
-        <v>46203.665925925925</v>
+        <v>46203.41339120371</v>
       </c>
       <c r="E98" s="1">
-        <v>46203.665925925925</v>
+        <v>46208.76133101852</v>
       </c>
       <c r="F98" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G98" s="0" t="s">
         <v>30</v>
@@ -7376,7 +7391,7 @@
         <v>25</v>
       </c>
       <c r="O98" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P98" s="0" t="s">
         <v>25</v>
@@ -7408,25 +7423,25 @@
         <v>23</v>
       </c>
       <c r="C99" s="0">
-        <v>2108</v>
+        <v>2012</v>
       </c>
       <c r="D99" s="1">
-        <v>46202.769537037035</v>
+        <v>46202.603946759256</v>
       </c>
       <c r="E99" s="1">
-        <v>46204.36974537037</v>
+        <v>46202.603946759256</v>
       </c>
       <c r="F99" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G99" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J99" s="0" t="s">
         <v>25</v>
@@ -7444,10 +7459,10 @@
         <v>25</v>
       </c>
       <c r="O99" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q99" s="0" t="s">
         <v>25</v>
@@ -7465,7 +7480,7 @@
         <v>25</v>
       </c>
       <c r="V99" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100">
@@ -7476,28 +7491,28 @@
         <v>23</v>
       </c>
       <c r="C100" s="0">
-        <v>2099</v>
+        <v>2518</v>
       </c>
       <c r="D100" s="1">
-        <v>46200.000439814816</v>
+        <v>46200.47917824074</v>
       </c>
       <c r="E100" s="1">
-        <v>46201.332870370374</v>
+        <v>46208.28020833333</v>
       </c>
       <c r="F100" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J100" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K100" s="0" t="s">
         <v>25</v>
@@ -7514,11 +7529,11 @@
       <c r="O100" s="0">
         <v>1</v>
       </c>
-      <c r="P100" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q100" s="0">
-        <v>0</v>
+      <c r="P100" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q100" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R100" s="0" t="s">
         <v>25</v>
@@ -7533,7 +7548,7 @@
         <v>25</v>
       </c>
       <c r="V100" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101">
@@ -7541,19 +7556,19 @@
         <v>131</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C101" s="0">
-        <v>112304</v>
+        <v>344</v>
       </c>
       <c r="D101" s="1">
-        <v>46197.03113425926</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="E101" s="1">
-        <v>46197.03113425926</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="F101" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>30</v>
@@ -7565,7 +7580,7 @@
         <v>30</v>
       </c>
       <c r="J101" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K101" s="0" t="s">
         <v>25</v>
@@ -7585,8 +7600,8 @@
       <c r="P101" s="0">
         <v>1</v>
       </c>
-      <c r="Q101" s="0">
-        <v>0</v>
+      <c r="Q101" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R101" s="0" t="s">
         <v>25</v>
@@ -7615,13 +7630,13 @@
         <v>2108</v>
       </c>
       <c r="D102" s="1">
-        <v>46200.04966435185</v>
+        <v>46202.769537037035</v>
       </c>
       <c r="E102" s="1">
-        <v>46200.98619212963</v>
+        <v>46204.36974537037</v>
       </c>
       <c r="F102" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>24</v>
@@ -7680,28 +7695,28 @@
         <v>23</v>
       </c>
       <c r="C103" s="0">
-        <v>2108</v>
+        <v>2099</v>
       </c>
       <c r="D103" s="1">
-        <v>46207.068391203706</v>
+        <v>46200.000439814816</v>
       </c>
       <c r="E103" s="1">
-        <v>46207.18613425926</v>
+        <v>46201.332870370374</v>
       </c>
       <c r="F103" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J103" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K103" s="0" t="s">
         <v>25</v>
@@ -7718,11 +7733,11 @@
       <c r="O103" s="0">
         <v>1</v>
       </c>
-      <c r="P103" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q103" s="0" t="s">
-        <v>25</v>
+      <c r="P103" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q103" s="0">
+        <v>0</v>
       </c>
       <c r="R103" s="0" t="s">
         <v>25</v>
@@ -7737,7 +7752,7 @@
         <v>25</v>
       </c>
       <c r="V103" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104">
@@ -7745,19 +7760,19 @@
         <v>134</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C104" s="0">
-        <v>0</v>
+        <v>112304</v>
       </c>
       <c r="D104" s="1">
-        <v>46198.763344907406</v>
+        <v>46197.03113425926</v>
       </c>
       <c r="E104" s="1">
-        <v>46198.763344907406</v>
+        <v>46197.03113425926</v>
       </c>
       <c r="F104" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>30</v>
@@ -7766,10 +7781,10 @@
         <v>30</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J104" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K104" s="0" t="s">
         <v>25</v>
@@ -7784,13 +7799,13 @@
         <v>25</v>
       </c>
       <c r="O104" s="0">
-        <v>1</v>
-      </c>
-      <c r="P104" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q104" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P104" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q104" s="0">
+        <v>1</v>
       </c>
       <c r="R104" s="0" t="s">
         <v>25</v>
@@ -7816,16 +7831,16 @@
         <v>23</v>
       </c>
       <c r="C105" s="0">
-        <v>2120</v>
+        <v>2108</v>
       </c>
       <c r="D105" s="1">
-        <v>46196.68797453704</v>
+        <v>46200.04966435185</v>
       </c>
       <c r="E105" s="1">
-        <v>46198.86886574074</v>
+        <v>46200.98619212963</v>
       </c>
       <c r="F105" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>24</v>
@@ -7855,7 +7870,7 @@
         <v>1</v>
       </c>
       <c r="P105" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q105" s="0">
         <v>0</v>
@@ -7881,25 +7896,25 @@
         <v>136</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C106" s="0">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="D106" s="1">
-        <v>46198.76422453704</v>
+        <v>46207.068391203706</v>
       </c>
       <c r="E106" s="1">
-        <v>46198.76422453704</v>
+        <v>46207.18613425926</v>
       </c>
       <c r="F106" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I106" s="0" t="s">
         <v>25</v>
@@ -7941,7 +7956,7 @@
         <v>25</v>
       </c>
       <c r="V106" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107">
@@ -7952,22 +7967,22 @@
         <v>23</v>
       </c>
       <c r="C107" s="0">
-        <v>2521</v>
+        <v>2108</v>
       </c>
       <c r="D107" s="1">
-        <v>46203.63976851852</v>
+        <v>46198.4140625</v>
       </c>
       <c r="E107" s="1">
-        <v>46206.29314814815</v>
+        <v>46210.8569212963</v>
       </c>
       <c r="F107" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I107" s="0" t="s">
         <v>25</v>
@@ -7988,7 +8003,7 @@
         <v>25</v>
       </c>
       <c r="O107" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P107" s="0" t="s">
         <v>25</v>
@@ -8009,7 +8024,7 @@
         <v>25</v>
       </c>
       <c r="V107" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="108">
@@ -8017,28 +8032,28 @@
         <v>138</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C108" s="0">
-        <v>2123</v>
+        <v>0</v>
       </c>
       <c r="D108" s="1">
-        <v>46206.39832175926</v>
+        <v>46198.763344907406</v>
       </c>
       <c r="E108" s="1">
-        <v>46206.39832175926</v>
+        <v>46198.763344907406</v>
       </c>
       <c r="F108" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J108" s="0" t="s">
         <v>25</v>
@@ -8056,10 +8071,10 @@
         <v>25</v>
       </c>
       <c r="O108" s="0">
-        <v>0</v>
-      </c>
-      <c r="P108" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P108" s="0">
+        <v>0</v>
       </c>
       <c r="Q108" s="0" t="s">
         <v>25</v>
@@ -8077,7 +8092,7 @@
         <v>25</v>
       </c>
       <c r="V108" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109">
@@ -8088,16 +8103,16 @@
         <v>23</v>
       </c>
       <c r="C109" s="0">
-        <v>2108</v>
+        <v>2120</v>
       </c>
       <c r="D109" s="1">
-        <v>46197.72638888889</v>
+        <v>46196.68797453704</v>
       </c>
       <c r="E109" s="1">
-        <v>46201.828206018516</v>
+        <v>46198.86886574074</v>
       </c>
       <c r="F109" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>24</v>
@@ -8109,7 +8124,7 @@
         <v>24</v>
       </c>
       <c r="J109" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K109" s="0" t="s">
         <v>25</v>
@@ -8124,13 +8139,13 @@
         <v>25</v>
       </c>
       <c r="O109" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="Q109" s="0">
+        <v>1</v>
       </c>
       <c r="R109" s="0" t="s">
         <v>25</v>
@@ -8153,19 +8168,19 @@
         <v>140</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="C110" s="0">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D110" s="1">
-        <v>46198.13282407408</v>
+        <v>46198.76422453704</v>
       </c>
       <c r="E110" s="1">
-        <v>46198.13486111111</v>
+        <v>46198.76422453704</v>
       </c>
       <c r="F110" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>30</v>
@@ -8177,7 +8192,7 @@
         <v>30</v>
       </c>
       <c r="J110" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K110" s="0" t="s">
         <v>25</v>
@@ -8195,10 +8210,10 @@
         <v>1</v>
       </c>
       <c r="P110" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q110" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R110" s="0" t="s">
         <v>25</v>
@@ -8218,34 +8233,34 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B111" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C111" s="0">
-        <v>2518</v>
+        <v>2521</v>
       </c>
       <c r="D111" s="1">
-        <v>46198.26168981481</v>
+        <v>46203.63976851852</v>
       </c>
       <c r="E111" s="1">
-        <v>46198.487546296295</v>
+        <v>46206.29314814815</v>
       </c>
       <c r="F111" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G111" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J111" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K111" s="0" t="s">
         <v>25</v>
@@ -8262,11 +8277,11 @@
       <c r="O111" s="0">
         <v>1</v>
       </c>
-      <c r="P111" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="0">
-        <v>0</v>
+      <c r="P111" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q111" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R111" s="0" t="s">
         <v>25</v>
@@ -8281,27 +8296,27 @@
         <v>25</v>
       </c>
       <c r="V111" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B112" s="0" t="s">
         <v>23</v>
       </c>
       <c r="C112" s="0">
-        <v>2518</v>
+        <v>2123</v>
       </c>
       <c r="D112" s="1">
-        <v>46198.6140625</v>
+        <v>46206.39832175926</v>
       </c>
       <c r="E112" s="1">
-        <v>46199.37</v>
+        <v>46206.39832175926</v>
       </c>
       <c r="F112" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>24</v>
@@ -8313,7 +8328,7 @@
         <v>24</v>
       </c>
       <c r="J112" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K112" s="0" t="s">
         <v>25</v>
@@ -8328,13 +8343,13 @@
         <v>25</v>
       </c>
       <c r="O112" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P112" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q112" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q112" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R112" s="0" t="s">
         <v>25</v>
@@ -8354,22 +8369,22 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C113" s="0">
-        <v>13108</v>
+        <v>2108</v>
       </c>
       <c r="D113" s="1">
-        <v>46200.21556712963</v>
+        <v>46197.72638888889</v>
       </c>
       <c r="E113" s="1">
-        <v>46200.507418981484</v>
+        <v>46201.828206018516</v>
       </c>
       <c r="F113" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>24</v>
@@ -8396,10 +8411,10 @@
         <v>25</v>
       </c>
       <c r="O113" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P113" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="0">
         <v>0</v>
@@ -8422,34 +8437,34 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B114" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="B114" s="0" t="s">
-        <v>38</v>
-      </c>
       <c r="C114" s="0">
-        <v>344</v>
+        <v>64</v>
       </c>
       <c r="D114" s="1">
-        <v>46203.41339120371</v>
+        <v>46198.13282407408</v>
       </c>
       <c r="E114" s="1">
-        <v>46208.7612037037</v>
+        <v>46198.13486111111</v>
       </c>
       <c r="F114" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H114" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J114" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K114" s="0" t="s">
         <v>25</v>
@@ -8464,13 +8479,13 @@
         <v>25</v>
       </c>
       <c r="O114" s="0">
-        <v>0</v>
-      </c>
-      <c r="P114" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q114" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P114" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q114" s="0">
+        <v>1</v>
       </c>
       <c r="R114" s="0" t="s">
         <v>25</v>
@@ -8485,7 +8500,7 @@
         <v>25</v>
       </c>
       <c r="V114" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115">
@@ -8496,16 +8511,16 @@
         <v>23</v>
       </c>
       <c r="C115" s="0">
-        <v>2126</v>
+        <v>2518</v>
       </c>
       <c r="D115" s="1">
-        <v>46206.616875</v>
+        <v>46198.26168981481</v>
       </c>
       <c r="E115" s="1">
-        <v>46206.616875</v>
+        <v>46198.487546296295</v>
       </c>
       <c r="F115" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>24</v>
@@ -8514,10 +8529,10 @@
         <v>24</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J115" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K115" s="0" t="s">
         <v>25</v>
@@ -8534,11 +8549,11 @@
       <c r="O115" s="0">
         <v>1</v>
       </c>
-      <c r="P115" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q115" s="0" t="s">
-        <v>25</v>
+      <c r="P115" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="0">
+        <v>0</v>
       </c>
       <c r="R115" s="0" t="s">
         <v>25</v>
@@ -8564,28 +8579,28 @@
         <v>23</v>
       </c>
       <c r="C116" s="0">
-        <v>2012</v>
+        <v>2518</v>
       </c>
       <c r="D116" s="1">
-        <v>46206.85376157407</v>
+        <v>46198.6140625</v>
       </c>
       <c r="E116" s="1">
-        <v>46206.85376157407</v>
+        <v>46199.37</v>
       </c>
       <c r="F116" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J116" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K116" s="0" t="s">
         <v>25</v>
@@ -8600,13 +8615,13 @@
         <v>25</v>
       </c>
       <c r="O116" s="0">
-        <v>0</v>
-      </c>
-      <c r="P116" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q116" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P116" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q116" s="0">
+        <v>0</v>
       </c>
       <c r="R116" s="0" t="s">
         <v>25</v>
@@ -8621,7 +8636,7 @@
         <v>25</v>
       </c>
       <c r="V116" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="117">
@@ -8629,31 +8644,31 @@
         <v>148</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C117" s="0">
-        <v>2518</v>
+        <v>13108</v>
       </c>
       <c r="D117" s="1">
-        <v>46208.34142361111</v>
+        <v>46200.21556712963</v>
       </c>
       <c r="E117" s="1">
-        <v>46208.34142361111</v>
+        <v>46200.507418981484</v>
       </c>
       <c r="F117" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J117" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K117" s="0" t="s">
         <v>25</v>
@@ -8670,11 +8685,11 @@
       <c r="O117" s="0">
         <v>1</v>
       </c>
-      <c r="P117" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q117" s="0" t="s">
-        <v>25</v>
+      <c r="P117" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q117" s="0">
+        <v>0</v>
       </c>
       <c r="R117" s="0" t="s">
         <v>25</v>
@@ -8689,7 +8704,7 @@
         <v>25</v>
       </c>
       <c r="V117" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="118">
@@ -8700,16 +8715,16 @@
         <v>38</v>
       </c>
       <c r="C118" s="0">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="D118" s="1">
-        <v>46206.18699074074</v>
+        <v>46203.41339120371</v>
       </c>
       <c r="E118" s="1">
-        <v>46207.44116898148</v>
+        <v>46208.7612037037</v>
       </c>
       <c r="F118" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>39</v>
@@ -8736,7 +8751,7 @@
         <v>25</v>
       </c>
       <c r="O118" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P118" s="0" t="s">
         <v>25</v>
@@ -8765,25 +8780,25 @@
         <v>150</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C119" s="0">
-        <v>318</v>
+        <v>2126</v>
       </c>
       <c r="D119" s="1">
-        <v>46205.74003472222</v>
+        <v>46206.616875</v>
       </c>
       <c r="E119" s="1">
-        <v>46205.74003472222</v>
+        <v>46206.616875</v>
       </c>
       <c r="F119" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>25</v>
@@ -8825,7 +8840,7 @@
         <v>25</v>
       </c>
       <c r="V119" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="120">
@@ -8836,28 +8851,28 @@
         <v>23</v>
       </c>
       <c r="C120" s="0">
-        <v>2521</v>
+        <v>2012</v>
       </c>
       <c r="D120" s="1">
-        <v>46196.88789351852</v>
+        <v>46206.85376157407</v>
       </c>
       <c r="E120" s="1">
-        <v>46199.95371527778</v>
+        <v>46206.85376157407</v>
       </c>
       <c r="F120" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G120" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J120" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K120" s="0" t="s">
         <v>25</v>
@@ -8874,11 +8889,11 @@
       <c r="O120" s="0">
         <v>1</v>
       </c>
-      <c r="P120" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q120" s="0">
-        <v>0</v>
+      <c r="P120" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q120" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R120" s="0" t="s">
         <v>25</v>
@@ -8893,7 +8908,7 @@
         <v>25</v>
       </c>
       <c r="V120" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121">
@@ -8901,25 +8916,25 @@
         <v>152</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C121" s="0">
-        <v>262</v>
+        <v>2518</v>
       </c>
       <c r="D121" s="1">
-        <v>46205.07099537037</v>
+        <v>46208.34142361111</v>
       </c>
       <c r="E121" s="1">
-        <v>46205.07099537037</v>
+        <v>46208.34142361111</v>
       </c>
       <c r="F121" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G121" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I121" s="0" t="s">
         <v>25</v>
@@ -8940,7 +8955,7 @@
         <v>25</v>
       </c>
       <c r="O121" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P121" s="0" t="s">
         <v>25</v>
@@ -8961,7 +8976,7 @@
         <v>25</v>
       </c>
       <c r="V121" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="122">
@@ -8969,25 +8984,25 @@
         <v>153</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C122" s="0">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="D122" s="1">
-        <v>46203.39921296296</v>
+        <v>46206.18699074074</v>
       </c>
       <c r="E122" s="1">
-        <v>46203.39921296296</v>
+        <v>46207.44116898148</v>
       </c>
       <c r="F122" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I122" s="0" t="s">
         <v>25</v>
@@ -9029,7 +9044,7 @@
         <v>25</v>
       </c>
       <c r="V122" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="123">
@@ -9037,28 +9052,28 @@
         <v>154</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C123" s="0">
-        <v>300144</v>
+        <v>318</v>
       </c>
       <c r="D123" s="1">
-        <v>46206.91523148148</v>
+        <v>46205.74003472222</v>
       </c>
       <c r="E123" s="1">
-        <v>46206.91523148148</v>
+        <v>46205.74003472222</v>
       </c>
       <c r="F123" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J123" s="0" t="s">
         <v>25</v>
@@ -9076,10 +9091,10 @@
         <v>25</v>
       </c>
       <c r="O123" s="0">
-        <v>0</v>
-      </c>
-      <c r="P123" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P123" s="0">
+        <v>0</v>
       </c>
       <c r="Q123" s="0" t="s">
         <v>25</v>
@@ -9097,7 +9112,7 @@
         <v>25</v>
       </c>
       <c r="V123" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="124">
@@ -9105,31 +9120,31 @@
         <v>155</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C124" s="0">
-        <v>0</v>
+        <v>2521</v>
       </c>
       <c r="D124" s="1">
-        <v>46199.06940972222</v>
+        <v>46196.88789351852</v>
       </c>
       <c r="E124" s="1">
-        <v>46199.06940972222</v>
+        <v>46199.95371527778</v>
       </c>
       <c r="F124" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H124" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J124" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K124" s="0" t="s">
         <v>25</v>
@@ -9146,11 +9161,11 @@
       <c r="O124" s="0">
         <v>1</v>
       </c>
-      <c r="P124" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q124" s="0" t="s">
-        <v>25</v>
+      <c r="P124" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q124" s="0">
+        <v>1</v>
       </c>
       <c r="R124" s="0" t="s">
         <v>25</v>
@@ -9165,7 +9180,7 @@
         <v>25</v>
       </c>
       <c r="V124" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="125">
@@ -9173,31 +9188,31 @@
         <v>156</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C125" s="0">
-        <v>2092</v>
+        <v>262</v>
       </c>
       <c r="D125" s="1">
-        <v>46198.29152777778</v>
+        <v>46205.07099537037</v>
       </c>
       <c r="E125" s="1">
-        <v>46199.395949074074</v>
+        <v>46205.07099537037</v>
       </c>
       <c r="F125" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H125" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J125" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K125" s="0" t="s">
         <v>25</v>
@@ -9214,11 +9229,11 @@
       <c r="O125" s="0">
         <v>1</v>
       </c>
-      <c r="P125" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q125" s="0">
-        <v>0</v>
+      <c r="P125" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q125" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R125" s="0" t="s">
         <v>25</v>
@@ -9233,7 +9248,7 @@
         <v>25</v>
       </c>
       <c r="V125" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126">
@@ -9247,13 +9262,13 @@
         <v>0</v>
       </c>
       <c r="D126" s="1">
-        <v>46198.756527777776</v>
+        <v>46203.39921296296</v>
       </c>
       <c r="E126" s="1">
-        <v>46198.756527777776</v>
+        <v>46203.39921296296</v>
       </c>
       <c r="F126" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>30</v>
@@ -9262,7 +9277,7 @@
         <v>30</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J126" s="0" t="s">
         <v>25</v>
@@ -9282,8 +9297,8 @@
       <c r="O126" s="0">
         <v>1</v>
       </c>
-      <c r="P126" s="0" t="s">
-        <v>25</v>
+      <c r="P126" s="0">
+        <v>0</v>
       </c>
       <c r="Q126" s="0" t="s">
         <v>25</v>
@@ -9309,19 +9324,19 @@
         <v>158</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C127" s="0">
-        <v>344</v>
+        <v>300144</v>
       </c>
       <c r="D127" s="1">
-        <v>46203.41339120371</v>
+        <v>46206.91523148148</v>
       </c>
       <c r="E127" s="1">
-        <v>46208.76128472222</v>
+        <v>46206.91523148148</v>
       </c>
       <c r="F127" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>30</v>
@@ -9348,7 +9363,7 @@
         <v>25</v>
       </c>
       <c r="O127" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P127" s="0" t="s">
         <v>25</v>
@@ -9383,13 +9398,13 @@
         <v>0</v>
       </c>
       <c r="D128" s="1">
-        <v>46198.76427083334</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="E128" s="1">
-        <v>46198.76427083334</v>
+        <v>46199.06940972222</v>
       </c>
       <c r="F128" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>30</v>
@@ -9398,7 +9413,7 @@
         <v>30</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J128" s="0" t="s">
         <v>25</v>
@@ -9418,8 +9433,8 @@
       <c r="O128" s="0">
         <v>1</v>
       </c>
-      <c r="P128" s="0" t="s">
-        <v>25</v>
+      <c r="P128" s="0">
+        <v>0</v>
       </c>
       <c r="Q128" s="0" t="s">
         <v>25</v>
@@ -9445,31 +9460,31 @@
         <v>160</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C129" s="0">
-        <v>0</v>
+        <v>2092</v>
       </c>
       <c r="D129" s="1">
-        <v>46196.08101851852</v>
+        <v>46198.29152777778</v>
       </c>
       <c r="E129" s="1">
-        <v>46196.08101851852</v>
+        <v>46199.395949074074</v>
       </c>
       <c r="F129" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G129" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J129" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K129" s="0" t="s">
         <v>25</v>
@@ -9490,7 +9505,7 @@
         <v>0</v>
       </c>
       <c r="Q129" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R129" s="0" t="s">
         <v>25</v>
@@ -9505,7 +9520,7 @@
         <v>25</v>
       </c>
       <c r="V129" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="130">
@@ -9519,13 +9534,13 @@
         <v>0</v>
       </c>
       <c r="D130" s="1">
-        <v>46207.28523148148</v>
+        <v>46198.756527777776</v>
       </c>
       <c r="E130" s="1">
-        <v>46207.28523148148</v>
+        <v>46198.756527777776</v>
       </c>
       <c r="F130" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>30</v>
@@ -9534,7 +9549,7 @@
         <v>30</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J130" s="0" t="s">
         <v>25</v>
@@ -9554,8 +9569,8 @@
       <c r="O130" s="0">
         <v>1</v>
       </c>
-      <c r="P130" s="0" t="s">
-        <v>25</v>
+      <c r="P130" s="0">
+        <v>0</v>
       </c>
       <c r="Q130" s="0" t="s">
         <v>25</v>
@@ -9584,16 +9599,16 @@
         <v>38</v>
       </c>
       <c r="C131" s="0">
-        <v>262</v>
+        <v>344</v>
       </c>
       <c r="D131" s="1">
-        <v>46196.788564814815</v>
+        <v>46203.41339120371</v>
       </c>
       <c r="E131" s="1">
-        <v>46196.788564814815</v>
+        <v>46208.76128472222</v>
       </c>
       <c r="F131" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>30</v>
@@ -9649,31 +9664,31 @@
         <v>163</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C132" s="0">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="D132" s="1">
-        <v>46200.45096064815</v>
+        <v>46198.76427083334</v>
       </c>
       <c r="E132" s="1">
-        <v>46200.45096064815</v>
+        <v>46198.76427083334</v>
       </c>
       <c r="F132" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G132" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J132" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K132" s="0" t="s">
         <v>25</v>
@@ -9688,13 +9703,13 @@
         <v>25</v>
       </c>
       <c r="O132" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P132" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q132" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q132" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R132" s="0" t="s">
         <v>25</v>
@@ -9709,7 +9724,7 @@
         <v>25</v>
       </c>
       <c r="V132" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133">
@@ -9717,19 +9732,19 @@
         <v>164</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C133" s="0">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="D133" s="1">
-        <v>46198.12163194444</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="E133" s="1">
-        <v>46207.18237268519</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="F133" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>30</v>
@@ -9738,10 +9753,10 @@
         <v>30</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J133" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K133" s="0" t="s">
         <v>25</v>
@@ -9758,11 +9773,11 @@
       <c r="O133" s="0">
         <v>1</v>
       </c>
-      <c r="P133" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q133" s="0" t="s">
-        <v>25</v>
+      <c r="P133" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="0">
+        <v>1</v>
       </c>
       <c r="R133" s="0" t="s">
         <v>25</v>
@@ -9785,31 +9800,31 @@
         <v>165</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C134" s="0">
-        <v>13108</v>
+        <v>0</v>
       </c>
       <c r="D134" s="1">
-        <v>46197.70695601852</v>
+        <v>46207.28523148148</v>
       </c>
       <c r="E134" s="1">
-        <v>46198.89733796296</v>
+        <v>46207.28523148148</v>
       </c>
       <c r="F134" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H134" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J134" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K134" s="0" t="s">
         <v>25</v>
@@ -9824,13 +9839,13 @@
         <v>25</v>
       </c>
       <c r="O134" s="0">
-        <v>0</v>
-      </c>
-      <c r="P134" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q134" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P134" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q134" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R134" s="0" t="s">
         <v>25</v>
@@ -9845,7 +9860,7 @@
         <v>25</v>
       </c>
       <c r="V134" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="135">
@@ -9853,28 +9868,28 @@
         <v>166</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C135" s="0">
-        <v>13108</v>
+        <v>262</v>
       </c>
       <c r="D135" s="1">
-        <v>46201.693333333336</v>
+        <v>46196.788564814815</v>
       </c>
       <c r="E135" s="1">
-        <v>46205.19603009259</v>
+        <v>46196.788564814815</v>
       </c>
       <c r="F135" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H135" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J135" s="0" t="s">
         <v>25</v>
@@ -9892,7 +9907,7 @@
         <v>25</v>
       </c>
       <c r="O135" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P135" s="0">
         <v>0</v>
@@ -9913,7 +9928,7 @@
         <v>25</v>
       </c>
       <c r="V135" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136">
@@ -9921,31 +9936,31 @@
         <v>167</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C136" s="0">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="D136" s="1">
-        <v>46196.08101851852</v>
+        <v>46200.45096064815</v>
       </c>
       <c r="E136" s="1">
-        <v>46196.08101851852</v>
+        <v>46200.45096064815</v>
       </c>
       <c r="F136" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H136" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J136" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K136" s="0" t="s">
         <v>25</v>
@@ -9960,7 +9975,7 @@
         <v>25</v>
       </c>
       <c r="O136" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P136" s="0">
         <v>1</v>
@@ -9981,7 +9996,7 @@
         <v>25</v>
       </c>
       <c r="V136" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="137">
@@ -9992,16 +10007,16 @@
         <v>38</v>
       </c>
       <c r="C137" s="0">
-        <v>262</v>
+        <v>336</v>
       </c>
       <c r="D137" s="1">
-        <v>46196.88885416667</v>
+        <v>46198.12163194444</v>
       </c>
       <c r="E137" s="1">
-        <v>46196.88885416667</v>
+        <v>46207.18237268519</v>
       </c>
       <c r="F137" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>30</v>
@@ -10031,7 +10046,7 @@
         <v>1</v>
       </c>
       <c r="P137" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q137" s="0" t="s">
         <v>25</v>
@@ -10057,19 +10072,19 @@
         <v>169</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C138" s="0">
-        <v>2108</v>
+        <v>13108</v>
       </c>
       <c r="D138" s="1">
-        <v>46199.89765046296</v>
+        <v>46197.70695601852</v>
       </c>
       <c r="E138" s="1">
-        <v>46199.89765046296</v>
+        <v>46198.89733796296</v>
       </c>
       <c r="F138" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>24</v>
@@ -10081,7 +10096,7 @@
         <v>24</v>
       </c>
       <c r="J138" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K138" s="0" t="s">
         <v>25</v>
@@ -10096,13 +10111,13 @@
         <v>25</v>
       </c>
       <c r="O138" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P138" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q138" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="Q138" s="0">
+        <v>0</v>
       </c>
       <c r="R138" s="0" t="s">
         <v>25</v>
@@ -10125,28 +10140,28 @@
         <v>170</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C139" s="0">
-        <v>0</v>
+        <v>13108</v>
       </c>
       <c r="D139" s="1">
-        <v>46203.38673611111</v>
+        <v>46201.693333333336</v>
       </c>
       <c r="E139" s="1">
-        <v>46203.38673611111</v>
+        <v>46205.19603009259</v>
       </c>
       <c r="F139" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G139" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H139" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J139" s="0" t="s">
         <v>25</v>
@@ -10164,7 +10179,7 @@
         <v>25</v>
       </c>
       <c r="O139" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P139" s="0">
         <v>0</v>
@@ -10185,7 +10200,7 @@
         <v>25</v>
       </c>
       <c r="V139" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="140">
@@ -10193,31 +10208,31 @@
         <v>171</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C140" s="0">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="D140" s="1">
-        <v>46208.24219907408</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="E140" s="1">
-        <v>46208.49730324074</v>
+        <v>46196.08101851852</v>
       </c>
       <c r="F140" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J140" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K140" s="0" t="s">
         <v>25</v>
@@ -10234,11 +10249,11 @@
       <c r="O140" s="0">
         <v>1</v>
       </c>
-      <c r="P140" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q140" s="0" t="s">
-        <v>25</v>
+      <c r="P140" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q140" s="0">
+        <v>1</v>
       </c>
       <c r="R140" s="0" t="s">
         <v>25</v>
@@ -10253,7 +10268,7 @@
         <v>25</v>
       </c>
       <c r="V140" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141">
@@ -10261,31 +10276,31 @@
         <v>172</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C141" s="0">
-        <v>2025</v>
+        <v>262</v>
       </c>
       <c r="D141" s="1">
-        <v>46202.83125</v>
+        <v>46196.88885416667</v>
       </c>
       <c r="E141" s="1">
-        <v>46205.35525462963</v>
+        <v>46196.88885416667</v>
       </c>
       <c r="F141" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J141" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K141" s="0" t="s">
         <v>25</v>
@@ -10300,13 +10315,13 @@
         <v>25</v>
       </c>
       <c r="O141" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P141" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q141" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="Q141" s="0">
+        <v>0</v>
       </c>
       <c r="R141" s="0" t="s">
         <v>25</v>
@@ -10321,7 +10336,7 @@
         <v>25</v>
       </c>
       <c r="V141" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142">
@@ -10329,31 +10344,31 @@
         <v>173</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C142" s="0">
-        <v>206</v>
+        <v>2108</v>
       </c>
       <c r="D142" s="1">
-        <v>46199.259988425925</v>
+        <v>46199.89765046296</v>
       </c>
       <c r="E142" s="1">
-        <v>46200.595925925925</v>
+        <v>46199.89765046296</v>
       </c>
       <c r="F142" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G142" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J142" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K142" s="0" t="s">
         <v>25</v>
@@ -10389,7 +10404,7 @@
         <v>25</v>
       </c>
       <c r="V142" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143">
@@ -10397,31 +10412,31 @@
         <v>174</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C143" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D143" s="1">
-        <v>46196.84064814815</v>
+        <v>46203.38673611111</v>
       </c>
       <c r="E143" s="1">
-        <v>46198.36408564815</v>
+        <v>46203.38673611111</v>
       </c>
       <c r="F143" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J143" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K143" s="0" t="s">
         <v>25</v>
@@ -10436,13 +10451,13 @@
         <v>25</v>
       </c>
       <c r="O143" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P143" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q143" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q143" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R143" s="0" t="s">
         <v>25</v>
@@ -10457,7 +10472,7 @@
         <v>25</v>
       </c>
       <c r="V143" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144">
@@ -10471,13 +10486,13 @@
         <v>2518</v>
       </c>
       <c r="D144" s="1">
-        <v>46208.95462962963</v>
+        <v>46208.24219907408</v>
       </c>
       <c r="E144" s="1">
-        <v>46208.95462962963</v>
+        <v>46208.49730324074</v>
       </c>
       <c r="F144" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>39</v>
@@ -10533,19 +10548,19 @@
         <v>176</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C145" s="0">
-        <v>13108</v>
+        <v>2025</v>
       </c>
       <c r="D145" s="1">
-        <v>46205.32334490741</v>
+        <v>46202.83125</v>
       </c>
       <c r="E145" s="1">
-        <v>46209.34474537037</v>
+        <v>46205.35525462963</v>
       </c>
       <c r="F145" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>24</v>
@@ -10554,7 +10569,7 @@
         <v>24</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J145" s="0" t="s">
         <v>25</v>
@@ -10572,10 +10587,10 @@
         <v>25</v>
       </c>
       <c r="O145" s="0">
-        <v>1</v>
-      </c>
-      <c r="P145" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P145" s="0">
+        <v>0</v>
       </c>
       <c r="Q145" s="0" t="s">
         <v>25</v>
@@ -10604,16 +10619,16 @@
         <v>38</v>
       </c>
       <c r="C146" s="0">
-        <v>344</v>
+        <v>206</v>
       </c>
       <c r="D146" s="1">
-        <v>46203.6659375</v>
+        <v>46199.259988425925</v>
       </c>
       <c r="E146" s="1">
-        <v>46203.6659375</v>
+        <v>46200.595925925925</v>
       </c>
       <c r="F146" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>30</v>
@@ -10622,10 +10637,10 @@
         <v>30</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J146" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K146" s="0" t="s">
         <v>25</v>
@@ -10640,13 +10655,13 @@
         <v>25</v>
       </c>
       <c r="O146" s="0">
-        <v>0</v>
-      </c>
-      <c r="P146" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q146" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P146" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q146" s="0">
+        <v>1</v>
       </c>
       <c r="R146" s="0" t="s">
         <v>25</v>
@@ -10672,16 +10687,16 @@
         <v>23</v>
       </c>
       <c r="C147" s="0">
-        <v>2518</v>
+        <v>2108</v>
       </c>
       <c r="D147" s="1">
-        <v>46200.18853009259</v>
+        <v>46196.84064814815</v>
       </c>
       <c r="E147" s="1">
-        <v>46200.84137731481</v>
+        <v>46198.36408564815</v>
       </c>
       <c r="F147" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>24</v>
@@ -10708,7 +10723,7 @@
         <v>25</v>
       </c>
       <c r="O147" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P147" s="0">
         <v>1</v>
@@ -10740,22 +10755,22 @@
         <v>23</v>
       </c>
       <c r="C148" s="0">
-        <v>2108</v>
+        <v>2518</v>
       </c>
       <c r="D148" s="1">
-        <v>46205.6671412037</v>
+        <v>46208.95462962963</v>
       </c>
       <c r="E148" s="1">
-        <v>46207.322233796294</v>
+        <v>46208.95462962963</v>
       </c>
       <c r="F148" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>25</v>
@@ -10797,7 +10812,7 @@
         <v>25</v>
       </c>
       <c r="V148" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="149">
@@ -10805,25 +10820,25 @@
         <v>180</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C149" s="0">
-        <v>344</v>
+        <v>13108</v>
       </c>
       <c r="D149" s="1">
-        <v>46203.665925925925</v>
+        <v>46205.32334490741</v>
       </c>
       <c r="E149" s="1">
-        <v>46203.665925925925</v>
+        <v>46209.34474537037</v>
       </c>
       <c r="F149" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I149" s="0" t="s">
         <v>25</v>
@@ -10865,7 +10880,7 @@
         <v>25</v>
       </c>
       <c r="V149" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="150">
@@ -10873,28 +10888,28 @@
         <v>181</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C150" s="0">
-        <v>2108</v>
+        <v>344</v>
       </c>
       <c r="D150" s="1">
-        <v>46207.904699074075</v>
+        <v>46203.6659375</v>
       </c>
       <c r="E150" s="1">
-        <v>46208.80619212963</v>
+        <v>46203.6659375</v>
       </c>
       <c r="F150" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J150" s="0" t="s">
         <v>25</v>
@@ -10914,8 +10929,8 @@
       <c r="O150" s="0">
         <v>0</v>
       </c>
-      <c r="P150" s="0" t="s">
-        <v>25</v>
+      <c r="P150" s="0">
+        <v>1</v>
       </c>
       <c r="Q150" s="0" t="s">
         <v>25</v>
@@ -10933,7 +10948,7 @@
         <v>25</v>
       </c>
       <c r="V150" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="151">
@@ -10944,28 +10959,28 @@
         <v>23</v>
       </c>
       <c r="C151" s="0">
-        <v>2123</v>
+        <v>2518</v>
       </c>
       <c r="D151" s="1">
-        <v>46205.68171296296</v>
+        <v>46200.18853009259</v>
       </c>
       <c r="E151" s="1">
-        <v>46207.24060185185</v>
+        <v>46200.84137731481</v>
       </c>
       <c r="F151" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J151" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K151" s="0" t="s">
         <v>25</v>
@@ -10982,11 +10997,11 @@
       <c r="O151" s="0">
         <v>1</v>
       </c>
-      <c r="P151" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q151" s="0" t="s">
-        <v>25</v>
+      <c r="P151" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q151" s="0">
+        <v>0</v>
       </c>
       <c r="R151" s="0" t="s">
         <v>25</v>
@@ -11001,7 +11016,7 @@
         <v>25</v>
       </c>
       <c r="V151" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="152">
@@ -11015,13 +11030,13 @@
         <v>2108</v>
       </c>
       <c r="D152" s="1">
-        <v>46199.41601851852</v>
+        <v>46205.6671412037</v>
       </c>
       <c r="E152" s="1">
-        <v>46202.50537037037</v>
+        <v>46207.322233796294</v>
       </c>
       <c r="F152" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>24</v>
@@ -11030,7 +11045,7 @@
         <v>24</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J152" s="0" t="s">
         <v>25</v>
@@ -11048,10 +11063,10 @@
         <v>25</v>
       </c>
       <c r="O152" s="0">
-        <v>0</v>
-      </c>
-      <c r="P152" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="P152" s="0">
+        <v>0</v>
       </c>
       <c r="Q152" s="0" t="s">
         <v>25</v>
@@ -11077,31 +11092,31 @@
         <v>184</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C153" s="0">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="D153" s="1">
-        <v>46196.08100694444</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="E153" s="1">
-        <v>46196.08100694444</v>
+        <v>46203.665925925925</v>
       </c>
       <c r="F153" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G153" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H153" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J153" s="0" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K153" s="0" t="s">
         <v>25</v>
@@ -11121,8 +11136,8 @@
       <c r="P153" s="0">
         <v>0</v>
       </c>
-      <c r="Q153" s="0">
-        <v>1</v>
+      <c r="Q153" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R153" s="0" t="s">
         <v>25</v>
@@ -11137,7 +11152,7 @@
         <v>25</v>
       </c>
       <c r="V153" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="154">
@@ -11148,28 +11163,28 @@
         <v>23</v>
       </c>
       <c r="C154" s="0">
-        <v>2518</v>
+        <v>2108</v>
       </c>
       <c r="D154" s="1">
-        <v>46198.78761574074</v>
+        <v>46207.904699074075</v>
       </c>
       <c r="E154" s="1">
-        <v>46200.24690972222</v>
+        <v>46208.80619212963</v>
       </c>
       <c r="F154" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J154" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K154" s="0" t="s">
         <v>25</v>
@@ -11184,13 +11199,13 @@
         <v>25</v>
       </c>
       <c r="O154" s="0">
-        <v>1</v>
-      </c>
-      <c r="P154" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q154" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P154" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q154" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R154" s="0" t="s">
         <v>25</v>
@@ -11216,16 +11231,16 @@
         <v>23</v>
       </c>
       <c r="C155" s="0">
-        <v>2099</v>
+        <v>2123</v>
       </c>
       <c r="D155" s="1">
-        <v>46200.39493055556</v>
+        <v>46205.68171296296</v>
       </c>
       <c r="E155" s="1">
-        <v>46200.39493055556</v>
+        <v>46207.24060185185</v>
       </c>
       <c r="F155" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>30</v>
@@ -11237,7 +11252,7 @@
         <v>30</v>
       </c>
       <c r="J155" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K155" s="0" t="s">
         <v>25</v>
@@ -11252,13 +11267,13 @@
         <v>25</v>
       </c>
       <c r="O155" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P155" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q155" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q155" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R155" s="0" t="s">
         <v>25</v>
@@ -11284,16 +11299,16 @@
         <v>23</v>
       </c>
       <c r="C156" s="0">
-        <v>2046</v>
+        <v>2108</v>
       </c>
       <c r="D156" s="1">
-        <v>46200.55334490741</v>
+        <v>46199.41601851852</v>
       </c>
       <c r="E156" s="1">
-        <v>46201.81197916667</v>
+        <v>46202.50537037037</v>
       </c>
       <c r="F156" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>24</v>
@@ -11302,7 +11317,7 @@
         <v>24</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J156" s="0" t="s">
         <v>25</v>
@@ -11322,8 +11337,8 @@
       <c r="O156" s="0">
         <v>0</v>
       </c>
-      <c r="P156" s="0">
-        <v>0</v>
+      <c r="P156" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="Q156" s="0" t="s">
         <v>25</v>
@@ -11349,31 +11364,31 @@
         <v>188</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C157" s="0">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="D157" s="1">
-        <v>46196.56989583333</v>
+        <v>46196.08100694444</v>
       </c>
       <c r="E157" s="1">
-        <v>46196.87100694444</v>
+        <v>46196.08100694444</v>
       </c>
       <c r="F157" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H157" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J157" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K157" s="0" t="s">
         <v>25</v>
@@ -11388,13 +11403,13 @@
         <v>25</v>
       </c>
       <c r="O157" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P157" s="0">
         <v>0</v>
       </c>
       <c r="Q157" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R157" s="0" t="s">
         <v>25</v>
@@ -11409,7 +11424,7 @@
         <v>25</v>
       </c>
       <c r="V157" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="158">
@@ -11417,31 +11432,31 @@
         <v>189</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C158" s="0">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="D158" s="1">
-        <v>46203.38674768519</v>
+        <v>46198.78761574074</v>
       </c>
       <c r="E158" s="1">
-        <v>46203.38674768519</v>
+        <v>46200.24690972222</v>
       </c>
       <c r="F158" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J158" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K158" s="0" t="s">
         <v>25</v>
@@ -11459,10 +11474,10 @@
         <v>1</v>
       </c>
       <c r="P158" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q158" s="0" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="Q158" s="0">
+        <v>1</v>
       </c>
       <c r="R158" s="0" t="s">
         <v>25</v>
@@ -11477,7 +11492,7 @@
         <v>25</v>
       </c>
       <c r="V158" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="159">
@@ -11485,19 +11500,19 @@
         <v>190</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C159" s="0">
-        <v>0</v>
+        <v>2099</v>
       </c>
       <c r="D159" s="1">
-        <v>46199.38827546296</v>
+        <v>46200.39493055556</v>
       </c>
       <c r="E159" s="1">
-        <v>46199.38827546296</v>
+        <v>46200.39493055556</v>
       </c>
       <c r="F159" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>30</v>
@@ -11509,7 +11524,7 @@
         <v>30</v>
       </c>
       <c r="J159" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K159" s="0" t="s">
         <v>25</v>
@@ -11524,13 +11539,13 @@
         <v>25</v>
       </c>
       <c r="O159" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P159" s="0">
         <v>1</v>
       </c>
-      <c r="Q159" s="0" t="s">
-        <v>25</v>
+      <c r="Q159" s="0">
+        <v>0</v>
       </c>
       <c r="R159" s="0" t="s">
         <v>25</v>
@@ -11553,31 +11568,31 @@
         <v>191</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C160" s="0">
-        <v>0</v>
+        <v>2046</v>
       </c>
       <c r="D160" s="1">
-        <v>46198.75832175926</v>
+        <v>46200.55334490741</v>
       </c>
       <c r="E160" s="1">
-        <v>46198.75832175926</v>
+        <v>46201.81197916667</v>
       </c>
       <c r="F160" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G160" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J160" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K160" s="0" t="s">
         <v>25</v>
@@ -11592,13 +11607,13 @@
         <v>25</v>
       </c>
       <c r="O160" s="0">
-        <v>1</v>
-      </c>
-      <c r="P160" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q160" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P160" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="0">
+        <v>0</v>
       </c>
       <c r="R160" s="0" t="s">
         <v>25</v>
@@ -11613,7 +11628,7 @@
         <v>25</v>
       </c>
       <c r="V160" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="161">
@@ -11624,16 +11639,16 @@
         <v>23</v>
       </c>
       <c r="C161" s="0">
-        <v>2025</v>
+        <v>2108</v>
       </c>
       <c r="D161" s="1">
-        <v>46200.08666666667</v>
+        <v>46196.56989583333</v>
       </c>
       <c r="E161" s="1">
-        <v>46200.08666666667</v>
+        <v>46196.87100694444</v>
       </c>
       <c r="F161" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>24</v>
@@ -11645,7 +11660,7 @@
         <v>24</v>
       </c>
       <c r="J161" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K161" s="0" t="s">
         <v>25</v>
@@ -11660,13 +11675,13 @@
         <v>25</v>
       </c>
       <c r="O161" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P161" s="0">
         <v>0</v>
       </c>
-      <c r="Q161" s="0" t="s">
-        <v>25</v>
+      <c r="Q161" s="0">
+        <v>0</v>
       </c>
       <c r="R161" s="0" t="s">
         <v>25</v>
@@ -11689,31 +11704,31 @@
         <v>193</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C162" s="0">
-        <v>336</v>
+        <v>2108</v>
       </c>
       <c r="D162" s="1">
-        <v>46191.19981481481</v>
+        <v>46209.70079861111</v>
       </c>
       <c r="E162" s="1">
-        <v>46191.20039351852</v>
+        <v>46211.287673611114</v>
       </c>
       <c r="F162" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H162" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J162" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K162" s="0" t="s">
         <v>25</v>
@@ -11728,13 +11743,13 @@
         <v>25</v>
       </c>
       <c r="O162" s="0">
-        <v>0</v>
-      </c>
-      <c r="P162" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q162" s="0">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P162" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q162" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R162" s="0" t="s">
         <v>25</v>
@@ -11749,7 +11764,7 @@
         <v>25</v>
       </c>
       <c r="V162" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="163">
@@ -11763,13 +11778,13 @@
         <v>0</v>
       </c>
       <c r="D163" s="1">
-        <v>46198.06826388889</v>
+        <v>46203.38674768519</v>
       </c>
       <c r="E163" s="1">
-        <v>46198.06826388889</v>
+        <v>46203.38674768519</v>
       </c>
       <c r="F163" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>30</v>
@@ -11778,7 +11793,7 @@
         <v>30</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J163" s="0" t="s">
         <v>25</v>
@@ -11798,8 +11813,8 @@
       <c r="O163" s="0">
         <v>1</v>
       </c>
-      <c r="P163" s="0" t="s">
-        <v>25</v>
+      <c r="P163" s="0">
+        <v>0</v>
       </c>
       <c r="Q163" s="0" t="s">
         <v>25</v>
@@ -11825,19 +11840,19 @@
         <v>195</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C164" s="0">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="D164" s="1">
-        <v>46197.6375462963</v>
+        <v>46199.38827546296</v>
       </c>
       <c r="E164" s="1">
-        <v>46197.6375462963</v>
+        <v>46199.38827546296</v>
       </c>
       <c r="F164" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>30</v>
@@ -11864,7 +11879,7 @@
         <v>25</v>
       </c>
       <c r="O164" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P164" s="0">
         <v>1</v>
@@ -11893,19 +11908,19 @@
         <v>196</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C165" s="0">
-        <v>304112</v>
+        <v>0</v>
       </c>
       <c r="D165" s="1">
-        <v>46197.037523148145</v>
+        <v>46198.75832175926</v>
       </c>
       <c r="E165" s="1">
-        <v>46197.037523148145</v>
+        <v>46198.75832175926</v>
       </c>
       <c r="F165" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>30</v>
@@ -11917,7 +11932,7 @@
         <v>30</v>
       </c>
       <c r="J165" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K165" s="0" t="s">
         <v>25</v>
@@ -11935,10 +11950,10 @@
         <v>1</v>
       </c>
       <c r="P165" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q165" s="0">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q165" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R165" s="0" t="s">
         <v>25</v>
@@ -11964,16 +11979,16 @@
         <v>23</v>
       </c>
       <c r="C166" s="0">
-        <v>2106</v>
+        <v>2025</v>
       </c>
       <c r="D166" s="1">
-        <v>46197.12175925926</v>
+        <v>46200.08666666667</v>
       </c>
       <c r="E166" s="1">
-        <v>46198.31060185185</v>
+        <v>46200.08666666667</v>
       </c>
       <c r="F166" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>24</v>
@@ -12003,7 +12018,7 @@
         <v>1</v>
       </c>
       <c r="P166" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q166" s="0">
         <v>0</v>
@@ -12029,31 +12044,31 @@
         <v>198</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C167" s="0">
-        <v>2108</v>
+        <v>336</v>
       </c>
       <c r="D167" s="1">
-        <v>46202.840995370374</v>
+        <v>46191.19981481481</v>
       </c>
       <c r="E167" s="1">
-        <v>46209.31466435185</v>
+        <v>46191.20039351852</v>
       </c>
       <c r="F167" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J167" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K167" s="0" t="s">
         <v>25</v>
@@ -12070,11 +12085,11 @@
       <c r="O167" s="0">
         <v>0</v>
       </c>
-      <c r="P167" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q167" s="0" t="s">
-        <v>25</v>
+      <c r="P167" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q167" s="0">
+        <v>0</v>
       </c>
       <c r="R167" s="0" t="s">
         <v>25</v>
@@ -12089,7 +12104,7 @@
         <v>25</v>
       </c>
       <c r="V167" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="168">
@@ -12097,28 +12112,28 @@
         <v>199</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C168" s="0">
-        <v>2009</v>
+        <v>0</v>
       </c>
       <c r="D168" s="1">
-        <v>46206.72038194445</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="E168" s="1">
-        <v>46206.72038194445</v>
+        <v>46198.06826388889</v>
       </c>
       <c r="F168" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J168" s="0" t="s">
         <v>25</v>
@@ -12138,8 +12153,8 @@
       <c r="O168" s="0">
         <v>1</v>
       </c>
-      <c r="P168" s="0" t="s">
-        <v>25</v>
+      <c r="P168" s="0">
+        <v>0</v>
       </c>
       <c r="Q168" s="0" t="s">
         <v>25</v>
@@ -12157,7 +12172,7 @@
         <v>25</v>
       </c>
       <c r="V168" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169">
@@ -12165,19 +12180,19 @@
         <v>200</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C169" s="0">
-        <v>2044</v>
+        <v>262</v>
       </c>
       <c r="D169" s="1">
-        <v>46197.46810185185</v>
+        <v>46197.6375462963</v>
       </c>
       <c r="E169" s="1">
-        <v>46197.46810185185</v>
+        <v>46197.6375462963</v>
       </c>
       <c r="F169" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>30</v>
@@ -12207,7 +12222,7 @@
         <v>0</v>
       </c>
       <c r="P169" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q169" s="0">
         <v>1</v>
@@ -12233,31 +12248,31 @@
         <v>201</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C170" s="0">
-        <v>2518</v>
+        <v>304112</v>
       </c>
       <c r="D170" s="1">
-        <v>46200.77527777778</v>
+        <v>46197.037523148145</v>
       </c>
       <c r="E170" s="1">
-        <v>46202.349328703705</v>
+        <v>46197.037523148145</v>
       </c>
       <c r="F170" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H170" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J170" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K170" s="0" t="s">
         <v>25</v>
@@ -12277,8 +12292,8 @@
       <c r="P170" s="0">
         <v>1</v>
       </c>
-      <c r="Q170" s="0" t="s">
-        <v>25</v>
+      <c r="Q170" s="0">
+        <v>1</v>
       </c>
       <c r="R170" s="0" t="s">
         <v>25</v>
@@ -12293,7 +12308,7 @@
         <v>25</v>
       </c>
       <c r="V170" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171">
@@ -12301,31 +12316,31 @@
         <v>202</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C171" s="0">
-        <v>0</v>
+        <v>2106</v>
       </c>
       <c r="D171" s="1">
-        <v>46198.75665509259</v>
+        <v>46197.12175925926</v>
       </c>
       <c r="E171" s="1">
-        <v>46198.75665509259</v>
+        <v>46198.31060185185</v>
       </c>
       <c r="F171" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G171" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H171" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J171" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K171" s="0" t="s">
         <v>25</v>
@@ -12342,11 +12357,11 @@
       <c r="O171" s="0">
         <v>1</v>
       </c>
-      <c r="P171" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q171" s="0" t="s">
-        <v>25</v>
+      <c r="P171" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q171" s="0">
+        <v>1</v>
       </c>
       <c r="R171" s="0" t="s">
         <v>25</v>
@@ -12361,7 +12376,7 @@
         <v>25</v>
       </c>
       <c r="V171" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="172">
@@ -12375,19 +12390,19 @@
         <v>2108</v>
       </c>
       <c r="D172" s="1">
-        <v>46205.784363425926</v>
+        <v>46202.840995370374</v>
       </c>
       <c r="E172" s="1">
-        <v>46205.784363425926</v>
+        <v>46209.31466435185</v>
       </c>
       <c r="F172" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H172" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I172" s="0" t="s">
         <v>25</v>
@@ -12408,7 +12423,7 @@
         <v>25</v>
       </c>
       <c r="O172" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P172" s="0" t="s">
         <v>25</v>
@@ -12429,7 +12444,7 @@
         <v>25</v>
       </c>
       <c r="V172" s="0" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="173">
@@ -12437,28 +12452,28 @@
         <v>204</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C173" s="0">
-        <v>0</v>
+        <v>2009</v>
       </c>
       <c r="D173" s="1">
-        <v>46198.75827546296</v>
+        <v>46206.72038194445</v>
       </c>
       <c r="E173" s="1">
-        <v>46198.75827546296</v>
+        <v>46206.72038194445</v>
       </c>
       <c r="F173" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G173" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J173" s="0" t="s">
         <v>25</v>
@@ -12478,8 +12493,8 @@
       <c r="O173" s="0">
         <v>1</v>
       </c>
-      <c r="P173" s="0" t="s">
-        <v>25</v>
+      <c r="P173" s="0">
+        <v>0</v>
       </c>
       <c r="Q173" s="0" t="s">
         <v>25</v>
@@ -12497,7 +12512,7 @@
         <v>25</v>
       </c>
       <c r="V173" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="174">
@@ -12508,28 +12523,28 @@
         <v>23</v>
       </c>
       <c r="C174" s="0">
-        <v>2025</v>
+        <v>2044</v>
       </c>
       <c r="D174" s="1">
-        <v>46203.80048611111</v>
+        <v>46197.46810185185</v>
       </c>
       <c r="E174" s="1">
-        <v>46203.80048611111</v>
+        <v>46197.46810185185</v>
       </c>
       <c r="F174" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J174" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K174" s="0" t="s">
         <v>25</v>
@@ -12544,13 +12559,13 @@
         <v>25</v>
       </c>
       <c r="O174" s="0">
-        <v>1</v>
-      </c>
-      <c r="P174" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q174" s="0" t="s">
-        <v>25</v>
+        <v>0</v>
+      </c>
+      <c r="P174" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="0">
+        <v>1</v>
       </c>
       <c r="R174" s="0" t="s">
         <v>25</v>
@@ -12565,7 +12580,7 @@
         <v>25</v>
       </c>
       <c r="V174" s="0" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175">
@@ -12576,16 +12591,16 @@
         <v>23</v>
       </c>
       <c r="C175" s="0">
-        <v>2108</v>
+        <v>2518</v>
       </c>
       <c r="D175" s="1">
-        <v>46205.49758101852</v>
+        <v>46200.77527777778</v>
       </c>
       <c r="E175" s="1">
-        <v>46207.377118055556</v>
+        <v>46202.349328703705</v>
       </c>
       <c r="F175" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>24</v>
@@ -12594,10 +12609,10 @@
         <v>24</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J175" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K175" s="0" t="s">
         <v>25</v>
@@ -12614,11 +12629,11 @@
       <c r="O175" s="0">
         <v>1</v>
       </c>
-      <c r="P175" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q175" s="0" t="s">
-        <v>25</v>
+      <c r="P175" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q175" s="0">
+        <v>0</v>
       </c>
       <c r="R175" s="0" t="s">
         <v>25</v>
@@ -12647,13 +12662,13 @@
         <v>0</v>
       </c>
       <c r="D176" s="1">
-        <v>46198.76320601852</v>
+        <v>46198.75665509259</v>
       </c>
       <c r="E176" s="1">
-        <v>46198.76320601852</v>
+        <v>46198.75665509259</v>
       </c>
       <c r="F176" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>30</v>
@@ -12662,7 +12677,7 @@
         <v>30</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J176" s="0" t="s">
         <v>25</v>
@@ -12682,8 +12697,8 @@
       <c r="O176" s="0">
         <v>1</v>
       </c>
-      <c r="P176" s="0" t="s">
-        <v>25</v>
+      <c r="P176" s="0">
+        <v>0</v>
       </c>
       <c r="Q176" s="0" t="s">
         <v>25</v>
@@ -12709,19 +12724,19 @@
         <v>208</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C177" s="0">
-        <v>205</v>
+        <v>2108</v>
       </c>
       <c r="D177" s="1">
-        <v>46207.94667824074</v>
+        <v>46205.784363425926</v>
       </c>
       <c r="E177" s="1">
-        <v>46209.364849537036</v>
+        <v>46205.784363425926</v>
       </c>
       <c r="F177" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>39</v>
@@ -12730,7 +12745,7 @@
         <v>39</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J177" s="0" t="s">
         <v>25</v>
@@ -12750,8 +12765,8 @@
       <c r="O177" s="0">
         <v>1</v>
       </c>
-      <c r="P177" s="0" t="s">
-        <v>25</v>
+      <c r="P177" s="0">
+        <v>0</v>
       </c>
       <c r="Q177" s="0" t="s">
         <v>25</v>
@@ -12783,13 +12798,13 @@
         <v>0</v>
       </c>
       <c r="D178" s="1">
-        <v>46198.76327546296</v>
+        <v>46198.75827546296</v>
       </c>
       <c r="E178" s="1">
-        <v>46198.76327546296</v>
+        <v>46198.75827546296</v>
       </c>
       <c r="F178" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>30</v>
@@ -12798,7 +12813,7 @@
         <v>30</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J178" s="0" t="s">
         <v>25</v>
@@ -12818,8 +12833,8 @@
       <c r="O178" s="0">
         <v>1</v>
       </c>
-      <c r="P178" s="0" t="s">
-        <v>25</v>
+      <c r="P178" s="0">
+        <v>0</v>
       </c>
       <c r="Q178" s="0" t="s">
         <v>25</v>
@@ -12845,31 +12860,31 @@
         <v>210</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C179" s="0">
-        <v>312</v>
+        <v>2025</v>
       </c>
       <c r="D179" s="1">
-        <v>46197.041238425925</v>
+        <v>46203.80048611111</v>
       </c>
       <c r="E179" s="1">
-        <v>46197.041238425925</v>
+        <v>46203.80048611111</v>
       </c>
       <c r="F179" s="1">
-        <v>46211.04225972222</v>
+        <v>46212.042284027775</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J179" s="0" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K179" s="0" t="s">
         <v>25</v>
@@ -12886,11 +12901,11 @@
       <c r="O179" s="0">
         <v>1</v>
       </c>
-      <c r="P179" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q179" s="0">
-        <v>0</v>
+      <c r="P179" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q179" s="0" t="s">
+        <v>25</v>
       </c>
       <c r="R179" s="0" t="s">
         <v>25</v>
@@ -12905,7 +12920,7 @@
         <v>25</v>
       </c>
       <c r="V179" s="0" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="180">
@@ -12913,66 +12928,406 @@
         <v>211</v>
       </c>
       <c r="B180" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C180" s="0">
+        <v>2108</v>
+      </c>
+      <c r="D180" s="1">
+        <v>46205.49758101852</v>
+      </c>
+      <c r="E180" s="1">
+        <v>46207.377118055556</v>
+      </c>
+      <c r="F180" s="1">
+        <v>46212.042284027775</v>
+      </c>
+      <c r="G180" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H180" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="I180" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="J180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O180" s="0">
+        <v>1</v>
+      </c>
+      <c r="P180" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U180" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V180" s="0" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="B181" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C181" s="0">
+        <v>0</v>
+      </c>
+      <c r="D181" s="1">
+        <v>46198.76320601852</v>
+      </c>
+      <c r="E181" s="1">
+        <v>46198.76320601852</v>
+      </c>
+      <c r="F181" s="1">
+        <v>46212.042284027775</v>
+      </c>
+      <c r="G181" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H181" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I181" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J181" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K181" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L181" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M181" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N181" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O181" s="0">
+        <v>1</v>
+      </c>
+      <c r="P181" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R181" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S181" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T181" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U181" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V181" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="B182" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C180" s="0">
+      <c r="C182" s="0">
+        <v>205</v>
+      </c>
+      <c r="D182" s="1">
+        <v>46207.94667824074</v>
+      </c>
+      <c r="E182" s="1">
+        <v>46209.364849537036</v>
+      </c>
+      <c r="F182" s="1">
+        <v>46212.042284027775</v>
+      </c>
+      <c r="G182" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="H182" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O182" s="0">
+        <v>1</v>
+      </c>
+      <c r="P182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U182" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V182" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="B183" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C183" s="0">
+        <v>0</v>
+      </c>
+      <c r="D183" s="1">
+        <v>46198.76327546296</v>
+      </c>
+      <c r="E183" s="1">
+        <v>46198.76327546296</v>
+      </c>
+      <c r="F183" s="1">
+        <v>46212.042284027775</v>
+      </c>
+      <c r="G183" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H183" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I183" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J183" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="K183" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L183" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M183" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N183" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O183" s="0">
+        <v>1</v>
+      </c>
+      <c r="P183" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q183" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="R183" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S183" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T183" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U183" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V183" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="B184" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C184" s="0">
+        <v>312</v>
+      </c>
+      <c r="D184" s="1">
+        <v>46197.041238425925</v>
+      </c>
+      <c r="E184" s="1">
+        <v>46197.041238425925</v>
+      </c>
+      <c r="F184" s="1">
+        <v>46212.042284027775</v>
+      </c>
+      <c r="G184" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H184" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I184" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J184" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K184" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L184" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M184" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N184" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O184" s="0">
+        <v>1</v>
+      </c>
+      <c r="P184" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q184" s="0">
+        <v>0</v>
+      </c>
+      <c r="R184" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S184" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T184" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U184" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V184" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="B185" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C185" s="0">
         <v>262</v>
       </c>
-      <c r="D180" s="1">
+      <c r="D185" s="1">
         <v>46200.44310185185</v>
       </c>
-      <c r="E180" s="1">
+      <c r="E185" s="1">
         <v>46200.44310185185</v>
       </c>
-      <c r="F180" s="1">
-        <v>46211.04225972222</v>
-      </c>
-      <c r="G180" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="H180" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="I180" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="J180" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="K180" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="L180" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="M180" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="N180" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="O180" s="0">
-        <v>0</v>
-      </c>
-      <c r="P180" s="0">
-        <v>1</v>
-      </c>
-      <c r="Q180" s="0">
-        <v>0</v>
-      </c>
-      <c r="R180" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="S180" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="T180" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="U180" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="V180" s="0" t="s">
+      <c r="F185" s="1">
+        <v>46212.042284027775</v>
+      </c>
+      <c r="G185" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H185" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I185" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J185" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K185" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L185" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="M185" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="N185" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="O185" s="0">
+        <v>0</v>
+      </c>
+      <c r="P185" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q185" s="0">
+        <v>0</v>
+      </c>
+      <c r="R185" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="S185" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T185" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="U185" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="V185" s="0" t="s">
         <v>30</v>
       </c>
     </row>

--- a/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
+++ b/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
@@ -1067,7 +1067,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F2" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>24</v>
@@ -1076,7 +1076,7 @@
         <v>24</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>25</v>
@@ -1096,8 +1096,8 @@
       <c r="O2" s="0">
         <v>0</v>
       </c>
-      <c r="P2" s="0" t="s">
-        <v>25</v>
+      <c r="P2" s="0">
+        <v>1</v>
       </c>
       <c r="Q2" s="0" t="s">
         <v>25</v>
@@ -1135,7 +1135,7 @@
         <v>46204.34583333333</v>
       </c>
       <c r="F3" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>46207.15827546296</v>
       </c>
       <c r="F4" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>28</v>
@@ -1215,7 +1215,7 @@
         <v>28</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K4" s="0" t="s">
         <v>25</v>
@@ -1235,8 +1235,8 @@
       <c r="P4" s="0">
         <v>0</v>
       </c>
-      <c r="Q4" s="0" t="s">
-        <v>25</v>
+      <c r="Q4" s="0">
+        <v>0</v>
       </c>
       <c r="R4" s="0" t="s">
         <v>25</v>
@@ -1271,7 +1271,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F5" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>24</v>
@@ -1280,7 +1280,7 @@
         <v>24</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>25</v>
@@ -1300,8 +1300,8 @@
       <c r="O5" s="0">
         <v>0</v>
       </c>
-      <c r="P5" s="0" t="s">
-        <v>25</v>
+      <c r="P5" s="0">
+        <v>1</v>
       </c>
       <c r="Q5" s="0" t="s">
         <v>25</v>
@@ -1339,7 +1339,7 @@
         <v>46200.30415509259</v>
       </c>
       <c r="F6" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>28</v>
@@ -1407,7 +1407,7 @@
         <v>46214.27086805556</v>
       </c>
       <c r="F7" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>28</v>
@@ -1475,7 +1475,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F8" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>24</v>
@@ -1543,7 +1543,7 @@
         <v>46211.80736111111</v>
       </c>
       <c r="F9" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>28</v>
@@ -1552,7 +1552,7 @@
         <v>28</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>25</v>
@@ -1572,8 +1572,8 @@
       <c r="O9" s="0">
         <v>0</v>
       </c>
-      <c r="P9" s="0" t="s">
-        <v>25</v>
+      <c r="P9" s="0">
+        <v>0</v>
       </c>
       <c r="Q9" s="0" t="s">
         <v>25</v>
@@ -1611,7 +1611,7 @@
         <v>46214.30170138889</v>
       </c>
       <c r="F10" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>24</v>
@@ -1679,7 +1679,7 @@
         <v>46211.689108796294</v>
       </c>
       <c r="F11" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>28</v>
@@ -1688,7 +1688,7 @@
         <v>28</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>25</v>
@@ -1708,8 +1708,8 @@
       <c r="O11" s="0">
         <v>1</v>
       </c>
-      <c r="P11" s="0" t="s">
-        <v>25</v>
+      <c r="P11" s="0">
+        <v>0</v>
       </c>
       <c r="Q11" s="0" t="s">
         <v>25</v>
@@ -1747,7 +1747,7 @@
         <v>46198.75680555555</v>
       </c>
       <c r="F12" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>24</v>
@@ -1759,7 +1759,7 @@
         <v>24</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12" s="0" t="s">
         <v>25</v>
@@ -1779,8 +1779,8 @@
       <c r="P12" s="0">
         <v>1</v>
       </c>
-      <c r="Q12" s="0" t="s">
-        <v>25</v>
+      <c r="Q12" s="0">
+        <v>0</v>
       </c>
       <c r="R12" s="0" t="s">
         <v>25</v>
@@ -1815,7 +1815,7 @@
         <v>46200.02773148148</v>
       </c>
       <c r="F13" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>28</v>
@@ -1883,7 +1883,7 @@
         <v>46200.57623842593</v>
       </c>
       <c r="F14" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>28</v>
@@ -1951,7 +1951,7 @@
         <v>46198.764027777775</v>
       </c>
       <c r="F15" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>24</v>
@@ -1963,7 +1963,7 @@
         <v>24</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K15" s="0" t="s">
         <v>25</v>
@@ -1983,8 +1983,8 @@
       <c r="P15" s="0">
         <v>1</v>
       </c>
-      <c r="Q15" s="0" t="s">
-        <v>25</v>
+      <c r="Q15" s="0">
+        <v>0</v>
       </c>
       <c r="R15" s="0" t="s">
         <v>25</v>
@@ -2019,7 +2019,7 @@
         <v>46198.18491898148</v>
       </c>
       <c r="F16" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>46203.81460648148</v>
       </c>
       <c r="F17" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G17" s="0" t="s">
         <v>45</v>
@@ -2155,7 +2155,7 @@
         <v>46201.33733796296</v>
       </c>
       <c r="F18" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>28</v>
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="R18" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="0" t="s">
         <v>25</v>
@@ -2223,7 +2223,7 @@
         <v>46203.71907407408</v>
       </c>
       <c r="F19" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G19" s="0" t="s">
         <v>28</v>
@@ -2291,7 +2291,7 @@
         <v>46195.59105324074</v>
       </c>
       <c r="F20" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G20" s="0" t="s">
         <v>24</v>
@@ -2359,7 +2359,7 @@
         <v>46201.06361111111</v>
       </c>
       <c r="F21" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G21" s="0" t="s">
         <v>28</v>
@@ -2374,7 +2374,7 @@
         <v>28</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L21" s="0" t="s">
         <v>25</v>
@@ -2394,8 +2394,8 @@
       <c r="Q21" s="0">
         <v>1</v>
       </c>
-      <c r="R21" s="0" t="s">
-        <v>25</v>
+      <c r="R21" s="0">
+        <v>0</v>
       </c>
       <c r="S21" s="0" t="s">
         <v>25</v>
@@ -2427,7 +2427,7 @@
         <v>46195.68219907407</v>
       </c>
       <c r="F22" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>24</v>
@@ -2454,7 +2454,7 @@
         <v>25</v>
       </c>
       <c r="O22" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="0" t="s">
         <v>25</v>
@@ -2495,7 +2495,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F23" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G23" s="0" t="s">
         <v>24</v>
@@ -2563,7 +2563,7 @@
         <v>46198.5140625</v>
       </c>
       <c r="F24" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>24</v>
@@ -2631,7 +2631,7 @@
         <v>46209.61792824074</v>
       </c>
       <c r="F25" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G25" s="0" t="s">
         <v>45</v>
@@ -2699,7 +2699,7 @@
         <v>46202.38591435185</v>
       </c>
       <c r="F26" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>28</v>
@@ -2714,7 +2714,7 @@
         <v>28</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L26" s="0" t="s">
         <v>25</v>
@@ -2734,8 +2734,8 @@
       <c r="Q26" s="0">
         <v>0</v>
       </c>
-      <c r="R26" s="0" t="s">
-        <v>25</v>
+      <c r="R26" s="0">
+        <v>0</v>
       </c>
       <c r="S26" s="0" t="s">
         <v>25</v>
@@ -2767,7 +2767,7 @@
         <v>46215.03915509259</v>
       </c>
       <c r="F27" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G27" s="0" t="s">
         <v>45</v>
@@ -2835,7 +2835,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F28" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>24</v>
@@ -2847,7 +2847,7 @@
         <v>24</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K28" s="0" t="s">
         <v>25</v>
@@ -2867,8 +2867,8 @@
       <c r="P28" s="0">
         <v>1</v>
       </c>
-      <c r="Q28" s="0" t="s">
-        <v>25</v>
+      <c r="Q28" s="0">
+        <v>0</v>
       </c>
       <c r="R28" s="0" t="s">
         <v>25</v>
@@ -2903,7 +2903,7 @@
         <v>46205.25707175926</v>
       </c>
       <c r="F29" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>28</v>
@@ -2971,7 +2971,7 @@
         <v>46203.77983796296</v>
       </c>
       <c r="F30" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>45</v>
@@ -3039,7 +3039,7 @@
         <v>46207.957766203705</v>
       </c>
       <c r="F31" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>45</v>
@@ -3107,7 +3107,7 @@
         <v>46204.23569444445</v>
       </c>
       <c r="F32" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>28</v>
@@ -3175,7 +3175,7 @@
         <v>46206.293020833335</v>
       </c>
       <c r="F33" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>45</v>
@@ -3243,7 +3243,7 @@
         <v>46214.75530092593</v>
       </c>
       <c r="F34" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>45</v>
@@ -3311,7 +3311,7 @@
         <v>46198.763715277775</v>
       </c>
       <c r="F35" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>24</v>
@@ -3323,7 +3323,7 @@
         <v>24</v>
       </c>
       <c r="J35" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K35" s="0" t="s">
         <v>25</v>
@@ -3343,8 +3343,8 @@
       <c r="P35" s="0">
         <v>1</v>
       </c>
-      <c r="Q35" s="0" t="s">
-        <v>25</v>
+      <c r="Q35" s="0">
+        <v>0</v>
       </c>
       <c r="R35" s="0" t="s">
         <v>25</v>
@@ -3379,7 +3379,7 @@
         <v>46205.502962962964</v>
       </c>
       <c r="F36" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>28</v>
@@ -3391,7 +3391,7 @@
         <v>28</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K36" s="0" t="s">
         <v>25</v>
@@ -3411,8 +3411,8 @@
       <c r="P36" s="0">
         <v>0</v>
       </c>
-      <c r="Q36" s="0" t="s">
-        <v>25</v>
+      <c r="Q36" s="0">
+        <v>0</v>
       </c>
       <c r="R36" s="0" t="s">
         <v>25</v>
@@ -3447,7 +3447,7 @@
         <v>46214.35975694445</v>
       </c>
       <c r="F37" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>28</v>
@@ -3474,7 +3474,7 @@
         <v>25</v>
       </c>
       <c r="O37" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" s="0" t="s">
         <v>25</v>
@@ -3515,7 +3515,7 @@
         <v>46200.67046296296</v>
       </c>
       <c r="F38" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>24</v>
@@ -3583,7 +3583,7 @@
         <v>46215.29809027778</v>
       </c>
       <c r="F39" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>28</v>
@@ -3651,7 +3651,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F40" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>24</v>
@@ -3660,7 +3660,7 @@
         <v>24</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J40" s="0" t="s">
         <v>25</v>
@@ -3680,8 +3680,8 @@
       <c r="O40" s="0">
         <v>0</v>
       </c>
-      <c r="P40" s="0" t="s">
-        <v>25</v>
+      <c r="P40" s="0">
+        <v>1</v>
       </c>
       <c r="Q40" s="0" t="s">
         <v>25</v>
@@ -3719,7 +3719,7 @@
         <v>46207.76193287037</v>
       </c>
       <c r="F41" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>24</v>
@@ -3728,7 +3728,7 @@
         <v>24</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J41" s="0" t="s">
         <v>25</v>
@@ -3748,8 +3748,8 @@
       <c r="O41" s="0">
         <v>1</v>
       </c>
-      <c r="P41" s="0" t="s">
-        <v>25</v>
+      <c r="P41" s="0">
+        <v>0</v>
       </c>
       <c r="Q41" s="0" t="s">
         <v>25</v>
@@ -3787,7 +3787,7 @@
         <v>46199.574282407404</v>
       </c>
       <c r="F42" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>28</v>
@@ -3855,7 +3855,7 @@
         <v>46198.758518518516</v>
       </c>
       <c r="F43" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>24</v>
@@ -3867,7 +3867,7 @@
         <v>24</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K43" s="0" t="s">
         <v>25</v>
@@ -3887,8 +3887,8 @@
       <c r="P43" s="0">
         <v>1</v>
       </c>
-      <c r="Q43" s="0" t="s">
-        <v>25</v>
+      <c r="Q43" s="0">
+        <v>0</v>
       </c>
       <c r="R43" s="0" t="s">
         <v>25</v>
@@ -3923,7 +3923,7 @@
         <v>46199.20893518518</v>
       </c>
       <c r="F44" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>28</v>
@@ -3991,7 +3991,7 @@
         <v>46198.76384259259</v>
       </c>
       <c r="F45" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>24</v>
@@ -4003,7 +4003,7 @@
         <v>24</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K45" s="0" t="s">
         <v>25</v>
@@ -4023,8 +4023,8 @@
       <c r="P45" s="0">
         <v>1</v>
       </c>
-      <c r="Q45" s="0" t="s">
-        <v>25</v>
+      <c r="Q45" s="0">
+        <v>0</v>
       </c>
       <c r="R45" s="0" t="s">
         <v>25</v>
@@ -4059,7 +4059,7 @@
         <v>46207.98546296296</v>
       </c>
       <c r="F46" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>28</v>
@@ -4127,7 +4127,7 @@
         <v>46198.758414351854</v>
       </c>
       <c r="F47" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>24</v>
@@ -4139,7 +4139,7 @@
         <v>24</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K47" s="0" t="s">
         <v>25</v>
@@ -4159,8 +4159,8 @@
       <c r="P47" s="0">
         <v>1</v>
       </c>
-      <c r="Q47" s="0" t="s">
-        <v>25</v>
+      <c r="Q47" s="0">
+        <v>0</v>
       </c>
       <c r="R47" s="0" t="s">
         <v>25</v>
@@ -4195,7 +4195,7 @@
         <v>46207.95777777778</v>
       </c>
       <c r="F48" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>24</v>
@@ -4263,7 +4263,7 @@
         <v>46213.479849537034</v>
       </c>
       <c r="F49" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G49" s="0" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>25</v>
       </c>
       <c r="O49" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" s="0" t="s">
         <v>25</v>
@@ -4331,7 +4331,7 @@
         <v>46213.89649305555</v>
       </c>
       <c r="F50" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>28</v>
@@ -4399,7 +4399,7 @@
         <v>46194.2578587963</v>
       </c>
       <c r="F51" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>28</v>
@@ -4435,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="R51" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" s="0" t="s">
         <v>25</v>
@@ -4467,7 +4467,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F52" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>24</v>
@@ -4535,7 +4535,7 @@
         <v>46214.741215277776</v>
       </c>
       <c r="F53" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>28</v>
@@ -4603,7 +4603,7 @@
         <v>46204.816157407404</v>
       </c>
       <c r="F54" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>24</v>
@@ -4612,7 +4612,7 @@
         <v>24</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J54" s="0" t="s">
         <v>25</v>
@@ -4632,8 +4632,8 @@
       <c r="O54" s="0">
         <v>0</v>
       </c>
-      <c r="P54" s="0" t="s">
-        <v>25</v>
+      <c r="P54" s="0">
+        <v>1</v>
       </c>
       <c r="Q54" s="0" t="s">
         <v>25</v>
@@ -4671,7 +4671,7 @@
         <v>46210.94122685185</v>
       </c>
       <c r="F55" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>28</v>
@@ -4739,7 +4739,7 @@
         <v>46211.91608796296</v>
       </c>
       <c r="F56" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>28</v>
@@ -4748,7 +4748,7 @@
         <v>28</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J56" s="0" t="s">
         <v>25</v>
@@ -4768,8 +4768,8 @@
       <c r="O56" s="0">
         <v>1</v>
       </c>
-      <c r="P56" s="0" t="s">
-        <v>25</v>
+      <c r="P56" s="0">
+        <v>0</v>
       </c>
       <c r="Q56" s="0" t="s">
         <v>25</v>
@@ -4807,7 +4807,7 @@
         <v>46211.9408912037</v>
       </c>
       <c r="F57" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G57" s="0" t="s">
         <v>28</v>
@@ -4816,7 +4816,7 @@
         <v>28</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J57" s="0" t="s">
         <v>25</v>
@@ -4836,8 +4836,8 @@
       <c r="O57" s="0">
         <v>0</v>
       </c>
-      <c r="P57" s="0" t="s">
-        <v>25</v>
+      <c r="P57" s="0">
+        <v>0</v>
       </c>
       <c r="Q57" s="0" t="s">
         <v>25</v>
@@ -4875,7 +4875,7 @@
         <v>46198.763449074075</v>
       </c>
       <c r="F58" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>24</v>
@@ -4887,7 +4887,7 @@
         <v>24</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K58" s="0" t="s">
         <v>25</v>
@@ -4907,8 +4907,8 @@
       <c r="P58" s="0">
         <v>1</v>
       </c>
-      <c r="Q58" s="0" t="s">
-        <v>25</v>
+      <c r="Q58" s="0">
+        <v>0</v>
       </c>
       <c r="R58" s="0" t="s">
         <v>25</v>
@@ -4943,7 +4943,7 @@
         <v>46198.758125</v>
       </c>
       <c r="F59" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>24</v>
@@ -4955,7 +4955,7 @@
         <v>24</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K59" s="0" t="s">
         <v>25</v>
@@ -4975,8 +4975,8 @@
       <c r="P59" s="0">
         <v>1</v>
       </c>
-      <c r="Q59" s="0" t="s">
-        <v>25</v>
+      <c r="Q59" s="0">
+        <v>0</v>
       </c>
       <c r="R59" s="0" t="s">
         <v>25</v>
@@ -5011,7 +5011,7 @@
         <v>46201.54498842593</v>
       </c>
       <c r="F60" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G60" s="0" t="s">
         <v>28</v>
@@ -5026,7 +5026,7 @@
         <v>28</v>
       </c>
       <c r="K60" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L60" s="0" t="s">
         <v>25</v>
@@ -5046,8 +5046,8 @@
       <c r="Q60" s="0">
         <v>0</v>
       </c>
-      <c r="R60" s="0" t="s">
-        <v>25</v>
+      <c r="R60" s="0">
+        <v>0</v>
       </c>
       <c r="S60" s="0" t="s">
         <v>25</v>
@@ -5079,7 +5079,7 @@
         <v>46198.76478009259</v>
       </c>
       <c r="F61" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>24</v>
@@ -5091,7 +5091,7 @@
         <v>24</v>
       </c>
       <c r="J61" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K61" s="0" t="s">
         <v>25</v>
@@ -5111,8 +5111,8 @@
       <c r="P61" s="0">
         <v>1</v>
       </c>
-      <c r="Q61" s="0" t="s">
-        <v>25</v>
+      <c r="Q61" s="0">
+        <v>0</v>
       </c>
       <c r="R61" s="0" t="s">
         <v>25</v>
@@ -5147,7 +5147,7 @@
         <v>46205.76315972222</v>
       </c>
       <c r="F62" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>28</v>
@@ -5215,7 +5215,7 @@
         <v>46204.83986111111</v>
       </c>
       <c r="F63" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>28</v>
@@ -5283,7 +5283,7 @@
         <v>46203.69975694444</v>
       </c>
       <c r="F64" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>45</v>
@@ -5351,7 +5351,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F65" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>24</v>
@@ -5360,7 +5360,7 @@
         <v>24</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J65" s="0" t="s">
         <v>25</v>
@@ -5380,8 +5380,8 @@
       <c r="O65" s="0">
         <v>0</v>
       </c>
-      <c r="P65" s="0" t="s">
-        <v>25</v>
+      <c r="P65" s="0">
+        <v>1</v>
       </c>
       <c r="Q65" s="0" t="s">
         <v>25</v>
@@ -5419,7 +5419,7 @@
         <v>46208.10663194444</v>
       </c>
       <c r="F66" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>28</v>
@@ -5487,7 +5487,7 @@
         <v>46200.854166666664</v>
       </c>
       <c r="F67" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>24</v>
@@ -5555,7 +5555,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F68" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>24</v>
@@ -5564,7 +5564,7 @@
         <v>24</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J68" s="0" t="s">
         <v>25</v>
@@ -5584,8 +5584,8 @@
       <c r="O68" s="0">
         <v>0</v>
       </c>
-      <c r="P68" s="0" t="s">
-        <v>25</v>
+      <c r="P68" s="0">
+        <v>1</v>
       </c>
       <c r="Q68" s="0" t="s">
         <v>25</v>
@@ -5623,7 +5623,7 @@
         <v>46205.07099537037</v>
       </c>
       <c r="F69" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>24</v>
@@ -5691,7 +5691,7 @@
         <v>46204.145219907405</v>
       </c>
       <c r="F70" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G70" s="0" t="s">
         <v>24</v>
@@ -5703,7 +5703,7 @@
         <v>24</v>
       </c>
       <c r="J70" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K70" s="0" t="s">
         <v>25</v>
@@ -5723,8 +5723,8 @@
       <c r="P70" s="0">
         <v>1</v>
       </c>
-      <c r="Q70" s="0" t="s">
-        <v>25</v>
+      <c r="Q70" s="0">
+        <v>0</v>
       </c>
       <c r="R70" s="0" t="s">
         <v>25</v>
@@ -5759,7 +5759,7 @@
         <v>46191.31182870371</v>
       </c>
       <c r="F71" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G71" s="0" t="s">
         <v>24</v>
@@ -5827,7 +5827,7 @@
         <v>46199.29518518518</v>
       </c>
       <c r="F72" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>46184.345671296294</v>
       </c>
       <c r="F73" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>24</v>
@@ -5904,7 +5904,7 @@
         <v>24</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J73" s="0" t="s">
         <v>25</v>
@@ -5924,8 +5924,8 @@
       <c r="O73" s="0">
         <v>1</v>
       </c>
-      <c r="P73" s="0" t="s">
-        <v>25</v>
+      <c r="P73" s="0">
+        <v>0</v>
       </c>
       <c r="Q73" s="0" t="s">
         <v>25</v>
@@ -5963,7 +5963,7 @@
         <v>46215.31277777778</v>
       </c>
       <c r="F74" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>28</v>
@@ -6031,7 +6031,7 @@
         <v>46198.758576388886</v>
       </c>
       <c r="F75" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>24</v>
@@ -6043,7 +6043,7 @@
         <v>24</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K75" s="0" t="s">
         <v>25</v>
@@ -6063,8 +6063,8 @@
       <c r="P75" s="0">
         <v>1</v>
       </c>
-      <c r="Q75" s="0" t="s">
-        <v>25</v>
+      <c r="Q75" s="0">
+        <v>0</v>
       </c>
       <c r="R75" s="0" t="s">
         <v>25</v>
@@ -6099,7 +6099,7 @@
         <v>46211.747719907406</v>
       </c>
       <c r="F76" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>24</v>
@@ -6108,7 +6108,7 @@
         <v>24</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>25</v>
@@ -6128,8 +6128,8 @@
       <c r="O76" s="0">
         <v>0</v>
       </c>
-      <c r="P76" s="0" t="s">
-        <v>25</v>
+      <c r="P76" s="0">
+        <v>1</v>
       </c>
       <c r="Q76" s="0" t="s">
         <v>25</v>
@@ -6167,7 +6167,7 @@
         <v>46196.6612962963</v>
       </c>
       <c r="F77" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>45</v>
@@ -6235,7 +6235,7 @@
         <v>46203.386967592596</v>
       </c>
       <c r="F78" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>24</v>
@@ -6303,7 +6303,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F79" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>28</v>
@@ -6371,7 +6371,7 @@
         <v>46202.30238425926</v>
       </c>
       <c r="F80" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>28</v>
@@ -6386,7 +6386,7 @@
         <v>28</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L80" s="0" t="s">
         <v>25</v>
@@ -6406,8 +6406,8 @@
       <c r="Q80" s="0">
         <v>1</v>
       </c>
-      <c r="R80" s="0" t="s">
-        <v>25</v>
+      <c r="R80" s="0">
+        <v>0</v>
       </c>
       <c r="S80" s="0" t="s">
         <v>25</v>
@@ -6439,7 +6439,7 @@
         <v>46208.76116898148</v>
       </c>
       <c r="F81" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>45</v>
@@ -6507,7 +6507,7 @@
         <v>46198.007743055554</v>
       </c>
       <c r="F82" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>24</v>
@@ -6575,7 +6575,7 @@
         <v>46204.82892361111</v>
       </c>
       <c r="F83" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>24</v>
@@ -6587,7 +6587,7 @@
         <v>24</v>
       </c>
       <c r="J83" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K83" s="0" t="s">
         <v>25</v>
@@ -6607,8 +6607,8 @@
       <c r="P83" s="0">
         <v>1</v>
       </c>
-      <c r="Q83" s="0" t="s">
-        <v>25</v>
+      <c r="Q83" s="0">
+        <v>0</v>
       </c>
       <c r="R83" s="0" t="s">
         <v>25</v>
@@ -6643,7 +6643,7 @@
         <v>46211.026354166665</v>
       </c>
       <c r="F84" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>24</v>
@@ -6673,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="P84" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" s="0" t="s">
         <v>25</v>
@@ -6711,7 +6711,7 @@
         <v>46206.49621527778</v>
       </c>
       <c r="F85" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>28</v>
       </c>
       <c r="J85" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K85" s="0" t="s">
         <v>25</v>
@@ -6743,8 +6743,8 @@
       <c r="P85" s="0">
         <v>1</v>
       </c>
-      <c r="Q85" s="0" t="s">
-        <v>25</v>
+      <c r="Q85" s="0">
+        <v>0</v>
       </c>
       <c r="R85" s="0" t="s">
         <v>25</v>
@@ -6779,7 +6779,7 @@
         <v>46194.10880787037</v>
       </c>
       <c r="F86" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>24</v>
@@ -6847,7 +6847,7 @@
         <v>46202.80762731482</v>
       </c>
       <c r="F87" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>28</v>
@@ -6915,7 +6915,7 @@
         <v>46212.191030092596</v>
       </c>
       <c r="F88" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G88" s="0" t="s">
         <v>28</v>
@@ -6924,7 +6924,7 @@
         <v>28</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J88" s="0" t="s">
         <v>25</v>
@@ -6944,8 +6944,8 @@
       <c r="O88" s="0">
         <v>1</v>
       </c>
-      <c r="P88" s="0" t="s">
-        <v>25</v>
+      <c r="P88" s="0">
+        <v>0</v>
       </c>
       <c r="Q88" s="0" t="s">
         <v>25</v>
@@ -6983,7 +6983,7 @@
         <v>46214.51880787037</v>
       </c>
       <c r="F89" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>28</v>
@@ -7051,7 +7051,7 @@
         <v>46198.053506944445</v>
       </c>
       <c r="F90" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>28</v>
@@ -7119,7 +7119,7 @@
         <v>46208.01679398148</v>
       </c>
       <c r="F91" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>28</v>
@@ -7187,7 +7187,7 @@
         <v>46199.4216087963</v>
       </c>
       <c r="F92" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>45</v>
@@ -7255,7 +7255,7 @@
         <v>46203.398622685185</v>
       </c>
       <c r="F93" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>24</v>
@@ -7267,7 +7267,7 @@
         <v>24</v>
       </c>
       <c r="J93" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K93" s="0" t="s">
         <v>25</v>
@@ -7287,8 +7287,8 @@
       <c r="P93" s="0">
         <v>1</v>
       </c>
-      <c r="Q93" s="0" t="s">
-        <v>25</v>
+      <c r="Q93" s="0">
+        <v>0</v>
       </c>
       <c r="R93" s="0" t="s">
         <v>25</v>
@@ -7323,7 +7323,7 @@
         <v>46204.071388888886</v>
       </c>
       <c r="F94" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>24</v>
@@ -7391,7 +7391,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F95" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>24</v>
@@ -7400,7 +7400,7 @@
         <v>24</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J95" s="0" t="s">
         <v>25</v>
@@ -7420,8 +7420,8 @@
       <c r="O95" s="0">
         <v>0</v>
       </c>
-      <c r="P95" s="0" t="s">
-        <v>25</v>
+      <c r="P95" s="0">
+        <v>1</v>
       </c>
       <c r="Q95" s="0" t="s">
         <v>25</v>
@@ -7459,7 +7459,7 @@
         <v>46207.340208333335</v>
       </c>
       <c r="F96" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>28</v>
@@ -7471,7 +7471,7 @@
         <v>28</v>
       </c>
       <c r="J96" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K96" s="0" t="s">
         <v>25</v>
@@ -7491,8 +7491,8 @@
       <c r="P96" s="0">
         <v>1</v>
       </c>
-      <c r="Q96" s="0" t="s">
-        <v>25</v>
+      <c r="Q96" s="0">
+        <v>0</v>
       </c>
       <c r="R96" s="0" t="s">
         <v>25</v>
@@ -7527,7 +7527,7 @@
         <v>46203.22761574074</v>
       </c>
       <c r="F97" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>28</v>
@@ -7539,7 +7539,7 @@
         <v>28</v>
       </c>
       <c r="J97" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K97" s="0" t="s">
         <v>25</v>
@@ -7559,8 +7559,8 @@
       <c r="P97" s="0">
         <v>0</v>
       </c>
-      <c r="Q97" s="0" t="s">
-        <v>25</v>
+      <c r="Q97" s="0">
+        <v>0</v>
       </c>
       <c r="R97" s="0" t="s">
         <v>25</v>
@@ -7595,7 +7595,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F98" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G98" s="0" t="s">
         <v>28</v>
@@ -7663,7 +7663,7 @@
         <v>46209.27856481481</v>
       </c>
       <c r="F99" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>28</v>
@@ -7731,7 +7731,7 @@
         <v>46203.241944444446</v>
       </c>
       <c r="F100" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>28</v>
@@ -7799,7 +7799,7 @@
         <v>46200.90429398148</v>
       </c>
       <c r="F101" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>24</v>
@@ -7829,7 +7829,7 @@
         <v>1</v>
       </c>
       <c r="P101" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="0" t="s">
         <v>25</v>
@@ -7867,7 +7867,7 @@
         <v>46201.17297453704</v>
       </c>
       <c r="F102" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>28</v>
@@ -7935,7 +7935,7 @@
         <v>46197.398356481484</v>
       </c>
       <c r="F103" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>24</v>
@@ -8003,7 +8003,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F104" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>24</v>
@@ -8015,7 +8015,7 @@
         <v>24</v>
       </c>
       <c r="J104" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K104" s="0" t="s">
         <v>25</v>
@@ -8035,8 +8035,8 @@
       <c r="P104" s="0">
         <v>1</v>
       </c>
-      <c r="Q104" s="0" t="s">
-        <v>25</v>
+      <c r="Q104" s="0">
+        <v>0</v>
       </c>
       <c r="R104" s="0" t="s">
         <v>25</v>
@@ -8071,7 +8071,7 @@
         <v>46204.81618055556</v>
       </c>
       <c r="F105" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>24</v>
@@ -8080,7 +8080,7 @@
         <v>24</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J105" s="0" t="s">
         <v>25</v>
@@ -8100,8 +8100,8 @@
       <c r="O105" s="0">
         <v>0</v>
       </c>
-      <c r="P105" s="0" t="s">
-        <v>25</v>
+      <c r="P105" s="0">
+        <v>1</v>
       </c>
       <c r="Q105" s="0" t="s">
         <v>25</v>
@@ -8139,7 +8139,7 @@
         <v>46184.345671296294</v>
       </c>
       <c r="F106" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>24</v>
@@ -8148,7 +8148,7 @@
         <v>24</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J106" s="0" t="s">
         <v>25</v>
@@ -8168,8 +8168,8 @@
       <c r="O106" s="0">
         <v>1</v>
       </c>
-      <c r="P106" s="0" t="s">
-        <v>25</v>
+      <c r="P106" s="0">
+        <v>0</v>
       </c>
       <c r="Q106" s="0" t="s">
         <v>25</v>
@@ -8207,7 +8207,7 @@
         <v>46198.76695601852</v>
       </c>
       <c r="F107" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>24</v>
@@ -8219,7 +8219,7 @@
         <v>24</v>
       </c>
       <c r="J107" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K107" s="0" t="s">
         <v>25</v>
@@ -8239,8 +8239,8 @@
       <c r="P107" s="0">
         <v>1</v>
       </c>
-      <c r="Q107" s="0" t="s">
-        <v>25</v>
+      <c r="Q107" s="0">
+        <v>0</v>
       </c>
       <c r="R107" s="0" t="s">
         <v>25</v>
@@ -8275,7 +8275,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F108" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>45</v>
@@ -8287,7 +8287,7 @@
         <v>45</v>
       </c>
       <c r="J108" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K108" s="0" t="s">
         <v>25</v>
@@ -8307,8 +8307,8 @@
       <c r="P108" s="0">
         <v>1</v>
       </c>
-      <c r="Q108" s="0" t="s">
-        <v>25</v>
+      <c r="Q108" s="0">
+        <v>0</v>
       </c>
       <c r="R108" s="0" t="s">
         <v>25</v>
@@ -8343,7 +8343,7 @@
         <v>46207.38381944445</v>
       </c>
       <c r="F109" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>28</v>
@@ -8355,7 +8355,7 @@
         <v>28</v>
       </c>
       <c r="J109" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K109" s="0" t="s">
         <v>25</v>
@@ -8375,8 +8375,8 @@
       <c r="P109" s="0">
         <v>1</v>
       </c>
-      <c r="Q109" s="0" t="s">
-        <v>25</v>
+      <c r="Q109" s="0">
+        <v>0</v>
       </c>
       <c r="R109" s="0" t="s">
         <v>25</v>
@@ -8411,7 +8411,7 @@
         <v>46198.764710648145</v>
       </c>
       <c r="F110" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>24</v>
@@ -8423,7 +8423,7 @@
         <v>24</v>
       </c>
       <c r="J110" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K110" s="0" t="s">
         <v>25</v>
@@ -8443,8 +8443,8 @@
       <c r="P110" s="0">
         <v>1</v>
       </c>
-      <c r="Q110" s="0" t="s">
-        <v>25</v>
+      <c r="Q110" s="0">
+        <v>0</v>
       </c>
       <c r="R110" s="0" t="s">
         <v>25</v>
@@ -8479,7 +8479,7 @@
         <v>46208.60445601852</v>
       </c>
       <c r="F111" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>28</v>
@@ -8547,7 +8547,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F112" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>45</v>
@@ -8559,7 +8559,7 @@
         <v>45</v>
       </c>
       <c r="J112" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K112" s="0" t="s">
         <v>25</v>
@@ -8579,8 +8579,8 @@
       <c r="P112" s="0">
         <v>1</v>
       </c>
-      <c r="Q112" s="0" t="s">
-        <v>25</v>
+      <c r="Q112" s="0">
+        <v>0</v>
       </c>
       <c r="R112" s="0" t="s">
         <v>25</v>
@@ -8615,7 +8615,7 @@
         <v>46198.7566087963</v>
       </c>
       <c r="F113" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>24</v>
@@ -8627,7 +8627,7 @@
         <v>24</v>
       </c>
       <c r="J113" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K113" s="0" t="s">
         <v>25</v>
@@ -8647,8 +8647,8 @@
       <c r="P113" s="0">
         <v>1</v>
       </c>
-      <c r="Q113" s="0" t="s">
-        <v>25</v>
+      <c r="Q113" s="0">
+        <v>0</v>
       </c>
       <c r="R113" s="0" t="s">
         <v>25</v>
@@ -8683,7 +8683,7 @@
         <v>46204.591203703705</v>
       </c>
       <c r="F114" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>28</v>
@@ -8692,7 +8692,7 @@
         <v>28</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J114" s="0" t="s">
         <v>25</v>
@@ -8712,8 +8712,8 @@
       <c r="O114" s="0">
         <v>0</v>
       </c>
-      <c r="P114" s="0" t="s">
-        <v>25</v>
+      <c r="P114" s="0">
+        <v>0</v>
       </c>
       <c r="Q114" s="0" t="s">
         <v>25</v>
@@ -8751,7 +8751,7 @@
         <v>46203.38690972222</v>
       </c>
       <c r="F115" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>24</v>
@@ -8819,7 +8819,7 @@
         <v>46199.954201388886</v>
       </c>
       <c r="F116" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>28</v>
@@ -8852,7 +8852,7 @@
         <v>1</v>
       </c>
       <c r="Q116" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="0" t="s">
         <v>25</v>
@@ -8887,7 +8887,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F117" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>45</v>
@@ -8899,7 +8899,7 @@
         <v>45</v>
       </c>
       <c r="J117" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K117" s="0" t="s">
         <v>25</v>
@@ -8919,8 +8919,8 @@
       <c r="P117" s="0">
         <v>1</v>
       </c>
-      <c r="Q117" s="0" t="s">
-        <v>25</v>
+      <c r="Q117" s="0">
+        <v>0</v>
       </c>
       <c r="R117" s="0" t="s">
         <v>25</v>
@@ -8955,7 +8955,7 @@
         <v>46193.45674768519</v>
       </c>
       <c r="F118" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>24</v>
@@ -9023,7 +9023,7 @@
         <v>46211.339479166665</v>
       </c>
       <c r="F119" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>24</v>
@@ -9091,7 +9091,7 @@
         <v>46184.344409722224</v>
       </c>
       <c r="F120" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>24</v>
@@ -9100,7 +9100,7 @@
         <v>24</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J120" s="0" t="s">
         <v>25</v>
@@ -9120,8 +9120,8 @@
       <c r="O120" s="0">
         <v>1</v>
       </c>
-      <c r="P120" s="0" t="s">
-        <v>25</v>
+      <c r="P120" s="0">
+        <v>0</v>
       </c>
       <c r="Q120" s="0" t="s">
         <v>25</v>
@@ -9159,7 +9159,7 @@
         <v>46196.43208333333</v>
       </c>
       <c r="F121" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>28</v>
@@ -9227,7 +9227,7 @@
         <v>46204.591203703705</v>
       </c>
       <c r="F122" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>28</v>
@@ -9236,7 +9236,7 @@
         <v>28</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J122" s="0" t="s">
         <v>25</v>
@@ -9256,8 +9256,8 @@
       <c r="O122" s="0">
         <v>0</v>
       </c>
-      <c r="P122" s="0" t="s">
-        <v>25</v>
+      <c r="P122" s="0">
+        <v>0</v>
       </c>
       <c r="Q122" s="0" t="s">
         <v>25</v>
@@ -9295,7 +9295,7 @@
         <v>46212.38707175926</v>
       </c>
       <c r="F123" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>28</v>
@@ -9363,7 +9363,7 @@
         <v>46205.85377314815</v>
       </c>
       <c r="F124" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>24</v>
@@ -9375,7 +9375,7 @@
         <v>24</v>
       </c>
       <c r="J124" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K124" s="0" t="s">
         <v>25</v>
@@ -9395,8 +9395,8 @@
       <c r="P124" s="0">
         <v>1</v>
       </c>
-      <c r="Q124" s="0" t="s">
-        <v>25</v>
+      <c r="Q124" s="0">
+        <v>0</v>
       </c>
       <c r="R124" s="0" t="s">
         <v>25</v>
@@ -9431,7 +9431,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F125" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>24</v>
@@ -9440,7 +9440,7 @@
         <v>24</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J125" s="0" t="s">
         <v>25</v>
@@ -9460,8 +9460,8 @@
       <c r="O125" s="0">
         <v>0</v>
       </c>
-      <c r="P125" s="0" t="s">
-        <v>25</v>
+      <c r="P125" s="0">
+        <v>1</v>
       </c>
       <c r="Q125" s="0" t="s">
         <v>25</v>
@@ -9499,7 +9499,7 @@
         <v>46194.496782407405</v>
       </c>
       <c r="F126" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>45</v>
@@ -9535,7 +9535,7 @@
         <v>1</v>
       </c>
       <c r="R126" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S126" s="0" t="s">
         <v>25</v>
@@ -9567,7 +9567,7 @@
         <v>46206.041817129626</v>
       </c>
       <c r="F127" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>28</v>
@@ -9635,7 +9635,7 @@
         <v>46211.74564814815</v>
       </c>
       <c r="F128" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>24</v>
@@ -9644,7 +9644,7 @@
         <v>24</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J128" s="0" t="s">
         <v>25</v>
@@ -9664,8 +9664,8 @@
       <c r="O128" s="0">
         <v>0</v>
       </c>
-      <c r="P128" s="0" t="s">
-        <v>25</v>
+      <c r="P128" s="0">
+        <v>1</v>
       </c>
       <c r="Q128" s="0" t="s">
         <v>25</v>
@@ -9703,7 +9703,7 @@
         <v>46198.76357638889</v>
       </c>
       <c r="F129" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>24</v>
@@ -9715,7 +9715,7 @@
         <v>24</v>
       </c>
       <c r="J129" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K129" s="0" t="s">
         <v>25</v>
@@ -9735,8 +9735,8 @@
       <c r="P129" s="0">
         <v>1</v>
       </c>
-      <c r="Q129" s="0" t="s">
-        <v>25</v>
+      <c r="Q129" s="0">
+        <v>0</v>
       </c>
       <c r="R129" s="0" t="s">
         <v>25</v>
@@ -9771,7 +9771,7 @@
         <v>46214.41127314815</v>
       </c>
       <c r="F130" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>28</v>
@@ -9839,7 +9839,7 @@
         <v>46210.39944444445</v>
       </c>
       <c r="F131" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>24</v>
@@ -9907,7 +9907,7 @@
         <v>46203.900046296294</v>
       </c>
       <c r="F132" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>45</v>
@@ -9919,7 +9919,7 @@
         <v>45</v>
       </c>
       <c r="J132" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K132" s="0" t="s">
         <v>25</v>
@@ -9939,8 +9939,8 @@
       <c r="P132" s="0">
         <v>1</v>
       </c>
-      <c r="Q132" s="0" t="s">
-        <v>25</v>
+      <c r="Q132" s="0">
+        <v>0</v>
       </c>
       <c r="R132" s="0" t="s">
         <v>25</v>
@@ -9975,7 +9975,7 @@
         <v>46198.75818287037</v>
       </c>
       <c r="F133" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>24</v>
@@ -9987,7 +9987,7 @@
         <v>24</v>
       </c>
       <c r="J133" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K133" s="0" t="s">
         <v>25</v>
@@ -10007,8 +10007,8 @@
       <c r="P133" s="0">
         <v>1</v>
       </c>
-      <c r="Q133" s="0" t="s">
-        <v>25</v>
+      <c r="Q133" s="0">
+        <v>0</v>
       </c>
       <c r="R133" s="0" t="s">
         <v>25</v>
@@ -10043,7 +10043,7 @@
         <v>46199.24039351852</v>
       </c>
       <c r="F134" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>28</v>
@@ -10111,7 +10111,7 @@
         <v>46207.7878125</v>
       </c>
       <c r="F135" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>28</v>
@@ -10179,7 +10179,7 @@
         <v>46200.88856481481</v>
       </c>
       <c r="F136" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>45</v>
@@ -10247,7 +10247,7 @@
         <v>46207.091145833336</v>
       </c>
       <c r="F137" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>28</v>
@@ -10259,7 +10259,7 @@
         <v>28</v>
       </c>
       <c r="J137" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K137" s="0" t="s">
         <v>25</v>
@@ -10279,8 +10279,8 @@
       <c r="P137" s="0">
         <v>1</v>
       </c>
-      <c r="Q137" s="0" t="s">
-        <v>25</v>
+      <c r="Q137" s="0">
+        <v>0</v>
       </c>
       <c r="R137" s="0" t="s">
         <v>25</v>
@@ -10315,7 +10315,7 @@
         <v>46209.81253472222</v>
       </c>
       <c r="F138" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>24</v>
@@ -10383,7 +10383,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F139" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>24</v>
@@ -10392,7 +10392,7 @@
         <v>24</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J139" s="0" t="s">
         <v>25</v>
@@ -10412,8 +10412,8 @@
       <c r="O139" s="0">
         <v>0</v>
       </c>
-      <c r="P139" s="0" t="s">
-        <v>25</v>
+      <c r="P139" s="0">
+        <v>1</v>
       </c>
       <c r="Q139" s="0" t="s">
         <v>25</v>
@@ -10451,7 +10451,7 @@
         <v>46208.76133101852</v>
       </c>
       <c r="F140" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>24</v>
@@ -10519,7 +10519,7 @@
         <v>46210.11184027778</v>
       </c>
       <c r="F141" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G141" s="0" t="s">
         <v>24</v>
@@ -10528,7 +10528,7 @@
         <v>24</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J141" s="0" t="s">
         <v>25</v>
@@ -10548,8 +10548,8 @@
       <c r="O141" s="0">
         <v>1</v>
       </c>
-      <c r="P141" s="0" t="s">
-        <v>25</v>
+      <c r="P141" s="0">
+        <v>0</v>
       </c>
       <c r="Q141" s="0" t="s">
         <v>25</v>
@@ -10587,7 +10587,7 @@
         <v>46202.603946759256</v>
       </c>
       <c r="F142" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>24</v>
@@ -10655,7 +10655,7 @@
         <v>46208.28020833333</v>
       </c>
       <c r="F143" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>45</v>
@@ -10723,7 +10723,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F144" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>24</v>
@@ -10735,7 +10735,7 @@
         <v>24</v>
       </c>
       <c r="J144" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K144" s="0" t="s">
         <v>25</v>
@@ -10755,8 +10755,8 @@
       <c r="P144" s="0">
         <v>1</v>
       </c>
-      <c r="Q144" s="0" t="s">
-        <v>25</v>
+      <c r="Q144" s="0">
+        <v>0</v>
       </c>
       <c r="R144" s="0" t="s">
         <v>25</v>
@@ -10791,7 +10791,7 @@
         <v>46187.9200462963</v>
       </c>
       <c r="F145" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>24</v>
@@ -10859,7 +10859,7 @@
         <v>46204.36974537037</v>
       </c>
       <c r="F146" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>28</v>
@@ -10927,7 +10927,7 @@
         <v>46201.332870370374</v>
       </c>
       <c r="F147" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>24</v>
@@ -10995,7 +10995,7 @@
         <v>46197.03113425926</v>
       </c>
       <c r="F148" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>24</v>
@@ -11063,7 +11063,7 @@
         <v>46212.285219907404</v>
       </c>
       <c r="F149" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>28</v>
@@ -11131,7 +11131,7 @@
         <v>46200.98619212963</v>
       </c>
       <c r="F150" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>28</v>
@@ -11146,7 +11146,7 @@
         <v>28</v>
       </c>
       <c r="K150" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L150" s="0" t="s">
         <v>25</v>
@@ -11166,8 +11166,8 @@
       <c r="Q150" s="0">
         <v>0</v>
       </c>
-      <c r="R150" s="0" t="s">
-        <v>25</v>
+      <c r="R150" s="0">
+        <v>0</v>
       </c>
       <c r="S150" s="0" t="s">
         <v>25</v>
@@ -11199,7 +11199,7 @@
         <v>46212.06758101852</v>
       </c>
       <c r="F151" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>28</v>
@@ -11208,7 +11208,7 @@
         <v>28</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J151" s="0" t="s">
         <v>25</v>
@@ -11228,8 +11228,8 @@
       <c r="O151" s="0">
         <v>0</v>
       </c>
-      <c r="P151" s="0" t="s">
-        <v>25</v>
+      <c r="P151" s="0">
+        <v>0</v>
       </c>
       <c r="Q151" s="0" t="s">
         <v>25</v>
@@ -11267,7 +11267,7 @@
         <v>46207.18613425926</v>
       </c>
       <c r="F152" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>28</v>
@@ -11335,7 +11335,7 @@
         <v>46210.8569212963</v>
       </c>
       <c r="F153" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>28</v>
@@ -11365,7 +11365,7 @@
         <v>1</v>
       </c>
       <c r="P153" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q153" s="0" t="s">
         <v>25</v>
@@ -11403,7 +11403,7 @@
         <v>46198.763344907406</v>
       </c>
       <c r="F154" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>24</v>
@@ -11415,7 +11415,7 @@
         <v>24</v>
       </c>
       <c r="J154" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K154" s="0" t="s">
         <v>25</v>
@@ -11435,8 +11435,8 @@
       <c r="P154" s="0">
         <v>1</v>
       </c>
-      <c r="Q154" s="0" t="s">
-        <v>25</v>
+      <c r="Q154" s="0">
+        <v>0</v>
       </c>
       <c r="R154" s="0" t="s">
         <v>25</v>
@@ -11471,7 +11471,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F155" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>24</v>
@@ -11480,7 +11480,7 @@
         <v>24</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J155" s="0" t="s">
         <v>25</v>
@@ -11500,8 +11500,8 @@
       <c r="O155" s="0">
         <v>0</v>
       </c>
-      <c r="P155" s="0" t="s">
-        <v>25</v>
+      <c r="P155" s="0">
+        <v>1</v>
       </c>
       <c r="Q155" s="0" t="s">
         <v>25</v>
@@ -11539,7 +11539,7 @@
         <v>46198.86886574074</v>
       </c>
       <c r="F156" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>28</v>
@@ -11607,7 +11607,7 @@
         <v>46198.76422453704</v>
       </c>
       <c r="F157" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G157" s="0" t="s">
         <v>24</v>
@@ -11619,7 +11619,7 @@
         <v>24</v>
       </c>
       <c r="J157" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K157" s="0" t="s">
         <v>25</v>
@@ -11639,8 +11639,8 @@
       <c r="P157" s="0">
         <v>1</v>
       </c>
-      <c r="Q157" s="0" t="s">
-        <v>25</v>
+      <c r="Q157" s="0">
+        <v>0</v>
       </c>
       <c r="R157" s="0" t="s">
         <v>25</v>
@@ -11675,7 +11675,7 @@
         <v>46206.29314814815</v>
       </c>
       <c r="F158" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G158" s="0" t="s">
         <v>45</v>
@@ -11705,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="P158" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q158" s="0" t="s">
         <v>25</v>
@@ -11743,7 +11743,7 @@
         <v>46206.39832175926</v>
       </c>
       <c r="F159" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>28</v>
@@ -11755,7 +11755,7 @@
         <v>28</v>
       </c>
       <c r="J159" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K159" s="0" t="s">
         <v>25</v>
@@ -11775,8 +11775,8 @@
       <c r="P159" s="0">
         <v>0</v>
       </c>
-      <c r="Q159" s="0" t="s">
-        <v>25</v>
+      <c r="Q159" s="0">
+        <v>0</v>
       </c>
       <c r="R159" s="0" t="s">
         <v>25</v>
@@ -11811,7 +11811,7 @@
         <v>46201.828206018516</v>
       </c>
       <c r="F160" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>28</v>
       </c>
       <c r="K160" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L160" s="0" t="s">
         <v>25</v>
@@ -11846,8 +11846,8 @@
       <c r="Q160" s="0">
         <v>1</v>
       </c>
-      <c r="R160" s="0" t="s">
-        <v>25</v>
+      <c r="R160" s="0">
+        <v>0</v>
       </c>
       <c r="S160" s="0" t="s">
         <v>25</v>
@@ -11879,7 +11879,7 @@
         <v>46198.13486111111</v>
       </c>
       <c r="F161" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>24</v>
@@ -11947,7 +11947,7 @@
         <v>46184.34568287037</v>
       </c>
       <c r="F162" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>24</v>
@@ -11956,7 +11956,7 @@
         <v>24</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J162" s="0" t="s">
         <v>25</v>
@@ -11976,8 +11976,8 @@
       <c r="O162" s="0">
         <v>1</v>
       </c>
-      <c r="P162" s="0" t="s">
-        <v>25</v>
+      <c r="P162" s="0">
+        <v>0</v>
       </c>
       <c r="Q162" s="0" t="s">
         <v>25</v>
@@ -12015,7 +12015,7 @@
         <v>46198.487546296295</v>
       </c>
       <c r="F163" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>28</v>
@@ -12083,7 +12083,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F164" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>24</v>
@@ -12092,7 +12092,7 @@
         <v>24</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J164" s="0" t="s">
         <v>25</v>
@@ -12112,8 +12112,8 @@
       <c r="O164" s="0">
         <v>0</v>
       </c>
-      <c r="P164" s="0" t="s">
-        <v>25</v>
+      <c r="P164" s="0">
+        <v>1</v>
       </c>
       <c r="Q164" s="0" t="s">
         <v>25</v>
@@ -12151,7 +12151,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F165" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>24</v>
@@ -12160,7 +12160,7 @@
         <v>24</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J165" s="0" t="s">
         <v>25</v>
@@ -12180,8 +12180,8 @@
       <c r="O165" s="0">
         <v>0</v>
       </c>
-      <c r="P165" s="0" t="s">
-        <v>25</v>
+      <c r="P165" s="0">
+        <v>1</v>
       </c>
       <c r="Q165" s="0" t="s">
         <v>25</v>
@@ -12219,7 +12219,7 @@
         <v>46199.37</v>
       </c>
       <c r="F166" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>28</v>
@@ -12287,7 +12287,7 @@
         <v>46200.507418981484</v>
       </c>
       <c r="F167" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>28</v>
@@ -12323,7 +12323,7 @@
         <v>1</v>
       </c>
       <c r="R167" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S167" s="0" t="s">
         <v>25</v>
@@ -12355,7 +12355,7 @@
         <v>46208.7612037037</v>
       </c>
       <c r="F168" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>45</v>
@@ -12385,7 +12385,7 @@
         <v>1</v>
       </c>
       <c r="P168" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q168" s="0" t="s">
         <v>25</v>
@@ -12423,7 +12423,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F169" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>24</v>
@@ -12432,7 +12432,7 @@
         <v>24</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J169" s="0" t="s">
         <v>25</v>
@@ -12452,8 +12452,8 @@
       <c r="O169" s="0">
         <v>0</v>
       </c>
-      <c r="P169" s="0" t="s">
-        <v>25</v>
+      <c r="P169" s="0">
+        <v>1</v>
       </c>
       <c r="Q169" s="0" t="s">
         <v>25</v>
@@ -12491,7 +12491,7 @@
         <v>46206.616875</v>
       </c>
       <c r="F170" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>28</v>
@@ -12559,7 +12559,7 @@
         <v>46206.85376157407</v>
       </c>
       <c r="F171" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>24</v>
@@ -12627,7 +12627,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F172" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>24</v>
@@ -12636,7 +12636,7 @@
         <v>24</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J172" s="0" t="s">
         <v>25</v>
@@ -12656,8 +12656,8 @@
       <c r="O172" s="0">
         <v>0</v>
       </c>
-      <c r="P172" s="0" t="s">
-        <v>25</v>
+      <c r="P172" s="0">
+        <v>1</v>
       </c>
       <c r="Q172" s="0" t="s">
         <v>25</v>
@@ -12695,7 +12695,7 @@
         <v>46215.346342592595</v>
       </c>
       <c r="F173" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>45</v>
@@ -12763,7 +12763,7 @@
         <v>46208.34142361111</v>
       </c>
       <c r="F174" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>45</v>
@@ -12831,7 +12831,7 @@
         <v>46184.34611111111</v>
       </c>
       <c r="F175" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>24</v>
@@ -12840,7 +12840,7 @@
         <v>24</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J175" s="0" t="s">
         <v>25</v>
@@ -12860,8 +12860,8 @@
       <c r="O175" s="0">
         <v>1</v>
       </c>
-      <c r="P175" s="0" t="s">
-        <v>25</v>
+      <c r="P175" s="0">
+        <v>0</v>
       </c>
       <c r="Q175" s="0" t="s">
         <v>25</v>
@@ -12899,7 +12899,7 @@
         <v>46207.44116898148</v>
       </c>
       <c r="F176" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>45</v>
@@ -12967,7 +12967,7 @@
         <v>46213.12200231481</v>
       </c>
       <c r="F177" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>28</v>
@@ -13035,7 +13035,7 @@
         <v>46211.78650462963</v>
       </c>
       <c r="F178" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>28</v>
@@ -13103,7 +13103,7 @@
         <v>46205.74003472222</v>
       </c>
       <c r="F179" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>45</v>
@@ -13115,7 +13115,7 @@
         <v>45</v>
       </c>
       <c r="J179" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K179" s="0" t="s">
         <v>25</v>
@@ -13135,8 +13135,8 @@
       <c r="P179" s="0">
         <v>0</v>
       </c>
-      <c r="Q179" s="0" t="s">
-        <v>25</v>
+      <c r="Q179" s="0">
+        <v>0</v>
       </c>
       <c r="R179" s="0" t="s">
         <v>25</v>
@@ -13171,7 +13171,7 @@
         <v>46214.6358912037</v>
       </c>
       <c r="F180" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G180" s="0" t="s">
         <v>28</v>
@@ -13239,7 +13239,7 @@
         <v>46199.95371527778</v>
       </c>
       <c r="F181" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>45</v>
@@ -13307,7 +13307,7 @@
         <v>46205.07099537037</v>
       </c>
       <c r="F182" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>24</v>
@@ -13375,7 +13375,7 @@
         <v>46215.09512731482</v>
       </c>
       <c r="F183" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>28</v>
@@ -13443,7 +13443,7 @@
         <v>46203.39921296296</v>
       </c>
       <c r="F184" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>24</v>
@@ -13455,7 +13455,7 @@
         <v>24</v>
       </c>
       <c r="J184" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K184" s="0" t="s">
         <v>25</v>
@@ -13475,8 +13475,8 @@
       <c r="P184" s="0">
         <v>1</v>
       </c>
-      <c r="Q184" s="0" t="s">
-        <v>25</v>
+      <c r="Q184" s="0">
+        <v>0</v>
       </c>
       <c r="R184" s="0" t="s">
         <v>25</v>
@@ -13511,7 +13511,7 @@
         <v>46206.91523148148</v>
       </c>
       <c r="F185" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>24</v>
@@ -13541,7 +13541,7 @@
         <v>1</v>
       </c>
       <c r="P185" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q185" s="0" t="s">
         <v>25</v>
@@ -13579,7 +13579,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F186" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G186" s="0" t="s">
         <v>24</v>
@@ -13591,7 +13591,7 @@
         <v>24</v>
       </c>
       <c r="J186" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K186" s="0" t="s">
         <v>25</v>
@@ -13611,8 +13611,8 @@
       <c r="P186" s="0">
         <v>1</v>
       </c>
-      <c r="Q186" s="0" t="s">
-        <v>25</v>
+      <c r="Q186" s="0">
+        <v>0</v>
       </c>
       <c r="R186" s="0" t="s">
         <v>25</v>
@@ -13647,7 +13647,7 @@
         <v>46212.73332175926</v>
       </c>
       <c r="F187" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>28</v>
@@ -13715,7 +13715,7 @@
         <v>46199.395949074074</v>
       </c>
       <c r="F188" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>28</v>
@@ -13783,7 +13783,7 @@
         <v>46184.34570601852</v>
       </c>
       <c r="F189" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>24</v>
@@ -13792,7 +13792,7 @@
         <v>24</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J189" s="0" t="s">
         <v>25</v>
@@ -13812,8 +13812,8 @@
       <c r="O189" s="0">
         <v>1</v>
       </c>
-      <c r="P189" s="0" t="s">
-        <v>25</v>
+      <c r="P189" s="0">
+        <v>0</v>
       </c>
       <c r="Q189" s="0" t="s">
         <v>25</v>
@@ -13851,7 +13851,7 @@
         <v>46198.756527777776</v>
       </c>
       <c r="F190" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>24</v>
@@ -13863,7 +13863,7 @@
         <v>24</v>
       </c>
       <c r="J190" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K190" s="0" t="s">
         <v>25</v>
@@ -13883,8 +13883,8 @@
       <c r="P190" s="0">
         <v>1</v>
       </c>
-      <c r="Q190" s="0" t="s">
-        <v>25</v>
+      <c r="Q190" s="0">
+        <v>0</v>
       </c>
       <c r="R190" s="0" t="s">
         <v>25</v>
@@ -13919,7 +13919,7 @@
         <v>46208.76128472222</v>
       </c>
       <c r="F191" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>24</v>
@@ -13987,7 +13987,7 @@
         <v>46198.76427083334</v>
       </c>
       <c r="F192" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>24</v>
@@ -13999,7 +13999,7 @@
         <v>24</v>
       </c>
       <c r="J192" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K192" s="0" t="s">
         <v>25</v>
@@ -14019,8 +14019,8 @@
       <c r="P192" s="0">
         <v>1</v>
       </c>
-      <c r="Q192" s="0" t="s">
-        <v>25</v>
+      <c r="Q192" s="0">
+        <v>0</v>
       </c>
       <c r="R192" s="0" t="s">
         <v>25</v>
@@ -14055,7 +14055,7 @@
         <v>46196.08101851852</v>
       </c>
       <c r="F193" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>24</v>
@@ -14123,7 +14123,7 @@
         <v>46207.28523148148</v>
       </c>
       <c r="F194" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G194" s="0" t="s">
         <v>24</v>
@@ -14191,7 +14191,7 @@
         <v>46196.788564814815</v>
       </c>
       <c r="F195" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G195" s="0" t="s">
         <v>24</v>
@@ -14203,7 +14203,7 @@
         <v>24</v>
       </c>
       <c r="J195" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K195" s="0" t="s">
         <v>25</v>
@@ -14223,8 +14223,8 @@
       <c r="P195" s="0">
         <v>1</v>
       </c>
-      <c r="Q195" s="0" t="s">
-        <v>25</v>
+      <c r="Q195" s="0">
+        <v>0</v>
       </c>
       <c r="R195" s="0" t="s">
         <v>25</v>
@@ -14259,7 +14259,7 @@
         <v>46200.45096064815</v>
       </c>
       <c r="F196" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G196" s="0" t="s">
         <v>45</v>
@@ -14327,7 +14327,7 @@
         <v>46213.44936342593</v>
       </c>
       <c r="F197" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G197" s="0" t="s">
         <v>28</v>
@@ -14395,7 +14395,7 @@
         <v>46207.18237268519</v>
       </c>
       <c r="F198" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G198" s="0" t="s">
         <v>24</v>
@@ -14407,7 +14407,7 @@
         <v>24</v>
       </c>
       <c r="J198" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K198" s="0" t="s">
         <v>25</v>
@@ -14427,8 +14427,8 @@
       <c r="P198" s="0">
         <v>1</v>
       </c>
-      <c r="Q198" s="0" t="s">
-        <v>25</v>
+      <c r="Q198" s="0">
+        <v>0</v>
       </c>
       <c r="R198" s="0" t="s">
         <v>25</v>
@@ -14463,7 +14463,7 @@
         <v>46198.89733796296</v>
       </c>
       <c r="F199" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>28</v>
@@ -14531,7 +14531,7 @@
         <v>46213.282858796294</v>
       </c>
       <c r="F200" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>28</v>
@@ -14599,7 +14599,7 @@
         <v>46205.19603009259</v>
       </c>
       <c r="F201" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>28</v>
@@ -14667,7 +14667,7 @@
         <v>46196.08101851852</v>
       </c>
       <c r="F202" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>24</v>
@@ -14735,7 +14735,7 @@
         <v>46196.88885416667</v>
       </c>
       <c r="F203" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>24</v>
@@ -14750,7 +14750,7 @@
         <v>24</v>
       </c>
       <c r="K203" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L203" s="0" t="s">
         <v>25</v>
@@ -14770,8 +14770,8 @@
       <c r="Q203" s="0">
         <v>1</v>
       </c>
-      <c r="R203" s="0" t="s">
-        <v>25</v>
+      <c r="R203" s="0">
+        <v>0</v>
       </c>
       <c r="S203" s="0" t="s">
         <v>25</v>
@@ -14803,7 +14803,7 @@
         <v>46199.89765046296</v>
       </c>
       <c r="F204" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>28</v>
@@ -14818,7 +14818,7 @@
         <v>28</v>
       </c>
       <c r="K204" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L204" s="0" t="s">
         <v>25</v>
@@ -14838,8 +14838,8 @@
       <c r="Q204" s="0">
         <v>1</v>
       </c>
-      <c r="R204" s="0" t="s">
-        <v>25</v>
+      <c r="R204" s="0">
+        <v>0</v>
       </c>
       <c r="S204" s="0" t="s">
         <v>25</v>
@@ -14871,7 +14871,7 @@
         <v>46203.38673611111</v>
       </c>
       <c r="F205" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>24</v>
@@ -14939,7 +14939,7 @@
         <v>46214.55940972222</v>
       </c>
       <c r="F206" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>28</v>
@@ -15007,7 +15007,7 @@
         <v>46215.391805555555</v>
       </c>
       <c r="F207" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G207" s="0" t="s">
         <v>45</v>
@@ -15075,7 +15075,7 @@
         <v>46208.49730324074</v>
       </c>
       <c r="F208" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G208" s="0" t="s">
         <v>45</v>
@@ -15143,7 +15143,7 @@
         <v>46205.35525462963</v>
       </c>
       <c r="F209" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G209" s="0" t="s">
         <v>28</v>
@@ -15211,7 +15211,7 @@
         <v>46200.595925925925</v>
       </c>
       <c r="F210" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>24</v>
@@ -15279,7 +15279,7 @@
         <v>46198.36408564815</v>
       </c>
       <c r="F211" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>28</v>
@@ -15347,7 +15347,7 @@
         <v>46214.184386574074</v>
       </c>
       <c r="F212" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>28</v>
@@ -15415,7 +15415,7 @@
         <v>46208.95462962963</v>
       </c>
       <c r="F213" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>45</v>
@@ -15483,7 +15483,7 @@
         <v>46209.34474537037</v>
       </c>
       <c r="F214" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>28</v>
@@ -15551,7 +15551,7 @@
         <v>46203.6659375</v>
       </c>
       <c r="F215" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>24</v>
@@ -15563,7 +15563,7 @@
         <v>24</v>
       </c>
       <c r="J215" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K215" s="0" t="s">
         <v>25</v>
@@ -15583,8 +15583,8 @@
       <c r="P215" s="0">
         <v>1</v>
       </c>
-      <c r="Q215" s="0" t="s">
-        <v>25</v>
+      <c r="Q215" s="0">
+        <v>0</v>
       </c>
       <c r="R215" s="0" t="s">
         <v>25</v>
@@ -15619,7 +15619,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F216" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>24</v>
@@ -15628,7 +15628,7 @@
         <v>24</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J216" s="0" t="s">
         <v>25</v>
@@ -15648,8 +15648,8 @@
       <c r="O216" s="0">
         <v>0</v>
       </c>
-      <c r="P216" s="0" t="s">
-        <v>25</v>
+      <c r="P216" s="0">
+        <v>1</v>
       </c>
       <c r="Q216" s="0" t="s">
         <v>25</v>
@@ -15687,7 +15687,7 @@
         <v>46200.84137731481</v>
       </c>
       <c r="F217" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>28</v>
@@ -15755,7 +15755,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F218" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>24</v>
@@ -15764,7 +15764,7 @@
         <v>24</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J218" s="0" t="s">
         <v>25</v>
@@ -15784,8 +15784,8 @@
       <c r="O218" s="0">
         <v>0</v>
       </c>
-      <c r="P218" s="0" t="s">
-        <v>25</v>
+      <c r="P218" s="0">
+        <v>1</v>
       </c>
       <c r="Q218" s="0" t="s">
         <v>25</v>
@@ -15823,7 +15823,7 @@
         <v>46207.322233796294</v>
       </c>
       <c r="F219" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>28</v>
@@ -15835,7 +15835,7 @@
         <v>28</v>
       </c>
       <c r="J219" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K219" s="0" t="s">
         <v>25</v>
@@ -15855,8 +15855,8 @@
       <c r="P219" s="0">
         <v>1</v>
       </c>
-      <c r="Q219" s="0" t="s">
-        <v>25</v>
+      <c r="Q219" s="0">
+        <v>0</v>
       </c>
       <c r="R219" s="0" t="s">
         <v>25</v>
@@ -15891,7 +15891,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F220" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G220" s="0" t="s">
         <v>24</v>
@@ -15903,7 +15903,7 @@
         <v>24</v>
       </c>
       <c r="J220" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K220" s="0" t="s">
         <v>25</v>
@@ -15923,8 +15923,8 @@
       <c r="P220" s="0">
         <v>1</v>
       </c>
-      <c r="Q220" s="0" t="s">
-        <v>25</v>
+      <c r="Q220" s="0">
+        <v>0</v>
       </c>
       <c r="R220" s="0" t="s">
         <v>25</v>
@@ -15959,7 +15959,7 @@
         <v>46208.80619212963</v>
       </c>
       <c r="F221" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>28</v>
@@ -16027,7 +16027,7 @@
         <v>46207.24060185185</v>
       </c>
       <c r="F222" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>24</v>
@@ -16039,7 +16039,7 @@
         <v>24</v>
       </c>
       <c r="J222" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K222" s="0" t="s">
         <v>25</v>
@@ -16059,8 +16059,8 @@
       <c r="P222" s="0">
         <v>1</v>
       </c>
-      <c r="Q222" s="0" t="s">
-        <v>25</v>
+      <c r="Q222" s="0">
+        <v>0</v>
       </c>
       <c r="R222" s="0" t="s">
         <v>25</v>
@@ -16095,7 +16095,7 @@
         <v>46213.36528935185</v>
       </c>
       <c r="F223" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>45</v>
@@ -16163,7 +16163,7 @@
         <v>46202.50537037037</v>
       </c>
       <c r="F224" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>28</v>
@@ -16231,7 +16231,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F225" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>45</v>
@@ -16299,7 +16299,7 @@
         <v>46200.24690972222</v>
       </c>
       <c r="F226" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>45</v>
@@ -16335,7 +16335,7 @@
         <v>1</v>
       </c>
       <c r="R226" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S226" s="0" t="s">
         <v>25</v>
@@ -16367,7 +16367,7 @@
         <v>46200.39493055556</v>
       </c>
       <c r="F227" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>24</v>
@@ -16435,7 +16435,7 @@
         <v>46200.50178240741</v>
       </c>
       <c r="F228" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G228" s="0" t="s">
         <v>28</v>
@@ -16503,7 +16503,7 @@
         <v>46201.81197916667</v>
       </c>
       <c r="F229" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>28</v>
       </c>
       <c r="K229" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L229" s="0" t="s">
         <v>25</v>
@@ -16538,8 +16538,8 @@
       <c r="Q229" s="0">
         <v>0</v>
       </c>
-      <c r="R229" s="0" t="s">
-        <v>25</v>
+      <c r="R229" s="0">
+        <v>0</v>
       </c>
       <c r="S229" s="0" t="s">
         <v>25</v>
@@ -16571,7 +16571,7 @@
         <v>46196.87100694444</v>
       </c>
       <c r="F230" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>28</v>
@@ -16639,7 +16639,7 @@
         <v>46211.287673611114</v>
       </c>
       <c r="F231" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G231" s="0" t="s">
         <v>28</v>
@@ -16707,7 +16707,7 @@
         <v>46213.33634259259</v>
       </c>
       <c r="F232" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>28</v>
@@ -16775,7 +16775,7 @@
         <v>46203.38674768519</v>
       </c>
       <c r="F233" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>24</v>
@@ -16843,7 +16843,7 @@
         <v>46199.38827546296</v>
       </c>
       <c r="F234" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G234" s="0" t="s">
         <v>24</v>
@@ -16858,7 +16858,7 @@
         <v>24</v>
       </c>
       <c r="K234" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L234" s="0" t="s">
         <v>25</v>
@@ -16878,8 +16878,8 @@
       <c r="Q234" s="0">
         <v>1</v>
       </c>
-      <c r="R234" s="0" t="s">
-        <v>25</v>
+      <c r="R234" s="0">
+        <v>0</v>
       </c>
       <c r="S234" s="0" t="s">
         <v>25</v>
@@ -16911,7 +16911,7 @@
         <v>46211.747569444444</v>
       </c>
       <c r="F235" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G235" s="0" t="s">
         <v>24</v>
@@ -16920,7 +16920,7 @@
         <v>24</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J235" s="0" t="s">
         <v>25</v>
@@ -16940,8 +16940,8 @@
       <c r="O235" s="0">
         <v>0</v>
       </c>
-      <c r="P235" s="0" t="s">
-        <v>25</v>
+      <c r="P235" s="0">
+        <v>1</v>
       </c>
       <c r="Q235" s="0" t="s">
         <v>25</v>
@@ -16979,7 +16979,7 @@
         <v>46214.036574074074</v>
       </c>
       <c r="F236" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>24</v>
@@ -17047,7 +17047,7 @@
         <v>46198.75832175926</v>
       </c>
       <c r="F237" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>24</v>
@@ -17059,7 +17059,7 @@
         <v>24</v>
       </c>
       <c r="J237" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K237" s="0" t="s">
         <v>25</v>
@@ -17079,8 +17079,8 @@
       <c r="P237" s="0">
         <v>1</v>
       </c>
-      <c r="Q237" s="0" t="s">
-        <v>25</v>
+      <c r="Q237" s="0">
+        <v>0</v>
       </c>
       <c r="R237" s="0" t="s">
         <v>25</v>
@@ -17115,7 +17115,7 @@
         <v>46213.1378125</v>
       </c>
       <c r="F238" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G238" s="0" t="s">
         <v>28</v>
@@ -17183,7 +17183,7 @@
         <v>46200.08666666667</v>
       </c>
       <c r="F239" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G239" s="0" t="s">
         <v>28</v>
@@ -17198,7 +17198,7 @@
         <v>28</v>
       </c>
       <c r="K239" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L239" s="0" t="s">
         <v>25</v>
@@ -17218,8 +17218,8 @@
       <c r="Q239" s="0">
         <v>0</v>
       </c>
-      <c r="R239" s="0" t="s">
-        <v>25</v>
+      <c r="R239" s="0">
+        <v>0</v>
       </c>
       <c r="S239" s="0" t="s">
         <v>25</v>
@@ -17251,7 +17251,7 @@
         <v>46191.20039351852</v>
       </c>
       <c r="F240" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>24</v>
@@ -17319,7 +17319,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F241" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G241" s="0" t="s">
         <v>24</v>
@@ -17331,7 +17331,7 @@
         <v>24</v>
       </c>
       <c r="J241" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K241" s="0" t="s">
         <v>25</v>
@@ -17351,8 +17351,8 @@
       <c r="P241" s="0">
         <v>1</v>
       </c>
-      <c r="Q241" s="0" t="s">
-        <v>25</v>
+      <c r="Q241" s="0">
+        <v>0</v>
       </c>
       <c r="R241" s="0" t="s">
         <v>25</v>
@@ -17387,7 +17387,7 @@
         <v>46197.6375462963</v>
       </c>
       <c r="F242" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G242" s="0" t="s">
         <v>24</v>
@@ -17455,7 +17455,7 @@
         <v>46197.037523148145</v>
       </c>
       <c r="F243" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>24</v>
@@ -17523,7 +17523,7 @@
         <v>46198.31060185185</v>
       </c>
       <c r="F244" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G244" s="0" t="s">
         <v>28</v>
@@ -17591,7 +17591,7 @@
         <v>46209.31466435185</v>
       </c>
       <c r="F245" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>28</v>
@@ -17659,7 +17659,7 @@
         <v>46206.72038194445</v>
       </c>
       <c r="F246" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G246" s="0" t="s">
         <v>28</v>
@@ -17671,7 +17671,7 @@
         <v>28</v>
       </c>
       <c r="J246" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K246" s="0" t="s">
         <v>25</v>
@@ -17691,8 +17691,8 @@
       <c r="P246" s="0">
         <v>1</v>
       </c>
-      <c r="Q246" s="0" t="s">
-        <v>25</v>
+      <c r="Q246" s="0">
+        <v>0</v>
       </c>
       <c r="R246" s="0" t="s">
         <v>25</v>
@@ -17727,7 +17727,7 @@
         <v>46197.46810185185</v>
       </c>
       <c r="F247" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>24</v>
@@ -17763,7 +17763,7 @@
         <v>1</v>
       </c>
       <c r="R247" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S247" s="0" t="s">
         <v>25</v>
@@ -17795,7 +17795,7 @@
         <v>46202.349328703705</v>
       </c>
       <c r="F248" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G248" s="0" t="s">
         <v>28</v>
@@ -17810,7 +17810,7 @@
         <v>28</v>
       </c>
       <c r="K248" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L248" s="0" t="s">
         <v>25</v>
@@ -17830,8 +17830,8 @@
       <c r="Q248" s="0">
         <v>1</v>
       </c>
-      <c r="R248" s="0" t="s">
-        <v>25</v>
+      <c r="R248" s="0">
+        <v>0</v>
       </c>
       <c r="S248" s="0" t="s">
         <v>25</v>
@@ -17863,7 +17863,7 @@
         <v>46198.75665509259</v>
       </c>
       <c r="F249" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G249" s="0" t="s">
         <v>24</v>
@@ -17875,7 +17875,7 @@
         <v>24</v>
       </c>
       <c r="J249" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K249" s="0" t="s">
         <v>25</v>
@@ -17895,8 +17895,8 @@
       <c r="P249" s="0">
         <v>1</v>
       </c>
-      <c r="Q249" s="0" t="s">
-        <v>25</v>
+      <c r="Q249" s="0">
+        <v>0</v>
       </c>
       <c r="R249" s="0" t="s">
         <v>25</v>
@@ -17931,7 +17931,7 @@
         <v>46205.784363425926</v>
       </c>
       <c r="F250" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G250" s="0" t="s">
         <v>45</v>
@@ -17943,7 +17943,7 @@
         <v>45</v>
       </c>
       <c r="J250" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K250" s="0" t="s">
         <v>25</v>
@@ -17963,8 +17963,8 @@
       <c r="P250" s="0">
         <v>1</v>
       </c>
-      <c r="Q250" s="0" t="s">
-        <v>25</v>
+      <c r="Q250" s="0">
+        <v>0</v>
       </c>
       <c r="R250" s="0" t="s">
         <v>25</v>
@@ -17999,7 +17999,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F251" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G251" s="0" t="s">
         <v>24</v>
@@ -18008,7 +18008,7 @@
         <v>24</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J251" s="0" t="s">
         <v>25</v>
@@ -18028,8 +18028,8 @@
       <c r="O251" s="0">
         <v>0</v>
       </c>
-      <c r="P251" s="0" t="s">
-        <v>25</v>
+      <c r="P251" s="0">
+        <v>1</v>
       </c>
       <c r="Q251" s="0" t="s">
         <v>25</v>
@@ -18067,7 +18067,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F252" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>24</v>
@@ -18076,7 +18076,7 @@
         <v>24</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J252" s="0" t="s">
         <v>25</v>
@@ -18096,8 +18096,8 @@
       <c r="O252" s="0">
         <v>0</v>
       </c>
-      <c r="P252" s="0" t="s">
-        <v>25</v>
+      <c r="P252" s="0">
+        <v>1</v>
       </c>
       <c r="Q252" s="0" t="s">
         <v>25</v>
@@ -18135,7 +18135,7 @@
         <v>46198.75827546296</v>
       </c>
       <c r="F253" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>24</v>
@@ -18147,7 +18147,7 @@
         <v>24</v>
       </c>
       <c r="J253" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K253" s="0" t="s">
         <v>25</v>
@@ -18167,8 +18167,8 @@
       <c r="P253" s="0">
         <v>1</v>
       </c>
-      <c r="Q253" s="0" t="s">
-        <v>25</v>
+      <c r="Q253" s="0">
+        <v>0</v>
       </c>
       <c r="R253" s="0" t="s">
         <v>25</v>
@@ -18203,7 +18203,7 @@
         <v>46203.80048611111</v>
       </c>
       <c r="F254" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G254" s="0" t="s">
         <v>45</v>
@@ -18271,7 +18271,7 @@
         <v>46207.377118055556</v>
       </c>
       <c r="F255" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G255" s="0" t="s">
         <v>28</v>
@@ -18283,7 +18283,7 @@
         <v>28</v>
       </c>
       <c r="J255" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K255" s="0" t="s">
         <v>25</v>
@@ -18303,8 +18303,8 @@
       <c r="P255" s="0">
         <v>0</v>
       </c>
-      <c r="Q255" s="0" t="s">
-        <v>25</v>
+      <c r="Q255" s="0">
+        <v>0</v>
       </c>
       <c r="R255" s="0" t="s">
         <v>25</v>
@@ -18339,7 +18339,7 @@
         <v>46198.76320601852</v>
       </c>
       <c r="F256" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>24</v>
@@ -18351,7 +18351,7 @@
         <v>24</v>
       </c>
       <c r="J256" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K256" s="0" t="s">
         <v>25</v>
@@ -18371,8 +18371,8 @@
       <c r="P256" s="0">
         <v>1</v>
       </c>
-      <c r="Q256" s="0" t="s">
-        <v>25</v>
+      <c r="Q256" s="0">
+        <v>0</v>
       </c>
       <c r="R256" s="0" t="s">
         <v>25</v>
@@ -18407,7 +18407,7 @@
         <v>46209.364849537036</v>
       </c>
       <c r="F257" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>45</v>
@@ -18475,7 +18475,7 @@
         <v>46198.76327546296</v>
       </c>
       <c r="F258" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>24</v>
@@ -18487,7 +18487,7 @@
         <v>24</v>
       </c>
       <c r="J258" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K258" s="0" t="s">
         <v>25</v>
@@ -18507,8 +18507,8 @@
       <c r="P258" s="0">
         <v>1</v>
       </c>
-      <c r="Q258" s="0" t="s">
-        <v>25</v>
+      <c r="Q258" s="0">
+        <v>0</v>
       </c>
       <c r="R258" s="0" t="s">
         <v>25</v>
@@ -18543,7 +18543,7 @@
         <v>46197.041238425925</v>
       </c>
       <c r="F259" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>24</v>
@@ -18611,7 +18611,7 @@
         <v>46212.017488425925</v>
       </c>
       <c r="F260" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>45</v>
@@ -18679,7 +18679,7 @@
         <v>46204.81549768519</v>
       </c>
       <c r="F261" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>24</v>
@@ -18688,7 +18688,7 @@
         <v>24</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J261" s="0" t="s">
         <v>25</v>
@@ -18708,8 +18708,8 @@
       <c r="O261" s="0">
         <v>0</v>
       </c>
-      <c r="P261" s="0" t="s">
-        <v>25</v>
+      <c r="P261" s="0">
+        <v>1</v>
       </c>
       <c r="Q261" s="0" t="s">
         <v>25</v>
@@ -18747,7 +18747,7 @@
         <v>46200.44310185185</v>
       </c>
       <c r="F262" s="1">
-        <v>46216.04230405093</v>
+        <v>46217.042329282405</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>24</v>

--- a/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
+++ b/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
@@ -1151,7 +1151,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F2" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>46204.34583333333</v>
       </c>
       <c r="F3" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>28</v>
@@ -1287,7 +1287,7 @@
         <v>46207.15827546296</v>
       </c>
       <c r="F4" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>28</v>
@@ -1355,7 +1355,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F5" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>24</v>
@@ -1423,7 +1423,7 @@
         <v>46200.30415509259</v>
       </c>
       <c r="F6" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>28</v>
@@ -1491,7 +1491,7 @@
         <v>46214.27086805556</v>
       </c>
       <c r="F7" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>28</v>
@@ -1500,7 +1500,7 @@
         <v>28</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>25</v>
@@ -1520,8 +1520,8 @@
       <c r="O7" s="0">
         <v>0</v>
       </c>
-      <c r="P7" s="0" t="s">
-        <v>25</v>
+      <c r="P7" s="0">
+        <v>0</v>
       </c>
       <c r="Q7" s="0" t="s">
         <v>25</v>
@@ -1559,7 +1559,7 @@
         <v>46216.91679398148</v>
       </c>
       <c r="F8" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>28</v>
@@ -1627,7 +1627,7 @@
         <v>46217.789305555554</v>
       </c>
       <c r="F9" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>36</v>
@@ -1695,7 +1695,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F10" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>24</v>
@@ -1763,7 +1763,7 @@
         <v>46211.80736111111</v>
       </c>
       <c r="F11" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>28</v>
@@ -1831,7 +1831,7 @@
         <v>46214.30170138889</v>
       </c>
       <c r="F12" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>24</v>
@@ -1899,7 +1899,7 @@
         <v>46211.689108796294</v>
       </c>
       <c r="F13" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>28</v>
@@ -1967,7 +1967,7 @@
         <v>46198.75680555555</v>
       </c>
       <c r="F14" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>24</v>
@@ -2035,7 +2035,7 @@
         <v>46200.02773148148</v>
       </c>
       <c r="F15" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>28</v>
@@ -2103,7 +2103,7 @@
         <v>46216.87899305556</v>
       </c>
       <c r="F16" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>28</v>
@@ -2171,7 +2171,7 @@
         <v>46200.57623842593</v>
       </c>
       <c r="F17" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G17" s="0" t="s">
         <v>28</v>
@@ -2239,7 +2239,7 @@
         <v>46198.764027777775</v>
       </c>
       <c r="F18" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>24</v>
@@ -2307,7 +2307,7 @@
         <v>46198.18491898148</v>
       </c>
       <c r="F19" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G19" s="0" t="s">
         <v>28</v>
@@ -2375,7 +2375,7 @@
         <v>46203.81460648148</v>
       </c>
       <c r="F20" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G20" s="0" t="s">
         <v>36</v>
@@ -2443,7 +2443,7 @@
         <v>46201.33733796296</v>
       </c>
       <c r="F21" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G21" s="0" t="s">
         <v>28</v>
@@ -2511,7 +2511,7 @@
         <v>46203.71907407408</v>
       </c>
       <c r="F22" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>28</v>
@@ -2579,7 +2579,7 @@
         <v>46195.59105324074</v>
       </c>
       <c r="F23" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G23" s="0" t="s">
         <v>24</v>
@@ -2647,7 +2647,7 @@
         <v>46201.06361111111</v>
       </c>
       <c r="F24" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>28</v>
@@ -2715,7 +2715,7 @@
         <v>46195.68219907407</v>
       </c>
       <c r="F25" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G25" s="0" t="s">
         <v>24</v>
@@ -2724,7 +2724,7 @@
         <v>24</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>25</v>
@@ -2744,8 +2744,8 @@
       <c r="O25" s="0">
         <v>1</v>
       </c>
-      <c r="P25" s="0" t="s">
-        <v>25</v>
+      <c r="P25" s="0">
+        <v>0</v>
       </c>
       <c r="Q25" s="0" t="s">
         <v>25</v>
@@ -2783,7 +2783,7 @@
         <v>46216.18634259259</v>
       </c>
       <c r="F26" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>28</v>
@@ -2851,7 +2851,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F27" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G27" s="0" t="s">
         <v>24</v>
@@ -2866,7 +2866,7 @@
         <v>24</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L27" s="0" t="s">
         <v>25</v>
@@ -2886,8 +2886,8 @@
       <c r="Q27" s="0">
         <v>1</v>
       </c>
-      <c r="R27" s="0" t="s">
-        <v>25</v>
+      <c r="R27" s="0">
+        <v>0</v>
       </c>
       <c r="S27" s="0" t="s">
         <v>25</v>
@@ -2919,7 +2919,7 @@
         <v>46198.5140625</v>
       </c>
       <c r="F28" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>24</v>
@@ -2955,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="R28" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" s="0" t="s">
         <v>25</v>
@@ -2987,7 +2987,7 @@
         <v>46209.61792824074</v>
       </c>
       <c r="F29" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>36</v>
@@ -2999,7 +2999,7 @@
         <v>36</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K29" s="0" t="s">
         <v>25</v>
@@ -3019,8 +3019,8 @@
       <c r="P29" s="0">
         <v>1</v>
       </c>
-      <c r="Q29" s="0" t="s">
-        <v>25</v>
+      <c r="Q29" s="0">
+        <v>0</v>
       </c>
       <c r="R29" s="0" t="s">
         <v>25</v>
@@ -3055,7 +3055,7 @@
         <v>46202.38591435185</v>
       </c>
       <c r="F30" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>28</v>
@@ -3123,7 +3123,7 @@
         <v>46215.03915509259</v>
       </c>
       <c r="F31" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>36</v>
@@ -3132,7 +3132,7 @@
         <v>36</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>25</v>
@@ -3152,8 +3152,8 @@
       <c r="O31" s="0">
         <v>1</v>
       </c>
-      <c r="P31" s="0" t="s">
-        <v>25</v>
+      <c r="P31" s="0">
+        <v>0</v>
       </c>
       <c r="Q31" s="0" t="s">
         <v>25</v>
@@ -3191,7 +3191,7 @@
         <v>46217.397997685184</v>
       </c>
       <c r="F32" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>24</v>
@@ -3259,7 +3259,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F33" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>24</v>
@@ -3327,7 +3327,7 @@
         <v>46205.25707175926</v>
       </c>
       <c r="F34" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>28</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L34" s="0" t="s">
         <v>25</v>
@@ -3362,8 +3362,8 @@
       <c r="Q34" s="0">
         <v>0</v>
       </c>
-      <c r="R34" s="0" t="s">
-        <v>25</v>
+      <c r="R34" s="0">
+        <v>0</v>
       </c>
       <c r="S34" s="0" t="s">
         <v>25</v>
@@ -3395,7 +3395,7 @@
         <v>46203.77983796296</v>
       </c>
       <c r="F35" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>36</v>
@@ -3404,7 +3404,7 @@
         <v>36</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>25</v>
@@ -3424,8 +3424,8 @@
       <c r="O35" s="0">
         <v>1</v>
       </c>
-      <c r="P35" s="0" t="s">
-        <v>25</v>
+      <c r="P35" s="0">
+        <v>0</v>
       </c>
       <c r="Q35" s="0" t="s">
         <v>25</v>
@@ -3463,7 +3463,7 @@
         <v>46207.957766203705</v>
       </c>
       <c r="F36" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>36</v>
@@ -3531,7 +3531,7 @@
         <v>46204.23569444445</v>
       </c>
       <c r="F37" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>28</v>
@@ -3599,7 +3599,7 @@
         <v>46206.293020833335</v>
       </c>
       <c r="F38" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>36</v>
@@ -3632,7 +3632,7 @@
         <v>1</v>
       </c>
       <c r="Q38" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="0" t="s">
         <v>25</v>
@@ -3667,7 +3667,7 @@
         <v>46214.75530092593</v>
       </c>
       <c r="F39" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>36</v>
@@ -3676,7 +3676,7 @@
         <v>36</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J39" s="0" t="s">
         <v>25</v>
@@ -3696,8 +3696,8 @@
       <c r="O39" s="0">
         <v>0</v>
       </c>
-      <c r="P39" s="0" t="s">
-        <v>25</v>
+      <c r="P39" s="0">
+        <v>0</v>
       </c>
       <c r="Q39" s="0" t="s">
         <v>25</v>
@@ -3735,7 +3735,7 @@
         <v>46198.763715277775</v>
       </c>
       <c r="F40" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>24</v>
@@ -3803,7 +3803,7 @@
         <v>46205.502962962964</v>
       </c>
       <c r="F41" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>28</v>
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="0" t="s">
         <v>25</v>
@@ -3871,7 +3871,7 @@
         <v>46214.35975694445</v>
       </c>
       <c r="F42" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>28</v>
@@ -3939,7 +3939,7 @@
         <v>46200.67046296296</v>
       </c>
       <c r="F43" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>24</v>
@@ -3954,7 +3954,7 @@
         <v>24</v>
       </c>
       <c r="K43" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L43" s="0" t="s">
         <v>25</v>
@@ -3974,8 +3974,8 @@
       <c r="Q43" s="0">
         <v>0</v>
       </c>
-      <c r="R43" s="0" t="s">
-        <v>25</v>
+      <c r="R43" s="0">
+        <v>0</v>
       </c>
       <c r="S43" s="0" t="s">
         <v>25</v>
@@ -4007,7 +4007,7 @@
         <v>46215.29809027778</v>
       </c>
       <c r="F44" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>28</v>
@@ -4016,7 +4016,7 @@
         <v>28</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J44" s="0" t="s">
         <v>25</v>
@@ -4036,8 +4036,8 @@
       <c r="O44" s="0">
         <v>0</v>
       </c>
-      <c r="P44" s="0" t="s">
-        <v>25</v>
+      <c r="P44" s="0">
+        <v>0</v>
       </c>
       <c r="Q44" s="0" t="s">
         <v>25</v>
@@ -4075,7 +4075,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F45" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>24</v>
@@ -4143,7 +4143,7 @@
         <v>46217.729409722226</v>
       </c>
       <c r="F46" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>24</v>
@@ -4211,7 +4211,7 @@
         <v>46207.76193287037</v>
       </c>
       <c r="F47" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>24</v>
@@ -4279,7 +4279,7 @@
         <v>46199.574282407404</v>
       </c>
       <c r="F48" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>28</v>
@@ -4347,7 +4347,7 @@
         <v>46198.758518518516</v>
       </c>
       <c r="F49" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G49" s="0" t="s">
         <v>24</v>
@@ -4415,7 +4415,7 @@
         <v>46199.20893518518</v>
       </c>
       <c r="F50" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>28</v>
@@ -4483,7 +4483,7 @@
         <v>46198.76384259259</v>
       </c>
       <c r="F51" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>24</v>
@@ -4551,7 +4551,7 @@
         <v>46207.98546296296</v>
       </c>
       <c r="F52" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>1</v>
       </c>
       <c r="Q52" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="0" t="s">
         <v>25</v>
@@ -4619,7 +4619,7 @@
         <v>46198.758414351854</v>
       </c>
       <c r="F53" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>24</v>
@@ -4687,7 +4687,7 @@
         <v>46207.95777777778</v>
       </c>
       <c r="F54" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>24</v>
@@ -4755,7 +4755,7 @@
         <v>46217.77034722222</v>
       </c>
       <c r="F55" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>24</v>
@@ -4823,7 +4823,7 @@
         <v>46213.479849537034</v>
       </c>
       <c r="F56" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>28</v>
@@ -4832,7 +4832,7 @@
         <v>28</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J56" s="0" t="s">
         <v>25</v>
@@ -4852,8 +4852,8 @@
       <c r="O56" s="0">
         <v>1</v>
       </c>
-      <c r="P56" s="0" t="s">
-        <v>25</v>
+      <c r="P56" s="0">
+        <v>0</v>
       </c>
       <c r="Q56" s="0" t="s">
         <v>25</v>
@@ -4891,7 +4891,7 @@
         <v>46213.89649305555</v>
       </c>
       <c r="F57" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G57" s="0" t="s">
         <v>28</v>
@@ -4900,7 +4900,7 @@
         <v>28</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J57" s="0" t="s">
         <v>25</v>
@@ -4920,8 +4920,8 @@
       <c r="O57" s="0">
         <v>0</v>
       </c>
-      <c r="P57" s="0" t="s">
-        <v>25</v>
+      <c r="P57" s="0">
+        <v>0</v>
       </c>
       <c r="Q57" s="0" t="s">
         <v>25</v>
@@ -4959,7 +4959,7 @@
         <v>46194.2578587963</v>
       </c>
       <c r="F58" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>28</v>
@@ -5027,7 +5027,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F59" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>24</v>
@@ -5042,7 +5042,7 @@
         <v>24</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L59" s="0" t="s">
         <v>25</v>
@@ -5062,8 +5062,8 @@
       <c r="Q59" s="0">
         <v>1</v>
       </c>
-      <c r="R59" s="0" t="s">
-        <v>25</v>
+      <c r="R59" s="0">
+        <v>0</v>
       </c>
       <c r="S59" s="0" t="s">
         <v>25</v>
@@ -5095,7 +5095,7 @@
         <v>46214.741215277776</v>
       </c>
       <c r="F60" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G60" s="0" t="s">
         <v>28</v>
@@ -5104,7 +5104,7 @@
         <v>28</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J60" s="0" t="s">
         <v>25</v>
@@ -5124,8 +5124,8 @@
       <c r="O60" s="0">
         <v>0</v>
       </c>
-      <c r="P60" s="0" t="s">
-        <v>25</v>
+      <c r="P60" s="0">
+        <v>0</v>
       </c>
       <c r="Q60" s="0" t="s">
         <v>25</v>
@@ -5163,7 +5163,7 @@
         <v>46204.816157407404</v>
       </c>
       <c r="F61" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>24</v>
@@ -5231,7 +5231,7 @@
         <v>46210.94122685185</v>
       </c>
       <c r="F62" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>28</v>
@@ -5261,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="P62" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="0" t="s">
         <v>25</v>
@@ -5299,7 +5299,7 @@
         <v>46211.91608796296</v>
       </c>
       <c r="F63" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>28</v>
@@ -5367,7 +5367,7 @@
         <v>46211.9408912037</v>
       </c>
       <c r="F64" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>46198.763449074075</v>
       </c>
       <c r="F65" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>24</v>
@@ -5503,7 +5503,7 @@
         <v>46198.758125</v>
       </c>
       <c r="F66" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>24</v>
@@ -5571,7 +5571,7 @@
         <v>46201.54498842593</v>
       </c>
       <c r="F67" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>28</v>
@@ -5639,7 +5639,7 @@
         <v>46198.76478009259</v>
       </c>
       <c r="F68" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>24</v>
@@ -5707,7 +5707,7 @@
         <v>46205.76315972222</v>
       </c>
       <c r="F69" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>28</v>
@@ -5775,7 +5775,7 @@
         <v>46204.83986111111</v>
       </c>
       <c r="F70" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G70" s="0" t="s">
         <v>28</v>
@@ -5790,7 +5790,7 @@
         <v>28</v>
       </c>
       <c r="K70" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L70" s="0" t="s">
         <v>25</v>
@@ -5810,8 +5810,8 @@
       <c r="Q70" s="0">
         <v>0</v>
       </c>
-      <c r="R70" s="0" t="s">
-        <v>25</v>
+      <c r="R70" s="0">
+        <v>0</v>
       </c>
       <c r="S70" s="0" t="s">
         <v>25</v>
@@ -5843,7 +5843,7 @@
         <v>46203.69975694444</v>
       </c>
       <c r="F71" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G71" s="0" t="s">
         <v>36</v>
@@ -5911,7 +5911,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F72" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>24</v>
@@ -5979,7 +5979,7 @@
         <v>46208.10663194444</v>
       </c>
       <c r="F73" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>28</v>
@@ -6047,7 +6047,7 @@
         <v>46200.854166666664</v>
       </c>
       <c r="F74" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>24</v>
@@ -6115,7 +6115,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F75" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>24</v>
@@ -6183,7 +6183,7 @@
         <v>46205.07099537037</v>
       </c>
       <c r="F76" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>24</v>
@@ -6195,7 +6195,7 @@
         <v>24</v>
       </c>
       <c r="J76" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K76" s="0" t="s">
         <v>25</v>
@@ -6215,8 +6215,8 @@
       <c r="P76" s="0">
         <v>1</v>
       </c>
-      <c r="Q76" s="0" t="s">
-        <v>25</v>
+      <c r="Q76" s="0">
+        <v>0</v>
       </c>
       <c r="R76" s="0" t="s">
         <v>25</v>
@@ -6251,7 +6251,7 @@
         <v>46204.145219907405</v>
       </c>
       <c r="F77" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>24</v>
@@ -6319,7 +6319,7 @@
         <v>46191.31182870371</v>
       </c>
       <c r="F78" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>24</v>
@@ -6387,7 +6387,7 @@
         <v>46199.29518518518</v>
       </c>
       <c r="F79" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>28</v>
@@ -6455,7 +6455,7 @@
         <v>46184.345671296294</v>
       </c>
       <c r="F80" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>24</v>
@@ -6523,7 +6523,7 @@
         <v>46218.3812962963</v>
       </c>
       <c r="F81" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>36</v>
@@ -6591,7 +6591,7 @@
         <v>46215.31277777778</v>
       </c>
       <c r="F82" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>28</v>
@@ -6600,7 +6600,7 @@
         <v>28</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J82" s="0" t="s">
         <v>25</v>
@@ -6620,8 +6620,8 @@
       <c r="O82" s="0">
         <v>1</v>
       </c>
-      <c r="P82" s="0" t="s">
-        <v>25</v>
+      <c r="P82" s="0">
+        <v>0</v>
       </c>
       <c r="Q82" s="0" t="s">
         <v>25</v>
@@ -6659,7 +6659,7 @@
         <v>46198.758576388886</v>
       </c>
       <c r="F83" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>24</v>
@@ -6727,7 +6727,7 @@
         <v>46211.747719907406</v>
       </c>
       <c r="F84" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>24</v>
@@ -6795,7 +6795,7 @@
         <v>46196.6612962963</v>
       </c>
       <c r="F85" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>36</v>
@@ -6863,7 +6863,7 @@
         <v>46203.386967592596</v>
       </c>
       <c r="F86" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>24</v>
@@ -6878,7 +6878,7 @@
         <v>24</v>
       </c>
       <c r="K86" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L86" s="0" t="s">
         <v>25</v>
@@ -6898,8 +6898,8 @@
       <c r="Q86" s="0">
         <v>1</v>
       </c>
-      <c r="R86" s="0" t="s">
-        <v>25</v>
+      <c r="R86" s="0">
+        <v>0</v>
       </c>
       <c r="S86" s="0" t="s">
         <v>25</v>
@@ -6931,7 +6931,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F87" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>46202.30238425926</v>
       </c>
       <c r="F88" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G88" s="0" t="s">
         <v>28</v>
@@ -7067,7 +7067,7 @@
         <v>46208.76116898148</v>
       </c>
       <c r="F89" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>36</v>
@@ -7079,7 +7079,7 @@
         <v>36</v>
       </c>
       <c r="J89" s="0" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K89" s="0" t="s">
         <v>25</v>
@@ -7099,8 +7099,8 @@
       <c r="P89" s="0">
         <v>1</v>
       </c>
-      <c r="Q89" s="0" t="s">
-        <v>25</v>
+      <c r="Q89" s="0">
+        <v>0</v>
       </c>
       <c r="R89" s="0" t="s">
         <v>25</v>
@@ -7135,7 +7135,7 @@
         <v>46217.76349537037</v>
       </c>
       <c r="F90" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>24</v>
@@ -7203,7 +7203,7 @@
         <v>46198.007743055554</v>
       </c>
       <c r="F91" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>24</v>
@@ -7271,7 +7271,7 @@
         <v>46204.82892361111</v>
       </c>
       <c r="F92" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>24</v>
@@ -7339,7 +7339,7 @@
         <v>46211.026354166665</v>
       </c>
       <c r="F93" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>24</v>
@@ -7407,7 +7407,7 @@
         <v>46206.49621527778</v>
       </c>
       <c r="F94" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>28</v>
@@ -7475,7 +7475,7 @@
         <v>46194.10880787037</v>
       </c>
       <c r="F95" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>24</v>
@@ -7543,7 +7543,7 @@
         <v>46202.80762731482</v>
       </c>
       <c r="F96" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>28</v>
@@ -7558,7 +7558,7 @@
         <v>28</v>
       </c>
       <c r="K96" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L96" s="0" t="s">
         <v>25</v>
@@ -7578,8 +7578,8 @@
       <c r="Q96" s="0">
         <v>0</v>
       </c>
-      <c r="R96" s="0" t="s">
-        <v>25</v>
+      <c r="R96" s="0">
+        <v>0</v>
       </c>
       <c r="S96" s="0" t="s">
         <v>25</v>
@@ -7611,7 +7611,7 @@
         <v>46212.191030092596</v>
       </c>
       <c r="F97" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>28</v>
@@ -7679,7 +7679,7 @@
         <v>46214.51880787037</v>
       </c>
       <c r="F98" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G98" s="0" t="s">
         <v>28</v>
@@ -7688,7 +7688,7 @@
         <v>28</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J98" s="0" t="s">
         <v>25</v>
@@ -7708,8 +7708,8 @@
       <c r="O98" s="0">
         <v>1</v>
       </c>
-      <c r="P98" s="0" t="s">
-        <v>25</v>
+      <c r="P98" s="0">
+        <v>0</v>
       </c>
       <c r="Q98" s="0" t="s">
         <v>25</v>
@@ -7747,7 +7747,7 @@
         <v>46198.053506944445</v>
       </c>
       <c r="F99" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>28</v>
@@ -7815,7 +7815,7 @@
         <v>46208.01679398148</v>
       </c>
       <c r="F100" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>28</v>
@@ -7883,7 +7883,7 @@
         <v>46199.4216087963</v>
       </c>
       <c r="F101" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>36</v>
@@ -7951,7 +7951,7 @@
         <v>46203.398622685185</v>
       </c>
       <c r="F102" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>24</v>
@@ -8019,7 +8019,7 @@
         <v>46204.071388888886</v>
       </c>
       <c r="F103" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>24</v>
@@ -8087,7 +8087,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F104" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>24</v>
@@ -8155,7 +8155,7 @@
         <v>46207.340208333335</v>
       </c>
       <c r="F105" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>28</v>
@@ -8223,7 +8223,7 @@
         <v>46203.22761574074</v>
       </c>
       <c r="F106" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>28</v>
@@ -8291,7 +8291,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F107" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>28</v>
@@ -8359,7 +8359,7 @@
         <v>46209.27856481481</v>
       </c>
       <c r="F108" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>28</v>
@@ -8427,7 +8427,7 @@
         <v>46203.241944444446</v>
       </c>
       <c r="F109" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>28</v>
@@ -8495,7 +8495,7 @@
         <v>46200.90429398148</v>
       </c>
       <c r="F110" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>24</v>
@@ -8563,7 +8563,7 @@
         <v>46201.17297453704</v>
       </c>
       <c r="F111" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>28</v>
@@ -8631,7 +8631,7 @@
         <v>46197.398356481484</v>
       </c>
       <c r="F112" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>24</v>
@@ -8699,7 +8699,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F113" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>24</v>
@@ -8767,7 +8767,7 @@
         <v>46204.81618055556</v>
       </c>
       <c r="F114" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>24</v>
@@ -8835,7 +8835,7 @@
         <v>46184.345671296294</v>
       </c>
       <c r="F115" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>24</v>
@@ -8903,7 +8903,7 @@
         <v>46198.76695601852</v>
       </c>
       <c r="F116" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>24</v>
@@ -8971,7 +8971,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F117" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>36</v>
@@ -9039,7 +9039,7 @@
         <v>46207.38381944445</v>
       </c>
       <c r="F118" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>28</v>
@@ -9107,7 +9107,7 @@
         <v>46198.764710648145</v>
       </c>
       <c r="F119" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>24</v>
@@ -9175,7 +9175,7 @@
         <v>46208.60445601852</v>
       </c>
       <c r="F120" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>28</v>
@@ -9208,7 +9208,7 @@
         <v>1</v>
       </c>
       <c r="Q120" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" s="0" t="s">
         <v>25</v>
@@ -9243,7 +9243,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F121" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>36</v>
@@ -9311,7 +9311,7 @@
         <v>46198.7566087963</v>
       </c>
       <c r="F122" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>24</v>
@@ -9379,7 +9379,7 @@
         <v>46204.591203703705</v>
       </c>
       <c r="F123" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>28</v>
@@ -9409,7 +9409,7 @@
         <v>0</v>
       </c>
       <c r="P123" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q123" s="0" t="s">
         <v>25</v>
@@ -9447,7 +9447,7 @@
         <v>46203.38690972222</v>
       </c>
       <c r="F124" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>24</v>
@@ -9462,7 +9462,7 @@
         <v>24</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L124" s="0" t="s">
         <v>25</v>
@@ -9482,8 +9482,8 @@
       <c r="Q124" s="0">
         <v>1</v>
       </c>
-      <c r="R124" s="0" t="s">
-        <v>25</v>
+      <c r="R124" s="0">
+        <v>0</v>
       </c>
       <c r="S124" s="0" t="s">
         <v>25</v>
@@ -9515,7 +9515,7 @@
         <v>46217.32613425926</v>
       </c>
       <c r="F125" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>28</v>
@@ -9583,7 +9583,7 @@
         <v>46199.954201388886</v>
       </c>
       <c r="F126" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>28</v>
       </c>
       <c r="K126" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L126" s="0" t="s">
         <v>25</v>
@@ -9618,8 +9618,8 @@
       <c r="Q126" s="0">
         <v>1</v>
       </c>
-      <c r="R126" s="0" t="s">
-        <v>25</v>
+      <c r="R126" s="0">
+        <v>0</v>
       </c>
       <c r="S126" s="0" t="s">
         <v>25</v>
@@ -9651,7 +9651,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F127" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>36</v>
@@ -9719,7 +9719,7 @@
         <v>46193.45674768519</v>
       </c>
       <c r="F128" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>24</v>
@@ -9787,7 +9787,7 @@
         <v>46211.339479166665</v>
       </c>
       <c r="F129" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>24</v>
@@ -9855,7 +9855,7 @@
         <v>46184.344409722224</v>
       </c>
       <c r="F130" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>24</v>
@@ -9923,7 +9923,7 @@
         <v>46217.72965277778</v>
       </c>
       <c r="F131" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>24</v>
@@ -9991,7 +9991,7 @@
         <v>46196.43208333333</v>
       </c>
       <c r="F132" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>28</v>
@@ -10059,7 +10059,7 @@
         <v>46204.591203703705</v>
       </c>
       <c r="F133" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>28</v>
@@ -10089,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="P133" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q133" s="0" t="s">
         <v>25</v>
@@ -10127,7 +10127,7 @@
         <v>46212.38707175926</v>
       </c>
       <c r="F134" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>28</v>
@@ -10195,7 +10195,7 @@
         <v>46205.85377314815</v>
       </c>
       <c r="F135" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>24</v>
@@ -10263,7 +10263,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F136" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>24</v>
@@ -10331,7 +10331,7 @@
         <v>46194.496782407405</v>
       </c>
       <c r="F137" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>36</v>
@@ -10399,7 +10399,7 @@
         <v>46206.041817129626</v>
       </c>
       <c r="F138" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>28</v>
@@ -10467,7 +10467,7 @@
         <v>46211.74564814815</v>
       </c>
       <c r="F139" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>24</v>
@@ -10535,7 +10535,7 @@
         <v>46198.76357638889</v>
       </c>
       <c r="F140" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>24</v>
@@ -10603,7 +10603,7 @@
         <v>46214.41127314815</v>
       </c>
       <c r="F141" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G141" s="0" t="s">
         <v>28</v>
@@ -10612,7 +10612,7 @@
         <v>28</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J141" s="0" t="s">
         <v>25</v>
@@ -10632,8 +10632,8 @@
       <c r="O141" s="0">
         <v>1</v>
       </c>
-      <c r="P141" s="0" t="s">
-        <v>25</v>
+      <c r="P141" s="0">
+        <v>0</v>
       </c>
       <c r="Q141" s="0" t="s">
         <v>25</v>
@@ -10671,7 +10671,7 @@
         <v>46210.39944444445</v>
       </c>
       <c r="F142" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>24</v>
@@ -10739,7 +10739,7 @@
         <v>46203.900046296294</v>
       </c>
       <c r="F143" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>36</v>
@@ -10807,7 +10807,7 @@
         <v>46198.75818287037</v>
       </c>
       <c r="F144" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>24</v>
@@ -10875,7 +10875,7 @@
         <v>46199.24039351852</v>
       </c>
       <c r="F145" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>28</v>
@@ -10943,7 +10943,7 @@
         <v>46207.7878125</v>
       </c>
       <c r="F146" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>28</v>
@@ -11011,7 +11011,7 @@
         <v>46200.88856481481</v>
       </c>
       <c r="F147" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>36</v>
@@ -11079,7 +11079,7 @@
         <v>46207.091145833336</v>
       </c>
       <c r="F148" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>28</v>
@@ -11147,7 +11147,7 @@
         <v>46209.81253472222</v>
       </c>
       <c r="F149" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>24</v>
@@ -11215,7 +11215,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F150" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>24</v>
@@ -11283,7 +11283,7 @@
         <v>46208.76133101852</v>
       </c>
       <c r="F151" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>24</v>
@@ -11295,7 +11295,7 @@
         <v>24</v>
       </c>
       <c r="J151" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K151" s="0" t="s">
         <v>25</v>
@@ -11315,8 +11315,8 @@
       <c r="P151" s="0">
         <v>1</v>
       </c>
-      <c r="Q151" s="0" t="s">
-        <v>25</v>
+      <c r="Q151" s="0">
+        <v>0</v>
       </c>
       <c r="R151" s="0" t="s">
         <v>25</v>
@@ -11351,7 +11351,7 @@
         <v>46210.11184027778</v>
       </c>
       <c r="F152" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>24</v>
@@ -11419,7 +11419,7 @@
         <v>46202.603946759256</v>
       </c>
       <c r="F153" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>24</v>
@@ -11487,7 +11487,7 @@
         <v>46208.28020833333</v>
       </c>
       <c r="F154" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>36</v>
@@ -11555,7 +11555,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F155" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>24</v>
@@ -11623,7 +11623,7 @@
         <v>46187.9200462963</v>
       </c>
       <c r="F156" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>24</v>
@@ -11632,7 +11632,7 @@
         <v>24</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J156" s="0" t="s">
         <v>25</v>
@@ -11652,8 +11652,8 @@
       <c r="O156" s="0">
         <v>0</v>
       </c>
-      <c r="P156" s="0" t="s">
-        <v>25</v>
+      <c r="P156" s="0">
+        <v>0</v>
       </c>
       <c r="Q156" s="0" t="s">
         <v>25</v>
@@ -11691,7 +11691,7 @@
         <v>46204.36974537037</v>
       </c>
       <c r="F157" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G157" s="0" t="s">
         <v>28</v>
@@ -11759,7 +11759,7 @@
         <v>46201.332870370374</v>
       </c>
       <c r="F158" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G158" s="0" t="s">
         <v>24</v>
@@ -11827,7 +11827,7 @@
         <v>46197.03113425926</v>
       </c>
       <c r="F159" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>24</v>
@@ -11895,7 +11895,7 @@
         <v>46212.285219907404</v>
       </c>
       <c r="F160" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>28</v>
@@ -11904,7 +11904,7 @@
         <v>28</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J160" s="0" t="s">
         <v>25</v>
@@ -11924,8 +11924,8 @@
       <c r="O160" s="0">
         <v>0</v>
       </c>
-      <c r="P160" s="0" t="s">
-        <v>25</v>
+      <c r="P160" s="0">
+        <v>0</v>
       </c>
       <c r="Q160" s="0" t="s">
         <v>25</v>
@@ -11963,7 +11963,7 @@
         <v>46200.98619212963</v>
       </c>
       <c r="F161" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>28</v>
@@ -12031,7 +12031,7 @@
         <v>46212.06758101852</v>
       </c>
       <c r="F162" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>28</v>
@@ -12099,7 +12099,7 @@
         <v>46207.18613425926</v>
       </c>
       <c r="F163" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>28</v>
@@ -12167,7 +12167,7 @@
         <v>46210.8569212963</v>
       </c>
       <c r="F164" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>28</v>
@@ -12235,7 +12235,7 @@
         <v>46198.763344907406</v>
       </c>
       <c r="F165" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>24</v>
@@ -12303,7 +12303,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F166" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>24</v>
@@ -12371,7 +12371,7 @@
         <v>46198.86886574074</v>
       </c>
       <c r="F167" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>28</v>
@@ -12439,7 +12439,7 @@
         <v>46198.76422453704</v>
       </c>
       <c r="F168" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>24</v>
@@ -12507,7 +12507,7 @@
         <v>46206.29314814815</v>
       </c>
       <c r="F169" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>36</v>
@@ -12519,7 +12519,7 @@
         <v>36</v>
       </c>
       <c r="J169" s="0" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K169" s="0" t="s">
         <v>25</v>
@@ -12539,8 +12539,8 @@
       <c r="P169" s="0">
         <v>1</v>
       </c>
-      <c r="Q169" s="0" t="s">
-        <v>25</v>
+      <c r="Q169" s="0">
+        <v>0</v>
       </c>
       <c r="R169" s="0" t="s">
         <v>25</v>
@@ -12575,7 +12575,7 @@
         <v>46206.39832175926</v>
       </c>
       <c r="F170" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>28</v>
@@ -12643,7 +12643,7 @@
         <v>46201.828206018516</v>
       </c>
       <c r="F171" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>28</v>
@@ -12711,7 +12711,7 @@
         <v>46198.13486111111</v>
       </c>
       <c r="F172" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>24</v>
@@ -12779,7 +12779,7 @@
         <v>46184.34568287037</v>
       </c>
       <c r="F173" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>24</v>
@@ -12847,7 +12847,7 @@
         <v>46217.38422453704</v>
       </c>
       <c r="F174" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>28</v>
@@ -12915,7 +12915,7 @@
         <v>46198.487546296295</v>
       </c>
       <c r="F175" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>28</v>
@@ -12983,7 +12983,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F176" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>24</v>
@@ -13051,7 +13051,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F177" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>24</v>
@@ -13119,7 +13119,7 @@
         <v>46199.37</v>
       </c>
       <c r="F178" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>28</v>
@@ -13187,7 +13187,7 @@
         <v>46200.507418981484</v>
       </c>
       <c r="F179" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>28</v>
@@ -13255,7 +13255,7 @@
         <v>46208.7612037037</v>
       </c>
       <c r="F180" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G180" s="0" t="s">
         <v>36</v>
@@ -13267,7 +13267,7 @@
         <v>36</v>
       </c>
       <c r="J180" s="0" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K180" s="0" t="s">
         <v>25</v>
@@ -13287,8 +13287,8 @@
       <c r="P180" s="0">
         <v>1</v>
       </c>
-      <c r="Q180" s="0" t="s">
-        <v>25</v>
+      <c r="Q180" s="0">
+        <v>0</v>
       </c>
       <c r="R180" s="0" t="s">
         <v>25</v>
@@ -13323,7 +13323,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F181" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>24</v>
@@ -13391,7 +13391,7 @@
         <v>46218.09614583333</v>
       </c>
       <c r="F182" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>36</v>
@@ -13459,7 +13459,7 @@
         <v>46206.616875</v>
       </c>
       <c r="F183" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>28</v>
@@ -13527,7 +13527,7 @@
         <v>46206.85376157407</v>
       </c>
       <c r="F184" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>24</v>
@@ -13595,7 +13595,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F185" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>24</v>
@@ -13663,7 +13663,7 @@
         <v>46215.346342592595</v>
       </c>
       <c r="F186" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G186" s="0" t="s">
         <v>36</v>
@@ -13672,7 +13672,7 @@
         <v>36</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J186" s="0" t="s">
         <v>25</v>
@@ -13692,8 +13692,8 @@
       <c r="O186" s="0">
         <v>1</v>
       </c>
-      <c r="P186" s="0" t="s">
-        <v>25</v>
+      <c r="P186" s="0">
+        <v>0</v>
       </c>
       <c r="Q186" s="0" t="s">
         <v>25</v>
@@ -13731,7 +13731,7 @@
         <v>46208.34142361111</v>
       </c>
       <c r="F187" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>36</v>
@@ -13799,7 +13799,7 @@
         <v>46184.34611111111</v>
       </c>
       <c r="F188" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>24</v>
@@ -13867,7 +13867,7 @@
         <v>46207.44116898148</v>
       </c>
       <c r="F189" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>36</v>
@@ -13935,7 +13935,7 @@
         <v>46217.771006944444</v>
       </c>
       <c r="F190" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>24</v>
@@ -14003,7 +14003,7 @@
         <v>46217.77065972222</v>
       </c>
       <c r="F191" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>24</v>
@@ -14071,7 +14071,7 @@
         <v>46213.12200231481</v>
       </c>
       <c r="F192" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>28</v>
@@ -14139,7 +14139,7 @@
         <v>46211.78650462963</v>
       </c>
       <c r="F193" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>28</v>
@@ -14207,7 +14207,7 @@
         <v>46205.74003472222</v>
       </c>
       <c r="F194" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G194" s="0" t="s">
         <v>36</v>
@@ -14275,7 +14275,7 @@
         <v>46214.6358912037</v>
       </c>
       <c r="F195" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G195" s="0" t="s">
         <v>28</v>
@@ -14284,7 +14284,7 @@
         <v>28</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J195" s="0" t="s">
         <v>25</v>
@@ -14304,8 +14304,8 @@
       <c r="O195" s="0">
         <v>1</v>
       </c>
-      <c r="P195" s="0" t="s">
-        <v>25</v>
+      <c r="P195" s="0">
+        <v>0</v>
       </c>
       <c r="Q195" s="0" t="s">
         <v>25</v>
@@ -14343,7 +14343,7 @@
         <v>46199.95371527778</v>
       </c>
       <c r="F196" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G196" s="0" t="s">
         <v>36</v>
@@ -14411,7 +14411,7 @@
         <v>46212.29601851852</v>
       </c>
       <c r="F197" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G197" s="0" t="s">
         <v>28</v>
@@ -14479,7 +14479,7 @@
         <v>46205.07099537037</v>
       </c>
       <c r="F198" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G198" s="0" t="s">
         <v>24</v>
@@ -14491,7 +14491,7 @@
         <v>24</v>
       </c>
       <c r="J198" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K198" s="0" t="s">
         <v>25</v>
@@ -14511,8 +14511,8 @@
       <c r="P198" s="0">
         <v>1</v>
       </c>
-      <c r="Q198" s="0" t="s">
-        <v>25</v>
+      <c r="Q198" s="0">
+        <v>0</v>
       </c>
       <c r="R198" s="0" t="s">
         <v>25</v>
@@ -14547,7 +14547,7 @@
         <v>46215.09512731482</v>
       </c>
       <c r="F199" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>28</v>
@@ -14556,7 +14556,7 @@
         <v>28</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J199" s="0" t="s">
         <v>25</v>
@@ -14576,8 +14576,8 @@
       <c r="O199" s="0">
         <v>1</v>
       </c>
-      <c r="P199" s="0" t="s">
-        <v>25</v>
+      <c r="P199" s="0">
+        <v>0</v>
       </c>
       <c r="Q199" s="0" t="s">
         <v>25</v>
@@ -14615,7 +14615,7 @@
         <v>46203.39921296296</v>
       </c>
       <c r="F200" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>24</v>
@@ -14683,7 +14683,7 @@
         <v>46206.91523148148</v>
       </c>
       <c r="F201" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>24</v>
@@ -14751,7 +14751,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F202" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>24</v>
@@ -14819,7 +14819,7 @@
         <v>46212.73332175926</v>
       </c>
       <c r="F203" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>28</v>
@@ -14887,7 +14887,7 @@
         <v>46199.395949074074</v>
       </c>
       <c r="F204" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>28</v>
@@ -14955,7 +14955,7 @@
         <v>46218.05547453704</v>
       </c>
       <c r="F205" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>24</v>
@@ -15023,7 +15023,7 @@
         <v>46184.34570601852</v>
       </c>
       <c r="F206" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>24</v>
@@ -15091,7 +15091,7 @@
         <v>46198.756527777776</v>
       </c>
       <c r="F207" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G207" s="0" t="s">
         <v>24</v>
@@ -15159,7 +15159,7 @@
         <v>46208.76128472222</v>
       </c>
       <c r="F208" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G208" s="0" t="s">
         <v>24</v>
@@ -15171,7 +15171,7 @@
         <v>24</v>
       </c>
       <c r="J208" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K208" s="0" t="s">
         <v>25</v>
@@ -15191,8 +15191,8 @@
       <c r="P208" s="0">
         <v>1</v>
       </c>
-      <c r="Q208" s="0" t="s">
-        <v>25</v>
+      <c r="Q208" s="0">
+        <v>0</v>
       </c>
       <c r="R208" s="0" t="s">
         <v>25</v>
@@ -15227,7 +15227,7 @@
         <v>46198.76427083334</v>
       </c>
       <c r="F209" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G209" s="0" t="s">
         <v>24</v>
@@ -15295,7 +15295,7 @@
         <v>46196.08101851852</v>
       </c>
       <c r="F210" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>24</v>
@@ -15363,7 +15363,7 @@
         <v>46207.28523148148</v>
       </c>
       <c r="F211" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>24</v>
@@ -15431,7 +15431,7 @@
         <v>46196.788564814815</v>
       </c>
       <c r="F212" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>24</v>
@@ -15499,7 +15499,7 @@
         <v>46217.99606481481</v>
       </c>
       <c r="F213" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>28</v>
@@ -15567,7 +15567,7 @@
         <v>46217.72994212963</v>
       </c>
       <c r="F214" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>24</v>
@@ -15635,7 +15635,7 @@
         <v>46200.45096064815</v>
       </c>
       <c r="F215" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>36</v>
@@ -15703,7 +15703,7 @@
         <v>46213.44936342593</v>
       </c>
       <c r="F216" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>28</v>
@@ -15733,7 +15733,7 @@
         <v>0</v>
       </c>
       <c r="P216" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q216" s="0" t="s">
         <v>25</v>
@@ -15771,7 +15771,7 @@
         <v>46207.18237268519</v>
       </c>
       <c r="F217" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>24</v>
@@ -15804,7 +15804,7 @@
         <v>1</v>
       </c>
       <c r="Q217" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R217" s="0" t="s">
         <v>25</v>
@@ -15839,7 +15839,7 @@
         <v>46198.89733796296</v>
       </c>
       <c r="F218" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>28</v>
@@ -15907,7 +15907,7 @@
         <v>46213.282858796294</v>
       </c>
       <c r="F219" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>28</v>
@@ -15975,7 +15975,7 @@
         <v>46217.69572916667</v>
       </c>
       <c r="F220" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G220" s="0" t="s">
         <v>28</v>
@@ -16043,7 +16043,7 @@
         <v>46205.19603009259</v>
       </c>
       <c r="F221" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>28</v>
       </c>
       <c r="K221" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L221" s="0" t="s">
         <v>25</v>
@@ -16078,8 +16078,8 @@
       <c r="Q221" s="0">
         <v>0</v>
       </c>
-      <c r="R221" s="0" t="s">
-        <v>25</v>
+      <c r="R221" s="0">
+        <v>0</v>
       </c>
       <c r="S221" s="0" t="s">
         <v>25</v>
@@ -16111,7 +16111,7 @@
         <v>46196.08101851852</v>
       </c>
       <c r="F222" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>24</v>
@@ -16179,7 +16179,7 @@
         <v>46196.88885416667</v>
       </c>
       <c r="F223" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>24</v>
@@ -16247,7 +16247,7 @@
         <v>46199.89765046296</v>
       </c>
       <c r="F224" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>28</v>
@@ -16283,7 +16283,7 @@
         <v>1</v>
       </c>
       <c r="R224" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S224" s="0" t="s">
         <v>25</v>
@@ -16315,7 +16315,7 @@
         <v>46203.38673611111</v>
       </c>
       <c r="F225" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>24</v>
@@ -16330,7 +16330,7 @@
         <v>24</v>
       </c>
       <c r="K225" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L225" s="0" t="s">
         <v>25</v>
@@ -16350,8 +16350,8 @@
       <c r="Q225" s="0">
         <v>0</v>
       </c>
-      <c r="R225" s="0" t="s">
-        <v>25</v>
+      <c r="R225" s="0">
+        <v>0</v>
       </c>
       <c r="S225" s="0" t="s">
         <v>25</v>
@@ -16383,7 +16383,7 @@
         <v>46214.55940972222</v>
       </c>
       <c r="F226" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>28</v>
@@ -16392,7 +16392,7 @@
         <v>28</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J226" s="0" t="s">
         <v>25</v>
@@ -16412,8 +16412,8 @@
       <c r="O226" s="0">
         <v>1</v>
       </c>
-      <c r="P226" s="0" t="s">
-        <v>25</v>
+      <c r="P226" s="0">
+        <v>0</v>
       </c>
       <c r="Q226" s="0" t="s">
         <v>25</v>
@@ -16451,7 +16451,7 @@
         <v>46218.193761574075</v>
       </c>
       <c r="F227" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>28</v>
@@ -16519,7 +16519,7 @@
         <v>46215.391805555555</v>
       </c>
       <c r="F228" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G228" s="0" t="s">
         <v>36</v>
@@ -16528,7 +16528,7 @@
         <v>36</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J228" s="0" t="s">
         <v>25</v>
@@ -16548,8 +16548,8 @@
       <c r="O228" s="0">
         <v>1</v>
       </c>
-      <c r="P228" s="0" t="s">
-        <v>25</v>
+      <c r="P228" s="0">
+        <v>0</v>
       </c>
       <c r="Q228" s="0" t="s">
         <v>25</v>
@@ -16587,7 +16587,7 @@
         <v>46208.49730324074</v>
       </c>
       <c r="F229" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>36</v>
@@ -16655,7 +16655,7 @@
         <v>46205.35525462963</v>
       </c>
       <c r="F230" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>28</v>
@@ -16670,7 +16670,7 @@
         <v>28</v>
       </c>
       <c r="K230" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L230" s="0" t="s">
         <v>25</v>
@@ -16690,8 +16690,8 @@
       <c r="Q230" s="0">
         <v>0</v>
       </c>
-      <c r="R230" s="0" t="s">
-        <v>25</v>
+      <c r="R230" s="0">
+        <v>0</v>
       </c>
       <c r="S230" s="0" t="s">
         <v>25</v>
@@ -16723,7 +16723,7 @@
         <v>46200.595925925925</v>
       </c>
       <c r="F231" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G231" s="0" t="s">
         <v>24</v>
@@ -16759,7 +16759,7 @@
         <v>1</v>
       </c>
       <c r="R231" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S231" s="0" t="s">
         <v>25</v>
@@ -16791,7 +16791,7 @@
         <v>46198.36408564815</v>
       </c>
       <c r="F232" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>28</v>
@@ -16859,7 +16859,7 @@
         <v>46214.184386574074</v>
       </c>
       <c r="F233" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>28</v>
@@ -16868,7 +16868,7 @@
         <v>28</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J233" s="0" t="s">
         <v>25</v>
@@ -16888,8 +16888,8 @@
       <c r="O233" s="0">
         <v>1</v>
       </c>
-      <c r="P233" s="0" t="s">
-        <v>25</v>
+      <c r="P233" s="0">
+        <v>0</v>
       </c>
       <c r="Q233" s="0" t="s">
         <v>25</v>
@@ -16927,7 +16927,7 @@
         <v>46208.95462962963</v>
       </c>
       <c r="F234" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G234" s="0" t="s">
         <v>36</v>
@@ -16995,7 +16995,7 @@
         <v>46209.34474537037</v>
       </c>
       <c r="F235" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G235" s="0" t="s">
         <v>28</v>
@@ -17063,7 +17063,7 @@
         <v>46203.6659375</v>
       </c>
       <c r="F236" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>24</v>
@@ -17131,7 +17131,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F237" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>24</v>
@@ -17199,7 +17199,7 @@
         <v>46200.84137731481</v>
       </c>
       <c r="F238" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G238" s="0" t="s">
         <v>28</v>
@@ -17267,7 +17267,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F239" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G239" s="0" t="s">
         <v>24</v>
@@ -17335,7 +17335,7 @@
         <v>46207.322233796294</v>
       </c>
       <c r="F240" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>28</v>
@@ -17403,7 +17403,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F241" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G241" s="0" t="s">
         <v>24</v>
@@ -17471,7 +17471,7 @@
         <v>46208.80619212963</v>
       </c>
       <c r="F242" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G242" s="0" t="s">
         <v>28</v>
@@ -17539,7 +17539,7 @@
         <v>46207.24060185185</v>
       </c>
       <c r="F243" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>24</v>
@@ -17607,7 +17607,7 @@
         <v>46213.36528935185</v>
       </c>
       <c r="F244" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G244" s="0" t="s">
         <v>36</v>
@@ -17675,7 +17675,7 @@
         <v>46202.50537037037</v>
       </c>
       <c r="F245" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>28</v>
@@ -17743,7 +17743,7 @@
         <v>46217.3975</v>
       </c>
       <c r="F246" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G246" s="0" t="s">
         <v>24</v>
@@ -17811,7 +17811,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F247" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>36</v>
@@ -17879,7 +17879,7 @@
         <v>46217.770949074074</v>
       </c>
       <c r="F248" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G248" s="0" t="s">
         <v>24</v>
@@ -17947,7 +17947,7 @@
         <v>46200.24690972222</v>
       </c>
       <c r="F249" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G249" s="0" t="s">
         <v>36</v>
@@ -18015,7 +18015,7 @@
         <v>46200.39493055556</v>
       </c>
       <c r="F250" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G250" s="0" t="s">
         <v>24</v>
@@ -18083,7 +18083,7 @@
         <v>46200.50178240741</v>
       </c>
       <c r="F251" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G251" s="0" t="s">
         <v>28</v>
@@ -18092,7 +18092,7 @@
         <v>28</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J251" s="0" t="s">
         <v>25</v>
@@ -18112,8 +18112,8 @@
       <c r="O251" s="0">
         <v>1</v>
       </c>
-      <c r="P251" s="0" t="s">
-        <v>25</v>
+      <c r="P251" s="0">
+        <v>0</v>
       </c>
       <c r="Q251" s="0" t="s">
         <v>25</v>
@@ -18151,7 +18151,7 @@
         <v>46201.81197916667</v>
       </c>
       <c r="F252" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>28</v>
@@ -18219,7 +18219,7 @@
         <v>46196.87100694444</v>
       </c>
       <c r="F253" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>28</v>
@@ -18287,7 +18287,7 @@
         <v>46211.287673611114</v>
       </c>
       <c r="F254" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G254" s="0" t="s">
         <v>28</v>
@@ -18355,7 +18355,7 @@
         <v>46217.07877314815</v>
       </c>
       <c r="F255" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G255" s="0" t="s">
         <v>28</v>
@@ -18423,7 +18423,7 @@
         <v>46213.33634259259</v>
       </c>
       <c r="F256" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>28</v>
@@ -18432,7 +18432,7 @@
         <v>28</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J256" s="0" t="s">
         <v>25</v>
@@ -18452,8 +18452,8 @@
       <c r="O256" s="0">
         <v>1</v>
       </c>
-      <c r="P256" s="0" t="s">
-        <v>25</v>
+      <c r="P256" s="0">
+        <v>0</v>
       </c>
       <c r="Q256" s="0" t="s">
         <v>25</v>
@@ -18491,7 +18491,7 @@
         <v>46203.38674768519</v>
       </c>
       <c r="F257" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>24</v>
@@ -18506,7 +18506,7 @@
         <v>24</v>
       </c>
       <c r="K257" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L257" s="0" t="s">
         <v>25</v>
@@ -18526,8 +18526,8 @@
       <c r="Q257" s="0">
         <v>1</v>
       </c>
-      <c r="R257" s="0" t="s">
-        <v>25</v>
+      <c r="R257" s="0">
+        <v>0</v>
       </c>
       <c r="S257" s="0" t="s">
         <v>25</v>
@@ -18559,7 +18559,7 @@
         <v>46199.38827546296</v>
       </c>
       <c r="F258" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>24</v>
@@ -18627,7 +18627,7 @@
         <v>46211.747569444444</v>
       </c>
       <c r="F259" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>24</v>
@@ -18695,7 +18695,7 @@
         <v>46214.036574074074</v>
       </c>
       <c r="F260" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>24</v>
@@ -18704,7 +18704,7 @@
         <v>24</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J260" s="0" t="s">
         <v>25</v>
@@ -18724,8 +18724,8 @@
       <c r="O260" s="0">
         <v>1</v>
       </c>
-      <c r="P260" s="0" t="s">
-        <v>25</v>
+      <c r="P260" s="0">
+        <v>0</v>
       </c>
       <c r="Q260" s="0" t="s">
         <v>25</v>
@@ -18763,7 +18763,7 @@
         <v>46198.75832175926</v>
       </c>
       <c r="F261" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>24</v>
@@ -18831,7 +18831,7 @@
         <v>46213.1378125</v>
       </c>
       <c r="F262" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>28</v>
@@ -18899,7 +18899,7 @@
         <v>46218.15008101852</v>
       </c>
       <c r="F263" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G263" s="0" t="s">
         <v>28</v>
@@ -18967,7 +18967,7 @@
         <v>46200.08666666667</v>
       </c>
       <c r="F264" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>28</v>
@@ -19035,7 +19035,7 @@
         <v>46191.20039351852</v>
       </c>
       <c r="F265" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G265" s="0" t="s">
         <v>24</v>
@@ -19103,7 +19103,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F266" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G266" s="0" t="s">
         <v>24</v>
@@ -19171,7 +19171,7 @@
         <v>46197.6375462963</v>
       </c>
       <c r="F267" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G267" s="0" t="s">
         <v>24</v>
@@ -19239,7 +19239,7 @@
         <v>46197.037523148145</v>
       </c>
       <c r="F268" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G268" s="0" t="s">
         <v>24</v>
@@ -19307,7 +19307,7 @@
         <v>46198.31060185185</v>
       </c>
       <c r="F269" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G269" s="0" t="s">
         <v>28</v>
@@ -19375,7 +19375,7 @@
         <v>46209.31466435185</v>
       </c>
       <c r="F270" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>28</v>
@@ -19443,7 +19443,7 @@
         <v>46206.72038194445</v>
       </c>
       <c r="F271" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>28</v>
@@ -19511,7 +19511,7 @@
         <v>46197.46810185185</v>
       </c>
       <c r="F272" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>24</v>
@@ -19579,7 +19579,7 @@
         <v>46202.349328703705</v>
       </c>
       <c r="F273" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G273" s="0" t="s">
         <v>28</v>
@@ -19647,7 +19647,7 @@
         <v>46217.73019675926</v>
       </c>
       <c r="F274" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>24</v>
@@ -19715,7 +19715,7 @@
         <v>46216.25659722222</v>
       </c>
       <c r="F275" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G275" s="0" t="s">
         <v>28</v>
@@ -19783,7 +19783,7 @@
         <v>46198.75665509259</v>
       </c>
       <c r="F276" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>24</v>
@@ -19851,7 +19851,7 @@
         <v>46205.784363425926</v>
       </c>
       <c r="F277" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G277" s="0" t="s">
         <v>36</v>
@@ -19919,7 +19919,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F278" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G278" s="0" t="s">
         <v>24</v>
@@ -19987,7 +19987,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F279" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G279" s="0" t="s">
         <v>24</v>
@@ -20055,7 +20055,7 @@
         <v>46198.75827546296</v>
       </c>
       <c r="F280" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>24</v>
@@ -20123,7 +20123,7 @@
         <v>46203.80048611111</v>
       </c>
       <c r="F281" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G281" s="0" t="s">
         <v>36</v>
@@ -20191,7 +20191,7 @@
         <v>46207.377118055556</v>
       </c>
       <c r="F282" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G282" s="0" t="s">
         <v>28</v>
@@ -20259,7 +20259,7 @@
         <v>46217.62388888889</v>
       </c>
       <c r="F283" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>36</v>
@@ -20327,7 +20327,7 @@
         <v>46198.76320601852</v>
       </c>
       <c r="F284" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G284" s="0" t="s">
         <v>24</v>
@@ -20395,7 +20395,7 @@
         <v>46209.364849537036</v>
       </c>
       <c r="F285" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G285" s="0" t="s">
         <v>36</v>
@@ -20428,7 +20428,7 @@
         <v>1</v>
       </c>
       <c r="Q285" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R285" s="0" t="s">
         <v>25</v>
@@ -20463,7 +20463,7 @@
         <v>46198.76327546296</v>
       </c>
       <c r="F286" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>24</v>
@@ -20531,7 +20531,7 @@
         <v>46197.041238425925</v>
       </c>
       <c r="F287" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>24</v>
@@ -20599,7 +20599,7 @@
         <v>46212.017488425925</v>
       </c>
       <c r="F288" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>36</v>
@@ -20608,7 +20608,7 @@
         <v>28</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J288" s="0" t="s">
         <v>25</v>
@@ -20628,8 +20628,8 @@
       <c r="O288" s="0">
         <v>1</v>
       </c>
-      <c r="P288" s="0" t="s">
-        <v>25</v>
+      <c r="P288" s="0">
+        <v>0</v>
       </c>
       <c r="Q288" s="0" t="s">
         <v>25</v>
@@ -20667,7 +20667,7 @@
         <v>46204.81549768519</v>
       </c>
       <c r="F289" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G289" s="0" t="s">
         <v>24</v>
@@ -20735,7 +20735,7 @@
         <v>46200.44310185185</v>
       </c>
       <c r="F290" s="1">
-        <v>46219.04229085648</v>
+        <v>46220.042274074076</v>
       </c>
       <c r="G290" s="0" t="s">
         <v>24</v>

--- a/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
+++ b/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
@@ -1472,7 +1472,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F2" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>24</v>
@@ -1484,7 +1484,7 @@
         <v>24</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>25</v>
@@ -1504,8 +1504,8 @@
       <c r="P2" s="0">
         <v>1</v>
       </c>
-      <c r="Q2" s="0" t="s">
-        <v>25</v>
+      <c r="Q2" s="0">
+        <v>0</v>
       </c>
       <c r="R2" s="0" t="s">
         <v>25</v>
@@ -1540,7 +1540,7 @@
         <v>46204.34583333333</v>
       </c>
       <c r="F3" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>28</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="0" t="s">
         <v>25</v>
@@ -1608,7 +1608,7 @@
         <v>46207.15827546296</v>
       </c>
       <c r="F4" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>28</v>
@@ -1623,7 +1623,7 @@
         <v>28</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L4" s="0" t="s">
         <v>25</v>
@@ -1643,8 +1643,8 @@
       <c r="Q4" s="0">
         <v>0</v>
       </c>
-      <c r="R4" s="0" t="s">
-        <v>25</v>
+      <c r="R4" s="0">
+        <v>0</v>
       </c>
       <c r="S4" s="0" t="s">
         <v>25</v>
@@ -1676,7 +1676,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F5" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>31</v>
@@ -1744,7 +1744,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F6" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>24</v>
@@ -1756,7 +1756,7 @@
         <v>24</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K6" s="0" t="s">
         <v>25</v>
@@ -1776,8 +1776,8 @@
       <c r="P6" s="0">
         <v>1</v>
       </c>
-      <c r="Q6" s="0" t="s">
-        <v>25</v>
+      <c r="Q6" s="0">
+        <v>0</v>
       </c>
       <c r="R6" s="0" t="s">
         <v>25</v>
@@ -1812,7 +1812,7 @@
         <v>46200.30415509259</v>
       </c>
       <c r="F7" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>28</v>
@@ -1880,7 +1880,7 @@
         <v>46214.27086805556</v>
       </c>
       <c r="F8" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>28</v>
@@ -1948,7 +1948,7 @@
         <v>46216.91679398148</v>
       </c>
       <c r="F9" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>25</v>
@@ -1977,8 +1977,8 @@
       <c r="O9" s="0">
         <v>1</v>
       </c>
-      <c r="P9" s="0" t="s">
-        <v>25</v>
+      <c r="P9" s="0">
+        <v>0</v>
       </c>
       <c r="Q9" s="0" t="s">
         <v>25</v>
@@ -2016,7 +2016,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F10" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>31</v>
@@ -2084,7 +2084,7 @@
         <v>46217.789305555554</v>
       </c>
       <c r="F11" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>31</v>
@@ -2152,7 +2152,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F12" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>24</v>
@@ -2220,7 +2220,7 @@
         <v>46211.80736111111</v>
       </c>
       <c r="F13" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>28</v>
@@ -2232,7 +2232,7 @@
         <v>28</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K13" s="0" t="s">
         <v>25</v>
@@ -2252,8 +2252,8 @@
       <c r="P13" s="0">
         <v>0</v>
       </c>
-      <c r="Q13" s="0" t="s">
-        <v>25</v>
+      <c r="Q13" s="0">
+        <v>0</v>
       </c>
       <c r="R13" s="0" t="s">
         <v>25</v>
@@ -2288,7 +2288,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F14" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>31</v>
@@ -2356,7 +2356,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F15" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>24</v>
@@ -2424,7 +2424,7 @@
         <v>46214.30170138889</v>
       </c>
       <c r="F16" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>24</v>
@@ -2492,7 +2492,7 @@
         <v>46211.689108796294</v>
       </c>
       <c r="F17" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G17" s="0" t="s">
         <v>28</v>
@@ -2504,7 +2504,7 @@
         <v>28</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K17" s="0" t="s">
         <v>25</v>
@@ -2524,8 +2524,8 @@
       <c r="P17" s="0">
         <v>1</v>
       </c>
-      <c r="Q17" s="0" t="s">
-        <v>25</v>
+      <c r="Q17" s="0">
+        <v>0</v>
       </c>
       <c r="R17" s="0" t="s">
         <v>25</v>
@@ -2560,7 +2560,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F18" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>31</v>
@@ -2628,7 +2628,7 @@
         <v>46198.75680555555</v>
       </c>
       <c r="F19" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G19" s="0" t="s">
         <v>24</v>
@@ -2643,7 +2643,7 @@
         <v>24</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L19" s="0" t="s">
         <v>25</v>
@@ -2663,8 +2663,8 @@
       <c r="Q19" s="0">
         <v>1</v>
       </c>
-      <c r="R19" s="0" t="s">
-        <v>25</v>
+      <c r="R19" s="0">
+        <v>0</v>
       </c>
       <c r="S19" s="0" t="s">
         <v>25</v>
@@ -2696,7 +2696,7 @@
         <v>46200.02773148148</v>
       </c>
       <c r="F20" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G20" s="0" t="s">
         <v>28</v>
@@ -2764,7 +2764,7 @@
         <v>46214.69945601852</v>
       </c>
       <c r="F21" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G21" s="0" t="s">
         <v>31</v>
@@ -2832,7 +2832,7 @@
         <v>46216.87899305556</v>
       </c>
       <c r="F22" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>28</v>
@@ -2841,7 +2841,7 @@
         <v>28</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>25</v>
@@ -2861,8 +2861,8 @@
       <c r="O22" s="0">
         <v>1</v>
       </c>
-      <c r="P22" s="0" t="s">
-        <v>25</v>
+      <c r="P22" s="0">
+        <v>0</v>
       </c>
       <c r="Q22" s="0" t="s">
         <v>25</v>
@@ -2900,7 +2900,7 @@
         <v>46200.57623842593</v>
       </c>
       <c r="F23" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G23" s="0" t="s">
         <v>28</v>
@@ -2968,7 +2968,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F24" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>31</v>
@@ -3036,7 +3036,7 @@
         <v>46198.764027777775</v>
       </c>
       <c r="F25" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G25" s="0" t="s">
         <v>24</v>
@@ -3051,7 +3051,7 @@
         <v>24</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L25" s="0" t="s">
         <v>25</v>
@@ -3071,8 +3071,8 @@
       <c r="Q25" s="0">
         <v>1</v>
       </c>
-      <c r="R25" s="0" t="s">
-        <v>25</v>
+      <c r="R25" s="0">
+        <v>0</v>
       </c>
       <c r="S25" s="0" t="s">
         <v>25</v>
@@ -3104,7 +3104,7 @@
         <v>46198.18491898148</v>
       </c>
       <c r="F26" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>28</v>
@@ -3172,7 +3172,7 @@
         <v>46203.81460648148</v>
       </c>
       <c r="F27" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G27" s="0" t="s">
         <v>31</v>
@@ -3240,7 +3240,7 @@
         <v>46201.33733796296</v>
       </c>
       <c r="F28" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>28</v>
@@ -3308,7 +3308,7 @@
         <v>46218.70291666667</v>
       </c>
       <c r="F29" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>28</v>
@@ -3376,7 +3376,7 @@
         <v>46203.71907407408</v>
       </c>
       <c r="F30" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>28</v>
@@ -3444,7 +3444,7 @@
         <v>46219.741423611114</v>
       </c>
       <c r="F31" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>28</v>
@@ -3512,7 +3512,7 @@
         <v>46195.59105324074</v>
       </c>
       <c r="F32" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>24</v>
@@ -3580,7 +3580,7 @@
         <v>46201.06361111111</v>
       </c>
       <c r="F33" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>28</v>
@@ -3648,7 +3648,7 @@
         <v>46195.68219907407</v>
       </c>
       <c r="F34" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>24</v>
@@ -3716,7 +3716,7 @@
         <v>46216.18634259259</v>
       </c>
       <c r="F35" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>28</v>
@@ -3725,7 +3725,7 @@
         <v>28</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>25</v>
@@ -3745,8 +3745,8 @@
       <c r="O35" s="0">
         <v>0</v>
       </c>
-      <c r="P35" s="0" t="s">
-        <v>25</v>
+      <c r="P35" s="0">
+        <v>0</v>
       </c>
       <c r="Q35" s="0" t="s">
         <v>25</v>
@@ -3784,7 +3784,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F36" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>24</v>
@@ -3852,7 +3852,7 @@
         <v>46198.5140625</v>
       </c>
       <c r="F37" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>24</v>
@@ -3920,7 +3920,7 @@
         <v>46209.61792824074</v>
       </c>
       <c r="F38" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>31</v>
@@ -3988,7 +3988,7 @@
         <v>46202.38591435185</v>
       </c>
       <c r="F39" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>28</v>
@@ -4024,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="R39" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="0" t="s">
         <v>25</v>
@@ -4056,7 +4056,7 @@
         <v>46215.03915509259</v>
       </c>
       <c r="F40" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>31</v>
@@ -4124,7 +4124,7 @@
         <v>46217.397997685184</v>
       </c>
       <c r="F41" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>24</v>
@@ -4192,7 +4192,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F42" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>24</v>
@@ -4207,7 +4207,7 @@
         <v>24</v>
       </c>
       <c r="K42" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L42" s="0" t="s">
         <v>25</v>
@@ -4227,8 +4227,8 @@
       <c r="Q42" s="0">
         <v>1</v>
       </c>
-      <c r="R42" s="0" t="s">
-        <v>25</v>
+      <c r="R42" s="0">
+        <v>0</v>
       </c>
       <c r="S42" s="0" t="s">
         <v>25</v>
@@ -4260,7 +4260,7 @@
         <v>46205.25707175926</v>
       </c>
       <c r="F43" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>28</v>
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="R43" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" s="0" t="s">
         <v>25</v>
@@ -4328,7 +4328,7 @@
         <v>46203.77983796296</v>
       </c>
       <c r="F44" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>31</v>
@@ -4396,7 +4396,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F45" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>31</v>
@@ -4464,7 +4464,7 @@
         <v>46207.957766203705</v>
       </c>
       <c r="F46" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>31</v>
@@ -4494,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="P46" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="0" t="s">
         <v>25</v>
@@ -4532,7 +4532,7 @@
         <v>46204.23569444445</v>
       </c>
       <c r="F47" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>28</v>
@@ -4568,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="R47" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" s="0" t="s">
         <v>25</v>
@@ -4600,7 +4600,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F48" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>24</v>
@@ -4668,7 +4668,7 @@
         <v>46206.293020833335</v>
       </c>
       <c r="F49" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G49" s="0" t="s">
         <v>31</v>
@@ -4736,7 +4736,7 @@
         <v>46214.75530092593</v>
       </c>
       <c r="F50" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>31</v>
@@ -4804,7 +4804,7 @@
         <v>46198.763715277775</v>
       </c>
       <c r="F51" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>24</v>
@@ -4819,7 +4819,7 @@
         <v>24</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L51" s="0" t="s">
         <v>25</v>
@@ -4839,8 +4839,8 @@
       <c r="Q51" s="0">
         <v>1</v>
       </c>
-      <c r="R51" s="0" t="s">
-        <v>25</v>
+      <c r="R51" s="0">
+        <v>0</v>
       </c>
       <c r="S51" s="0" t="s">
         <v>25</v>
@@ -4872,7 +4872,7 @@
         <v>46205.502962962964</v>
       </c>
       <c r="F52" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>28</v>
@@ -4887,7 +4887,7 @@
         <v>28</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L52" s="0" t="s">
         <v>25</v>
@@ -4907,8 +4907,8 @@
       <c r="Q52" s="0">
         <v>1</v>
       </c>
-      <c r="R52" s="0" t="s">
-        <v>25</v>
+      <c r="R52" s="0">
+        <v>0</v>
       </c>
       <c r="S52" s="0" t="s">
         <v>25</v>
@@ -4940,7 +4940,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F53" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>24</v>
@@ -5008,7 +5008,7 @@
         <v>46214.35975694445</v>
       </c>
       <c r="F54" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>28</v>
@@ -5076,7 +5076,7 @@
         <v>46200.67046296296</v>
       </c>
       <c r="F55" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>24</v>
@@ -5144,7 +5144,7 @@
         <v>46215.29809027778</v>
       </c>
       <c r="F56" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>28</v>
@@ -5212,7 +5212,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F57" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G57" s="0" t="s">
         <v>24</v>
@@ -5224,7 +5224,7 @@
         <v>24</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K57" s="0" t="s">
         <v>25</v>
@@ -5244,8 +5244,8 @@
       <c r="P57" s="0">
         <v>1</v>
       </c>
-      <c r="Q57" s="0" t="s">
-        <v>25</v>
+      <c r="Q57" s="0">
+        <v>0</v>
       </c>
       <c r="R57" s="0" t="s">
         <v>25</v>
@@ -5280,7 +5280,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F58" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>31</v>
@@ -5348,7 +5348,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F59" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>24</v>
@@ -5416,7 +5416,7 @@
         <v>46217.729409722226</v>
       </c>
       <c r="F60" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G60" s="0" t="s">
         <v>24</v>
@@ -5484,7 +5484,7 @@
         <v>46207.76193287037</v>
       </c>
       <c r="F61" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>24</v>
@@ -5496,7 +5496,7 @@
         <v>24</v>
       </c>
       <c r="J61" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K61" s="0" t="s">
         <v>25</v>
@@ -5516,8 +5516,8 @@
       <c r="P61" s="0">
         <v>1</v>
       </c>
-      <c r="Q61" s="0" t="s">
-        <v>25</v>
+      <c r="Q61" s="0">
+        <v>0</v>
       </c>
       <c r="R61" s="0" t="s">
         <v>25</v>
@@ -5552,7 +5552,7 @@
         <v>46199.574282407404</v>
       </c>
       <c r="F62" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>28</v>
@@ -5620,7 +5620,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F63" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>31</v>
@@ -5688,7 +5688,7 @@
         <v>46198.758518518516</v>
       </c>
       <c r="F64" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>24</v>
@@ -5703,7 +5703,7 @@
         <v>24</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L64" s="0" t="s">
         <v>25</v>
@@ -5723,8 +5723,8 @@
       <c r="Q64" s="0">
         <v>1</v>
       </c>
-      <c r="R64" s="0" t="s">
-        <v>25</v>
+      <c r="R64" s="0">
+        <v>0</v>
       </c>
       <c r="S64" s="0" t="s">
         <v>25</v>
@@ -5756,7 +5756,7 @@
         <v>46199.20893518518</v>
       </c>
       <c r="F65" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>28</v>
@@ -5824,7 +5824,7 @@
         <v>46198.76384259259</v>
       </c>
       <c r="F66" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>24</v>
@@ -5839,7 +5839,7 @@
         <v>24</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L66" s="0" t="s">
         <v>25</v>
@@ -5859,8 +5859,8 @@
       <c r="Q66" s="0">
         <v>1</v>
       </c>
-      <c r="R66" s="0" t="s">
-        <v>25</v>
+      <c r="R66" s="0">
+        <v>0</v>
       </c>
       <c r="S66" s="0" t="s">
         <v>25</v>
@@ -5892,7 +5892,7 @@
         <v>46207.98546296296</v>
       </c>
       <c r="F67" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>28</v>
@@ -5960,7 +5960,7 @@
         <v>46198.758414351854</v>
       </c>
       <c r="F68" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>24</v>
@@ -5975,7 +5975,7 @@
         <v>24</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L68" s="0" t="s">
         <v>25</v>
@@ -5995,8 +5995,8 @@
       <c r="Q68" s="0">
         <v>1</v>
       </c>
-      <c r="R68" s="0" t="s">
-        <v>25</v>
+      <c r="R68" s="0">
+        <v>0</v>
       </c>
       <c r="S68" s="0" t="s">
         <v>25</v>
@@ -6028,7 +6028,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F69" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>31</v>
@@ -6096,7 +6096,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F70" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G70" s="0" t="s">
         <v>24</v>
@@ -6164,7 +6164,7 @@
         <v>46207.95777777778</v>
       </c>
       <c r="F71" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G71" s="0" t="s">
         <v>24</v>
@@ -6194,7 +6194,7 @@
         <v>1</v>
       </c>
       <c r="P71" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="0" t="s">
         <v>25</v>
@@ -6232,7 +6232,7 @@
         <v>46217.77034722222</v>
       </c>
       <c r="F72" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>24</v>
@@ -6300,7 +6300,7 @@
         <v>46213.479849537034</v>
       </c>
       <c r="F73" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>28</v>
@@ -6368,7 +6368,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F74" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>24</v>
@@ -6436,7 +6436,7 @@
         <v>46213.89649305555</v>
       </c>
       <c r="F75" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>28</v>
@@ -6504,7 +6504,7 @@
         <v>46194.2578587963</v>
       </c>
       <c r="F76" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>28</v>
@@ -6572,7 +6572,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F77" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>24</v>
@@ -6640,7 +6640,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F78" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>31</v>
@@ -6708,7 +6708,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F79" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>24</v>
@@ -6776,7 +6776,7 @@
         <v>46214.741215277776</v>
       </c>
       <c r="F80" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>28</v>
@@ -6844,7 +6844,7 @@
         <v>46204.816157407404</v>
       </c>
       <c r="F81" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>24</v>
@@ -6856,7 +6856,7 @@
         <v>24</v>
       </c>
       <c r="J81" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K81" s="0" t="s">
         <v>25</v>
@@ -6876,8 +6876,8 @@
       <c r="P81" s="0">
         <v>1</v>
       </c>
-      <c r="Q81" s="0" t="s">
-        <v>25</v>
+      <c r="Q81" s="0">
+        <v>0</v>
       </c>
       <c r="R81" s="0" t="s">
         <v>25</v>
@@ -6912,7 +6912,7 @@
         <v>46210.94122685185</v>
       </c>
       <c r="F82" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>28</v>
@@ -6980,7 +6980,7 @@
         <v>46211.91608796296</v>
       </c>
       <c r="F83" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>28</v>
@@ -6992,7 +6992,7 @@
         <v>28</v>
       </c>
       <c r="J83" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K83" s="0" t="s">
         <v>25</v>
@@ -7012,8 +7012,8 @@
       <c r="P83" s="0">
         <v>1</v>
       </c>
-      <c r="Q83" s="0" t="s">
-        <v>25</v>
+      <c r="Q83" s="0">
+        <v>0</v>
       </c>
       <c r="R83" s="0" t="s">
         <v>25</v>
@@ -7048,7 +7048,7 @@
         <v>46211.9408912037</v>
       </c>
       <c r="F84" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>28</v>
@@ -7060,7 +7060,7 @@
         <v>28</v>
       </c>
       <c r="J84" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K84" s="0" t="s">
         <v>25</v>
@@ -7080,8 +7080,8 @@
       <c r="P84" s="0">
         <v>0</v>
       </c>
-      <c r="Q84" s="0" t="s">
-        <v>25</v>
+      <c r="Q84" s="0">
+        <v>0</v>
       </c>
       <c r="R84" s="0" t="s">
         <v>25</v>
@@ -7116,7 +7116,7 @@
         <v>46198.763449074075</v>
       </c>
       <c r="F85" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>24</v>
@@ -7131,7 +7131,7 @@
         <v>24</v>
       </c>
       <c r="K85" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L85" s="0" t="s">
         <v>25</v>
@@ -7151,8 +7151,8 @@
       <c r="Q85" s="0">
         <v>1</v>
       </c>
-      <c r="R85" s="0" t="s">
-        <v>25</v>
+      <c r="R85" s="0">
+        <v>0</v>
       </c>
       <c r="S85" s="0" t="s">
         <v>25</v>
@@ -7184,7 +7184,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F86" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>31</v>
@@ -7252,7 +7252,7 @@
         <v>46198.758125</v>
       </c>
       <c r="F87" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>24</v>
@@ -7267,7 +7267,7 @@
         <v>24</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L87" s="0" t="s">
         <v>25</v>
@@ -7287,8 +7287,8 @@
       <c r="Q87" s="0">
         <v>1</v>
       </c>
-      <c r="R87" s="0" t="s">
-        <v>25</v>
+      <c r="R87" s="0">
+        <v>0</v>
       </c>
       <c r="S87" s="0" t="s">
         <v>25</v>
@@ -7320,7 +7320,7 @@
         <v>46201.54498842593</v>
       </c>
       <c r="F88" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G88" s="0" t="s">
         <v>28</v>
@@ -7388,7 +7388,7 @@
         <v>46198.76478009259</v>
       </c>
       <c r="F89" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>24</v>
@@ -7403,7 +7403,7 @@
         <v>24</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L89" s="0" t="s">
         <v>25</v>
@@ -7423,8 +7423,8 @@
       <c r="Q89" s="0">
         <v>0</v>
       </c>
-      <c r="R89" s="0" t="s">
-        <v>25</v>
+      <c r="R89" s="0">
+        <v>0</v>
       </c>
       <c r="S89" s="0" t="s">
         <v>25</v>
@@ -7456,7 +7456,7 @@
         <v>46205.76315972222</v>
       </c>
       <c r="F90" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>28</v>
@@ -7524,7 +7524,7 @@
         <v>46204.83986111111</v>
       </c>
       <c r="F91" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>28</v>
@@ -7592,7 +7592,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F92" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>31</v>
@@ -7660,7 +7660,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F93" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>24</v>
@@ -7728,7 +7728,7 @@
         <v>46203.69975694444</v>
       </c>
       <c r="F94" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>31</v>
@@ -7796,7 +7796,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F95" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>24</v>
@@ -7808,7 +7808,7 @@
         <v>24</v>
       </c>
       <c r="J95" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K95" s="0" t="s">
         <v>25</v>
@@ -7828,8 +7828,8 @@
       <c r="P95" s="0">
         <v>1</v>
       </c>
-      <c r="Q95" s="0" t="s">
-        <v>25</v>
+      <c r="Q95" s="0">
+        <v>0</v>
       </c>
       <c r="R95" s="0" t="s">
         <v>25</v>
@@ -7864,7 +7864,7 @@
         <v>46208.10663194444</v>
       </c>
       <c r="F96" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>28</v>
@@ -7932,7 +7932,7 @@
         <v>46200.854166666664</v>
       </c>
       <c r="F97" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>24</v>
@@ -8000,7 +8000,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F98" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G98" s="0" t="s">
         <v>24</v>
@@ -8012,7 +8012,7 @@
         <v>24</v>
       </c>
       <c r="J98" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K98" s="0" t="s">
         <v>25</v>
@@ -8032,8 +8032,8 @@
       <c r="P98" s="0">
         <v>1</v>
       </c>
-      <c r="Q98" s="0" t="s">
-        <v>25</v>
+      <c r="Q98" s="0">
+        <v>0</v>
       </c>
       <c r="R98" s="0" t="s">
         <v>25</v>
@@ -8068,7 +8068,7 @@
         <v>46212.5203125</v>
       </c>
       <c r="F99" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>24</v>
@@ -8136,7 +8136,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F100" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>24</v>
@@ -8204,7 +8204,7 @@
         <v>46205.07099537037</v>
       </c>
       <c r="F101" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>24</v>
@@ -8272,7 +8272,7 @@
         <v>46204.145219907405</v>
       </c>
       <c r="F102" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>24</v>
@@ -8287,7 +8287,7 @@
         <v>24</v>
       </c>
       <c r="K102" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L102" s="0" t="s">
         <v>25</v>
@@ -8307,8 +8307,8 @@
       <c r="Q102" s="0">
         <v>1</v>
       </c>
-      <c r="R102" s="0" t="s">
-        <v>25</v>
+      <c r="R102" s="0">
+        <v>0</v>
       </c>
       <c r="S102" s="0" t="s">
         <v>25</v>
@@ -8340,7 +8340,7 @@
         <v>46191.31182870371</v>
       </c>
       <c r="F103" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>24</v>
@@ -8408,7 +8408,7 @@
         <v>46199.29518518518</v>
       </c>
       <c r="F104" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>28</v>
@@ -8476,7 +8476,7 @@
         <v>46184.345671296294</v>
       </c>
       <c r="F105" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>24</v>
@@ -8488,7 +8488,7 @@
         <v>24</v>
       </c>
       <c r="J105" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K105" s="0" t="s">
         <v>25</v>
@@ -8508,8 +8508,8 @@
       <c r="P105" s="0">
         <v>0</v>
       </c>
-      <c r="Q105" s="0" t="s">
-        <v>25</v>
+      <c r="Q105" s="0">
+        <v>0</v>
       </c>
       <c r="R105" s="0" t="s">
         <v>25</v>
@@ -8544,7 +8544,7 @@
         <v>46218.3812962963</v>
       </c>
       <c r="F106" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>31</v>
@@ -8612,7 +8612,7 @@
         <v>46215.31277777778</v>
       </c>
       <c r="F107" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>28</v>
@@ -8680,7 +8680,7 @@
         <v>46219.47236111111</v>
       </c>
       <c r="F108" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>28</v>
@@ -8748,7 +8748,7 @@
         <v>46198.758576388886</v>
       </c>
       <c r="F109" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>24</v>
@@ -8763,7 +8763,7 @@
         <v>24</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L109" s="0" t="s">
         <v>25</v>
@@ -8783,8 +8783,8 @@
       <c r="Q109" s="0">
         <v>1</v>
       </c>
-      <c r="R109" s="0" t="s">
-        <v>25</v>
+      <c r="R109" s="0">
+        <v>0</v>
       </c>
       <c r="S109" s="0" t="s">
         <v>25</v>
@@ -8816,7 +8816,7 @@
         <v>46211.747719907406</v>
       </c>
       <c r="F110" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>24</v>
@@ -8828,7 +8828,7 @@
         <v>24</v>
       </c>
       <c r="J110" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K110" s="0" t="s">
         <v>25</v>
@@ -8848,8 +8848,8 @@
       <c r="P110" s="0">
         <v>1</v>
       </c>
-      <c r="Q110" s="0" t="s">
-        <v>25</v>
+      <c r="Q110" s="0">
+        <v>0</v>
       </c>
       <c r="R110" s="0" t="s">
         <v>25</v>
@@ -8884,7 +8884,7 @@
         <v>46196.6612962963</v>
       </c>
       <c r="F111" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>31</v>
@@ -8952,7 +8952,7 @@
         <v>46203.386967592596</v>
       </c>
       <c r="F112" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>24</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="R112" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S112" s="0" t="s">
         <v>25</v>
@@ -9020,7 +9020,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F113" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>28</v>
@@ -9088,7 +9088,7 @@
         <v>46202.30238425926</v>
       </c>
       <c r="F114" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>28</v>
@@ -9156,7 +9156,7 @@
         <v>46210.49642361111</v>
       </c>
       <c r="F115" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>31</v>
@@ -9224,7 +9224,7 @@
         <v>46208.76116898148</v>
       </c>
       <c r="F116" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>31</v>
@@ -9292,7 +9292,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F117" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>24</v>
@@ -9360,7 +9360,7 @@
         <v>46217.79634259259</v>
       </c>
       <c r="F118" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>31</v>
@@ -9428,7 +9428,7 @@
         <v>46217.76349537037</v>
       </c>
       <c r="F119" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>24</v>
@@ -9496,7 +9496,7 @@
         <v>46198.007743055554</v>
       </c>
       <c r="F120" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>24</v>
@@ -9564,7 +9564,7 @@
         <v>46204.82892361111</v>
       </c>
       <c r="F121" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>24</v>
@@ -9579,7 +9579,7 @@
         <v>24</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L121" s="0" t="s">
         <v>25</v>
@@ -9599,8 +9599,8 @@
       <c r="Q121" s="0">
         <v>1</v>
       </c>
-      <c r="R121" s="0" t="s">
-        <v>25</v>
+      <c r="R121" s="0">
+        <v>0</v>
       </c>
       <c r="S121" s="0" t="s">
         <v>25</v>
@@ -9632,7 +9632,7 @@
         <v>46211.026354166665</v>
       </c>
       <c r="F122" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>24</v>
@@ -9700,7 +9700,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F123" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>31</v>
@@ -9768,7 +9768,7 @@
         <v>46206.49621527778</v>
       </c>
       <c r="F124" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>28</v>
@@ -9783,7 +9783,7 @@
         <v>28</v>
       </c>
       <c r="K124" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L124" s="0" t="s">
         <v>25</v>
@@ -9803,8 +9803,8 @@
       <c r="Q124" s="0">
         <v>1</v>
       </c>
-      <c r="R124" s="0" t="s">
-        <v>25</v>
+      <c r="R124" s="0">
+        <v>0</v>
       </c>
       <c r="S124" s="0" t="s">
         <v>25</v>
@@ -9836,7 +9836,7 @@
         <v>46194.10880787037</v>
       </c>
       <c r="F125" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>24</v>
@@ -9904,7 +9904,7 @@
         <v>46220.05306712963</v>
       </c>
       <c r="F126" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>28</v>
@@ -9972,7 +9972,7 @@
         <v>46202.80762731482</v>
       </c>
       <c r="F127" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>28</v>
@@ -10008,7 +10008,7 @@
         <v>0</v>
       </c>
       <c r="R127" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S127" s="0" t="s">
         <v>25</v>
@@ -10040,7 +10040,7 @@
         <v>46212.191030092596</v>
       </c>
       <c r="F128" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>28</v>
@@ -10052,7 +10052,7 @@
         <v>28</v>
       </c>
       <c r="J128" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K128" s="0" t="s">
         <v>25</v>
@@ -10072,8 +10072,8 @@
       <c r="P128" s="0">
         <v>1</v>
       </c>
-      <c r="Q128" s="0" t="s">
-        <v>25</v>
+      <c r="Q128" s="0">
+        <v>0</v>
       </c>
       <c r="R128" s="0" t="s">
         <v>25</v>
@@ -10108,7 +10108,7 @@
         <v>46214.51880787037</v>
       </c>
       <c r="F129" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>28</v>
@@ -10176,7 +10176,7 @@
         <v>46198.053506944445</v>
       </c>
       <c r="F130" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>28</v>
@@ -10244,7 +10244,7 @@
         <v>46217.92925925926</v>
       </c>
       <c r="F131" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>24</v>
@@ -10312,7 +10312,7 @@
         <v>46208.01679398148</v>
       </c>
       <c r="F132" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>28</v>
@@ -10345,7 +10345,7 @@
         <v>1</v>
       </c>
       <c r="Q132" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R132" s="0" t="s">
         <v>25</v>
@@ -10380,7 +10380,7 @@
         <v>46199.4216087963</v>
       </c>
       <c r="F133" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>31</v>
@@ -10448,7 +10448,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F134" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>31</v>
@@ -10516,7 +10516,7 @@
         <v>46218.91337962963</v>
       </c>
       <c r="F135" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F136" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>24</v>
@@ -10652,7 +10652,7 @@
         <v>46203.398622685185</v>
       </c>
       <c r="F137" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>24</v>
@@ -10667,7 +10667,7 @@
         <v>24</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L137" s="0" t="s">
         <v>25</v>
@@ -10687,8 +10687,8 @@
       <c r="Q137" s="0">
         <v>1</v>
       </c>
-      <c r="R137" s="0" t="s">
-        <v>25</v>
+      <c r="R137" s="0">
+        <v>0</v>
       </c>
       <c r="S137" s="0" t="s">
         <v>25</v>
@@ -10720,7 +10720,7 @@
         <v>46204.071388888886</v>
       </c>
       <c r="F138" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>24</v>
@@ -10788,7 +10788,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F139" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>24</v>
@@ -10800,7 +10800,7 @@
         <v>24</v>
       </c>
       <c r="J139" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K139" s="0" t="s">
         <v>25</v>
@@ -10820,8 +10820,8 @@
       <c r="P139" s="0">
         <v>1</v>
       </c>
-      <c r="Q139" s="0" t="s">
-        <v>25</v>
+      <c r="Q139" s="0">
+        <v>0</v>
       </c>
       <c r="R139" s="0" t="s">
         <v>25</v>
@@ -10856,7 +10856,7 @@
         <v>46207.340208333335</v>
       </c>
       <c r="F140" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>28</v>
@@ -10871,7 +10871,7 @@
         <v>28</v>
       </c>
       <c r="K140" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L140" s="0" t="s">
         <v>25</v>
@@ -10891,8 +10891,8 @@
       <c r="Q140" s="0">
         <v>0</v>
       </c>
-      <c r="R140" s="0" t="s">
-        <v>25</v>
+      <c r="R140" s="0">
+        <v>0</v>
       </c>
       <c r="S140" s="0" t="s">
         <v>25</v>
@@ -10924,7 +10924,7 @@
         <v>46203.22761574074</v>
       </c>
       <c r="F141" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G141" s="0" t="s">
         <v>28</v>
@@ -10939,7 +10939,7 @@
         <v>28</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L141" s="0" t="s">
         <v>25</v>
@@ -10959,8 +10959,8 @@
       <c r="Q141" s="0">
         <v>0</v>
       </c>
-      <c r="R141" s="0" t="s">
-        <v>25</v>
+      <c r="R141" s="0">
+        <v>0</v>
       </c>
       <c r="S141" s="0" t="s">
         <v>25</v>
@@ -10992,7 +10992,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F142" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>28</v>
@@ -11060,7 +11060,7 @@
         <v>46209.27856481481</v>
       </c>
       <c r="F143" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>28</v>
@@ -11128,7 +11128,7 @@
         <v>46203.241944444446</v>
       </c>
       <c r="F144" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>28</v>
@@ -11196,7 +11196,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F145" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>24</v>
@@ -11264,7 +11264,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F146" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>24</v>
@@ -11332,7 +11332,7 @@
         <v>46200.90429398148</v>
       </c>
       <c r="F147" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>24</v>
@@ -11400,7 +11400,7 @@
         <v>46201.17297453704</v>
       </c>
       <c r="F148" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>28</v>
@@ -11436,7 +11436,7 @@
         <v>1</v>
       </c>
       <c r="R148" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S148" s="0" t="s">
         <v>25</v>
@@ -11468,7 +11468,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F149" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>24</v>
@@ -11536,7 +11536,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F150" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>24</v>
@@ -11604,7 +11604,7 @@
         <v>46197.398356481484</v>
       </c>
       <c r="F151" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>24</v>
@@ -11672,7 +11672,7 @@
         <v>46216.91412037037</v>
       </c>
       <c r="F152" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>24</v>
@@ -11740,7 +11740,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F153" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>24</v>
@@ -11755,7 +11755,7 @@
         <v>24</v>
       </c>
       <c r="K153" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L153" s="0" t="s">
         <v>25</v>
@@ -11775,8 +11775,8 @@
       <c r="Q153" s="0">
         <v>1</v>
       </c>
-      <c r="R153" s="0" t="s">
-        <v>25</v>
+      <c r="R153" s="0">
+        <v>0</v>
       </c>
       <c r="S153" s="0" t="s">
         <v>25</v>
@@ -11808,7 +11808,7 @@
         <v>46204.81618055556</v>
       </c>
       <c r="F154" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>24</v>
@@ -11820,7 +11820,7 @@
         <v>24</v>
       </c>
       <c r="J154" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K154" s="0" t="s">
         <v>25</v>
@@ -11840,8 +11840,8 @@
       <c r="P154" s="0">
         <v>1</v>
       </c>
-      <c r="Q154" s="0" t="s">
-        <v>25</v>
+      <c r="Q154" s="0">
+        <v>0</v>
       </c>
       <c r="R154" s="0" t="s">
         <v>25</v>
@@ -11876,7 +11876,7 @@
         <v>46184.345671296294</v>
       </c>
       <c r="F155" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>24</v>
@@ -11888,7 +11888,7 @@
         <v>24</v>
       </c>
       <c r="J155" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K155" s="0" t="s">
         <v>25</v>
@@ -11908,8 +11908,8 @@
       <c r="P155" s="0">
         <v>0</v>
       </c>
-      <c r="Q155" s="0" t="s">
-        <v>25</v>
+      <c r="Q155" s="0">
+        <v>0</v>
       </c>
       <c r="R155" s="0" t="s">
         <v>25</v>
@@ -11944,7 +11944,7 @@
         <v>46198.76695601852</v>
       </c>
       <c r="F156" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>24</v>
@@ -11959,7 +11959,7 @@
         <v>24</v>
       </c>
       <c r="K156" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L156" s="0" t="s">
         <v>25</v>
@@ -11979,8 +11979,8 @@
       <c r="Q156" s="0">
         <v>1</v>
       </c>
-      <c r="R156" s="0" t="s">
-        <v>25</v>
+      <c r="R156" s="0">
+        <v>0</v>
       </c>
       <c r="S156" s="0" t="s">
         <v>25</v>
@@ -12012,7 +12012,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F157" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G157" s="0" t="s">
         <v>24</v>
@@ -12080,7 +12080,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F158" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G158" s="0" t="s">
         <v>31</v>
@@ -12095,7 +12095,7 @@
         <v>31</v>
       </c>
       <c r="K158" s="0" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L158" s="0" t="s">
         <v>25</v>
@@ -12115,8 +12115,8 @@
       <c r="Q158" s="0">
         <v>1</v>
       </c>
-      <c r="R158" s="0" t="s">
-        <v>25</v>
+      <c r="R158" s="0">
+        <v>0</v>
       </c>
       <c r="S158" s="0" t="s">
         <v>25</v>
@@ -12148,7 +12148,7 @@
         <v>46207.38381944445</v>
       </c>
       <c r="F159" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>28</v>
@@ -12163,7 +12163,7 @@
         <v>28</v>
       </c>
       <c r="K159" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L159" s="0" t="s">
         <v>25</v>
@@ -12183,8 +12183,8 @@
       <c r="Q159" s="0">
         <v>1</v>
       </c>
-      <c r="R159" s="0" t="s">
-        <v>25</v>
+      <c r="R159" s="0">
+        <v>0</v>
       </c>
       <c r="S159" s="0" t="s">
         <v>25</v>
@@ -12216,7 +12216,7 @@
         <v>46198.764710648145</v>
       </c>
       <c r="F160" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>24</v>
@@ -12231,7 +12231,7 @@
         <v>24</v>
       </c>
       <c r="K160" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L160" s="0" t="s">
         <v>25</v>
@@ -12251,8 +12251,8 @@
       <c r="Q160" s="0">
         <v>1</v>
       </c>
-      <c r="R160" s="0" t="s">
-        <v>25</v>
+      <c r="R160" s="0">
+        <v>0</v>
       </c>
       <c r="S160" s="0" t="s">
         <v>25</v>
@@ -12284,7 +12284,7 @@
         <v>46208.60445601852</v>
       </c>
       <c r="F161" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>28</v>
@@ -12352,7 +12352,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F162" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>31</v>
@@ -12367,7 +12367,7 @@
         <v>31</v>
       </c>
       <c r="K162" s="0" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L162" s="0" t="s">
         <v>25</v>
@@ -12387,8 +12387,8 @@
       <c r="Q162" s="0">
         <v>1</v>
       </c>
-      <c r="R162" s="0" t="s">
-        <v>25</v>
+      <c r="R162" s="0">
+        <v>0</v>
       </c>
       <c r="S162" s="0" t="s">
         <v>25</v>
@@ -12420,7 +12420,7 @@
         <v>46198.7566087963</v>
       </c>
       <c r="F163" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>24</v>
@@ -12435,7 +12435,7 @@
         <v>24</v>
       </c>
       <c r="K163" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L163" s="0" t="s">
         <v>25</v>
@@ -12455,8 +12455,8 @@
       <c r="Q163" s="0">
         <v>1</v>
       </c>
-      <c r="R163" s="0" t="s">
-        <v>25</v>
+      <c r="R163" s="0">
+        <v>0</v>
       </c>
       <c r="S163" s="0" t="s">
         <v>25</v>
@@ -12488,7 +12488,7 @@
         <v>46204.591203703705</v>
       </c>
       <c r="F164" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>28</v>
@@ -12500,7 +12500,7 @@
         <v>28</v>
       </c>
       <c r="J164" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K164" s="0" t="s">
         <v>25</v>
@@ -12520,8 +12520,8 @@
       <c r="P164" s="0">
         <v>1</v>
       </c>
-      <c r="Q164" s="0" t="s">
-        <v>25</v>
+      <c r="Q164" s="0">
+        <v>0</v>
       </c>
       <c r="R164" s="0" t="s">
         <v>25</v>
@@ -12556,7 +12556,7 @@
         <v>46203.38690972222</v>
       </c>
       <c r="F165" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>24</v>
@@ -12592,7 +12592,7 @@
         <v>1</v>
       </c>
       <c r="R165" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S165" s="0" t="s">
         <v>25</v>
@@ -12624,7 +12624,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F166" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>24</v>
@@ -12692,7 +12692,7 @@
         <v>46217.32613425926</v>
       </c>
       <c r="F167" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>28</v>
@@ -12701,7 +12701,7 @@
         <v>28</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J167" s="0" t="s">
         <v>25</v>
@@ -12721,8 +12721,8 @@
       <c r="O167" s="0">
         <v>0</v>
       </c>
-      <c r="P167" s="0" t="s">
-        <v>25</v>
+      <c r="P167" s="0">
+        <v>0</v>
       </c>
       <c r="Q167" s="0" t="s">
         <v>25</v>
@@ -12760,7 +12760,7 @@
         <v>46199.954201388886</v>
       </c>
       <c r="F168" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>28</v>
@@ -12828,7 +12828,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F169" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>31</v>
@@ -12843,7 +12843,7 @@
         <v>31</v>
       </c>
       <c r="K169" s="0" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L169" s="0" t="s">
         <v>25</v>
@@ -12863,8 +12863,8 @@
       <c r="Q169" s="0">
         <v>1</v>
       </c>
-      <c r="R169" s="0" t="s">
-        <v>25</v>
+      <c r="R169" s="0">
+        <v>0</v>
       </c>
       <c r="S169" s="0" t="s">
         <v>25</v>
@@ -12896,7 +12896,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F170" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>24</v>
@@ -12964,7 +12964,7 @@
         <v>46193.45674768519</v>
       </c>
       <c r="F171" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>24</v>
@@ -13032,7 +13032,7 @@
         <v>46211.339479166665</v>
       </c>
       <c r="F172" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>24</v>
@@ -13065,7 +13065,7 @@
         <v>0</v>
       </c>
       <c r="Q172" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R172" s="0" t="s">
         <v>25</v>
@@ -13100,7 +13100,7 @@
         <v>46184.344409722224</v>
       </c>
       <c r="F173" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>24</v>
@@ -13112,7 +13112,7 @@
         <v>24</v>
       </c>
       <c r="J173" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K173" s="0" t="s">
         <v>25</v>
@@ -13132,8 +13132,8 @@
       <c r="P173" s="0">
         <v>0</v>
       </c>
-      <c r="Q173" s="0" t="s">
-        <v>25</v>
+      <c r="Q173" s="0">
+        <v>0</v>
       </c>
       <c r="R173" s="0" t="s">
         <v>25</v>
@@ -13168,7 +13168,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F174" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>31</v>
@@ -13236,7 +13236,7 @@
         <v>46217.72965277778</v>
       </c>
       <c r="F175" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>24</v>
@@ -13304,7 +13304,7 @@
         <v>46196.43208333333</v>
       </c>
       <c r="F176" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>28</v>
@@ -13372,7 +13372,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F177" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>31</v>
@@ -13440,7 +13440,7 @@
         <v>46204.591203703705</v>
       </c>
       <c r="F178" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>28</v>
@@ -13452,7 +13452,7 @@
         <v>28</v>
       </c>
       <c r="J178" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K178" s="0" t="s">
         <v>25</v>
@@ -13472,8 +13472,8 @@
       <c r="P178" s="0">
         <v>1</v>
       </c>
-      <c r="Q178" s="0" t="s">
-        <v>25</v>
+      <c r="Q178" s="0">
+        <v>0</v>
       </c>
       <c r="R178" s="0" t="s">
         <v>25</v>
@@ -13508,7 +13508,7 @@
         <v>46212.38707175926</v>
       </c>
       <c r="F179" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>28</v>
@@ -13576,7 +13576,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F180" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G180" s="0" t="s">
         <v>31</v>
@@ -13644,7 +13644,7 @@
         <v>46219.39318287037</v>
       </c>
       <c r="F181" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>46205.85377314815</v>
       </c>
       <c r="F182" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>24</v>
@@ -13727,7 +13727,7 @@
         <v>24</v>
       </c>
       <c r="K182" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L182" s="0" t="s">
         <v>25</v>
@@ -13747,8 +13747,8 @@
       <c r="Q182" s="0">
         <v>1</v>
       </c>
-      <c r="R182" s="0" t="s">
-        <v>25</v>
+      <c r="R182" s="0">
+        <v>0</v>
       </c>
       <c r="S182" s="0" t="s">
         <v>25</v>
@@ -13780,7 +13780,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F183" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>24</v>
@@ -13792,7 +13792,7 @@
         <v>24</v>
       </c>
       <c r="J183" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K183" s="0" t="s">
         <v>25</v>
@@ -13812,8 +13812,8 @@
       <c r="P183" s="0">
         <v>1</v>
       </c>
-      <c r="Q183" s="0" t="s">
-        <v>25</v>
+      <c r="Q183" s="0">
+        <v>0</v>
       </c>
       <c r="R183" s="0" t="s">
         <v>25</v>
@@ -13848,7 +13848,7 @@
         <v>46194.496782407405</v>
       </c>
       <c r="F184" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>31</v>
@@ -13916,7 +13916,7 @@
         <v>46206.041817129626</v>
       </c>
       <c r="F185" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>28</v>
@@ -13984,7 +13984,7 @@
         <v>46211.74564814815</v>
       </c>
       <c r="F186" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G186" s="0" t="s">
         <v>24</v>
@@ -13996,7 +13996,7 @@
         <v>24</v>
       </c>
       <c r="J186" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K186" s="0" t="s">
         <v>25</v>
@@ -14016,8 +14016,8 @@
       <c r="P186" s="0">
         <v>1</v>
       </c>
-      <c r="Q186" s="0" t="s">
-        <v>25</v>
+      <c r="Q186" s="0">
+        <v>0</v>
       </c>
       <c r="R186" s="0" t="s">
         <v>25</v>
@@ -14052,7 +14052,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F187" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>24</v>
@@ -14120,7 +14120,7 @@
         <v>46198.76357638889</v>
       </c>
       <c r="F188" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>24</v>
@@ -14135,7 +14135,7 @@
         <v>24</v>
       </c>
       <c r="K188" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L188" s="0" t="s">
         <v>25</v>
@@ -14155,8 +14155,8 @@
       <c r="Q188" s="0">
         <v>1</v>
       </c>
-      <c r="R188" s="0" t="s">
-        <v>25</v>
+      <c r="R188" s="0">
+        <v>0</v>
       </c>
       <c r="S188" s="0" t="s">
         <v>25</v>
@@ -14188,7 +14188,7 @@
         <v>46214.41127314815</v>
       </c>
       <c r="F189" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>28</v>
@@ -14256,7 +14256,7 @@
         <v>46210.39944444445</v>
       </c>
       <c r="F190" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>24</v>
@@ -14286,7 +14286,7 @@
         <v>1</v>
       </c>
       <c r="P190" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q190" s="0" t="s">
         <v>25</v>
@@ -14324,7 +14324,7 @@
         <v>46219.765706018516</v>
       </c>
       <c r="F191" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>24</v>
@@ -14392,7 +14392,7 @@
         <v>46203.900046296294</v>
       </c>
       <c r="F192" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>31</v>
@@ -14407,7 +14407,7 @@
         <v>31</v>
       </c>
       <c r="K192" s="0" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L192" s="0" t="s">
         <v>25</v>
@@ -14427,8 +14427,8 @@
       <c r="Q192" s="0">
         <v>0</v>
       </c>
-      <c r="R192" s="0" t="s">
-        <v>25</v>
+      <c r="R192" s="0">
+        <v>0</v>
       </c>
       <c r="S192" s="0" t="s">
         <v>25</v>
@@ -14460,7 +14460,7 @@
         <v>46198.75818287037</v>
       </c>
       <c r="F193" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>24</v>
@@ -14475,7 +14475,7 @@
         <v>24</v>
       </c>
       <c r="K193" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L193" s="0" t="s">
         <v>25</v>
@@ -14495,8 +14495,8 @@
       <c r="Q193" s="0">
         <v>0</v>
       </c>
-      <c r="R193" s="0" t="s">
-        <v>25</v>
+      <c r="R193" s="0">
+        <v>0</v>
       </c>
       <c r="S193" s="0" t="s">
         <v>25</v>
@@ -14528,7 +14528,7 @@
         <v>46199.24039351852</v>
       </c>
       <c r="F194" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G194" s="0" t="s">
         <v>28</v>
@@ -14596,7 +14596,7 @@
         <v>46207.7878125</v>
       </c>
       <c r="F195" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G195" s="0" t="s">
         <v>28</v>
@@ -14664,7 +14664,7 @@
         <v>46200.88856481481</v>
       </c>
       <c r="F196" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G196" s="0" t="s">
         <v>31</v>
@@ -14732,7 +14732,7 @@
         <v>46207.091145833336</v>
       </c>
       <c r="F197" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G197" s="0" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>28</v>
       </c>
       <c r="K197" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L197" s="0" t="s">
         <v>25</v>
@@ -14767,8 +14767,8 @@
       <c r="Q197" s="0">
         <v>0</v>
       </c>
-      <c r="R197" s="0" t="s">
-        <v>25</v>
+      <c r="R197" s="0">
+        <v>0</v>
       </c>
       <c r="S197" s="0" t="s">
         <v>25</v>
@@ -14800,7 +14800,7 @@
         <v>46209.81253472222</v>
       </c>
       <c r="F198" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G198" s="0" t="s">
         <v>24</v>
@@ -14833,7 +14833,7 @@
         <v>0</v>
       </c>
       <c r="Q198" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R198" s="0" t="s">
         <v>25</v>
@@ -14868,7 +14868,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F199" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>24</v>
@@ -14880,7 +14880,7 @@
         <v>24</v>
       </c>
       <c r="J199" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K199" s="0" t="s">
         <v>25</v>
@@ -14900,8 +14900,8 @@
       <c r="P199" s="0">
         <v>1</v>
       </c>
-      <c r="Q199" s="0" t="s">
-        <v>25</v>
+      <c r="Q199" s="0">
+        <v>0</v>
       </c>
       <c r="R199" s="0" t="s">
         <v>25</v>
@@ -14936,7 +14936,7 @@
         <v>46208.76133101852</v>
       </c>
       <c r="F200" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>24</v>
@@ -15004,7 +15004,7 @@
         <v>46197.33201388889</v>
       </c>
       <c r="F201" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>24</v>
@@ -15072,7 +15072,7 @@
         <v>46210.11184027778</v>
       </c>
       <c r="F202" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>24</v>
@@ -15084,7 +15084,7 @@
         <v>24</v>
       </c>
       <c r="J202" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K202" s="0" t="s">
         <v>25</v>
@@ -15104,8 +15104,8 @@
       <c r="P202" s="0">
         <v>0</v>
       </c>
-      <c r="Q202" s="0" t="s">
-        <v>25</v>
+      <c r="Q202" s="0">
+        <v>0</v>
       </c>
       <c r="R202" s="0" t="s">
         <v>25</v>
@@ -15140,7 +15140,7 @@
         <v>46202.603946759256</v>
       </c>
       <c r="F203" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>24</v>
@@ -15208,7 +15208,7 @@
         <v>46208.28020833333</v>
       </c>
       <c r="F204" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>31</v>
@@ -15276,7 +15276,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F205" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>24</v>
@@ -15291,7 +15291,7 @@
         <v>24</v>
       </c>
       <c r="K205" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L205" s="0" t="s">
         <v>25</v>
@@ -15311,8 +15311,8 @@
       <c r="Q205" s="0">
         <v>1</v>
       </c>
-      <c r="R205" s="0" t="s">
-        <v>25</v>
+      <c r="R205" s="0">
+        <v>0</v>
       </c>
       <c r="S205" s="0" t="s">
         <v>25</v>
@@ -15344,7 +15344,7 @@
         <v>46187.9200462963</v>
       </c>
       <c r="F206" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>24</v>
@@ -15374,7 +15374,7 @@
         <v>0</v>
       </c>
       <c r="P206" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q206" s="0" t="s">
         <v>25</v>
@@ -15412,7 +15412,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F207" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G207" s="0" t="s">
         <v>31</v>
@@ -15480,7 +15480,7 @@
         <v>46204.36974537037</v>
       </c>
       <c r="F208" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G208" s="0" t="s">
         <v>28</v>
@@ -15548,7 +15548,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F209" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G209" s="0" t="s">
         <v>24</v>
@@ -15616,7 +15616,7 @@
         <v>46201.332870370374</v>
       </c>
       <c r="F210" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>24</v>
@@ -15652,7 +15652,7 @@
         <v>1</v>
       </c>
       <c r="R210" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S210" s="0" t="s">
         <v>25</v>
@@ -15684,7 +15684,7 @@
         <v>46197.03113425926</v>
       </c>
       <c r="F211" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>24</v>
@@ -15752,7 +15752,7 @@
         <v>46212.285219907404</v>
       </c>
       <c r="F212" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="P212" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q212" s="0" t="s">
         <v>25</v>
@@ -15820,7 +15820,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F213" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>24</v>
@@ -15888,7 +15888,7 @@
         <v>46200.98619212963</v>
       </c>
       <c r="F214" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>28</v>
@@ -15956,7 +15956,7 @@
         <v>46212.06758101852</v>
       </c>
       <c r="F215" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>28</v>
@@ -15968,7 +15968,7 @@
         <v>28</v>
       </c>
       <c r="J215" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K215" s="0" t="s">
         <v>25</v>
@@ -15988,8 +15988,8 @@
       <c r="P215" s="0">
         <v>0</v>
       </c>
-      <c r="Q215" s="0" t="s">
-        <v>25</v>
+      <c r="Q215" s="0">
+        <v>0</v>
       </c>
       <c r="R215" s="0" t="s">
         <v>25</v>
@@ -16024,7 +16024,7 @@
         <v>46207.18613425926</v>
       </c>
       <c r="F216" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>28</v>
@@ -16092,7 +16092,7 @@
         <v>46218.881574074076</v>
       </c>
       <c r="F217" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>31</v>
@@ -16160,7 +16160,7 @@
         <v>46210.8569212963</v>
       </c>
       <c r="F218" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>28</v>
@@ -16193,7 +16193,7 @@
         <v>1</v>
       </c>
       <c r="Q218" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R218" s="0" t="s">
         <v>25</v>
@@ -16228,7 +16228,7 @@
         <v>46198.763344907406</v>
       </c>
       <c r="F219" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>24</v>
@@ -16243,7 +16243,7 @@
         <v>24</v>
       </c>
       <c r="K219" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L219" s="0" t="s">
         <v>25</v>
@@ -16263,8 +16263,8 @@
       <c r="Q219" s="0">
         <v>1</v>
       </c>
-      <c r="R219" s="0" t="s">
-        <v>25</v>
+      <c r="R219" s="0">
+        <v>0</v>
       </c>
       <c r="S219" s="0" t="s">
         <v>25</v>
@@ -16296,7 +16296,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F220" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G220" s="0" t="s">
         <v>24</v>
@@ -16308,7 +16308,7 @@
         <v>24</v>
       </c>
       <c r="J220" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K220" s="0" t="s">
         <v>25</v>
@@ -16328,8 +16328,8 @@
       <c r="P220" s="0">
         <v>1</v>
       </c>
-      <c r="Q220" s="0" t="s">
-        <v>25</v>
+      <c r="Q220" s="0">
+        <v>0</v>
       </c>
       <c r="R220" s="0" t="s">
         <v>25</v>
@@ -16364,7 +16364,7 @@
         <v>46198.86886574074</v>
       </c>
       <c r="F221" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>28</v>
@@ -16432,7 +16432,7 @@
         <v>46198.76422453704</v>
       </c>
       <c r="F222" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>24</v>
@@ -16447,7 +16447,7 @@
         <v>24</v>
       </c>
       <c r="K222" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L222" s="0" t="s">
         <v>25</v>
@@ -16467,8 +16467,8 @@
       <c r="Q222" s="0">
         <v>1</v>
       </c>
-      <c r="R222" s="0" t="s">
-        <v>25</v>
+      <c r="R222" s="0">
+        <v>0</v>
       </c>
       <c r="S222" s="0" t="s">
         <v>25</v>
@@ -16500,7 +16500,7 @@
         <v>46206.29314814815</v>
       </c>
       <c r="F223" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>31</v>
@@ -16568,7 +16568,7 @@
         <v>46206.39832175926</v>
       </c>
       <c r="F224" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>28</v>
@@ -16583,7 +16583,7 @@
         <v>28</v>
       </c>
       <c r="K224" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L224" s="0" t="s">
         <v>25</v>
@@ -16603,8 +16603,8 @@
       <c r="Q224" s="0">
         <v>1</v>
       </c>
-      <c r="R224" s="0" t="s">
-        <v>25</v>
+      <c r="R224" s="0">
+        <v>0</v>
       </c>
       <c r="S224" s="0" t="s">
         <v>25</v>
@@ -16636,7 +16636,7 @@
         <v>46201.828206018516</v>
       </c>
       <c r="F225" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>28</v>
@@ -16704,7 +16704,7 @@
         <v>46198.13486111111</v>
       </c>
       <c r="F226" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>24</v>
@@ -16772,7 +16772,7 @@
         <v>46184.34568287037</v>
       </c>
       <c r="F227" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>24</v>
@@ -16784,7 +16784,7 @@
         <v>24</v>
       </c>
       <c r="J227" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K227" s="0" t="s">
         <v>25</v>
@@ -16804,8 +16804,8 @@
       <c r="P227" s="0">
         <v>0</v>
       </c>
-      <c r="Q227" s="0" t="s">
-        <v>25</v>
+      <c r="Q227" s="0">
+        <v>0</v>
       </c>
       <c r="R227" s="0" t="s">
         <v>25</v>
@@ -16840,7 +16840,7 @@
         <v>46217.38422453704</v>
       </c>
       <c r="F228" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G228" s="0" t="s">
         <v>28</v>
@@ -16908,7 +16908,7 @@
         <v>46198.487546296295</v>
       </c>
       <c r="F229" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>28</v>
@@ -16976,7 +16976,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F230" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>24</v>
@@ -16988,7 +16988,7 @@
         <v>24</v>
       </c>
       <c r="J230" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K230" s="0" t="s">
         <v>25</v>
@@ -17008,8 +17008,8 @@
       <c r="P230" s="0">
         <v>1</v>
       </c>
-      <c r="Q230" s="0" t="s">
-        <v>25</v>
+      <c r="Q230" s="0">
+        <v>0</v>
       </c>
       <c r="R230" s="0" t="s">
         <v>25</v>
@@ -17044,7 +17044,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F231" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G231" s="0" t="s">
         <v>24</v>
@@ -17056,7 +17056,7 @@
         <v>24</v>
       </c>
       <c r="J231" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K231" s="0" t="s">
         <v>25</v>
@@ -17076,8 +17076,8 @@
       <c r="P231" s="0">
         <v>1</v>
       </c>
-      <c r="Q231" s="0" t="s">
-        <v>25</v>
+      <c r="Q231" s="0">
+        <v>0</v>
       </c>
       <c r="R231" s="0" t="s">
         <v>25</v>
@@ -17112,7 +17112,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F232" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>28</v>
@@ -17180,7 +17180,7 @@
         <v>46199.37</v>
       </c>
       <c r="F233" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>28</v>
@@ -17248,7 +17248,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F234" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G234" s="0" t="s">
         <v>31</v>
@@ -17316,7 +17316,7 @@
         <v>46200.507418981484</v>
       </c>
       <c r="F235" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G235" s="0" t="s">
         <v>28</v>
@@ -17384,7 +17384,7 @@
         <v>46208.7612037037</v>
       </c>
       <c r="F236" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>31</v>
@@ -17452,7 +17452,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F237" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>31</v>
@@ -17520,7 +17520,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F238" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G238" s="0" t="s">
         <v>24</v>
@@ -17532,7 +17532,7 @@
         <v>24</v>
       </c>
       <c r="J238" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K238" s="0" t="s">
         <v>25</v>
@@ -17552,8 +17552,8 @@
       <c r="P238" s="0">
         <v>1</v>
       </c>
-      <c r="Q238" s="0" t="s">
-        <v>25</v>
+      <c r="Q238" s="0">
+        <v>0</v>
       </c>
       <c r="R238" s="0" t="s">
         <v>25</v>
@@ -17588,7 +17588,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F239" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G239" s="0" t="s">
         <v>24</v>
@@ -17656,7 +17656,7 @@
         <v>46218.09614583333</v>
       </c>
       <c r="F240" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>31</v>
@@ -17724,7 +17724,7 @@
         <v>46206.616875</v>
       </c>
       <c r="F241" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G241" s="0" t="s">
         <v>28</v>
@@ -17757,7 +17757,7 @@
         <v>1</v>
       </c>
       <c r="Q241" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R241" s="0" t="s">
         <v>25</v>
@@ -17792,7 +17792,7 @@
         <v>46206.85376157407</v>
       </c>
       <c r="F242" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G242" s="0" t="s">
         <v>24</v>
@@ -17860,7 +17860,7 @@
         <v>46220.37621527778</v>
       </c>
       <c r="F243" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>28</v>
@@ -17928,7 +17928,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F244" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G244" s="0" t="s">
         <v>24</v>
@@ -17940,7 +17940,7 @@
         <v>24</v>
       </c>
       <c r="J244" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K244" s="0" t="s">
         <v>25</v>
@@ -17960,8 +17960,8 @@
       <c r="P244" s="0">
         <v>1</v>
       </c>
-      <c r="Q244" s="0" t="s">
-        <v>25</v>
+      <c r="Q244" s="0">
+        <v>0</v>
       </c>
       <c r="R244" s="0" t="s">
         <v>25</v>
@@ -17996,7 +17996,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F245" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>31</v>
@@ -18064,7 +18064,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F246" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G246" s="0" t="s">
         <v>24</v>
@@ -18132,7 +18132,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F247" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>31</v>
@@ -18200,7 +18200,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F248" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G248" s="0" t="s">
         <v>24</v>
@@ -18268,7 +18268,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F249" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G249" s="0" t="s">
         <v>31</v>
@@ -18336,7 +18336,7 @@
         <v>46215.346342592595</v>
       </c>
       <c r="F250" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G250" s="0" t="s">
         <v>31</v>
@@ -18404,7 +18404,7 @@
         <v>46208.34142361111</v>
       </c>
       <c r="F251" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G251" s="0" t="s">
         <v>31</v>
@@ -18472,7 +18472,7 @@
         <v>46184.34611111111</v>
       </c>
       <c r="F252" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>24</v>
@@ -18484,7 +18484,7 @@
         <v>24</v>
       </c>
       <c r="J252" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K252" s="0" t="s">
         <v>25</v>
@@ -18504,8 +18504,8 @@
       <c r="P252" s="0">
         <v>0</v>
       </c>
-      <c r="Q252" s="0" t="s">
-        <v>25</v>
+      <c r="Q252" s="0">
+        <v>0</v>
       </c>
       <c r="R252" s="0" t="s">
         <v>25</v>
@@ -18540,7 +18540,7 @@
         <v>46207.44116898148</v>
       </c>
       <c r="F253" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>31</v>
@@ -18608,7 +18608,7 @@
         <v>46217.771006944444</v>
       </c>
       <c r="F254" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G254" s="0" t="s">
         <v>24</v>
@@ -18676,7 +18676,7 @@
         <v>46217.77065972222</v>
       </c>
       <c r="F255" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G255" s="0" t="s">
         <v>24</v>
@@ -18744,7 +18744,7 @@
         <v>46213.12200231481</v>
       </c>
       <c r="F256" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>28</v>
@@ -18812,7 +18812,7 @@
         <v>46211.78650462963</v>
       </c>
       <c r="F257" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>28</v>
@@ -18880,7 +18880,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F258" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>31</v>
@@ -18948,7 +18948,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F259" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>31</v>
@@ -19016,7 +19016,7 @@
         <v>46205.74003472222</v>
       </c>
       <c r="F260" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>31</v>
@@ -19031,7 +19031,7 @@
         <v>31</v>
       </c>
       <c r="K260" s="0" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L260" s="0" t="s">
         <v>25</v>
@@ -19051,8 +19051,8 @@
       <c r="Q260" s="0">
         <v>1</v>
       </c>
-      <c r="R260" s="0" t="s">
-        <v>25</v>
+      <c r="R260" s="0">
+        <v>0</v>
       </c>
       <c r="S260" s="0" t="s">
         <v>25</v>
@@ -19084,7 +19084,7 @@
         <v>46214.6358912037</v>
       </c>
       <c r="F261" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>28</v>
@@ -19152,7 +19152,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F262" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>31</v>
@@ -19220,7 +19220,7 @@
         <v>46199.95371527778</v>
       </c>
       <c r="F263" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G263" s="0" t="s">
         <v>31</v>
@@ -19288,7 +19288,7 @@
         <v>46212.29601851852</v>
       </c>
       <c r="F264" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>28</v>
@@ -19356,7 +19356,7 @@
         <v>46205.07099537037</v>
       </c>
       <c r="F265" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G265" s="0" t="s">
         <v>24</v>
@@ -19424,7 +19424,7 @@
         <v>46215.09512731482</v>
       </c>
       <c r="F266" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G266" s="0" t="s">
         <v>28</v>
@@ -19492,7 +19492,7 @@
         <v>46203.39921296296</v>
       </c>
       <c r="F267" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G267" s="0" t="s">
         <v>24</v>
@@ -19507,7 +19507,7 @@
         <v>24</v>
       </c>
       <c r="K267" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L267" s="0" t="s">
         <v>25</v>
@@ -19527,8 +19527,8 @@
       <c r="Q267" s="0">
         <v>1</v>
       </c>
-      <c r="R267" s="0" t="s">
-        <v>25</v>
+      <c r="R267" s="0">
+        <v>0</v>
       </c>
       <c r="S267" s="0" t="s">
         <v>25</v>
@@ -19560,7 +19560,7 @@
         <v>46206.91523148148</v>
       </c>
       <c r="F268" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G268" s="0" t="s">
         <v>24</v>
@@ -19628,7 +19628,7 @@
         <v>46216.794907407406</v>
       </c>
       <c r="F269" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G269" s="0" t="s">
         <v>24</v>
@@ -19696,7 +19696,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F270" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>24</v>
@@ -19711,7 +19711,7 @@
         <v>24</v>
       </c>
       <c r="K270" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L270" s="0" t="s">
         <v>25</v>
@@ -19731,8 +19731,8 @@
       <c r="Q270" s="0">
         <v>1</v>
       </c>
-      <c r="R270" s="0" t="s">
-        <v>25</v>
+      <c r="R270" s="0">
+        <v>0</v>
       </c>
       <c r="S270" s="0" t="s">
         <v>25</v>
@@ -19764,7 +19764,7 @@
         <v>46212.73332175926</v>
       </c>
       <c r="F271" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>0</v>
       </c>
       <c r="P271" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q271" s="0" t="s">
         <v>25</v>
@@ -19832,7 +19832,7 @@
         <v>46218.88267361111</v>
       </c>
       <c r="F272" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>24</v>
@@ -19900,7 +19900,7 @@
         <v>46220.21396990741</v>
       </c>
       <c r="F273" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G273" s="0" t="s">
         <v>28</v>
@@ -19968,7 +19968,7 @@
         <v>46199.395949074074</v>
       </c>
       <c r="F274" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>28</v>
@@ -20036,7 +20036,7 @@
         <v>46218.05547453704</v>
       </c>
       <c r="F275" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G275" s="0" t="s">
         <v>24</v>
@@ -20104,7 +20104,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F276" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>31</v>
@@ -20172,7 +20172,7 @@
         <v>46184.34570601852</v>
       </c>
       <c r="F277" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G277" s="0" t="s">
         <v>24</v>
@@ -20184,7 +20184,7 @@
         <v>24</v>
       </c>
       <c r="J277" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K277" s="0" t="s">
         <v>25</v>
@@ -20204,8 +20204,8 @@
       <c r="P277" s="0">
         <v>0</v>
       </c>
-      <c r="Q277" s="0" t="s">
-        <v>25</v>
+      <c r="Q277" s="0">
+        <v>0</v>
       </c>
       <c r="R277" s="0" t="s">
         <v>25</v>
@@ -20240,7 +20240,7 @@
         <v>46198.756527777776</v>
       </c>
       <c r="F278" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G278" s="0" t="s">
         <v>24</v>
@@ -20255,7 +20255,7 @@
         <v>24</v>
       </c>
       <c r="K278" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L278" s="0" t="s">
         <v>25</v>
@@ -20275,8 +20275,8 @@
       <c r="Q278" s="0">
         <v>1</v>
       </c>
-      <c r="R278" s="0" t="s">
-        <v>25</v>
+      <c r="R278" s="0">
+        <v>0</v>
       </c>
       <c r="S278" s="0" t="s">
         <v>25</v>
@@ -20308,7 +20308,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F279" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G279" s="0" t="s">
         <v>31</v>
@@ -20376,7 +20376,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F280" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>31</v>
@@ -20444,7 +20444,7 @@
         <v>46208.76128472222</v>
       </c>
       <c r="F281" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G281" s="0" t="s">
         <v>24</v>
@@ -20512,7 +20512,7 @@
         <v>46198.76427083334</v>
       </c>
       <c r="F282" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G282" s="0" t="s">
         <v>24</v>
@@ -20527,7 +20527,7 @@
         <v>24</v>
       </c>
       <c r="K282" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L282" s="0" t="s">
         <v>25</v>
@@ -20547,8 +20547,8 @@
       <c r="Q282" s="0">
         <v>1</v>
       </c>
-      <c r="R282" s="0" t="s">
-        <v>25</v>
+      <c r="R282" s="0">
+        <v>0</v>
       </c>
       <c r="S282" s="0" t="s">
         <v>25</v>
@@ -20580,7 +20580,7 @@
         <v>46196.08101851852</v>
       </c>
       <c r="F283" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>24</v>
@@ -20648,7 +20648,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F284" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G284" s="0" t="s">
         <v>31</v>
@@ -20716,7 +20716,7 @@
         <v>46207.28523148148</v>
       </c>
       <c r="F285" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G285" s="0" t="s">
         <v>24</v>
@@ -20749,7 +20749,7 @@
         <v>1</v>
       </c>
       <c r="Q285" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R285" s="0" t="s">
         <v>25</v>
@@ -20784,7 +20784,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F286" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>31</v>
@@ -20852,7 +20852,7 @@
         <v>46196.788564814815</v>
       </c>
       <c r="F287" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>24</v>
@@ -20867,7 +20867,7 @@
         <v>24</v>
       </c>
       <c r="K287" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L287" s="0" t="s">
         <v>25</v>
@@ -20887,8 +20887,8 @@
       <c r="Q287" s="0">
         <v>1</v>
       </c>
-      <c r="R287" s="0" t="s">
-        <v>25</v>
+      <c r="R287" s="0">
+        <v>0</v>
       </c>
       <c r="S287" s="0" t="s">
         <v>25</v>
@@ -20920,7 +20920,7 @@
         <v>46217.99606481481</v>
       </c>
       <c r="F288" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>28</v>
@@ -20988,7 +20988,7 @@
         <v>46217.72994212963</v>
       </c>
       <c r="F289" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G289" s="0" t="s">
         <v>24</v>
@@ -21056,7 +21056,7 @@
         <v>46200.45096064815</v>
       </c>
       <c r="F290" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G290" s="0" t="s">
         <v>31</v>
@@ -21124,7 +21124,7 @@
         <v>46213.44936342593</v>
       </c>
       <c r="F291" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G291" s="0" t="s">
         <v>28</v>
@@ -21192,7 +21192,7 @@
         <v>46207.18237268519</v>
       </c>
       <c r="F292" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G292" s="0" t="s">
         <v>24</v>
@@ -21207,7 +21207,7 @@
         <v>24</v>
       </c>
       <c r="K292" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L292" s="0" t="s">
         <v>25</v>
@@ -21227,8 +21227,8 @@
       <c r="Q292" s="0">
         <v>1</v>
       </c>
-      <c r="R292" s="0" t="s">
-        <v>25</v>
+      <c r="R292" s="0">
+        <v>0</v>
       </c>
       <c r="S292" s="0" t="s">
         <v>25</v>
@@ -21260,7 +21260,7 @@
         <v>46220.24438657407</v>
       </c>
       <c r="F293" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G293" s="0" t="s">
         <v>28</v>
@@ -21287,7 +21287,7 @@
         <v>25</v>
       </c>
       <c r="O293" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P293" s="0" t="s">
         <v>25</v>
@@ -21328,7 +21328,7 @@
         <v>46198.89733796296</v>
       </c>
       <c r="F294" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G294" s="0" t="s">
         <v>28</v>
@@ -21396,7 +21396,7 @@
         <v>46213.282858796294</v>
       </c>
       <c r="F295" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>1</v>
       </c>
       <c r="P295" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q295" s="0" t="s">
         <v>25</v>
@@ -21464,7 +21464,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F296" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>24</v>
@@ -21532,7 +21532,7 @@
         <v>46217.69572916667</v>
       </c>
       <c r="F297" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G297" s="0" t="s">
         <v>28</v>
@@ -21600,7 +21600,7 @@
         <v>46219.77547453704</v>
       </c>
       <c r="F298" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>28</v>
@@ -21668,7 +21668,7 @@
         <v>46219.43380787037</v>
       </c>
       <c r="F299" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G299" s="0" t="s">
         <v>28</v>
@@ -21736,7 +21736,7 @@
         <v>46205.19603009259</v>
       </c>
       <c r="F300" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G300" s="0" t="s">
         <v>28</v>
@@ -21772,7 +21772,7 @@
         <v>0</v>
       </c>
       <c r="R300" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S300" s="0" t="s">
         <v>25</v>
@@ -21804,7 +21804,7 @@
         <v>46196.08101851852</v>
       </c>
       <c r="F301" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G301" s="0" t="s">
         <v>24</v>
@@ -21872,7 +21872,7 @@
         <v>46196.88885416667</v>
       </c>
       <c r="F302" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G302" s="0" t="s">
         <v>24</v>
@@ -21940,7 +21940,7 @@
         <v>46199.89765046296</v>
       </c>
       <c r="F303" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G303" s="0" t="s">
         <v>28</v>
@@ -22008,7 +22008,7 @@
         <v>46203.38673611111</v>
       </c>
       <c r="F304" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G304" s="0" t="s">
         <v>24</v>
@@ -22076,7 +22076,7 @@
         <v>46214.55940972222</v>
       </c>
       <c r="F305" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G305" s="0" t="s">
         <v>28</v>
@@ -22144,7 +22144,7 @@
         <v>46218.193761574075</v>
       </c>
       <c r="F306" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G306" s="0" t="s">
         <v>28</v>
@@ -22212,7 +22212,7 @@
         <v>46215.391805555555</v>
       </c>
       <c r="F307" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G307" s="0" t="s">
         <v>31</v>
@@ -22280,7 +22280,7 @@
         <v>46208.49730324074</v>
       </c>
       <c r="F308" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G308" s="0" t="s">
         <v>31</v>
@@ -22348,7 +22348,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F309" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G309" s="0" t="s">
         <v>24</v>
@@ -22416,7 +22416,7 @@
         <v>46205.35525462963</v>
       </c>
       <c r="F310" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>28</v>
@@ -22484,7 +22484,7 @@
         <v>46200.595925925925</v>
       </c>
       <c r="F311" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>24</v>
@@ -22552,7 +22552,7 @@
         <v>46198.36408564815</v>
       </c>
       <c r="F312" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>28</v>
@@ -22620,7 +22620,7 @@
         <v>46214.184386574074</v>
       </c>
       <c r="F313" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G313" s="0" t="s">
         <v>28</v>
@@ -22688,7 +22688,7 @@
         <v>46208.95462962963</v>
       </c>
       <c r="F314" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G314" s="0" t="s">
         <v>31</v>
@@ -22756,7 +22756,7 @@
         <v>46209.34474537037</v>
       </c>
       <c r="F315" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G315" s="0" t="s">
         <v>28</v>
@@ -22789,7 +22789,7 @@
         <v>1</v>
       </c>
       <c r="Q315" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R315" s="0" t="s">
         <v>25</v>
@@ -22824,7 +22824,7 @@
         <v>46203.6659375</v>
       </c>
       <c r="F316" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G316" s="0" t="s">
         <v>24</v>
@@ -22839,7 +22839,7 @@
         <v>24</v>
       </c>
       <c r="K316" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L316" s="0" t="s">
         <v>25</v>
@@ -22859,8 +22859,8 @@
       <c r="Q316" s="0">
         <v>1</v>
       </c>
-      <c r="R316" s="0" t="s">
-        <v>25</v>
+      <c r="R316" s="0">
+        <v>0</v>
       </c>
       <c r="S316" s="0" t="s">
         <v>25</v>
@@ -22892,7 +22892,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F317" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G317" s="0" t="s">
         <v>24</v>
@@ -22904,7 +22904,7 @@
         <v>24</v>
       </c>
       <c r="J317" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K317" s="0" t="s">
         <v>25</v>
@@ -22924,8 +22924,8 @@
       <c r="P317" s="0">
         <v>1</v>
       </c>
-      <c r="Q317" s="0" t="s">
-        <v>25</v>
+      <c r="Q317" s="0">
+        <v>0</v>
       </c>
       <c r="R317" s="0" t="s">
         <v>25</v>
@@ -22960,7 +22960,7 @@
         <v>46200.84137731481</v>
       </c>
       <c r="F318" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G318" s="0" t="s">
         <v>28</v>
@@ -23028,7 +23028,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F319" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G319" s="0" t="s">
         <v>31</v>
@@ -23096,7 +23096,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F320" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G320" s="0" t="s">
         <v>24</v>
@@ -23108,7 +23108,7 @@
         <v>24</v>
       </c>
       <c r="J320" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K320" s="0" t="s">
         <v>25</v>
@@ -23128,8 +23128,8 @@
       <c r="P320" s="0">
         <v>1</v>
       </c>
-      <c r="Q320" s="0" t="s">
-        <v>25</v>
+      <c r="Q320" s="0">
+        <v>0</v>
       </c>
       <c r="R320" s="0" t="s">
         <v>25</v>
@@ -23164,7 +23164,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F321" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G321" s="0" t="s">
         <v>24</v>
@@ -23232,7 +23232,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F322" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>24</v>
@@ -23300,7 +23300,7 @@
         <v>46207.322233796294</v>
       </c>
       <c r="F323" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G323" s="0" t="s">
         <v>28</v>
@@ -23315,7 +23315,7 @@
         <v>28</v>
       </c>
       <c r="K323" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L323" s="0" t="s">
         <v>25</v>
@@ -23335,8 +23335,8 @@
       <c r="Q323" s="0">
         <v>1</v>
       </c>
-      <c r="R323" s="0" t="s">
-        <v>25</v>
+      <c r="R323" s="0">
+        <v>0</v>
       </c>
       <c r="S323" s="0" t="s">
         <v>25</v>
@@ -23368,7 +23368,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F324" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G324" s="0" t="s">
         <v>24</v>
@@ -23383,7 +23383,7 @@
         <v>24</v>
       </c>
       <c r="K324" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L324" s="0" t="s">
         <v>25</v>
@@ -23403,8 +23403,8 @@
       <c r="Q324" s="0">
         <v>1</v>
       </c>
-      <c r="R324" s="0" t="s">
-        <v>25</v>
+      <c r="R324" s="0">
+        <v>0</v>
       </c>
       <c r="S324" s="0" t="s">
         <v>25</v>
@@ -23436,7 +23436,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F325" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G325" s="0" t="s">
         <v>24</v>
@@ -23504,7 +23504,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F326" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G326" s="0" t="s">
         <v>24</v>
@@ -23572,7 +23572,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F327" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G327" s="0" t="s">
         <v>24</v>
@@ -23640,7 +23640,7 @@
         <v>46208.80619212963</v>
       </c>
       <c r="F328" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G328" s="0" t="s">
         <v>28</v>
@@ -23708,7 +23708,7 @@
         <v>46207.24060185185</v>
       </c>
       <c r="F329" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G329" s="0" t="s">
         <v>24</v>
@@ -23723,7 +23723,7 @@
         <v>24</v>
       </c>
       <c r="K329" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L329" s="0" t="s">
         <v>25</v>
@@ -23743,8 +23743,8 @@
       <c r="Q329" s="0">
         <v>1</v>
       </c>
-      <c r="R329" s="0" t="s">
-        <v>25</v>
+      <c r="R329" s="0">
+        <v>0</v>
       </c>
       <c r="S329" s="0" t="s">
         <v>25</v>
@@ -23776,7 +23776,7 @@
         <v>46213.36528935185</v>
       </c>
       <c r="F330" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G330" s="0" t="s">
         <v>31</v>
@@ -23844,7 +23844,7 @@
         <v>46202.50537037037</v>
       </c>
       <c r="F331" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G331" s="0" t="s">
         <v>28</v>
@@ -23912,7 +23912,7 @@
         <v>46217.3975</v>
       </c>
       <c r="F332" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G332" s="0" t="s">
         <v>24</v>
@@ -23980,7 +23980,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F333" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G333" s="0" t="s">
         <v>31</v>
@@ -24048,7 +24048,7 @@
         <v>46217.770949074074</v>
       </c>
       <c r="F334" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G334" s="0" t="s">
         <v>24</v>
@@ -24116,7 +24116,7 @@
         <v>46200.24690972222</v>
       </c>
       <c r="F335" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G335" s="0" t="s">
         <v>31</v>
@@ -24184,7 +24184,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F336" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>31</v>
@@ -24252,7 +24252,7 @@
         <v>46197.26045138889</v>
       </c>
       <c r="F337" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>24</v>
@@ -24320,7 +24320,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F338" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G338" s="0" t="s">
         <v>31</v>
@@ -24388,7 +24388,7 @@
         <v>46200.39493055556</v>
       </c>
       <c r="F339" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G339" s="0" t="s">
         <v>24</v>
@@ -24456,7 +24456,7 @@
         <v>46200.50178240741</v>
       </c>
       <c r="F340" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>28</v>
@@ -24524,7 +24524,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F341" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G341" s="0" t="s">
         <v>31</v>
@@ -24592,7 +24592,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F342" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G342" s="0" t="s">
         <v>31</v>
@@ -24660,7 +24660,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F343" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>31</v>
@@ -24728,7 +24728,7 @@
         <v>46201.81197916667</v>
       </c>
       <c r="F344" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G344" s="0" t="s">
         <v>28</v>
@@ -24796,7 +24796,7 @@
         <v>46196.87100694444</v>
       </c>
       <c r="F345" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G345" s="0" t="s">
         <v>28</v>
@@ -24864,7 +24864,7 @@
         <v>46211.287673611114</v>
       </c>
       <c r="F346" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G346" s="0" t="s">
         <v>28</v>
@@ -24932,7 +24932,7 @@
         <v>46217.07877314815</v>
       </c>
       <c r="F347" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G347" s="0" t="s">
         <v>28</v>
@@ -24941,7 +24941,7 @@
         <v>28</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J347" s="0" t="s">
         <v>25</v>
@@ -24961,8 +24961,8 @@
       <c r="O347" s="0">
         <v>1</v>
       </c>
-      <c r="P347" s="0" t="s">
-        <v>25</v>
+      <c r="P347" s="0">
+        <v>0</v>
       </c>
       <c r="Q347" s="0" t="s">
         <v>25</v>
@@ -25000,7 +25000,7 @@
         <v>46213.33634259259</v>
       </c>
       <c r="F348" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>28</v>
@@ -25068,7 +25068,7 @@
         <v>46203.38674768519</v>
       </c>
       <c r="F349" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G349" s="0" t="s">
         <v>24</v>
@@ -25104,7 +25104,7 @@
         <v>1</v>
       </c>
       <c r="R349" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S349" s="0" t="s">
         <v>25</v>
@@ -25136,7 +25136,7 @@
         <v>46216.91412037037</v>
       </c>
       <c r="F350" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G350" s="0" t="s">
         <v>24</v>
@@ -25204,7 +25204,7 @@
         <v>46199.38827546296</v>
       </c>
       <c r="F351" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>24</v>
@@ -25272,7 +25272,7 @@
         <v>46211.747569444444</v>
       </c>
       <c r="F352" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G352" s="0" t="s">
         <v>24</v>
@@ -25284,7 +25284,7 @@
         <v>24</v>
       </c>
       <c r="J352" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K352" s="0" t="s">
         <v>25</v>
@@ -25304,8 +25304,8 @@
       <c r="P352" s="0">
         <v>1</v>
       </c>
-      <c r="Q352" s="0" t="s">
-        <v>25</v>
+      <c r="Q352" s="0">
+        <v>0</v>
       </c>
       <c r="R352" s="0" t="s">
         <v>25</v>
@@ -25340,7 +25340,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F353" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G353" s="0" t="s">
         <v>31</v>
@@ -25408,7 +25408,7 @@
         <v>46214.036574074074</v>
       </c>
       <c r="F354" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G354" s="0" t="s">
         <v>24</v>
@@ -25476,7 +25476,7 @@
         <v>46198.75832175926</v>
       </c>
       <c r="F355" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G355" s="0" t="s">
         <v>24</v>
@@ -25491,7 +25491,7 @@
         <v>24</v>
       </c>
       <c r="K355" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L355" s="0" t="s">
         <v>25</v>
@@ -25511,8 +25511,8 @@
       <c r="Q355" s="0">
         <v>1</v>
       </c>
-      <c r="R355" s="0" t="s">
-        <v>25</v>
+      <c r="R355" s="0">
+        <v>0</v>
       </c>
       <c r="S355" s="0" t="s">
         <v>25</v>
@@ -25544,7 +25544,7 @@
         <v>46213.1378125</v>
       </c>
       <c r="F356" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G356" s="0" t="s">
         <v>28</v>
@@ -25612,7 +25612,7 @@
         <v>46218.15008101852</v>
       </c>
       <c r="F357" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G357" s="0" t="s">
         <v>28</v>
@@ -25680,7 +25680,7 @@
         <v>46200.08666666667</v>
       </c>
       <c r="F358" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G358" s="0" t="s">
         <v>28</v>
@@ -25748,7 +25748,7 @@
         <v>46191.20039351852</v>
       </c>
       <c r="F359" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G359" s="0" t="s">
         <v>24</v>
@@ -25816,7 +25816,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F360" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G360" s="0" t="s">
         <v>31</v>
@@ -25884,7 +25884,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F361" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G361" s="0" t="s">
         <v>24</v>
@@ -25899,7 +25899,7 @@
         <v>24</v>
       </c>
       <c r="K361" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L361" s="0" t="s">
         <v>25</v>
@@ -25919,8 +25919,8 @@
       <c r="Q361" s="0">
         <v>0</v>
       </c>
-      <c r="R361" s="0" t="s">
-        <v>25</v>
+      <c r="R361" s="0">
+        <v>0</v>
       </c>
       <c r="S361" s="0" t="s">
         <v>25</v>
@@ -25952,7 +25952,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F362" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G362" s="0" t="s">
         <v>24</v>
@@ -26020,7 +26020,7 @@
         <v>46197.6375462963</v>
       </c>
       <c r="F363" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G363" s="0" t="s">
         <v>24</v>
@@ -26088,7 +26088,7 @@
         <v>46197.037523148145</v>
       </c>
       <c r="F364" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G364" s="0" t="s">
         <v>24</v>
@@ -26156,7 +26156,7 @@
         <v>46198.31060185185</v>
       </c>
       <c r="F365" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G365" s="0" t="s">
         <v>28</v>
@@ -26224,7 +26224,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F366" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G366" s="0" t="s">
         <v>24</v>
@@ -26292,7 +26292,7 @@
         <v>46209.31466435185</v>
       </c>
       <c r="F367" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G367" s="0" t="s">
         <v>28</v>
@@ -26325,7 +26325,7 @@
         <v>1</v>
       </c>
       <c r="Q367" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R367" s="0" t="s">
         <v>25</v>
@@ -26360,7 +26360,7 @@
         <v>46206.72038194445</v>
       </c>
       <c r="F368" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G368" s="0" t="s">
         <v>28</v>
@@ -26375,7 +26375,7 @@
         <v>28</v>
       </c>
       <c r="K368" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L368" s="0" t="s">
         <v>25</v>
@@ -26395,8 +26395,8 @@
       <c r="Q368" s="0">
         <v>1</v>
       </c>
-      <c r="R368" s="0" t="s">
-        <v>25</v>
+      <c r="R368" s="0">
+        <v>0</v>
       </c>
       <c r="S368" s="0" t="s">
         <v>25</v>
@@ -26428,7 +26428,7 @@
         <v>46197.46810185185</v>
       </c>
       <c r="F369" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G369" s="0" t="s">
         <v>24</v>
@@ -26496,7 +26496,7 @@
         <v>46217.79634259259</v>
       </c>
       <c r="F370" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G370" s="0" t="s">
         <v>31</v>
@@ -26564,7 +26564,7 @@
         <v>46202.349328703705</v>
       </c>
       <c r="F371" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G371" s="0" t="s">
         <v>28</v>
@@ -26632,7 +26632,7 @@
         <v>46217.73019675926</v>
       </c>
       <c r="F372" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G372" s="0" t="s">
         <v>24</v>
@@ -26700,7 +26700,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F373" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G373" s="0" t="s">
         <v>24</v>
@@ -26768,7 +26768,7 @@
         <v>46216.25659722222</v>
       </c>
       <c r="F374" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G374" s="0" t="s">
         <v>28</v>
@@ -26777,7 +26777,7 @@
         <v>28</v>
       </c>
       <c r="I374" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J374" s="0" t="s">
         <v>25</v>
@@ -26797,8 +26797,8 @@
       <c r="O374" s="0">
         <v>0</v>
       </c>
-      <c r="P374" s="0" t="s">
-        <v>25</v>
+      <c r="P374" s="0">
+        <v>0</v>
       </c>
       <c r="Q374" s="0" t="s">
         <v>25</v>
@@ -26836,7 +26836,7 @@
         <v>46198.75665509259</v>
       </c>
       <c r="F375" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G375" s="0" t="s">
         <v>24</v>
@@ -26851,7 +26851,7 @@
         <v>24</v>
       </c>
       <c r="K375" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L375" s="0" t="s">
         <v>25</v>
@@ -26871,8 +26871,8 @@
       <c r="Q375" s="0">
         <v>1</v>
       </c>
-      <c r="R375" s="0" t="s">
-        <v>25</v>
+      <c r="R375" s="0">
+        <v>0</v>
       </c>
       <c r="S375" s="0" t="s">
         <v>25</v>
@@ -26904,7 +26904,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F376" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G376" s="0" t="s">
         <v>31</v>
@@ -26972,7 +26972,7 @@
         <v>46205.784363425926</v>
       </c>
       <c r="F377" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G377" s="0" t="s">
         <v>31</v>
@@ -26987,7 +26987,7 @@
         <v>31</v>
       </c>
       <c r="K377" s="0" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L377" s="0" t="s">
         <v>25</v>
@@ -27007,8 +27007,8 @@
       <c r="Q377" s="0">
         <v>1</v>
       </c>
-      <c r="R377" s="0" t="s">
-        <v>25</v>
+      <c r="R377" s="0">
+        <v>0</v>
       </c>
       <c r="S377" s="0" t="s">
         <v>25</v>
@@ -27040,7 +27040,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F378" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G378" s="0" t="s">
         <v>24</v>
@@ -27052,7 +27052,7 @@
         <v>24</v>
       </c>
       <c r="J378" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K378" s="0" t="s">
         <v>25</v>
@@ -27072,8 +27072,8 @@
       <c r="P378" s="0">
         <v>1</v>
       </c>
-      <c r="Q378" s="0" t="s">
-        <v>25</v>
+      <c r="Q378" s="0">
+        <v>0</v>
       </c>
       <c r="R378" s="0" t="s">
         <v>25</v>
@@ -27108,7 +27108,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F379" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G379" s="0" t="s">
         <v>24</v>
@@ -27120,7 +27120,7 @@
         <v>24</v>
       </c>
       <c r="J379" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K379" s="0" t="s">
         <v>25</v>
@@ -27140,8 +27140,8 @@
       <c r="P379" s="0">
         <v>1</v>
       </c>
-      <c r="Q379" s="0" t="s">
-        <v>25</v>
+      <c r="Q379" s="0">
+        <v>0</v>
       </c>
       <c r="R379" s="0" t="s">
         <v>25</v>
@@ -27176,7 +27176,7 @@
         <v>46198.75827546296</v>
       </c>
       <c r="F380" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G380" s="0" t="s">
         <v>24</v>
@@ -27191,7 +27191,7 @@
         <v>24</v>
       </c>
       <c r="K380" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L380" s="0" t="s">
         <v>25</v>
@@ -27211,8 +27211,8 @@
       <c r="Q380" s="0">
         <v>0</v>
       </c>
-      <c r="R380" s="0" t="s">
-        <v>25</v>
+      <c r="R380" s="0">
+        <v>0</v>
       </c>
       <c r="S380" s="0" t="s">
         <v>25</v>
@@ -27244,7 +27244,7 @@
         <v>46203.80048611111</v>
       </c>
       <c r="F381" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G381" s="0" t="s">
         <v>31</v>
@@ -27312,7 +27312,7 @@
         <v>46216.914131944446</v>
       </c>
       <c r="F382" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G382" s="0" t="s">
         <v>24</v>
@@ -27380,7 +27380,7 @@
         <v>46207.377118055556</v>
       </c>
       <c r="F383" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G383" s="0" t="s">
         <v>28</v>
@@ -27395,7 +27395,7 @@
         <v>28</v>
       </c>
       <c r="K383" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L383" s="0" t="s">
         <v>25</v>
@@ -27415,8 +27415,8 @@
       <c r="Q383" s="0">
         <v>0</v>
       </c>
-      <c r="R383" s="0" t="s">
-        <v>25</v>
+      <c r="R383" s="0">
+        <v>0</v>
       </c>
       <c r="S383" s="0" t="s">
         <v>25</v>
@@ -27448,7 +27448,7 @@
         <v>46217.62388888889</v>
       </c>
       <c r="F384" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G384" s="0" t="s">
         <v>31</v>
@@ -27516,7 +27516,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F385" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G385" s="0" t="s">
         <v>31</v>
@@ -27584,7 +27584,7 @@
         <v>46216.91412037037</v>
       </c>
       <c r="F386" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G386" s="0" t="s">
         <v>24</v>
@@ -27652,7 +27652,7 @@
         <v>46198.76320601852</v>
       </c>
       <c r="F387" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G387" s="0" t="s">
         <v>24</v>
@@ -27667,7 +27667,7 @@
         <v>24</v>
       </c>
       <c r="K387" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L387" s="0" t="s">
         <v>25</v>
@@ -27687,8 +27687,8 @@
       <c r="Q387" s="0">
         <v>0</v>
       </c>
-      <c r="R387" s="0" t="s">
-        <v>25</v>
+      <c r="R387" s="0">
+        <v>0</v>
       </c>
       <c r="S387" s="0" t="s">
         <v>25</v>
@@ -27720,7 +27720,7 @@
         <v>46209.364849537036</v>
       </c>
       <c r="F388" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G388" s="0" t="s">
         <v>31</v>
@@ -27788,7 +27788,7 @@
         <v>46210.49642361111</v>
       </c>
       <c r="F389" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G389" s="0" t="s">
         <v>31</v>
@@ -27856,7 +27856,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F390" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G390" s="0" t="s">
         <v>31</v>
@@ -27924,7 +27924,7 @@
         <v>46218.668599537035</v>
       </c>
       <c r="F391" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G391" s="0" t="s">
         <v>28</v>
@@ -27992,7 +27992,7 @@
         <v>46198.76327546296</v>
       </c>
       <c r="F392" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G392" s="0" t="s">
         <v>24</v>
@@ -28007,7 +28007,7 @@
         <v>24</v>
       </c>
       <c r="K392" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L392" s="0" t="s">
         <v>25</v>
@@ -28027,8 +28027,8 @@
       <c r="Q392" s="0">
         <v>1</v>
       </c>
-      <c r="R392" s="0" t="s">
-        <v>25</v>
+      <c r="R392" s="0">
+        <v>0</v>
       </c>
       <c r="S392" s="0" t="s">
         <v>25</v>
@@ -28060,7 +28060,7 @@
         <v>46197.041238425925</v>
       </c>
       <c r="F393" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G393" s="0" t="s">
         <v>24</v>
@@ -28128,7 +28128,7 @@
         <v>46212.017488425925</v>
       </c>
       <c r="F394" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G394" s="0" t="s">
         <v>31</v>
@@ -28196,7 +28196,7 @@
         <v>46204.81549768519</v>
       </c>
       <c r="F395" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G395" s="0" t="s">
         <v>24</v>
@@ -28208,7 +28208,7 @@
         <v>24</v>
       </c>
       <c r="J395" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K395" s="0" t="s">
         <v>25</v>
@@ -28228,8 +28228,8 @@
       <c r="P395" s="0">
         <v>1</v>
       </c>
-      <c r="Q395" s="0" t="s">
-        <v>25</v>
+      <c r="Q395" s="0">
+        <v>0</v>
       </c>
       <c r="R395" s="0" t="s">
         <v>25</v>
@@ -28264,7 +28264,7 @@
         <v>46200.44310185185</v>
       </c>
       <c r="F396" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G396" s="0" t="s">
         <v>24</v>
@@ -28332,7 +28332,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F397" s="1">
-        <v>46221.042352662036</v>
+        <v>46222.04253125</v>
       </c>
       <c r="G397" s="0" t="s">
         <v>24</v>

--- a/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
+++ b/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
@@ -1781,7 +1781,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F2" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>24</v>
@@ -1849,7 +1849,7 @@
         <v>46213.61586805555</v>
       </c>
       <c r="F3" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>27</v>
@@ -1917,7 +1917,7 @@
         <v>46204.34583333333</v>
       </c>
       <c r="F4" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>30</v>
@@ -1985,7 +1985,7 @@
         <v>46207.15827546296</v>
       </c>
       <c r="F5" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>30</v>
@@ -2053,7 +2053,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F6" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>27</v>
@@ -2121,7 +2121,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F7" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>24</v>
@@ -2189,7 +2189,7 @@
         <v>46200.30415509259</v>
       </c>
       <c r="F8" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>30</v>
@@ -2257,7 +2257,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F9" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>27</v>
@@ -2325,7 +2325,7 @@
         <v>46214.27086805556</v>
       </c>
       <c r="F10" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>30</v>
@@ -2393,7 +2393,7 @@
         <v>46216.91679398148</v>
       </c>
       <c r="F11" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>30</v>
@@ -2461,7 +2461,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F12" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>27</v>
@@ -2529,7 +2529,7 @@
         <v>46217.789305555554</v>
       </c>
       <c r="F13" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>27</v>
@@ -2597,7 +2597,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F14" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>24</v>
@@ -2665,7 +2665,7 @@
         <v>46211.80736111111</v>
       </c>
       <c r="F15" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>30</v>
@@ -2733,7 +2733,7 @@
         <v>46213.618055555555</v>
       </c>
       <c r="F16" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>27</v>
@@ -2801,7 +2801,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F17" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G17" s="0" t="s">
         <v>27</v>
@@ -2869,7 +2869,7 @@
         <v>46222.964467592596</v>
       </c>
       <c r="F18" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>30</v>
@@ -2937,7 +2937,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F19" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G19" s="0" t="s">
         <v>24</v>
@@ -3005,7 +3005,7 @@
         <v>46213.61806712963</v>
       </c>
       <c r="F20" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G20" s="0" t="s">
         <v>24</v>
@@ -3073,7 +3073,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F21" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G21" s="0" t="s">
         <v>24</v>
@@ -3141,7 +3141,7 @@
         <v>46214.30170138889</v>
       </c>
       <c r="F22" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>24</v>
@@ -3209,7 +3209,7 @@
         <v>46213.61802083333</v>
       </c>
       <c r="F23" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G23" s="0" t="s">
         <v>24</v>
@@ -3277,7 +3277,7 @@
         <v>46222.379108796296</v>
       </c>
       <c r="F24" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>30</v>
@@ -3345,7 +3345,7 @@
         <v>46211.689108796294</v>
       </c>
       <c r="F25" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G25" s="0" t="s">
         <v>30</v>
@@ -3413,7 +3413,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F26" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>27</v>
@@ -3481,7 +3481,7 @@
         <v>46198.75680555555</v>
       </c>
       <c r="F27" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G27" s="0" t="s">
         <v>24</v>
@@ -3549,7 +3549,7 @@
         <v>46200.02773148148</v>
       </c>
       <c r="F28" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>30</v>
@@ -3617,7 +3617,7 @@
         <v>46214.69945601852</v>
       </c>
       <c r="F29" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>27</v>
@@ -3685,7 +3685,7 @@
         <v>46216.87899305556</v>
       </c>
       <c r="F30" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>30</v>
@@ -3753,7 +3753,7 @@
         <v>46200.57623842593</v>
       </c>
       <c r="F31" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>30</v>
@@ -3821,7 +3821,7 @@
         <v>46213.61833333333</v>
       </c>
       <c r="F32" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>27</v>
@@ -3889,7 +3889,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F33" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>27</v>
@@ -3957,7 +3957,7 @@
         <v>46198.764027777775</v>
       </c>
       <c r="F34" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>24</v>
@@ -4025,7 +4025,7 @@
         <v>46198.18491898148</v>
       </c>
       <c r="F35" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>30</v>
@@ -4093,7 +4093,7 @@
         <v>46203.81460648148</v>
       </c>
       <c r="F36" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>27</v>
@@ -4161,7 +4161,7 @@
         <v>46213.61833333333</v>
       </c>
       <c r="F37" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>27</v>
@@ -4229,7 +4229,7 @@
         <v>46213.61802083333</v>
       </c>
       <c r="F38" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>27</v>
@@ -4297,7 +4297,7 @@
         <v>46201.33733796296</v>
       </c>
       <c r="F39" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>30</v>
@@ -4365,7 +4365,7 @@
         <v>46218.70291666667</v>
       </c>
       <c r="F40" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>30</v>
@@ -4433,7 +4433,7 @@
         <v>46203.71907407408</v>
       </c>
       <c r="F41" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>30</v>
@@ -4501,7 +4501,7 @@
         <v>46219.741423611114</v>
       </c>
       <c r="F42" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>30</v>
@@ -4569,7 +4569,7 @@
         <v>46195.59105324074</v>
       </c>
       <c r="F43" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>24</v>
@@ -4637,7 +4637,7 @@
         <v>46201.06361111111</v>
       </c>
       <c r="F44" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>30</v>
@@ -4705,7 +4705,7 @@
         <v>46195.68219907407</v>
       </c>
       <c r="F45" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>24</v>
@@ -4773,7 +4773,7 @@
         <v>46216.18634259259</v>
       </c>
       <c r="F46" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>30</v>
@@ -4841,7 +4841,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F47" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>24</v>
@@ -4909,7 +4909,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F48" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>27</v>
@@ -4977,7 +4977,7 @@
         <v>46202.38591435185</v>
       </c>
       <c r="F49" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G49" s="0" t="s">
         <v>30</v>
@@ -5045,7 +5045,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F50" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>24</v>
@@ -5113,7 +5113,7 @@
         <v>46215.03915509259</v>
       </c>
       <c r="F51" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>27</v>
@@ -5181,7 +5181,7 @@
         <v>46217.397997685184</v>
       </c>
       <c r="F52" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>24</v>
@@ -5249,7 +5249,7 @@
         <v>46222.348495370374</v>
       </c>
       <c r="F53" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>27</v>
@@ -5317,7 +5317,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F54" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>24</v>
@@ -5385,7 +5385,7 @@
         <v>46205.25707175926</v>
       </c>
       <c r="F55" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>30</v>
@@ -5453,7 +5453,7 @@
         <v>46203.77983796296</v>
       </c>
       <c r="F56" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>27</v>
@@ -5521,7 +5521,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F57" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G57" s="0" t="s">
         <v>24</v>
@@ -5589,7 +5589,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F58" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>27</v>
@@ -5657,7 +5657,7 @@
         <v>46207.957766203705</v>
       </c>
       <c r="F59" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>27</v>
@@ -5725,7 +5725,7 @@
         <v>46204.23569444445</v>
       </c>
       <c r="F60" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G60" s="0" t="s">
         <v>30</v>
@@ -5793,7 +5793,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F61" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>24</v>
@@ -5861,7 +5861,7 @@
         <v>46206.293020833335</v>
       </c>
       <c r="F62" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>27</v>
@@ -5929,7 +5929,7 @@
         <v>46214.75530092593</v>
       </c>
       <c r="F63" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>27</v>
@@ -5997,7 +5997,7 @@
         <v>46198.763715277775</v>
       </c>
       <c r="F64" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>24</v>
@@ -6065,7 +6065,7 @@
         <v>46205.502962962964</v>
       </c>
       <c r="F65" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>30</v>
@@ -6133,7 +6133,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F66" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>24</v>
@@ -6201,7 +6201,7 @@
         <v>46214.35975694445</v>
       </c>
       <c r="F67" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>30</v>
@@ -6269,7 +6269,7 @@
         <v>46213.618055555555</v>
       </c>
       <c r="F68" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>24</v>
@@ -6337,7 +6337,7 @@
         <v>46200.67046296296</v>
       </c>
       <c r="F69" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>24</v>
@@ -6405,7 +6405,7 @@
         <v>46215.29809027778</v>
       </c>
       <c r="F70" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G70" s="0" t="s">
         <v>30</v>
@@ -6473,7 +6473,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F71" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G71" s="0" t="s">
         <v>24</v>
@@ -6541,7 +6541,7 @@
         <v>46222.94975694444</v>
       </c>
       <c r="F72" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>30</v>
@@ -6609,7 +6609,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F73" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>27</v>
@@ -6677,7 +6677,7 @@
         <v>46222.341782407406</v>
       </c>
       <c r="F74" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>30</v>
@@ -6745,7 +6745,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F75" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>24</v>
@@ -6813,7 +6813,7 @@
         <v>46217.729409722226</v>
       </c>
       <c r="F76" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>24</v>
@@ -6881,7 +6881,7 @@
         <v>46207.76193287037</v>
       </c>
       <c r="F77" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>24</v>
@@ -6949,7 +6949,7 @@
         <v>46199.574282407404</v>
       </c>
       <c r="F78" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>30</v>
@@ -7017,7 +7017,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F79" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>27</v>
@@ -7085,7 +7085,7 @@
         <v>46198.758518518516</v>
       </c>
       <c r="F80" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>24</v>
@@ -7153,7 +7153,7 @@
         <v>46199.20893518518</v>
       </c>
       <c r="F81" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>30</v>
@@ -7221,7 +7221,7 @@
         <v>46198.76384259259</v>
       </c>
       <c r="F82" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>24</v>
@@ -7289,7 +7289,7 @@
         <v>46207.98546296296</v>
       </c>
       <c r="F83" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>30</v>
@@ -7357,7 +7357,7 @@
         <v>46198.758414351854</v>
       </c>
       <c r="F84" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>24</v>
@@ -7425,7 +7425,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F85" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>27</v>
@@ -7493,7 +7493,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F86" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>24</v>
@@ -7561,7 +7561,7 @@
         <v>46207.95777777778</v>
       </c>
       <c r="F87" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>24</v>
@@ -7629,7 +7629,7 @@
         <v>46217.77034722222</v>
       </c>
       <c r="F88" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G88" s="0" t="s">
         <v>24</v>
@@ -7697,7 +7697,7 @@
         <v>46213.61802083333</v>
       </c>
       <c r="F89" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>27</v>
@@ -7765,7 +7765,7 @@
         <v>46213.479849537034</v>
       </c>
       <c r="F90" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>30</v>
@@ -7833,7 +7833,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F91" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>24</v>
@@ -7901,7 +7901,7 @@
         <v>46213.89649305555</v>
       </c>
       <c r="F92" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>30</v>
@@ -7969,7 +7969,7 @@
         <v>46194.2578587963</v>
       </c>
       <c r="F93" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>30</v>
@@ -8037,7 +8037,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F94" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>24</v>
@@ -8105,7 +8105,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F95" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>27</v>
@@ -8173,7 +8173,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F96" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>27</v>
@@ -8241,7 +8241,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F97" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>24</v>
@@ -8309,7 +8309,7 @@
         <v>46214.741215277776</v>
       </c>
       <c r="F98" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G98" s="0" t="s">
         <v>30</v>
@@ -8377,7 +8377,7 @@
         <v>46204.816157407404</v>
       </c>
       <c r="F99" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>24</v>
@@ -8445,7 +8445,7 @@
         <v>46210.94122685185</v>
       </c>
       <c r="F100" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>30</v>
@@ -8513,7 +8513,7 @@
         <v>46211.91608796296</v>
       </c>
       <c r="F101" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>30</v>
@@ -8581,7 +8581,7 @@
         <v>46213.618310185186</v>
       </c>
       <c r="F102" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>27</v>
@@ -8649,7 +8649,7 @@
         <v>46211.9408912037</v>
       </c>
       <c r="F103" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>30</v>
@@ -8717,7 +8717,7 @@
         <v>46198.763449074075</v>
       </c>
       <c r="F104" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>24</v>
@@ -8785,7 +8785,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F105" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>27</v>
@@ -8853,7 +8853,7 @@
         <v>46222.727164351854</v>
       </c>
       <c r="F106" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>27</v>
@@ -8921,7 +8921,7 @@
         <v>46198.758125</v>
       </c>
       <c r="F107" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>24</v>
@@ -8989,7 +8989,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F108" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>24</v>
@@ -9057,7 +9057,7 @@
         <v>46201.54498842593</v>
       </c>
       <c r="F109" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>30</v>
@@ -9125,7 +9125,7 @@
         <v>46198.76478009259</v>
       </c>
       <c r="F110" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>24</v>
@@ -9193,7 +9193,7 @@
         <v>46205.76315972222</v>
       </c>
       <c r="F111" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>30</v>
@@ -9261,7 +9261,7 @@
         <v>46204.83986111111</v>
       </c>
       <c r="F112" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>30</v>
@@ -9329,7 +9329,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F113" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>27</v>
@@ -9397,7 +9397,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F114" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>24</v>
@@ -9465,7 +9465,7 @@
         <v>46203.69975694444</v>
       </c>
       <c r="F115" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>27</v>
@@ -9533,7 +9533,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F116" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>24</v>
@@ -9601,7 +9601,7 @@
         <v>46208.10663194444</v>
       </c>
       <c r="F117" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>30</v>
@@ -9669,7 +9669,7 @@
         <v>46200.854166666664</v>
       </c>
       <c r="F118" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>24</v>
@@ -9737,7 +9737,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F119" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>24</v>
@@ -9805,7 +9805,7 @@
         <v>46212.5203125</v>
       </c>
       <c r="F120" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>24</v>
@@ -9873,7 +9873,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F121" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>24</v>
@@ -9941,7 +9941,7 @@
         <v>46204.145219907405</v>
       </c>
       <c r="F122" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>24</v>
@@ -10009,7 +10009,7 @@
         <v>46191.31182870371</v>
       </c>
       <c r="F123" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>24</v>
@@ -10077,7 +10077,7 @@
         <v>46199.29518518518</v>
       </c>
       <c r="F124" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>30</v>
@@ -10145,7 +10145,7 @@
         <v>46184.345671296294</v>
       </c>
       <c r="F125" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>24</v>
@@ -10213,7 +10213,7 @@
         <v>46218.3812962963</v>
       </c>
       <c r="F126" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>27</v>
@@ -10281,7 +10281,7 @@
         <v>46215.31277777778</v>
       </c>
       <c r="F127" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>30</v>
@@ -10349,7 +10349,7 @@
         <v>46219.47236111111</v>
       </c>
       <c r="F128" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>30</v>
@@ -10417,7 +10417,7 @@
         <v>46198.758576388886</v>
       </c>
       <c r="F129" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>24</v>
@@ -10485,7 +10485,7 @@
         <v>46211.747719907406</v>
       </c>
       <c r="F130" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>24</v>
@@ -10553,7 +10553,7 @@
         <v>46196.6612962963</v>
       </c>
       <c r="F131" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>27</v>
@@ -10621,7 +10621,7 @@
         <v>46203.386967592596</v>
       </c>
       <c r="F132" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>24</v>
@@ -10689,7 +10689,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F133" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>30</v>
@@ -10757,7 +10757,7 @@
         <v>46202.30238425926</v>
       </c>
       <c r="F134" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>30</v>
@@ -10825,7 +10825,7 @@
         <v>46210.49642361111</v>
       </c>
       <c r="F135" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>27</v>
@@ -10893,7 +10893,7 @@
         <v>46213.61802083333</v>
       </c>
       <c r="F136" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>27</v>
@@ -10961,7 +10961,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F137" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>24</v>
@@ -11029,7 +11029,7 @@
         <v>46217.79634259259</v>
       </c>
       <c r="F138" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>27</v>
@@ -11097,7 +11097,7 @@
         <v>46217.76349537037</v>
       </c>
       <c r="F139" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>24</v>
@@ -11165,7 +11165,7 @@
         <v>46198.007743055554</v>
       </c>
       <c r="F140" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>24</v>
@@ -11233,7 +11233,7 @@
         <v>46213.615798611114</v>
       </c>
       <c r="F141" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G141" s="0" t="s">
         <v>27</v>
@@ -11301,7 +11301,7 @@
         <v>46221.49884259259</v>
       </c>
       <c r="F142" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>30</v>
@@ -11369,7 +11369,7 @@
         <v>46204.82892361111</v>
       </c>
       <c r="F143" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>24</v>
@@ -11437,7 +11437,7 @@
         <v>46213.615798611114</v>
       </c>
       <c r="F144" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>27</v>
@@ -11505,7 +11505,7 @@
         <v>46222.723344907405</v>
       </c>
       <c r="F145" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>27</v>
@@ -11573,7 +11573,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F146" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>27</v>
@@ -11641,7 +11641,7 @@
         <v>46206.49621527778</v>
       </c>
       <c r="F147" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>30</v>
@@ -11709,7 +11709,7 @@
         <v>46194.10880787037</v>
       </c>
       <c r="F148" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>24</v>
@@ -11777,7 +11777,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F149" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>30</v>
@@ -11845,7 +11845,7 @@
         <v>46220.31099537037</v>
       </c>
       <c r="F150" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>30</v>
@@ -11913,7 +11913,7 @@
         <v>46220.05306712963</v>
       </c>
       <c r="F151" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>30</v>
@@ -11981,7 +11981,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F152" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>30</v>
@@ -12049,7 +12049,7 @@
         <v>46202.80762731482</v>
       </c>
       <c r="F153" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>30</v>
@@ -12117,7 +12117,7 @@
         <v>46213.61820601852</v>
       </c>
       <c r="F154" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>30</v>
@@ -12185,7 +12185,7 @@
         <v>46212.191030092596</v>
       </c>
       <c r="F155" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>30</v>
@@ -12253,7 +12253,7 @@
         <v>46214.51880787037</v>
       </c>
       <c r="F156" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>30</v>
@@ -12321,7 +12321,7 @@
         <v>46198.053506944445</v>
       </c>
       <c r="F157" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G157" s="0" t="s">
         <v>30</v>
@@ -12389,7 +12389,7 @@
         <v>46197.68172453704</v>
       </c>
       <c r="F158" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G158" s="0" t="s">
         <v>30</v>
@@ -12457,7 +12457,7 @@
         <v>46217.92925925926</v>
       </c>
       <c r="F159" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>24</v>
@@ -12525,7 +12525,7 @@
         <v>46208.01679398148</v>
       </c>
       <c r="F160" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>30</v>
@@ -12593,7 +12593,7 @@
         <v>46199.4216087963</v>
       </c>
       <c r="F161" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>27</v>
@@ -12661,7 +12661,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F162" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>27</v>
@@ -12729,7 +12729,7 @@
         <v>46218.91337962963</v>
       </c>
       <c r="F163" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>30</v>
@@ -12797,7 +12797,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F164" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>24</v>
@@ -12865,7 +12865,7 @@
         <v>46203.398622685185</v>
       </c>
       <c r="F165" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>24</v>
@@ -12933,7 +12933,7 @@
         <v>46204.071388888886</v>
       </c>
       <c r="F166" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>24</v>
@@ -13001,7 +13001,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F167" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>27</v>
@@ -13069,7 +13069,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F168" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>24</v>
@@ -13137,7 +13137,7 @@
         <v>46207.340208333335</v>
       </c>
       <c r="F169" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>30</v>
@@ -13205,7 +13205,7 @@
         <v>46203.22761574074</v>
       </c>
       <c r="F170" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>30</v>
@@ -13273,7 +13273,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F171" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>30</v>
@@ -13341,7 +13341,7 @@
         <v>46209.27856481481</v>
       </c>
       <c r="F172" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>30</v>
@@ -13409,7 +13409,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F173" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>24</v>
@@ -13477,7 +13477,7 @@
         <v>46222.71545138889</v>
       </c>
       <c r="F174" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>30</v>
@@ -13545,7 +13545,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F175" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>24</v>
@@ -13613,7 +13613,7 @@
         <v>46221.20269675926</v>
       </c>
       <c r="F176" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>30</v>
@@ -13681,7 +13681,7 @@
         <v>46200.90429398148</v>
       </c>
       <c r="F177" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>24</v>
@@ -13749,7 +13749,7 @@
         <v>46201.17297453704</v>
       </c>
       <c r="F178" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>30</v>
@@ -13817,7 +13817,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F179" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>24</v>
@@ -13885,7 +13885,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F180" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G180" s="0" t="s">
         <v>24</v>
@@ -13953,7 +13953,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F181" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>24</v>
@@ -14021,7 +14021,7 @@
         <v>46197.398356481484</v>
       </c>
       <c r="F182" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>24</v>
@@ -14089,7 +14089,7 @@
         <v>46213.6180787037</v>
       </c>
       <c r="F183" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>24</v>
@@ -14157,7 +14157,7 @@
         <v>46216.91412037037</v>
       </c>
       <c r="F184" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>24</v>
@@ -14225,7 +14225,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F185" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>24</v>
@@ -14293,7 +14293,7 @@
         <v>46204.81618055556</v>
       </c>
       <c r="F186" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G186" s="0" t="s">
         <v>24</v>
@@ -14361,7 +14361,7 @@
         <v>46184.345671296294</v>
       </c>
       <c r="F187" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>24</v>
@@ -14429,7 +14429,7 @@
         <v>46213.61584490741</v>
       </c>
       <c r="F188" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>24</v>
@@ -14497,7 +14497,7 @@
         <v>46198.76695601852</v>
       </c>
       <c r="F189" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>24</v>
@@ -14565,7 +14565,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F190" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>24</v>
@@ -14633,7 +14633,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F191" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>27</v>
@@ -14701,7 +14701,7 @@
         <v>46207.38381944445</v>
       </c>
       <c r="F192" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>30</v>
@@ -14769,7 +14769,7 @@
         <v>46198.764710648145</v>
       </c>
       <c r="F193" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>24</v>
@@ -14837,7 +14837,7 @@
         <v>46208.60445601852</v>
       </c>
       <c r="F194" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G194" s="0" t="s">
         <v>30</v>
@@ -14905,7 +14905,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F195" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G195" s="0" t="s">
         <v>27</v>
@@ -14973,7 +14973,7 @@
         <v>46213.61833333333</v>
       </c>
       <c r="F196" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G196" s="0" t="s">
         <v>27</v>
@@ -15041,7 +15041,7 @@
         <v>46198.7566087963</v>
       </c>
       <c r="F197" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G197" s="0" t="s">
         <v>24</v>
@@ -15109,7 +15109,7 @@
         <v>46204.591203703705</v>
       </c>
       <c r="F198" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G198" s="0" t="s">
         <v>30</v>
@@ -15177,7 +15177,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F199" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>24</v>
@@ -15245,7 +15245,7 @@
         <v>46203.38690972222</v>
       </c>
       <c r="F200" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>24</v>
@@ -15313,7 +15313,7 @@
         <v>46223.08658564815</v>
       </c>
       <c r="F201" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>30</v>
@@ -15381,7 +15381,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F202" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>24</v>
@@ -15449,7 +15449,7 @@
         <v>46217.32613425926</v>
       </c>
       <c r="F203" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>30</v>
@@ -15517,7 +15517,7 @@
         <v>46199.954201388886</v>
       </c>
       <c r="F204" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>30</v>
@@ -15585,7 +15585,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F205" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>27</v>
@@ -15653,7 +15653,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F206" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>27</v>
@@ -15721,7 +15721,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F207" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G207" s="0" t="s">
         <v>24</v>
@@ -15789,7 +15789,7 @@
         <v>46184.344409722224</v>
       </c>
       <c r="F208" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G208" s="0" t="s">
         <v>24</v>
@@ -15857,7 +15857,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F209" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G209" s="0" t="s">
         <v>27</v>
@@ -15925,7 +15925,7 @@
         <v>46217.72965277778</v>
       </c>
       <c r="F210" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>24</v>
@@ -15993,7 +15993,7 @@
         <v>46196.43208333333</v>
       </c>
       <c r="F211" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>30</v>
@@ -16061,7 +16061,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F212" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>27</v>
@@ -16129,7 +16129,7 @@
         <v>46204.591203703705</v>
       </c>
       <c r="F213" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>30</v>
@@ -16197,7 +16197,7 @@
         <v>46212.38707175926</v>
       </c>
       <c r="F214" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>30</v>
@@ -16265,7 +16265,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F215" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>27</v>
@@ -16333,7 +16333,7 @@
         <v>46219.39318287037</v>
       </c>
       <c r="F216" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>30</v>
@@ -16401,7 +16401,7 @@
         <v>46213.61585648148</v>
       </c>
       <c r="F217" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>24</v>
@@ -16469,7 +16469,7 @@
         <v>46205.85377314815</v>
       </c>
       <c r="F218" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>24</v>
@@ -16537,7 +16537,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F219" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>24</v>
@@ -16605,7 +16605,7 @@
         <v>46194.496782407405</v>
       </c>
       <c r="F220" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G220" s="0" t="s">
         <v>27</v>
@@ -16673,7 +16673,7 @@
         <v>46206.041817129626</v>
       </c>
       <c r="F221" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>30</v>
@@ -16741,7 +16741,7 @@
         <v>46211.74564814815</v>
       </c>
       <c r="F222" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>24</v>
@@ -16809,7 +16809,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F223" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>24</v>
@@ -16877,7 +16877,7 @@
         <v>46198.76357638889</v>
       </c>
       <c r="F224" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>24</v>
@@ -16945,7 +16945,7 @@
         <v>46214.41127314815</v>
       </c>
       <c r="F225" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>30</v>
@@ -17013,7 +17013,7 @@
         <v>46210.39944444445</v>
       </c>
       <c r="F226" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>24</v>
@@ -17081,7 +17081,7 @@
         <v>46219.765706018516</v>
       </c>
       <c r="F227" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>24</v>
@@ -17149,7 +17149,7 @@
         <v>46203.900046296294</v>
       </c>
       <c r="F228" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G228" s="0" t="s">
         <v>27</v>
@@ -17217,7 +17217,7 @@
         <v>46213.618310185186</v>
       </c>
       <c r="F229" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>27</v>
@@ -17285,7 +17285,7 @@
         <v>46198.75818287037</v>
       </c>
       <c r="F230" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>24</v>
@@ -17353,7 +17353,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F231" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G231" s="0" t="s">
         <v>27</v>
@@ -17421,7 +17421,7 @@
         <v>46199.24039351852</v>
       </c>
       <c r="F232" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>30</v>
@@ -17489,7 +17489,7 @@
         <v>46207.7878125</v>
       </c>
       <c r="F233" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>30</v>
@@ -17557,7 +17557,7 @@
         <v>46200.88856481481</v>
       </c>
       <c r="F234" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G234" s="0" t="s">
         <v>27</v>
@@ -17625,7 +17625,7 @@
         <v>46207.091145833336</v>
       </c>
       <c r="F235" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G235" s="0" t="s">
         <v>30</v>
@@ -17693,7 +17693,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F236" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>24</v>
@@ -17761,7 +17761,7 @@
         <v>46197.33201388889</v>
       </c>
       <c r="F237" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>24</v>
@@ -17829,7 +17829,7 @@
         <v>46210.11184027778</v>
       </c>
       <c r="F238" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G238" s="0" t="s">
         <v>24</v>
@@ -17897,7 +17897,7 @@
         <v>46202.603946759256</v>
       </c>
       <c r="F239" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G239" s="0" t="s">
         <v>24</v>
@@ -17965,7 +17965,7 @@
         <v>46213.61804398148</v>
       </c>
       <c r="F240" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>24</v>
@@ -18033,7 +18033,7 @@
         <v>46208.28020833333</v>
       </c>
       <c r="F241" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G241" s="0" t="s">
         <v>27</v>
@@ -18101,7 +18101,7 @@
         <v>46213.618055555555</v>
       </c>
       <c r="F242" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G242" s="0" t="s">
         <v>27</v>
@@ -18169,7 +18169,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F243" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>27</v>
@@ -18237,7 +18237,7 @@
         <v>46220.95984953704</v>
       </c>
       <c r="F244" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G244" s="0" t="s">
         <v>30</v>
@@ -18305,7 +18305,7 @@
         <v>46221.91984953704</v>
       </c>
       <c r="F245" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>30</v>
@@ -18373,7 +18373,7 @@
         <v>46222.38579861111</v>
       </c>
       <c r="F246" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G246" s="0" t="s">
         <v>30</v>
@@ -18441,7 +18441,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F247" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>24</v>
@@ -18509,7 +18509,7 @@
         <v>46187.9200462963</v>
       </c>
       <c r="F248" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G248" s="0" t="s">
         <v>24</v>
@@ -18577,7 +18577,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F249" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G249" s="0" t="s">
         <v>27</v>
@@ -18645,7 +18645,7 @@
         <v>46204.36974537037</v>
       </c>
       <c r="F250" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G250" s="0" t="s">
         <v>30</v>
@@ -18713,7 +18713,7 @@
         <v>46213.61809027778</v>
       </c>
       <c r="F251" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G251" s="0" t="s">
         <v>27</v>
@@ -18781,7 +18781,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F252" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>24</v>
@@ -18849,7 +18849,7 @@
         <v>46213.61819444445</v>
       </c>
       <c r="F253" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>27</v>
@@ -18917,7 +18917,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F254" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G254" s="0" t="s">
         <v>24</v>
@@ -18985,7 +18985,7 @@
         <v>46222.62453703704</v>
       </c>
       <c r="F255" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G255" s="0" t="s">
         <v>30</v>
@@ -19053,7 +19053,7 @@
         <v>46201.332870370374</v>
       </c>
       <c r="F256" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>24</v>
@@ -19121,7 +19121,7 @@
         <v>46223.26967592593</v>
       </c>
       <c r="F257" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>30</v>
@@ -19189,7 +19189,7 @@
         <v>46197.03113425926</v>
       </c>
       <c r="F258" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>24</v>
@@ -19257,7 +19257,7 @@
         <v>46212.285219907404</v>
       </c>
       <c r="F259" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>30</v>
@@ -19325,7 +19325,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F260" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>24</v>
@@ -19393,7 +19393,7 @@
         <v>46200.98619212963</v>
       </c>
       <c r="F261" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>30</v>
@@ -19461,7 +19461,7 @@
         <v>46213.61833333333</v>
       </c>
       <c r="F262" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>27</v>
@@ -19529,7 +19529,7 @@
         <v>46212.06758101852</v>
       </c>
       <c r="F263" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G263" s="0" t="s">
         <v>30</v>
@@ -19597,7 +19597,7 @@
         <v>46213.61584490741</v>
       </c>
       <c r="F264" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>27</v>
@@ -19665,7 +19665,7 @@
         <v>46207.18613425926</v>
       </c>
       <c r="F265" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G265" s="0" t="s">
         <v>30</v>
@@ -19733,7 +19733,7 @@
         <v>46218.881574074076</v>
       </c>
       <c r="F266" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G266" s="0" t="s">
         <v>27</v>
@@ -19801,7 +19801,7 @@
         <v>46215.3794212963</v>
       </c>
       <c r="F267" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G267" s="0" t="s">
         <v>27</v>
@@ -19869,7 +19869,7 @@
         <v>46198.763344907406</v>
       </c>
       <c r="F268" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G268" s="0" t="s">
         <v>24</v>
@@ -19937,7 +19937,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F269" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G269" s="0" t="s">
         <v>24</v>
@@ -20005,7 +20005,7 @@
         <v>46198.86886574074</v>
       </c>
       <c r="F270" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>30</v>
@@ -20073,7 +20073,7 @@
         <v>46198.76422453704</v>
       </c>
       <c r="F271" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>24</v>
@@ -20141,7 +20141,7 @@
         <v>46206.39832175926</v>
       </c>
       <c r="F272" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>30</v>
@@ -20209,7 +20209,7 @@
         <v>46201.828206018516</v>
       </c>
       <c r="F273" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G273" s="0" t="s">
         <v>30</v>
@@ -20277,7 +20277,7 @@
         <v>46198.13486111111</v>
       </c>
       <c r="F274" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>24</v>
@@ -20345,7 +20345,7 @@
         <v>46184.34568287037</v>
       </c>
       <c r="F275" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G275" s="0" t="s">
         <v>24</v>
@@ -20413,7 +20413,7 @@
         <v>46217.38422453704</v>
       </c>
       <c r="F276" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>30</v>
@@ -20481,7 +20481,7 @@
         <v>46210.52042824074</v>
       </c>
       <c r="F277" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G277" s="0" t="s">
         <v>24</v>
@@ -20549,7 +20549,7 @@
         <v>46198.487546296295</v>
       </c>
       <c r="F278" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G278" s="0" t="s">
         <v>30</v>
@@ -20617,7 +20617,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F279" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G279" s="0" t="s">
         <v>24</v>
@@ -20685,7 +20685,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F280" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>24</v>
@@ -20753,7 +20753,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F281" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G281" s="0" t="s">
         <v>24</v>
@@ -20821,7 +20821,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F282" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G282" s="0" t="s">
         <v>30</v>
@@ -20889,7 +20889,7 @@
         <v>46199.37</v>
       </c>
       <c r="F283" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>30</v>
@@ -20957,7 +20957,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F284" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G284" s="0" t="s">
         <v>27</v>
@@ -21025,7 +21025,7 @@
         <v>46200.507418981484</v>
       </c>
       <c r="F285" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G285" s="0" t="s">
         <v>30</v>
@@ -21093,7 +21093,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F286" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>27</v>
@@ -21161,7 +21161,7 @@
         <v>46219.00199074074</v>
       </c>
       <c r="F287" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>24</v>
@@ -21229,7 +21229,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F288" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>24</v>
@@ -21297,7 +21297,7 @@
         <v>46222.21196759259</v>
       </c>
       <c r="F289" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G289" s="0" t="s">
         <v>30</v>
@@ -21365,7 +21365,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F290" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G290" s="0" t="s">
         <v>24</v>
@@ -21433,7 +21433,7 @@
         <v>46218.09614583333</v>
       </c>
       <c r="F291" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G291" s="0" t="s">
         <v>27</v>
@@ -21501,7 +21501,7 @@
         <v>46206.616875</v>
       </c>
       <c r="F292" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G292" s="0" t="s">
         <v>30</v>
@@ -21569,7 +21569,7 @@
         <v>46206.85376157407</v>
       </c>
       <c r="F293" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G293" s="0" t="s">
         <v>24</v>
@@ -21637,7 +21637,7 @@
         <v>46220.37621527778</v>
       </c>
       <c r="F294" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G294" s="0" t="s">
         <v>30</v>
@@ -21705,7 +21705,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F295" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>24</v>
@@ -21773,7 +21773,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F296" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>27</v>
@@ -21841,7 +21841,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F297" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G297" s="0" t="s">
         <v>24</v>
@@ -21909,7 +21909,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F298" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>27</v>
@@ -21977,7 +21977,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F299" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G299" s="0" t="s">
         <v>24</v>
@@ -22045,7 +22045,7 @@
         <v>46213.6180787037</v>
       </c>
       <c r="F300" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G300" s="0" t="s">
         <v>27</v>
@@ -22113,7 +22113,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F301" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G301" s="0" t="s">
         <v>27</v>
@@ -22181,7 +22181,7 @@
         <v>46215.346342592595</v>
       </c>
       <c r="F302" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G302" s="0" t="s">
         <v>27</v>
@@ -22249,7 +22249,7 @@
         <v>46208.34142361111</v>
       </c>
       <c r="F303" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G303" s="0" t="s">
         <v>27</v>
@@ -22317,7 +22317,7 @@
         <v>46184.34611111111</v>
       </c>
       <c r="F304" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G304" s="0" t="s">
         <v>24</v>
@@ -22385,7 +22385,7 @@
         <v>46207.44116898148</v>
       </c>
       <c r="F305" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G305" s="0" t="s">
         <v>27</v>
@@ -22453,7 +22453,7 @@
         <v>46217.771006944444</v>
       </c>
       <c r="F306" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G306" s="0" t="s">
         <v>24</v>
@@ -22521,7 +22521,7 @@
         <v>46217.77065972222</v>
       </c>
       <c r="F307" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G307" s="0" t="s">
         <v>24</v>
@@ -22589,7 +22589,7 @@
         <v>46213.12200231481</v>
       </c>
       <c r="F308" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G308" s="0" t="s">
         <v>30</v>
@@ -22657,7 +22657,7 @@
         <v>46211.78650462963</v>
       </c>
       <c r="F309" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G309" s="0" t="s">
         <v>30</v>
@@ -22725,7 +22725,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F310" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>27</v>
@@ -22793,7 +22793,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F311" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>30</v>
@@ -22861,7 +22861,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F312" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>27</v>
@@ -22929,7 +22929,7 @@
         <v>46205.74003472222</v>
       </c>
       <c r="F313" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G313" s="0" t="s">
         <v>27</v>
@@ -22997,7 +22997,7 @@
         <v>46223.341828703706</v>
       </c>
       <c r="F314" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G314" s="0" t="s">
         <v>30</v>
@@ -23065,7 +23065,7 @@
         <v>46213.61578703704</v>
       </c>
       <c r="F315" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G315" s="0" t="s">
         <v>27</v>
@@ -23133,7 +23133,7 @@
         <v>46214.6358912037</v>
       </c>
       <c r="F316" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G316" s="0" t="s">
         <v>30</v>
@@ -23201,7 +23201,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F317" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G317" s="0" t="s">
         <v>27</v>
@@ -23269,7 +23269,7 @@
         <v>46222.05388888889</v>
       </c>
       <c r="F318" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G318" s="0" t="s">
         <v>30</v>
@@ -23337,7 +23337,7 @@
         <v>46199.95371527778</v>
       </c>
       <c r="F319" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G319" s="0" t="s">
         <v>27</v>
@@ -23405,7 +23405,7 @@
         <v>46212.29601851852</v>
       </c>
       <c r="F320" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G320" s="0" t="s">
         <v>30</v>
@@ -23473,7 +23473,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F321" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G321" s="0" t="s">
         <v>24</v>
@@ -23541,7 +23541,7 @@
         <v>46215.09512731482</v>
       </c>
       <c r="F322" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>30</v>
@@ -23609,7 +23609,7 @@
         <v>46203.39921296296</v>
       </c>
       <c r="F323" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G323" s="0" t="s">
         <v>24</v>
@@ -23677,7 +23677,7 @@
         <v>46206.91523148148</v>
       </c>
       <c r="F324" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G324" s="0" t="s">
         <v>24</v>
@@ -23745,7 +23745,7 @@
         <v>46213.618055555555</v>
       </c>
       <c r="F325" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G325" s="0" t="s">
         <v>24</v>
@@ -23813,7 +23813,7 @@
         <v>46213.61820601852</v>
       </c>
       <c r="F326" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G326" s="0" t="s">
         <v>24</v>
@@ -23881,7 +23881,7 @@
         <v>46216.794907407406</v>
       </c>
       <c r="F327" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G327" s="0" t="s">
         <v>24</v>
@@ -23949,7 +23949,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F328" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G328" s="0" t="s">
         <v>24</v>
@@ -24017,7 +24017,7 @@
         <v>46212.73332175926</v>
       </c>
       <c r="F329" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G329" s="0" t="s">
         <v>30</v>
@@ -24085,7 +24085,7 @@
         <v>46218.88267361111</v>
       </c>
       <c r="F330" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G330" s="0" t="s">
         <v>24</v>
@@ -24153,7 +24153,7 @@
         <v>46220.21396990741</v>
       </c>
       <c r="F331" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G331" s="0" t="s">
         <v>30</v>
@@ -24221,7 +24221,7 @@
         <v>46212.47420138889</v>
       </c>
       <c r="F332" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G332" s="0" t="s">
         <v>24</v>
@@ -24289,7 +24289,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F333" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G333" s="0" t="s">
         <v>27</v>
@@ -24357,7 +24357,7 @@
         <v>46199.395949074074</v>
       </c>
       <c r="F334" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G334" s="0" t="s">
         <v>30</v>
@@ -24425,7 +24425,7 @@
         <v>46218.05547453704</v>
       </c>
       <c r="F335" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G335" s="0" t="s">
         <v>24</v>
@@ -24493,7 +24493,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F336" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>27</v>
@@ -24561,7 +24561,7 @@
         <v>46184.34570601852</v>
       </c>
       <c r="F337" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>24</v>
@@ -24629,7 +24629,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F338" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G338" s="0" t="s">
         <v>27</v>
@@ -24697,7 +24697,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F339" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G339" s="0" t="s">
         <v>27</v>
@@ -24765,7 +24765,7 @@
         <v>46198.756527777776</v>
       </c>
       <c r="F340" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>24</v>
@@ -24833,7 +24833,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F341" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G341" s="0" t="s">
         <v>27</v>
@@ -24901,7 +24901,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F342" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G342" s="0" t="s">
         <v>27</v>
@@ -24969,7 +24969,7 @@
         <v>46198.76427083334</v>
       </c>
       <c r="F343" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>24</v>
@@ -25037,7 +25037,7 @@
         <v>46196.08101851852</v>
       </c>
       <c r="F344" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G344" s="0" t="s">
         <v>24</v>
@@ -25105,7 +25105,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F345" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G345" s="0" t="s">
         <v>27</v>
@@ -25173,7 +25173,7 @@
         <v>46207.28523148148</v>
       </c>
       <c r="F346" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G346" s="0" t="s">
         <v>24</v>
@@ -25241,7 +25241,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F347" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G347" s="0" t="s">
         <v>27</v>
@@ -25309,7 +25309,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F348" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>27</v>
@@ -25377,7 +25377,7 @@
         <v>46196.788564814815</v>
       </c>
       <c r="F349" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G349" s="0" t="s">
         <v>24</v>
@@ -25445,7 +25445,7 @@
         <v>46217.99606481481</v>
       </c>
       <c r="F350" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G350" s="0" t="s">
         <v>30</v>
@@ -25513,7 +25513,7 @@
         <v>46217.72994212963</v>
       </c>
       <c r="F351" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>24</v>
@@ -25581,7 +25581,7 @@
         <v>46200.45096064815</v>
       </c>
       <c r="F352" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G352" s="0" t="s">
         <v>27</v>
@@ -25649,7 +25649,7 @@
         <v>46213.44936342593</v>
       </c>
       <c r="F353" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G353" s="0" t="s">
         <v>30</v>
@@ -25717,7 +25717,7 @@
         <v>46207.18237268519</v>
       </c>
       <c r="F354" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G354" s="0" t="s">
         <v>24</v>
@@ -25785,7 +25785,7 @@
         <v>46220.24438657407</v>
       </c>
       <c r="F355" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G355" s="0" t="s">
         <v>30</v>
@@ -25853,7 +25853,7 @@
         <v>46198.89733796296</v>
       </c>
       <c r="F356" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G356" s="0" t="s">
         <v>30</v>
@@ -25921,7 +25921,7 @@
         <v>46213.282858796294</v>
       </c>
       <c r="F357" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G357" s="0" t="s">
         <v>30</v>
@@ -25989,7 +25989,7 @@
         <v>46218.46706018518</v>
       </c>
       <c r="F358" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G358" s="0" t="s">
         <v>30</v>
@@ -26057,7 +26057,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F359" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G359" s="0" t="s">
         <v>24</v>
@@ -26125,7 +26125,7 @@
         <v>46217.69572916667</v>
       </c>
       <c r="F360" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G360" s="0" t="s">
         <v>30</v>
@@ -26193,7 +26193,7 @@
         <v>46219.77547453704</v>
       </c>
       <c r="F361" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G361" s="0" t="s">
         <v>30</v>
@@ -26261,7 +26261,7 @@
         <v>46219.43380787037</v>
       </c>
       <c r="F362" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G362" s="0" t="s">
         <v>30</v>
@@ -26329,7 +26329,7 @@
         <v>46205.19603009259</v>
       </c>
       <c r="F363" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G363" s="0" t="s">
         <v>30</v>
@@ -26397,7 +26397,7 @@
         <v>46196.08101851852</v>
       </c>
       <c r="F364" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G364" s="0" t="s">
         <v>24</v>
@@ -26465,7 +26465,7 @@
         <v>46196.88885416667</v>
       </c>
       <c r="F365" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G365" s="0" t="s">
         <v>24</v>
@@ -26533,7 +26533,7 @@
         <v>46213.618055555555</v>
       </c>
       <c r="F366" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G366" s="0" t="s">
         <v>27</v>
@@ -26601,7 +26601,7 @@
         <v>46199.89765046296</v>
       </c>
       <c r="F367" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G367" s="0" t="s">
         <v>30</v>
@@ -26669,7 +26669,7 @@
         <v>46203.38673611111</v>
       </c>
       <c r="F368" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G368" s="0" t="s">
         <v>24</v>
@@ -26737,7 +26737,7 @@
         <v>46214.55940972222</v>
       </c>
       <c r="F369" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G369" s="0" t="s">
         <v>30</v>
@@ -26805,7 +26805,7 @@
         <v>46218.193761574075</v>
       </c>
       <c r="F370" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G370" s="0" t="s">
         <v>30</v>
@@ -26873,7 +26873,7 @@
         <v>46215.391805555555</v>
       </c>
       <c r="F371" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G371" s="0" t="s">
         <v>27</v>
@@ -26941,7 +26941,7 @@
         <v>46208.49730324074</v>
       </c>
       <c r="F372" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G372" s="0" t="s">
         <v>27</v>
@@ -27009,7 +27009,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F373" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G373" s="0" t="s">
         <v>24</v>
@@ -27077,7 +27077,7 @@
         <v>46223.20361111111</v>
       </c>
       <c r="F374" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G374" s="0" t="s">
         <v>30</v>
@@ -27145,7 +27145,7 @@
         <v>46220.93790509259</v>
       </c>
       <c r="F375" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G375" s="0" t="s">
         <v>30</v>
@@ -27213,7 +27213,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F376" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G376" s="0" t="s">
         <v>24</v>
@@ -27281,7 +27281,7 @@
         <v>46205.35525462963</v>
       </c>
       <c r="F377" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G377" s="0" t="s">
         <v>30</v>
@@ -27349,7 +27349,7 @@
         <v>46200.595925925925</v>
       </c>
       <c r="F378" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G378" s="0" t="s">
         <v>24</v>
@@ -27417,7 +27417,7 @@
         <v>46198.36408564815</v>
       </c>
       <c r="F379" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G379" s="0" t="s">
         <v>30</v>
@@ -27485,7 +27485,7 @@
         <v>46213.61833333333</v>
       </c>
       <c r="F380" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G380" s="0" t="s">
         <v>27</v>
@@ -27553,7 +27553,7 @@
         <v>46213.61821759259</v>
       </c>
       <c r="F381" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G381" s="0" t="s">
         <v>27</v>
@@ -27621,7 +27621,7 @@
         <v>46214.184386574074</v>
       </c>
       <c r="F382" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G382" s="0" t="s">
         <v>30</v>
@@ -27689,7 +27689,7 @@
         <v>46208.95462962963</v>
       </c>
       <c r="F383" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G383" s="0" t="s">
         <v>27</v>
@@ -27757,7 +27757,7 @@
         <v>46209.34474537037</v>
       </c>
       <c r="F384" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G384" s="0" t="s">
         <v>30</v>
@@ -27825,7 +27825,7 @@
         <v>46203.6659375</v>
       </c>
       <c r="F385" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G385" s="0" t="s">
         <v>24</v>
@@ -27893,7 +27893,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F386" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G386" s="0" t="s">
         <v>24</v>
@@ -27961,7 +27961,7 @@
         <v>46200.84137731481</v>
       </c>
       <c r="F387" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G387" s="0" t="s">
         <v>30</v>
@@ -28029,7 +28029,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F388" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G388" s="0" t="s">
         <v>27</v>
@@ -28097,7 +28097,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F389" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G389" s="0" t="s">
         <v>24</v>
@@ -28165,7 +28165,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F390" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G390" s="0" t="s">
         <v>24</v>
@@ -28233,7 +28233,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F391" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G391" s="0" t="s">
         <v>24</v>
@@ -28301,7 +28301,7 @@
         <v>46207.322233796294</v>
       </c>
       <c r="F392" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G392" s="0" t="s">
         <v>30</v>
@@ -28369,7 +28369,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F393" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G393" s="0" t="s">
         <v>24</v>
@@ -28437,7 +28437,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F394" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G394" s="0" t="s">
         <v>24</v>
@@ -28505,7 +28505,7 @@
         <v>46213.615798611114</v>
       </c>
       <c r="F395" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G395" s="0" t="s">
         <v>24</v>
@@ -28573,7 +28573,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F396" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G396" s="0" t="s">
         <v>24</v>
@@ -28641,7 +28641,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F397" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G397" s="0" t="s">
         <v>24</v>
@@ -28709,7 +28709,7 @@
         <v>46208.80619212963</v>
       </c>
       <c r="F398" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G398" s="0" t="s">
         <v>30</v>
@@ -28777,7 +28777,7 @@
         <v>46207.24060185185</v>
       </c>
       <c r="F399" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G399" s="0" t="s">
         <v>24</v>
@@ -28845,7 +28845,7 @@
         <v>46213.36528935185</v>
       </c>
       <c r="F400" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G400" s="0" t="s">
         <v>27</v>
@@ -28913,7 +28913,7 @@
         <v>46202.50537037037</v>
       </c>
       <c r="F401" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G401" s="0" t="s">
         <v>30</v>
@@ -28981,7 +28981,7 @@
         <v>46217.3975</v>
       </c>
       <c r="F402" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G402" s="0" t="s">
         <v>24</v>
@@ -29049,7 +29049,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F403" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G403" s="0" t="s">
         <v>27</v>
@@ -29117,7 +29117,7 @@
         <v>46217.770949074074</v>
       </c>
       <c r="F404" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G404" s="0" t="s">
         <v>24</v>
@@ -29185,7 +29185,7 @@
         <v>46213.61601851852</v>
       </c>
       <c r="F405" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G405" s="0" t="s">
         <v>24</v>
@@ -29253,7 +29253,7 @@
         <v>46200.24690972222</v>
       </c>
       <c r="F406" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G406" s="0" t="s">
         <v>27</v>
@@ -29321,7 +29321,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F407" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G407" s="0" t="s">
         <v>27</v>
@@ -29389,7 +29389,7 @@
         <v>46197.26045138889</v>
       </c>
       <c r="F408" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G408" s="0" t="s">
         <v>24</v>
@@ -29457,7 +29457,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F409" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G409" s="0" t="s">
         <v>27</v>
@@ -29525,7 +29525,7 @@
         <v>46200.39493055556</v>
       </c>
       <c r="F410" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G410" s="0" t="s">
         <v>24</v>
@@ -29593,7 +29593,7 @@
         <v>46200.50178240741</v>
       </c>
       <c r="F411" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G411" s="0" t="s">
         <v>30</v>
@@ -29661,7 +29661,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F412" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G412" s="0" t="s">
         <v>27</v>
@@ -29729,7 +29729,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F413" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G413" s="0" t="s">
         <v>27</v>
@@ -29797,7 +29797,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F414" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G414" s="0" t="s">
         <v>24</v>
@@ -29865,7 +29865,7 @@
         <v>46223.340416666666</v>
       </c>
       <c r="F415" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G415" s="0" t="s">
         <v>30</v>
@@ -29933,7 +29933,7 @@
         <v>46222.22011574074</v>
       </c>
       <c r="F416" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G416" s="0" t="s">
         <v>30</v>
@@ -30001,7 +30001,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F417" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G417" s="0" t="s">
         <v>27</v>
@@ -30069,7 +30069,7 @@
         <v>46221.56353009259</v>
       </c>
       <c r="F418" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G418" s="0" t="s">
         <v>30</v>
@@ -30137,7 +30137,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F419" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G419" s="0" t="s">
         <v>27</v>
@@ -30205,7 +30205,7 @@
         <v>46201.81197916667</v>
       </c>
       <c r="F420" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G420" s="0" t="s">
         <v>30</v>
@@ -30273,7 +30273,7 @@
         <v>46196.87100694444</v>
       </c>
       <c r="F421" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G421" s="0" t="s">
         <v>30</v>
@@ -30341,7 +30341,7 @@
         <v>46217.07877314815</v>
       </c>
       <c r="F422" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G422" s="0" t="s">
         <v>30</v>
@@ -30409,7 +30409,7 @@
         <v>46223.367638888885</v>
       </c>
       <c r="F423" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G423" s="0" t="s">
         <v>30</v>
@@ -30477,7 +30477,7 @@
         <v>46213.33634259259</v>
       </c>
       <c r="F424" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G424" s="0" t="s">
         <v>30</v>
@@ -30545,7 +30545,7 @@
         <v>46203.38674768519</v>
       </c>
       <c r="F425" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G425" s="0" t="s">
         <v>24</v>
@@ -30613,7 +30613,7 @@
         <v>46216.91412037037</v>
       </c>
       <c r="F426" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G426" s="0" t="s">
         <v>24</v>
@@ -30681,7 +30681,7 @@
         <v>46199.38827546296</v>
       </c>
       <c r="F427" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G427" s="0" t="s">
         <v>24</v>
@@ -30749,7 +30749,7 @@
         <v>46211.747569444444</v>
       </c>
       <c r="F428" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G428" s="0" t="s">
         <v>24</v>
@@ -30817,7 +30817,7 @@
         <v>46222.36450231481</v>
       </c>
       <c r="F429" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G429" s="0" t="s">
         <v>27</v>
@@ -30885,7 +30885,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F430" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G430" s="0" t="s">
         <v>27</v>
@@ -30953,7 +30953,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F431" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G431" s="0" t="s">
         <v>27</v>
@@ -31021,7 +31021,7 @@
         <v>46214.036574074074</v>
       </c>
       <c r="F432" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G432" s="0" t="s">
         <v>24</v>
@@ -31089,7 +31089,7 @@
         <v>46198.75832175926</v>
       </c>
       <c r="F433" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G433" s="0" t="s">
         <v>24</v>
@@ -31157,7 +31157,7 @@
         <v>46213.1378125</v>
       </c>
       <c r="F434" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G434" s="0" t="s">
         <v>30</v>
@@ -31225,7 +31225,7 @@
         <v>46218.15008101852</v>
       </c>
       <c r="F435" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G435" s="0" t="s">
         <v>30</v>
@@ -31293,7 +31293,7 @@
         <v>46200.08666666667</v>
       </c>
       <c r="F436" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G436" s="0" t="s">
         <v>30</v>
@@ -31361,7 +31361,7 @@
         <v>46221.995520833334</v>
       </c>
       <c r="F437" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G437" s="0" t="s">
         <v>30</v>
@@ -31429,7 +31429,7 @@
         <v>46191.20039351852</v>
       </c>
       <c r="F438" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G438" s="0" t="s">
         <v>24</v>
@@ -31497,7 +31497,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F439" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G439" s="0" t="s">
         <v>27</v>
@@ -31565,7 +31565,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F440" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G440" s="0" t="s">
         <v>24</v>
@@ -31633,7 +31633,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F441" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G441" s="0" t="s">
         <v>24</v>
@@ -31701,7 +31701,7 @@
         <v>46197.6375462963</v>
       </c>
       <c r="F442" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G442" s="0" t="s">
         <v>24</v>
@@ -31769,7 +31769,7 @@
         <v>46197.037523148145</v>
       </c>
       <c r="F443" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G443" s="0" t="s">
         <v>24</v>
@@ -31837,7 +31837,7 @@
         <v>46198.31060185185</v>
       </c>
       <c r="F444" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G444" s="0" t="s">
         <v>30</v>
@@ -31905,7 +31905,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F445" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G445" s="0" t="s">
         <v>24</v>
@@ -31973,7 +31973,7 @@
         <v>46209.31466435185</v>
       </c>
       <c r="F446" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G446" s="0" t="s">
         <v>30</v>
@@ -32041,7 +32041,7 @@
         <v>46206.72038194445</v>
       </c>
       <c r="F447" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G447" s="0" t="s">
         <v>30</v>
@@ -32109,7 +32109,7 @@
         <v>46197.46810185185</v>
       </c>
       <c r="F448" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G448" s="0" t="s">
         <v>24</v>
@@ -32177,7 +32177,7 @@
         <v>46221.68960648148</v>
       </c>
       <c r="F449" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G449" s="0" t="s">
         <v>30</v>
@@ -32245,7 +32245,7 @@
         <v>46217.79634259259</v>
       </c>
       <c r="F450" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G450" s="0" t="s">
         <v>27</v>
@@ -32313,7 +32313,7 @@
         <v>46202.349328703705</v>
       </c>
       <c r="F451" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G451" s="0" t="s">
         <v>30</v>
@@ -32381,7 +32381,7 @@
         <v>46213.61802083333</v>
       </c>
       <c r="F452" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G452" s="0" t="s">
         <v>27</v>
@@ -32449,7 +32449,7 @@
         <v>46220.67443287037</v>
       </c>
       <c r="F453" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G453" s="0" t="s">
         <v>30</v>
@@ -32517,7 +32517,7 @@
         <v>46217.73019675926</v>
       </c>
       <c r="F454" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G454" s="0" t="s">
         <v>24</v>
@@ -32585,7 +32585,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F455" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G455" s="0" t="s">
         <v>24</v>
@@ -32653,7 +32653,7 @@
         <v>46216.25659722222</v>
       </c>
       <c r="F456" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G456" s="0" t="s">
         <v>30</v>
@@ -32721,7 +32721,7 @@
         <v>46198.75665509259</v>
       </c>
       <c r="F457" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G457" s="0" t="s">
         <v>24</v>
@@ -32789,7 +32789,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F458" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G458" s="0" t="s">
         <v>27</v>
@@ -32857,7 +32857,7 @@
         <v>46205.784363425926</v>
       </c>
       <c r="F459" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G459" s="0" t="s">
         <v>27</v>
@@ -32925,7 +32925,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F460" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G460" s="0" t="s">
         <v>24</v>
@@ -32993,7 +32993,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F461" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G461" s="0" t="s">
         <v>24</v>
@@ -33061,7 +33061,7 @@
         <v>46198.75827546296</v>
       </c>
       <c r="F462" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G462" s="0" t="s">
         <v>24</v>
@@ -33129,7 +33129,7 @@
         <v>46203.80048611111</v>
       </c>
       <c r="F463" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G463" s="0" t="s">
         <v>27</v>
@@ -33197,7 +33197,7 @@
         <v>46222.2834375</v>
       </c>
       <c r="F464" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G464" s="0" t="s">
         <v>30</v>
@@ -33265,7 +33265,7 @@
         <v>46216.914131944446</v>
       </c>
       <c r="F465" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G465" s="0" t="s">
         <v>24</v>
@@ -33333,7 +33333,7 @@
         <v>46213.61585648148</v>
       </c>
       <c r="F466" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G466" s="0" t="s">
         <v>27</v>
@@ -33401,7 +33401,7 @@
         <v>46207.377118055556</v>
       </c>
       <c r="F467" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G467" s="0" t="s">
         <v>30</v>
@@ -33469,7 +33469,7 @@
         <v>46213.61584490741</v>
       </c>
       <c r="F468" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G468" s="0" t="s">
         <v>27</v>
@@ -33537,7 +33537,7 @@
         <v>46217.62388888889</v>
       </c>
       <c r="F469" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G469" s="0" t="s">
         <v>27</v>
@@ -33605,7 +33605,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F470" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G470" s="0" t="s">
         <v>27</v>
@@ -33673,7 +33673,7 @@
         <v>46216.91412037037</v>
       </c>
       <c r="F471" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G471" s="0" t="s">
         <v>24</v>
@@ -33741,7 +33741,7 @@
         <v>46198.76320601852</v>
       </c>
       <c r="F472" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G472" s="0" t="s">
         <v>24</v>
@@ -33809,7 +33809,7 @@
         <v>46209.364849537036</v>
       </c>
       <c r="F473" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G473" s="0" t="s">
         <v>27</v>
@@ -33877,7 +33877,7 @@
         <v>46210.49642361111</v>
       </c>
       <c r="F474" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G474" s="0" t="s">
         <v>27</v>
@@ -33945,7 +33945,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F475" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G475" s="0" t="s">
         <v>27</v>
@@ -34013,7 +34013,7 @@
         <v>46218.668599537035</v>
       </c>
       <c r="F476" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G476" s="0" t="s">
         <v>30</v>
@@ -34081,7 +34081,7 @@
         <v>46198.76327546296</v>
       </c>
       <c r="F477" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G477" s="0" t="s">
         <v>24</v>
@@ -34149,7 +34149,7 @@
         <v>46197.041238425925</v>
       </c>
       <c r="F478" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G478" s="0" t="s">
         <v>24</v>
@@ -34217,7 +34217,7 @@
         <v>46212.017488425925</v>
       </c>
       <c r="F479" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G479" s="0" t="s">
         <v>27</v>
@@ -34285,7 +34285,7 @@
         <v>46204.81549768519</v>
       </c>
       <c r="F480" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G480" s="0" t="s">
         <v>24</v>
@@ -34353,7 +34353,7 @@
         <v>46200.44310185185</v>
       </c>
       <c r="F481" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G481" s="0" t="s">
         <v>24</v>
@@ -34421,7 +34421,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F482" s="1">
-        <v>46225.362637962964</v>
+        <v>46225.36573055555</v>
       </c>
       <c r="G482" s="0" t="s">
         <v>24</v>

--- a/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
+++ b/AicsTracker/AicsGlobal_Classifications_TimeWindows.xlsx
@@ -2783,7 +2783,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F2" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>24</v>
@@ -2851,7 +2851,7 @@
         <v>46231.978530092594</v>
       </c>
       <c r="F3" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>28</v>
@@ -2878,7 +2878,7 @@
         <v>25</v>
       </c>
       <c r="O3" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="0" t="s">
         <v>25</v>
@@ -2919,7 +2919,7 @@
         <v>46213.61586805555</v>
       </c>
       <c r="F4" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>28</v>
@@ -2987,7 +2987,7 @@
         <v>46227.3103125</v>
       </c>
       <c r="F5" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>28</v>
@@ -3055,7 +3055,7 @@
         <v>46204.34583333333</v>
       </c>
       <c r="F6" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>33</v>
@@ -3094,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="S6" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="0" t="s">
         <v>25</v>
@@ -3123,7 +3123,7 @@
         <v>46216.51424768518</v>
       </c>
       <c r="F7" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>24</v>
@@ -3153,7 +3153,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="0" t="s">
         <v>25</v>
@@ -3191,7 +3191,7 @@
         <v>46207.15827546296</v>
       </c>
       <c r="F8" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>33</v>
@@ -3209,7 +3209,7 @@
         <v>33</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M8" s="0" t="s">
         <v>25</v>
@@ -3229,8 +3229,8 @@
       <c r="R8" s="0">
         <v>1</v>
       </c>
-      <c r="S8" s="0" t="s">
-        <v>25</v>
+      <c r="S8" s="0">
+        <v>0</v>
       </c>
       <c r="T8" s="0" t="s">
         <v>25</v>
@@ -3259,7 +3259,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F9" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>28</v>
@@ -3327,7 +3327,7 @@
         <v>46233.37951388889</v>
       </c>
       <c r="F10" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>28</v>
@@ -3395,7 +3395,7 @@
         <v>46223.86820601852</v>
       </c>
       <c r="F11" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>24</v>
@@ -3463,7 +3463,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F12" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>24</v>
@@ -3531,7 +3531,7 @@
         <v>46225.80055555556</v>
       </c>
       <c r="F13" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>33</v>
@@ -3599,7 +3599,7 @@
         <v>46218.369733796295</v>
       </c>
       <c r="F14" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>24</v>
@@ -3667,7 +3667,7 @@
         <v>46200.30415509259</v>
       </c>
       <c r="F15" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>33</v>
@@ -3735,7 +3735,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F16" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>28</v>
@@ -3803,7 +3803,7 @@
         <v>46214.27086805556</v>
       </c>
       <c r="F17" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G17" s="0" t="s">
         <v>33</v>
@@ -3839,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="R17" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="0" t="s">
         <v>25</v>
@@ -3871,7 +3871,7 @@
         <v>46216.91679398148</v>
       </c>
       <c r="F18" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>33</v>
@@ -3939,7 +3939,7 @@
         <v>46216.51368055555</v>
       </c>
       <c r="F19" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G19" s="0" t="s">
         <v>24</v>
@@ -3969,7 +3969,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="0" t="s">
         <v>25</v>
@@ -4007,7 +4007,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F20" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G20" s="0" t="s">
         <v>28</v>
@@ -4075,7 +4075,7 @@
         <v>46217.789305555554</v>
       </c>
       <c r="F21" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G21" s="0" t="s">
         <v>28</v>
@@ -4143,7 +4143,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F22" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>24</v>
@@ -4211,7 +4211,7 @@
         <v>46217.853541666664</v>
       </c>
       <c r="F23" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G23" s="0" t="s">
         <v>28</v>
@@ -4279,7 +4279,7 @@
         <v>46227.41837962963</v>
       </c>
       <c r="F24" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>33</v>
@@ -4291,7 +4291,7 @@
         <v>33</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K24" s="0" t="s">
         <v>25</v>
@@ -4311,8 +4311,8 @@
       <c r="P24" s="0">
         <v>1</v>
       </c>
-      <c r="Q24" s="0" t="s">
-        <v>25</v>
+      <c r="Q24" s="0">
+        <v>0</v>
       </c>
       <c r="R24" s="0" t="s">
         <v>25</v>
@@ -4347,7 +4347,7 @@
         <v>46211.80736111111</v>
       </c>
       <c r="F25" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G25" s="0" t="s">
         <v>33</v>
@@ -4415,7 +4415,7 @@
         <v>46226.997199074074</v>
       </c>
       <c r="F26" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>28</v>
@@ -4483,7 +4483,7 @@
         <v>46232.09787037037</v>
       </c>
       <c r="F27" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G27" s="0" t="s">
         <v>33</v>
@@ -4551,7 +4551,7 @@
         <v>46213.618055555555</v>
       </c>
       <c r="F28" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>28</v>
@@ -4619,7 +4619,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F29" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G29" s="0" t="s">
         <v>28</v>
@@ -4687,7 +4687,7 @@
         <v>46231.97855324074</v>
       </c>
       <c r="F30" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>24</v>
@@ -4755,7 +4755,7 @@
         <v>46222.964467592596</v>
       </c>
       <c r="F31" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>33</v>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="0" t="s">
         <v>25</v>
@@ -4823,7 +4823,7 @@
         <v>46230.14399305556</v>
       </c>
       <c r="F32" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>33</v>
@@ -4891,7 +4891,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F33" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>24</v>
@@ -4959,7 +4959,7 @@
         <v>46213.61806712963</v>
       </c>
       <c r="F34" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G34" s="0" t="s">
         <v>24</v>
@@ -5027,7 +5027,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F35" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>24</v>
@@ -5095,7 +5095,7 @@
         <v>46214.30170138889</v>
       </c>
       <c r="F36" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>24</v>
@@ -5163,7 +5163,7 @@
         <v>46213.61802083333</v>
       </c>
       <c r="F37" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>24</v>
@@ -5231,7 +5231,7 @@
         <v>46222.379108796296</v>
       </c>
       <c r="F38" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>33</v>
@@ -5299,7 +5299,7 @@
         <v>46233.60729166667</v>
       </c>
       <c r="F39" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>24</v>
@@ -5367,7 +5367,7 @@
         <v>46218.38333333333</v>
       </c>
       <c r="F40" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>24</v>
@@ -5435,7 +5435,7 @@
         <v>46209.39716435185</v>
       </c>
       <c r="F41" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G41" s="0" t="s">
         <v>24</v>
@@ -5503,7 +5503,7 @@
         <v>46221.126967592594</v>
       </c>
       <c r="F42" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>24</v>
@@ -5571,7 +5571,7 @@
         <v>46211.689108796294</v>
       </c>
       <c r="F43" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>33</v>
@@ -5639,7 +5639,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F44" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>28</v>
@@ -5707,7 +5707,7 @@
         <v>46234.37630787037</v>
       </c>
       <c r="F45" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G45" s="0" t="s">
         <v>24</v>
@@ -5775,7 +5775,7 @@
         <v>46217.843506944446</v>
       </c>
       <c r="F46" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>24</v>
@@ -5843,7 +5843,7 @@
         <v>46228.897824074076</v>
       </c>
       <c r="F47" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>33</v>
@@ -5911,7 +5911,7 @@
         <v>46198.75680555555</v>
       </c>
       <c r="F48" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>24</v>
@@ -5929,7 +5929,7 @@
         <v>24</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M48" s="0" t="s">
         <v>25</v>
@@ -5949,8 +5949,8 @@
       <c r="R48" s="0">
         <v>1</v>
       </c>
-      <c r="S48" s="0" t="s">
-        <v>25</v>
+      <c r="S48" s="0">
+        <v>0</v>
       </c>
       <c r="T48" s="0" t="s">
         <v>25</v>
@@ -5979,7 +5979,7 @@
         <v>46229.37550925926</v>
       </c>
       <c r="F49" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G49" s="0" t="s">
         <v>33</v>
@@ -6047,7 +6047,7 @@
         <v>46213.27148148148</v>
       </c>
       <c r="F50" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>33</v>
@@ -6059,7 +6059,7 @@
         <v>33</v>
       </c>
       <c r="J50" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K50" s="0" t="s">
         <v>25</v>
@@ -6079,8 +6079,8 @@
       <c r="P50" s="0">
         <v>1</v>
       </c>
-      <c r="Q50" s="0" t="s">
-        <v>25</v>
+      <c r="Q50" s="0">
+        <v>0</v>
       </c>
       <c r="R50" s="0" t="s">
         <v>25</v>
@@ -6115,7 +6115,7 @@
         <v>46229.780127314814</v>
       </c>
       <c r="F51" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>24</v>
@@ -6183,7 +6183,7 @@
         <v>46200.02773148148</v>
       </c>
       <c r="F52" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>33</v>
@@ -6251,7 +6251,7 @@
         <v>46214.69945601852</v>
       </c>
       <c r="F53" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>28</v>
@@ -6319,7 +6319,7 @@
         <v>46232.26054398148</v>
       </c>
       <c r="F54" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>24</v>
@@ -6387,7 +6387,7 @@
         <v>46218.06186342592</v>
       </c>
       <c r="F55" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>24</v>
@@ -6455,7 +6455,7 @@
         <v>46216.87899305556</v>
       </c>
       <c r="F56" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>33</v>
@@ -6523,7 +6523,7 @@
         <v>46200.57623842593</v>
       </c>
       <c r="F57" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G57" s="0" t="s">
         <v>33</v>
@@ -6591,7 +6591,7 @@
         <v>46213.61833333333</v>
       </c>
       <c r="F58" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G58" s="0" t="s">
         <v>28</v>
@@ -6659,7 +6659,7 @@
         <v>46233.55042824074</v>
       </c>
       <c r="F59" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>28</v>
@@ -6686,7 +6686,7 @@
         <v>25</v>
       </c>
       <c r="O59" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" s="0" t="s">
         <v>25</v>
@@ -6727,7 +6727,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F60" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G60" s="0" t="s">
         <v>28</v>
@@ -6795,7 +6795,7 @@
         <v>46228.81559027778</v>
       </c>
       <c r="F61" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>33</v>
@@ -6863,7 +6863,7 @@
         <v>46229.768229166664</v>
       </c>
       <c r="F62" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>33</v>
@@ -6931,7 +6931,7 @@
         <v>46221.10252314815</v>
       </c>
       <c r="F63" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>24</v>
@@ -6999,7 +6999,7 @@
         <v>46198.764027777775</v>
       </c>
       <c r="F64" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>24</v>
@@ -7017,7 +7017,7 @@
         <v>24</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M64" s="0" t="s">
         <v>25</v>
@@ -7037,8 +7037,8 @@
       <c r="R64" s="0">
         <v>1</v>
       </c>
-      <c r="S64" s="0" t="s">
-        <v>25</v>
+      <c r="S64" s="0">
+        <v>0</v>
       </c>
       <c r="T64" s="0" t="s">
         <v>25</v>
@@ -7067,7 +7067,7 @@
         <v>46219.03289351852</v>
       </c>
       <c r="F65" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G65" s="0" t="s">
         <v>24</v>
@@ -7135,7 +7135,7 @@
         <v>46218.38391203704</v>
       </c>
       <c r="F66" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>24</v>
@@ -7203,7 +7203,7 @@
         <v>46198.18491898148</v>
       </c>
       <c r="F67" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>33</v>
@@ -7271,7 +7271,7 @@
         <v>46229.65642361111</v>
       </c>
       <c r="F68" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>28</v>
@@ -7339,7 +7339,7 @@
         <v>46203.81460648148</v>
       </c>
       <c r="F69" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>28</v>
@@ -7407,7 +7407,7 @@
         <v>46229.57506944444</v>
       </c>
       <c r="F70" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G70" s="0" t="s">
         <v>33</v>
@@ -7475,7 +7475,7 @@
         <v>46213.61833333333</v>
       </c>
       <c r="F71" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G71" s="0" t="s">
         <v>28</v>
@@ -7543,7 +7543,7 @@
         <v>46224.5487037037</v>
       </c>
       <c r="F72" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>33</v>
@@ -7611,7 +7611,7 @@
         <v>46213.61802083333</v>
       </c>
       <c r="F73" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G73" s="0" t="s">
         <v>28</v>
@@ -7679,7 +7679,7 @@
         <v>46201.33733796296</v>
       </c>
       <c r="F74" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>33</v>
@@ -7747,7 +7747,7 @@
         <v>46218.70291666667</v>
       </c>
       <c r="F75" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>33</v>
@@ -7815,7 +7815,7 @@
         <v>46203.71907407408</v>
       </c>
       <c r="F76" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>33</v>
@@ -7883,7 +7883,7 @@
         <v>46216.513865740744</v>
       </c>
       <c r="F77" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>24</v>
@@ -7913,7 +7913,7 @@
         <v>1</v>
       </c>
       <c r="P77" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" s="0" t="s">
         <v>25</v>
@@ -7951,7 +7951,7 @@
         <v>46217.494409722225</v>
       </c>
       <c r="F78" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>24</v>
@@ -7981,7 +7981,7 @@
         <v>1</v>
       </c>
       <c r="P78" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" s="0" t="s">
         <v>25</v>
@@ -8019,7 +8019,7 @@
         <v>46219.741423611114</v>
       </c>
       <c r="F79" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>33</v>
@@ -8087,7 +8087,7 @@
         <v>46195.59105324074</v>
       </c>
       <c r="F80" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G80" s="0" t="s">
         <v>24</v>
@@ -8155,7 +8155,7 @@
         <v>46201.06361111111</v>
       </c>
       <c r="F81" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>33</v>
@@ -8223,7 +8223,7 @@
         <v>46213.7575</v>
       </c>
       <c r="F82" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>33</v>
@@ -8291,7 +8291,7 @@
         <v>46195.68219907407</v>
       </c>
       <c r="F83" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>24</v>
@@ -8359,7 +8359,7 @@
         <v>46216.18634259259</v>
       </c>
       <c r="F84" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G84" s="0" t="s">
         <v>33</v>
@@ -8427,7 +8427,7 @@
         <v>46226.925775462965</v>
       </c>
       <c r="F85" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G85" s="0" t="s">
         <v>33</v>
@@ -8439,7 +8439,7 @@
         <v>33</v>
       </c>
       <c r="J85" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K85" s="0" t="s">
         <v>25</v>
@@ -8459,8 +8459,8 @@
       <c r="P85" s="0">
         <v>0</v>
       </c>
-      <c r="Q85" s="0" t="s">
-        <v>25</v>
+      <c r="Q85" s="0">
+        <v>0</v>
       </c>
       <c r="R85" s="0" t="s">
         <v>25</v>
@@ -8495,7 +8495,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F86" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>24</v>
@@ -8563,7 +8563,7 @@
         <v>46207.51556712963</v>
       </c>
       <c r="F87" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>24</v>
@@ -8631,7 +8631,7 @@
         <v>46220.012395833335</v>
       </c>
       <c r="F88" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G88" s="0" t="s">
         <v>24</v>
@@ -8699,7 +8699,7 @@
         <v>46231.978634259256</v>
       </c>
       <c r="F89" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>24</v>
@@ -8726,7 +8726,7 @@
         <v>25</v>
       </c>
       <c r="O89" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89" s="0" t="s">
         <v>25</v>
@@ -8767,7 +8767,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F90" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>28</v>
@@ -8835,7 +8835,7 @@
         <v>46210.47645833333</v>
       </c>
       <c r="F91" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G91" s="0" t="s">
         <v>33</v>
@@ -8903,7 +8903,7 @@
         <v>46201.306608796294</v>
       </c>
       <c r="F92" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G92" s="0" t="s">
         <v>28</v>
@@ -8971,7 +8971,7 @@
         <v>46229.78009259259</v>
       </c>
       <c r="F93" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G93" s="0" t="s">
         <v>24</v>
@@ -9039,7 +9039,7 @@
         <v>46202.38591435185</v>
       </c>
       <c r="F94" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G94" s="0" t="s">
         <v>33</v>
@@ -9107,7 +9107,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F95" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G95" s="0" t="s">
         <v>24</v>
@@ -9175,7 +9175,7 @@
         <v>46228.01648148148</v>
       </c>
       <c r="F96" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G96" s="0" t="s">
         <v>33</v>
@@ -9243,7 +9243,7 @@
         <v>46215.03915509259</v>
       </c>
       <c r="F97" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G97" s="0" t="s">
         <v>28</v>
@@ -9311,7 +9311,7 @@
         <v>46229.78011574074</v>
       </c>
       <c r="F98" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G98" s="0" t="s">
         <v>24</v>
@@ -9341,7 +9341,7 @@
         <v>1</v>
       </c>
       <c r="P98" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" s="0" t="s">
         <v>25</v>
@@ -9379,7 +9379,7 @@
         <v>46217.397997685184</v>
       </c>
       <c r="F99" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>24</v>
@@ -9447,7 +9447,7 @@
         <v>46216.51425925926</v>
       </c>
       <c r="F100" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>24</v>
@@ -9515,7 +9515,7 @@
         <v>46222.348495370374</v>
       </c>
       <c r="F101" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G101" s="0" t="s">
         <v>28</v>
@@ -9530,7 +9530,7 @@
         <v>28</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L101" s="0" t="s">
         <v>25</v>
@@ -9550,8 +9550,8 @@
       <c r="Q101" s="0">
         <v>1</v>
       </c>
-      <c r="R101" s="0" t="s">
-        <v>25</v>
+      <c r="R101" s="0">
+        <v>0</v>
       </c>
       <c r="S101" s="0" t="s">
         <v>25</v>
@@ -9583,7 +9583,7 @@
         <v>46217.49438657407</v>
       </c>
       <c r="F102" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G102" s="0" t="s">
         <v>24</v>
@@ -9613,7 +9613,7 @@
         <v>1</v>
       </c>
       <c r="P102" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" s="0" t="s">
         <v>25</v>
@@ -9651,7 +9651,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F103" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>24</v>
@@ -9669,7 +9669,7 @@
         <v>24</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M103" s="0" t="s">
         <v>25</v>
@@ -9689,8 +9689,8 @@
       <c r="R103" s="0">
         <v>1</v>
       </c>
-      <c r="S103" s="0" t="s">
-        <v>25</v>
+      <c r="S103" s="0">
+        <v>0</v>
       </c>
       <c r="T103" s="0" t="s">
         <v>25</v>
@@ -9719,7 +9719,7 @@
         <v>46205.25707175926</v>
       </c>
       <c r="F104" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G104" s="0" t="s">
         <v>33</v>
@@ -9787,7 +9787,7 @@
         <v>46219.01215277778</v>
       </c>
       <c r="F105" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>24</v>
@@ -9855,7 +9855,7 @@
         <v>46203.77983796296</v>
       </c>
       <c r="F106" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G106" s="0" t="s">
         <v>28</v>
@@ -9923,7 +9923,7 @@
         <v>46221.07472222222</v>
       </c>
       <c r="F107" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>24</v>
@@ -9991,7 +9991,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F108" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G108" s="0" t="s">
         <v>24</v>
@@ -10059,7 +10059,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F109" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G109" s="0" t="s">
         <v>28</v>
@@ -10127,7 +10127,7 @@
         <v>46234.34340277778</v>
       </c>
       <c r="F110" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G110" s="0" t="s">
         <v>33</v>
@@ -10195,7 +10195,7 @@
         <v>46207.957766203705</v>
       </c>
       <c r="F111" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G111" s="0" t="s">
         <v>28</v>
@@ -10263,7 +10263,7 @@
         <v>46234.280185185184</v>
       </c>
       <c r="F112" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>33</v>
@@ -10331,7 +10331,7 @@
         <v>46229.34652777778</v>
       </c>
       <c r="F113" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G113" s="0" t="s">
         <v>33</v>
@@ -10361,7 +10361,7 @@
         <v>1</v>
       </c>
       <c r="P113" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="0" t="s">
         <v>25</v>
@@ -10399,7 +10399,7 @@
         <v>46204.23569444445</v>
       </c>
       <c r="F114" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G114" s="0" t="s">
         <v>33</v>
@@ -10438,7 +10438,7 @@
         <v>1</v>
       </c>
       <c r="S114" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T114" s="0" t="s">
         <v>25</v>
@@ -10467,7 +10467,7 @@
         <v>46216.51424768518</v>
       </c>
       <c r="F115" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>24</v>
@@ -10497,7 +10497,7 @@
         <v>1</v>
       </c>
       <c r="P115" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="0" t="s">
         <v>25</v>
@@ -10535,7 +10535,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F116" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>24</v>
@@ -10603,7 +10603,7 @@
         <v>46211.850625</v>
       </c>
       <c r="F117" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G117" s="0" t="s">
         <v>33</v>
@@ -10671,7 +10671,7 @@
         <v>46206.293020833335</v>
       </c>
       <c r="F118" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G118" s="0" t="s">
         <v>28</v>
@@ -10739,7 +10739,7 @@
         <v>46225.07</v>
       </c>
       <c r="F119" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>33</v>
@@ -10807,7 +10807,7 @@
         <v>46214.75530092593</v>
       </c>
       <c r="F120" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G120" s="0" t="s">
         <v>28</v>
@@ -10875,7 +10875,7 @@
         <v>46221.18425925926</v>
       </c>
       <c r="F121" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>24</v>
@@ -10943,7 +10943,7 @@
         <v>46221.24065972222</v>
       </c>
       <c r="F122" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>24</v>
@@ -11011,7 +11011,7 @@
         <v>46198.763715277775</v>
       </c>
       <c r="F123" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>24</v>
@@ -11029,7 +11029,7 @@
         <v>24</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M123" s="0" t="s">
         <v>25</v>
@@ -11049,8 +11049,8 @@
       <c r="R123" s="0">
         <v>1</v>
       </c>
-      <c r="S123" s="0" t="s">
-        <v>25</v>
+      <c r="S123" s="0">
+        <v>0</v>
       </c>
       <c r="T123" s="0" t="s">
         <v>25</v>
@@ -11079,7 +11079,7 @@
         <v>46220.03362268519</v>
       </c>
       <c r="F124" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>24</v>
@@ -11147,7 +11147,7 @@
         <v>46231.26783564815</v>
       </c>
       <c r="F125" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>33</v>
@@ -11215,7 +11215,7 @@
         <v>46221.123761574076</v>
       </c>
       <c r="F126" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G126" s="0" t="s">
         <v>24</v>
@@ -11283,7 +11283,7 @@
         <v>46205.502962962964</v>
       </c>
       <c r="F127" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G127" s="0" t="s">
         <v>33</v>
@@ -11301,7 +11301,7 @@
         <v>33</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M127" s="0" t="s">
         <v>25</v>
@@ -11321,8 +11321,8 @@
       <c r="R127" s="0">
         <v>0</v>
       </c>
-      <c r="S127" s="0" t="s">
-        <v>25</v>
+      <c r="S127" s="0">
+        <v>0</v>
       </c>
       <c r="T127" s="0" t="s">
         <v>25</v>
@@ -11351,7 +11351,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F128" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>24</v>
@@ -11419,7 +11419,7 @@
         <v>46214.35975694445</v>
       </c>
       <c r="F129" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>33</v>
@@ -11487,7 +11487,7 @@
         <v>46213.618055555555</v>
       </c>
       <c r="F130" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>24</v>
@@ -11555,7 +11555,7 @@
         <v>46229.78009259259</v>
       </c>
       <c r="F131" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G131" s="0" t="s">
         <v>24</v>
@@ -11623,7 +11623,7 @@
         <v>46226.39813657408</v>
       </c>
       <c r="F132" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>24</v>
@@ -11691,7 +11691,7 @@
         <v>46225.69733796296</v>
       </c>
       <c r="F133" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>33</v>
@@ -11759,7 +11759,7 @@
         <v>46200.67046296296</v>
       </c>
       <c r="F134" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>24</v>
@@ -11827,7 +11827,7 @@
         <v>46215.29809027778</v>
       </c>
       <c r="F135" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>33</v>
@@ -11895,7 +11895,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F136" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G136" s="0" t="s">
         <v>24</v>
@@ -11963,7 +11963,7 @@
         <v>46222.609398148146</v>
       </c>
       <c r="F137" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>28</v>
@@ -12031,7 +12031,7 @@
         <v>46222.94975694444</v>
       </c>
       <c r="F138" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G138" s="0" t="s">
         <v>33</v>
@@ -12099,7 +12099,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F139" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>28</v>
@@ -12167,7 +12167,7 @@
         <v>46220.005208333336</v>
       </c>
       <c r="F140" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>24</v>
@@ -12235,7 +12235,7 @@
         <v>46222.341782407406</v>
       </c>
       <c r="F141" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G141" s="0" t="s">
         <v>33</v>
@@ -12303,7 +12303,7 @@
         <v>46232.39592592593</v>
       </c>
       <c r="F142" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>33</v>
@@ -12312,7 +12312,7 @@
         <v>33</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J142" s="0" t="s">
         <v>25</v>
@@ -12332,8 +12332,8 @@
       <c r="O142" s="0">
         <v>1</v>
       </c>
-      <c r="P142" s="0" t="s">
-        <v>25</v>
+      <c r="P142" s="0">
+        <v>0</v>
       </c>
       <c r="Q142" s="0" t="s">
         <v>25</v>
@@ -12371,7 +12371,7 @@
         <v>46216.51429398148</v>
       </c>
       <c r="F143" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G143" s="0" t="s">
         <v>24</v>
@@ -12401,7 +12401,7 @@
         <v>1</v>
       </c>
       <c r="P143" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q143" s="0" t="s">
         <v>25</v>
@@ -12439,7 +12439,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F144" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>24</v>
@@ -12507,7 +12507,7 @@
         <v>46217.729409722226</v>
       </c>
       <c r="F145" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>24</v>
@@ -12575,7 +12575,7 @@
         <v>46207.76193287037</v>
       </c>
       <c r="F146" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G146" s="0" t="s">
         <v>24</v>
@@ -12643,7 +12643,7 @@
         <v>46199.574282407404</v>
       </c>
       <c r="F147" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>33</v>
@@ -12711,7 +12711,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F148" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G148" s="0" t="s">
         <v>28</v>
@@ -12779,7 +12779,7 @@
         <v>46216.460694444446</v>
       </c>
       <c r="F149" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G149" s="0" t="s">
         <v>33</v>
@@ -12847,7 +12847,7 @@
         <v>46219.03226851852</v>
       </c>
       <c r="F150" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G150" s="0" t="s">
         <v>24</v>
@@ -12915,7 +12915,7 @@
         <v>46198.758518518516</v>
       </c>
       <c r="F151" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G151" s="0" t="s">
         <v>24</v>
@@ -12933,7 +12933,7 @@
         <v>24</v>
       </c>
       <c r="L151" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M151" s="0" t="s">
         <v>25</v>
@@ -12953,8 +12953,8 @@
       <c r="R151" s="0">
         <v>1</v>
       </c>
-      <c r="S151" s="0" t="s">
-        <v>25</v>
+      <c r="S151" s="0">
+        <v>0</v>
       </c>
       <c r="T151" s="0" t="s">
         <v>25</v>
@@ -12983,7 +12983,7 @@
         <v>46199.20893518518</v>
       </c>
       <c r="F152" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G152" s="0" t="s">
         <v>33</v>
@@ -13051,7 +13051,7 @@
         <v>46198.76384259259</v>
       </c>
       <c r="F153" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>24</v>
@@ -13069,7 +13069,7 @@
         <v>24</v>
       </c>
       <c r="L153" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M153" s="0" t="s">
         <v>25</v>
@@ -13089,8 +13089,8 @@
       <c r="R153" s="0">
         <v>1</v>
       </c>
-      <c r="S153" s="0" t="s">
-        <v>25</v>
+      <c r="S153" s="0">
+        <v>0</v>
       </c>
       <c r="T153" s="0" t="s">
         <v>25</v>
@@ -13119,7 +13119,7 @@
         <v>46207.98546296296</v>
       </c>
       <c r="F154" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G154" s="0" t="s">
         <v>33</v>
@@ -13187,7 +13187,7 @@
         <v>46198.758414351854</v>
       </c>
       <c r="F155" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>24</v>
@@ -13205,7 +13205,7 @@
         <v>24</v>
       </c>
       <c r="L155" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M155" s="0" t="s">
         <v>25</v>
@@ -13225,8 +13225,8 @@
       <c r="R155" s="0">
         <v>1</v>
       </c>
-      <c r="S155" s="0" t="s">
-        <v>25</v>
+      <c r="S155" s="0">
+        <v>0</v>
       </c>
       <c r="T155" s="0" t="s">
         <v>25</v>
@@ -13255,7 +13255,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F156" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>28</v>
@@ -13323,7 +13323,7 @@
         <v>46210.47645833333</v>
       </c>
       <c r="F157" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G157" s="0" t="s">
         <v>33</v>
@@ -13335,7 +13335,7 @@
         <v>33</v>
       </c>
       <c r="J157" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K157" s="0" t="s">
         <v>25</v>
@@ -13355,8 +13355,8 @@
       <c r="P157" s="0">
         <v>1</v>
       </c>
-      <c r="Q157" s="0" t="s">
-        <v>25</v>
+      <c r="Q157" s="0">
+        <v>0</v>
       </c>
       <c r="R157" s="0" t="s">
         <v>25</v>
@@ -13391,7 +13391,7 @@
         <v>46217.494409722225</v>
       </c>
       <c r="F158" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G158" s="0" t="s">
         <v>24</v>
@@ -13421,7 +13421,7 @@
         <v>1</v>
       </c>
       <c r="P158" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q158" s="0" t="s">
         <v>25</v>
@@ -13459,7 +13459,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F159" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G159" s="0" t="s">
         <v>24</v>
@@ -13527,7 +13527,7 @@
         <v>46207.95777777778</v>
       </c>
       <c r="F160" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G160" s="0" t="s">
         <v>24</v>
@@ -13595,7 +13595,7 @@
         <v>46216.460694444446</v>
       </c>
       <c r="F161" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>24</v>
@@ -13625,7 +13625,7 @@
         <v>1</v>
       </c>
       <c r="P161" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q161" s="0" t="s">
         <v>25</v>
@@ -13663,7 +13663,7 @@
         <v>46217.77034722222</v>
       </c>
       <c r="F162" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G162" s="0" t="s">
         <v>24</v>
@@ -13731,7 +13731,7 @@
         <v>46221.85356481482</v>
       </c>
       <c r="F163" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>24</v>
@@ -13799,7 +13799,7 @@
         <v>46213.393483796295</v>
       </c>
       <c r="F164" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>24</v>
@@ -13829,7 +13829,7 @@
         <v>1</v>
       </c>
       <c r="P164" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q164" s="0" t="s">
         <v>25</v>
@@ -13867,7 +13867,7 @@
         <v>46213.61802083333</v>
       </c>
       <c r="F165" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G165" s="0" t="s">
         <v>28</v>
@@ -13935,7 +13935,7 @@
         <v>46213.479849537034</v>
       </c>
       <c r="F166" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G166" s="0" t="s">
         <v>33</v>
@@ -13971,7 +13971,7 @@
         <v>0</v>
       </c>
       <c r="R166" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S166" s="0" t="s">
         <v>25</v>
@@ -14003,7 +14003,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F167" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G167" s="0" t="s">
         <v>24</v>
@@ -14071,7 +14071,7 @@
         <v>46213.89649305555</v>
       </c>
       <c r="F168" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>33</v>
@@ -14107,7 +14107,7 @@
         <v>0</v>
       </c>
       <c r="R168" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S168" s="0" t="s">
         <v>25</v>
@@ -14139,7 +14139,7 @@
         <v>46224.748032407406</v>
       </c>
       <c r="F169" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G169" s="0" t="s">
         <v>33</v>
@@ -14207,7 +14207,7 @@
         <v>46194.2578587963</v>
       </c>
       <c r="F170" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>33</v>
@@ -14275,7 +14275,7 @@
         <v>46231.9369212963</v>
       </c>
       <c r="F171" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>24</v>
@@ -14302,7 +14302,7 @@
         <v>25</v>
       </c>
       <c r="O171" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P171" s="0" t="s">
         <v>25</v>
@@ -14343,7 +14343,7 @@
         <v>46197.83574074074</v>
       </c>
       <c r="F172" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G172" s="0" t="s">
         <v>24</v>
@@ -14411,7 +14411,7 @@
         <v>46203.91997685185</v>
       </c>
       <c r="F173" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>24</v>
@@ -14479,7 +14479,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F174" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G174" s="0" t="s">
         <v>28</v>
@@ -14547,7 +14547,7 @@
         <v>46226.960706018515</v>
       </c>
       <c r="F175" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G175" s="0" t="s">
         <v>33</v>
@@ -14559,7 +14559,7 @@
         <v>33</v>
       </c>
       <c r="J175" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K175" s="0" t="s">
         <v>25</v>
@@ -14579,8 +14579,8 @@
       <c r="P175" s="0">
         <v>1</v>
       </c>
-      <c r="Q175" s="0" t="s">
-        <v>25</v>
+      <c r="Q175" s="0">
+        <v>1</v>
       </c>
       <c r="R175" s="0" t="s">
         <v>25</v>
@@ -14615,7 +14615,7 @@
         <v>46230.76190972222</v>
       </c>
       <c r="F176" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G176" s="0" t="s">
         <v>24</v>
@@ -14683,7 +14683,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F177" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>28</v>
@@ -14751,7 +14751,7 @@
         <v>46227.39533564815</v>
       </c>
       <c r="F178" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G178" s="0" t="s">
         <v>33</v>
@@ -14819,7 +14819,7 @@
         <v>46224.92780092593</v>
       </c>
       <c r="F179" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G179" s="0" t="s">
         <v>33</v>
@@ -14887,7 +14887,7 @@
         <v>46221.23185185185</v>
       </c>
       <c r="F180" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G180" s="0" t="s">
         <v>24</v>
@@ -14955,7 +14955,7 @@
         <v>46229.59564814815</v>
       </c>
       <c r="F181" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G181" s="0" t="s">
         <v>33</v>
@@ -14985,7 +14985,7 @@
         <v>1</v>
       </c>
       <c r="P181" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q181" s="0" t="s">
         <v>25</v>
@@ -15023,7 +15023,7 @@
         <v>46220.10337962963</v>
       </c>
       <c r="F182" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G182" s="0" t="s">
         <v>24</v>
@@ -15091,7 +15091,7 @@
         <v>46218.0619212963</v>
       </c>
       <c r="F183" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G183" s="0" t="s">
         <v>24</v>
@@ -15159,7 +15159,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F184" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G184" s="0" t="s">
         <v>24</v>
@@ -15227,7 +15227,7 @@
         <v>46214.741215277776</v>
       </c>
       <c r="F185" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G185" s="0" t="s">
         <v>33</v>
@@ -15295,7 +15295,7 @@
         <v>46204.816157407404</v>
       </c>
       <c r="F186" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G186" s="0" t="s">
         <v>24</v>
@@ -15363,7 +15363,7 @@
         <v>46210.94122685185</v>
       </c>
       <c r="F187" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G187" s="0" t="s">
         <v>33</v>
@@ -15431,7 +15431,7 @@
         <v>46221.21726851852</v>
       </c>
       <c r="F188" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G188" s="0" t="s">
         <v>24</v>
@@ -15499,7 +15499,7 @@
         <v>46219.0249537037</v>
       </c>
       <c r="F189" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G189" s="0" t="s">
         <v>24</v>
@@ -15567,7 +15567,7 @@
         <v>46217.85380787037</v>
       </c>
       <c r="F190" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G190" s="0" t="s">
         <v>24</v>
@@ -15594,7 +15594,7 @@
         <v>25</v>
       </c>
       <c r="O190" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P190" s="0" t="s">
         <v>25</v>
@@ -15635,7 +15635,7 @@
         <v>46232.21041666667</v>
       </c>
       <c r="F191" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G191" s="0" t="s">
         <v>24</v>
@@ -15703,7 +15703,7 @@
         <v>46211.91608796296</v>
       </c>
       <c r="F192" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G192" s="0" t="s">
         <v>33</v>
@@ -15771,7 +15771,7 @@
         <v>46213.618310185186</v>
       </c>
       <c r="F193" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G193" s="0" t="s">
         <v>28</v>
@@ -15839,7 +15839,7 @@
         <v>46211.9408912037</v>
       </c>
       <c r="F194" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G194" s="0" t="s">
         <v>33</v>
@@ -15907,7 +15907,7 @@
         <v>46221.22954861111</v>
       </c>
       <c r="F195" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G195" s="0" t="s">
         <v>24</v>
@@ -15975,7 +15975,7 @@
         <v>46230.69074074074</v>
       </c>
       <c r="F196" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G196" s="0" t="s">
         <v>28</v>
@@ -16002,7 +16002,7 @@
         <v>25</v>
       </c>
       <c r="O196" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P196" s="0" t="s">
         <v>25</v>
@@ -16043,7 +16043,7 @@
         <v>46218.06193287037</v>
       </c>
       <c r="F197" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G197" s="0" t="s">
         <v>24</v>
@@ -16111,7 +16111,7 @@
         <v>46198.763449074075</v>
       </c>
       <c r="F198" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G198" s="0" t="s">
         <v>24</v>
@@ -16129,7 +16129,7 @@
         <v>24</v>
       </c>
       <c r="L198" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M198" s="0" t="s">
         <v>25</v>
@@ -16149,8 +16149,8 @@
       <c r="R198" s="0">
         <v>1</v>
       </c>
-      <c r="S198" s="0" t="s">
-        <v>25</v>
+      <c r="S198" s="0">
+        <v>0</v>
       </c>
       <c r="T198" s="0" t="s">
         <v>25</v>
@@ -16179,7 +16179,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F199" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>28</v>
@@ -16247,7 +16247,7 @@
         <v>46233.88229166667</v>
       </c>
       <c r="F200" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G200" s="0" t="s">
         <v>28</v>
@@ -16274,7 +16274,7 @@
         <v>25</v>
       </c>
       <c r="O200" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P200" s="0" t="s">
         <v>25</v>
@@ -16315,7 +16315,7 @@
         <v>46227.32268518519</v>
       </c>
       <c r="F201" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>33</v>
@@ -16327,7 +16327,7 @@
         <v>33</v>
       </c>
       <c r="J201" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K201" s="0" t="s">
         <v>25</v>
@@ -16347,8 +16347,8 @@
       <c r="P201" s="0">
         <v>1</v>
       </c>
-      <c r="Q201" s="0" t="s">
-        <v>25</v>
+      <c r="Q201" s="0">
+        <v>0</v>
       </c>
       <c r="R201" s="0" t="s">
         <v>25</v>
@@ -16383,7 +16383,7 @@
         <v>46222.727164351854</v>
       </c>
       <c r="F202" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G202" s="0" t="s">
         <v>28</v>
@@ -16451,7 +16451,7 @@
         <v>46198.758125</v>
       </c>
       <c r="F203" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G203" s="0" t="s">
         <v>24</v>
@@ -16469,7 +16469,7 @@
         <v>24</v>
       </c>
       <c r="L203" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M203" s="0" t="s">
         <v>25</v>
@@ -16489,8 +16489,8 @@
       <c r="R203" s="0">
         <v>1</v>
       </c>
-      <c r="S203" s="0" t="s">
-        <v>25</v>
+      <c r="S203" s="0">
+        <v>0</v>
       </c>
       <c r="T203" s="0" t="s">
         <v>25</v>
@@ -16519,7 +16519,7 @@
         <v>46220.11025462963</v>
       </c>
       <c r="F204" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G204" s="0" t="s">
         <v>24</v>
@@ -16587,7 +16587,7 @@
         <v>46230.41988425926</v>
       </c>
       <c r="F205" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G205" s="0" t="s">
         <v>28</v>
@@ -16655,7 +16655,7 @@
         <v>46225.792858796296</v>
       </c>
       <c r="F206" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G206" s="0" t="s">
         <v>33</v>
@@ -16723,7 +16723,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F207" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G207" s="0" t="s">
         <v>24</v>
@@ -16791,7 +16791,7 @@
         <v>46201.54498842593</v>
       </c>
       <c r="F208" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G208" s="0" t="s">
         <v>33</v>
@@ -16859,7 +16859,7 @@
         <v>46235.061747685184</v>
       </c>
       <c r="F209" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G209" s="0" t="s">
         <v>33</v>
@@ -16927,7 +16927,7 @@
         <v>46217.85381944444</v>
       </c>
       <c r="F210" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G210" s="0" t="s">
         <v>24</v>
@@ -16995,7 +16995,7 @@
         <v>46198.76478009259</v>
       </c>
       <c r="F211" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G211" s="0" t="s">
         <v>24</v>
@@ -17013,7 +17013,7 @@
         <v>24</v>
       </c>
       <c r="L211" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M211" s="0" t="s">
         <v>25</v>
@@ -17033,8 +17033,8 @@
       <c r="R211" s="0">
         <v>1</v>
       </c>
-      <c r="S211" s="0" t="s">
-        <v>25</v>
+      <c r="S211" s="0">
+        <v>0</v>
       </c>
       <c r="T211" s="0" t="s">
         <v>25</v>
@@ -17063,7 +17063,7 @@
         <v>46205.76315972222</v>
       </c>
       <c r="F212" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>33</v>
@@ -17131,7 +17131,7 @@
         <v>46221.0327662037</v>
       </c>
       <c r="F213" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G213" s="0" t="s">
         <v>24</v>
@@ -17199,7 +17199,7 @@
         <v>46204.83986111111</v>
       </c>
       <c r="F214" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G214" s="0" t="s">
         <v>33</v>
@@ -17267,7 +17267,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F215" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G215" s="0" t="s">
         <v>28</v>
@@ -17335,7 +17335,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F216" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>24</v>
@@ -17403,7 +17403,7 @@
         <v>46203.69975694444</v>
       </c>
       <c r="F217" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G217" s="0" t="s">
         <v>28</v>
@@ -17442,7 +17442,7 @@
         <v>1</v>
       </c>
       <c r="S217" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T217" s="0" t="s">
         <v>25</v>
@@ -17471,7 +17471,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F218" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G218" s="0" t="s">
         <v>24</v>
@@ -17539,7 +17539,7 @@
         <v>46208.10663194444</v>
       </c>
       <c r="F219" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G219" s="0" t="s">
         <v>33</v>
@@ -17607,7 +17607,7 @@
         <v>46200.854166666664</v>
       </c>
       <c r="F220" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G220" s="0" t="s">
         <v>24</v>
@@ -17675,7 +17675,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F221" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G221" s="0" t="s">
         <v>24</v>
@@ -17743,7 +17743,7 @@
         <v>46221.087476851855</v>
       </c>
       <c r="F222" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G222" s="0" t="s">
         <v>24</v>
@@ -17811,7 +17811,7 @@
         <v>46212.5203125</v>
       </c>
       <c r="F223" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G223" s="0" t="s">
         <v>24</v>
@@ -17879,7 +17879,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F224" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G224" s="0" t="s">
         <v>24</v>
@@ -17947,7 +17947,7 @@
         <v>46218.366956018515</v>
       </c>
       <c r="F225" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G225" s="0" t="s">
         <v>24</v>
@@ -18015,7 +18015,7 @@
         <v>46223.899201388886</v>
       </c>
       <c r="F226" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G226" s="0" t="s">
         <v>24</v>
@@ -18083,7 +18083,7 @@
         <v>46204.145219907405</v>
       </c>
       <c r="F227" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G227" s="0" t="s">
         <v>24</v>
@@ -18101,7 +18101,7 @@
         <v>24</v>
       </c>
       <c r="L227" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M227" s="0" t="s">
         <v>25</v>
@@ -18121,8 +18121,8 @@
       <c r="R227" s="0">
         <v>1</v>
       </c>
-      <c r="S227" s="0" t="s">
-        <v>25</v>
+      <c r="S227" s="0">
+        <v>0</v>
       </c>
       <c r="T227" s="0" t="s">
         <v>25</v>
@@ -18151,7 +18151,7 @@
         <v>46191.31182870371</v>
       </c>
       <c r="F228" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G228" s="0" t="s">
         <v>24</v>
@@ -18219,7 +18219,7 @@
         <v>46199.29518518518</v>
       </c>
       <c r="F229" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G229" s="0" t="s">
         <v>33</v>
@@ -18287,7 +18287,7 @@
         <v>46184.345671296294</v>
       </c>
       <c r="F230" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G230" s="0" t="s">
         <v>24</v>
@@ -18355,7 +18355,7 @@
         <v>46218.3812962963</v>
       </c>
       <c r="F231" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G231" s="0" t="s">
         <v>28</v>
@@ -18423,7 +18423,7 @@
         <v>46215.31277777778</v>
       </c>
       <c r="F232" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G232" s="0" t="s">
         <v>33</v>
@@ -18491,7 +18491,7 @@
         <v>46218.359664351854</v>
       </c>
       <c r="F233" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G233" s="0" t="s">
         <v>24</v>
@@ -18559,7 +18559,7 @@
         <v>46219.47236111111</v>
       </c>
       <c r="F234" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G234" s="0" t="s">
         <v>33</v>
@@ -18595,7 +18595,7 @@
         <v>0</v>
       </c>
       <c r="R234" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S234" s="0" t="s">
         <v>25</v>
@@ -18627,7 +18627,7 @@
         <v>46227.55447916667</v>
       </c>
       <c r="F235" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G235" s="0" t="s">
         <v>33</v>
@@ -18695,7 +18695,7 @@
         <v>46198.758576388886</v>
       </c>
       <c r="F236" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G236" s="0" t="s">
         <v>24</v>
@@ -18713,7 +18713,7 @@
         <v>24</v>
       </c>
       <c r="L236" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M236" s="0" t="s">
         <v>25</v>
@@ -18733,8 +18733,8 @@
       <c r="R236" s="0">
         <v>1</v>
       </c>
-      <c r="S236" s="0" t="s">
-        <v>25</v>
+      <c r="S236" s="0">
+        <v>0</v>
       </c>
       <c r="T236" s="0" t="s">
         <v>25</v>
@@ -18763,7 +18763,7 @@
         <v>46211.747719907406</v>
       </c>
       <c r="F237" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G237" s="0" t="s">
         <v>24</v>
@@ -18831,7 +18831,7 @@
         <v>46196.6612962963</v>
       </c>
       <c r="F238" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G238" s="0" t="s">
         <v>28</v>
@@ -18899,7 +18899,7 @@
         <v>46220.07247685185</v>
       </c>
       <c r="F239" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G239" s="0" t="s">
         <v>24</v>
@@ -18967,7 +18967,7 @@
         <v>46235.05255787037</v>
       </c>
       <c r="F240" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G240" s="0" t="s">
         <v>33</v>
@@ -19035,7 +19035,7 @@
         <v>46220.07025462963</v>
       </c>
       <c r="F241" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G241" s="0" t="s">
         <v>24</v>
@@ -19103,7 +19103,7 @@
         <v>46203.386967592596</v>
       </c>
       <c r="F242" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G242" s="0" t="s">
         <v>24</v>
@@ -19171,7 +19171,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F243" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G243" s="0" t="s">
         <v>33</v>
@@ -19239,7 +19239,7 @@
         <v>46225.85364583333</v>
       </c>
       <c r="F244" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G244" s="0" t="s">
         <v>33</v>
@@ -19251,7 +19251,7 @@
         <v>33</v>
       </c>
       <c r="J244" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K244" s="0" t="s">
         <v>25</v>
@@ -19271,8 +19271,8 @@
       <c r="P244" s="0">
         <v>1</v>
       </c>
-      <c r="Q244" s="0" t="s">
-        <v>25</v>
+      <c r="Q244" s="0">
+        <v>0</v>
       </c>
       <c r="R244" s="0" t="s">
         <v>25</v>
@@ -19307,7 +19307,7 @@
         <v>46234.235138888886</v>
       </c>
       <c r="F245" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G245" s="0" t="s">
         <v>33</v>
@@ -19375,7 +19375,7 @@
         <v>46229.984502314815</v>
       </c>
       <c r="F246" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G246" s="0" t="s">
         <v>33</v>
@@ -19443,7 +19443,7 @@
         <v>46202.30238425926</v>
       </c>
       <c r="F247" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G247" s="0" t="s">
         <v>33</v>
@@ -19511,7 +19511,7 @@
         <v>46210.49642361111</v>
       </c>
       <c r="F248" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G248" s="0" t="s">
         <v>28</v>
@@ -19579,7 +19579,7 @@
         <v>46227.94118055556</v>
       </c>
       <c r="F249" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G249" s="0" t="s">
         <v>33</v>
@@ -19647,7 +19647,7 @@
         <v>46220.11326388889</v>
       </c>
       <c r="F250" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G250" s="0" t="s">
         <v>24</v>
@@ -19715,7 +19715,7 @@
         <v>46221.241585648146</v>
       </c>
       <c r="F251" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G251" s="0" t="s">
         <v>24</v>
@@ -19783,7 +19783,7 @@
         <v>46221.104409722226</v>
       </c>
       <c r="F252" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G252" s="0" t="s">
         <v>24</v>
@@ -19851,7 +19851,7 @@
         <v>46234.76284722222</v>
       </c>
       <c r="F253" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>28</v>
@@ -19919,7 +19919,7 @@
         <v>46228.72872685185</v>
       </c>
       <c r="F254" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G254" s="0" t="s">
         <v>33</v>
@@ -19987,7 +19987,7 @@
         <v>46220.11571759259</v>
       </c>
       <c r="F255" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G255" s="0" t="s">
         <v>24</v>
@@ -20055,7 +20055,7 @@
         <v>46213.61802083333</v>
       </c>
       <c r="F256" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G256" s="0" t="s">
         <v>28</v>
@@ -20123,7 +20123,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F257" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G257" s="0" t="s">
         <v>24</v>
@@ -20191,7 +20191,7 @@
         <v>46224.83597222222</v>
       </c>
       <c r="F258" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>28</v>
@@ -20259,7 +20259,7 @@
         <v>46217.79634259259</v>
       </c>
       <c r="F259" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>28</v>
@@ -20327,7 +20327,7 @@
         <v>46219.02664351852</v>
       </c>
       <c r="F260" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G260" s="0" t="s">
         <v>24</v>
@@ -20395,7 +20395,7 @@
         <v>46217.76349537037</v>
       </c>
       <c r="F261" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G261" s="0" t="s">
         <v>24</v>
@@ -20463,7 +20463,7 @@
         <v>46198.007743055554</v>
       </c>
       <c r="F262" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>24</v>
@@ -20531,7 +20531,7 @@
         <v>46221.04346064815</v>
       </c>
       <c r="F263" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G263" s="0" t="s">
         <v>24</v>
@@ -20599,7 +20599,7 @@
         <v>46213.615798611114</v>
       </c>
       <c r="F264" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>28</v>
@@ -20667,7 +20667,7 @@
         <v>46221.49884259259</v>
       </c>
       <c r="F265" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G265" s="0" t="s">
         <v>33</v>
@@ -20682,7 +20682,7 @@
         <v>33</v>
       </c>
       <c r="K265" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L265" s="0" t="s">
         <v>25</v>
@@ -20702,8 +20702,8 @@
       <c r="Q265" s="0">
         <v>0</v>
       </c>
-      <c r="R265" s="0" t="s">
-        <v>25</v>
+      <c r="R265" s="0">
+        <v>0</v>
       </c>
       <c r="S265" s="0" t="s">
         <v>25</v>
@@ -20735,7 +20735,7 @@
         <v>46204.82892361111</v>
       </c>
       <c r="F266" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G266" s="0" t="s">
         <v>24</v>
@@ -20753,7 +20753,7 @@
         <v>24</v>
       </c>
       <c r="L266" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M266" s="0" t="s">
         <v>25</v>
@@ -20773,8 +20773,8 @@
       <c r="R266" s="0">
         <v>1</v>
       </c>
-      <c r="S266" s="0" t="s">
-        <v>25</v>
+      <c r="S266" s="0">
+        <v>0</v>
       </c>
       <c r="T266" s="0" t="s">
         <v>25</v>
@@ -20803,7 +20803,7 @@
         <v>46207.95777777778</v>
       </c>
       <c r="F267" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G267" s="0" t="s">
         <v>24</v>
@@ -20815,7 +20815,7 @@
         <v>24</v>
       </c>
       <c r="J267" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K267" s="0" t="s">
         <v>25</v>
@@ -20835,8 +20835,8 @@
       <c r="P267" s="0">
         <v>1</v>
       </c>
-      <c r="Q267" s="0" t="s">
-        <v>25</v>
+      <c r="Q267" s="0">
+        <v>0</v>
       </c>
       <c r="R267" s="0" t="s">
         <v>25</v>
@@ -20871,7 +20871,7 @@
         <v>46221.16929398148</v>
       </c>
       <c r="F268" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G268" s="0" t="s">
         <v>24</v>
@@ -20939,7 +20939,7 @@
         <v>46213.615798611114</v>
       </c>
       <c r="F269" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G269" s="0" t="s">
         <v>28</v>
@@ -21007,7 +21007,7 @@
         <v>46220.02643518519</v>
       </c>
       <c r="F270" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G270" s="0" t="s">
         <v>24</v>
@@ -21075,7 +21075,7 @@
         <v>46233.79090277778</v>
       </c>
       <c r="F271" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G271" s="0" t="s">
         <v>24</v>
@@ -21143,7 +21143,7 @@
         <v>46222.723344907405</v>
       </c>
       <c r="F272" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G272" s="0" t="s">
         <v>28</v>
@@ -21176,7 +21176,7 @@
         <v>1</v>
       </c>
       <c r="Q272" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R272" s="0" t="s">
         <v>25</v>
@@ -21211,7 +21211,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F273" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G273" s="0" t="s">
         <v>28</v>
@@ -21279,7 +21279,7 @@
         <v>46206.49621527778</v>
       </c>
       <c r="F274" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G274" s="0" t="s">
         <v>33</v>
@@ -21297,7 +21297,7 @@
         <v>33</v>
       </c>
       <c r="L274" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M274" s="0" t="s">
         <v>25</v>
@@ -21317,8 +21317,8 @@
       <c r="R274" s="0">
         <v>1</v>
       </c>
-      <c r="S274" s="0" t="s">
-        <v>25</v>
+      <c r="S274" s="0">
+        <v>0</v>
       </c>
       <c r="T274" s="0" t="s">
         <v>25</v>
@@ -21347,7 +21347,7 @@
         <v>46194.10880787037</v>
       </c>
       <c r="F275" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G275" s="0" t="s">
         <v>24</v>
@@ -21415,7 +21415,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F276" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G276" s="0" t="s">
         <v>33</v>
@@ -21483,7 +21483,7 @@
         <v>46220.31099537037</v>
       </c>
       <c r="F277" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G277" s="0" t="s">
         <v>33</v>
@@ -21551,7 +21551,7 @@
         <v>46221.05189814815</v>
       </c>
       <c r="F278" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G278" s="0" t="s">
         <v>24</v>
@@ -21619,7 +21619,7 @@
         <v>46220.05306712963</v>
       </c>
       <c r="F279" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G279" s="0" t="s">
         <v>33</v>
@@ -21655,7 +21655,7 @@
         <v>0</v>
       </c>
       <c r="R279" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S279" s="0" t="s">
         <v>25</v>
@@ -21687,7 +21687,7 @@
         <v>46229.36074074074</v>
       </c>
       <c r="F280" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G280" s="0" t="s">
         <v>33</v>
@@ -21755,7 +21755,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F281" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G281" s="0" t="s">
         <v>33</v>
@@ -21823,7 +21823,7 @@
         <v>46202.80762731482</v>
       </c>
       <c r="F282" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G282" s="0" t="s">
         <v>33</v>
@@ -21862,7 +21862,7 @@
         <v>1</v>
       </c>
       <c r="S282" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T282" s="0" t="s">
         <v>25</v>
@@ -21891,7 +21891,7 @@
         <v>46213.61820601852</v>
       </c>
       <c r="F283" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G283" s="0" t="s">
         <v>33</v>
@@ -21959,7 +21959,7 @@
         <v>46212.191030092596</v>
       </c>
       <c r="F284" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G284" s="0" t="s">
         <v>33</v>
@@ -22027,7 +22027,7 @@
         <v>46214.51880787037</v>
       </c>
       <c r="F285" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G285" s="0" t="s">
         <v>33</v>
@@ -22095,7 +22095,7 @@
         <v>46217.85386574074</v>
       </c>
       <c r="F286" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>24</v>
@@ -22122,7 +22122,7 @@
         <v>25</v>
       </c>
       <c r="O286" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P286" s="0" t="s">
         <v>25</v>
@@ -22163,7 +22163,7 @@
         <v>46198.053506944445</v>
       </c>
       <c r="F287" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>33</v>
@@ -22231,7 +22231,7 @@
         <v>46225.94484953704</v>
       </c>
       <c r="F288" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G288" s="0" t="s">
         <v>33</v>
@@ -22243,7 +22243,7 @@
         <v>33</v>
       </c>
       <c r="J288" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K288" s="0" t="s">
         <v>25</v>
@@ -22263,8 +22263,8 @@
       <c r="P288" s="0">
         <v>1</v>
       </c>
-      <c r="Q288" s="0" t="s">
-        <v>25</v>
+      <c r="Q288" s="0">
+        <v>0</v>
       </c>
       <c r="R288" s="0" t="s">
         <v>25</v>
@@ -22299,7 +22299,7 @@
         <v>46197.68172453704</v>
       </c>
       <c r="F289" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G289" s="0" t="s">
         <v>33</v>
@@ -22332,7 +22332,7 @@
         <v>0</v>
       </c>
       <c r="Q289" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R289" s="0" t="s">
         <v>25</v>
@@ -22367,7 +22367,7 @@
         <v>46218.38079861111</v>
       </c>
       <c r="F290" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G290" s="0" t="s">
         <v>24</v>
@@ -22435,7 +22435,7 @@
         <v>46218.407002314816</v>
       </c>
       <c r="F291" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G291" s="0" t="s">
         <v>24</v>
@@ -22503,7 +22503,7 @@
         <v>46217.92925925926</v>
       </c>
       <c r="F292" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G292" s="0" t="s">
         <v>24</v>
@@ -22571,7 +22571,7 @@
         <v>46208.01679398148</v>
       </c>
       <c r="F293" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G293" s="0" t="s">
         <v>33</v>
@@ -22639,7 +22639,7 @@
         <v>46217.85398148148</v>
       </c>
       <c r="F294" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G294" s="0" t="s">
         <v>24</v>
@@ -22666,7 +22666,7 @@
         <v>25</v>
       </c>
       <c r="O294" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P294" s="0" t="s">
         <v>25</v>
@@ -22707,7 +22707,7 @@
         <v>46226.854050925926</v>
       </c>
       <c r="F295" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G295" s="0" t="s">
         <v>24</v>
@@ -22775,7 +22775,7 @@
         <v>46199.4216087963</v>
       </c>
       <c r="F296" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G296" s="0" t="s">
         <v>28</v>
@@ -22843,7 +22843,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F297" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G297" s="0" t="s">
         <v>28</v>
@@ -22911,7 +22911,7 @@
         <v>46218.91337962963</v>
       </c>
       <c r="F298" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G298" s="0" t="s">
         <v>33</v>
@@ -22979,7 +22979,7 @@
         <v>46228.97625</v>
       </c>
       <c r="F299" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G299" s="0" t="s">
         <v>28</v>
@@ -23047,7 +23047,7 @@
         <v>46221.15589120371</v>
       </c>
       <c r="F300" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G300" s="0" t="s">
         <v>24</v>
@@ -23115,7 +23115,7 @@
         <v>46224.57979166666</v>
       </c>
       <c r="F301" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G301" s="0" t="s">
         <v>33</v>
@@ -23145,7 +23145,7 @@
         <v>0</v>
       </c>
       <c r="P301" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q301" s="0" t="s">
         <v>25</v>
@@ -23183,7 +23183,7 @@
         <v>46226.85146990741</v>
       </c>
       <c r="F302" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G302" s="0" t="s">
         <v>33</v>
@@ -23195,7 +23195,7 @@
         <v>33</v>
       </c>
       <c r="J302" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K302" s="0" t="s">
         <v>25</v>
@@ -23215,8 +23215,8 @@
       <c r="P302" s="0">
         <v>0</v>
       </c>
-      <c r="Q302" s="0" t="s">
-        <v>25</v>
+      <c r="Q302" s="0">
+        <v>0</v>
       </c>
       <c r="R302" s="0" t="s">
         <v>25</v>
@@ -23251,7 +23251,7 @@
         <v>46221.08181712963</v>
       </c>
       <c r="F303" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G303" s="0" t="s">
         <v>24</v>
@@ -23319,7 +23319,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F304" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G304" s="0" t="s">
         <v>24</v>
@@ -23387,7 +23387,7 @@
         <v>46221.17738425926</v>
       </c>
       <c r="F305" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G305" s="0" t="s">
         <v>24</v>
@@ -23455,7 +23455,7 @@
         <v>46203.398622685185</v>
       </c>
       <c r="F306" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G306" s="0" t="s">
         <v>24</v>
@@ -23473,7 +23473,7 @@
         <v>24</v>
       </c>
       <c r="L306" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M306" s="0" t="s">
         <v>25</v>
@@ -23493,8 +23493,8 @@
       <c r="R306" s="0">
         <v>1</v>
       </c>
-      <c r="S306" s="0" t="s">
-        <v>25</v>
+      <c r="S306" s="0">
+        <v>0</v>
       </c>
       <c r="T306" s="0" t="s">
         <v>25</v>
@@ -23523,7 +23523,7 @@
         <v>46204.071388888886</v>
       </c>
       <c r="F307" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G307" s="0" t="s">
         <v>24</v>
@@ -23591,7 +23591,7 @@
         <v>46227.35508101852</v>
       </c>
       <c r="F308" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G308" s="0" t="s">
         <v>24</v>
@@ -23621,7 +23621,7 @@
         <v>1</v>
       </c>
       <c r="P308" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q308" s="0" t="s">
         <v>25</v>
@@ -23659,7 +23659,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F309" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G309" s="0" t="s">
         <v>28</v>
@@ -23727,7 +23727,7 @@
         <v>46220.05663194445</v>
       </c>
       <c r="F310" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G310" s="0" t="s">
         <v>24</v>
@@ -23795,7 +23795,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F311" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G311" s="0" t="s">
         <v>24</v>
@@ -23863,7 +23863,7 @@
         <v>46230.258576388886</v>
       </c>
       <c r="F312" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G312" s="0" t="s">
         <v>33</v>
@@ -23931,7 +23931,7 @@
         <v>46207.340208333335</v>
       </c>
       <c r="F313" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G313" s="0" t="s">
         <v>33</v>
@@ -23949,7 +23949,7 @@
         <v>33</v>
       </c>
       <c r="L313" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M313" s="0" t="s">
         <v>25</v>
@@ -23969,8 +23969,8 @@
       <c r="R313" s="0">
         <v>1</v>
       </c>
-      <c r="S313" s="0" t="s">
-        <v>25</v>
+      <c r="S313" s="0">
+        <v>0</v>
       </c>
       <c r="T313" s="0" t="s">
         <v>25</v>
@@ -23999,7 +23999,7 @@
         <v>46203.22761574074</v>
       </c>
       <c r="F314" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G314" s="0" t="s">
         <v>33</v>
@@ -24017,7 +24017,7 @@
         <v>33</v>
       </c>
       <c r="L314" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M314" s="0" t="s">
         <v>25</v>
@@ -24037,8 +24037,8 @@
       <c r="R314" s="0">
         <v>1</v>
       </c>
-      <c r="S314" s="0" t="s">
-        <v>25</v>
+      <c r="S314" s="0">
+        <v>0</v>
       </c>
       <c r="T314" s="0" t="s">
         <v>25</v>
@@ -24067,7 +24067,7 @@
         <v>46203.73695601852</v>
       </c>
       <c r="F315" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G315" s="0" t="s">
         <v>33</v>
@@ -24135,7 +24135,7 @@
         <v>46209.27856481481</v>
       </c>
       <c r="F316" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G316" s="0" t="s">
         <v>33</v>
@@ -24203,7 +24203,7 @@
         <v>46221.03878472222</v>
       </c>
       <c r="F317" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G317" s="0" t="s">
         <v>24</v>
@@ -24271,7 +24271,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F318" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G318" s="0" t="s">
         <v>24</v>
@@ -24339,7 +24339,7 @@
         <v>46222.71545138889</v>
       </c>
       <c r="F319" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G319" s="0" t="s">
         <v>33</v>
@@ -24407,7 +24407,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F320" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G320" s="0" t="s">
         <v>24</v>
@@ -24475,13 +24475,13 @@
         <v>46234.76244212963</v>
       </c>
       <c r="F321" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G321" s="0" t="s">
         <v>28</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I321" s="0" t="s">
         <v>25</v>
@@ -24502,7 +24502,7 @@
         <v>25</v>
       </c>
       <c r="O321" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P321" s="0" t="s">
         <v>25</v>
@@ -24523,7 +24523,7 @@
         <v>25</v>
       </c>
       <c r="V321" s="0" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="322">
@@ -24543,7 +24543,7 @@
         <v>46221.20269675926</v>
       </c>
       <c r="F322" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G322" s="0" t="s">
         <v>33</v>
@@ -24611,7 +24611,7 @@
         <v>46234.06684027778</v>
       </c>
       <c r="F323" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G323" s="0" t="s">
         <v>33</v>
@@ -24679,7 +24679,7 @@
         <v>46230.76188657407</v>
       </c>
       <c r="F324" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G324" s="0" t="s">
         <v>24</v>
@@ -24747,7 +24747,7 @@
         <v>46233.76460648148</v>
       </c>
       <c r="F325" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G325" s="0" t="s">
         <v>33</v>
@@ -24815,7 +24815,7 @@
         <v>46200.90429398148</v>
       </c>
       <c r="F326" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G326" s="0" t="s">
         <v>24</v>
@@ -24883,7 +24883,7 @@
         <v>46201.17297453704</v>
       </c>
       <c r="F327" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G327" s="0" t="s">
         <v>33</v>
@@ -24951,7 +24951,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F328" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G328" s="0" t="s">
         <v>24</v>
@@ -25019,7 +25019,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F329" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G329" s="0" t="s">
         <v>24</v>
@@ -25087,7 +25087,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F330" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G330" s="0" t="s">
         <v>24</v>
@@ -25155,7 +25155,7 @@
         <v>46218.3946875</v>
       </c>
       <c r="F331" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G331" s="0" t="s">
         <v>24</v>
@@ -25223,7 +25223,7 @@
         <v>46220.044120370374</v>
       </c>
       <c r="F332" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G332" s="0" t="s">
         <v>24</v>
@@ -25291,7 +25291,7 @@
         <v>46223.899201388886</v>
       </c>
       <c r="F333" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G333" s="0" t="s">
         <v>24</v>
@@ -25359,7 +25359,7 @@
         <v>46209.39717592593</v>
       </c>
       <c r="F334" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G334" s="0" t="s">
         <v>24</v>
@@ -25427,7 +25427,7 @@
         <v>46197.398356481484</v>
       </c>
       <c r="F335" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G335" s="0" t="s">
         <v>24</v>
@@ -25495,7 +25495,7 @@
         <v>46226.854050925926</v>
       </c>
       <c r="F336" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G336" s="0" t="s">
         <v>24</v>
@@ -25563,7 +25563,7 @@
         <v>46230.38767361111</v>
       </c>
       <c r="F337" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>33</v>
@@ -25631,7 +25631,7 @@
         <v>46226.892534722225</v>
       </c>
       <c r="F338" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G338" s="0" t="s">
         <v>33</v>
@@ -25699,7 +25699,7 @@
         <v>46213.6180787037</v>
       </c>
       <c r="F339" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G339" s="0" t="s">
         <v>24</v>
@@ -25767,7 +25767,7 @@
         <v>46222.00641203704</v>
       </c>
       <c r="F340" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G340" s="0" t="s">
         <v>24</v>
@@ -25835,7 +25835,7 @@
         <v>46220.099016203705</v>
       </c>
       <c r="F341" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G341" s="0" t="s">
         <v>24</v>
@@ -25903,7 +25903,7 @@
         <v>46229.92053240741</v>
       </c>
       <c r="F342" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G342" s="0" t="s">
         <v>33</v>
@@ -25971,7 +25971,7 @@
         <v>46224.436886574076</v>
       </c>
       <c r="F343" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G343" s="0" t="s">
         <v>24</v>
@@ -25998,7 +25998,7 @@
         <v>25</v>
       </c>
       <c r="O343" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P343" s="0" t="s">
         <v>25</v>
@@ -26039,7 +26039,7 @@
         <v>46216.91412037037</v>
       </c>
       <c r="F344" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G344" s="0" t="s">
         <v>24</v>
@@ -26107,7 +26107,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F345" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G345" s="0" t="s">
         <v>24</v>
@@ -26125,7 +26125,7 @@
         <v>24</v>
       </c>
       <c r="L345" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M345" s="0" t="s">
         <v>25</v>
@@ -26145,8 +26145,8 @@
       <c r="R345" s="0">
         <v>1</v>
       </c>
-      <c r="S345" s="0" t="s">
-        <v>25</v>
+      <c r="S345" s="0">
+        <v>0</v>
       </c>
       <c r="T345" s="0" t="s">
         <v>25</v>
@@ -26175,7 +26175,7 @@
         <v>46221.21163194445</v>
       </c>
       <c r="F346" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G346" s="0" t="s">
         <v>24</v>
@@ -26202,7 +26202,7 @@
         <v>25</v>
       </c>
       <c r="O346" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P346" s="0" t="s">
         <v>25</v>
@@ -26243,7 +26243,7 @@
         <v>46213.27150462963</v>
       </c>
       <c r="F347" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G347" s="0" t="s">
         <v>33</v>
@@ -26255,7 +26255,7 @@
         <v>33</v>
       </c>
       <c r="J347" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K347" s="0" t="s">
         <v>25</v>
@@ -26275,8 +26275,8 @@
       <c r="P347" s="0">
         <v>1</v>
       </c>
-      <c r="Q347" s="0" t="s">
-        <v>25</v>
+      <c r="Q347" s="0">
+        <v>0</v>
       </c>
       <c r="R347" s="0" t="s">
         <v>25</v>
@@ -26311,7 +26311,7 @@
         <v>46232.92104166667</v>
       </c>
       <c r="F348" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G348" s="0" t="s">
         <v>33</v>
@@ -26379,7 +26379,7 @@
         <v>46204.81618055556</v>
       </c>
       <c r="F349" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G349" s="0" t="s">
         <v>24</v>
@@ -26447,7 +26447,7 @@
         <v>46184.345671296294</v>
       </c>
       <c r="F350" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G350" s="0" t="s">
         <v>24</v>
@@ -26515,7 +26515,7 @@
         <v>46213.61584490741</v>
       </c>
       <c r="F351" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>24</v>
@@ -26583,7 +26583,7 @@
         <v>46220.05876157407</v>
       </c>
       <c r="F352" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G352" s="0" t="s">
         <v>24</v>
@@ -26651,7 +26651,7 @@
         <v>46198.76695601852</v>
       </c>
       <c r="F353" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G353" s="0" t="s">
         <v>24</v>
@@ -26669,7 +26669,7 @@
         <v>24</v>
       </c>
       <c r="L353" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M353" s="0" t="s">
         <v>25</v>
@@ -26689,8 +26689,8 @@
       <c r="R353" s="0">
         <v>1</v>
       </c>
-      <c r="S353" s="0" t="s">
-        <v>25</v>
+      <c r="S353" s="0">
+        <v>0</v>
       </c>
       <c r="T353" s="0" t="s">
         <v>25</v>
@@ -26719,7 +26719,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F354" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G354" s="0" t="s">
         <v>24</v>
@@ -26787,7 +26787,7 @@
         <v>46231.41795138889</v>
       </c>
       <c r="F355" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G355" s="0" t="s">
         <v>33</v>
@@ -26796,7 +26796,7 @@
         <v>33</v>
       </c>
       <c r="I355" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J355" s="0" t="s">
         <v>25</v>
@@ -26816,8 +26816,8 @@
       <c r="O355" s="0">
         <v>0</v>
       </c>
-      <c r="P355" s="0" t="s">
-        <v>25</v>
+      <c r="P355" s="0">
+        <v>0</v>
       </c>
       <c r="Q355" s="0" t="s">
         <v>25</v>
@@ -26855,7 +26855,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F356" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G356" s="0" t="s">
         <v>28</v>
@@ -26873,7 +26873,7 @@
         <v>28</v>
       </c>
       <c r="L356" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M356" s="0" t="s">
         <v>25</v>
@@ -26893,8 +26893,8 @@
       <c r="R356" s="0">
         <v>1</v>
       </c>
-      <c r="S356" s="0" t="s">
-        <v>25</v>
+      <c r="S356" s="0">
+        <v>0</v>
       </c>
       <c r="T356" s="0" t="s">
         <v>25</v>
@@ -26923,7 +26923,7 @@
         <v>46207.38381944445</v>
       </c>
       <c r="F357" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G357" s="0" t="s">
         <v>33</v>
@@ -26941,7 +26941,7 @@
         <v>33</v>
       </c>
       <c r="L357" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M357" s="0" t="s">
         <v>25</v>
@@ -26961,8 +26961,8 @@
       <c r="R357" s="0">
         <v>1</v>
       </c>
-      <c r="S357" s="0" t="s">
-        <v>25</v>
+      <c r="S357" s="0">
+        <v>0</v>
       </c>
       <c r="T357" s="0" t="s">
         <v>25</v>
@@ -26991,7 +26991,7 @@
         <v>46198.764710648145</v>
       </c>
       <c r="F358" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G358" s="0" t="s">
         <v>24</v>
@@ -27009,7 +27009,7 @@
         <v>24</v>
       </c>
       <c r="L358" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M358" s="0" t="s">
         <v>25</v>
@@ -27029,8 +27029,8 @@
       <c r="R358" s="0">
         <v>1</v>
       </c>
-      <c r="S358" s="0" t="s">
-        <v>25</v>
+      <c r="S358" s="0">
+        <v>0</v>
       </c>
       <c r="T358" s="0" t="s">
         <v>25</v>
@@ -27059,7 +27059,7 @@
         <v>46208.60445601852</v>
       </c>
       <c r="F359" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G359" s="0" t="s">
         <v>33</v>
@@ -27127,7 +27127,7 @@
         <v>46228.05704861111</v>
       </c>
       <c r="F360" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G360" s="0" t="s">
         <v>33</v>
@@ -27195,7 +27195,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F361" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G361" s="0" t="s">
         <v>28</v>
@@ -27213,7 +27213,7 @@
         <v>28</v>
       </c>
       <c r="L361" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M361" s="0" t="s">
         <v>25</v>
@@ -27233,8 +27233,8 @@
       <c r="R361" s="0">
         <v>1</v>
       </c>
-      <c r="S361" s="0" t="s">
-        <v>25</v>
+      <c r="S361" s="0">
+        <v>0</v>
       </c>
       <c r="T361" s="0" t="s">
         <v>25</v>
@@ -27263,7 +27263,7 @@
         <v>46213.61833333333</v>
       </c>
       <c r="F362" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G362" s="0" t="s">
         <v>28</v>
@@ -27331,7 +27331,7 @@
         <v>46198.7566087963</v>
       </c>
       <c r="F363" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G363" s="0" t="s">
         <v>24</v>
@@ -27349,7 +27349,7 @@
         <v>24</v>
       </c>
       <c r="L363" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M363" s="0" t="s">
         <v>25</v>
@@ -27369,8 +27369,8 @@
       <c r="R363" s="0">
         <v>1</v>
       </c>
-      <c r="S363" s="0" t="s">
-        <v>25</v>
+      <c r="S363" s="0">
+        <v>0</v>
       </c>
       <c r="T363" s="0" t="s">
         <v>25</v>
@@ -27399,7 +27399,7 @@
         <v>46230.76185185185</v>
       </c>
       <c r="F364" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G364" s="0" t="s">
         <v>24</v>
@@ -27467,7 +27467,7 @@
         <v>46221.105474537035</v>
       </c>
       <c r="F365" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G365" s="0" t="s">
         <v>24</v>
@@ -27535,7 +27535,7 @@
         <v>46227.35528935185</v>
       </c>
       <c r="F366" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G366" s="0" t="s">
         <v>24</v>
@@ -27603,7 +27603,7 @@
         <v>46228.424259259256</v>
       </c>
       <c r="F367" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G367" s="0" t="s">
         <v>33</v>
@@ -27671,7 +27671,7 @@
         <v>46204.591203703705</v>
       </c>
       <c r="F368" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G368" s="0" t="s">
         <v>33</v>
@@ -27739,7 +27739,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F369" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G369" s="0" t="s">
         <v>24</v>
@@ -27807,7 +27807,7 @@
         <v>46225.22864583333</v>
       </c>
       <c r="F370" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G370" s="0" t="s">
         <v>24</v>
@@ -27875,7 +27875,7 @@
         <v>46203.38690972222</v>
       </c>
       <c r="F371" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G371" s="0" t="s">
         <v>24</v>
@@ -27943,7 +27943,7 @@
         <v>46223.08658564815</v>
       </c>
       <c r="F372" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G372" s="0" t="s">
         <v>33</v>
@@ -28011,7 +28011,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F373" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G373" s="0" t="s">
         <v>24</v>
@@ -28079,7 +28079,7 @@
         <v>46217.32613425926</v>
       </c>
       <c r="F374" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G374" s="0" t="s">
         <v>33</v>
@@ -28115,7 +28115,7 @@
         <v>0</v>
       </c>
       <c r="R374" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S374" s="0" t="s">
         <v>25</v>
@@ -28147,7 +28147,7 @@
         <v>46199.954201388886</v>
       </c>
       <c r="F375" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G375" s="0" t="s">
         <v>33</v>
@@ -28215,7 +28215,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F376" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G376" s="0" t="s">
         <v>28</v>
@@ -28233,7 +28233,7 @@
         <v>28</v>
       </c>
       <c r="L376" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M376" s="0" t="s">
         <v>25</v>
@@ -28253,8 +28253,8 @@
       <c r="R376" s="0">
         <v>1</v>
       </c>
-      <c r="S376" s="0" t="s">
-        <v>25</v>
+      <c r="S376" s="0">
+        <v>0</v>
       </c>
       <c r="T376" s="0" t="s">
         <v>25</v>
@@ -28283,7 +28283,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F377" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G377" s="0" t="s">
         <v>28</v>
@@ -28351,7 +28351,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F378" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G378" s="0" t="s">
         <v>24</v>
@@ -28419,7 +28419,7 @@
         <v>46231.97907407407</v>
       </c>
       <c r="F379" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G379" s="0" t="s">
         <v>24</v>
@@ -28446,7 +28446,7 @@
         <v>25</v>
       </c>
       <c r="O379" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P379" s="0" t="s">
         <v>25</v>
@@ -28487,7 +28487,7 @@
         <v>46184.344409722224</v>
       </c>
       <c r="F380" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G380" s="0" t="s">
         <v>24</v>
@@ -28555,7 +28555,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F381" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G381" s="0" t="s">
         <v>28</v>
@@ -28623,7 +28623,7 @@
         <v>46217.72965277778</v>
       </c>
       <c r="F382" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G382" s="0" t="s">
         <v>24</v>
@@ -28691,7 +28691,7 @@
         <v>46223.899201388886</v>
       </c>
       <c r="F383" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G383" s="0" t="s">
         <v>24</v>
@@ -28759,7 +28759,7 @@
         <v>46233.8608912037</v>
       </c>
       <c r="F384" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G384" s="0" t="s">
         <v>33</v>
@@ -28827,7 +28827,7 @@
         <v>46231.97912037037</v>
       </c>
       <c r="F385" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G385" s="0" t="s">
         <v>24</v>
@@ -28854,7 +28854,7 @@
         <v>25</v>
       </c>
       <c r="O385" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P385" s="0" t="s">
         <v>25</v>
@@ -28895,7 +28895,7 @@
         <v>46229.354837962965</v>
       </c>
       <c r="F386" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G386" s="0" t="s">
         <v>28</v>
@@ -28963,7 +28963,7 @@
         <v>46220.87525462963</v>
       </c>
       <c r="F387" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G387" s="0" t="s">
         <v>24</v>
@@ -29031,7 +29031,7 @@
         <v>46202.8822337963</v>
       </c>
       <c r="F388" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G388" s="0" t="s">
         <v>24</v>
@@ -29043,7 +29043,7 @@
         <v>24</v>
       </c>
       <c r="J388" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K388" s="0" t="s">
         <v>25</v>
@@ -29063,8 +29063,8 @@
       <c r="P388" s="0">
         <v>0</v>
       </c>
-      <c r="Q388" s="0" t="s">
-        <v>25</v>
+      <c r="Q388" s="0">
+        <v>0</v>
       </c>
       <c r="R388" s="0" t="s">
         <v>25</v>
@@ -29099,7 +29099,7 @@
         <v>46196.43208333333</v>
       </c>
       <c r="F389" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G389" s="0" t="s">
         <v>33</v>
@@ -29167,7 +29167,7 @@
         <v>46225.41782407407</v>
       </c>
       <c r="F390" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G390" s="0" t="s">
         <v>28</v>
@@ -29200,7 +29200,7 @@
         <v>1</v>
       </c>
       <c r="Q390" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R390" s="0" t="s">
         <v>25</v>
@@ -29235,7 +29235,7 @@
         <v>46226.138449074075</v>
       </c>
       <c r="F391" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G391" s="0" t="s">
         <v>33</v>
@@ -29303,7 +29303,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F392" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G392" s="0" t="s">
         <v>28</v>
@@ -29371,7 +29371,7 @@
         <v>46234.25630787037</v>
       </c>
       <c r="F393" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G393" s="0" t="s">
         <v>24</v>
@@ -29439,7 +29439,7 @@
         <v>46204.591203703705</v>
       </c>
       <c r="F394" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G394" s="0" t="s">
         <v>33</v>
@@ -29507,7 +29507,7 @@
         <v>46212.38707175926</v>
       </c>
       <c r="F395" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G395" s="0" t="s">
         <v>33</v>
@@ -29575,7 +29575,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F396" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G396" s="0" t="s">
         <v>28</v>
@@ -29643,7 +29643,7 @@
         <v>46205.00303240741</v>
       </c>
       <c r="F397" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G397" s="0" t="s">
         <v>24</v>
@@ -29711,7 +29711,7 @@
         <v>46219.39318287037</v>
       </c>
       <c r="F398" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G398" s="0" t="s">
         <v>33</v>
@@ -29779,7 +29779,7 @@
         <v>46221.08862268519</v>
       </c>
       <c r="F399" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G399" s="0" t="s">
         <v>24</v>
@@ -29847,7 +29847,7 @@
         <v>46213.61585648148</v>
       </c>
       <c r="F400" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G400" s="0" t="s">
         <v>24</v>
@@ -29915,7 +29915,7 @@
         <v>46205.85377314815</v>
       </c>
       <c r="F401" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G401" s="0" t="s">
         <v>24</v>
@@ -29933,7 +29933,7 @@
         <v>24</v>
       </c>
       <c r="L401" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M401" s="0" t="s">
         <v>25</v>
@@ -29953,8 +29953,8 @@
       <c r="R401" s="0">
         <v>1</v>
       </c>
-      <c r="S401" s="0" t="s">
-        <v>25</v>
+      <c r="S401" s="0">
+        <v>0</v>
       </c>
       <c r="T401" s="0" t="s">
         <v>25</v>
@@ -29983,7 +29983,7 @@
         <v>46218.73540509259</v>
       </c>
       <c r="F402" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G402" s="0" t="s">
         <v>24</v>
@@ -30013,7 +30013,7 @@
         <v>1</v>
       </c>
       <c r="P402" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q402" s="0" t="s">
         <v>25</v>
@@ -30051,7 +30051,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F403" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G403" s="0" t="s">
         <v>24</v>
@@ -30119,7 +30119,7 @@
         <v>46194.496782407405</v>
       </c>
       <c r="F404" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G404" s="0" t="s">
         <v>28</v>
@@ -30187,7 +30187,7 @@
         <v>46206.041817129626</v>
       </c>
       <c r="F405" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G405" s="0" t="s">
         <v>33</v>
@@ -30255,7 +30255,7 @@
         <v>46223.92380787037</v>
       </c>
       <c r="F406" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G406" s="0" t="s">
         <v>28</v>
@@ -30323,7 +30323,7 @@
         <v>46211.74564814815</v>
       </c>
       <c r="F407" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G407" s="0" t="s">
         <v>24</v>
@@ -30391,7 +30391,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F408" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G408" s="0" t="s">
         <v>24</v>
@@ -30459,7 +30459,7 @@
         <v>46232.53965277778</v>
       </c>
       <c r="F409" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G409" s="0" t="s">
         <v>24</v>
@@ -30527,7 +30527,7 @@
         <v>46198.76357638889</v>
       </c>
       <c r="F410" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G410" s="0" t="s">
         <v>24</v>
@@ -30545,7 +30545,7 @@
         <v>24</v>
       </c>
       <c r="L410" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M410" s="0" t="s">
         <v>25</v>
@@ -30565,8 +30565,8 @@
       <c r="R410" s="0">
         <v>1</v>
       </c>
-      <c r="S410" s="0" t="s">
-        <v>25</v>
+      <c r="S410" s="0">
+        <v>0</v>
       </c>
       <c r="T410" s="0" t="s">
         <v>25</v>
@@ -30595,7 +30595,7 @@
         <v>46214.41127314815</v>
       </c>
       <c r="F411" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G411" s="0" t="s">
         <v>33</v>
@@ -30663,7 +30663,7 @@
         <v>46210.39944444445</v>
       </c>
       <c r="F412" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G412" s="0" t="s">
         <v>24</v>
@@ -30731,7 +30731,7 @@
         <v>46219.765706018516</v>
       </c>
       <c r="F413" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G413" s="0" t="s">
         <v>24</v>
@@ -30799,7 +30799,7 @@
         <v>46203.900046296294</v>
       </c>
       <c r="F414" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G414" s="0" t="s">
         <v>28</v>
@@ -30817,7 +30817,7 @@
         <v>28</v>
       </c>
       <c r="L414" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M414" s="0" t="s">
         <v>25</v>
@@ -30837,8 +30837,8 @@
       <c r="R414" s="0">
         <v>1</v>
       </c>
-      <c r="S414" s="0" t="s">
-        <v>25</v>
+      <c r="S414" s="0">
+        <v>0</v>
       </c>
       <c r="T414" s="0" t="s">
         <v>25</v>
@@ -30867,7 +30867,7 @@
         <v>46220.009421296294</v>
       </c>
       <c r="F415" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G415" s="0" t="s">
         <v>24</v>
@@ -30935,7 +30935,7 @@
         <v>46219.015127314815</v>
       </c>
       <c r="F416" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G416" s="0" t="s">
         <v>24</v>
@@ -31003,7 +31003,7 @@
         <v>46213.618310185186</v>
       </c>
       <c r="F417" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G417" s="0" t="s">
         <v>28</v>
@@ -31071,7 +31071,7 @@
         <v>46218.40199074074</v>
       </c>
       <c r="F418" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G418" s="0" t="s">
         <v>24</v>
@@ -31139,7 +31139,7 @@
         <v>46198.75818287037</v>
       </c>
       <c r="F419" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G419" s="0" t="s">
         <v>24</v>
@@ -31157,7 +31157,7 @@
         <v>24</v>
       </c>
       <c r="L419" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M419" s="0" t="s">
         <v>25</v>
@@ -31177,8 +31177,8 @@
       <c r="R419" s="0">
         <v>1</v>
       </c>
-      <c r="S419" s="0" t="s">
-        <v>25</v>
+      <c r="S419" s="0">
+        <v>0</v>
       </c>
       <c r="T419" s="0" t="s">
         <v>25</v>
@@ -31207,7 +31207,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F420" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G420" s="0" t="s">
         <v>28</v>
@@ -31275,7 +31275,7 @@
         <v>46199.24039351852</v>
       </c>
       <c r="F421" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G421" s="0" t="s">
         <v>33</v>
@@ -31343,7 +31343,7 @@
         <v>46217.854097222225</v>
       </c>
       <c r="F422" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G422" s="0" t="s">
         <v>24</v>
@@ -31370,7 +31370,7 @@
         <v>25</v>
       </c>
       <c r="O422" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P422" s="0" t="s">
         <v>25</v>
@@ -31411,7 +31411,7 @@
         <v>46207.7878125</v>
       </c>
       <c r="F423" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G423" s="0" t="s">
         <v>33</v>
@@ -31479,7 +31479,7 @@
         <v>46217.09547453704</v>
       </c>
       <c r="F424" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G424" s="0" t="s">
         <v>24</v>
@@ -31491,7 +31491,7 @@
         <v>24</v>
       </c>
       <c r="J424" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K424" s="0" t="s">
         <v>25</v>
@@ -31511,8 +31511,8 @@
       <c r="P424" s="0">
         <v>1</v>
       </c>
-      <c r="Q424" s="0" t="s">
-        <v>25</v>
+      <c r="Q424" s="0">
+        <v>1</v>
       </c>
       <c r="R424" s="0" t="s">
         <v>25</v>
@@ -31547,7 +31547,7 @@
         <v>46200.88856481481</v>
       </c>
       <c r="F425" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G425" s="0" t="s">
         <v>28</v>
@@ -31615,7 +31615,7 @@
         <v>46207.091145833336</v>
       </c>
       <c r="F426" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G426" s="0" t="s">
         <v>33</v>
@@ -31633,7 +31633,7 @@
         <v>33</v>
       </c>
       <c r="L426" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M426" s="0" t="s">
         <v>25</v>
@@ -31653,8 +31653,8 @@
       <c r="R426" s="0">
         <v>1</v>
       </c>
-      <c r="S426" s="0" t="s">
-        <v>25</v>
+      <c r="S426" s="0">
+        <v>0</v>
       </c>
       <c r="T426" s="0" t="s">
         <v>25</v>
@@ -31683,7 +31683,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F427" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G427" s="0" t="s">
         <v>24</v>
@@ -31751,7 +31751,7 @@
         <v>46197.33201388889</v>
       </c>
       <c r="F428" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G428" s="0" t="s">
         <v>24</v>
@@ -31819,7 +31819,7 @@
         <v>46210.11184027778</v>
       </c>
       <c r="F429" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G429" s="0" t="s">
         <v>24</v>
@@ -31887,7 +31887,7 @@
         <v>46202.603946759256</v>
       </c>
       <c r="F430" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G430" s="0" t="s">
         <v>24</v>
@@ -31955,7 +31955,7 @@
         <v>46213.61804398148</v>
       </c>
       <c r="F431" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G431" s="0" t="s">
         <v>24</v>
@@ -32023,7 +32023,7 @@
         <v>46208.28020833333</v>
       </c>
       <c r="F432" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G432" s="0" t="s">
         <v>28</v>
@@ -32091,7 +32091,7 @@
         <v>46209.39716435185</v>
       </c>
       <c r="F433" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G433" s="0" t="s">
         <v>24</v>
@@ -32159,7 +32159,7 @@
         <v>46213.618055555555</v>
       </c>
       <c r="F434" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G434" s="0" t="s">
         <v>28</v>
@@ -32227,7 +32227,7 @@
         <v>46224.63983796296</v>
       </c>
       <c r="F435" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G435" s="0" t="s">
         <v>33</v>
@@ -32260,7 +32260,7 @@
         <v>0</v>
       </c>
       <c r="Q435" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R435" s="0" t="s">
         <v>25</v>
@@ -32295,7 +32295,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F436" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G436" s="0" t="s">
         <v>28</v>
@@ -32363,7 +32363,7 @@
         <v>46220.95984953704</v>
       </c>
       <c r="F437" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G437" s="0" t="s">
         <v>33</v>
@@ -32431,7 +32431,7 @@
         <v>46231.97927083333</v>
       </c>
       <c r="F438" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G438" s="0" t="s">
         <v>24</v>
@@ -32458,7 +32458,7 @@
         <v>25</v>
       </c>
       <c r="O438" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P438" s="0" t="s">
         <v>25</v>
@@ -32499,7 +32499,7 @@
         <v>46221.91984953704</v>
       </c>
       <c r="F439" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G439" s="0" t="s">
         <v>33</v>
@@ -32514,7 +32514,7 @@
         <v>33</v>
       </c>
       <c r="K439" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L439" s="0" t="s">
         <v>25</v>
@@ -32534,8 +32534,8 @@
       <c r="Q439" s="0">
         <v>1</v>
       </c>
-      <c r="R439" s="0" t="s">
-        <v>25</v>
+      <c r="R439" s="0">
+        <v>0</v>
       </c>
       <c r="S439" s="0" t="s">
         <v>25</v>
@@ -32567,7 +32567,7 @@
         <v>46234.256319444445</v>
       </c>
       <c r="F440" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G440" s="0" t="s">
         <v>24</v>
@@ -32635,7 +32635,7 @@
         <v>46222.38579861111</v>
       </c>
       <c r="F441" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G441" s="0" t="s">
         <v>33</v>
@@ -32703,7 +32703,7 @@
         <v>46225.796331018515</v>
       </c>
       <c r="F442" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G442" s="0" t="s">
         <v>33</v>
@@ -32715,7 +32715,7 @@
         <v>33</v>
       </c>
       <c r="J442" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K442" s="0" t="s">
         <v>25</v>
@@ -32735,8 +32735,8 @@
       <c r="P442" s="0">
         <v>1</v>
       </c>
-      <c r="Q442" s="0" t="s">
-        <v>25</v>
+      <c r="Q442" s="0">
+        <v>0</v>
       </c>
       <c r="R442" s="0" t="s">
         <v>25</v>
@@ -32771,7 +32771,7 @@
         <v>46226.6258912037</v>
       </c>
       <c r="F443" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G443" s="0" t="s">
         <v>33</v>
@@ -32839,7 +32839,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F444" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G444" s="0" t="s">
         <v>24</v>
@@ -32857,7 +32857,7 @@
         <v>24</v>
       </c>
       <c r="L444" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M444" s="0" t="s">
         <v>25</v>
@@ -32877,8 +32877,8 @@
       <c r="R444" s="0">
         <v>1</v>
       </c>
-      <c r="S444" s="0" t="s">
-        <v>25</v>
+      <c r="S444" s="0">
+        <v>0</v>
       </c>
       <c r="T444" s="0" t="s">
         <v>25</v>
@@ -32907,7 +32907,7 @@
         <v>46187.9200462963</v>
       </c>
       <c r="F445" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G445" s="0" t="s">
         <v>24</v>
@@ -32975,7 +32975,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F446" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G446" s="0" t="s">
         <v>28</v>
@@ -33043,7 +33043,7 @@
         <v>46221.14616898148</v>
       </c>
       <c r="F447" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G447" s="0" t="s">
         <v>24</v>
@@ -33111,7 +33111,7 @@
         <v>46232.813055555554</v>
       </c>
       <c r="F448" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G448" s="0" t="s">
         <v>28</v>
@@ -33179,7 +33179,7 @@
         <v>46204.36974537037</v>
       </c>
       <c r="F449" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G449" s="0" t="s">
         <v>33</v>
@@ -33218,7 +33218,7 @@
         <v>1</v>
       </c>
       <c r="S449" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T449" s="0" t="s">
         <v>25</v>
@@ -33247,7 +33247,7 @@
         <v>46213.61809027778</v>
       </c>
       <c r="F450" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G450" s="0" t="s">
         <v>28</v>
@@ -33315,7 +33315,7 @@
         <v>46218.06209490741</v>
       </c>
       <c r="F451" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G451" s="0" t="s">
         <v>24</v>
@@ -33383,7 +33383,7 @@
         <v>46219.01453703704</v>
       </c>
       <c r="F452" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G452" s="0" t="s">
         <v>24</v>
@@ -33451,7 +33451,7 @@
         <v>46224.790613425925</v>
       </c>
       <c r="F453" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G453" s="0" t="s">
         <v>33</v>
@@ -33519,7 +33519,7 @@
         <v>46225.15122685185</v>
       </c>
       <c r="F454" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G454" s="0" t="s">
         <v>33</v>
@@ -33587,7 +33587,7 @@
         <v>46220.101539351854</v>
       </c>
       <c r="F455" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G455" s="0" t="s">
         <v>24</v>
@@ -33655,7 +33655,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F456" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G456" s="0" t="s">
         <v>24</v>
@@ -33723,7 +33723,7 @@
         <v>46213.61819444445</v>
       </c>
       <c r="F457" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G457" s="0" t="s">
         <v>28</v>
@@ -33791,7 +33791,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F458" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G458" s="0" t="s">
         <v>24</v>
@@ -33859,7 +33859,7 @@
         <v>46222.62453703704</v>
       </c>
       <c r="F459" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G459" s="0" t="s">
         <v>33</v>
@@ -33927,7 +33927,7 @@
         <v>46219.037777777776</v>
       </c>
       <c r="F460" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G460" s="0" t="s">
         <v>24</v>
@@ -33995,7 +33995,7 @@
         <v>46201.332870370374</v>
       </c>
       <c r="F461" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G461" s="0" t="s">
         <v>24</v>
@@ -34063,7 +34063,7 @@
         <v>46220.12614583333</v>
       </c>
       <c r="F462" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G462" s="0" t="s">
         <v>24</v>
@@ -34131,7 +34131,7 @@
         <v>46223.26967592593</v>
       </c>
       <c r="F463" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G463" s="0" t="s">
         <v>33</v>
@@ -34199,7 +34199,7 @@
         <v>46230.404965277776</v>
       </c>
       <c r="F464" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G464" s="0" t="s">
         <v>24</v>
@@ -34267,7 +34267,7 @@
         <v>46197.03113425926</v>
       </c>
       <c r="F465" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G465" s="0" t="s">
         <v>24</v>
@@ -34335,7 +34335,7 @@
         <v>46212.285219907404</v>
       </c>
       <c r="F466" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G466" s="0" t="s">
         <v>33</v>
@@ -34403,7 +34403,7 @@
         <v>46220.11040509259</v>
       </c>
       <c r="F467" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G467" s="0" t="s">
         <v>24</v>
@@ -34471,7 +34471,7 @@
         <v>46221.19097222222</v>
       </c>
       <c r="F468" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G468" s="0" t="s">
         <v>24</v>
@@ -34539,7 +34539,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F469" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G469" s="0" t="s">
         <v>24</v>
@@ -34607,7 +34607,7 @@
         <v>46200.98619212963</v>
       </c>
       <c r="F470" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G470" s="0" t="s">
         <v>33</v>
@@ -34675,7 +34675,7 @@
         <v>46213.61833333333</v>
       </c>
       <c r="F471" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G471" s="0" t="s">
         <v>28</v>
@@ -34743,7 +34743,7 @@
         <v>46231.646944444445</v>
       </c>
       <c r="F472" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G472" s="0" t="s">
         <v>33</v>
@@ -34770,7 +34770,7 @@
         <v>25</v>
       </c>
       <c r="O472" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P472" s="0" t="s">
         <v>25</v>
@@ -34811,7 +34811,7 @@
         <v>46212.06758101852</v>
       </c>
       <c r="F473" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G473" s="0" t="s">
         <v>33</v>
@@ -34879,7 +34879,7 @@
         <v>46213.61584490741</v>
       </c>
       <c r="F474" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G474" s="0" t="s">
         <v>28</v>
@@ -34947,7 +34947,7 @@
         <v>46207.18613425926</v>
       </c>
       <c r="F475" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G475" s="0" t="s">
         <v>33</v>
@@ -35015,7 +35015,7 @@
         <v>46218.881574074076</v>
       </c>
       <c r="F476" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G476" s="0" t="s">
         <v>28</v>
@@ -35083,7 +35083,7 @@
         <v>46218.40934027778</v>
       </c>
       <c r="F477" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G477" s="0" t="s">
         <v>24</v>
@@ -35151,7 +35151,7 @@
         <v>46232.55458333333</v>
       </c>
       <c r="F478" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G478" s="0" t="s">
         <v>24</v>
@@ -35219,7 +35219,7 @@
         <v>46215.3794212963</v>
       </c>
       <c r="F479" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G479" s="0" t="s">
         <v>28</v>
@@ -35234,7 +35234,7 @@
         <v>28</v>
       </c>
       <c r="K479" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L479" s="0" t="s">
         <v>25</v>
@@ -35254,8 +35254,8 @@
       <c r="Q479" s="0">
         <v>1</v>
       </c>
-      <c r="R479" s="0" t="s">
-        <v>25</v>
+      <c r="R479" s="0">
+        <v>0</v>
       </c>
       <c r="S479" s="0" t="s">
         <v>25</v>
@@ -35287,7 +35287,7 @@
         <v>46198.763344907406</v>
       </c>
       <c r="F480" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G480" s="0" t="s">
         <v>24</v>
@@ -35305,7 +35305,7 @@
         <v>24</v>
       </c>
       <c r="L480" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M480" s="0" t="s">
         <v>25</v>
@@ -35325,8 +35325,8 @@
       <c r="R480" s="0">
         <v>1</v>
       </c>
-      <c r="S480" s="0" t="s">
-        <v>25</v>
+      <c r="S480" s="0">
+        <v>0</v>
       </c>
       <c r="T480" s="0" t="s">
         <v>25</v>
@@ -35355,7 +35355,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F481" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G481" s="0" t="s">
         <v>24</v>
@@ -35423,7 +35423,7 @@
         <v>46198.86886574074</v>
       </c>
       <c r="F482" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G482" s="0" t="s">
         <v>33</v>
@@ -35491,7 +35491,7 @@
         <v>46196.739953703705</v>
       </c>
       <c r="F483" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G483" s="0" t="s">
         <v>24</v>
@@ -35559,7 +35559,7 @@
         <v>46220.17188657408</v>
       </c>
       <c r="F484" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G484" s="0" t="s">
         <v>33</v>
@@ -35627,7 +35627,7 @@
         <v>46198.76422453704</v>
       </c>
       <c r="F485" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G485" s="0" t="s">
         <v>24</v>
@@ -35645,7 +35645,7 @@
         <v>24</v>
       </c>
       <c r="L485" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M485" s="0" t="s">
         <v>25</v>
@@ -35665,8 +35665,8 @@
       <c r="R485" s="0">
         <v>1</v>
       </c>
-      <c r="S485" s="0" t="s">
-        <v>25</v>
+      <c r="S485" s="0">
+        <v>0</v>
       </c>
       <c r="T485" s="0" t="s">
         <v>25</v>
@@ -35695,7 +35695,7 @@
         <v>46206.39832175926</v>
       </c>
       <c r="F486" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G486" s="0" t="s">
         <v>33</v>
@@ -35713,7 +35713,7 @@
         <v>33</v>
       </c>
       <c r="L486" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M486" s="0" t="s">
         <v>25</v>
@@ -35733,8 +35733,8 @@
       <c r="R486" s="0">
         <v>1</v>
       </c>
-      <c r="S486" s="0" t="s">
-        <v>25</v>
+      <c r="S486" s="0">
+        <v>0</v>
       </c>
       <c r="T486" s="0" t="s">
         <v>25</v>
@@ -35763,7 +35763,7 @@
         <v>46221.20111111111</v>
       </c>
       <c r="F487" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G487" s="0" t="s">
         <v>24</v>
@@ -35831,7 +35831,7 @@
         <v>46201.828206018516</v>
       </c>
       <c r="F488" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G488" s="0" t="s">
         <v>33</v>
@@ -35899,7 +35899,7 @@
         <v>46225.14921296296</v>
       </c>
       <c r="F489" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G489" s="0" t="s">
         <v>24</v>
@@ -35967,7 +35967,7 @@
         <v>46220.02171296296</v>
       </c>
       <c r="F490" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G490" s="0" t="s">
         <v>28</v>
@@ -35979,7 +35979,7 @@
         <v>28</v>
       </c>
       <c r="J490" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K490" s="0" t="s">
         <v>25</v>
@@ -35999,8 +35999,8 @@
       <c r="P490" s="0">
         <v>0</v>
       </c>
-      <c r="Q490" s="0" t="s">
-        <v>25</v>
+      <c r="Q490" s="0">
+        <v>0</v>
       </c>
       <c r="R490" s="0" t="s">
         <v>25</v>
@@ -36035,7 +36035,7 @@
         <v>46198.13486111111</v>
       </c>
       <c r="F491" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G491" s="0" t="s">
         <v>24</v>
@@ -36103,7 +36103,7 @@
         <v>46184.34568287037</v>
       </c>
       <c r="F492" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G492" s="0" t="s">
         <v>24</v>
@@ -36171,7 +36171,7 @@
         <v>46217.38422453704</v>
       </c>
       <c r="F493" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G493" s="0" t="s">
         <v>33</v>
@@ -36239,7 +36239,7 @@
         <v>46225.52695601852</v>
       </c>
       <c r="F494" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G494" s="0" t="s">
         <v>33</v>
@@ -36307,7 +36307,7 @@
         <v>46221.16657407407</v>
       </c>
       <c r="F495" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G495" s="0" t="s">
         <v>24</v>
@@ -36375,7 +36375,7 @@
         <v>46230.330462962964</v>
       </c>
       <c r="F496" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G496" s="0" t="s">
         <v>33</v>
@@ -36443,7 +36443,7 @@
         <v>46210.52042824074</v>
       </c>
       <c r="F497" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G497" s="0" t="s">
         <v>24</v>
@@ -36511,7 +36511,7 @@
         <v>46218.367951388886</v>
       </c>
       <c r="F498" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G498" s="0" t="s">
         <v>24</v>
@@ -36579,7 +36579,7 @@
         <v>46198.487546296295</v>
       </c>
       <c r="F499" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G499" s="0" t="s">
         <v>33</v>
@@ -36647,7 +36647,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F500" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G500" s="0" t="s">
         <v>24</v>
@@ -36715,7 +36715,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F501" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G501" s="0" t="s">
         <v>24</v>
@@ -36783,7 +36783,7 @@
         <v>46204.815405092595</v>
       </c>
       <c r="F502" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G502" s="0" t="s">
         <v>24</v>
@@ -36851,7 +36851,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F503" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G503" s="0" t="s">
         <v>33</v>
@@ -36919,7 +36919,7 @@
         <v>46199.37</v>
       </c>
       <c r="F504" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G504" s="0" t="s">
         <v>33</v>
@@ -36987,7 +36987,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F505" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G505" s="0" t="s">
         <v>28</v>
@@ -37055,7 +37055,7 @@
         <v>46225.073067129626</v>
       </c>
       <c r="F506" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G506" s="0" t="s">
         <v>33</v>
@@ -37123,7 +37123,7 @@
         <v>46224.54877314815</v>
       </c>
       <c r="F507" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G507" s="0" t="s">
         <v>33</v>
@@ -37191,7 +37191,7 @@
         <v>46229.89236111111</v>
       </c>
       <c r="F508" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G508" s="0" t="s">
         <v>33</v>
@@ -37259,7 +37259,7 @@
         <v>46200.507418981484</v>
       </c>
       <c r="F509" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G509" s="0" t="s">
         <v>33</v>
@@ -37327,7 +37327,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F510" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G510" s="0" t="s">
         <v>28</v>
@@ -37395,7 +37395,7 @@
         <v>46210.47645833333</v>
       </c>
       <c r="F511" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G511" s="0" t="s">
         <v>33</v>
@@ -37407,7 +37407,7 @@
         <v>33</v>
       </c>
       <c r="J511" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K511" s="0" t="s">
         <v>25</v>
@@ -37427,8 +37427,8 @@
       <c r="P511" s="0">
         <v>1</v>
       </c>
-      <c r="Q511" s="0" t="s">
-        <v>25</v>
+      <c r="Q511" s="0">
+        <v>0</v>
       </c>
       <c r="R511" s="0" t="s">
         <v>25</v>
@@ -37463,7 +37463,7 @@
         <v>46219.00199074074</v>
       </c>
       <c r="F512" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G512" s="0" t="s">
         <v>24</v>
@@ -37478,7 +37478,7 @@
         <v>24</v>
       </c>
       <c r="K512" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L512" s="0" t="s">
         <v>25</v>
@@ -37498,8 +37498,8 @@
       <c r="Q512" s="0">
         <v>1</v>
       </c>
-      <c r="R512" s="0" t="s">
-        <v>25</v>
+      <c r="R512" s="0">
+        <v>0</v>
       </c>
       <c r="S512" s="0" t="s">
         <v>25</v>
@@ -37531,7 +37531,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F513" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G513" s="0" t="s">
         <v>24</v>
@@ -37599,7 +37599,7 @@
         <v>46225.17865740741</v>
       </c>
       <c r="F514" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G514" s="0" t="s">
         <v>33</v>
@@ -37667,7 +37667,7 @@
         <v>46222.21196759259</v>
       </c>
       <c r="F515" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G515" s="0" t="s">
         <v>33</v>
@@ -37735,7 +37735,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F516" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G516" s="0" t="s">
         <v>24</v>
@@ -37803,7 +37803,7 @@
         <v>46218.09614583333</v>
       </c>
       <c r="F517" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G517" s="0" t="s">
         <v>28</v>
@@ -37871,7 +37871,7 @@
         <v>46206.616875</v>
       </c>
       <c r="F518" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G518" s="0" t="s">
         <v>33</v>
@@ -37939,7 +37939,7 @@
         <v>46206.85376157407</v>
       </c>
       <c r="F519" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G519" s="0" t="s">
         <v>24</v>
@@ -38007,7 +38007,7 @@
         <v>46219.0275</v>
       </c>
       <c r="F520" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G520" s="0" t="s">
         <v>24</v>
@@ -38075,7 +38075,7 @@
         <v>46220.37621527778</v>
       </c>
       <c r="F521" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G521" s="0" t="s">
         <v>33</v>
@@ -38143,7 +38143,7 @@
         <v>46221.063263888886</v>
       </c>
       <c r="F522" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G522" s="0" t="s">
         <v>24</v>
@@ -38211,7 +38211,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F523" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G523" s="0" t="s">
         <v>24</v>
@@ -38279,7 +38279,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F524" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G524" s="0" t="s">
         <v>28</v>
@@ -38347,7 +38347,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F525" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G525" s="0" t="s">
         <v>24</v>
@@ -38415,7 +38415,7 @@
         <v>46232.88266203704</v>
       </c>
       <c r="F526" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G526" s="0" t="s">
         <v>33</v>
@@ -38483,7 +38483,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F527" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G527" s="0" t="s">
         <v>28</v>
@@ -38551,7 +38551,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F528" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G528" s="0" t="s">
         <v>24</v>
@@ -38619,7 +38619,7 @@
         <v>46228.28525462963</v>
       </c>
       <c r="F529" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G529" s="0" t="s">
         <v>33</v>
@@ -38687,7 +38687,7 @@
         <v>46213.6180787037</v>
       </c>
       <c r="F530" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G530" s="0" t="s">
         <v>28</v>
@@ -38755,7 +38755,7 @@
         <v>46230.399305555555</v>
       </c>
       <c r="F531" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G531" s="0" t="s">
         <v>33</v>
@@ -38823,7 +38823,7 @@
         <v>46231.97938657407</v>
       </c>
       <c r="F532" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G532" s="0" t="s">
         <v>24</v>
@@ -38850,7 +38850,7 @@
         <v>25</v>
       </c>
       <c r="O532" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P532" s="0" t="s">
         <v>25</v>
@@ -38891,7 +38891,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F533" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G533" s="0" t="s">
         <v>28</v>
@@ -38959,7 +38959,7 @@
         <v>46215.346342592595</v>
       </c>
       <c r="F534" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G534" s="0" t="s">
         <v>28</v>
@@ -39027,7 +39027,7 @@
         <v>46231.97939814815</v>
       </c>
       <c r="F535" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G535" s="0" t="s">
         <v>24</v>
@@ -39054,7 +39054,7 @@
         <v>25</v>
       </c>
       <c r="O535" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P535" s="0" t="s">
         <v>25</v>
@@ -39095,7 +39095,7 @@
         <v>46208.34142361111</v>
       </c>
       <c r="F536" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G536" s="0" t="s">
         <v>28</v>
@@ -39163,7 +39163,7 @@
         <v>46184.34611111111</v>
       </c>
       <c r="F537" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G537" s="0" t="s">
         <v>24</v>
@@ -39231,7 +39231,7 @@
         <v>46207.44116898148</v>
       </c>
       <c r="F538" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G538" s="0" t="s">
         <v>28</v>
@@ -39299,7 +39299,7 @@
         <v>46217.771006944444</v>
       </c>
       <c r="F539" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G539" s="0" t="s">
         <v>24</v>
@@ -39367,7 +39367,7 @@
         <v>46227.807592592595</v>
       </c>
       <c r="F540" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G540" s="0" t="s">
         <v>33</v>
@@ -39435,7 +39435,7 @@
         <v>46218.360914351855</v>
       </c>
       <c r="F541" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G541" s="0" t="s">
         <v>24</v>
@@ -39503,7 +39503,7 @@
         <v>46217.77065972222</v>
       </c>
       <c r="F542" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G542" s="0" t="s">
         <v>24</v>
@@ -39571,7 +39571,7 @@
         <v>46213.12200231481</v>
       </c>
       <c r="F543" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G543" s="0" t="s">
         <v>33</v>
@@ -39639,7 +39639,7 @@
         <v>46231.75850694445</v>
       </c>
       <c r="F544" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G544" s="0" t="s">
         <v>33</v>
@@ -39707,7 +39707,7 @@
         <v>46228.24151620371</v>
       </c>
       <c r="F545" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G545" s="0" t="s">
         <v>33</v>
@@ -39775,7 +39775,7 @@
         <v>46230.25894675926</v>
       </c>
       <c r="F546" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G546" s="0" t="s">
         <v>33</v>
@@ -39843,7 +39843,7 @@
         <v>46221.0571875</v>
       </c>
       <c r="F547" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G547" s="0" t="s">
         <v>24</v>
@@ -39911,7 +39911,7 @@
         <v>46211.78650462963</v>
       </c>
       <c r="F548" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G548" s="0" t="s">
         <v>33</v>
@@ -39979,7 +39979,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F549" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G549" s="0" t="s">
         <v>28</v>
@@ -40047,7 +40047,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F550" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G550" s="0" t="s">
         <v>33</v>
@@ -40115,7 +40115,7 @@
         <v>46217.85449074074</v>
       </c>
       <c r="F551" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G551" s="0" t="s">
         <v>24</v>
@@ -40183,7 +40183,7 @@
         <v>46220.02423611111</v>
       </c>
       <c r="F552" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G552" s="0" t="s">
         <v>24</v>
@@ -40251,7 +40251,7 @@
         <v>46221.035358796296</v>
       </c>
       <c r="F553" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G553" s="0" t="s">
         <v>33</v>
@@ -40319,7 +40319,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F554" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G554" s="0" t="s">
         <v>28</v>
@@ -40387,7 +40387,7 @@
         <v>46235.03388888889</v>
       </c>
       <c r="F555" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G555" s="0" t="s">
         <v>33</v>
@@ -40455,7 +40455,7 @@
         <v>46222.006423611114</v>
       </c>
       <c r="F556" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G556" s="0" t="s">
         <v>24</v>
@@ -40523,7 +40523,7 @@
         <v>46225.40353009259</v>
       </c>
       <c r="F557" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G557" s="0" t="s">
         <v>24</v>
@@ -40591,7 +40591,7 @@
         <v>46205.74003472222</v>
       </c>
       <c r="F558" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G558" s="0" t="s">
         <v>28</v>
@@ -40609,7 +40609,7 @@
         <v>28</v>
       </c>
       <c r="L558" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M558" s="0" t="s">
         <v>25</v>
@@ -40629,8 +40629,8 @@
       <c r="R558" s="0">
         <v>1</v>
       </c>
-      <c r="S558" s="0" t="s">
-        <v>25</v>
+      <c r="S558" s="0">
+        <v>0</v>
       </c>
       <c r="T558" s="0" t="s">
         <v>25</v>
@@ -40659,7 +40659,7 @@
         <v>46223.341828703706</v>
       </c>
       <c r="F559" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G559" s="0" t="s">
         <v>33</v>
@@ -40727,7 +40727,7 @@
         <v>46231.97938657407</v>
       </c>
       <c r="F560" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G560" s="0" t="s">
         <v>24</v>
@@ -40754,7 +40754,7 @@
         <v>25</v>
       </c>
       <c r="O560" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P560" s="0" t="s">
         <v>25</v>
@@ -40795,7 +40795,7 @@
         <v>46213.61578703704</v>
       </c>
       <c r="F561" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G561" s="0" t="s">
         <v>28</v>
@@ -40863,7 +40863,7 @@
         <v>46214.6358912037</v>
       </c>
       <c r="F562" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G562" s="0" t="s">
         <v>33</v>
@@ -40931,7 +40931,7 @@
         <v>46199.06565972222</v>
       </c>
       <c r="F563" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G563" s="0" t="s">
         <v>24</v>
@@ -40999,7 +40999,7 @@
         <v>46221.08719907407</v>
       </c>
       <c r="F564" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G564" s="0" t="s">
         <v>24</v>
@@ -41067,7 +41067,7 @@
         <v>46229.6030787037</v>
       </c>
       <c r="F565" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G565" s="0" t="s">
         <v>33</v>
@@ -41076,7 +41076,7 @@
         <v>33</v>
       </c>
       <c r="I565" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J565" s="0" t="s">
         <v>25</v>
@@ -41096,8 +41096,8 @@
       <c r="O565" s="0">
         <v>0</v>
       </c>
-      <c r="P565" s="0" t="s">
-        <v>25</v>
+      <c r="P565" s="0">
+        <v>0</v>
       </c>
       <c r="Q565" s="0" t="s">
         <v>25</v>
@@ -41135,7 +41135,7 @@
         <v>46235.21309027778</v>
       </c>
       <c r="F566" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G566" s="0" t="s">
         <v>33</v>
@@ -41203,7 +41203,7 @@
         <v>46218.06217592592</v>
       </c>
       <c r="F567" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G567" s="0" t="s">
         <v>24</v>
@@ -41271,7 +41271,7 @@
         <v>46220.071921296294</v>
       </c>
       <c r="F568" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G568" s="0" t="s">
         <v>24</v>
@@ -41339,7 +41339,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F569" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G569" s="0" t="s">
         <v>28</v>
@@ -41407,7 +41407,7 @@
         <v>46220.00987268519</v>
       </c>
       <c r="F570" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G570" s="0" t="s">
         <v>24</v>
@@ -41475,7 +41475,7 @@
         <v>46222.05388888889</v>
       </c>
       <c r="F571" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G571" s="0" t="s">
         <v>33</v>
@@ -41490,7 +41490,7 @@
         <v>33</v>
       </c>
       <c r="K571" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L571" s="0" t="s">
         <v>25</v>
@@ -41510,8 +41510,8 @@
       <c r="Q571" s="0">
         <v>1</v>
       </c>
-      <c r="R571" s="0" t="s">
-        <v>25</v>
+      <c r="R571" s="0">
+        <v>0</v>
       </c>
       <c r="S571" s="0" t="s">
         <v>25</v>
@@ -41543,7 +41543,7 @@
         <v>46199.95371527778</v>
       </c>
       <c r="F572" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G572" s="0" t="s">
         <v>28</v>
@@ -41611,7 +41611,7 @@
         <v>46212.29601851852</v>
       </c>
       <c r="F573" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G573" s="0" t="s">
         <v>33</v>
@@ -41679,7 +41679,7 @@
         <v>46220.10313657407</v>
       </c>
       <c r="F574" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G574" s="0" t="s">
         <v>24</v>
@@ -41747,7 +41747,7 @@
         <v>46217.85451388889</v>
       </c>
       <c r="F575" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G575" s="0" t="s">
         <v>24</v>
@@ -41774,7 +41774,7 @@
         <v>25</v>
       </c>
       <c r="O575" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P575" s="0" t="s">
         <v>25</v>
@@ -41815,7 +41815,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F576" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G576" s="0" t="s">
         <v>24</v>
@@ -41883,7 +41883,7 @@
         <v>46220.014131944445</v>
       </c>
       <c r="F577" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G577" s="0" t="s">
         <v>24</v>
@@ -41951,7 +41951,7 @@
         <v>46231.979479166665</v>
       </c>
       <c r="F578" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G578" s="0" t="s">
         <v>24</v>
@@ -42019,7 +42019,7 @@
         <v>46215.09512731482</v>
       </c>
       <c r="F579" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G579" s="0" t="s">
         <v>33</v>
@@ -42087,7 +42087,7 @@
         <v>46231.979525462964</v>
       </c>
       <c r="F580" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G580" s="0" t="s">
         <v>24</v>
@@ -42155,7 +42155,7 @@
         <v>46203.39921296296</v>
       </c>
       <c r="F581" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G581" s="0" t="s">
         <v>24</v>
@@ -42173,7 +42173,7 @@
         <v>24</v>
       </c>
       <c r="L581" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M581" s="0" t="s">
         <v>25</v>
@@ -42193,8 +42193,8 @@
       <c r="R581" s="0">
         <v>1</v>
       </c>
-      <c r="S581" s="0" t="s">
-        <v>25</v>
+      <c r="S581" s="0">
+        <v>0</v>
       </c>
       <c r="T581" s="0" t="s">
         <v>25</v>
@@ -42223,7 +42223,7 @@
         <v>46218.373460648145</v>
       </c>
       <c r="F582" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G582" s="0" t="s">
         <v>24</v>
@@ -42291,7 +42291,7 @@
         <v>46206.91523148148</v>
       </c>
       <c r="F583" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G583" s="0" t="s">
         <v>24</v>
@@ -42359,7 +42359,7 @@
         <v>46213.618055555555</v>
       </c>
       <c r="F584" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G584" s="0" t="s">
         <v>24</v>
@@ -42427,7 +42427,7 @@
         <v>46213.61820601852</v>
       </c>
       <c r="F585" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G585" s="0" t="s">
         <v>24</v>
@@ -42495,7 +42495,7 @@
         <v>46216.794907407406</v>
       </c>
       <c r="F586" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G586" s="0" t="s">
         <v>24</v>
@@ -42563,7 +42563,7 @@
         <v>46217.85457175926</v>
       </c>
       <c r="F587" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G587" s="0" t="s">
         <v>24</v>
@@ -42631,7 +42631,7 @@
         <v>46199.06940972222</v>
       </c>
       <c r="F588" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G588" s="0" t="s">
         <v>24</v>
@@ -42649,7 +42649,7 @@
         <v>24</v>
       </c>
       <c r="L588" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M588" s="0" t="s">
         <v>25</v>
@@ -42669,8 +42669,8 @@
       <c r="R588" s="0">
         <v>1</v>
       </c>
-      <c r="S588" s="0" t="s">
-        <v>25</v>
+      <c r="S588" s="0">
+        <v>0</v>
       </c>
       <c r="T588" s="0" t="s">
         <v>25</v>
@@ -42699,7 +42699,7 @@
         <v>46220.09737268519</v>
       </c>
       <c r="F589" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G589" s="0" t="s">
         <v>24</v>
@@ -42767,7 +42767,7 @@
         <v>46212.73332175926</v>
       </c>
       <c r="F590" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G590" s="0" t="s">
         <v>33</v>
@@ -42835,7 +42835,7 @@
         <v>46221.07461805556</v>
       </c>
       <c r="F591" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G591" s="0" t="s">
         <v>24</v>
@@ -42903,7 +42903,7 @@
         <v>46218.88267361111</v>
       </c>
       <c r="F592" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G592" s="0" t="s">
         <v>24</v>
@@ -42971,7 +42971,7 @@
         <v>46221.197384259256</v>
       </c>
       <c r="F593" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G593" s="0" t="s">
         <v>24</v>
@@ -43039,7 +43039,7 @@
         <v>46220.21396990741</v>
       </c>
       <c r="F594" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G594" s="0" t="s">
         <v>33</v>
@@ -43107,7 +43107,7 @@
         <v>46233.22719907408</v>
       </c>
       <c r="F595" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G595" s="0" t="s">
         <v>24</v>
@@ -43134,7 +43134,7 @@
         <v>25</v>
       </c>
       <c r="O595" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P595" s="0" t="s">
         <v>25</v>
@@ -43175,7 +43175,7 @@
         <v>46212.47420138889</v>
       </c>
       <c r="F596" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G596" s="0" t="s">
         <v>24</v>
@@ -43243,7 +43243,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F597" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G597" s="0" t="s">
         <v>28</v>
@@ -43311,7 +43311,7 @@
         <v>46199.395949074074</v>
       </c>
       <c r="F598" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G598" s="0" t="s">
         <v>33</v>
@@ -43379,7 +43379,7 @@
         <v>46218.05547453704</v>
       </c>
       <c r="F599" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G599" s="0" t="s">
         <v>24</v>
@@ -43447,7 +43447,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F600" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G600" s="0" t="s">
         <v>28</v>
@@ -43515,7 +43515,7 @@
         <v>46220.12163194444</v>
       </c>
       <c r="F601" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G601" s="0" t="s">
         <v>24</v>
@@ -43583,7 +43583,7 @@
         <v>46184.34570601852</v>
       </c>
       <c r="F602" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G602" s="0" t="s">
         <v>24</v>
@@ -43651,7 +43651,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F603" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G603" s="0" t="s">
         <v>28</v>
@@ -43719,7 +43719,7 @@
         <v>46213.61800925926</v>
       </c>
       <c r="F604" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G604" s="0" t="s">
         <v>28</v>
@@ -43787,7 +43787,7 @@
         <v>46198.756527777776</v>
       </c>
       <c r="F605" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G605" s="0" t="s">
         <v>24</v>
@@ -43805,7 +43805,7 @@
         <v>24</v>
       </c>
       <c r="L605" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M605" s="0" t="s">
         <v>25</v>
@@ -43825,8 +43825,8 @@
       <c r="R605" s="0">
         <v>1</v>
       </c>
-      <c r="S605" s="0" t="s">
-        <v>25</v>
+      <c r="S605" s="0">
+        <v>0</v>
       </c>
       <c r="T605" s="0" t="s">
         <v>25</v>
@@ -43855,7 +43855,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F606" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G606" s="0" t="s">
         <v>28</v>
@@ -43923,7 +43923,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F607" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G607" s="0" t="s">
         <v>28</v>
@@ -43991,7 +43991,7 @@
         <v>46221.00100694445</v>
       </c>
       <c r="F608" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G608" s="0" t="s">
         <v>24</v>
@@ -44059,7 +44059,7 @@
         <v>46198.76427083334</v>
       </c>
       <c r="F609" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G609" s="0" t="s">
         <v>24</v>
@@ -44077,7 +44077,7 @@
         <v>24</v>
       </c>
       <c r="L609" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M609" s="0" t="s">
         <v>25</v>
@@ -44097,8 +44097,8 @@
       <c r="R609" s="0">
         <v>1</v>
       </c>
-      <c r="S609" s="0" t="s">
-        <v>25</v>
+      <c r="S609" s="0">
+        <v>0</v>
       </c>
       <c r="T609" s="0" t="s">
         <v>25</v>
@@ -44127,7 +44127,7 @@
         <v>46209.39717592593</v>
       </c>
       <c r="F610" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G610" s="0" t="s">
         <v>24</v>
@@ -44195,7 +44195,7 @@
         <v>46196.08101851852</v>
       </c>
       <c r="F611" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G611" s="0" t="s">
         <v>24</v>
@@ -44263,7 +44263,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F612" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G612" s="0" t="s">
         <v>28</v>
@@ -44331,7 +44331,7 @@
         <v>46207.28523148148</v>
       </c>
       <c r="F613" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G613" s="0" t="s">
         <v>24</v>
@@ -44399,7 +44399,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F614" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G614" s="0" t="s">
         <v>28</v>
@@ -44467,7 +44467,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F615" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G615" s="0" t="s">
         <v>28</v>
@@ -44535,7 +44535,7 @@
         <v>46220.87535879629</v>
       </c>
       <c r="F616" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G616" s="0" t="s">
         <v>24</v>
@@ -44603,7 +44603,7 @@
         <v>46233.56857638889</v>
       </c>
       <c r="F617" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G617" s="0" t="s">
         <v>33</v>
@@ -44671,7 +44671,7 @@
         <v>46221.05228009259</v>
       </c>
       <c r="F618" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G618" s="0" t="s">
         <v>24</v>
@@ -44739,7 +44739,7 @@
         <v>46223.64939814815</v>
       </c>
       <c r="F619" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G619" s="0" t="s">
         <v>33</v>
@@ -44807,7 +44807,7 @@
         <v>46196.788564814815</v>
       </c>
       <c r="F620" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G620" s="0" t="s">
         <v>24</v>
@@ -44825,7 +44825,7 @@
         <v>24</v>
       </c>
       <c r="L620" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M620" s="0" t="s">
         <v>25</v>
@@ -44845,8 +44845,8 @@
       <c r="R620" s="0">
         <v>1</v>
       </c>
-      <c r="S620" s="0" t="s">
-        <v>25</v>
+      <c r="S620" s="0">
+        <v>0</v>
       </c>
       <c r="T620" s="0" t="s">
         <v>25</v>
@@ -44875,7 +44875,7 @@
         <v>46217.99606481481</v>
       </c>
       <c r="F621" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G621" s="0" t="s">
         <v>33</v>
@@ -44943,7 +44943,7 @@
         <v>46217.72994212963</v>
       </c>
       <c r="F622" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G622" s="0" t="s">
         <v>24</v>
@@ -45011,7 +45011,7 @@
         <v>46200.45096064815</v>
       </c>
       <c r="F623" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G623" s="0" t="s">
         <v>28</v>
@@ -45079,7 +45079,7 @@
         <v>46213.44936342593</v>
       </c>
       <c r="F624" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G624" s="0" t="s">
         <v>33</v>
@@ -45147,7 +45147,7 @@
         <v>46222.98751157407</v>
       </c>
       <c r="F625" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G625" s="0" t="s">
         <v>24</v>
@@ -45215,7 +45215,7 @@
         <v>46221.228321759256</v>
       </c>
       <c r="F626" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G626" s="0" t="s">
         <v>24</v>
@@ -45283,7 +45283,7 @@
         <v>46207.18237268519</v>
       </c>
       <c r="F627" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G627" s="0" t="s">
         <v>24</v>
@@ -45301,7 +45301,7 @@
         <v>24</v>
       </c>
       <c r="L627" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M627" s="0" t="s">
         <v>25</v>
@@ -45321,8 +45321,8 @@
       <c r="R627" s="0">
         <v>1</v>
       </c>
-      <c r="S627" s="0" t="s">
-        <v>25</v>
+      <c r="S627" s="0">
+        <v>0</v>
       </c>
       <c r="T627" s="0" t="s">
         <v>25</v>
@@ -45351,7 +45351,7 @@
         <v>46220.24438657407</v>
       </c>
       <c r="F628" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G628" s="0" t="s">
         <v>33</v>
@@ -45419,7 +45419,7 @@
         <v>46198.89733796296</v>
       </c>
       <c r="F629" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G629" s="0" t="s">
         <v>33</v>
@@ -45487,7 +45487,7 @@
         <v>46213.282858796294</v>
       </c>
       <c r="F630" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G630" s="0" t="s">
         <v>33</v>
@@ -45555,7 +45555,7 @@
         <v>46225.61315972222</v>
       </c>
       <c r="F631" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G631" s="0" t="s">
         <v>33</v>
@@ -45588,7 +45588,7 @@
         <v>1</v>
       </c>
       <c r="Q631" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R631" s="0" t="s">
         <v>25</v>
@@ -45623,7 +45623,7 @@
         <v>46218.46706018518</v>
       </c>
       <c r="F632" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G632" s="0" t="s">
         <v>33</v>
@@ -45638,7 +45638,7 @@
         <v>33</v>
       </c>
       <c r="K632" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L632" s="0" t="s">
         <v>25</v>
@@ -45658,8 +45658,8 @@
       <c r="Q632" s="0">
         <v>0</v>
       </c>
-      <c r="R632" s="0" t="s">
-        <v>25</v>
+      <c r="R632" s="0">
+        <v>0</v>
       </c>
       <c r="S632" s="0" t="s">
         <v>25</v>
@@ -45691,7 +45691,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F633" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G633" s="0" t="s">
         <v>24</v>
@@ -45759,7 +45759,7 @@
         <v>46220.87540509259</v>
       </c>
       <c r="F634" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G634" s="0" t="s">
         <v>24</v>
@@ -45827,7 +45827,7 @@
         <v>46229.62666666666</v>
       </c>
       <c r="F635" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G635" s="0" t="s">
         <v>33</v>
@@ -45895,7 +45895,7 @@
         <v>46217.69572916667</v>
       </c>
       <c r="F636" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G636" s="0" t="s">
         <v>33</v>
@@ -45963,7 +45963,7 @@
         <v>46219.77547453704</v>
       </c>
       <c r="F637" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G637" s="0" t="s">
         <v>33</v>
@@ -46031,7 +46031,7 @@
         <v>46221.18212962963</v>
       </c>
       <c r="F638" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G638" s="0" t="s">
         <v>28</v>
@@ -46099,7 +46099,7 @@
         <v>46219.43380787037</v>
       </c>
       <c r="F639" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G639" s="0" t="s">
         <v>33</v>
@@ -46135,7 +46135,7 @@
         <v>0</v>
       </c>
       <c r="R639" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S639" s="0" t="s">
         <v>25</v>
@@ -46167,7 +46167,7 @@
         <v>46205.19603009259</v>
       </c>
       <c r="F640" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G640" s="0" t="s">
         <v>33</v>
@@ -46206,7 +46206,7 @@
         <v>1</v>
       </c>
       <c r="S640" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T640" s="0" t="s">
         <v>25</v>
@@ -46235,7 +46235,7 @@
         <v>46196.08101851852</v>
       </c>
       <c r="F641" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G641" s="0" t="s">
         <v>24</v>
@@ -46303,7 +46303,7 @@
         <v>46196.88885416667</v>
       </c>
       <c r="F642" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G642" s="0" t="s">
         <v>24</v>
@@ -46371,7 +46371,7 @@
         <v>46213.618055555555</v>
       </c>
       <c r="F643" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G643" s="0" t="s">
         <v>28</v>
@@ -46439,7 +46439,7 @@
         <v>46199.89765046296</v>
       </c>
       <c r="F644" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G644" s="0" t="s">
         <v>33</v>
@@ -46507,7 +46507,7 @@
         <v>46203.38673611111</v>
       </c>
       <c r="F645" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G645" s="0" t="s">
         <v>24</v>
@@ -46575,7 +46575,7 @@
         <v>46234.25630787037</v>
       </c>
       <c r="F646" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G646" s="0" t="s">
         <v>24</v>
@@ -46643,7 +46643,7 @@
         <v>46226.854050925926</v>
       </c>
       <c r="F647" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G647" s="0" t="s">
         <v>24</v>
@@ -46711,7 +46711,7 @@
         <v>46214.55940972222</v>
       </c>
       <c r="F648" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G648" s="0" t="s">
         <v>33</v>
@@ -46747,7 +46747,7 @@
         <v>0</v>
       </c>
       <c r="R648" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S648" s="0" t="s">
         <v>25</v>
@@ -46779,7 +46779,7 @@
         <v>46218.193761574075</v>
       </c>
       <c r="F649" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G649" s="0" t="s">
         <v>33</v>
@@ -46847,7 +46847,7 @@
         <v>46215.391805555555</v>
       </c>
       <c r="F650" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G650" s="0" t="s">
         <v>28</v>
@@ -46915,7 +46915,7 @@
         <v>46208.49730324074</v>
       </c>
       <c r="F651" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G651" s="0" t="s">
         <v>28</v>
@@ -46983,7 +46983,7 @@
         <v>46233.71238425926</v>
       </c>
       <c r="F652" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G652" s="0" t="s">
         <v>28</v>
@@ -47051,7 +47051,7 @@
         <v>46218.375763888886</v>
       </c>
       <c r="F653" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G653" s="0" t="s">
         <v>24</v>
@@ -47119,7 +47119,7 @@
         <v>46207.957766203705</v>
       </c>
       <c r="F654" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G654" s="0" t="s">
         <v>24</v>
@@ -47131,7 +47131,7 @@
         <v>24</v>
       </c>
       <c r="J654" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K654" s="0" t="s">
         <v>25</v>
@@ -47151,8 +47151,8 @@
       <c r="P654" s="0">
         <v>1</v>
       </c>
-      <c r="Q654" s="0" t="s">
-        <v>25</v>
+      <c r="Q654" s="0">
+        <v>0</v>
       </c>
       <c r="R654" s="0" t="s">
         <v>25</v>
@@ -47187,7 +47187,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F655" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G655" s="0" t="s">
         <v>24</v>
@@ -47255,7 +47255,7 @@
         <v>46223.20361111111</v>
       </c>
       <c r="F656" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G656" s="0" t="s">
         <v>33</v>
@@ -47288,7 +47288,7 @@
         <v>0</v>
       </c>
       <c r="Q656" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R656" s="0" t="s">
         <v>25</v>
@@ -47323,7 +47323,7 @@
         <v>46220.93790509259</v>
       </c>
       <c r="F657" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G657" s="0" t="s">
         <v>33</v>
@@ -47391,7 +47391,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F658" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G658" s="0" t="s">
         <v>24</v>
@@ -47459,7 +47459,7 @@
         <v>46232.40199074074</v>
       </c>
       <c r="F659" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G659" s="0" t="s">
         <v>24</v>
@@ -47527,7 +47527,7 @@
         <v>46205.35525462963</v>
       </c>
       <c r="F660" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G660" s="0" t="s">
         <v>33</v>
@@ -47566,7 +47566,7 @@
         <v>0</v>
       </c>
       <c r="S660" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T660" s="0" t="s">
         <v>25</v>
@@ -47595,7 +47595,7 @@
         <v>46200.595925925925</v>
       </c>
       <c r="F661" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G661" s="0" t="s">
         <v>24</v>
@@ -47663,7 +47663,7 @@
         <v>46198.36408564815</v>
       </c>
       <c r="F662" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G662" s="0" t="s">
         <v>33</v>
@@ -47731,7 +47731,7 @@
         <v>46213.61833333333</v>
       </c>
       <c r="F663" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G663" s="0" t="s">
         <v>28</v>
@@ -47799,7 +47799,7 @@
         <v>46221.210335648146</v>
       </c>
       <c r="F664" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G664" s="0" t="s">
         <v>24</v>
@@ -47867,7 +47867,7 @@
         <v>46213.61821759259</v>
       </c>
       <c r="F665" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G665" s="0" t="s">
         <v>28</v>
@@ -47935,7 +47935,7 @@
         <v>46220.05509259259</v>
       </c>
       <c r="F666" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G666" s="0" t="s">
         <v>24</v>
@@ -48003,7 +48003,7 @@
         <v>46232.4221875</v>
       </c>
       <c r="F667" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G667" s="0" t="s">
         <v>33</v>
@@ -48012,7 +48012,7 @@
         <v>33</v>
       </c>
       <c r="I667" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J667" s="0" t="s">
         <v>25</v>
@@ -48032,8 +48032,8 @@
       <c r="O667" s="0">
         <v>1</v>
       </c>
-      <c r="P667" s="0" t="s">
-        <v>25</v>
+      <c r="P667" s="0">
+        <v>0</v>
       </c>
       <c r="Q667" s="0" t="s">
         <v>25</v>
@@ -48071,7 +48071,7 @@
         <v>46214.184386574074</v>
       </c>
       <c r="F668" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G668" s="0" t="s">
         <v>33</v>
@@ -48139,7 +48139,7 @@
         <v>46208.95462962963</v>
       </c>
       <c r="F669" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G669" s="0" t="s">
         <v>28</v>
@@ -48207,7 +48207,7 @@
         <v>46231.97965277778</v>
       </c>
       <c r="F670" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G670" s="0" t="s">
         <v>24</v>
@@ -48275,7 +48275,7 @@
         <v>46217.85456018519</v>
       </c>
       <c r="F671" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G671" s="0" t="s">
         <v>24</v>
@@ -48343,7 +48343,7 @@
         <v>46209.34474537037</v>
       </c>
       <c r="F672" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G672" s="0" t="s">
         <v>33</v>
@@ -48411,7 +48411,7 @@
         <v>46203.6659375</v>
       </c>
       <c r="F673" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G673" s="0" t="s">
         <v>24</v>
@@ -48429,7 +48429,7 @@
         <v>24</v>
       </c>
       <c r="L673" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M673" s="0" t="s">
         <v>25</v>
@@ -48449,8 +48449,8 @@
       <c r="R673" s="0">
         <v>1</v>
       </c>
-      <c r="S673" s="0" t="s">
-        <v>25</v>
+      <c r="S673" s="0">
+        <v>0</v>
       </c>
       <c r="T673" s="0" t="s">
         <v>25</v>
@@ -48479,7 +48479,7 @@
         <v>46204.815416666665</v>
       </c>
       <c r="F674" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G674" s="0" t="s">
         <v>24</v>
@@ -48547,7 +48547,7 @@
         <v>46200.84137731481</v>
       </c>
       <c r="F675" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G675" s="0" t="s">
         <v>33</v>
@@ -48615,7 +48615,7 @@
         <v>46217.79622685185</v>
       </c>
       <c r="F676" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G676" s="0" t="s">
         <v>28</v>
@@ -48683,7 +48683,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F677" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G677" s="0" t="s">
         <v>24</v>
@@ -48751,7 +48751,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F678" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G678" s="0" t="s">
         <v>24</v>
@@ -48819,7 +48819,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F679" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G679" s="0" t="s">
         <v>24</v>
@@ -48887,7 +48887,7 @@
         <v>46207.322233796294</v>
       </c>
       <c r="F680" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G680" s="0" t="s">
         <v>33</v>
@@ -48905,7 +48905,7 @@
         <v>33</v>
       </c>
       <c r="L680" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M680" s="0" t="s">
         <v>25</v>
@@ -48925,8 +48925,8 @@
       <c r="R680" s="0">
         <v>1</v>
       </c>
-      <c r="S680" s="0" t="s">
-        <v>25</v>
+      <c r="S680" s="0">
+        <v>0</v>
       </c>
       <c r="T680" s="0" t="s">
         <v>25</v>
@@ -48955,7 +48955,7 @@
         <v>46221.022685185184</v>
       </c>
       <c r="F681" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G681" s="0" t="s">
         <v>24</v>
@@ -49023,7 +49023,7 @@
         <v>46203.665925925925</v>
       </c>
       <c r="F682" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G682" s="0" t="s">
         <v>24</v>
@@ -49041,7 +49041,7 @@
         <v>24</v>
       </c>
       <c r="L682" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M682" s="0" t="s">
         <v>25</v>
@@ -49061,8 +49061,8 @@
       <c r="R682" s="0">
         <v>1</v>
       </c>
-      <c r="S682" s="0" t="s">
-        <v>25</v>
+      <c r="S682" s="0">
+        <v>0</v>
       </c>
       <c r="T682" s="0" t="s">
         <v>25</v>
@@ -49091,7 +49091,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F683" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G683" s="0" t="s">
         <v>24</v>
@@ -49159,7 +49159,7 @@
         <v>46213.615798611114</v>
       </c>
       <c r="F684" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G684" s="0" t="s">
         <v>24</v>
@@ -49227,7 +49227,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F685" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G685" s="0" t="s">
         <v>24</v>
@@ -49295,7 +49295,7 @@
         <v>46221.094351851854</v>
       </c>
       <c r="F686" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G686" s="0" t="s">
         <v>24</v>
@@ -49363,7 +49363,7 @@
         <v>46229.55255787037</v>
       </c>
       <c r="F687" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G687" s="0" t="s">
         <v>28</v>
@@ -49431,7 +49431,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F688" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G688" s="0" t="s">
         <v>24</v>
@@ -49499,7 +49499,7 @@
         <v>46208.80619212963</v>
       </c>
       <c r="F689" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G689" s="0" t="s">
         <v>33</v>
@@ -49567,7 +49567,7 @@
         <v>46207.24060185185</v>
       </c>
       <c r="F690" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G690" s="0" t="s">
         <v>24</v>
@@ -49585,7 +49585,7 @@
         <v>28</v>
       </c>
       <c r="L690" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M690" s="0" t="s">
         <v>25</v>
@@ -49605,8 +49605,8 @@
       <c r="R690" s="0">
         <v>1</v>
       </c>
-      <c r="S690" s="0" t="s">
-        <v>25</v>
+      <c r="S690" s="0">
+        <v>1</v>
       </c>
       <c r="T690" s="0" t="s">
         <v>25</v>
@@ -49615,7 +49615,7 @@
         <v>25</v>
       </c>
       <c r="V690" s="0" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="691">
@@ -49635,7 +49635,7 @@
         <v>46225.759733796294</v>
       </c>
       <c r="F691" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G691" s="0" t="s">
         <v>33</v>
@@ -49703,7 +49703,7 @@
         <v>46221.116631944446</v>
       </c>
       <c r="F692" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G692" s="0" t="s">
         <v>24</v>
@@ -49771,7 +49771,7 @@
         <v>46227.287453703706</v>
       </c>
       <c r="F693" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G693" s="0" t="s">
         <v>33</v>
@@ -49783,7 +49783,7 @@
         <v>33</v>
       </c>
       <c r="J693" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K693" s="0" t="s">
         <v>25</v>
@@ -49803,8 +49803,8 @@
       <c r="P693" s="0">
         <v>1</v>
       </c>
-      <c r="Q693" s="0" t="s">
-        <v>25</v>
+      <c r="Q693" s="0">
+        <v>0</v>
       </c>
       <c r="R693" s="0" t="s">
         <v>25</v>
@@ -49839,7 +49839,7 @@
         <v>46213.36528935185</v>
       </c>
       <c r="F694" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G694" s="0" t="s">
         <v>28</v>
@@ -49907,7 +49907,7 @@
         <v>46220.030439814815</v>
       </c>
       <c r="F695" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G695" s="0" t="s">
         <v>24</v>
@@ -49975,7 +49975,7 @@
         <v>46221.020636574074</v>
       </c>
       <c r="F696" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G696" s="0" t="s">
         <v>24</v>
@@ -50043,7 +50043,7 @@
         <v>46202.50537037037</v>
       </c>
       <c r="F697" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G697" s="0" t="s">
         <v>33</v>
@@ -50111,7 +50111,7 @@
         <v>46217.3975</v>
       </c>
       <c r="F698" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G698" s="0" t="s">
         <v>24</v>
@@ -50179,7 +50179,7 @@
         <v>46221.20960648148</v>
       </c>
       <c r="F699" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G699" s="0" t="s">
         <v>24</v>
@@ -50247,7 +50247,7 @@
         <v>46196.08100694444</v>
       </c>
       <c r="F700" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G700" s="0" t="s">
         <v>28</v>
@@ -50315,7 +50315,7 @@
         <v>46218.41074074074</v>
       </c>
       <c r="F701" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G701" s="0" t="s">
         <v>24</v>
@@ -50383,7 +50383,7 @@
         <v>46217.770949074074</v>
       </c>
       <c r="F702" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G702" s="0" t="s">
         <v>24</v>
@@ -50451,7 +50451,7 @@
         <v>46213.61601851852</v>
       </c>
       <c r="F703" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G703" s="0" t="s">
         <v>24</v>
@@ -50519,7 +50519,7 @@
         <v>46200.24690972222</v>
       </c>
       <c r="F704" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G704" s="0" t="s">
         <v>28</v>
@@ -50587,7 +50587,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F705" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G705" s="0" t="s">
         <v>28</v>
@@ -50655,7 +50655,7 @@
         <v>46197.26045138889</v>
       </c>
       <c r="F706" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G706" s="0" t="s">
         <v>24</v>
@@ -50723,7 +50723,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F707" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G707" s="0" t="s">
         <v>28</v>
@@ -50791,7 +50791,7 @@
         <v>46200.39493055556</v>
       </c>
       <c r="F708" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G708" s="0" t="s">
         <v>24</v>
@@ -50859,7 +50859,7 @@
         <v>46200.50178240741</v>
       </c>
       <c r="F709" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G709" s="0" t="s">
         <v>33</v>
@@ -50927,7 +50927,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F710" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G710" s="0" t="s">
         <v>28</v>
@@ -50995,7 +50995,7 @@
         <v>46217.796273148146</v>
       </c>
       <c r="F711" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G711" s="0" t="s">
         <v>28</v>
@@ -51063,7 +51063,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F712" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G712" s="0" t="s">
         <v>24</v>
@@ -51131,7 +51131,7 @@
         <v>46221.14179398148</v>
       </c>
       <c r="F713" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G713" s="0" t="s">
         <v>24</v>
@@ -51199,7 +51199,7 @@
         <v>46223.340416666666</v>
       </c>
       <c r="F714" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G714" s="0" t="s">
         <v>33</v>
@@ -51267,7 +51267,7 @@
         <v>46226.398194444446</v>
       </c>
       <c r="F715" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G715" s="0" t="s">
         <v>24</v>
@@ -51297,7 +51297,7 @@
         <v>1</v>
       </c>
       <c r="P715" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q715" s="0" t="s">
         <v>25</v>
@@ -51335,7 +51335,7 @@
         <v>46222.22011574074</v>
       </c>
       <c r="F716" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G716" s="0" t="s">
         <v>33</v>
@@ -51350,7 +51350,7 @@
         <v>33</v>
       </c>
       <c r="K716" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L716" s="0" t="s">
         <v>25</v>
@@ -51370,8 +51370,8 @@
       <c r="Q716" s="0">
         <v>1</v>
       </c>
-      <c r="R716" s="0" t="s">
-        <v>25</v>
+      <c r="R716" s="0">
+        <v>0</v>
       </c>
       <c r="S716" s="0" t="s">
         <v>25</v>
@@ -51403,7 +51403,7 @@
         <v>46213.61583333334</v>
       </c>
       <c r="F717" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G717" s="0" t="s">
         <v>28</v>
@@ -51471,7 +51471,7 @@
         <v>46221.56353009259</v>
       </c>
       <c r="F718" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G718" s="0" t="s">
         <v>33</v>
@@ -51486,7 +51486,7 @@
         <v>33</v>
       </c>
       <c r="K718" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L718" s="0" t="s">
         <v>25</v>
@@ -51506,8 +51506,8 @@
       <c r="Q718" s="0">
         <v>1</v>
       </c>
-      <c r="R718" s="0" t="s">
-        <v>25</v>
+      <c r="R718" s="0">
+        <v>0</v>
       </c>
       <c r="S718" s="0" t="s">
         <v>25</v>
@@ -51539,7 +51539,7 @@
         <v>46217.79630787037</v>
       </c>
       <c r="F719" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G719" s="0" t="s">
         <v>28</v>
@@ -51607,7 +51607,7 @@
         <v>46201.81197916667</v>
       </c>
       <c r="F720" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G720" s="0" t="s">
         <v>33</v>
@@ -51675,7 +51675,7 @@
         <v>46196.87100694444</v>
       </c>
       <c r="F721" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G721" s="0" t="s">
         <v>33</v>
@@ -51743,7 +51743,7 @@
         <v>46221.06548611111</v>
       </c>
       <c r="F722" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G722" s="0" t="s">
         <v>28</v>
@@ -51811,7 +51811,7 @@
         <v>46221.181863425925</v>
       </c>
       <c r="F723" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G723" s="0" t="s">
         <v>24</v>
@@ -51879,7 +51879,7 @@
         <v>46217.07877314815</v>
       </c>
       <c r="F724" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G724" s="0" t="s">
         <v>33</v>
@@ -51947,7 +51947,7 @@
         <v>46223.367638888885</v>
       </c>
       <c r="F725" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G725" s="0" t="s">
         <v>33</v>
@@ -51980,7 +51980,7 @@
         <v>1</v>
       </c>
       <c r="Q725" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R725" s="0" t="s">
         <v>25</v>
@@ -52015,7 +52015,7 @@
         <v>46213.33634259259</v>
       </c>
       <c r="F726" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G726" s="0" t="s">
         <v>33</v>
@@ -52083,7 +52083,7 @@
         <v>46230.76193287037</v>
       </c>
       <c r="F727" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G727" s="0" t="s">
         <v>24</v>
@@ -52151,7 +52151,7 @@
         <v>46203.38674768519</v>
       </c>
       <c r="F728" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G728" s="0" t="s">
         <v>24</v>
@@ -52219,7 +52219,7 @@
         <v>46216.91412037037</v>
       </c>
       <c r="F729" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G729" s="0" t="s">
         <v>24</v>
@@ -52287,7 +52287,7 @@
         <v>46218.42864583333</v>
       </c>
       <c r="F730" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G730" s="0" t="s">
         <v>24</v>
@@ -52355,7 +52355,7 @@
         <v>46220.000231481485</v>
       </c>
       <c r="F731" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G731" s="0" t="s">
         <v>24</v>
@@ -52423,7 +52423,7 @@
         <v>46199.38827546296</v>
       </c>
       <c r="F732" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G732" s="0" t="s">
         <v>24</v>
@@ -52491,7 +52491,7 @@
         <v>46211.747569444444</v>
       </c>
       <c r="F733" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G733" s="0" t="s">
         <v>24</v>
@@ -52559,7 +52559,7 @@
         <v>46222.36450231481</v>
       </c>
       <c r="F734" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G734" s="0" t="s">
         <v>28</v>
@@ -52574,7 +52574,7 @@
         <v>28</v>
       </c>
       <c r="K734" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L734" s="0" t="s">
         <v>25</v>
@@ -52594,8 +52594,8 @@
       <c r="Q734" s="0">
         <v>1</v>
       </c>
-      <c r="R734" s="0" t="s">
-        <v>25</v>
+      <c r="R734" s="0">
+        <v>0</v>
       </c>
       <c r="S734" s="0" t="s">
         <v>25</v>
@@ -52627,7 +52627,7 @@
         <v>46220.06927083333</v>
       </c>
       <c r="F735" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G735" s="0" t="s">
         <v>24</v>
@@ -52695,7 +52695,7 @@
         <v>46223.80173611111</v>
       </c>
       <c r="F736" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G736" s="0" t="s">
         <v>28</v>
@@ -52763,7 +52763,7 @@
         <v>46213.61803240741</v>
       </c>
       <c r="F737" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G737" s="0" t="s">
         <v>28</v>
@@ -52831,7 +52831,7 @@
         <v>46213.27148148148</v>
       </c>
       <c r="F738" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G738" s="0" t="s">
         <v>33</v>
@@ -52843,7 +52843,7 @@
         <v>33</v>
       </c>
       <c r="J738" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K738" s="0" t="s">
         <v>25</v>
@@ -52863,8 +52863,8 @@
       <c r="P738" s="0">
         <v>1</v>
       </c>
-      <c r="Q738" s="0" t="s">
-        <v>25</v>
+      <c r="Q738" s="0">
+        <v>0</v>
       </c>
       <c r="R738" s="0" t="s">
         <v>25</v>
@@ -52899,7 +52899,7 @@
         <v>46231.97975694444</v>
       </c>
       <c r="F739" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G739" s="0" t="s">
         <v>24</v>
@@ -52926,7 +52926,7 @@
         <v>25</v>
       </c>
       <c r="O739" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P739" s="0" t="s">
         <v>25</v>
@@ -52967,7 +52967,7 @@
         <v>46229.19846064815</v>
       </c>
       <c r="F740" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G740" s="0" t="s">
         <v>33</v>
@@ -52997,7 +52997,7 @@
         <v>0</v>
       </c>
       <c r="P740" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q740" s="0" t="s">
         <v>25</v>
@@ -53035,7 +53035,7 @@
         <v>46217.79628472222</v>
       </c>
       <c r="F741" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G741" s="0" t="s">
         <v>28</v>
@@ -53103,7 +53103,7 @@
         <v>46214.036574074074</v>
       </c>
       <c r="F742" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G742" s="0" t="s">
         <v>24</v>
@@ -53171,7 +53171,7 @@
         <v>46198.75832175926</v>
       </c>
       <c r="F743" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G743" s="0" t="s">
         <v>24</v>
@@ -53189,7 +53189,7 @@
         <v>24</v>
       </c>
       <c r="L743" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M743" s="0" t="s">
         <v>25</v>
@@ -53209,8 +53209,8 @@
       <c r="R743" s="0">
         <v>1</v>
       </c>
-      <c r="S743" s="0" t="s">
-        <v>25</v>
+      <c r="S743" s="0">
+        <v>0</v>
       </c>
       <c r="T743" s="0" t="s">
         <v>25</v>
@@ -53239,7 +53239,7 @@
         <v>46213.1378125</v>
       </c>
       <c r="F744" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G744" s="0" t="s">
         <v>33</v>
@@ -53307,7 +53307,7 @@
         <v>46230.26619212963</v>
       </c>
       <c r="F745" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G745" s="0" t="s">
         <v>33</v>
@@ -53375,7 +53375,7 @@
         <v>46221.02222222222</v>
       </c>
       <c r="F746" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G746" s="0" t="s">
         <v>24</v>
@@ -53443,7 +53443,7 @@
         <v>46218.15008101852</v>
       </c>
       <c r="F747" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G747" s="0" t="s">
         <v>33</v>
@@ -53511,7 +53511,7 @@
         <v>46200.08666666667</v>
       </c>
       <c r="F748" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G748" s="0" t="s">
         <v>33</v>
@@ -53579,7 +53579,7 @@
         <v>46221.995520833334</v>
       </c>
       <c r="F749" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G749" s="0" t="s">
         <v>33</v>
@@ -53594,7 +53594,7 @@
         <v>33</v>
       </c>
       <c r="K749" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L749" s="0" t="s">
         <v>25</v>
@@ -53614,8 +53614,8 @@
       <c r="Q749" s="0">
         <v>0</v>
       </c>
-      <c r="R749" s="0" t="s">
-        <v>25</v>
+      <c r="R749" s="0">
+        <v>0</v>
       </c>
       <c r="S749" s="0" t="s">
         <v>25</v>
@@ -53647,7 +53647,7 @@
         <v>46191.20039351852</v>
       </c>
       <c r="F750" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G750" s="0" t="s">
         <v>24</v>
@@ -53715,7 +53715,7 @@
         <v>46223.899201388886</v>
       </c>
       <c r="F751" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G751" s="0" t="s">
         <v>24</v>
@@ -53783,7 +53783,7 @@
         <v>46221.16846064815</v>
       </c>
       <c r="F752" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G752" s="0" t="s">
         <v>24</v>
@@ -53851,7 +53851,7 @@
         <v>46217.79625</v>
       </c>
       <c r="F753" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G753" s="0" t="s">
         <v>28</v>
@@ -53919,7 +53919,7 @@
         <v>46224.472349537034</v>
       </c>
       <c r="F754" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G754" s="0" t="s">
         <v>33</v>
@@ -53987,7 +53987,7 @@
         <v>46198.06826388889</v>
       </c>
       <c r="F755" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G755" s="0" t="s">
         <v>24</v>
@@ -54005,7 +54005,7 @@
         <v>24</v>
       </c>
       <c r="L755" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M755" s="0" t="s">
         <v>25</v>
@@ -54025,8 +54025,8 @@
       <c r="R755" s="0">
         <v>1</v>
       </c>
-      <c r="S755" s="0" t="s">
-        <v>25</v>
+      <c r="S755" s="0">
+        <v>0</v>
       </c>
       <c r="T755" s="0" t="s">
         <v>25</v>
@@ -54055,7 +54055,7 @@
         <v>46217.7962962963</v>
       </c>
       <c r="F756" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G756" s="0" t="s">
         <v>24</v>
@@ -54123,7 +54123,7 @@
         <v>46197.6375462963</v>
       </c>
       <c r="F757" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G757" s="0" t="s">
         <v>24</v>
@@ -54191,7 +54191,7 @@
         <v>46197.037523148145</v>
       </c>
       <c r="F758" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G758" s="0" t="s">
         <v>24</v>
@@ -54259,7 +54259,7 @@
         <v>46198.31060185185</v>
       </c>
       <c r="F759" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G759" s="0" t="s">
         <v>33</v>
@@ -54327,7 +54327,7 @@
         <v>46221.100636574076</v>
       </c>
       <c r="F760" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G760" s="0" t="s">
         <v>24</v>
@@ -54395,7 +54395,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F761" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G761" s="0" t="s">
         <v>24</v>
@@ -54463,7 +54463,7 @@
         <v>46209.31466435185</v>
       </c>
       <c r="F762" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G762" s="0" t="s">
         <v>33</v>
@@ -54531,7 +54531,7 @@
         <v>46206.72038194445</v>
       </c>
       <c r="F763" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G763" s="0" t="s">
         <v>33</v>
@@ -54549,7 +54549,7 @@
         <v>33</v>
       </c>
       <c r="L763" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M763" s="0" t="s">
         <v>25</v>
@@ -54569,8 +54569,8 @@
       <c r="R763" s="0">
         <v>1</v>
       </c>
-      <c r="S763" s="0" t="s">
-        <v>25</v>
+      <c r="S763" s="0">
+        <v>0</v>
       </c>
       <c r="T763" s="0" t="s">
         <v>25</v>
@@ -54599,7 +54599,7 @@
         <v>46234.299629629626</v>
       </c>
       <c r="F764" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G764" s="0" t="s">
         <v>33</v>
@@ -54667,7 +54667,7 @@
         <v>46197.46810185185</v>
       </c>
       <c r="F765" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G765" s="0" t="s">
         <v>24</v>
@@ -54735,7 +54735,7 @@
         <v>46221.68960648148</v>
       </c>
       <c r="F766" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G766" s="0" t="s">
         <v>33</v>
@@ -54803,7 +54803,7 @@
         <v>46217.79634259259</v>
       </c>
       <c r="F767" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G767" s="0" t="s">
         <v>28</v>
@@ -54871,7 +54871,7 @@
         <v>46202.349328703705</v>
       </c>
       <c r="F768" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G768" s="0" t="s">
         <v>33</v>
@@ -54939,7 +54939,7 @@
         <v>46213.61802083333</v>
       </c>
       <c r="F769" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G769" s="0" t="s">
         <v>28</v>
@@ -55007,7 +55007,7 @@
         <v>46221.16261574074</v>
       </c>
       <c r="F770" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G770" s="0" t="s">
         <v>24</v>
@@ -55075,7 +55075,7 @@
         <v>46220.67443287037</v>
       </c>
       <c r="F771" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G771" s="0" t="s">
         <v>33</v>
@@ -55143,7 +55143,7 @@
         <v>46235.37511574074</v>
       </c>
       <c r="F772" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G772" s="0" t="s">
         <v>33</v>
@@ -55211,7 +55211,7 @@
         <v>46217.73019675926</v>
       </c>
       <c r="F773" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G773" s="0" t="s">
         <v>24</v>
@@ -55279,7 +55279,7 @@
         <v>46217.796331018515</v>
       </c>
       <c r="F774" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G774" s="0" t="s">
         <v>24</v>
@@ -55347,7 +55347,7 @@
         <v>46216.25659722222</v>
       </c>
       <c r="F775" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G775" s="0" t="s">
         <v>33</v>
@@ -55415,7 +55415,7 @@
         <v>46198.75665509259</v>
       </c>
       <c r="F776" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G776" s="0" t="s">
         <v>24</v>
@@ -55433,7 +55433,7 @@
         <v>24</v>
       </c>
       <c r="L776" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M776" s="0" t="s">
         <v>25</v>
@@ -55453,8 +55453,8 @@
       <c r="R776" s="0">
         <v>1</v>
       </c>
-      <c r="S776" s="0" t="s">
-        <v>25</v>
+      <c r="S776" s="0">
+        <v>0</v>
       </c>
       <c r="T776" s="0" t="s">
         <v>25</v>
@@ -55483,7 +55483,7 @@
         <v>46217.796319444446</v>
       </c>
       <c r="F777" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G777" s="0" t="s">
         <v>28</v>
@@ -55551,7 +55551,7 @@
         <v>46225.76219907407</v>
       </c>
       <c r="F778" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G778" s="0" t="s">
         <v>33</v>
@@ -55563,7 +55563,7 @@
         <v>33</v>
       </c>
       <c r="J778" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K778" s="0" t="s">
         <v>25</v>
@@ -55583,8 +55583,8 @@
       <c r="P778" s="0">
         <v>0</v>
       </c>
-      <c r="Q778" s="0" t="s">
-        <v>25</v>
+      <c r="Q778" s="0">
+        <v>0</v>
       </c>
       <c r="R778" s="0" t="s">
         <v>25</v>
@@ -55619,7 +55619,7 @@
         <v>46205.784363425926</v>
       </c>
       <c r="F779" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G779" s="0" t="s">
         <v>28</v>
@@ -55637,7 +55637,7 @@
         <v>28</v>
       </c>
       <c r="L779" s="0" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M779" s="0" t="s">
         <v>25</v>
@@ -55657,8 +55657,8 @@
       <c r="R779" s="0">
         <v>1</v>
       </c>
-      <c r="S779" s="0" t="s">
-        <v>25</v>
+      <c r="S779" s="0">
+        <v>0</v>
       </c>
       <c r="T779" s="0" t="s">
         <v>25</v>
@@ -55687,7 +55687,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F780" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G780" s="0" t="s">
         <v>24</v>
@@ -55755,7 +55755,7 @@
         <v>46204.81548611111</v>
       </c>
       <c r="F781" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G781" s="0" t="s">
         <v>24</v>
@@ -55823,7 +55823,7 @@
         <v>46198.75827546296</v>
       </c>
       <c r="F782" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G782" s="0" t="s">
         <v>24</v>
@@ -55841,7 +55841,7 @@
         <v>24</v>
       </c>
       <c r="L782" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M782" s="0" t="s">
         <v>25</v>
@@ -55861,8 +55861,8 @@
       <c r="R782" s="0">
         <v>1</v>
       </c>
-      <c r="S782" s="0" t="s">
-        <v>25</v>
+      <c r="S782" s="0">
+        <v>0</v>
       </c>
       <c r="T782" s="0" t="s">
         <v>25</v>
@@ -55891,7 +55891,7 @@
         <v>46231.97190972222</v>
       </c>
       <c r="F783" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G783" s="0" t="s">
         <v>24</v>
@@ -55918,7 +55918,7 @@
         <v>25</v>
       </c>
       <c r="O783" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P783" s="0" t="s">
         <v>25</v>
@@ -55959,7 +55959,7 @@
         <v>46203.80048611111</v>
       </c>
       <c r="F784" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G784" s="0" t="s">
         <v>28</v>
@@ -56027,7 +56027,7 @@
         <v>46222.2834375</v>
       </c>
       <c r="F785" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G785" s="0" t="s">
         <v>33</v>
@@ -56095,7 +56095,7 @@
         <v>46231.398831018516</v>
       </c>
       <c r="F786" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G786" s="0" t="s">
         <v>24</v>
@@ -56163,7 +56163,7 @@
         <v>46216.914131944446</v>
       </c>
       <c r="F787" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G787" s="0" t="s">
         <v>24</v>
@@ -56231,7 +56231,7 @@
         <v>46213.61585648148</v>
       </c>
       <c r="F788" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G788" s="0" t="s">
         <v>28</v>
@@ -56299,7 +56299,7 @@
         <v>46217.854837962965</v>
       </c>
       <c r="F789" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G789" s="0" t="s">
         <v>28</v>
@@ -56367,7 +56367,7 @@
         <v>46207.377118055556</v>
       </c>
       <c r="F790" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G790" s="0" t="s">
         <v>33</v>
@@ -56385,7 +56385,7 @@
         <v>33</v>
       </c>
       <c r="L790" s="0" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M790" s="0" t="s">
         <v>25</v>
@@ -56405,8 +56405,8 @@
       <c r="R790" s="0">
         <v>1</v>
       </c>
-      <c r="S790" s="0" t="s">
-        <v>25</v>
+      <c r="S790" s="0">
+        <v>0</v>
       </c>
       <c r="T790" s="0" t="s">
         <v>25</v>
@@ -56435,7 +56435,7 @@
         <v>46213.61584490741</v>
       </c>
       <c r="F791" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G791" s="0" t="s">
         <v>28</v>
@@ -56503,7 +56503,7 @@
         <v>46226.854050925926</v>
       </c>
       <c r="F792" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G792" s="0" t="s">
         <v>24</v>
@@ -56571,7 +56571,7 @@
         <v>46217.62388888889</v>
       </c>
       <c r="F793" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G793" s="0" t="s">
         <v>28</v>
@@ -56639,7 +56639,7 @@
         <v>46217.79623842592</v>
       </c>
       <c r="F794" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G794" s="0" t="s">
         <v>28</v>
@@ -56707,7 +56707,7 @@
         <v>46216.91412037037</v>
       </c>
       <c r="F795" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G795" s="0" t="s">
         <v>24</v>
@@ -56775,7 +56775,7 @@
         <v>46222.00664351852</v>
       </c>
       <c r="F796" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G796" s="0" t="s">
         <v>24</v>
@@ -56787,7 +56787,7 @@
         <v>24</v>
       </c>
       <c r="J796" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K796" s="0" t="s">
         <v>25</v>
@@ -56807,8 +56807,8 @@
       <c r="P796" s="0">
         <v>1</v>
       </c>
-      <c r="Q796" s="0" t="s">
-        <v>25</v>
+      <c r="Q796" s="0">
+        <v>0</v>
       </c>
       <c r="R796" s="0" t="s">
         <v>25</v>
@@ -56843,7 +56843,7 @@
         <v>46220.02006944444</v>
       </c>
       <c r="F797" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G797" s="0" t="s">
         <v>24</v>
@@ -56911,7 +56911,7 @@
         <v>46220.11394675926</v>
       </c>
       <c r="F798" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G798" s="0" t="s">
         <v>24</v>
@@ -56979,7 +56979,7 @@
         <v>46219.039131944446</v>
       </c>
       <c r="F799" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G799" s="0" t="s">
         <v>24</v>
@@ -57047,7 +57047,7 @@
         <v>46198.76320601852</v>
       </c>
       <c r="F800" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G800" s="0" t="s">
         <v>24</v>
@@ -57065,7 +57065,7 @@
         <v>24</v>
       </c>
       <c r="L800" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M800" s="0" t="s">
         <v>25</v>
@@ -57085,8 +57085,8 @@
       <c r="R800" s="0">
         <v>1</v>
       </c>
-      <c r="S800" s="0" t="s">
-        <v>25</v>
+      <c r="S800" s="0">
+        <v>0</v>
       </c>
       <c r="T800" s="0" t="s">
         <v>25</v>
@@ -57115,7 +57115,7 @@
         <v>46234.25630787037</v>
       </c>
       <c r="F801" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G801" s="0" t="s">
         <v>24</v>
@@ -57183,7 +57183,7 @@
         <v>46224.96215277778</v>
       </c>
       <c r="F802" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G802" s="0" t="s">
         <v>28</v>
@@ -57216,7 +57216,7 @@
         <v>1</v>
       </c>
       <c r="Q802" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R802" s="0" t="s">
         <v>25</v>
@@ -57251,7 +57251,7 @@
         <v>46209.364849537036</v>
       </c>
       <c r="F803" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G803" s="0" t="s">
         <v>28</v>
@@ -57319,7 +57319,7 @@
         <v>46217.85474537037</v>
       </c>
       <c r="F804" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G804" s="0" t="s">
         <v>24</v>
@@ -57387,7 +57387,7 @@
         <v>46210.49642361111</v>
       </c>
       <c r="F805" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G805" s="0" t="s">
         <v>28</v>
@@ -57455,7 +57455,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F806" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G806" s="0" t="s">
         <v>28</v>
@@ -57523,7 +57523,7 @@
         <v>46218.668599537035</v>
       </c>
       <c r="F807" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G807" s="0" t="s">
         <v>33</v>
@@ -57591,7 +57591,7 @@
         <v>46230.345046296294</v>
       </c>
       <c r="F808" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G808" s="0" t="s">
         <v>28</v>
@@ -57621,7 +57621,7 @@
         <v>1</v>
       </c>
       <c r="P808" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q808" s="0" t="s">
         <v>25</v>
@@ -57659,7 +57659,7 @@
         <v>46198.76327546296</v>
       </c>
       <c r="F809" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G809" s="0" t="s">
         <v>24</v>
@@ -57677,7 +57677,7 @@
         <v>24</v>
       </c>
       <c r="L809" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M809" s="0" t="s">
         <v>25</v>
@@ -57697,8 +57697,8 @@
       <c r="R809" s="0">
         <v>1</v>
       </c>
-      <c r="S809" s="0" t="s">
-        <v>25</v>
+      <c r="S809" s="0">
+        <v>0</v>
       </c>
       <c r="T809" s="0" t="s">
         <v>25</v>
@@ -57727,7 +57727,7 @@
         <v>46213.61584490741</v>
       </c>
       <c r="F810" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G810" s="0" t="s">
         <v>24</v>
@@ -57795,7 +57795,7 @@
         <v>46197.041238425925</v>
       </c>
       <c r="F811" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G811" s="0" t="s">
         <v>24</v>
@@ -57863,7 +57863,7 @@
         <v>46212.017488425925</v>
       </c>
       <c r="F812" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G812" s="0" t="s">
         <v>28</v>
@@ -57931,7 +57931,7 @@
         <v>46213.61585648148</v>
       </c>
       <c r="F813" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G813" s="0" t="s">
         <v>24</v>
@@ -57999,7 +57999,7 @@
         <v>46204.81549768519</v>
       </c>
       <c r="F814" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G814" s="0" t="s">
         <v>24</v>
@@ -58067,7 +58067,7 @@
         <v>46213.61832175926</v>
       </c>
       <c r="F815" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G815" s="0" t="s">
         <v>24</v>
@@ -58135,7 +58135,7 @@
         <v>46200.44310185185</v>
       </c>
       <c r="F816" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G816" s="0" t="s">
         <v>24</v>
@@ -58203,7 +58203,7 @@
         <v>46217.796261574076</v>
       </c>
       <c r="F817" s="1">
-        <v>46236.0424375</v>
+        <v>46237.04255648148</v>
       </c>
       <c r="G817" s="0" t="s">
         <v>24</v>
